--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Slate" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Bet Log" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Team Profiles" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Model Comparison" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Slate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bet Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Profiles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Comparison" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3569,6 +3569,11 @@
         <f>IF(I29="","",I29-#REF!)</f>
         <v/>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L29" s="11">
         <f>IF(K29="W",IF(G29&lt;0,H29*100/ABS(G29),H29*G29/100),IF(K29="L",-H29,0))</f>
         <v/>
@@ -3615,6 +3620,11 @@
         <f>IF(I30="","",I30-#REF!)</f>
         <v/>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L30" s="11">
         <f>IF(K30="W",IF(G30&lt;0,H30*100/ABS(G30),H30*G30/100),IF(K30="L",-H30,0))</f>
         <v/>
@@ -3658,6 +3668,11 @@
         <f>IF(I31="","",I31-#REF!)</f>
         <v/>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L31" s="11">
         <f>IF(K31="W",IF(G31&lt;0,H31*100/ABS(G31),H31*G31/100),IF(K31="L",-H31,0))</f>
         <v/>
@@ -3701,6 +3716,11 @@
         <f>IF(I32="","",I32-#REF!)</f>
         <v/>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L32" s="11">
         <f>IF(K32="W",IF(G32&lt;0,H32*100/ABS(G32),H32*G32/100),IF(K32="L",-H32,0))</f>
         <v/>
@@ -3711,7 +3731,44 @@
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Maryland @ Uconn</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Uconn</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
       <c r="J33" s="6" t="n"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L33" s="11">
         <f>IF(K33="W",IF(G33&lt;0,H33*100/ABS(G33),H33*G33/100),IF(K33="L",-H33,0))</f>
         <v/>
@@ -3722,9 +3779,43 @@
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ohio State @ Texas</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>500</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40</v>
+      </c>
       <c r="J34" s="6">
         <f>IF(I34="","",I34-F34)</f>
         <v/>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
       </c>
       <c r="L34" s="11">
         <f>IF(K34="W",IF(G34&lt;0,H34*100/ABS(G34),H34*G34/100),IF(K34="L",-H34,0))</f>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Slate" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bet Log" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Profiles" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Comparison" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Slate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Bet Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Team Profiles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Model Comparison" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -118,8 +118,36 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -153,8 +181,23 @@
         <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -201,11 +244,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -231,6 +288,15 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -881,28 +947,28 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNLV</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Central Michigan</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-3.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G2" s="6">
         <f>F2-E2</f>
@@ -913,10 +979,10 @@
         <v/>
       </c>
       <c r="I2" t="n">
-        <v>63.2</v>
+        <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>56.8</v>
+        <v>39.5</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -939,25 +1005,28 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Northern Colorado</t>
+          <t>UTEP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-17.1</v>
+        <v>-29.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-36.5</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -968,7 +1037,10 @@
         <v/>
       </c>
       <c r="I3" t="n">
-        <v>55.2</v>
+        <v>46.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>49.5</v>
       </c>
       <c r="K3" s="6">
         <f>I3-J3</f>
@@ -989,25 +1061,28 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mercyhurst</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Middle Tennessee</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-17.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.5</v>
       </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
@@ -1018,7 +1093,10 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>54.1</v>
+        <v>63.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49.5</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -1039,25 +1117,28 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Illinois State</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Northern Illinois</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-16</v>
+        <v>-10.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-23.5</v>
       </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
@@ -1068,7 +1149,10 @@
         <v/>
       </c>
       <c r="I5" t="n">
-        <v>54.9</v>
+        <v>45.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>48.5</v>
       </c>
       <c r="K5" s="6">
         <f>I5-J5</f>
@@ -1094,25 +1178,28 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Texas Southern</t>
+          <t>North Dakota State</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UTEP</t>
+          <t>Sacramento State</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-16.1</v>
+        <v>35.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.5</v>
       </c>
       <c r="G6" s="6">
         <f>F6-E6</f>
@@ -1123,7 +1210,10 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>55.2</v>
+        <v>43.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>53.5</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -1149,27 +1239,29 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Cal Poly</t>
+          <t>Northern Illinois</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>San José State</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-21</v>
-      </c>
-      <c r="F7" s="10" t="n"/>
+        <v>-30.9</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>-35.5</v>
+      </c>
       <c r="G7" s="10">
         <f>F7-E7</f>
         <v/>
@@ -1179,9 +1271,11 @@
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="J7" s="10" t="n"/>
+        <v>33.2</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K7" s="10">
         <f>I7-J7</f>
         <v/>
@@ -1206,28 +1300,28 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Dakota State</t>
+          <t>Fresno State</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Air Force</t>
+          <t>San José State</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.9</v>
+        <v>1.2</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G8" s="6">
         <f>F8-E8</f>
@@ -1238,10 +1332,10 @@
         <v/>
       </c>
       <c r="I8" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
-        <v>47.2</v>
+        <v>52.5</v>
       </c>
       <c r="K8" s="6">
         <f>I8-J8</f>
@@ -1266,30 +1360,6 @@
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Montana State</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nevada</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>-17.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="G9" s="6">
         <f>F9-E9</f>
         <v/>
@@ -1298,12 +1368,6 @@
         <f>IF(G9=0,"Pick'em",IF(G9&gt;0,"Home","Away"))</f>
         <v/>
       </c>
-      <c r="I9" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>49.5</v>
-      </c>
       <c r="K9" s="6">
         <f>I9-J9</f>
         <v/>
@@ -1327,30 +1391,6 @@
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>New Mexico State</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hawai'i</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-7.5</v>
-      </c>
       <c r="G10" s="6">
         <f>F10-E10</f>
         <v/>
@@ -1358,12 +1398,6 @@
       <c r="H10" s="6">
         <f>IF(G10=0,"Pick'em",IF(G10&gt;0,"Home","Away"))</f>
         <v/>
-      </c>
-      <c r="I10" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>49.8</v>
       </c>
       <c r="K10" s="6">
         <f>I10-J10</f>
@@ -2119,7 +2153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2336,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="6">
-        <f>IF(I4="","",I4-F5)</f>
+        <f>IF(I4="","",I4-F4)</f>
         <v/>
       </c>
       <c r="K4" t="inlineStr">
@@ -2384,7 +2418,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="6">
-        <f>IF(I5="","",I5-#REF!)</f>
+        <f>IF(I5="","",I5-F5)</f>
         <v/>
       </c>
       <c r="K5" t="inlineStr">
@@ -2689,6 +2723,10 @@
       <c r="H11" t="n">
         <v>2</v>
       </c>
+      <c r="J11" s="6">
+        <f>IF(I11="","",I11-F11)</f>
+        <v/>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>W</t>
@@ -2736,6 +2774,10 @@
       <c r="H12" t="n">
         <v>3</v>
       </c>
+      <c r="J12" s="6">
+        <f>IF(I12="","",I12-F12)</f>
+        <v/>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>W</t>
@@ -2780,6 +2822,10 @@
       <c r="H13" t="n">
         <v>1</v>
       </c>
+      <c r="J13" s="6">
+        <f>IF(I13="","",I13-F13)</f>
+        <v/>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>L</t>
@@ -2827,6 +2873,10 @@
       <c r="H14" t="n">
         <v>3</v>
       </c>
+      <c r="J14" s="6">
+        <f>IF(I14="","",I14-F14)</f>
+        <v/>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>W</t>
@@ -2874,6 +2924,10 @@
       <c r="H15" t="n">
         <v>3</v>
       </c>
+      <c r="J15" s="6">
+        <f>IF(I15="","",I15-F15)</f>
+        <v/>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>W</t>
@@ -3024,7 +3078,7 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="6">
-        <f>IF(I18="","",I18-F29)</f>
+        <f>IF(I18="","",I18-F18)</f>
         <v/>
       </c>
       <c r="K18" t="inlineStr">
@@ -3033,7 +3087,7 @@
         </is>
       </c>
       <c r="L18" s="11">
-        <f>IF(K18="W",IF(G29&lt;0,H29*100/ABS(G29),H29*G29/100),IF(K18="L",-H29,0))</f>
+        <f>IF(K18="W",IF(G18&lt;0,H18*100/ABS(G18),H18*G18/100),IF(K18="L",-H18,0))</f>
         <v/>
       </c>
       <c r="M18" s="11">
@@ -3072,7 +3126,7 @@
         <v>11.5</v>
       </c>
       <c r="J19" s="6">
-        <f>IF(I19="","",I19-F30)</f>
+        <f>IF(I19="","",I19-F19)</f>
         <v/>
       </c>
       <c r="K19" t="inlineStr">
@@ -3081,7 +3135,7 @@
         </is>
       </c>
       <c r="L19" s="11">
-        <f>IF(K19="W",IF(G30&lt;0,H30*100/ABS(G30),H30*G30/100),IF(K19="L",-H30,0))</f>
+        <f>IF(K19="W",IF(G19&lt;0,H19*100/ABS(G19),H19*G19/100),IF(K19="L",-H19,0))</f>
         <v/>
       </c>
       <c r="M19" s="11">
@@ -3123,7 +3177,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="6">
-        <f>IF(I20="","",I20-F31)</f>
+        <f>IF(I20="","",I20-F20)</f>
         <v/>
       </c>
       <c r="K20" t="inlineStr">
@@ -3132,7 +3186,7 @@
         </is>
       </c>
       <c r="L20" s="11">
-        <f>IF(K20="W",IF(G31&lt;0,H31*100/ABS(G31),H31*G31/100),IF(K20="L",-H31,0))</f>
+        <f>IF(K20="W",IF(G20&lt;0,H20*100/ABS(G20),H20*G20/100),IF(K20="L",-H20,0))</f>
         <v/>
       </c>
       <c r="M20" s="11">
@@ -3171,7 +3225,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="6">
-        <f>IF(I21="","",I21-F32)</f>
+        <f>IF(I21="","",I21-F21)</f>
         <v/>
       </c>
       <c r="K21" t="inlineStr">
@@ -3180,7 +3234,7 @@
         </is>
       </c>
       <c r="L21" s="11">
-        <f>IF(K21="W",IF(G32&lt;0,H32*100/ABS(G32),H32*G32/100),IF(K21="L",-H32,0))</f>
+        <f>IF(K21="W",IF(G21&lt;0,H21*100/ABS(G21),H21*G21/100),IF(K21="L",-H21,0))</f>
         <v/>
       </c>
       <c r="M21" s="11">
@@ -3222,7 +3276,7 @@
         <v>2.5</v>
       </c>
       <c r="J22" s="6">
-        <f>IF(I22="","",I22-F33)</f>
+        <f>IF(I22="","",I22-F22)</f>
         <v/>
       </c>
       <c r="K22" t="inlineStr">
@@ -3231,7 +3285,7 @@
         </is>
       </c>
       <c r="L22" s="11">
-        <f>IF(K22="W",IF(G33&lt;0,H33*100/ABS(G33),H33*G33/100),IF(K22="L",-H33,0))</f>
+        <f>IF(K22="W",IF(G22&lt;0,H22*100/ABS(G22),H22*G22/100),IF(K22="L",-H22,0))</f>
         <v/>
       </c>
       <c r="M22" s="11">
@@ -3515,7 +3569,7 @@
         <v>2</v>
       </c>
       <c r="J28" s="6">
-        <f>IF(I28="","",I28-#REF!)</f>
+        <f>IF(I28="","",I28-F28)</f>
         <v/>
       </c>
       <c r="K28" t="inlineStr">
@@ -3565,8 +3619,11 @@
       <c r="H29" t="n">
         <v>1</v>
       </c>
+      <c r="I29" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J29" s="6">
-        <f>IF(I29="","",I29-#REF!)</f>
+        <f>IF(I29="","",I29-F29)</f>
         <v/>
       </c>
       <c r="K29" t="inlineStr">
@@ -3616,8 +3673,11 @@
       <c r="H30" t="n">
         <v>2.5</v>
       </c>
+      <c r="I30" t="n">
+        <v>2.5</v>
+      </c>
       <c r="J30" s="6">
-        <f>IF(I30="","",I30-#REF!)</f>
+        <f>IF(I30="","",I30-F30)</f>
         <v/>
       </c>
       <c r="K30" t="inlineStr">
@@ -3665,7 +3725,7 @@
         <v>2.5</v>
       </c>
       <c r="J31" s="6">
-        <f>IF(I31="","",I31-#REF!)</f>
+        <f>IF(I31="","",I31-F31)</f>
         <v/>
       </c>
       <c r="K31" t="inlineStr">
@@ -3713,7 +3773,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="6">
-        <f>IF(I32="","",I32-#REF!)</f>
+        <f>IF(I32="","",I32-F32)</f>
         <v/>
       </c>
       <c r="K32" t="inlineStr">
@@ -3755,7 +3815,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="G33" t="n">
         <v>-110</v>
@@ -3763,7 +3823,13 @@
       <c r="H33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n"/>
+      <c r="I33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J33" s="6">
+        <f>IF(I33="","",I33-F33)</f>
+        <v/>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>L</t>
@@ -3841,6 +3907,10 @@
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
+      <c r="J36" s="6">
+        <f>IF(I36="","",I36-F36)</f>
+        <v/>
+      </c>
       <c r="L36" s="11">
         <f>IF(K36="W",IF(G36&lt;0,H36*100/ABS(G36),H36*G36/100),IF(K36="L",-H36,0))</f>
         <v/>
@@ -3851,6 +3921,10 @@
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
+      <c r="J37" s="6">
+        <f>IF(I37="","",I37-F37)</f>
+        <v/>
+      </c>
       <c r="L37" s="11">
         <f>IF(K37="W",IF(G37&lt;0,H37*100/ABS(G37),H37*G37/100),IF(K37="L",-H37,0))</f>
         <v/>
@@ -3861,6 +3935,10 @@
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
+      <c r="J38" s="6">
+        <f>IF(I38="","",I38-F38)</f>
+        <v/>
+      </c>
       <c r="L38" s="11">
         <f>IF(K38="W",IF(G38&lt;0,H38*100/ABS(G38),H38*G38/100),IF(K38="L",-H38,0))</f>
         <v/>
@@ -3871,6 +3949,10 @@
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
+      <c r="J39" s="6">
+        <f>IF(I39="","",I39-F39)</f>
+        <v/>
+      </c>
       <c r="L39" s="11">
         <f>IF(K39="W",IF(G39&lt;0,H39*100/ABS(G39),H39*G39/100),IF(K39="L",-H39,0))</f>
         <v/>
@@ -3881,6 +3963,10 @@
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
+      <c r="J40" s="6">
+        <f>IF(I40="","",I40-F40)</f>
+        <v/>
+      </c>
       <c r="L40" s="11">
         <f>IF(K40="W",IF(G40&lt;0,H40*100/ABS(G40),H40*G40/100),IF(K40="L",-H40,0))</f>
         <v/>
@@ -3891,6 +3977,10 @@
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
+      <c r="J41" s="6">
+        <f>IF(I41="","",I41-F41)</f>
+        <v/>
+      </c>
       <c r="L41" s="11">
         <f>IF(K41="W",IF(G41&lt;0,H41*100/ABS(G41),H41*G41/100),IF(K41="L",-H41,0))</f>
         <v/>
@@ -3900,11 +3990,1241 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="J42" s="6">
+        <f>IF(I42="","",I42-F42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="11">
+        <f>IF(K42="W",IF(G42&lt;0,H42*100/ABS(G42),H42*G42/100),IF(K42="L",-H42,0))</f>
+        <v/>
+      </c>
+      <c r="M42" s="11">
+        <f>Settings!$B$4+SUM(L$2:L42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="J43" s="6">
+        <f>IF(I43="","",I43-F43)</f>
+        <v/>
+      </c>
+      <c r="L43" s="11">
+        <f>IF(K43="W",IF(G43&lt;0,H43*100/ABS(G43),H43*G43/100),IF(K43="L",-H43,0))</f>
+        <v/>
+      </c>
+      <c r="M43" s="11">
+        <f>Settings!$B$4+SUM(L$2:L43)</f>
+        <v/>
+      </c>
+    </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="J44" s="6">
+        <f>IF(I44="","",I44-F44)</f>
+        <v/>
+      </c>
+      <c r="L44" s="11">
+        <f>IF(K44="W",IF(G44&lt;0,H44*100/ABS(G44),H44*G44/100),IF(K44="L",-H44,0))</f>
+        <v/>
+      </c>
+      <c r="M44" s="11">
+        <f>Settings!$B$4+SUM(L$2:L44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="L45" s="11">
+        <f>IF(K45="W",IF(G45&lt;0,H45*100/ABS(G45),H45*G45/100),IF(K45="L",-H45,0))</f>
+        <v/>
+      </c>
+      <c r="M45" s="11">
+        <f>Settings!$B$4+SUM(L$2:L45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="L46" s="11">
+        <f>IF(K46="W",IF(G46&lt;0,H46*100/ABS(G46),H46*G46/100),IF(K46="L",-H46,0))</f>
+        <v/>
+      </c>
+      <c r="M46" s="11">
+        <f>Settings!$B$4+SUM(L$2:L46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="L47" s="11">
+        <f>IF(K47="W",IF(G47&lt;0,H47*100/ABS(G47),H47*G47/100),IF(K47="L",-H47,0))</f>
+        <v/>
+      </c>
+      <c r="M47" s="11">
+        <f>Settings!$B$4+SUM(L$2:L47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="L48" s="11">
+        <f>IF(K48="W",IF(G48&lt;0,H48*100/ABS(G48),H48*G48/100),IF(K48="L",-H48,0))</f>
+        <v/>
+      </c>
+      <c r="M48" s="11">
+        <f>Settings!$B$4+SUM(L$2:L48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="L49" s="11">
+        <f>IF(K49="W",IF(G49&lt;0,H49*100/ABS(G49),H49*G49/100),IF(K49="L",-H49,0))</f>
+        <v/>
+      </c>
+      <c r="M49" s="11">
+        <f>Settings!$B$4+SUM(L$2:L49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="L50" s="11">
+        <f>IF(K50="W",IF(G50&lt;0,H50*100/ABS(G50),H50*G50/100),IF(K50="L",-H50,0))</f>
+        <v/>
+      </c>
+      <c r="M50" s="11">
+        <f>Settings!$B$4+SUM(L$2:L50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="L51" s="11">
+        <f>IF(K51="W",IF(G51&lt;0,H51*100/ABS(G51),H51*G51/100),IF(K51="L",-H51,0))</f>
+        <v/>
+      </c>
+      <c r="M51" s="11">
+        <f>Settings!$B$4+SUM(L$2:L51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="L52" s="11">
+        <f>IF(K52="W",IF(G52&lt;0,H52*100/ABS(G52),H52*G52/100),IF(K52="L",-H52,0))</f>
+        <v/>
+      </c>
+      <c r="M52" s="11">
+        <f>Settings!$B$4+SUM(L$2:L52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="L53" s="11">
+        <f>IF(K53="W",IF(G53&lt;0,H53*100/ABS(G53),H53*G53/100),IF(K53="L",-H53,0))</f>
+        <v/>
+      </c>
+      <c r="M53" s="11">
+        <f>Settings!$B$4+SUM(L$2:L53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="L54" s="11">
+        <f>IF(K54="W",IF(G54&lt;0,H54*100/ABS(G54),H54*G54/100),IF(K54="L",-H54,0))</f>
+        <v/>
+      </c>
+      <c r="M54" s="11">
+        <f>Settings!$B$4+SUM(L$2:L54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="L55" s="11">
+        <f>IF(K55="W",IF(G55&lt;0,H55*100/ABS(G55),H55*G55/100),IF(K55="L",-H55,0))</f>
+        <v/>
+      </c>
+      <c r="M55" s="11">
+        <f>Settings!$B$4+SUM(L$2:L55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="L56" s="11">
+        <f>IF(K56="W",IF(G56&lt;0,H56*100/ABS(G56),H56*G56/100),IF(K56="L",-H56,0))</f>
+        <v/>
+      </c>
+      <c r="M56" s="11">
+        <f>Settings!$B$4+SUM(L$2:L56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="L57" s="11">
+        <f>IF(K57="W",IF(G57&lt;0,H57*100/ABS(G57),H57*G57/100),IF(K57="L",-H57,0))</f>
+        <v/>
+      </c>
+      <c r="M57" s="11">
+        <f>Settings!$B$4+SUM(L$2:L57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="L58" s="11">
+        <f>IF(K58="W",IF(G58&lt;0,H58*100/ABS(G58),H58*G58/100),IF(K58="L",-H58,0))</f>
+        <v/>
+      </c>
+      <c r="M58" s="11">
+        <f>Settings!$B$4+SUM(L$2:L58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="L59" s="11">
+        <f>IF(K59="W",IF(G59&lt;0,H59*100/ABS(G59),H59*G59/100),IF(K59="L",-H59,0))</f>
+        <v/>
+      </c>
+      <c r="M59" s="11">
+        <f>Settings!$B$4+SUM(L$2:L59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="L60" s="11">
+        <f>IF(K60="W",IF(G60&lt;0,H60*100/ABS(G60),H60*G60/100),IF(K60="L",-H60,0))</f>
+        <v/>
+      </c>
+      <c r="M60" s="11">
+        <f>Settings!$B$4+SUM(L$2:L60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="L61" s="11">
+        <f>IF(K61="W",IF(G61&lt;0,H61*100/ABS(G61),H61*G61/100),IF(K61="L",-H61,0))</f>
+        <v/>
+      </c>
+      <c r="M61" s="11">
+        <f>Settings!$B$4+SUM(L$2:L61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>CLV note: Closing Line - Line Taken. For a favorite (negative number), a less-negative closing line than what you bet means the market moved toward you -- positive CLV. Read each row in context of which side you took.</t>
         </is>
+      </c>
+      <c r="L62" s="11">
+        <f>IF(K62="W",IF(G62&lt;0,H62*100/ABS(G62),H62*G62/100),IF(K62="L",-H62,0))</f>
+        <v/>
+      </c>
+      <c r="M62" s="11">
+        <f>Settings!$B$4+SUM(L$2:L62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="L63" s="11">
+        <f>IF(K63="W",IF(G63&lt;0,H63*100/ABS(G63),H63*G63/100),IF(K63="L",-H63,0))</f>
+        <v/>
+      </c>
+      <c r="M63" s="11">
+        <f>Settings!$B$4+SUM(L$2:L63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="L64" s="11">
+        <f>IF(K64="W",IF(G64&lt;0,H64*100/ABS(G64),H64*G64/100),IF(K64="L",-H64,0))</f>
+        <v/>
+      </c>
+      <c r="M64" s="11">
+        <f>Settings!$B$4+SUM(L$2:L64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="L65" s="11">
+        <f>IF(K65="W",IF(G65&lt;0,H65*100/ABS(G65),H65*G65/100),IF(K65="L",-H65,0))</f>
+        <v/>
+      </c>
+      <c r="M65" s="11">
+        <f>Settings!$B$4+SUM(L$2:L65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="L66" s="11">
+        <f>IF(K66="W",IF(G66&lt;0,H66*100/ABS(G66),H66*G66/100),IF(K66="L",-H66,0))</f>
+        <v/>
+      </c>
+      <c r="M66" s="11">
+        <f>Settings!$B$4+SUM(L$2:L66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="L67" s="11">
+        <f>IF(K67="W",IF(G67&lt;0,H67*100/ABS(G67),H67*G67/100),IF(K67="L",-H67,0))</f>
+        <v/>
+      </c>
+      <c r="M67" s="11">
+        <f>Settings!$B$4+SUM(L$2:L67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="L68" s="11">
+        <f>IF(K68="W",IF(G68&lt;0,H68*100/ABS(G68),H68*G68/100),IF(K68="L",-H68,0))</f>
+        <v/>
+      </c>
+      <c r="M68" s="11">
+        <f>Settings!$B$4+SUM(L$2:L68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="L69" s="11">
+        <f>IF(K69="W",IF(G69&lt;0,H69*100/ABS(G69),H69*G69/100),IF(K69="L",-H69,0))</f>
+        <v/>
+      </c>
+      <c r="M69" s="11">
+        <f>Settings!$B$4+SUM(L$2:L69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="L70" s="11">
+        <f>IF(K70="W",IF(G70&lt;0,H70*100/ABS(G70),H70*G70/100),IF(K70="L",-H70,0))</f>
+        <v/>
+      </c>
+      <c r="M70" s="11">
+        <f>Settings!$B$4+SUM(L$2:L70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="L71" s="11">
+        <f>IF(K71="W",IF(G71&lt;0,H71*100/ABS(G71),H71*G71/100),IF(K71="L",-H71,0))</f>
+        <v/>
+      </c>
+      <c r="M71" s="11">
+        <f>Settings!$B$4+SUM(L$2:L71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="L72" s="11">
+        <f>IF(K72="W",IF(G72&lt;0,H72*100/ABS(G72),H72*G72/100),IF(K72="L",-H72,0))</f>
+        <v/>
+      </c>
+      <c r="M72" s="11">
+        <f>Settings!$B$4+SUM(L$2:L72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="L73" s="11">
+        <f>IF(K73="W",IF(G73&lt;0,H73*100/ABS(G73),H73*G73/100),IF(K73="L",-H73,0))</f>
+        <v/>
+      </c>
+      <c r="M73" s="11">
+        <f>Settings!$B$4+SUM(L$2:L73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="L74" s="11">
+        <f>IF(K74="W",IF(G74&lt;0,H74*100/ABS(G74),H74*G74/100),IF(K74="L",-H74,0))</f>
+        <v/>
+      </c>
+      <c r="M74" s="11">
+        <f>Settings!$B$4+SUM(L$2:L74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="L75" s="11">
+        <f>IF(K75="W",IF(G75&lt;0,H75*100/ABS(G75),H75*G75/100),IF(K75="L",-H75,0))</f>
+        <v/>
+      </c>
+      <c r="M75" s="11">
+        <f>Settings!$B$4+SUM(L$2:L75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="L76" s="11">
+        <f>IF(K76="W",IF(G76&lt;0,H76*100/ABS(G76),H76*G76/100),IF(K76="L",-H76,0))</f>
+        <v/>
+      </c>
+      <c r="M76" s="11">
+        <f>Settings!$B$4+SUM(L$2:L76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="L77" s="11">
+        <f>IF(K77="W",IF(G77&lt;0,H77*100/ABS(G77),H77*G77/100),IF(K77="L",-H77,0))</f>
+        <v/>
+      </c>
+      <c r="M77" s="11">
+        <f>Settings!$B$4+SUM(L$2:L77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="L78" s="11">
+        <f>IF(K78="W",IF(G78&lt;0,H78*100/ABS(G78),H78*G78/100),IF(K78="L",-H78,0))</f>
+        <v/>
+      </c>
+      <c r="M78" s="11">
+        <f>Settings!$B$4+SUM(L$2:L78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="L79" s="11">
+        <f>IF(K79="W",IF(G79&lt;0,H79*100/ABS(G79),H79*G79/100),IF(K79="L",-H79,0))</f>
+        <v/>
+      </c>
+      <c r="M79" s="11">
+        <f>Settings!$B$4+SUM(L$2:L79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="L80" s="11">
+        <f>IF(K80="W",IF(G80&lt;0,H80*100/ABS(G80),H80*G80/100),IF(K80="L",-H80,0))</f>
+        <v/>
+      </c>
+      <c r="M80" s="11">
+        <f>Settings!$B$4+SUM(L$2:L80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="L81" s="11">
+        <f>IF(K81="W",IF(G81&lt;0,H81*100/ABS(G81),H81*G81/100),IF(K81="L",-H81,0))</f>
+        <v/>
+      </c>
+      <c r="M81" s="11">
+        <f>Settings!$B$4+SUM(L$2:L81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="L82" s="11">
+        <f>IF(K82="W",IF(G82&lt;0,H82*100/ABS(G82),H82*G82/100),IF(K82="L",-H82,0))</f>
+        <v/>
+      </c>
+      <c r="M82" s="11">
+        <f>Settings!$B$4+SUM(L$2:L82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="L83" s="11">
+        <f>IF(K83="W",IF(G83&lt;0,H83*100/ABS(G83),H83*G83/100),IF(K83="L",-H83,0))</f>
+        <v/>
+      </c>
+      <c r="M83" s="11">
+        <f>Settings!$B$4+SUM(L$2:L83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="L84" s="11">
+        <f>IF(K84="W",IF(G84&lt;0,H84*100/ABS(G84),H84*G84/100),IF(K84="L",-H84,0))</f>
+        <v/>
+      </c>
+      <c r="M84" s="11">
+        <f>Settings!$B$4+SUM(L$2:L84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="L85" s="11">
+        <f>IF(K85="W",IF(G85&lt;0,H85*100/ABS(G85),H85*G85/100),IF(K85="L",-H85,0))</f>
+        <v/>
+      </c>
+      <c r="M85" s="11">
+        <f>Settings!$B$4+SUM(L$2:L85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="L86" s="11">
+        <f>IF(K86="W",IF(G86&lt;0,H86*100/ABS(G86),H86*G86/100),IF(K86="L",-H86,0))</f>
+        <v/>
+      </c>
+      <c r="M86" s="11">
+        <f>Settings!$B$4+SUM(L$2:L86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="L87" s="11">
+        <f>IF(K87="W",IF(G87&lt;0,H87*100/ABS(G87),H87*G87/100),IF(K87="L",-H87,0))</f>
+        <v/>
+      </c>
+      <c r="M87" s="11">
+        <f>Settings!$B$4+SUM(L$2:L87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="L88" s="11">
+        <f>IF(K88="W",IF(G88&lt;0,H88*100/ABS(G88),H88*G88/100),IF(K88="L",-H88,0))</f>
+        <v/>
+      </c>
+      <c r="M88" s="11">
+        <f>Settings!$B$4+SUM(L$2:L88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="L89" s="11">
+        <f>IF(K89="W",IF(G89&lt;0,H89*100/ABS(G89),H89*G89/100),IF(K89="L",-H89,0))</f>
+        <v/>
+      </c>
+      <c r="M89" s="11">
+        <f>Settings!$B$4+SUM(L$2:L89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="L90" s="11">
+        <f>IF(K90="W",IF(G90&lt;0,H90*100/ABS(G90),H90*G90/100),IF(K90="L",-H90,0))</f>
+        <v/>
+      </c>
+      <c r="M90" s="11">
+        <f>Settings!$B$4+SUM(L$2:L90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="L91" s="11">
+        <f>IF(K91="W",IF(G91&lt;0,H91*100/ABS(G91),H91*G91/100),IF(K91="L",-H91,0))</f>
+        <v/>
+      </c>
+      <c r="M91" s="11">
+        <f>Settings!$B$4+SUM(L$2:L91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="L92" s="11">
+        <f>IF(K92="W",IF(G92&lt;0,H92*100/ABS(G92),H92*G92/100),IF(K92="L",-H92,0))</f>
+        <v/>
+      </c>
+      <c r="M92" s="11">
+        <f>Settings!$B$4+SUM(L$2:L92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="L93" s="11">
+        <f>IF(K93="W",IF(G93&lt;0,H93*100/ABS(G93),H93*G93/100),IF(K93="L",-H93,0))</f>
+        <v/>
+      </c>
+      <c r="M93" s="11">
+        <f>Settings!$B$4+SUM(L$2:L93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="L94" s="11">
+        <f>IF(K94="W",IF(G94&lt;0,H94*100/ABS(G94),H94*G94/100),IF(K94="L",-H94,0))</f>
+        <v/>
+      </c>
+      <c r="M94" s="11">
+        <f>Settings!$B$4+SUM(L$2:L94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="L95" s="11">
+        <f>IF(K95="W",IF(G95&lt;0,H95*100/ABS(G95),H95*G95/100),IF(K95="L",-H95,0))</f>
+        <v/>
+      </c>
+      <c r="M95" s="11">
+        <f>Settings!$B$4+SUM(L$2:L95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="L96" s="11">
+        <f>IF(K96="W",IF(G96&lt;0,H96*100/ABS(G96),H96*G96/100),IF(K96="L",-H96,0))</f>
+        <v/>
+      </c>
+      <c r="M96" s="11">
+        <f>Settings!$B$4+SUM(L$2:L96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="L97" s="11">
+        <f>IF(K97="W",IF(G97&lt;0,H97*100/ABS(G97),H97*G97/100),IF(K97="L",-H97,0))</f>
+        <v/>
+      </c>
+      <c r="M97" s="11">
+        <f>Settings!$B$4+SUM(L$2:L97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="L98" s="11">
+        <f>IF(K98="W",IF(G98&lt;0,H98*100/ABS(G98),H98*G98/100),IF(K98="L",-H98,0))</f>
+        <v/>
+      </c>
+      <c r="M98" s="11">
+        <f>Settings!$B$4+SUM(L$2:L98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="L99" s="11">
+        <f>IF(K99="W",IF(G99&lt;0,H99*100/ABS(G99),H99*G99/100),IF(K99="L",-H99,0))</f>
+        <v/>
+      </c>
+      <c r="M99" s="11">
+        <f>Settings!$B$4+SUM(L$2:L99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="L100" s="11">
+        <f>IF(K100="W",IF(G100&lt;0,H100*100/ABS(G100),H100*G100/100),IF(K100="L",-H100,0))</f>
+        <v/>
+      </c>
+      <c r="M100" s="11">
+        <f>Settings!$B$4+SUM(L$2:L100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="L101" s="11">
+        <f>IF(K101="W",IF(G101&lt;0,H101*100/ABS(G101),H101*G101/100),IF(K101="L",-H101,0))</f>
+        <v/>
+      </c>
+      <c r="M101" s="11">
+        <f>Settings!$B$4+SUM(L$2:L101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="L102" s="11">
+        <f>IF(K102="W",IF(G102&lt;0,H102*100/ABS(G102),H102*G102/100),IF(K102="L",-H102,0))</f>
+        <v/>
+      </c>
+      <c r="M102" s="11">
+        <f>Settings!$B$4+SUM(L$2:L102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="L103" s="11">
+        <f>IF(K103="W",IF(G103&lt;0,H103*100/ABS(G103),H103*G103/100),IF(K103="L",-H103,0))</f>
+        <v/>
+      </c>
+      <c r="M103" s="11">
+        <f>Settings!$B$4+SUM(L$2:L103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="L104" s="11">
+        <f>IF(K104="W",IF(G104&lt;0,H104*100/ABS(G104),H104*G104/100),IF(K104="L",-H104,0))</f>
+        <v/>
+      </c>
+      <c r="M104" s="11">
+        <f>Settings!$B$4+SUM(L$2:L104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="L105" s="11">
+        <f>IF(K105="W",IF(G105&lt;0,H105*100/ABS(G105),H105*G105/100),IF(K105="L",-H105,0))</f>
+        <v/>
+      </c>
+      <c r="M105" s="11">
+        <f>Settings!$B$4+SUM(L$2:L105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="L106" s="11">
+        <f>IF(K106="W",IF(G106&lt;0,H106*100/ABS(G106),H106*G106/100),IF(K106="L",-H106,0))</f>
+        <v/>
+      </c>
+      <c r="M106" s="11">
+        <f>Settings!$B$4+SUM(L$2:L106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="L107" s="11">
+        <f>IF(K107="W",IF(G107&lt;0,H107*100/ABS(G107),H107*G107/100),IF(K107="L",-H107,0))</f>
+        <v/>
+      </c>
+      <c r="M107" s="11">
+        <f>Settings!$B$4+SUM(L$2:L107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="L108" s="11">
+        <f>IF(K108="W",IF(G108&lt;0,H108*100/ABS(G108),H108*G108/100),IF(K108="L",-H108,0))</f>
+        <v/>
+      </c>
+      <c r="M108" s="11">
+        <f>Settings!$B$4+SUM(L$2:L108)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="L109" s="11">
+        <f>IF(K109="W",IF(G109&lt;0,H109*100/ABS(G109),H109*G109/100),IF(K109="L",-H109,0))</f>
+        <v/>
+      </c>
+      <c r="M109" s="11">
+        <f>Settings!$B$4+SUM(L$2:L109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="L110" s="11">
+        <f>IF(K110="W",IF(G110&lt;0,H110*100/ABS(G110),H110*G110/100),IF(K110="L",-H110,0))</f>
+        <v/>
+      </c>
+      <c r="M110" s="11">
+        <f>Settings!$B$4+SUM(L$2:L110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="L111" s="11">
+        <f>IF(K111="W",IF(G111&lt;0,H111*100/ABS(G111),H111*G111/100),IF(K111="L",-H111,0))</f>
+        <v/>
+      </c>
+      <c r="M111" s="11">
+        <f>Settings!$B$4+SUM(L$2:L111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="L112" s="11">
+        <f>IF(K112="W",IF(G112&lt;0,H112*100/ABS(G112),H112*G112/100),IF(K112="L",-H112,0))</f>
+        <v/>
+      </c>
+      <c r="M112" s="11">
+        <f>Settings!$B$4+SUM(L$2:L112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="L113" s="11">
+        <f>IF(K113="W",IF(G113&lt;0,H113*100/ABS(G113),H113*G113/100),IF(K113="L",-H113,0))</f>
+        <v/>
+      </c>
+      <c r="M113" s="11">
+        <f>Settings!$B$4+SUM(L$2:L113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="L114" s="11">
+        <f>IF(K114="W",IF(G114&lt;0,H114*100/ABS(G114),H114*G114/100),IF(K114="L",-H114,0))</f>
+        <v/>
+      </c>
+      <c r="M114" s="11">
+        <f>Settings!$B$4+SUM(L$2:L114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="L115" s="11">
+        <f>IF(K115="W",IF(G115&lt;0,H115*100/ABS(G115),H115*G115/100),IF(K115="L",-H115,0))</f>
+        <v/>
+      </c>
+      <c r="M115" s="11">
+        <f>Settings!$B$4+SUM(L$2:L115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="L116" s="11">
+        <f>IF(K116="W",IF(G116&lt;0,H116*100/ABS(G116),H116*G116/100),IF(K116="L",-H116,0))</f>
+        <v/>
+      </c>
+      <c r="M116" s="11">
+        <f>Settings!$B$4+SUM(L$2:L116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="L117" s="11">
+        <f>IF(K117="W",IF(G117&lt;0,H117*100/ABS(G117),H117*G117/100),IF(K117="L",-H117,0))</f>
+        <v/>
+      </c>
+      <c r="M117" s="11">
+        <f>Settings!$B$4+SUM(L$2:L117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="L118" s="11">
+        <f>IF(K118="W",IF(G118&lt;0,H118*100/ABS(G118),H118*G118/100),IF(K118="L",-H118,0))</f>
+        <v/>
+      </c>
+      <c r="M118" s="11">
+        <f>Settings!$B$4+SUM(L$2:L118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="L119" s="11">
+        <f>IF(K119="W",IF(G119&lt;0,H119*100/ABS(G119),H119*G119/100),IF(K119="L",-H119,0))</f>
+        <v/>
+      </c>
+      <c r="M119" s="11">
+        <f>Settings!$B$4+SUM(L$2:L119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="L120" s="11">
+        <f>IF(K120="W",IF(G120&lt;0,H120*100/ABS(G120),H120*G120/100),IF(K120="L",-H120,0))</f>
+        <v/>
+      </c>
+      <c r="M120" s="11">
+        <f>Settings!$B$4+SUM(L$2:L120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="L121" s="11">
+        <f>IF(K121="W",IF(G121&lt;0,H121*100/ABS(G121),H121*G121/100),IF(K121="L",-H121,0))</f>
+        <v/>
+      </c>
+      <c r="M121" s="11">
+        <f>Settings!$B$4+SUM(L$2:L121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="L122" s="11">
+        <f>IF(K122="W",IF(G122&lt;0,H122*100/ABS(G122),H122*G122/100),IF(K122="L",-H122,0))</f>
+        <v/>
+      </c>
+      <c r="M122" s="11">
+        <f>Settings!$B$4+SUM(L$2:L122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="L123" s="11">
+        <f>IF(K123="W",IF(G123&lt;0,H123*100/ABS(G123),H123*G123/100),IF(K123="L",-H123,0))</f>
+        <v/>
+      </c>
+      <c r="M123" s="11">
+        <f>Settings!$B$4+SUM(L$2:L123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="L124" s="11">
+        <f>IF(K124="W",IF(G124&lt;0,H124*100/ABS(G124),H124*G124/100),IF(K124="L",-H124,0))</f>
+        <v/>
+      </c>
+      <c r="M124" s="11">
+        <f>Settings!$B$4+SUM(L$2:L124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="L125" s="11">
+        <f>IF(K125="W",IF(G125&lt;0,H125*100/ABS(G125),H125*G125/100),IF(K125="L",-H125,0))</f>
+        <v/>
+      </c>
+      <c r="M125" s="11">
+        <f>Settings!$B$4+SUM(L$2:L125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="L126" s="11">
+        <f>IF(K126="W",IF(G126&lt;0,H126*100/ABS(G126),H126*G126/100),IF(K126="L",-H126,0))</f>
+        <v/>
+      </c>
+      <c r="M126" s="11">
+        <f>Settings!$B$4+SUM(L$2:L126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="L127" s="11">
+        <f>IF(K127="W",IF(G127&lt;0,H127*100/ABS(G127),H127*G127/100),IF(K127="L",-H127,0))</f>
+        <v/>
+      </c>
+      <c r="M127" s="11">
+        <f>Settings!$B$4+SUM(L$2:L127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="L128" s="11">
+        <f>IF(K128="W",IF(G128&lt;0,H128*100/ABS(G128),H128*G128/100),IF(K128="L",-H128,0))</f>
+        <v/>
+      </c>
+      <c r="M128" s="11">
+        <f>Settings!$B$4+SUM(L$2:L128)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="L129" s="11">
+        <f>IF(K129="W",IF(G129&lt;0,H129*100/ABS(G129),H129*G129/100),IF(K129="L",-H129,0))</f>
+        <v/>
+      </c>
+      <c r="M129" s="11">
+        <f>Settings!$B$4+SUM(L$2:L129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="L130" s="11">
+        <f>IF(K130="W",IF(G130&lt;0,H130*100/ABS(G130),H130*G130/100),IF(K130="L",-H130,0))</f>
+        <v/>
+      </c>
+      <c r="M130" s="11">
+        <f>Settings!$B$4+SUM(L$2:L130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="L131" s="11">
+        <f>IF(K131="W",IF(G131&lt;0,H131*100/ABS(G131),H131*G131/100),IF(K131="L",-H131,0))</f>
+        <v/>
+      </c>
+      <c r="M131" s="11">
+        <f>Settings!$B$4+SUM(L$2:L131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="L132" s="11">
+        <f>IF(K132="W",IF(G132&lt;0,H132*100/ABS(G132),H132*G132/100),IF(K132="L",-H132,0))</f>
+        <v/>
+      </c>
+      <c r="M132" s="11">
+        <f>Settings!$B$4+SUM(L$2:L132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="L133" s="11">
+        <f>IF(K133="W",IF(G133&lt;0,H133*100/ABS(G133),H133*G133/100),IF(K133="L",-H133,0))</f>
+        <v/>
+      </c>
+      <c r="M133" s="11">
+        <f>Settings!$B$4+SUM(L$2:L133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="L134" s="11">
+        <f>IF(K134="W",IF(G134&lt;0,H134*100/ABS(G134),H134*G134/100),IF(K134="L",-H134,0))</f>
+        <v/>
+      </c>
+      <c r="M134" s="11">
+        <f>Settings!$B$4+SUM(L$2:L134)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="L135" s="11">
+        <f>IF(K135="W",IF(G135&lt;0,H135*100/ABS(G135),H135*G135/100),IF(K135="L",-H135,0))</f>
+        <v/>
+      </c>
+      <c r="M135" s="11">
+        <f>Settings!$B$4+SUM(L$2:L135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="L136" s="11">
+        <f>IF(K136="W",IF(G136&lt;0,H136*100/ABS(G136),H136*G136/100),IF(K136="L",-H136,0))</f>
+        <v/>
+      </c>
+      <c r="M136" s="11">
+        <f>Settings!$B$4+SUM(L$2:L136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="L137" s="11">
+        <f>IF(K137="W",IF(G137&lt;0,H137*100/ABS(G137),H137*G137/100),IF(K137="L",-H137,0))</f>
+        <v/>
+      </c>
+      <c r="M137" s="11">
+        <f>Settings!$B$4+SUM(L$2:L137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="L138" s="11">
+        <f>IF(K138="W",IF(G138&lt;0,H138*100/ABS(G138),H138*G138/100),IF(K138="L",-H138,0))</f>
+        <v/>
+      </c>
+      <c r="M138" s="11">
+        <f>Settings!$B$4+SUM(L$2:L138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="L139" s="11">
+        <f>IF(K139="W",IF(G139&lt;0,H139*100/ABS(G139),H139*G139/100),IF(K139="L",-H139,0))</f>
+        <v/>
+      </c>
+      <c r="M139" s="11">
+        <f>Settings!$B$4+SUM(L$2:L139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="L140" s="11">
+        <f>IF(K140="W",IF(G140&lt;0,H140*100/ABS(G140),H140*G140/100),IF(K140="L",-H140,0))</f>
+        <v/>
+      </c>
+      <c r="M140" s="11">
+        <f>Settings!$B$4+SUM(L$2:L140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="L141" s="11">
+        <f>IF(K141="W",IF(G141&lt;0,H141*100/ABS(G141),H141*G141/100),IF(K141="L",-H141,0))</f>
+        <v/>
+      </c>
+      <c r="M141" s="11">
+        <f>Settings!$B$4+SUM(L$2:L141)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="L142" s="11">
+        <f>IF(K142="W",IF(G142&lt;0,H142*100/ABS(G142),H142*G142/100),IF(K142="L",-H142,0))</f>
+        <v/>
+      </c>
+      <c r="M142" s="11">
+        <f>Settings!$B$4+SUM(L$2:L142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="L143" s="11">
+        <f>IF(K143="W",IF(G143&lt;0,H143*100/ABS(G143),H143*G143/100),IF(K143="L",-H143,0))</f>
+        <v/>
+      </c>
+      <c r="M143" s="11">
+        <f>Settings!$B$4+SUM(L$2:L143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="L144" s="11">
+        <f>IF(K144="W",IF(G144&lt;0,H144*100/ABS(G144),H144*G144/100),IF(K144="L",-H144,0))</f>
+        <v/>
+      </c>
+      <c r="M144" s="11">
+        <f>Settings!$B$4+SUM(L$2:L144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="L145" s="11">
+        <f>IF(K145="W",IF(G145&lt;0,H145*100/ABS(G145),H145*G145/100),IF(K145="L",-H145,0))</f>
+        <v/>
+      </c>
+      <c r="M145" s="11">
+        <f>Settings!$B$4+SUM(L$2:L145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="L146" s="11">
+        <f>IF(K146="W",IF(G146&lt;0,H146*100/ABS(G146),H146*G146/100),IF(K146="L",-H146,0))</f>
+        <v/>
+      </c>
+      <c r="M146" s="11">
+        <f>Settings!$B$4+SUM(L$2:L146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="L147" s="11">
+        <f>IF(K147="W",IF(G147&lt;0,H147*100/ABS(G147),H147*G147/100),IF(K147="L",-H147,0))</f>
+        <v/>
+      </c>
+      <c r="M147" s="11">
+        <f>Settings!$B$4+SUM(L$2:L147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="L148" s="11">
+        <f>IF(K148="W",IF(G148&lt;0,H148*100/ABS(G148),H148*G148/100),IF(K148="L",-H148,0))</f>
+        <v/>
+      </c>
+      <c r="M148" s="11">
+        <f>Settings!$B$4+SUM(L$2:L148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="L149" s="11">
+        <f>IF(K149="W",IF(G149&lt;0,H149*100/ABS(G149),H149*G149/100),IF(K149="L",-H149,0))</f>
+        <v/>
+      </c>
+      <c r="M149" s="11">
+        <f>Settings!$B$4+SUM(L$2:L149)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="L150" s="11">
+        <f>IF(K150="W",IF(G150&lt;0,H150*100/ABS(G150),H150*G150/100),IF(K150="L",-H150,0))</f>
+        <v/>
+      </c>
+      <c r="M150" s="11">
+        <f>Settings!$B$4+SUM(L$2:L150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="L151" s="11">
+        <f>IF(K151="W",IF(G151&lt;0,H151*100/ABS(G151),H151*G151/100),IF(K151="L",-H151,0))</f>
+        <v/>
+      </c>
+      <c r="M151" s="11">
+        <f>Settings!$B$4+SUM(L$2:L151)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="L152" s="11">
+        <f>IF(K152="W",IF(G152&lt;0,H152*100/ABS(G152),H152*G152/100),IF(K152="L",-H152,0))</f>
+        <v/>
+      </c>
+      <c r="M152" s="11">
+        <f>Settings!$B$4+SUM(L$2:L152)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="L153" s="11">
+        <f>IF(K153="W",IF(G153&lt;0,H153*100/ABS(G153),H153*G153/100),IF(K153="L",-H153,0))</f>
+        <v/>
+      </c>
+      <c r="M153" s="11">
+        <f>Settings!$B$4+SUM(L$2:L153)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="L154" s="11">
+        <f>IF(K154="W",IF(G154&lt;0,H154*100/ABS(G154),H154*G154/100),IF(K154="L",-H154,0))</f>
+        <v/>
+      </c>
+      <c r="M154" s="11">
+        <f>Settings!$B$4+SUM(L$2:L154)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="L155" s="11">
+        <f>IF(K155="W",IF(G155&lt;0,H155*100/ABS(G155),H155*G155/100),IF(K155="L",-H155,0))</f>
+        <v/>
+      </c>
+      <c r="M155" s="11">
+        <f>Settings!$B$4+SUM(L$2:L155)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="L156" s="11">
+        <f>IF(K156="W",IF(G156&lt;0,H156*100/ABS(G156),H156*G156/100),IF(K156="L",-H156,0))</f>
+        <v/>
+      </c>
+      <c r="M156" s="11">
+        <f>Settings!$B$4+SUM(L$2:L156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="L157" s="11">
+        <f>IF(K157="W",IF(G157&lt;0,H157*100/ABS(G157),H157*G157/100),IF(K157="L",-H157,0))</f>
+        <v/>
+      </c>
+      <c r="M157" s="11">
+        <f>Settings!$B$4+SUM(L$2:L157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="L158" s="11">
+        <f>IF(K158="W",IF(G158&lt;0,H158*100/ABS(G158),H158*G158/100),IF(K158="L",-H158,0))</f>
+        <v/>
+      </c>
+      <c r="M158" s="11">
+        <f>Settings!$B$4+SUM(L$2:L158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="L159" s="11">
+        <f>IF(K159="W",IF(G159&lt;0,H159*100/ABS(G159),H159*G159/100),IF(K159="L",-H159,0))</f>
+        <v/>
+      </c>
+      <c r="M159" s="11">
+        <f>Settings!$B$4+SUM(L$2:L159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="L160" s="11">
+        <f>IF(K160="W",IF(G160&lt;0,H160*100/ABS(G160),H160*G160/100),IF(K160="L",-H160,0))</f>
+        <v/>
+      </c>
+      <c r="M160" s="11">
+        <f>Settings!$B$4+SUM(L$2:L160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="L161" s="11">
+        <f>IF(K161="W",IF(G161&lt;0,H161*100/ABS(G161),H161*G161/100),IF(K161="L",-H161,0))</f>
+        <v/>
+      </c>
+      <c r="M161" s="11">
+        <f>Settings!$B$4+SUM(L$2:L161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="L162" s="11">
+        <f>IF(K162="W",IF(G162&lt;0,H162*100/ABS(G162),H162*G162/100),IF(K162="L",-H162,0))</f>
+        <v/>
+      </c>
+      <c r="M162" s="11">
+        <f>Settings!$B$4+SUM(L$2:L162)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="L163" s="11">
+        <f>IF(K163="W",IF(G163&lt;0,H163*100/ABS(G163),H163*G163/100),IF(K163="L",-H163,0))</f>
+        <v/>
+      </c>
+      <c r="M163" s="11">
+        <f>Settings!$B$4+SUM(L$2:L163)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3996,16 +5316,16 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>1738.7</v>
+        <v>1748.4</v>
       </c>
       <c r="E2" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0.2389024157458295</v>
+        <v>0.2002609517831881</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>-0.3131041177462083</v>
+        <v>-0.08468069682844867</v>
       </c>
       <c r="H2" s="9" t="n">
         <v>117</v>
@@ -4033,16 +5353,16 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>1613.1</v>
+        <v>1583.6</v>
       </c>
       <c r="E3" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.1200261378324967</v>
+        <v>0.03013079137574626</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.08928513545289066</v>
+        <v>0.1749736433847927</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>63</v>
@@ -4070,16 +5390,16 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>1569</v>
+        <v>1589.7</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>4.4</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.2187107716098359</v>
+        <v>0.2398792226531314</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>-0.05218195799544816</v>
+        <v>-0.1015329642420215</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>87</v>
@@ -4107,16 +5427,16 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>1491.7</v>
+        <v>1506.1</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>-7</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>-0.00677990204860647</v>
+        <v>0.03929231499690881</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.246843337573555</v>
+        <v>0.2015151012249312</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>124</v>
@@ -4144,16 +5464,16 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1499.4</v>
+        <v>1489.8</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>1.1</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.3988945801089721</v>
+        <v>0.338359480548565</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-0.2481185633682991</v>
+        <v>-0.04039565395890091</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>141</v>
@@ -4181,16 +5501,16 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1396.8</v>
+        <v>1417.7</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>-15.2</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>-0.02510769911461149</v>
+        <v>0.08317358946764059</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.3012418203750481</v>
+        <v>0.1674629735086709</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>114</v>
@@ -4218,16 +5538,16 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1412.1</v>
+        <v>1394.7</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>-22.3</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.3317320736505183</v>
+        <v>-0.1927453831838216</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.06131739304185656</v>
+        <v>0.02562052620265337</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>82</v>
@@ -4255,16 +5575,16 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1432.7</v>
+        <v>1451.7</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>-12.8</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.1654454108123683</v>
+        <v>0.203967017726322</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.1926127829579521</v>
+        <v>0.1500243787948437</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>129</v>
@@ -4292,16 +5612,16 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1439.9</v>
+        <v>1411.8</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>-6.1</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.556278847672138</v>
+        <v>0.2050857447960789</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.06562288621201061</v>
+        <v>0.09970684340957239</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>98</v>
@@ -4329,16 +5649,16 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1344.5</v>
+        <v>1382.6</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>-24.3</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>-0.2513514097581536</v>
+        <v>0.02348707331145269</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.3871905835315659</v>
+        <v>0.2115799586162578</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>92</v>
@@ -4361,2968 +5681,3900 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="5"/>
-    <col width="11" customWidth="1" min="6" max="7"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="15"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="23"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Ridge vs. XGBoost vs. Dub Gamma -- Model Comparison</t>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Dub Gamma vs. Ridge vs. XGBoost -- Model Comparison</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Informational only. Ridge is still the live model everywhere else in this workbook and on the website -- XGBoost and the Dub Gamma Model are candidates being evaluated here, not replacements. Gamma has no rating (and so no prediction) for any season before it was seeded -- its columns read "n/a" for older games.</t>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Informational only. The Dub Gamma Model (Sonny-Moore-seeded) is the live model everywhere else in this workbook and on the website -- Ridge and XGBoost are candidates being evaluated here, not replacements. Gamma has no rating (and so no prediction) for any season before it was seeded -- its columns read "n/a" for older games.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>All-Time (every season in the backtest)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="38.25" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Games Graded</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Picks Graded</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Pushes</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>ATS Win %</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>ROI (flat stake)</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>Real Edge Bets</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>Real Edge Win %</t>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>Tightest Of The Three (CLV)</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>CLV Pts (cum.)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Ridge (live model) -- all FBS</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>8531</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>8457</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>4224</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>4233</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Dub Gamma Model (live model) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>8618</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>183</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>107</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>76</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>58.5%</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>+11.6%</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>155</v>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>57.8%</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>74/185 (40%)</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>+731.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Dub Gamma Model (live model) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>978</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>+38.8%</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>5/22 (23%)</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>+120.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Ridge (candidate) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>8618</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>8548</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>4273</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>6684</v>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>-4.6%</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>6762</v>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>49.7%</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>4036/8531 (47%)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>+5676.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Ridge (live model) -- MW-involved</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>969</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>957</v>
-      </c>
-      <c r="D7" s="16" t="n">
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>4057/8618 (47%)</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>+5565.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Ridge (candidate) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>978</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>966</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>492</v>
+      </c>
+      <c r="E9" s="23" t="n">
         <v>474</v>
       </c>
-      <c r="E7" s="16" t="n">
-        <v>483</v>
-      </c>
-      <c r="F7" s="16" t="n">
+      <c r="F9" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>49.5%</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>-5.4%</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>776</v>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>50.9%</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="n">
+        <v>784</v>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>49.4%</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>454/969 (47%)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>+600.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>456/978 (47%)</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>+591.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>XGBoost (candidate) -- all FBS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>8531</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>8460</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>4270</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>4190</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="B10" s="23" t="n">
+        <v>8618</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>8548</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>4261</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>4287</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>49.9%</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>-4.8%</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="n">
+        <v>6695</v>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>50.5%</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>-3.6%</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>6625</v>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>50.5%</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>4478/8531 (52%)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>+758.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>4487/8618 (52%)</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>+566.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>XGBoost (candidate) -- MW-involved</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>969</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>957</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>485</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>472</v>
-      </c>
-      <c r="F9" s="16" t="n">
+      <c r="B11" s="23" t="n">
+        <v>978</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>966</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>487</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>479</v>
+      </c>
+      <c r="F11" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>50.7%</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>-3.2%</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>740</v>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>51.5%</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>512/969 (53%)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>+895.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Dub Gamma Model (candidate) -- all FBS</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>8531</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>97</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="F10" s="16" t="n">
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>50.4%</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>-3.8%</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="n">
+        <v>747</v>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>51.3%</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>517/978 (53%)</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>+907.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>2026 Season Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Games Graded</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Picks Graded</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Losses</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Pushes</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>ATS Win %</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>ROI (flat stake)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>Real Edge Bets</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Real Edge Win %</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>Tightest Of The Three (CLV)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>CLV Pts (cum.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Dub Gamma Model (live model) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>185</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>183</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>107</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>58.5%</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>+11.6%</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="n">
+        <v>155</v>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>57.8%</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>74/185 (40%)</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>+731.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Dub Gamma Model (live model) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+38.8%</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>5/22 (23%)</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>+120.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Ridge (candidate) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>185</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>183</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>78</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>105</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>42.6%</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>-18.6%</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="n">
+        <v>166</v>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>41.5%</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>54/185 (29%)</t>
+        </is>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>-529.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Ridge (candidate) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>-4.5%</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>6/22 (27%)</t>
+        </is>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>XGBoost (candidate) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n">
+        <v>185</v>
+      </c>
+      <c r="C19" s="23" t="n">
+        <v>183</v>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="E19" s="23" t="n">
+        <v>98</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>46.5%</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>-11.3%</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="n">
+        <v>154</v>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>44.1%</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>57/185 (31%)</t>
+        </is>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>-344.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>XGBoost (candidate) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>-30.6%</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>11/22 (50%)</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.0% of all graded games. Ridge agrees with the live model (Gamma) in 48.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 60.0% of games it has a rating for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Upcoming Games -- Ridge vs. XGBoost vs. Dub Gamma (Not Yet Graded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Matchup</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Line</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Line</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Line</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Lean</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Lean</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Lean</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>Ridge/XGBoost Agree?</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>Tightest (Live)*</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Wyoming @ Central Michigan</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>-9.6</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>-8.6</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>-9.3</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>UTEP @ Michigan</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>-36.5</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>-32.4</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>-29.7</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>Away (auto)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Nevada @ Middle Tennessee</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>-3.7</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>+2.3</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>+2.9</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>New Mexico @ Oklahoma</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>-23.5</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>-14.2</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>-14.6</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>-10.8</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>North Dakota State @ Sacramento State</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>+26.5</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>+12.6</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>+18.8</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>+35.9</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Northern Illinois @ Arizona</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>-35.5</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>-26.4</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>-20.8</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>-30.9</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Fresno State @ San José State</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>+10.3</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>* Tightest (Live) compares each model's line to TODAY's still-moving market line, not a final closing line -- it will keep changing until kickoff. See the graded Game-by-Game table below for the real, closing-line version of this comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>2026 Mountain West Games -- Game by Game</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Matchup</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Final Score</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>Vegas Spread (Home)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>Actual Margin (Home)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Line</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Edge</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Lean</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Result</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Line</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Edge</t>
+        </is>
+      </c>
+      <c r="L37" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Lean</t>
+        </is>
+      </c>
+      <c r="M37" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Result</t>
+        </is>
+      </c>
+      <c r="N37" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Line</t>
+        </is>
+      </c>
+      <c r="O37" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Edge</t>
+        </is>
+      </c>
+      <c r="P37" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Lean</t>
+        </is>
+      </c>
+      <c r="Q37" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Result</t>
+        </is>
+      </c>
+      <c r="R37" s="22" t="inlineStr">
+        <is>
+          <t>Ridge/XGBoost Agree?</t>
+        </is>
+      </c>
+      <c r="S37" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Agrees (w/ Live Model)?</t>
+        </is>
+      </c>
+      <c r="T37" s="22" t="inlineStr">
+        <is>
+          <t>Tightest CLV Line</t>
+        </is>
+      </c>
+      <c r="U37" s="22" t="inlineStr">
+        <is>
+          <t>Ridge CLV Pts (Cum.)</t>
+        </is>
+      </c>
+      <c r="V37" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost CLV Pts (Cum.)</t>
+        </is>
+      </c>
+      <c r="W37" s="22" t="inlineStr">
+        <is>
+          <t>Gamma CLV Pts (Cum.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>53.6%</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>+2.3%</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>91</v>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>17/98 (17%)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>-1491.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Dub Gamma Model (candidate) -- MW-involved</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>969</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" s="16" t="n">
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Duquesne @ Air Force</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>0-34</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>-30.0</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>+34.0</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>-17.0</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I38" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>-28.3</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M38" s="25" t="inlineStr">
+        <is>
+          <t>Loss (no real edge)</t>
+        </is>
+      </c>
+      <c r="N38" s="23" t="inlineStr">
+        <is>
+          <t>-36.5</t>
+        </is>
+      </c>
+      <c r="O38" s="23" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+      <c r="P38" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q38" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R38" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S38" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U38" s="23" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="V38" s="23" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="W38" s="23" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>+76.2%</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>91.7%</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>3/13 (23%)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>-36.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>2026 Season Only</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Games Graded</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Picks Graded</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Wins</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>Losses</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>Pushes</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>ATS Win %</t>
-        </is>
-      </c>
-      <c r="H14" s="15" t="inlineStr">
-        <is>
-          <t>ROI (flat stake)</t>
-        </is>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Real Edge Bets</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Real Edge Win %</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
-        <is>
-          <t>Tightest Of The Three (CLV)</t>
-        </is>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>CLV Pts (cum.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Ridge (live model) -- all FBS</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>97</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="F15" s="16" t="n">
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Wyoming @ Colorado State</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>13-35</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>+22.0</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>-7.8</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>+5.1</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="L39" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M39" s="25" t="inlineStr">
+        <is>
+          <t>Loss (no real edge)</t>
+        </is>
+      </c>
+      <c r="N39" s="23" t="inlineStr">
+        <is>
+          <t>-6.4</t>
+        </is>
+      </c>
+      <c r="O39" s="23" t="inlineStr">
+        <is>
+          <t>+3.7</t>
+        </is>
+      </c>
+      <c r="P39" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q39" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S39" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U39" s="23" t="inlineStr">
+        <is>
+          <t>-7.9</t>
+        </is>
+      </c>
+      <c r="V39" s="23" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="W39" s="23" t="inlineStr">
+        <is>
+          <t>+10.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>42.3%</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>-19.3%</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>88</v>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>40.2%</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>34/98 (35%)</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>-418.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Ridge (live model) -- MW-involved</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>-26.6%</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>4/13 (31%)</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>San José State @ Eastern Michigan</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>27-21</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>-15.8</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>+14.3</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I40" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>+9.0</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M40" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N40" s="23" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P40" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q40" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U40" s="23" t="inlineStr">
+        <is>
+          <t>+6.4</t>
+        </is>
+      </c>
+      <c r="V40" s="23" t="inlineStr">
+        <is>
+          <t>+7.2</t>
+        </is>
+      </c>
+      <c r="W40" s="23" t="inlineStr">
+        <is>
+          <t>+8.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>UNLV @ Hawai'i</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>21-6</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>-15.0</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>+2.9</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>+4.6</t>
+        </is>
+      </c>
+      <c r="L41" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M41" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N41" s="23" t="inlineStr">
+        <is>
+          <t>+4.4</t>
+        </is>
+      </c>
+      <c r="O41" s="23" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="P41" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q41" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge) (seed week)</t>
+        </is>
+      </c>
+      <c r="R41" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S41" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U41" s="23" t="inlineStr">
+        <is>
+          <t>+6.2</t>
+        </is>
+      </c>
+      <c r="V41" s="23" t="inlineStr">
+        <is>
+          <t>+11.8</t>
+        </is>
+      </c>
+      <c r="W41" s="23" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Northern Illinois @ Iowa</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>0-40</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>-31.8</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>+40.0</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>-28.3</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I42" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>-25.4</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>-6.4</t>
+        </is>
+      </c>
+      <c r="L42" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M42" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N42" s="23" t="inlineStr">
+        <is>
+          <t>-41.0</t>
+        </is>
+      </c>
+      <c r="O42" s="23" t="inlineStr">
+        <is>
+          <t>+9.2</t>
+        </is>
+      </c>
+      <c r="P42" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q42" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R42" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S42" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U42" s="23" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
+      <c r="V42" s="23" t="inlineStr">
+        <is>
+          <t>+5.4</t>
+        </is>
+      </c>
+      <c r="W42" s="23" t="inlineStr">
+        <is>
+          <t>+15.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Western Kentucky @ Nevada</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>14-49</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>+35.0</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>+3.3</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I43" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>+7.3</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>-7.1</t>
+        </is>
+      </c>
+      <c r="L43" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M43" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N43" s="23" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="O43" s="23" t="inlineStr">
+        <is>
+          <t>+2.7</t>
+        </is>
+      </c>
+      <c r="P43" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q43" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R43" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S43" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U43" s="23" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="V43" s="23" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="W43" s="23" t="inlineStr">
+        <is>
+          <t>+18.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Central Michigan @ New Mexico</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>7-38</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>-11.2</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>+31.0</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>-17.5</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>+6.2</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>-11.6</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M44" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N44" s="23" t="inlineStr">
+        <is>
+          <t>-15.6</t>
+        </is>
+      </c>
+      <c r="O44" s="23" t="inlineStr">
+        <is>
+          <t>+4.3</t>
+        </is>
+      </c>
+      <c r="P44" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q44" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R44" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S44" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U44" s="23" t="inlineStr">
+        <is>
+          <t>+5.9</t>
+        </is>
+      </c>
+      <c r="V44" s="23" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="W44" s="23" t="inlineStr">
+        <is>
+          <t>+22.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Jacksonville State @ North Dakota State</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>7-33</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>-6.8</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>+26.0</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>-18.4</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>+11.6</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>-14.4</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>+7.7</t>
+        </is>
+      </c>
+      <c r="L45" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M45" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N45" s="23" t="inlineStr">
+        <is>
+          <t>-25.5</t>
+        </is>
+      </c>
+      <c r="O45" s="23" t="inlineStr">
+        <is>
+          <t>+18.7</t>
+        </is>
+      </c>
+      <c r="P45" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q45" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R45" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S45" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U45" s="23" t="inlineStr">
+        <is>
+          <t>+17.6</t>
+        </is>
+      </c>
+      <c r="V45" s="23" t="inlineStr">
+        <is>
+          <t>+6.3</t>
+        </is>
+      </c>
+      <c r="W45" s="23" t="inlineStr">
+        <is>
+          <t>+41.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Fordham @ North Dakota State</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>0-38</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>-41.5</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>+38.0</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>-40.9</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="L46" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M46" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N46" s="23" t="inlineStr">
+        <is>
+          <t>-58.5</t>
+        </is>
+      </c>
+      <c r="O46" s="23" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="P46" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q46" s="25" t="inlineStr">
+        <is>
+          <t>Loss (seed week)</t>
+        </is>
+      </c>
+      <c r="R46" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S46" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U46" s="23" t="inlineStr">
+        <is>
+          <t>+16.9</t>
+        </is>
+      </c>
+      <c r="V46" s="23" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="W46" s="23" t="inlineStr">
+        <is>
+          <t>+58.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>UTEP @ Oklahoma</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>0-51</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>-40.8</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>+51.0</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>-34.8</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>-5.9</t>
+        </is>
+      </c>
+      <c r="H47" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I47" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>-32.8</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="L47" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M47" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N47" s="23" t="inlineStr">
+        <is>
+          <t>-44.4</t>
+        </is>
+      </c>
+      <c r="O47" s="23" t="inlineStr">
+        <is>
+          <t>+3.6</t>
+        </is>
+      </c>
+      <c r="P47" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q47" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R47" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S47" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U47" s="23" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
+      <c r="V47" s="23" t="inlineStr">
+        <is>
+          <t>-8.2</t>
+        </is>
+      </c>
+      <c r="W47" s="23" t="inlineStr">
+        <is>
+          <t>+62.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Hawai'i @ Stanford</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>27-37</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>-4.8</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>-3.3</t>
+        </is>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I48" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>+1.1</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>-5.8</t>
+        </is>
+      </c>
+      <c r="L48" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M48" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N48" s="23" t="inlineStr">
+        <is>
+          <t>-11.2</t>
+        </is>
+      </c>
+      <c r="O48" s="23" t="inlineStr">
+        <is>
+          <t>+6.4</t>
+        </is>
+      </c>
+      <c r="P48" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q48" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R48" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S48" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U48" s="23" t="inlineStr">
+        <is>
+          <t>+7.7</t>
+        </is>
+      </c>
+      <c r="V48" s="23" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
+      <c r="W48" s="23" t="inlineStr">
+        <is>
+          <t>+68.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Memphis @ UNLV</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>27-21</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>-4.8</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>-10.9</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>+6.2</t>
+        </is>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I49" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>-7.4</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>+2.6</t>
+        </is>
+      </c>
+      <c r="L49" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M49" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N49" s="23" t="inlineStr">
+        <is>
+          <t>+1.6</t>
+        </is>
+      </c>
+      <c r="O49" s="23" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
+      <c r="P49" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q49" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R49" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S49" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U49" s="23" t="inlineStr">
+        <is>
+          <t>+13.9</t>
+        </is>
+      </c>
+      <c r="V49" s="23" t="inlineStr">
+        <is>
+          <t>-11.4</t>
+        </is>
+      </c>
+      <c r="W49" s="23" t="inlineStr">
+        <is>
+          <t>+62.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>San José State @ USC</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>26-42</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>-37.2</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>+16.0</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>-34.6</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>-35.3</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="L50" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M50" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N50" s="23" t="inlineStr">
+        <is>
+          <t>-30.3</t>
+        </is>
+      </c>
+      <c r="O50" s="23" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
+      <c r="P50" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q50" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R50" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S50" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U50" s="23" t="inlineStr">
         <is>
           <t>+11.2</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>XGBoost (candidate) -- all FBS</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>97</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>44.3%</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>-15.4%</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>47/98 (48%)</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>-151.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>XGBoost (candidate) -- MW-involved</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>-26.6%</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>6/13 (46%)</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="V50" s="23" t="inlineStr">
         <is>
           <t>-13.3</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Dub Gamma Model (candidate) -- all FBS</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>97</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>53.6%</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>+2.3%</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="n">
-        <v>91</v>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>17/98 (17%)</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>-1491.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Dub Gamma Model (candidate) -- MW-involved</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>+76.2%</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>91.7%</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>3/13 (23%)</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>-36.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Ridge and XGBoost agree on which side to lean in 77.4% of all graded games. Gamma agrees with Ridge in 68.4% of games it has a rating for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Upcoming Games -- Ridge vs. XGBoost vs. Dub Gamma (Not Yet Graded)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="38.25" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Matchup</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>Ridge Line</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>XGBoost Line</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>Gamma Line</t>
-        </is>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>Ridge Lean</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>XGBoost Lean</t>
-        </is>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Gamma Lean</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Ridge/XGBoost Agree?</t>
-        </is>
-      </c>
-      <c r="K25" s="15" t="inlineStr">
-        <is>
-          <t>Tightest (Live)*</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="n">
+      <c r="W50" s="23" t="inlineStr">
+        <is>
+          <t>+55.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>North Dakota State @ Air Force</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>38-32</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>+1.8</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>-15.3</t>
+        </is>
+      </c>
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J51" s="23" t="inlineStr">
+        <is>
+          <t>+14.7</t>
+        </is>
+      </c>
+      <c r="K51" s="23" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="L51" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M51" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N51" s="23" t="inlineStr">
+        <is>
+          <t>+17.9</t>
+        </is>
+      </c>
+      <c r="O51" s="23" t="inlineStr">
+        <is>
+          <t>-16.2</t>
+        </is>
+      </c>
+      <c r="P51" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q51" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R51" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S51" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U51" s="23" t="inlineStr">
+        <is>
+          <t>-4.1</t>
+        </is>
+      </c>
+      <c r="V51" s="23" t="inlineStr">
+        <is>
+          <t>-26.3</t>
+        </is>
+      </c>
+      <c r="W51" s="23" t="inlineStr">
+        <is>
+          <t>+39.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>New Mexico State @ Hawai'i</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>19-29</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>-14.1</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>+6.6</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>-13.3</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr">
+        <is>
+          <t>+5.8</t>
+        </is>
+      </c>
+      <c r="L52" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M52" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N52" s="23" t="inlineStr">
+        <is>
+          <t>-7.6</t>
+        </is>
+      </c>
+      <c r="O52" s="23" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
+      <c r="P52" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q52" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="R52" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S52" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U52" s="23" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="V52" s="23" t="inlineStr">
+        <is>
+          <t>-20.5</t>
+        </is>
+      </c>
+      <c r="W52" s="23" t="inlineStr">
+        <is>
+          <t>+39.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>Montana State @ Nevada</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>20-7</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>-17.2</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>+22.2</t>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I53" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>-11.6</t>
+        </is>
+      </c>
+      <c r="K53" s="23" t="inlineStr">
+        <is>
+          <t>+16.6</t>
+        </is>
+      </c>
+      <c r="L53" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M53" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N53" s="23" t="inlineStr">
+        <is>
+          <t>-33.6</t>
+        </is>
+      </c>
+      <c r="O53" s="23" t="inlineStr">
+        <is>
+          <t>+38.6</t>
+        </is>
+      </c>
+      <c r="P53" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q53" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R53" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S53" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U53" s="23" t="inlineStr">
+        <is>
+          <t>+24.8</t>
+        </is>
+      </c>
+      <c r="V53" s="23" t="inlineStr">
+        <is>
+          <t>-3.9</t>
+        </is>
+      </c>
+      <c r="W53" s="23" t="inlineStr">
+        <is>
+          <t>+77.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>Mercyhurst @ New Mexico</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>7-70</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>-42.2</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>+63.0</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>-17.0</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>-25.2</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I54" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>-28.0</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr">
+        <is>
+          <t>-14.3</t>
+        </is>
+      </c>
+      <c r="L54" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M54" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N54" s="23" t="inlineStr">
+        <is>
+          <t>-45.6</t>
+        </is>
+      </c>
+      <c r="O54" s="23" t="inlineStr">
+        <is>
+          <t>+3.3</t>
+        </is>
+      </c>
+      <c r="P54" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q54" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R54" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S54" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U54" s="23" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="V54" s="23" t="inlineStr">
+        <is>
+          <t>-18.2</t>
+        </is>
+      </c>
+      <c r="W54" s="23" t="inlineStr">
+        <is>
+          <t>+81.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>UNLV @ North Texas</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>-3.9</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>6-44</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>+38.0</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>+6.3</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
+      <c r="K55" s="23" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
+      <c r="L55" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M55" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N55" s="23" t="inlineStr">
         <is>
           <t>-5.3</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="O55" s="23" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
+      <c r="P55" s="23" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>Away (auto)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="Q55" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R55" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S55" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T55" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U55" s="23" t="inlineStr">
+        <is>
+          <t>+5.9</t>
+        </is>
+      </c>
+      <c r="V55" s="23" t="inlineStr">
+        <is>
+          <t>-16.8</t>
+        </is>
+      </c>
+      <c r="W55" s="23" t="inlineStr">
+        <is>
+          <t>+89.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>Illinois State @ Northern Illinois</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>28-24</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>-15.0</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>+17.5</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I56" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>-16.3</t>
+        </is>
+      </c>
+      <c r="K56" s="23" t="inlineStr">
+        <is>
+          <t>+18.8</t>
+        </is>
+      </c>
+      <c r="L56" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M56" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N56" s="23" t="inlineStr">
+        <is>
+          <t>-23.3</t>
+        </is>
+      </c>
+      <c r="O56" s="23" t="inlineStr">
+        <is>
+          <t>+25.8</t>
+        </is>
+      </c>
+      <c r="P56" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q56" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R56" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S56" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T56" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U56" s="23" t="inlineStr">
+        <is>
+          <t>+23.4</t>
+        </is>
+      </c>
+      <c r="V56" s="23" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="W56" s="23" t="inlineStr">
+        <is>
+          <t>+114.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>Cal Poly @ San José State</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>-21.5</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>+10.0</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>-19.9</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="H57" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J57" s="23" t="inlineStr">
+        <is>
+          <t>-27.6</t>
+        </is>
+      </c>
+      <c r="K57" s="23" t="inlineStr">
+        <is>
+          <t>+6.1</t>
+        </is>
+      </c>
+      <c r="L57" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M57" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N57" s="23" t="inlineStr">
+        <is>
+          <t>-30.7</t>
+        </is>
+      </c>
+      <c r="O57" s="23" t="inlineStr">
+        <is>
+          <t>+9.2</t>
+        </is>
+      </c>
+      <c r="P57" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q57" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R57" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="S57" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U57" s="23" t="inlineStr">
+        <is>
+          <t>+21.8</t>
+        </is>
+      </c>
+      <c r="V57" s="23" t="inlineStr">
+        <is>
+          <t>+8.1</t>
+        </is>
+      </c>
+      <c r="W57" s="23" t="inlineStr">
+        <is>
+          <t>+124.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>Texas Southern @ UTEP</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>10-51</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>-27.2</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>+41.0</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>-14.6</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
+        <is>
+          <t>-12.6</t>
+        </is>
+      </c>
+      <c r="H58" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I58" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>-19.9</t>
+        </is>
+      </c>
+      <c r="K58" s="23" t="inlineStr">
+        <is>
+          <t>-7.4</t>
+        </is>
+      </c>
+      <c r="L58" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M58" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N58" s="23" t="inlineStr">
+        <is>
+          <t>-19.8</t>
+        </is>
+      </c>
+      <c r="O58" s="23" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
+      <c r="P58" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q58" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R58" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S58" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T58" s="24" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="n">
+      <c r="U58" s="23" t="inlineStr">
+        <is>
+          <t>+9.2</t>
+        </is>
+      </c>
+      <c r="V58" s="23" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
+      <c r="W58" s="23" t="inlineStr">
+        <is>
+          <t>+116.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B59" s="23" t="inlineStr">
         <is>
           <t>Northern Colorado @ Wyoming</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>-17.1</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>-21.5</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>+11.3</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Mercyhurst @ New Mexico</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>-17.1</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>-27.1</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>-6.7</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>Illinois State @ Northern Illinois</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>-16.0</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>-17.9</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>+15.6</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>Texas Southern @ UTEP</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>-16.1</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>-21.4</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>+19.1</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>Cal Poly @ San José State</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>-21.0</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>-30.0</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>+8.1</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>North Dakota State @ Air Force</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>+16.9</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>+15.3</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>+17.9</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>13-21</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>-23.5</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>-16.3</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>-7.2</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>-22.1</t>
+        </is>
+      </c>
+      <c r="K59" s="23" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="L59" s="23" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="M59" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N59" s="23" t="inlineStr">
+        <is>
+          <t>-27.6</t>
+        </is>
+      </c>
+      <c r="O59" s="23" t="inlineStr">
+        <is>
+          <t>+4.1</t>
+        </is>
+      </c>
+      <c r="P59" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q59" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R59" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K32" s="17" t="inlineStr">
+      <c r="S59" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T59" s="24" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>Montana State @ Nevada</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>-17.2</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>-12.7</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>+5.3</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K33" s="16" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>New Mexico State @ Hawai'i</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>-8.5</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>-14.2</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>-13.2</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>-7.6</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K34" s="17" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>* Tightest (Live) compares each model's line to TODAY's still-moving market line, not a final closing line -- it will keep changing until kickoff. See the graded Game-by-Game table below for the real, closing-line version of this comparison.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>2026 Mountain West Games -- Game by Game</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Matchup</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>Final Score</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>Vegas Spread (Home)</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>Actual Margin (Home)</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>Ridge Line</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>Ridge Edge</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>Ridge Lean</t>
-        </is>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Ridge Result</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>XGBoost Line</t>
-        </is>
-      </c>
-      <c r="K39" s="15" t="inlineStr">
-        <is>
-          <t>XGBoost Edge</t>
-        </is>
-      </c>
-      <c r="L39" s="15" t="inlineStr">
-        <is>
-          <t>XGBoost Lean</t>
-        </is>
-      </c>
-      <c r="M39" s="15" t="inlineStr">
-        <is>
-          <t>XGBoost Result</t>
-        </is>
-      </c>
-      <c r="N39" s="15" t="inlineStr">
-        <is>
-          <t>Gamma Line</t>
-        </is>
-      </c>
-      <c r="O39" s="15" t="inlineStr">
-        <is>
-          <t>Gamma Edge</t>
-        </is>
-      </c>
-      <c r="P39" s="15" t="inlineStr">
-        <is>
-          <t>Gamma Lean</t>
-        </is>
-      </c>
-      <c r="Q39" s="15" t="inlineStr">
-        <is>
-          <t>Gamma Result</t>
-        </is>
-      </c>
-      <c r="R39" s="15" t="inlineStr">
-        <is>
-          <t>Ridge/XGBoost Agree?</t>
-        </is>
-      </c>
-      <c r="S39" s="15" t="inlineStr">
-        <is>
-          <t>Gamma Agrees (w/ Ridge)?</t>
-        </is>
-      </c>
-      <c r="T39" s="15" t="inlineStr">
-        <is>
-          <t>Tightest CLV Line</t>
-        </is>
-      </c>
-      <c r="U39" s="15" t="inlineStr">
-        <is>
-          <t>Ridge CLV Pts (Cum.)</t>
-        </is>
-      </c>
-      <c r="V39" s="15" t="inlineStr">
-        <is>
-          <t>XGBoost CLV Pts (Cum.)</t>
-        </is>
-      </c>
-      <c r="W39" s="15" t="inlineStr">
-        <is>
-          <t>Gamma CLV Pts (Cum.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Duquesne @ Air Force</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>0-34</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>-30.0</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>+34.0</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>-17.0</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I40" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>-28.3</t>
-        </is>
-      </c>
-      <c r="K40" s="16" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
-      <c r="L40" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M40" s="17" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N40" s="16" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
-      <c r="O40" s="16" t="inlineStr">
-        <is>
-          <t>-32.3</t>
-        </is>
-      </c>
-      <c r="P40" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q40" s="18" t="inlineStr">
-        <is>
-          <t>Loss (seed week)</t>
-        </is>
-      </c>
-      <c r="R40" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S40" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T40" s="17" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U40" s="16" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
-      <c r="V40" s="16" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
-      <c r="W40" s="16" t="inlineStr">
-        <is>
-          <t>-32.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>Wyoming @ Colorado State</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>13-35</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>-7.8</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>+5.1</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="K41" s="16" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="L41" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M41" s="17" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N41" s="16" t="inlineStr">
-        <is>
-          <t>-6.4</t>
-        </is>
-      </c>
-      <c r="O41" s="16" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
-      <c r="P41" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q41" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R41" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S41" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T41" s="17" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U41" s="16" t="inlineStr">
-        <is>
-          <t>-7.9</t>
-        </is>
-      </c>
-      <c r="V41" s="16" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="W41" s="16" t="inlineStr">
-        <is>
-          <t>-28.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>San José State @ Eastern Michigan</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>27-21</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>-15.8</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>+14.3</t>
-        </is>
-      </c>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I42" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
-      <c r="K42" s="16" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
-      <c r="L42" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M42" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N42" s="16" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="O42" s="16" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="P42" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q42" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R42" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S42" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T42" s="17" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U42" s="16" t="inlineStr">
-        <is>
-          <t>+6.4</t>
-        </is>
-      </c>
-      <c r="V42" s="16" t="inlineStr">
-        <is>
-          <t>+7.2</t>
-        </is>
-      </c>
-      <c r="W42" s="16" t="inlineStr">
-        <is>
-          <t>-30.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>UNLV @ Hawai'i</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>21-6</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
-      <c r="K43" s="16" t="inlineStr">
-        <is>
-          <t>+4.6</t>
-        </is>
-      </c>
-      <c r="L43" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M43" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N43" s="16" t="inlineStr">
-        <is>
-          <t>+4.4</t>
-        </is>
-      </c>
-      <c r="O43" s="16" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="P43" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q43" s="17" t="inlineStr">
-        <is>
-          <t>Win (no real edge) (seed week)</t>
-        </is>
-      </c>
-      <c r="R43" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S43" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T43" s="17" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U43" s="16" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
-      <c r="V43" s="16" t="inlineStr">
-        <is>
-          <t>+11.8</t>
-        </is>
-      </c>
-      <c r="W43" s="16" t="inlineStr">
-        <is>
-          <t>-32.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>Northern Illinois @ Iowa</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>0-40</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>-31.8</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>+40.0</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>-28.3</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>-25.4</t>
-        </is>
-      </c>
-      <c r="K44" s="16" t="inlineStr">
-        <is>
-          <t>-6.4</t>
-        </is>
-      </c>
-      <c r="L44" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M44" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N44" s="16" t="inlineStr">
-        <is>
-          <t>-41.0</t>
-        </is>
-      </c>
-      <c r="O44" s="16" t="inlineStr">
-        <is>
-          <t>+9.2</t>
-        </is>
-      </c>
-      <c r="P44" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q44" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R44" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T44" s="17" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U44" s="16" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
-      <c r="V44" s="16" t="inlineStr">
-        <is>
-          <t>+5.4</t>
-        </is>
-      </c>
-      <c r="W44" s="16" t="inlineStr">
-        <is>
-          <t>-23.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>Western Kentucky @ Nevada</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>14-49</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>+35.0</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>+3.3</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>+7.3</t>
-        </is>
-      </c>
-      <c r="K45" s="16" t="inlineStr">
-        <is>
-          <t>-7.1</t>
-        </is>
-      </c>
-      <c r="L45" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M45" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N45" s="16" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="O45" s="16" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
-      <c r="P45" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q45" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R45" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S45" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T45" s="17" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U45" s="16" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="V45" s="16" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
-      <c r="W45" s="16" t="inlineStr">
-        <is>
-          <t>-20.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>Central Michigan @ New Mexico</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>7-38</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>-11.2</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>+31.0</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>-17.5</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I46" s="17" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>-11.6</t>
-        </is>
-      </c>
-      <c r="K46" s="16" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
-      <c r="L46" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M46" s="17" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N46" s="16" t="inlineStr">
-        <is>
-          <t>-15.6</t>
-        </is>
-      </c>
-      <c r="O46" s="16" t="inlineStr">
-        <is>
-          <t>+4.3</t>
-        </is>
-      </c>
-      <c r="P46" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q46" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R46" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S46" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T46" s="17" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U46" s="16" t="inlineStr">
-        <is>
-          <t>+5.9</t>
-        </is>
-      </c>
-      <c r="V46" s="16" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="W46" s="16" t="inlineStr">
-        <is>
-          <t>-16.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>Jacksonville State @ North Dakota State</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>7-33</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>-6.8</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>+26.0</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>-18.4</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>+11.6</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>-14.4</t>
-        </is>
-      </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>+7.7</t>
-        </is>
-      </c>
-      <c r="L47" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M47" s="17" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N47" s="16" t="inlineStr">
-        <is>
-          <t>-25.5</t>
-        </is>
-      </c>
-      <c r="O47" s="16" t="inlineStr">
-        <is>
-          <t>+18.7</t>
-        </is>
-      </c>
-      <c r="P47" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q47" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R47" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S47" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T47" s="17" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U47" s="16" t="inlineStr">
-        <is>
-          <t>+17.6</t>
-        </is>
-      </c>
-      <c r="V47" s="16" t="inlineStr">
-        <is>
-          <t>+6.3</t>
-        </is>
-      </c>
-      <c r="W47" s="16" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>Fordham @ North Dakota State</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>0-38</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>-41.5</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>+38.0</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>-40.9</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="U59" s="23" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="V59" s="23" t="inlineStr">
         <is>
           <t>-0.6</t>
         </is>
       </c>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>Loss (no real edge)</t>
-        </is>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>-35.0</t>
-        </is>
-      </c>
-      <c r="K48" s="16" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
-      <c r="L48" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M48" s="17" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N48" s="16" t="inlineStr">
-        <is>
-          <t>-19.6</t>
-        </is>
-      </c>
-      <c r="O48" s="16" t="inlineStr">
-        <is>
-          <t>-21.9</t>
-        </is>
-      </c>
-      <c r="P48" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R48" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S48" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T48" s="17" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U48" s="16" t="inlineStr">
-        <is>
-          <t>+16.9</t>
-        </is>
-      </c>
-      <c r="V48" s="16" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="W48" s="16" t="inlineStr">
-        <is>
-          <t>-19.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>UTEP @ Oklahoma</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>0-51</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>-40.8</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>+51.0</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>-34.8</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>-5.9</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>-32.8</t>
-        </is>
-      </c>
-      <c r="K49" s="16" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
-      <c r="L49" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M49" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N49" s="16" t="inlineStr">
-        <is>
-          <t>-44.4</t>
-        </is>
-      </c>
-      <c r="O49" s="16" t="inlineStr">
-        <is>
-          <t>+3.6</t>
-        </is>
-      </c>
-      <c r="P49" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q49" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R49" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S49" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T49" s="17" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U49" s="16" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
-      <c r="V49" s="16" t="inlineStr">
-        <is>
-          <t>-8.2</t>
-        </is>
-      </c>
-      <c r="W49" s="16" t="inlineStr">
-        <is>
-          <t>-15.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Hawai'i @ Stanford</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>27-37</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>-4.8</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>-3.3</t>
-        </is>
-      </c>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I50" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
-      <c r="K50" s="16" t="inlineStr">
-        <is>
-          <t>-5.8</t>
-        </is>
-      </c>
-      <c r="L50" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M50" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N50" s="16" t="inlineStr">
-        <is>
-          <t>-11.2</t>
-        </is>
-      </c>
-      <c r="O50" s="16" t="inlineStr">
-        <is>
-          <t>+6.4</t>
-        </is>
-      </c>
-      <c r="P50" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q50" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R50" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S50" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T50" s="17" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U50" s="16" t="inlineStr">
-        <is>
-          <t>+7.7</t>
-        </is>
-      </c>
-      <c r="V50" s="16" t="inlineStr">
-        <is>
-          <t>-14.0</t>
-        </is>
-      </c>
-      <c r="W50" s="16" t="inlineStr">
-        <is>
-          <t>-9.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>Memphis @ UNLV</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>27-21</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>-4.8</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I51" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>-7.4</t>
-        </is>
-      </c>
-      <c r="K51" s="16" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
-      <c r="L51" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M51" s="18" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N51" s="16" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
-      <c r="O51" s="16" t="inlineStr">
-        <is>
-          <t>-6.3</t>
-        </is>
-      </c>
-      <c r="P51" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q51" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R51" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S51" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T51" s="17" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U51" s="16" t="inlineStr">
-        <is>
-          <t>+13.9</t>
-        </is>
-      </c>
-      <c r="V51" s="16" t="inlineStr">
-        <is>
-          <t>-11.4</t>
-        </is>
-      </c>
-      <c r="W51" s="16" t="inlineStr">
-        <is>
-          <t>-15.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>San José State @ USC</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>26-42</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>-37.2</t>
-        </is>
-      </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>+16.0</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>-34.6</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>-2.7</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>-35.3</t>
-        </is>
-      </c>
-      <c r="K52" s="16" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="L52" s="16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M52" s="18" t="inlineStr">
-        <is>
-          <t>Loss (no real edge)</t>
-        </is>
-      </c>
-      <c r="N52" s="16" t="inlineStr">
-        <is>
-          <t>-16.1</t>
-        </is>
-      </c>
-      <c r="O52" s="16" t="inlineStr">
-        <is>
-          <t>-21.1</t>
-        </is>
-      </c>
-      <c r="P52" s="16" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q52" s="17" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R52" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S52" s="16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T52" s="17" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U52" s="16" t="inlineStr">
-        <is>
-          <t>+11.2</t>
-        </is>
-      </c>
-      <c r="V52" s="16" t="inlineStr">
-        <is>
-          <t>-13.3</t>
-        </is>
-      </c>
-      <c r="W52" s="16" t="inlineStr">
-        <is>
-          <t>-36.7</t>
+      <c r="W59" s="23" t="inlineStr">
+        <is>
+          <t>+120.7</t>
         </is>
       </c>
     </row>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -3893,6 +3893,38 @@
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wyoming @ Central Michigan</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Central Michigan</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
       <c r="J35" s="6">
         <f>IF(I35="","",I35-F35)</f>
         <v/>
@@ -3907,6 +3939,38 @@
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wyoming @ Central Michigan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Central Michigan</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
       <c r="J36" s="6">
         <f>IF(I36="","",I36-F36)</f>
         <v/>
@@ -3921,6 +3985,38 @@
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sacramento State @ North Dakota State</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>-27.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
       <c r="J37" s="6">
         <f>IF(I37="","",I37-F37)</f>
         <v/>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -974,7 +974,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G2" s="6">
         <f>F2-E2</f>
@@ -985,10 +985,10 @@
         <v/>
       </c>
       <c r="I2" t="n">
-        <v>43.2</v>
+        <v>36.6</v>
       </c>
       <c r="J2" t="n">
-        <v>39.5</v>
+        <v>38.8</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -1032,7 +1032,7 @@
         <v>-29.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-35.2</v>
+        <v>-34.8</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -1043,7 +1043,7 @@
         <v/>
       </c>
       <c r="I3" t="n">
-        <v>47.5</v>
+        <v>41.8</v>
       </c>
       <c r="J3" t="n">
         <v>48.5</v>
@@ -1088,7 +1088,7 @@
         <v>2.9</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
@@ -1099,7 +1099,7 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>53.6</v>
+        <v>51.6</v>
       </c>
       <c r="J4" t="n">
         <v>50.5</v>
@@ -1144,7 +1144,7 @@
         <v>-10.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-23</v>
+        <v>-21.8</v>
       </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
@@ -1155,10 +1155,10 @@
         <v/>
       </c>
       <c r="I5" t="n">
-        <v>43.8</v>
+        <v>37</v>
       </c>
       <c r="J5" t="n">
-        <v>47</v>
+        <v>45.5</v>
       </c>
       <c r="K5" s="6">
         <f>I5-J5</f>
@@ -1205,7 +1205,7 @@
         <v>35.9</v>
       </c>
       <c r="F6" t="n">
-        <v>27.8</v>
+        <v>27</v>
       </c>
       <c r="G6" s="6">
         <f>F6-E6</f>
@@ -1216,10 +1216,10 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>47.9</v>
+        <v>44</v>
       </c>
       <c r="J6" t="n">
-        <v>52.8</v>
+        <v>50.5</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -1266,7 +1266,7 @@
         <v>-30.9</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>-34.5</v>
+        <v>-33.8</v>
       </c>
       <c r="G7" s="10">
         <f>F7-E7</f>
@@ -1277,10 +1277,10 @@
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>41</v>
+        <v>36.8</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="K7" s="10">
         <f>I7-J7</f>
@@ -1338,10 +1338,10 @@
         <v/>
       </c>
       <c r="I8" t="n">
-        <v>50.8</v>
+        <v>46.5</v>
       </c>
       <c r="J8" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
       <c r="K8" s="6">
         <f>I8-J8</f>
@@ -5424,10 +5424,10 @@
         <v>4.2</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0.2002609517831881</v>
+        <v>0.1779024536014308</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>-0.08468069682844867</v>
+        <v>-0.1642277760509774</v>
       </c>
       <c r="H2" s="9" t="n">
         <v>117</v>
@@ -5461,10 +5461,10 @@
         <v>-2.7</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.03013079137574626</v>
+        <v>-0.05248930944528065</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.1749736433847927</v>
+        <v>0.1471056400027093</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>63</v>
@@ -5498,10 +5498,10 @@
         <v>5</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.2398792226531314</v>
+        <v>0.2352301586935283</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>-0.1015329642420215</v>
+        <v>-0.298944742674818</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>87</v>
@@ -5535,10 +5535,10 @@
         <v>-5.8</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.03929231499690881</v>
+        <v>0.03294096360944201</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.2015151012249312</v>
+        <v>0.1296644642024742</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>124</v>
@@ -5572,10 +5572,10 @@
         <v>-0.1</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.338359480548565</v>
+        <v>0.3168724868895267</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-0.04039565395890091</v>
+        <v>-0.07900441286649691</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>141</v>
@@ -5609,10 +5609,10 @@
         <v>-13.7</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.08317358946764059</v>
+        <v>-0.002827735068849334</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.1674629735086709</v>
+        <v>0.06489075558866486</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>114</v>
@@ -5646,10 +5646,10 @@
         <v>-16.9</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.1927453831838216</v>
+        <v>-0.2402103302415052</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.02562052620265337</v>
+        <v>0.003955245944769085</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>82</v>
@@ -5683,10 +5683,10 @@
         <v>-12.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.203967017726322</v>
+        <v>0.1640411560777529</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.1500243787948437</v>
+        <v>0.07569306543146938</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>129</v>
@@ -5720,10 +5720,10 @@
         <v>-7.6</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.2050857447960789</v>
+        <v>0.1253495981030349</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.09970684340957239</v>
+        <v>0.08041411531454036</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>98</v>
@@ -5757,10 +5757,10 @@
         <v>-16.2</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.02348707331145269</v>
+        <v>-0.134943446773656</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.2115799586162578</v>
+        <v>0.1797364798378445</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>92</v>
@@ -5901,13 +5901,13 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>8618</v>
+        <v>8619</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>76</v>
@@ -5917,30 +5917,30 @@
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+12.1%</t>
         </is>
       </c>
       <c r="I6" s="23" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t>75/185 (41%)</t>
+          <t>74/186 (40%)</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
         <is>
-          <t>+731.7</t>
+          <t>+743.4</t>
         </is>
       </c>
     </row>
@@ -6001,16 +6001,16 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>8618</v>
+        <v>8619</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>8548</v>
+        <v>8549</v>
       </c>
       <c r="D8" s="23" t="n">
         <v>4273</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>4275</v>
+        <v>4276</v>
       </c>
       <c r="F8" s="23" t="n">
         <v>70</v>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="K8" s="23" t="inlineStr">
         <is>
-          <t>4096/8618 (48%)</t>
+          <t>4093/8619 (47%)</t>
         </is>
       </c>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t>+5565.3</t>
+          <t>+5563.6</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>461/978 (47%)</t>
+          <t>456/978 (47%)</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -6101,32 +6101,32 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>8618</v>
+        <v>8619</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>8548</v>
+        <v>8549</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>4306</v>
+        <v>4273</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4242</v>
+        <v>4276</v>
       </c>
       <c r="F10" s="23" t="n">
         <v>70</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="I10" s="23" t="n">
-        <v>6719</v>
+        <v>6734</v>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
@@ -6135,12 +6135,12 @@
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>4447/8618 (52%)</t>
+          <t>4452/8619 (52%)</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t>+539.0</t>
+          <t>+732.6</t>
         </is>
       </c>
     </row>
@@ -6176,21 +6176,21 @@
         </is>
       </c>
       <c r="I11" s="23" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>512/978 (52%)</t>
+          <t>517/978 (53%)</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t>+909.2</t>
+          <t>+985.9</t>
         </is>
       </c>
     </row>
@@ -6270,13 +6270,13 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E15" s="23" t="n">
         <v>76</v>
@@ -6286,30 +6286,30 @@
       </c>
       <c r="G15" s="23" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+12.1%</t>
         </is>
       </c>
       <c r="I15" s="23" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="K15" s="23" t="inlineStr">
         <is>
-          <t>75/185 (41%)</t>
+          <t>74/186 (40%)</t>
         </is>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
-          <t>+731.7</t>
+          <t>+743.4</t>
         </is>
       </c>
     </row>
@@ -6370,28 +6370,28 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D17" s="23" t="n">
         <v>78</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17" s="23" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="I17" s="23" t="n">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>53/185 (29%)</t>
+          <t>53/186 (28%)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
         <is>
-          <t>-529.7</t>
+          <t>-531.3</t>
         </is>
       </c>
     </row>
@@ -6470,46 +6470,46 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F19" s="23" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="I19" s="23" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>57/185 (31%)</t>
+          <t>59/186 (32%)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
-          <t>-373.3</t>
+          <t>-360.6</t>
         </is>
       </c>
     </row>
@@ -6559,14 +6559,14 @@
       </c>
       <c r="L20" s="23" t="inlineStr">
         <is>
-          <t>+0.4</t>
+          <t>+0.1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.2% of all graded games. Ridge agrees with the live model (Gamma) in 48.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 61.6% of games it has a rating for.</t>
+          <t>Ridge and XGBoost (the two candidates) agree with each other in 76.9% of all graded games. Ridge agrees with the live model (Gamma) in 47.8% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 61.3% of games it has a rating for.</t>
         </is>
       </c>
     </row>
@@ -6640,27 +6640,27 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Wyoming @ Central Michigan</t>
+          <t>North Dakota State @ Sacramento State</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+27.0</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>+12.6</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>-9.7</t>
+          <t>+18.3</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>+35.9</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="K26" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -6695,42 +6695,42 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>UTEP @ Michigan</t>
+          <t>Wyoming @ Central Michigan</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>-35.2</t>
+          <t>+1.2</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>-35.0</t>
+          <t>-9.6</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>-32.8</t>
+          <t>-8.8</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>-29.7</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -6750,52 +6750,52 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>Nevada @ Middle Tennessee</t>
+          <t>UTEP @ Michigan</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>-34.8</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-35.0</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>+2.1</t>
+          <t>-31.5</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>+2.9</t>
+          <t>-29.7</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K28" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -6805,42 +6805,42 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>New Mexico @ Oklahoma</t>
+          <t>Nevada @ Middle Tennessee</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>-23.0</t>
+          <t>+3.8</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>-14.2</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>-15.4</t>
+          <t>+1.3</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>-10.8</t>
+          <t>+2.9</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -6860,27 +6860,27 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Northern Illinois @ Arizona</t>
+          <t>New Mexico @ Oklahoma</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>-34.5</t>
+          <t>-21.8</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>-26.4</t>
+          <t>-14.2</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>-21.7</t>
+          <t>-15.2</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>-30.9</t>
+          <t>-10.8</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="K30" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -6915,37 +6915,37 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>North Dakota State @ Sacramento State</t>
+          <t>Northern Illinois @ Arizona</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>+27.8</t>
+          <t>-33.8</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>+12.6</t>
+          <t>-26.4</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>+18.0</t>
+          <t>-20.3</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>+35.9</t>
+          <t>-30.9</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>+11.5</t>
+          <t>+11.7</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>-28.2</t>
+          <t>-28.0</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="L38" s="23" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="V38" s="23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="W38" s="23" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>+0.3</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="V39" s="23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="W39" s="23" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="V40" s="23" t="inlineStr">
         <is>
-          <t>+7.5</t>
+          <t>+7.6</t>
         </is>
       </c>
       <c r="W40" s="23" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>+4.2</t>
         </is>
       </c>
       <c r="L41" s="23" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="V41" s="23" t="inlineStr">
         <is>
-          <t>+12.5</t>
+          <t>+11.8</t>
         </is>
       </c>
       <c r="W41" s="23" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>-25.0</t>
+          <t>-24.9</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="L42" s="23" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="V42" s="23" t="inlineStr">
         <is>
-          <t>+5.8</t>
+          <t>+5.0</t>
         </is>
       </c>
       <c r="W42" s="23" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>+6.6</t>
+          <t>+7.2</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="L43" s="23" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="V43" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="W43" s="23" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
         <is>
-          <t>+0.3</t>
+          <t>+1.3</t>
         </is>
       </c>
       <c r="L44" s="23" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="V44" s="23" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="W44" s="23" t="inlineStr">
@@ -7961,57 +7961,57 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Fordham @ North Dakota State</t>
+          <t>Jacksonville State @ North Dakota State</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>0-38</t>
+          <t>7-33</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>-41.5</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>+38.0</t>
+          <t>+26.0</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>-40.9</t>
+          <t>-18.4</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>+11.6</t>
         </is>
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I45" s="24" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>-34.9</t>
+          <t>-14.0</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>+7.2</t>
         </is>
       </c>
       <c r="L45" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="M45" s="24" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="N45" s="23" t="inlineStr">
         <is>
-          <t>-58.5</t>
+          <t>-25.5</t>
         </is>
       </c>
       <c r="O45" s="23" t="inlineStr">
         <is>
-          <t>+17.0</t>
+          <t>+18.7</t>
         </is>
       </c>
       <c r="P45" s="23" t="inlineStr">
@@ -8034,9 +8034,9 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q45" s="25" t="inlineStr">
-        <is>
-          <t>Loss (seed week)</t>
+      <c r="Q45" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R45" s="23" t="inlineStr">
@@ -8046,27 +8046,27 @@
       </c>
       <c r="S45" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T45" s="24" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="U45" s="23" t="inlineStr">
         <is>
-          <t>+5.3</t>
+          <t>+17.6</t>
         </is>
       </c>
       <c r="V45" s="23" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>+6.6</t>
         </is>
       </c>
       <c r="W45" s="23" t="inlineStr">
         <is>
-          <t>+39.8</t>
+          <t>+41.6</t>
         </is>
       </c>
     </row>
@@ -8076,82 +8076,82 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Jacksonville State @ North Dakota State</t>
+          <t>Fordham @ North Dakota State</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>7-33</t>
+          <t>0-38</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-41.5</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>+26.0</t>
+          <t>+38.0</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>-18.4</t>
+          <t>-40.9</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>+11.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="H46" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>-36.0</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
+      <c r="L46" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M46" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N46" s="23" t="inlineStr">
+        <is>
+          <t>-58.5</t>
+        </is>
+      </c>
+      <c r="O46" s="23" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="P46" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>-14.8</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
-      <c r="L46" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M46" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N46" s="23" t="inlineStr">
-        <is>
-          <t>-25.5</t>
-        </is>
-      </c>
-      <c r="O46" s="23" t="inlineStr">
-        <is>
-          <t>+18.7</t>
-        </is>
-      </c>
-      <c r="P46" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q46" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
+      <c r="Q46" s="25" t="inlineStr">
+        <is>
+          <t>Loss (seed week)</t>
         </is>
       </c>
       <c r="R46" s="23" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="S46" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="U46" s="23" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="V46" s="23" t="inlineStr">
         <is>
-          <t>+1.2</t>
+          <t>+1.1</t>
         </is>
       </c>
       <c r="W46" s="23" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>-31.7</t>
+          <t>-33.1</t>
         </is>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-7.6</t>
         </is>
       </c>
       <c r="L47" s="23" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="V47" s="23" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="W47" s="23" t="inlineStr">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>+0.6</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="L48" s="23" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="V48" s="23" t="inlineStr">
         <is>
-          <t>-12.5</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="W48" s="23" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>+2.6</t>
+          <t>+2.3</t>
         </is>
       </c>
       <c r="L49" s="23" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="V49" s="23" t="inlineStr">
         <is>
-          <t>-9.9</t>
+          <t>-9.6</t>
         </is>
       </c>
       <c r="W49" s="23" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>-35.6</t>
+          <t>-35.5</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="L50" s="23" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="V50" s="23" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="W50" s="23" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>+13.8</t>
+          <t>+14.5</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.8</t>
         </is>
       </c>
       <c r="L51" s="23" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="V51" s="23" t="inlineStr">
         <is>
-          <t>-23.6</t>
+          <t>-24.1</t>
         </is>
       </c>
       <c r="W51" s="23" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>-12.8</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="K52" s="23" t="inlineStr">
         <is>
-          <t>+5.3</t>
+          <t>+5.4</t>
         </is>
       </c>
       <c r="L52" s="23" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="V52" s="23" t="inlineStr">
         <is>
-          <t>-18.3</t>
+          <t>-18.7</t>
         </is>
       </c>
       <c r="W52" s="23" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="J53" s="23" t="inlineStr">
         <is>
-          <t>-11.2</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="K53" s="23" t="inlineStr">
         <is>
-          <t>+16.2</t>
+          <t>+17.5</t>
         </is>
       </c>
       <c r="L53" s="23" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="V53" s="23" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="W53" s="23" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>-27.6</t>
+          <t>-27.1</t>
         </is>
       </c>
       <c r="K54" s="23" t="inlineStr">
         <is>
-          <t>-14.7</t>
+          <t>-15.2</t>
         </is>
       </c>
       <c r="L54" s="23" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="V54" s="23" t="inlineStr">
         <is>
-          <t>-16.8</t>
+          <t>-16.4</t>
         </is>
       </c>
       <c r="W54" s="23" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>+1.4</t>
+          <t>+1.9</t>
         </is>
       </c>
       <c r="K55" s="23" t="inlineStr">
         <is>
-          <t>+1.3</t>
+          <t>+0.9</t>
         </is>
       </c>
       <c r="L55" s="23" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="V55" s="23" t="inlineStr">
         <is>
-          <t>-15.4</t>
+          <t>-15.5</t>
         </is>
       </c>
       <c r="W55" s="23" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="J56" s="23" t="inlineStr">
         <is>
-          <t>-16.3</t>
+          <t>-15.6</t>
         </is>
       </c>
       <c r="K56" s="23" t="inlineStr">
         <is>
-          <t>+18.8</t>
+          <t>+18.1</t>
         </is>
       </c>
       <c r="L56" s="23" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="V56" s="23" t="inlineStr">
         <is>
-          <t>+3.4</t>
+          <t>+2.6</t>
         </is>
       </c>
       <c r="W56" s="23" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>-27.6</t>
+          <t>-27.9</t>
         </is>
       </c>
       <c r="K57" s="23" t="inlineStr">
         <is>
-          <t>+6.1</t>
+          <t>+6.4</t>
         </is>
       </c>
       <c r="L57" s="23" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="V57" s="23" t="inlineStr">
         <is>
-          <t>+9.5</t>
+          <t>+9.0</t>
         </is>
       </c>
       <c r="W57" s="23" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="J58" s="23" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-20.1</t>
         </is>
       </c>
       <c r="K58" s="23" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="L58" s="23" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="V58" s="23" t="inlineStr">
         <is>
-          <t>+2.2</t>
+          <t>+1.9</t>
         </is>
       </c>
       <c r="W58" s="23" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="V59" s="23" t="inlineStr">
         <is>
-          <t>+0.4</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="W59" s="23" t="inlineStr">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1216,7 +1216,7 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="J6" t="n">
         <v>50.5</v>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -953,28 +953,25 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>UNLV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Central Michigan</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="G2" s="6">
         <f>F2-E2</f>
@@ -985,10 +982,7 @@
         <v/>
       </c>
       <c r="I2" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>38.8</v>
+        <v>49.1</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -1011,28 +1005,25 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UTEP</t>
+          <t>Northern Illinois</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Georgia State</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-29.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-34.8</v>
+        <v>-7.8</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -1043,10 +1034,7 @@
         <v/>
       </c>
       <c r="I3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>48.5</v>
+        <v>43.3</v>
       </c>
       <c r="K3" s="6">
         <f>I3-J3</f>
@@ -1067,28 +1055,25 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Hawai'i</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Middle Tennessee</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
@@ -1099,10 +1084,7 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>50.5</v>
+        <v>42.9</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -1123,11 +1105,11 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,14 +1119,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>New Mexico State</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-21.8</v>
+        <v>18.8</v>
       </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
@@ -1155,10 +1134,7 @@
         <v/>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
-      </c>
-      <c r="J5" t="n">
-        <v>45.5</v>
+        <v>47.1</v>
       </c>
       <c r="K5" s="6">
         <f>I5-J5</f>
@@ -1184,28 +1160,25 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>North Dakota State</t>
+          <t>Oregon State</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sacramento State</t>
+          <t>UTEP</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="G6" s="6">
         <f>F6-E6</f>
@@ -1216,10 +1189,7 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -1245,29 +1215,27 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Northern Illinois</t>
+          <t>Air Force</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-30.9</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>-33.8</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="F7" s="10" t="n"/>
       <c r="G7" s="10">
         <f>F7-E7</f>
         <v/>
@@ -1277,11 +1245,9 @@
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>50.2</v>
-      </c>
+        <v>47.2</v>
+      </c>
+      <c r="J7" s="10" t="n"/>
       <c r="K7" s="10">
         <f>I7-J7</f>
         <v/>
@@ -1305,30 +1271,6 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Fresno State</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>San José State</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6.5</v>
-      </c>
       <c r="G8" s="6">
         <f>F8-E8</f>
         <v/>
@@ -1336,12 +1278,6 @@
       <c r="H8" s="6">
         <f>IF(G8=0,"Pick'em",IF(G8&gt;0,"Home","Away"))</f>
         <v/>
-      </c>
-      <c r="I8" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>49.8</v>
       </c>
       <c r="K8" s="6">
         <f>I8-J8</f>
@@ -5418,7 +5354,7 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>1748.4</v>
+        <v>1760.7</v>
       </c>
       <c r="E2" s="9" t="n">
         <v>4.2</v>
@@ -5492,7 +5428,7 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>1589.7</v>
+        <v>1575.5</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>5</v>
@@ -5603,7 +5539,7 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1417.7</v>
+        <v>1399.2</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>-13.7</v>
@@ -5640,7 +5576,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1394.7</v>
+        <v>1385.2</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>-16.9</v>
@@ -5677,7 +5613,7 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1451.7</v>
+        <v>1428.8</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>-12.5</v>
@@ -5714,7 +5650,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1411.8</v>
+        <v>1393.9</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>-7.6</v>
@@ -5751,7 +5687,7 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1382.6</v>
+        <v>1375.4</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>-16.2</v>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.9</v>
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14</v>
       </c>
       <c r="G2" s="6">
         <f>F2-E2</f>
@@ -983,6 +986,9 @@
       </c>
       <c r="I2" t="n">
         <v>49.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>49.5</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -1025,6 +1031,9 @@
       <c r="E3" t="n">
         <v>-7.8</v>
       </c>
+      <c r="F3" t="n">
+        <v>-8.5</v>
+      </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
         <v/>
@@ -1035,6 +1044,9 @@
       </c>
       <c r="I3" t="n">
         <v>43.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>54.5</v>
       </c>
       <c r="K3" s="6">
         <f>I3-J3</f>
@@ -1075,6 +1087,9 @@
       <c r="E4" t="n">
         <v>1.9</v>
       </c>
+      <c r="F4" t="n">
+        <v>5.5</v>
+      </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
         <v/>
@@ -1085,6 +1100,9 @@
       </c>
       <c r="I4" t="n">
         <v>42.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44.5</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -1125,6 +1143,9 @@
       <c r="E5" t="n">
         <v>18.8</v>
       </c>
+      <c r="F5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
         <v/>
@@ -1135,6 +1156,9 @@
       </c>
       <c r="I5" t="n">
         <v>47.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>49.5</v>
       </c>
       <c r="K5" s="6">
         <f>I5-J5</f>
@@ -1233,7 +1257,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10">
@@ -5360,10 +5384,10 @@
         <v>4.2</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0.1779024536014308</v>
+        <v>0.156824607490598</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>-0.1642277760509774</v>
+        <v>-0.1560976801881319</v>
       </c>
       <c r="H2" s="9" t="n">
         <v>117</v>
@@ -5434,10 +5458,10 @@
         <v>5</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.2352301586935283</v>
+        <v>0.1020851442163246</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>-0.298944742674818</v>
+        <v>-0.2195335782064906</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>87</v>
@@ -5545,10 +5569,10 @@
         <v>-13.7</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>-0.002827735068849334</v>
+        <v>0.04058174869502743</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.06489075558866486</v>
+        <v>0.1412199979036408</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>114</v>
@@ -5582,10 +5606,10 @@
         <v>-16.9</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.2402103302415052</v>
+        <v>-0.1421253070922879</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.003955245944769085</v>
+        <v>0.1376337108568448</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>82</v>
@@ -5619,10 +5643,10 @@
         <v>-12.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.1640411560777529</v>
+        <v>0.08220884405806574</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.07569306543146938</v>
+        <v>0.06609743084098561</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>129</v>
@@ -5656,10 +5680,10 @@
         <v>-7.6</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.1253495981030349</v>
+        <v>0.07825850329211136</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.08041411531454036</v>
+        <v>0.1036882953044283</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>98</v>
@@ -5693,10 +5717,10 @@
         <v>-16.2</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>-0.134943446773656</v>
+        <v>-0.1670547546022537</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.1797364798378445</v>
+        <v>0.2343692976201658</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>92</v>
@@ -5719,7 +5743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W59"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5837,46 +5861,46 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>8619</v>
+        <v>8693</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>+12.1%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="I6" s="23" t="n">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t>74/186 (40%)</t>
+          <t>106/260 (41%)</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
         <is>
-          <t>+743.4</t>
+          <t>+808.1</t>
         </is>
       </c>
     </row>
@@ -5887,46 +5911,46 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>+38.8%</t>
+          <t>+31.7%</t>
         </is>
       </c>
       <c r="I7" s="23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>5/22 (23%)</t>
+          <t>7/29 (24%)</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
         <is>
-          <t>+120.7</t>
+          <t>+106.2</t>
         </is>
       </c>
     </row>
@@ -5937,46 +5961,46 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>8619</v>
+        <v>8693</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>8549</v>
+        <v>8622</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>4273</v>
+        <v>4316</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>4276</v>
+        <v>4306</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="I8" s="23" t="n">
-        <v>6762</v>
+        <v>6826</v>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr">
         <is>
-          <t>4093/8619 (47%)</t>
+          <t>4102/8693 (47%)</t>
         </is>
       </c>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t>+5563.6</t>
+          <t>+5473.7</t>
         </is>
       </c>
     </row>
@@ -5987,46 +6011,46 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F9" s="23" t="n">
         <v>12</v>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="I9" s="23" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>456/978 (47%)</t>
+          <t>461/985 (47%)</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
         <is>
-          <t>+591.7</t>
+          <t>+608.7</t>
         </is>
       </c>
     </row>
@@ -6037,46 +6061,46 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>8619</v>
+        <v>8693</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>8549</v>
+        <v>8622</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>4273</v>
+        <v>4359</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4276</v>
+        <v>4263</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="I10" s="23" t="n">
-        <v>6734</v>
+        <v>6745</v>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>4452/8619 (52%)</t>
+          <t>4485/8693 (52%)</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t>+732.6</t>
+          <t>+346.5</t>
         </is>
       </c>
     </row>
@@ -6087,46 +6111,46 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="F11" s="23" t="n">
         <v>12</v>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="I11" s="23" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>517/978 (53%)</t>
+          <t>517/985 (52%)</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t>+985.9</t>
+          <t>+872.3</t>
         </is>
       </c>
     </row>
@@ -6206,46 +6230,46 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>186</v>
+        <v>260</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="E15" s="23" t="n">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="23" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>+12.1%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="I15" s="23" t="n">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K15" s="23" t="inlineStr">
         <is>
-          <t>74/186 (40%)</t>
+          <t>106/260 (41%)</t>
         </is>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
-          <t>+743.4</t>
+          <t>+808.1</t>
         </is>
       </c>
     </row>
@@ -6256,46 +6280,46 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E16" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>+38.8%</t>
+          <t>+31.7%</t>
         </is>
       </c>
       <c r="I16" s="23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
         <is>
-          <t>5/22 (23%)</t>
+          <t>7/29 (24%)</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
         <is>
-          <t>+120.7</t>
+          <t>+106.2</t>
         </is>
       </c>
     </row>
@@ -6306,46 +6330,46 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>186</v>
+        <v>260</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="I17" s="23" t="n">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>53/186 (28%)</t>
+          <t>71/260 (27%)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
         <is>
-          <t>-531.3</t>
+          <t>-621.2</t>
         </is>
       </c>
     </row>
@@ -6356,46 +6380,46 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>+11.9%</t>
         </is>
       </c>
       <c r="I18" s="23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>6/22 (27%)</t>
+          <t>8/29 (28%)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+19.1</t>
         </is>
       </c>
     </row>
@@ -6406,46 +6430,46 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>186</v>
+        <v>260</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="I19" s="23" t="n">
-        <v>155</v>
+        <v>219</v>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>59/186 (32%)</t>
+          <t>83/260 (32%)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
-          <t>-360.6</t>
+          <t>-580.8</t>
         </is>
       </c>
     </row>
@@ -6456,53 +6480,53 @@
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="I20" s="23" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>11/22 (50%)</t>
+          <t>14/29 (48%)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>-6.1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Ridge and XGBoost (the two candidates) agree with each other in 76.9% of all graded games. Ridge agrees with the live model (Gamma) in 47.8% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 61.3% of games it has a rating for.</t>
+          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.2% of all graded games. Ridge agrees with the live model (Gamma) in 53.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 62.7% of games it has a rating for.</t>
         </is>
       </c>
     </row>
@@ -6572,31 +6596,31 @@
     </row>
     <row r="26">
       <c r="A26" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>North Dakota State @ Sacramento State</t>
+          <t>UNLV @ Akron</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>+27.0</t>
+          <t>+14.0</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>+12.6</t>
+          <t>+1.4</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>+18.3</t>
+          <t>+9.7</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>+35.9</t>
+          <t>+4.0</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -6611,7 +6635,7 @@
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -6627,31 +6651,31 @@
     </row>
     <row r="27">
       <c r="A27" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>Wyoming @ Central Michigan</t>
+          <t>Northern Illinois @ Georgia State</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>+1.2</t>
+          <t>-8.5</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>-8.8</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -6661,67 +6685,67 @@
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>UTEP @ Michigan</t>
+          <t>Hawai'i @ Wyoming</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>-34.8</t>
+          <t>+5.5</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>-35.0</t>
+          <t>+6.1</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>-31.5</t>
+          <t>+0.4</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>-29.7</t>
+          <t>+1.9</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -6737,31 +6761,31 @@
     </row>
     <row r="29">
       <c r="A29" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Nevada @ Middle Tennessee</t>
+          <t>New Mexico @ New Mexico State</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>+3.8</t>
+          <t>+12.5</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>+6.7</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>+1.3</t>
+          <t>+12.8</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>+2.9</t>
+          <t>+18.8</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -6771,318 +6795,378 @@
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>New Mexico @ Oklahoma</t>
+          <t>Oregon State @ UTEP</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>-21.8</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>-14.2</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>-15.2</t>
+          <t>+0.8</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>-10.8</t>
+          <t>+10.5</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Northern Illinois @ Arizona</t>
+          <t>Air Force @ Nevada</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>-33.8</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>-26.4</t>
+          <t>+3.5</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>-20.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>-30.9</t>
+          <t>+2.3</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>* Tightest (Live) compares each model's line to TODAY's still-moving market line, not a final closing line -- it will keep changing until kickoff. See the graded Game-by-Game table below for the real, closing-line version of this comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>2026 Mountain West Games -- Game by Game</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Matchup</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Final Score</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Vegas Spread (Home)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>Actual Margin (Home)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Line</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Edge</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Lean</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Result</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Line</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Edge</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Lean</t>
+        </is>
+      </c>
+      <c r="M36" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost Result</t>
+        </is>
+      </c>
+      <c r="N36" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Line</t>
+        </is>
+      </c>
+      <c r="O36" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Edge</t>
+        </is>
+      </c>
+      <c r="P36" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Lean</t>
+        </is>
+      </c>
+      <c r="Q36" s="22" t="inlineStr">
+        <is>
+          <t>Gamma Result</t>
+        </is>
+      </c>
+      <c r="R36" s="22" t="inlineStr">
+        <is>
+          <t>Ridge/XGBoost Agree?</t>
+        </is>
+      </c>
+      <c r="S36" s="22" t="inlineStr">
+        <is>
+          <t>Ridge Agrees (w/ Live Model)?</t>
+        </is>
+      </c>
+      <c r="T36" s="22" t="inlineStr">
+        <is>
+          <t>Tightest CLV Line</t>
+        </is>
+      </c>
+      <c r="U36" s="22" t="inlineStr">
+        <is>
+          <t>Ridge CLV Pts (Cum.)</t>
+        </is>
+      </c>
+      <c r="V36" s="22" t="inlineStr">
+        <is>
+          <t>XGBoost CLV Pts (Cum.)</t>
+        </is>
+      </c>
+      <c r="W36" s="22" t="inlineStr">
+        <is>
+          <t>Gamma CLV Pts (Cum.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Duquesne @ Air Force</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>0-34</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>-30.0</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>+34.0</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>-17.0</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="I37" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>-28.4</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="L37" s="23" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I31" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
+      <c r="M37" s="25" t="inlineStr">
+        <is>
+          <t>Loss (no real edge)</t>
+        </is>
+      </c>
+      <c r="N37" s="23" t="inlineStr">
+        <is>
+          <t>-36.5</t>
+        </is>
+      </c>
+      <c r="O37" s="23" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+      <c r="P37" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q37" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R37" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K31" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>Fresno State @ San José State</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="S37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U37" s="23" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="V37" s="23" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="W37" s="23" t="inlineStr">
         <is>
           <t>+6.5</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>+11.7</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="H32" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I32" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>* Tightest (Live) compares each model's line to TODAY's still-moving market line, not a final closing line -- it will keep changing until kickoff. See the graded Game-by-Game table below for the real, closing-line version of this comparison.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>2026 Mountain West Games -- Game by Game</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>Matchup</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="inlineStr">
-        <is>
-          <t>Final Score</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="inlineStr">
-        <is>
-          <t>Vegas Spread (Home)</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>Actual Margin (Home)</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="inlineStr">
-        <is>
-          <t>Ridge Line</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr">
-        <is>
-          <t>Ridge Edge</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
-        <is>
-          <t>Ridge Lean</t>
-        </is>
-      </c>
-      <c r="I37" s="22" t="inlineStr">
-        <is>
-          <t>Ridge Result</t>
-        </is>
-      </c>
-      <c r="J37" s="22" t="inlineStr">
-        <is>
-          <t>XGBoost Line</t>
-        </is>
-      </c>
-      <c r="K37" s="22" t="inlineStr">
-        <is>
-          <t>XGBoost Edge</t>
-        </is>
-      </c>
-      <c r="L37" s="22" t="inlineStr">
-        <is>
-          <t>XGBoost Lean</t>
-        </is>
-      </c>
-      <c r="M37" s="22" t="inlineStr">
-        <is>
-          <t>XGBoost Result</t>
-        </is>
-      </c>
-      <c r="N37" s="22" t="inlineStr">
-        <is>
-          <t>Gamma Line</t>
-        </is>
-      </c>
-      <c r="O37" s="22" t="inlineStr">
-        <is>
-          <t>Gamma Edge</t>
-        </is>
-      </c>
-      <c r="P37" s="22" t="inlineStr">
-        <is>
-          <t>Gamma Lean</t>
-        </is>
-      </c>
-      <c r="Q37" s="22" t="inlineStr">
-        <is>
-          <t>Gamma Result</t>
-        </is>
-      </c>
-      <c r="R37" s="22" t="inlineStr">
-        <is>
-          <t>Ridge/XGBoost Agree?</t>
-        </is>
-      </c>
-      <c r="S37" s="22" t="inlineStr">
-        <is>
-          <t>Ridge Agrees (w/ Live Model)?</t>
-        </is>
-      </c>
-      <c r="T37" s="22" t="inlineStr">
-        <is>
-          <t>Tightest CLV Line</t>
-        </is>
-      </c>
-      <c r="U37" s="22" t="inlineStr">
-        <is>
-          <t>Ridge CLV Pts (Cum.)</t>
-        </is>
-      </c>
-      <c r="V37" s="22" t="inlineStr">
-        <is>
-          <t>XGBoost CLV Pts (Cum.)</t>
-        </is>
-      </c>
-      <c r="W37" s="22" t="inlineStr">
-        <is>
-          <t>Gamma CLV Pts (Cum.)</t>
         </is>
       </c>
     </row>
@@ -7092,59 +7176,59 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Duquesne @ Air Force</t>
+          <t>Wyoming @ Colorado State</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>0-34</t>
+          <t>13-35</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>-30.0</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>+34.0</t>
+          <t>+22.0</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>-17.0</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>+5.1</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I38" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>-28.0</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="L38" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
       <c r="M38" s="25" t="inlineStr">
         <is>
           <t>Loss (no real edge)</t>
@@ -7152,12 +7236,12 @@
       </c>
       <c r="N38" s="23" t="inlineStr">
         <is>
-          <t>-36.5</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="O38" s="23" t="inlineStr">
         <is>
-          <t>+6.5</t>
+          <t>+3.7</t>
         </is>
       </c>
       <c r="P38" s="23" t="inlineStr">
@@ -7172,14 +7256,14 @@
       </c>
       <c r="R38" s="23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S38" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S38" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
           <t>XGBoost</t>
@@ -7187,17 +7271,17 @@
       </c>
       <c r="U38" s="23" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="V38" s="23" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="W38" s="23" t="inlineStr">
         <is>
-          <t>+6.5</t>
+          <t>+10.2</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7291,32 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>Wyoming @ Colorado State</t>
+          <t>San José State @ Eastern Michigan</t>
         </is>
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>13-35</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>+22.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-15.8</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t>+5.1</t>
+          <t>+14.3</t>
         </is>
       </c>
       <c r="H39" s="23" t="inlineStr">
@@ -7240,44 +7324,44 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="I39" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
+          <t>+9.4</t>
+        </is>
+      </c>
+      <c r="L39" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M39" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N39" s="23" t="inlineStr">
+        <is>
           <t>+0.5</t>
         </is>
       </c>
-      <c r="L39" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M39" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N39" s="23" t="inlineStr">
-        <is>
-          <t>-6.4</t>
-        </is>
-      </c>
       <c r="O39" s="23" t="inlineStr">
         <is>
-          <t>+3.7</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="P39" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="Q39" s="24" t="inlineStr">
@@ -7292,27 +7376,27 @@
       </c>
       <c r="S39" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="U39" s="23" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>+6.4</t>
         </is>
       </c>
       <c r="V39" s="23" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+7.7</t>
         </is>
       </c>
       <c r="W39" s="23" t="inlineStr">
         <is>
-          <t>+10.2</t>
+          <t>+8.2</t>
         </is>
       </c>
     </row>
@@ -7322,72 +7406,72 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>San José State @ Eastern Michigan</t>
+          <t>UNLV @ Hawai'i</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>21-6</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+2.8</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>-15.8</t>
+          <t>+2.9</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>+14.3</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="H40" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>+5.4</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I40" s="25" t="inlineStr">
+      <c r="M40" s="25" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>-10.6</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>+9.1</t>
-        </is>
-      </c>
-      <c r="L40" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M40" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
       <c r="N40" s="23" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+4.4</t>
         </is>
       </c>
       <c r="O40" s="23" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="P40" s="23" t="inlineStr">
@@ -7397,37 +7481,37 @@
       </c>
       <c r="Q40" s="24" t="inlineStr">
         <is>
-          <t>Win (seed week)</t>
+          <t>Win (no real edge) (seed week)</t>
         </is>
       </c>
       <c r="R40" s="23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S40" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S40" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="U40" s="23" t="inlineStr">
         <is>
-          <t>+6.4</t>
+          <t>+6.2</t>
         </is>
       </c>
       <c r="V40" s="23" t="inlineStr">
         <is>
-          <t>+7.6</t>
+          <t>+13.1</t>
         </is>
       </c>
       <c r="W40" s="23" t="inlineStr">
         <is>
-          <t>+8.2</t>
+          <t>+6.5</t>
         </is>
       </c>
     </row>
@@ -7437,112 +7521,112 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>UNLV @ Hawai'i</t>
+          <t>Northern Illinois @ Iowa</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>21-6</t>
+          <t>0-40</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
+          <t>-31.8</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>+40.0</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>-28.3</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I41" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>-25.4</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
+      <c r="L41" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M41" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N41" s="23" t="inlineStr">
+        <is>
+          <t>-41.0</t>
+        </is>
+      </c>
+      <c r="O41" s="23" t="inlineStr">
+        <is>
+          <t>+9.2</t>
+        </is>
+      </c>
+      <c r="P41" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q41" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R41" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S41" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U41" s="23" t="inlineStr">
+        <is>
           <t>+2.8</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>+4.2</t>
-        </is>
-      </c>
-      <c r="L41" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M41" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N41" s="23" t="inlineStr">
-        <is>
-          <t>+4.4</t>
-        </is>
-      </c>
-      <c r="O41" s="23" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="P41" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q41" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge) (seed week)</t>
-        </is>
-      </c>
-      <c r="R41" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S41" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U41" s="23" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
       <c r="V41" s="23" t="inlineStr">
         <is>
-          <t>+11.8</t>
+          <t>+6.8</t>
         </is>
       </c>
       <c r="W41" s="23" t="inlineStr">
         <is>
-          <t>+6.5</t>
+          <t>+15.8</t>
         </is>
       </c>
     </row>
@@ -7552,32 +7636,32 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Northern Illinois @ Iowa</t>
+          <t>Western Kentucky @ Nevada</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>0-40</t>
+          <t>14-49</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>-31.8</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>+40.0</t>
+          <t>+35.0</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>-28.3</t>
+          <t>+3.3</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="H42" s="23" t="inlineStr">
@@ -7592,12 +7676,12 @@
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>-24.9</t>
+          <t>+7.6</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="L42" s="23" t="inlineStr">
@@ -7612,12 +7696,12 @@
       </c>
       <c r="N42" s="23" t="inlineStr">
         <is>
-          <t>-41.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="O42" s="23" t="inlineStr">
         <is>
-          <t>+9.2</t>
+          <t>+2.7</t>
         </is>
       </c>
       <c r="P42" s="23" t="inlineStr">
@@ -7642,22 +7726,22 @@
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="U42" s="23" t="inlineStr">
         <is>
-          <t>+2.8</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="V42" s="23" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="W42" s="23" t="inlineStr">
         <is>
-          <t>+15.8</t>
+          <t>+18.5</t>
         </is>
       </c>
     </row>
@@ -7667,72 +7751,72 @@
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Western Kentucky @ Nevada</t>
+          <t>Central Michigan @ New Mexico</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>14-49</t>
+          <t>7-38</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>-11.2</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>+35.0</t>
+          <t>+31.0</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>+3.3</t>
+          <t>-17.5</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>+6.2</t>
         </is>
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="L43" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I43" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>+7.2</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr">
-        <is>
-          <t>-6.9</t>
-        </is>
-      </c>
-      <c r="L43" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
       <c r="M43" s="25" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Loss (no real edge)</t>
         </is>
       </c>
       <c r="N43" s="23" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-15.6</t>
         </is>
       </c>
       <c r="O43" s="23" t="inlineStr">
         <is>
-          <t>+2.7</t>
+          <t>+4.3</t>
         </is>
       </c>
       <c r="P43" s="23" t="inlineStr">
@@ -7747,32 +7831,32 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S43" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S43" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="U43" s="23" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>+5.9</t>
         </is>
       </c>
       <c r="V43" s="23" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="W43" s="23" t="inlineStr">
         <is>
-          <t>+18.5</t>
+          <t>+22.9</t>
         </is>
       </c>
     </row>
@@ -7782,82 +7866,82 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Central Michigan @ New Mexico</t>
+          <t>Fordham @ North Dakota State</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>7-38</t>
+          <t>0-38</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>-11.2</t>
+          <t>-41.5</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>+31.0</t>
+          <t>+38.0</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>-17.5</t>
+          <t>-40.9</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
-          <t>+6.2</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="H44" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>-36.1</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>-5.4</t>
+        </is>
+      </c>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M44" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N44" s="23" t="inlineStr">
+        <is>
+          <t>-58.5</t>
+        </is>
+      </c>
+      <c r="O44" s="23" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="P44" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>-12.5</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
-      <c r="L44" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M44" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N44" s="23" t="inlineStr">
-        <is>
-          <t>-15.6</t>
-        </is>
-      </c>
-      <c r="O44" s="23" t="inlineStr">
-        <is>
-          <t>+4.3</t>
-        </is>
-      </c>
-      <c r="P44" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q44" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
+      <c r="Q44" s="25" t="inlineStr">
+        <is>
+          <t>Loss (seed week)</t>
         </is>
       </c>
       <c r="R44" s="23" t="inlineStr">
@@ -7867,27 +7951,27 @@
       </c>
       <c r="S44" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="U44" s="23" t="inlineStr">
         <is>
-          <t>+5.9</t>
+          <t>+5.3</t>
         </is>
       </c>
       <c r="V44" s="23" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="W44" s="23" t="inlineStr">
         <is>
-          <t>+22.9</t>
+          <t>+39.8</t>
         </is>
       </c>
     </row>
@@ -7937,7 +8021,7 @@
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-13.9</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
@@ -7992,17 +8076,17 @@
       </c>
       <c r="U45" s="23" t="inlineStr">
         <is>
-          <t>+17.6</t>
+          <t>+16.9</t>
         </is>
       </c>
       <c r="V45" s="23" t="inlineStr">
         <is>
-          <t>+6.6</t>
+          <t>+0.4</t>
         </is>
       </c>
       <c r="W45" s="23" t="inlineStr">
         <is>
-          <t>+41.6</t>
+          <t>+58.5</t>
         </is>
       </c>
     </row>
@@ -8012,32 +8096,32 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Fordham @ North Dakota State</t>
+          <t>UTEP @ Oklahoma</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>0-38</t>
+          <t>0-51</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>-41.5</t>
+          <t>-40.8</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>+38.0</t>
+          <t>+51.0</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>-40.9</t>
+          <t>-34.8</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="H46" s="23" t="inlineStr">
@@ -8045,19 +8129,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
+      <c r="I46" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>-36.0</t>
+          <t>-32.1</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-8.6</t>
         </is>
       </c>
       <c r="L46" s="23" t="inlineStr">
@@ -8065,19 +8149,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="M46" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="M46" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="N46" s="23" t="inlineStr">
         <is>
-          <t>-58.5</t>
+          <t>-44.4</t>
         </is>
       </c>
       <c r="O46" s="23" t="inlineStr">
         <is>
-          <t>+17.0</t>
+          <t>+3.6</t>
         </is>
       </c>
       <c r="P46" s="23" t="inlineStr">
@@ -8085,9 +8169,9 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q46" s="25" t="inlineStr">
-        <is>
-          <t>Loss (seed week)</t>
+      <c r="Q46" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R46" s="23" t="inlineStr">
@@ -8102,22 +8186,22 @@
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="U46" s="23" t="inlineStr">
         <is>
-          <t>+16.9</t>
+          <t>+11.0</t>
         </is>
       </c>
       <c r="V46" s="23" t="inlineStr">
         <is>
-          <t>+1.1</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="W46" s="23" t="inlineStr">
         <is>
-          <t>+58.5</t>
+          <t>+62.1</t>
         </is>
       </c>
     </row>
@@ -8127,32 +8211,32 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>UTEP @ Oklahoma</t>
+          <t>Hawai'i @ Stanford</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>0-51</t>
+          <t>27-37</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>-40.8</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>+51.0</t>
+          <t>+10.0</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>-34.8</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="H47" s="23" t="inlineStr">
@@ -8167,12 +8251,12 @@
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>-33.1</t>
+          <t>+0.7</t>
         </is>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>-7.6</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="L47" s="23" t="inlineStr">
@@ -8187,12 +8271,12 @@
       </c>
       <c r="N47" s="23" t="inlineStr">
         <is>
-          <t>-44.4</t>
+          <t>-11.2</t>
         </is>
       </c>
       <c r="O47" s="23" t="inlineStr">
         <is>
-          <t>+3.6</t>
+          <t>+6.4</t>
         </is>
       </c>
       <c r="P47" s="23" t="inlineStr">
@@ -8217,22 +8301,22 @@
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="U47" s="23" t="inlineStr">
         <is>
-          <t>+11.0</t>
+          <t>+7.7</t>
         </is>
       </c>
       <c r="V47" s="23" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-13.7</t>
         </is>
       </c>
       <c r="W47" s="23" t="inlineStr">
         <is>
-          <t>+62.1</t>
+          <t>+68.5</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8326,12 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Hawai'i @ Stanford</t>
+          <t>Memphis @ UNLV</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>27-37</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
@@ -8257,64 +8341,64 @@
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>+10.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>+6.2</t>
         </is>
       </c>
       <c r="H48" s="23" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I48" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>-7.2</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>+2.4</t>
+        </is>
+      </c>
+      <c r="L48" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M48" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N48" s="23" t="inlineStr">
+        <is>
+          <t>+1.6</t>
+        </is>
+      </c>
+      <c r="O48" s="23" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
+      <c r="P48" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I48" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr">
-        <is>
-          <t>-5.4</t>
-        </is>
-      </c>
-      <c r="L48" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M48" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N48" s="23" t="inlineStr">
-        <is>
-          <t>-11.2</t>
-        </is>
-      </c>
-      <c r="O48" s="23" t="inlineStr">
-        <is>
-          <t>+6.4</t>
-        </is>
-      </c>
-      <c r="P48" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
       <c r="Q48" s="24" t="inlineStr">
         <is>
           <t>Win (seed week)</t>
@@ -8332,22 +8416,22 @@
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="U48" s="23" t="inlineStr">
         <is>
-          <t>+7.7</t>
+          <t>+13.9</t>
         </is>
       </c>
       <c r="V48" s="23" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.3</t>
         </is>
       </c>
       <c r="W48" s="23" t="inlineStr">
         <is>
-          <t>+68.5</t>
+          <t>+62.2</t>
         </is>
       </c>
     </row>
@@ -8357,72 +8441,72 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>Memphis @ UNLV</t>
+          <t>San José State @ USC</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>26-42</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-37.2</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>+16.0</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-34.6</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>+6.2</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I49" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>-7.1</t>
+          <t>-36.0</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>+2.3</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="L49" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M49" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M49" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
         </is>
       </c>
       <c r="N49" s="23" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>-30.3</t>
         </is>
       </c>
       <c r="O49" s="23" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="P49" s="23" t="inlineStr">
@@ -8442,7 +8526,7 @@
       </c>
       <c r="S49" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T49" s="24" t="inlineStr">
@@ -8452,52 +8536,52 @@
       </c>
       <c r="U49" s="23" t="inlineStr">
         <is>
-          <t>+13.9</t>
+          <t>+11.2</t>
         </is>
       </c>
       <c r="V49" s="23" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="W49" s="23" t="inlineStr">
         <is>
-          <t>+62.2</t>
+          <t>+55.2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>San José State @ USC</t>
+          <t>North Dakota State @ Air Force</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>26-42</t>
+          <t>38-32</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>-37.2</t>
+          <t>+1.8</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>+16.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>-34.6</t>
+          <t>+17.0</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-15.3</t>
         </is>
       </c>
       <c r="H50" s="23" t="inlineStr">
@@ -8512,12 +8596,12 @@
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>-35.5</t>
+          <t>+14.2</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="L50" s="23" t="inlineStr">
@@ -8527,17 +8611,17 @@
       </c>
       <c r="M50" s="24" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="N50" s="23" t="inlineStr">
         <is>
-          <t>-30.3</t>
+          <t>+17.9</t>
         </is>
       </c>
       <c r="O50" s="23" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-16.2</t>
         </is>
       </c>
       <c r="P50" s="23" t="inlineStr">
@@ -8547,7 +8631,7 @@
       </c>
       <c r="Q50" s="24" t="inlineStr">
         <is>
-          <t>Win (seed week)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="R50" s="23" t="inlineStr">
@@ -8567,17 +8651,17 @@
       </c>
       <c r="U50" s="23" t="inlineStr">
         <is>
-          <t>+11.2</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="V50" s="23" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-25.0</t>
         </is>
       </c>
       <c r="W50" s="23" t="inlineStr">
         <is>
-          <t>+55.2</t>
+          <t>+39.0</t>
         </is>
       </c>
     </row>
@@ -8587,37 +8671,37 @@
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>North Dakota State @ Air Force</t>
+          <t>New Mexico State @ Hawai'i</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>38-32</t>
+          <t>19-29</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>+1.8</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>+10.0</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>+17.0</t>
+          <t>-14.1</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>-15.3</t>
+          <t>+6.6</t>
         </is>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I51" s="24" t="inlineStr">
@@ -8627,17 +8711,17 @@
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>+14.5</t>
+          <t>-13.6</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>-12.8</t>
+          <t>+6.1</t>
         </is>
       </c>
       <c r="L51" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="M51" s="24" t="inlineStr">
@@ -8647,22 +8731,22 @@
       </c>
       <c r="N51" s="23" t="inlineStr">
         <is>
-          <t>+17.9</t>
+          <t>-7.6</t>
         </is>
       </c>
       <c r="O51" s="23" t="inlineStr">
         <is>
-          <t>-16.2</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="P51" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="Q51" s="24" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Win (no real edge)</t>
         </is>
       </c>
       <c r="R51" s="23" t="inlineStr">
@@ -8677,22 +8761,22 @@
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="U51" s="23" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="V51" s="23" t="inlineStr">
         <is>
-          <t>-24.1</t>
+          <t>-19.0</t>
         </is>
       </c>
       <c r="W51" s="23" t="inlineStr">
         <is>
-          <t>+39.0</t>
+          <t>+39.1</t>
         </is>
       </c>
     </row>
@@ -8702,32 +8786,32 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>New Mexico State @ Hawai'i</t>
+          <t>Montana State @ Nevada</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
-          <t>19-29</t>
+          <t>20-7</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>+5.0</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>+10.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>-14.1</t>
+          <t>-17.2</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
-          <t>+6.6</t>
+          <t>+22.2</t>
         </is>
       </c>
       <c r="H52" s="23" t="inlineStr">
@@ -8735,19 +8819,19 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="I52" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="K52" s="23" t="inlineStr">
         <is>
-          <t>+5.4</t>
+          <t>+17.6</t>
         </is>
       </c>
       <c r="L52" s="23" t="inlineStr">
@@ -8755,19 +8839,19 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="M52" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="M52" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="N52" s="23" t="inlineStr">
         <is>
-          <t>-7.6</t>
+          <t>-33.6</t>
         </is>
       </c>
       <c r="O52" s="23" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+38.6</t>
         </is>
       </c>
       <c r="P52" s="23" t="inlineStr">
@@ -8775,9 +8859,9 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q52" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
+      <c r="Q52" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="R52" s="23" t="inlineStr">
@@ -8792,22 +8876,22 @@
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="U52" s="23" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>+24.8</t>
         </is>
       </c>
       <c r="V52" s="23" t="inlineStr">
         <is>
-          <t>-18.7</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="W52" s="23" t="inlineStr">
         <is>
-          <t>+39.1</t>
+          <t>+77.8</t>
         </is>
       </c>
     </row>
@@ -8817,82 +8901,82 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>Montana State @ Nevada</t>
+          <t>Mercyhurst @ New Mexico</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>20-7</t>
+          <t>7-70</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>-42.2</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>+63.0</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>-17.2</t>
+          <t>-17.0</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>+22.2</t>
+          <t>-25.2</t>
         </is>
       </c>
       <c r="H53" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I53" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>-27.7</t>
+        </is>
+      </c>
+      <c r="K53" s="23" t="inlineStr">
+        <is>
+          <t>-14.5</t>
+        </is>
+      </c>
+      <c r="L53" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M53" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N53" s="23" t="inlineStr">
+        <is>
+          <t>-45.6</t>
+        </is>
+      </c>
+      <c r="O53" s="23" t="inlineStr">
+        <is>
+          <t>+3.3</t>
+        </is>
+      </c>
+      <c r="P53" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I53" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J53" s="23" t="inlineStr">
-        <is>
-          <t>-12.5</t>
-        </is>
-      </c>
-      <c r="K53" s="23" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
-      <c r="L53" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M53" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N53" s="23" t="inlineStr">
-        <is>
-          <t>-33.6</t>
-        </is>
-      </c>
-      <c r="O53" s="23" t="inlineStr">
-        <is>
-          <t>+38.6</t>
-        </is>
-      </c>
-      <c r="P53" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q53" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="Q53" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="R53" s="23" t="inlineStr">
@@ -8902,27 +8986,27 @@
       </c>
       <c r="S53" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
       <c r="U53" s="23" t="inlineStr">
         <is>
-          <t>+24.8</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="V53" s="23" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-15.8</t>
         </is>
       </c>
       <c r="W53" s="23" t="inlineStr">
         <is>
-          <t>+77.8</t>
+          <t>+81.1</t>
         </is>
       </c>
     </row>
@@ -8932,72 +9016,72 @@
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Mercyhurst @ New Mexico</t>
+          <t>UNLV @ North Texas</t>
         </is>
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>7-70</t>
+          <t>6-44</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>-42.2</t>
+          <t>+2.8</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>+63.0</t>
+          <t>+38.0</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>-17.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>-25.2</t>
+          <t>+6.3</t>
         </is>
       </c>
       <c r="H54" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I54" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>-27.1</t>
+          <t>+0.7</t>
         </is>
       </c>
       <c r="K54" s="23" t="inlineStr">
         <is>
-          <t>-15.2</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="L54" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M54" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M54" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="N54" s="23" t="inlineStr">
         <is>
-          <t>-45.6</t>
+          <t>-5.3</t>
         </is>
       </c>
       <c r="O54" s="23" t="inlineStr">
         <is>
-          <t>+3.3</t>
+          <t>+8.0</t>
         </is>
       </c>
       <c r="P54" s="23" t="inlineStr">
@@ -9017,27 +9101,27 @@
       </c>
       <c r="S54" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T54" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="U54" s="23" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+5.9</t>
         </is>
       </c>
       <c r="V54" s="23" t="inlineStr">
         <is>
-          <t>-16.4</t>
+          <t>-13.8</t>
         </is>
       </c>
       <c r="W54" s="23" t="inlineStr">
         <is>
-          <t>+81.1</t>
+          <t>+89.1</t>
         </is>
       </c>
     </row>
@@ -9047,32 +9131,32 @@
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>UNLV @ North Texas</t>
+          <t>Illinois State @ Northern Illinois</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
-          <t>6-44</t>
+          <t>28-24</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>+2.8</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>+38.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>+6.3</t>
+          <t>+17.5</t>
         </is>
       </c>
       <c r="H55" s="23" t="inlineStr">
@@ -9080,19 +9164,19 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="I55" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="I55" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>+1.9</t>
+          <t>-16.0</t>
         </is>
       </c>
       <c r="K55" s="23" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>+18.5</t>
         </is>
       </c>
       <c r="L55" s="23" t="inlineStr">
@@ -9100,19 +9184,19 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="M55" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
+      <c r="M55" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="N55" s="23" t="inlineStr">
         <is>
-          <t>-5.3</t>
+          <t>-23.3</t>
         </is>
       </c>
       <c r="O55" s="23" t="inlineStr">
         <is>
-          <t>+8.0</t>
+          <t>+25.8</t>
         </is>
       </c>
       <c r="P55" s="23" t="inlineStr">
@@ -9120,9 +9204,9 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q55" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="Q55" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="R55" s="23" t="inlineStr">
@@ -9137,22 +9221,22 @@
       </c>
       <c r="T55" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="U55" s="23" t="inlineStr">
         <is>
-          <t>+5.9</t>
+          <t>+23.4</t>
         </is>
       </c>
       <c r="V55" s="23" t="inlineStr">
         <is>
-          <t>-15.5</t>
+          <t>+4.7</t>
         </is>
       </c>
       <c r="W55" s="23" t="inlineStr">
         <is>
-          <t>+89.1</t>
+          <t>+114.9</t>
         </is>
       </c>
     </row>
@@ -9162,92 +9246,92 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Illinois State @ Northern Illinois</t>
+          <t>Cal Poly @ San José State</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>28-24</t>
+          <t>20-30</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>-21.5</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>+10.0</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>-19.9</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
-          <t>+17.5</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>-27.8</t>
+        </is>
+      </c>
+      <c r="K56" s="23" t="inlineStr">
+        <is>
+          <t>+6.3</t>
+        </is>
+      </c>
+      <c r="L56" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I56" s="25" t="inlineStr">
+      <c r="M56" s="25" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="J56" s="23" t="inlineStr">
-        <is>
-          <t>-15.6</t>
-        </is>
-      </c>
-      <c r="K56" s="23" t="inlineStr">
-        <is>
-          <t>+18.1</t>
-        </is>
-      </c>
-      <c r="L56" s="23" t="inlineStr">
+      <c r="N56" s="23" t="inlineStr">
+        <is>
+          <t>-30.7</t>
+        </is>
+      </c>
+      <c r="O56" s="23" t="inlineStr">
+        <is>
+          <t>+9.2</t>
+        </is>
+      </c>
+      <c r="P56" s="23" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="M56" s="25" t="inlineStr">
+      <c r="Q56" s="25" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="N56" s="23" t="inlineStr">
-        <is>
-          <t>-23.3</t>
-        </is>
-      </c>
-      <c r="O56" s="23" t="inlineStr">
-        <is>
-          <t>+25.8</t>
-        </is>
-      </c>
-      <c r="P56" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q56" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
       <c r="R56" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S56" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T56" s="24" t="inlineStr">
@@ -9257,17 +9341,17 @@
       </c>
       <c r="U56" s="23" t="inlineStr">
         <is>
-          <t>+23.4</t>
+          <t>+21.8</t>
         </is>
       </c>
       <c r="V56" s="23" t="inlineStr">
         <is>
-          <t>+2.6</t>
+          <t>+11.0</t>
         </is>
       </c>
       <c r="W56" s="23" t="inlineStr">
         <is>
-          <t>+114.9</t>
+          <t>+124.1</t>
         </is>
       </c>
     </row>
@@ -9277,32 +9361,32 @@
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>Cal Poly @ San José State</t>
+          <t>Texas Southern @ UTEP</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>10-51</t>
         </is>
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>-21.5</t>
+          <t>-27.2</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>+10.0</t>
+          <t>+41.0</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>-19.9</t>
+          <t>-14.6</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="H57" s="23" t="inlineStr">
@@ -9310,24 +9394,24 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="I57" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
+      <c r="I57" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>-27.9</t>
+          <t>-20.0</t>
         </is>
       </c>
       <c r="K57" s="23" t="inlineStr">
         <is>
-          <t>+6.4</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="L57" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="M57" s="25" t="inlineStr">
@@ -9337,52 +9421,52 @@
       </c>
       <c r="N57" s="23" t="inlineStr">
         <is>
-          <t>-30.7</t>
+          <t>-19.8</t>
         </is>
       </c>
       <c r="O57" s="23" t="inlineStr">
         <is>
+          <t>-7.5</t>
+        </is>
+      </c>
+      <c r="P57" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q57" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R57" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S57" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U57" s="23" t="inlineStr">
+        <is>
           <t>+9.2</t>
         </is>
       </c>
-      <c r="P57" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q57" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="R57" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S57" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T57" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U57" s="23" t="inlineStr">
-        <is>
-          <t>+21.8</t>
-        </is>
-      </c>
       <c r="V57" s="23" t="inlineStr">
         <is>
-          <t>+9.0</t>
+          <t>+3.8</t>
         </is>
       </c>
       <c r="W57" s="23" t="inlineStr">
         <is>
-          <t>+124.1</t>
+          <t>+116.6</t>
         </is>
       </c>
     </row>
@@ -9392,32 +9476,32 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Texas Southern @ UTEP</t>
+          <t>Northern Colorado @ Wyoming</t>
         </is>
       </c>
       <c r="C58" s="23" t="inlineStr">
         <is>
-          <t>10-51</t>
+          <t>13-21</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>-27.2</t>
+          <t>-23.5</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>+41.0</t>
+          <t>+8.0</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>-14.6</t>
+          <t>-16.3</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="H58" s="23" t="inlineStr">
@@ -9425,51 +9509,51 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="I58" s="25" t="inlineStr">
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>-22.3</t>
+        </is>
+      </c>
+      <c r="K58" s="23" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="L58" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M58" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N58" s="23" t="inlineStr">
+        <is>
+          <t>-27.6</t>
+        </is>
+      </c>
+      <c r="O58" s="23" t="inlineStr">
+        <is>
+          <t>+4.1</t>
+        </is>
+      </c>
+      <c r="P58" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q58" s="25" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="J58" s="23" t="inlineStr">
-        <is>
-          <t>-20.1</t>
-        </is>
-      </c>
-      <c r="K58" s="23" t="inlineStr">
-        <is>
-          <t>-7.1</t>
-        </is>
-      </c>
-      <c r="L58" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M58" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N58" s="23" t="inlineStr">
-        <is>
-          <t>-19.8</t>
-        </is>
-      </c>
-      <c r="O58" s="23" t="inlineStr">
-        <is>
-          <t>-7.5</t>
-        </is>
-      </c>
-      <c r="P58" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q58" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
       <c r="R58" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9477,7 +9561,7 @@
       </c>
       <c r="S58" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T58" s="24" t="inlineStr">
@@ -9487,132 +9571,822 @@
       </c>
       <c r="U58" s="23" t="inlineStr">
         <is>
-          <t>+9.2</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="V58" s="23" t="inlineStr">
         <is>
-          <t>+1.9</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="W58" s="23" t="inlineStr">
         <is>
-          <t>+116.6</t>
+          <t>+120.7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>Northern Colorado @ Wyoming</t>
+          <t>Northern Illinois @ Arizona</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>13-21</t>
+          <t>17-42</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
         <is>
-          <t>-23.5</t>
+          <t>-34.5</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
+          <t>+25.0</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>-26.3</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>-8.2</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>-20.7</t>
+        </is>
+      </c>
+      <c r="K59" s="23" t="inlineStr">
+        <is>
+          <t>-13.8</t>
+        </is>
+      </c>
+      <c r="L59" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M59" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N59" s="23" t="inlineStr">
+        <is>
+          <t>-30.9</t>
+        </is>
+      </c>
+      <c r="O59" s="23" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="P59" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q59" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R59" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S59" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T59" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U59" s="23" t="inlineStr">
+        <is>
+          <t>-6.2</t>
+        </is>
+      </c>
+      <c r="V59" s="23" t="inlineStr">
+        <is>
+          <t>-11.3</t>
+        </is>
+      </c>
+      <c r="W59" s="23" t="inlineStr">
+        <is>
+          <t>+117.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>Wyoming @ Central Michigan</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="inlineStr">
+        <is>
+          <t>10-24</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="inlineStr">
+        <is>
+          <t>+1.8</t>
+        </is>
+      </c>
+      <c r="E60" s="23" t="inlineStr">
+        <is>
+          <t>+14.0</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>+11.3</t>
+        </is>
+      </c>
+      <c r="H60" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J60" s="23" t="inlineStr">
+        <is>
+          <t>-9.1</t>
+        </is>
+      </c>
+      <c r="K60" s="23" t="inlineStr">
+        <is>
+          <t>+10.9</t>
+        </is>
+      </c>
+      <c r="L60" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M60" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N60" s="23" t="inlineStr">
+        <is>
+          <t>-9.3</t>
+        </is>
+      </c>
+      <c r="O60" s="23" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
+      <c r="P60" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q60" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R60" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S60" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T60" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U60" s="23" t="inlineStr">
+        <is>
+          <t>+5.1</t>
+        </is>
+      </c>
+      <c r="V60" s="23" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="W60" s="23" t="inlineStr">
+        <is>
+          <t>+128.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>UTEP @ Michigan</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>17-52</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>-34.5</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>+35.0</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="H61" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
+        <is>
+          <t>-31.7</t>
+        </is>
+      </c>
+      <c r="K61" s="23" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="L61" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M61" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N61" s="23" t="inlineStr">
+        <is>
+          <t>-29.7</t>
+        </is>
+      </c>
+      <c r="O61" s="23" t="inlineStr">
+        <is>
+          <t>-4.8</t>
+        </is>
+      </c>
+      <c r="P61" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q61" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R61" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S61" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T61" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U61" s="23" t="inlineStr">
+        <is>
+          <t>+5.6</t>
+        </is>
+      </c>
+      <c r="V61" s="23" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="W61" s="23" t="inlineStr">
+        <is>
+          <t>+123.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t>Nevada @ Middle Tennessee</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>20-27</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="inlineStr">
+        <is>
+          <t>+3.8</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>+7.3</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
+      <c r="K62" s="23" t="inlineStr">
+        <is>
+          <t>+2.4</t>
+        </is>
+      </c>
+      <c r="L62" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M62" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N62" s="23" t="inlineStr">
+        <is>
+          <t>+2.9</t>
+        </is>
+      </c>
+      <c r="O62" s="23" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
+      <c r="P62" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q62" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="R62" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S62" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T62" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U62" s="23" t="inlineStr">
+        <is>
+          <t>+12.9</t>
+        </is>
+      </c>
+      <c r="V62" s="23" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="W62" s="23" t="inlineStr">
+        <is>
+          <t>+124.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>New Mexico @ Oklahoma</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>6-14</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>-21.2</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
           <t>+8.0</t>
         </is>
       </c>
-      <c r="F59" s="23" t="inlineStr">
-        <is>
-          <t>-16.3</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr">
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>-14.1</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
         <is>
           <t>-7.2</t>
         </is>
       </c>
-      <c r="H59" s="23" t="inlineStr">
+      <c r="H63" s="23" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I59" s="24" t="inlineStr">
+      <c r="I63" s="24" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="J59" s="23" t="inlineStr">
-        <is>
-          <t>-21.7</t>
-        </is>
-      </c>
-      <c r="K59" s="23" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
-      <c r="L59" s="23" t="inlineStr">
+      <c r="J63" s="23" t="inlineStr">
+        <is>
+          <t>-15.1</t>
+        </is>
+      </c>
+      <c r="K63" s="23" t="inlineStr">
+        <is>
+          <t>-6.1</t>
+        </is>
+      </c>
+      <c r="L63" s="23" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="M59" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N59" s="23" t="inlineStr">
-        <is>
-          <t>-27.6</t>
-        </is>
-      </c>
-      <c r="O59" s="23" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
-      <c r="P59" s="23" t="inlineStr">
+      <c r="M63" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N63" s="23" t="inlineStr">
+        <is>
+          <t>-10.8</t>
+        </is>
+      </c>
+      <c r="O63" s="23" t="inlineStr">
+        <is>
+          <t>-10.4</t>
+        </is>
+      </c>
+      <c r="P63" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q63" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R63" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S63" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T63" s="24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U63" s="23" t="inlineStr">
+        <is>
+          <t>+5.7</t>
+        </is>
+      </c>
+      <c r="V63" s="23" t="inlineStr">
+        <is>
+          <t>-6.9</t>
+        </is>
+      </c>
+      <c r="W63" s="23" t="inlineStr">
+        <is>
+          <t>+113.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t>North Dakota State @ Sacramento State</t>
+        </is>
+      </c>
+      <c r="C64" s="23" t="inlineStr">
+        <is>
+          <t>31-10</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="inlineStr">
+        <is>
+          <t>+25.5</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
+        <is>
+          <t>-21.0</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>+13.0</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr">
+        <is>
+          <t>+12.5</t>
+        </is>
+      </c>
+      <c r="H64" s="23" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="Q59" s="25" t="inlineStr">
+      <c r="I64" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J64" s="23" t="inlineStr">
+        <is>
+          <t>+17.6</t>
+        </is>
+      </c>
+      <c r="K64" s="23" t="inlineStr">
+        <is>
+          <t>+7.9</t>
+        </is>
+      </c>
+      <c r="L64" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M64" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N64" s="23" t="inlineStr">
+        <is>
+          <t>+35.9</t>
+        </is>
+      </c>
+      <c r="O64" s="23" t="inlineStr">
+        <is>
+          <t>-10.4</t>
+        </is>
+      </c>
+      <c r="P64" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q64" s="25" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="R59" s="23" t="inlineStr">
+      <c r="R64" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S59" s="23" t="inlineStr">
+      <c r="S64" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T59" s="24" t="inlineStr">
+      <c r="T64" s="24" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U59" s="23" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
-      <c r="V59" s="23" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
-      <c r="W59" s="23" t="inlineStr">
-        <is>
-          <t>+120.7</t>
+      <c r="U64" s="23" t="inlineStr">
+        <is>
+          <t>+18.2</t>
+        </is>
+      </c>
+      <c r="V64" s="23" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
+      <c r="W64" s="23" t="inlineStr">
+        <is>
+          <t>+103.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>Fresno State @ San José State</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>26-10</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>-16.0</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
+      <c r="H65" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I65" s="25" t="inlineStr">
+        <is>
+          <t>Loss (no real edge)</t>
+        </is>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
+        <is>
+          <t>+11.1</t>
+        </is>
+      </c>
+      <c r="K65" s="23" t="inlineStr">
+        <is>
+          <t>-7.1</t>
+        </is>
+      </c>
+      <c r="L65" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M65" s="24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N65" s="23" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
+      <c r="O65" s="23" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
+      <c r="P65" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q65" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R65" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S65" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T65" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="U65" s="23" t="inlineStr">
+        <is>
+          <t>+19.1</t>
+        </is>
+      </c>
+      <c r="V65" s="23" t="inlineStr">
+        <is>
+          <t>-6.1</t>
+        </is>
+      </c>
+      <c r="W65" s="23" t="inlineStr">
+        <is>
+          <t>+106.2</t>
         </is>
       </c>
     </row>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -974,7 +974,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G2" s="6">
         <f>F2-E2</f>
@@ -985,10 +985,10 @@
         <v/>
       </c>
       <c r="I2" t="n">
-        <v>49.1</v>
+        <v>47.8</v>
       </c>
       <c r="J2" t="n">
-        <v>49.5</v>
+        <v>50.8</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -1032,7 +1032,7 @@
         <v>-7.8</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.5</v>
+        <v>-10</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -1043,10 +1043,10 @@
         <v/>
       </c>
       <c r="I3" t="n">
-        <v>43.3</v>
+        <v>46.1</v>
       </c>
       <c r="J3" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="K3" s="6">
         <f>I3-J3</f>
@@ -1088,7 +1088,7 @@
         <v>1.9</v>
       </c>
       <c r="F4" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
@@ -1099,10 +1099,10 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>42.9</v>
+        <v>44.9</v>
       </c>
       <c r="J4" t="n">
-        <v>44.5</v>
+        <v>45.8</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -1144,7 +1144,7 @@
         <v>18.8</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
@@ -1155,10 +1155,10 @@
         <v/>
       </c>
       <c r="I5" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="J5" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="K5" s="6">
         <f>I5-J5</f>
@@ -1204,6 +1204,9 @@
       <c r="E6" t="n">
         <v>10.5</v>
       </c>
+      <c r="F6" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G6" s="6">
         <f>F6-E6</f>
         <v/>
@@ -1213,7 +1216,10 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>49</v>
+        <v>50.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>53.5</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -1259,7 +1265,9 @@
       <c r="E7" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="F7" s="10" t="n"/>
+      <c r="F7" s="10" t="n">
+        <v>5.5</v>
+      </c>
       <c r="G7" s="10">
         <f>F7-E7</f>
         <v/>
@@ -1269,9 +1277,11 @@
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="J7" s="10" t="n"/>
+        <v>46.6</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>48.8</v>
+      </c>
       <c r="K7" s="10">
         <f>I7-J7</f>
         <v/>
@@ -5895,7 +5905,7 @@
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t>106/260 (41%)</t>
+          <t>104/260 (40%)</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
@@ -5945,7 +5955,7 @@
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>7/29 (24%)</t>
+          <t>6/29 (21%)</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
@@ -6045,7 +6055,7 @@
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>461/985 (47%)</t>
+          <t>449/985 (46%)</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -6067,26 +6077,26 @@
         <v>8622</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>4359</v>
+        <v>4317</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4263</v>
+        <v>4305</v>
       </c>
       <c r="F10" s="23" t="n">
         <v>71</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="I10" s="23" t="n">
-        <v>6745</v>
+        <v>6746</v>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
@@ -6095,12 +6105,12 @@
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>4485/8693 (52%)</t>
+          <t>4487/8693 (52%)</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t>+346.5</t>
+          <t>+253.2</t>
         </is>
       </c>
     </row>
@@ -6117,40 +6127,40 @@
         <v>973</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F11" s="23" t="n">
         <v>12</v>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="I11" s="23" t="n">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>517/985 (52%)</t>
+          <t>530/985 (54%)</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t>+872.3</t>
+          <t>+908.0</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6274,7 @@
       </c>
       <c r="K15" s="23" t="inlineStr">
         <is>
-          <t>106/260 (41%)</t>
+          <t>104/260 (40%)</t>
         </is>
       </c>
       <c r="L15" s="23" t="inlineStr">
@@ -6314,7 +6324,7 @@
       </c>
       <c r="K16" s="23" t="inlineStr">
         <is>
-          <t>7/29 (24%)</t>
+          <t>6/29 (21%)</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
@@ -6364,7 +6374,7 @@
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>71/260 (27%)</t>
+          <t>72/260 (28%)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -6414,7 +6424,7 @@
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>8/29 (28%)</t>
+          <t>9/29 (31%)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -6436,40 +6446,40 @@
         <v>257</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F19" s="23" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="I19" s="23" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>83/260 (32%)</t>
+          <t>84/260 (32%)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
-          <t>-580.8</t>
+          <t>-576.9</t>
         </is>
       </c>
     </row>
@@ -6486,30 +6496,30 @@
         <v>29</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="I20" s="23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
@@ -6519,14 +6529,14 @@
       </c>
       <c r="L20" s="23" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-12.8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.2% of all graded games. Ridge agrees with the live model (Gamma) in 53.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 62.7% of games it has a rating for.</t>
+          <t>Ridge and XGBoost (the two candidates) agree with each other in 76.8% of all graded games. Ridge agrees with the live model (Gamma) in 53.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 62.3% of games it has a rating for.</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6615,7 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>+14.0</t>
+          <t>+13.5</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -6615,7 +6625,7 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>+9.7</t>
+          <t>+9.3</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -6660,7 +6670,7 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>-8.5</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -6670,7 +6680,7 @@
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -6680,7 +6690,7 @@
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -6690,7 +6700,7 @@
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -6700,7 +6710,7 @@
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6725,7 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>+5.5</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -6725,7 +6735,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>+0.4</t>
+          <t>+1.2</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -6735,17 +6745,17 @@
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -6755,7 +6765,7 @@
       </c>
       <c r="K28" s="24" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6780,7 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>+12.5</t>
+          <t>+12.8</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -6780,7 +6790,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>+12.8</t>
+          <t>+12.1</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
@@ -6795,7 +6805,7 @@
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -6805,7 +6815,7 @@
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K29" s="24" t="inlineStr">
@@ -6825,7 +6835,7 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+10.5</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -6835,7 +6845,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>+0.8</t>
+          <t>+0.9</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -6845,27 +6855,27 @@
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pick'em</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6890,7 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+5.5</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -6890,7 +6900,7 @@
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>+0.7</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -6900,27 +6910,27 @@
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7111,12 @@
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>-28.4</t>
+          <t>-29.0</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="L37" s="23" t="inlineStr">
@@ -7161,7 +7171,7 @@
       </c>
       <c r="V37" s="23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="W37" s="23" t="inlineStr">
@@ -7216,22 +7226,22 @@
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="L38" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M38" s="25" t="inlineStr">
-        <is>
-          <t>Loss (no real edge)</t>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M38" s="24" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
         </is>
       </c>
       <c r="N38" s="23" t="inlineStr">
@@ -7256,7 +7266,7 @@
       </c>
       <c r="R38" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S38" s="23" t="inlineStr">
@@ -7276,7 +7286,7 @@
       </c>
       <c r="V38" s="23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="W38" s="23" t="inlineStr">
@@ -7331,12 +7341,12 @@
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.1</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>+9.4</t>
+          <t>+8.6</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -7391,7 +7401,7 @@
       </c>
       <c r="V39" s="23" t="inlineStr">
         <is>
-          <t>+7.7</t>
+          <t>+7.8</t>
         </is>
       </c>
       <c r="W39" s="23" t="inlineStr">
@@ -7446,12 +7456,12 @@
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>+5.4</t>
+          <t>+4.6</t>
         </is>
       </c>
       <c r="L40" s="23" t="inlineStr">
@@ -7506,7 +7516,7 @@
       </c>
       <c r="V40" s="23" t="inlineStr">
         <is>
-          <t>+13.1</t>
+          <t>+12.4</t>
         </is>
       </c>
       <c r="W40" s="23" t="inlineStr">
@@ -7561,12 +7571,12 @@
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>-25.4</t>
+          <t>-24.3</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="L41" s="23" t="inlineStr">
@@ -7621,7 +7631,7 @@
       </c>
       <c r="V41" s="23" t="inlineStr">
         <is>
-          <t>+6.8</t>
+          <t>+4.9</t>
         </is>
       </c>
       <c r="W41" s="23" t="inlineStr">
@@ -7676,12 +7686,12 @@
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>+7.6</t>
+          <t>+6.7</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="L42" s="23" t="inlineStr">
@@ -7736,7 +7746,7 @@
       </c>
       <c r="V42" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="W42" s="23" t="inlineStr">
@@ -7791,7 +7801,7 @@
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-10.6</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
@@ -7851,7 +7861,7 @@
       </c>
       <c r="V43" s="23" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="W43" s="23" t="inlineStr">
@@ -7906,12 +7916,12 @@
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>-36.1</t>
+          <t>-34.8</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="L44" s="23" t="inlineStr">
@@ -7966,7 +7976,7 @@
       </c>
       <c r="V44" s="23" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="W44" s="23" t="inlineStr">
@@ -8021,12 +8031,12 @@
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>-13.9</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>+7.2</t>
+          <t>+8.3</t>
         </is>
       </c>
       <c r="L45" s="23" t="inlineStr">
@@ -8081,7 +8091,7 @@
       </c>
       <c r="V45" s="23" t="inlineStr">
         <is>
-          <t>+0.4</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="W45" s="23" t="inlineStr">
@@ -8136,67 +8146,67 @@
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>-32.1</t>
+          <t>-32.8</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="L46" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M46" s="25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N46" s="23" t="inlineStr">
+        <is>
+          <t>-44.4</t>
+        </is>
+      </c>
+      <c r="O46" s="23" t="inlineStr">
+        <is>
+          <t>+3.6</t>
+        </is>
+      </c>
+      <c r="P46" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q46" s="24" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
+        </is>
+      </c>
+      <c r="R46" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S46" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="U46" s="23" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
+      <c r="V46" s="23" t="inlineStr">
+        <is>
           <t>-8.6</t>
-        </is>
-      </c>
-      <c r="L46" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M46" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N46" s="23" t="inlineStr">
-        <is>
-          <t>-44.4</t>
-        </is>
-      </c>
-      <c r="O46" s="23" t="inlineStr">
-        <is>
-          <t>+3.6</t>
-        </is>
-      </c>
-      <c r="P46" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q46" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R46" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S46" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T46" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U46" s="23" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
-      <c r="V46" s="23" t="inlineStr">
-        <is>
-          <t>-8.2</t>
         </is>
       </c>
       <c r="W46" s="23" t="inlineStr">
@@ -8251,12 +8261,12 @@
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>+0.7</t>
+          <t>+0.6</t>
         </is>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-5.3</t>
         </is>
       </c>
       <c r="L47" s="23" t="inlineStr">
@@ -8311,7 +8321,7 @@
       </c>
       <c r="V47" s="23" t="inlineStr">
         <is>
-          <t>-13.7</t>
+          <t>-14.0</t>
         </is>
       </c>
       <c r="W47" s="23" t="inlineStr">
@@ -8366,12 +8376,12 @@
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>+2.4</t>
+          <t>+1.4</t>
         </is>
       </c>
       <c r="L48" s="23" t="inlineStr">
@@ -8381,7 +8391,7 @@
       </c>
       <c r="M48" s="25" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Loss (no real edge)</t>
         </is>
       </c>
       <c r="N48" s="23" t="inlineStr">
@@ -8426,7 +8436,7 @@
       </c>
       <c r="V48" s="23" t="inlineStr">
         <is>
-          <t>-11.3</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="W48" s="23" t="inlineStr">
@@ -8481,12 +8491,12 @@
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>-36.0</t>
+          <t>-34.3</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="L49" s="23" t="inlineStr">
@@ -8496,7 +8506,7 @@
       </c>
       <c r="M49" s="24" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="N49" s="23" t="inlineStr">
@@ -8531,7 +8541,7 @@
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="U49" s="23" t="inlineStr">
@@ -8541,7 +8551,7 @@
       </c>
       <c r="V49" s="23" t="inlineStr">
         <is>
-          <t>-12.5</t>
+          <t>-15.5</t>
         </is>
       </c>
       <c r="W49" s="23" t="inlineStr">
@@ -8596,7 +8606,7 @@
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>+14.2</t>
+          <t>+14.3</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
@@ -8656,7 +8666,7 @@
       </c>
       <c r="V50" s="23" t="inlineStr">
         <is>
-          <t>-25.0</t>
+          <t>-28.0</t>
         </is>
       </c>
       <c r="W50" s="23" t="inlineStr">
@@ -8711,12 +8721,12 @@
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>-13.6</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>+6.1</t>
+          <t>+5.4</t>
         </is>
       </c>
       <c r="L51" s="23" t="inlineStr">
@@ -8771,7 +8781,7 @@
       </c>
       <c r="V51" s="23" t="inlineStr">
         <is>
-          <t>-19.0</t>
+          <t>-22.5</t>
         </is>
       </c>
       <c r="W51" s="23" t="inlineStr">
@@ -8826,12 +8836,12 @@
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>-13.2</t>
         </is>
       </c>
       <c r="K52" s="23" t="inlineStr">
         <is>
-          <t>+17.6</t>
+          <t>+18.2</t>
         </is>
       </c>
       <c r="L52" s="23" t="inlineStr">
@@ -8886,7 +8896,7 @@
       </c>
       <c r="V52" s="23" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="W52" s="23" t="inlineStr">
@@ -8946,7 +8956,7 @@
       </c>
       <c r="K53" s="23" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>-14.6</t>
         </is>
       </c>
       <c r="L53" s="23" t="inlineStr">
@@ -9001,7 +9011,7 @@
       </c>
       <c r="V53" s="23" t="inlineStr">
         <is>
-          <t>-15.8</t>
+          <t>-18.9</t>
         </is>
       </c>
       <c r="W53" s="23" t="inlineStr">
@@ -9056,12 +9066,12 @@
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>+0.7</t>
+          <t>+1.1</t>
         </is>
       </c>
       <c r="K54" s="23" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+1.6</t>
         </is>
       </c>
       <c r="L54" s="23" t="inlineStr">
@@ -9071,29 +9081,29 @@
       </c>
       <c r="M54" s="24" t="inlineStr">
         <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N54" s="23" t="inlineStr">
+        <is>
+          <t>-5.3</t>
+        </is>
+      </c>
+      <c r="O54" s="23" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
+      <c r="P54" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q54" s="24" t="inlineStr">
+        <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="N54" s="23" t="inlineStr">
-        <is>
-          <t>-5.3</t>
-        </is>
-      </c>
-      <c r="O54" s="23" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
-      <c r="P54" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q54" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
       <c r="R54" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9116,7 +9126,7 @@
       </c>
       <c r="V54" s="23" t="inlineStr">
         <is>
-          <t>-13.8</t>
+          <t>-17.3</t>
         </is>
       </c>
       <c r="W54" s="23" t="inlineStr">
@@ -9171,12 +9181,12 @@
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>-15.7</t>
         </is>
       </c>
       <c r="K55" s="23" t="inlineStr">
         <is>
-          <t>+18.5</t>
+          <t>+18.2</t>
         </is>
       </c>
       <c r="L55" s="23" t="inlineStr">
@@ -9231,7 +9241,7 @@
       </c>
       <c r="V55" s="23" t="inlineStr">
         <is>
-          <t>+4.7</t>
+          <t>+0.9</t>
         </is>
       </c>
       <c r="W55" s="23" t="inlineStr">
@@ -9286,12 +9296,12 @@
       </c>
       <c r="J56" s="23" t="inlineStr">
         <is>
-          <t>-27.8</t>
+          <t>-27.7</t>
         </is>
       </c>
       <c r="K56" s="23" t="inlineStr">
         <is>
-          <t>+6.3</t>
+          <t>+6.2</t>
         </is>
       </c>
       <c r="L56" s="23" t="inlineStr">
@@ -9346,7 +9356,7 @@
       </c>
       <c r="V56" s="23" t="inlineStr">
         <is>
-          <t>+11.0</t>
+          <t>+7.1</t>
         </is>
       </c>
       <c r="W56" s="23" t="inlineStr">
@@ -9401,12 +9411,12 @@
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-20.3</t>
         </is>
       </c>
       <c r="K57" s="23" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="L57" s="23" t="inlineStr">
@@ -9461,7 +9471,7 @@
       </c>
       <c r="V57" s="23" t="inlineStr">
         <is>
-          <t>+3.8</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="W57" s="23" t="inlineStr">
@@ -9516,12 +9526,12 @@
       </c>
       <c r="J58" s="23" t="inlineStr">
         <is>
-          <t>-22.3</t>
+          <t>-21.9</t>
         </is>
       </c>
       <c r="K58" s="23" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="L58" s="23" t="inlineStr">
@@ -9576,7 +9586,7 @@
       </c>
       <c r="V58" s="23" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="W58" s="23" t="inlineStr">
@@ -9631,12 +9641,12 @@
       </c>
       <c r="J59" s="23" t="inlineStr">
         <is>
-          <t>-20.7</t>
+          <t>-23.8</t>
         </is>
       </c>
       <c r="K59" s="23" t="inlineStr">
         <is>
-          <t>-13.8</t>
+          <t>-10.7</t>
         </is>
       </c>
       <c r="L59" s="23" t="inlineStr">
@@ -9691,7 +9701,7 @@
       </c>
       <c r="V59" s="23" t="inlineStr">
         <is>
-          <t>-11.3</t>
+          <t>-12.2</t>
         </is>
       </c>
       <c r="W59" s="23" t="inlineStr">
@@ -9746,12 +9756,12 @@
       </c>
       <c r="J60" s="23" t="inlineStr">
         <is>
-          <t>-9.1</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="K60" s="23" t="inlineStr">
         <is>
-          <t>+10.9</t>
+          <t>+9.5</t>
         </is>
       </c>
       <c r="L60" s="23" t="inlineStr">
@@ -9806,7 +9816,7 @@
       </c>
       <c r="V60" s="23" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="W60" s="23" t="inlineStr">
@@ -9861,12 +9871,12 @@
       </c>
       <c r="J61" s="23" t="inlineStr">
         <is>
-          <t>-31.7</t>
+          <t>-30.8</t>
         </is>
       </c>
       <c r="K61" s="23" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="L61" s="23" t="inlineStr">
@@ -9921,7 +9931,7 @@
       </c>
       <c r="V61" s="23" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="W61" s="23" t="inlineStr">
@@ -9976,12 +9986,12 @@
       </c>
       <c r="J62" s="23" t="inlineStr">
         <is>
-          <t>+1.4</t>
+          <t>+2.9</t>
         </is>
       </c>
       <c r="K62" s="23" t="inlineStr">
         <is>
-          <t>+2.4</t>
+          <t>+0.9</t>
         </is>
       </c>
       <c r="L62" s="23" t="inlineStr">
@@ -9991,7 +10001,7 @@
       </c>
       <c r="M62" s="24" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Win (no real edge)</t>
         </is>
       </c>
       <c r="N62" s="23" t="inlineStr">
@@ -10026,7 +10036,7 @@
       </c>
       <c r="T62" s="24" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="U62" s="23" t="inlineStr">
@@ -10036,7 +10046,7 @@
       </c>
       <c r="V62" s="23" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="W62" s="23" t="inlineStr">
@@ -10091,12 +10101,12 @@
       </c>
       <c r="J63" s="23" t="inlineStr">
         <is>
-          <t>-15.1</t>
+          <t>-14.4</t>
         </is>
       </c>
       <c r="K63" s="23" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="L63" s="23" t="inlineStr">
@@ -10151,7 +10161,7 @@
       </c>
       <c r="V63" s="23" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-12.4</t>
         </is>
       </c>
       <c r="W63" s="23" t="inlineStr">
@@ -10206,12 +10216,12 @@
       </c>
       <c r="J64" s="23" t="inlineStr">
         <is>
-          <t>+17.6</t>
+          <t>+19.8</t>
         </is>
       </c>
       <c r="K64" s="23" t="inlineStr">
         <is>
-          <t>+7.9</t>
+          <t>+5.7</t>
         </is>
       </c>
       <c r="L64" s="23" t="inlineStr">
@@ -10266,7 +10276,7 @@
       </c>
       <c r="V64" s="23" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="W64" s="23" t="inlineStr">
@@ -10321,12 +10331,12 @@
       </c>
       <c r="J65" s="23" t="inlineStr">
         <is>
-          <t>+11.1</t>
+          <t>+10.1</t>
         </is>
       </c>
       <c r="K65" s="23" t="inlineStr">
         <is>
-          <t>-7.1</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="L65" s="23" t="inlineStr">
@@ -10381,7 +10391,7 @@
       </c>
       <c r="V65" s="23" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-12.8</t>
         </is>
       </c>
       <c r="W65" s="23" t="inlineStr">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="2" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -119,12 +119,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <sz val="8"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
@@ -194,12 +188,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -294,15 +288,15 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -586,7 +580,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
@@ -742,7 +736,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -846,19 +840,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="20.5703125" customWidth="1" min="3" max="3"/>
+    <col width="20.54296875" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="6"/>
-    <col width="12.7109375" customWidth="1" min="7" max="7"/>
-    <col width="7.5703125" customWidth="1" min="8" max="8"/>
+    <col width="12.7265625" customWidth="1" min="7" max="7"/>
+    <col width="7.54296875" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="5.5703125" customWidth="1" min="12" max="12"/>
-    <col width="14.28515625" customWidth="1" min="13" max="14"/>
+    <col width="5.54296875" customWidth="1" min="12" max="12"/>
+    <col width="14.26953125" customWidth="1" min="13" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="18" max="18"/>
@@ -2130,13 +2124,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M163"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="37.42578125" customWidth="1" min="3" max="3"/>
+    <col width="37.453125" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22.28515625" customWidth="1" min="5" max="5"/>
+    <col width="22.26953125" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="9"/>
@@ -3901,10 +3895,18 @@
       <c r="H35" t="n">
         <v>1</v>
       </c>
+      <c r="I35" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="J35" s="6">
         <f>IF(I35="","",I35-F35)</f>
         <v/>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L35" s="11">
         <f>IF(K35="W",IF(G35&lt;0,H35*100/ABS(G35),H35*G35/100),IF(K35="L",-H35,0))</f>
         <v/>
@@ -3951,6 +3953,11 @@
         <f>IF(I36="","",I36-F36)</f>
         <v/>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L36" s="11">
         <f>IF(K36="W",IF(G36&lt;0,H36*100/ABS(G36),H36*G36/100),IF(K36="L",-H36,0))</f>
         <v/>
@@ -3993,10 +4000,18 @@
       <c r="H37" t="n">
         <v>2</v>
       </c>
+      <c r="I37" t="n">
+        <v>-27.5</v>
+      </c>
       <c r="J37" s="6">
         <f>IF(I37="","",I37-F37)</f>
         <v/>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L37" s="11">
         <f>IF(K37="W",IF(G37&lt;0,H37*100/ABS(G37),H37*G37/100),IF(K37="L",-H37,0))</f>
         <v/>
@@ -4007,10 +4022,44 @@
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SMU @ Louisville</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SMU</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>134</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
       <c r="J38" s="6">
         <f>IF(I38="","",I38-F38)</f>
         <v/>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L38" s="11">
         <f>IF(K38="W",IF(G38&lt;0,H38*100/ABS(G38),H38*G38/100),IF(K38="L",-H38,0))</f>
         <v/>
@@ -4021,10 +4070,44 @@
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LSU @ Ole Miss</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LSU</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>350</v>
+      </c>
+      <c r="H39" t="n">
+        <v>36</v>
+      </c>
       <c r="J39" s="6">
         <f>IF(I39="","",I39-F39)</f>
         <v/>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L39" s="11">
         <f>IF(K39="W",IF(G39&lt;0,H39*100/ABS(G39),H39*G39/100),IF(K39="L",-H39,0))</f>
         <v/>
@@ -4035,10 +4118,50 @@
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wyoming @ Central Michigan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Central Michigan</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="J40" s="6">
         <f>IF(I40="","",I40-F40)</f>
         <v/>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L40" s="11">
         <f>IF(K40="W",IF(G40&lt;0,H40*100/ABS(G40),H40*G40/100),IF(K40="L",-H40,0))</f>
         <v/>
@@ -4049,10 +4172,50 @@
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Coastal Carolina @ Delaware</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="J41" s="6">
         <f>IF(I41="","",I41-F41)</f>
         <v/>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="L41" s="11">
         <f>IF(K41="W",IF(G41&lt;0,H41*100/ABS(G41),H41*G41/100),IF(K41="L",-H41,0))</f>
         <v/>
@@ -4063,10 +4226,50 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Houston @ Texas Tech</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Texas Tech</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="J42" s="6">
         <f>IF(I42="","",I42-F42)</f>
         <v/>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L42" s="11">
         <f>IF(K42="W",IF(G42&lt;0,H42*100/ABS(G42),H42*G42/100),IF(K42="L",-H42,0))</f>
         <v/>
@@ -4077,9 +4280,51 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2\3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Miami @ Wake Forest</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Wake Forest</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-140</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20.5</v>
+      </c>
       <c r="J43" s="6">
         <f>IF(I43="","",I43-F43)</f>
         <v/>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
       </c>
       <c r="L43" s="11">
         <f>IF(K43="W",IF(G43&lt;0,H43*100/ABS(G43),H43*G43/100),IF(K43="L",-H43,0))</f>
@@ -5312,11 +5557,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="7.140625" customWidth="1" min="3" max="3"/>
+    <col width="7.1796875" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
@@ -5753,7 +5998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:AB63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5773,25 +6018,30 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Dub Gamma vs. Ridge vs. XGBoost -- Model Comparison</t>
+          <t>Dub Gamma vs. Ridge vs. XGBoost vs. Massey -- Model Comparison</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Informational only. The Dub Gamma Model (Sonny-Moore-seeded) is the live model everywhere else in this workbook and on the website -- Ridge and XGBoost are candidates being evaluated here, not replacements. Gamma has no rating (and so no prediction) for any season before it was seeded -- its columns read "n/a" for older games.</t>
+          <t>Informational only. The Dub Gamma Model (Sonny-Moore-seeded) is the live model everywhere else in this workbook and on the website -- Ridge, XGBoost, and Massey are candidates being evaluated here, not replacements. Gamma has no rating (and so no prediction) for any season before it was seeded -- its columns read "n/a" for older games. Massey (a simultaneous-solve rating method, see src/massey_model.py) needs no seed, so it's graded across every season here; it isn't shown in the live Upcoming Games table below since predict_week.py doesn't produce a Massey prediction yet.</t>
         </is>
       </c>
     </row>
@@ -5855,7 +6105,7 @@
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>Tightest Of The Three (CLV)</t>
+          <t>Tightest Of The Four (CLV)</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr">
@@ -5871,46 +6121,46 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>8693</v>
+        <v>8618</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>+7.7%</t>
+          <t>+11.6%</t>
         </is>
       </c>
       <c r="I6" s="23" t="n">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t>104/260 (40%)</t>
+          <t>71/185 (38%)</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
         <is>
-          <t>+808.1</t>
+          <t>+731.7</t>
         </is>
       </c>
     </row>
@@ -5921,46 +6171,46 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>+31.7%</t>
+          <t>+38.8%</t>
         </is>
       </c>
       <c r="I7" s="23" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>6/29 (21%)</t>
+          <t>5/22 (23%)</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
         <is>
-          <t>+106.2</t>
+          <t>+120.7</t>
         </is>
       </c>
     </row>
@@ -5971,46 +6221,46 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>8693</v>
+        <v>8618</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>8622</v>
+        <v>8548</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>4316</v>
+        <v>4273</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>4306</v>
+        <v>4275</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="I8" s="23" t="n">
-        <v>6826</v>
+        <v>6762</v>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr">
         <is>
-          <t>4102/8693 (47%)</t>
+          <t>2633/8618 (31%)</t>
         </is>
       </c>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t>+5473.7</t>
+          <t>+5565.3</t>
         </is>
       </c>
     </row>
@@ -6021,46 +6271,46 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F9" s="23" t="n">
         <v>12</v>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="I9" s="23" t="n">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>449/985 (46%)</t>
+          <t>302/978 (31%)</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
         <is>
-          <t>+608.7</t>
+          <t>+591.7</t>
         </is>
       </c>
     </row>
@@ -6071,46 +6321,46 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>8693</v>
+        <v>8618</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>8622</v>
+        <v>8548</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>4317</v>
+        <v>4261</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4305</v>
+        <v>4287</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="I10" s="23" t="n">
-        <v>6746</v>
+        <v>6695</v>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>4487/8693 (52%)</t>
+          <t>3102/8618 (36%)</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t>+253.2</t>
+          <t>+566.3</t>
         </is>
       </c>
     </row>
@@ -6121,32 +6371,32 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="F11" s="23" t="n">
         <v>12</v>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="I11" s="23" t="n">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
@@ -6155,727 +6405,659 @@
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>530/985 (54%)</t>
+          <t>342/978 (35%)</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t>+908.0</t>
+          <t>+907.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Massey (candidate) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>8618</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>7369</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>3639</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>-3.4%</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>5613</v>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>2812/7429 (38%)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>-10178.7</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Massey (candidate) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>978</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>825</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>416</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>409</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>50.4%</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>-3.7%</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="n">
+        <v>626</v>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>50.2%</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>329/835 (39%)</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>-178.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2026 Season Only</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Games Graded</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Picks Graded</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>Pushes</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>ATS Win %</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>ROI (flat stake)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Real Edge Bets</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>Real Edge Win %</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
-        <is>
-          <t>Tightest Of The Three (CLV)</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>Tightest Of The Four (CLV)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>CLV Pts (cum.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Dub Gamma Model (live model) -- all FBS</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>260</v>
-      </c>
-      <c r="C15" s="23" t="n">
-        <v>257</v>
-      </c>
-      <c r="D15" s="23" t="n">
-        <v>145</v>
-      </c>
-      <c r="E15" s="23" t="n">
-        <v>112</v>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>56.4%</t>
-        </is>
-      </c>
-      <c r="H15" s="23" t="inlineStr">
-        <is>
-          <t>+7.7%</t>
-        </is>
-      </c>
-      <c r="I15" s="23" t="n">
-        <v>213</v>
-      </c>
-      <c r="J15" s="23" t="inlineStr">
-        <is>
-          <t>55.7%</t>
-        </is>
-      </c>
-      <c r="K15" s="23" t="inlineStr">
-        <is>
-          <t>104/260 (40%)</t>
-        </is>
-      </c>
-      <c r="L15" s="23" t="inlineStr">
-        <is>
-          <t>+808.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>Dub Gamma Model (live model) -- MW-involved</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="C16" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="D16" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>69.0%</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+31.7%</t>
-        </is>
-      </c>
-      <c r="I16" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>65.4%</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="inlineStr">
-        <is>
-          <t>6/29 (21%)</t>
-        </is>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>+106.2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>Ridge (candidate) -- all FBS</t>
+          <t>Dub Gamma Model (live model) -- all FBS</t>
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>260</v>
+        <v>185</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>+11.6%</t>
         </is>
       </c>
       <c r="I17" s="23" t="n">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>72/260 (28%)</t>
+          <t>71/185 (38%)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
         <is>
-          <t>-621.2</t>
+          <t>+731.7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>Ridge (candidate) -- MW-involved</t>
+          <t>Dub Gamma Model (live model) -- MW-involved</t>
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>+11.9%</t>
+          <t>+38.8%</t>
         </is>
       </c>
       <c r="I18" s="23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>9/29 (31%)</t>
+          <t>5/22 (23%)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
-          <t>+19.1</t>
+          <t>+120.7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>XGBoost (candidate) -- all FBS</t>
+          <t>Ridge (candidate) -- all FBS</t>
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>260</v>
+        <v>185</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="I19" s="23" t="n">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>84/260 (32%)</t>
+          <t>52/185 (28%)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
-          <t>-576.9</t>
+          <t>-529.7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>XGBoost (candidate) -- MW-involved</t>
+          <t>Ridge (candidate) -- MW-involved</t>
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="I20" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>5/22 (23%)</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>XGBoost (candidate) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>185</v>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>183</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>98</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>46.5%</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>-11.3%</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="n">
+        <v>154</v>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>44.1%</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>54/185 (29%)</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>-344.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>XGBoost (candidate) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="K20" s="23" t="inlineStr">
-        <is>
-          <t>14/29 (48%)</t>
-        </is>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
-        <is>
-          <t>-12.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Ridge and XGBoost (the two candidates) agree with each other in 76.8% of all graded games. Ridge agrees with the live model (Gamma) in 53.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 62.3% of games it has a rating for.</t>
+      <c r="C22" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>-30.6%</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>10/22 (45%)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Massey (candidate) -- all FBS</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>185</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>86</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>51</v>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>-22.3%</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>8/86 (9%)</t>
+        </is>
+      </c>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>-1344.9</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Massey (candidate) -- MW-involved</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>-15.2%</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>2/9 (22%)</t>
+        </is>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>-99.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.0% of all graded games. Ridge agrees with the live model (Gamma) in 48.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 60.0% of games it has a rating for. Massey agrees with the live model (Gamma) in 34.9% of games it has a rating for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Upcoming Games -- Ridge vs. XGBoost vs. Dub Gamma (Not Yet Graded)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Massey (the fourth candidate below in the graded tables) isn't shown here -- predict_week.py doesn't produce a Massey prediction yet, so it has no live line to show for upcoming games.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Market Line (Home)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>Ridge Line</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>XGBoost Line</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>Gamma Line</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>Ridge Lean</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>XGBoost Lean</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>Gamma Lean</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>Ridge/XGBoost Agree?</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K30" s="22" t="inlineStr">
         <is>
           <t>Tightest (Live)*</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>UNLV @ Akron</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>+13.5</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>+9.3</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="H26" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I26" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Northern Illinois @ Georgia State</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>-10.0</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>-11.7</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>-3.2</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>-7.8</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>Hawai'i @ Wyoming</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>+6.1</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
-        </is>
-      </c>
-      <c r="I28" s="23" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>New Mexico @ New Mexico State</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>+12.8</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>+6.7</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>+12.1</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>+18.8</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
-        </is>
-      </c>
-      <c r="I29" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K29" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>Oregon State @ UTEP</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>-3.8</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>Pick'em</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -6885,758 +7067,483 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
+          <t>UNLV @ Akron</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>+9.3</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Northern Illinois @ Georgia State</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>-11.7</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>-7.8</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Hawai'i @ Wyoming</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>+6.1</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>+1.9</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>New Mexico @ New Mexico State</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>+6.7</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>+12.1</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>+18.8</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Oregon State @ UTEP</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>-3.8</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>+10.5</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
           <t>Air Force @ Nevada</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>+3.5</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>+0.7</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>+2.3</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I31" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>* Tightest (Live) compares each model's line to TODAY's still-moving market line, not a final closing line -- it will keep changing until kickoff. See the graded Game-by-Game table below for the real, closing-line version of this comparison.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2026 Mountain West Games -- Game by Game</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>Final Score</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>Vegas Spread (Home)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>Actual Margin (Home)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>Ridge Line</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G41" s="22" t="inlineStr">
         <is>
           <t>Ridge Edge</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>Ridge Lean</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I41" s="22" t="inlineStr">
         <is>
           <t>Ridge Result</t>
         </is>
       </c>
-      <c r="J36" s="22" t="inlineStr">
+      <c r="J41" s="22" t="inlineStr">
         <is>
           <t>XGBoost Line</t>
         </is>
       </c>
-      <c r="K36" s="22" t="inlineStr">
+      <c r="K41" s="22" t="inlineStr">
         <is>
           <t>XGBoost Edge</t>
         </is>
       </c>
-      <c r="L36" s="22" t="inlineStr">
+      <c r="L41" s="22" t="inlineStr">
         <is>
           <t>XGBoost Lean</t>
         </is>
       </c>
-      <c r="M36" s="22" t="inlineStr">
+      <c r="M41" s="22" t="inlineStr">
         <is>
           <t>XGBoost Result</t>
         </is>
       </c>
-      <c r="N36" s="22" t="inlineStr">
+      <c r="N41" s="22" t="inlineStr">
         <is>
           <t>Gamma Line</t>
         </is>
       </c>
-      <c r="O36" s="22" t="inlineStr">
+      <c r="O41" s="22" t="inlineStr">
         <is>
           <t>Gamma Edge</t>
         </is>
       </c>
-      <c r="P36" s="22" t="inlineStr">
+      <c r="P41" s="22" t="inlineStr">
         <is>
           <t>Gamma Lean</t>
         </is>
       </c>
-      <c r="Q36" s="22" t="inlineStr">
+      <c r="Q41" s="22" t="inlineStr">
         <is>
           <t>Gamma Result</t>
         </is>
       </c>
-      <c r="R36" s="22" t="inlineStr">
+      <c r="R41" s="22" t="inlineStr">
+        <is>
+          <t>Massey Line</t>
+        </is>
+      </c>
+      <c r="S41" s="22" t="inlineStr">
+        <is>
+          <t>Massey Edge</t>
+        </is>
+      </c>
+      <c r="T41" s="22" t="inlineStr">
+        <is>
+          <t>Massey Lean</t>
+        </is>
+      </c>
+      <c r="U41" s="22" t="inlineStr">
+        <is>
+          <t>Massey Result</t>
+        </is>
+      </c>
+      <c r="V41" s="22" t="inlineStr">
         <is>
           <t>Ridge/XGBoost Agree?</t>
         </is>
       </c>
-      <c r="S36" s="22" t="inlineStr">
+      <c r="W41" s="22" t="inlineStr">
         <is>
           <t>Ridge Agrees (w/ Live Model)?</t>
         </is>
       </c>
-      <c r="T36" s="22" t="inlineStr">
+      <c r="X41" s="22" t="inlineStr">
         <is>
           <t>Tightest CLV Line</t>
         </is>
       </c>
-      <c r="U36" s="22" t="inlineStr">
+      <c r="Y41" s="22" t="inlineStr">
         <is>
           <t>Ridge CLV Pts (Cum.)</t>
         </is>
       </c>
-      <c r="V36" s="22" t="inlineStr">
+      <c r="Z41" s="22" t="inlineStr">
         <is>
           <t>XGBoost CLV Pts (Cum.)</t>
         </is>
       </c>
-      <c r="W36" s="22" t="inlineStr">
+      <c r="AA41" s="22" t="inlineStr">
         <is>
           <t>Gamma CLV Pts (Cum.)</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Duquesne @ Air Force</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="inlineStr">
-        <is>
-          <t>0-34</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>-30.0</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>+34.0</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>-17.0</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I37" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>-29.0</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="L37" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M37" s="25" t="inlineStr">
-        <is>
-          <t>Loss (no real edge)</t>
-        </is>
-      </c>
-      <c r="N37" s="23" t="inlineStr">
-        <is>
-          <t>-36.5</t>
-        </is>
-      </c>
-      <c r="O37" s="23" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
-      <c r="P37" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q37" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R37" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S37" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T37" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U37" s="23" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
-      <c r="V37" s="23" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="W37" s="23" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Wyoming @ Colorado State</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>13-35</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>-7.8</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>+5.1</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>-2.9</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
-      <c r="L38" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M38" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N38" s="23" t="inlineStr">
-        <is>
-          <t>-6.4</t>
-        </is>
-      </c>
-      <c r="O38" s="23" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
-      <c r="P38" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q38" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R38" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S38" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T38" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U38" s="23" t="inlineStr">
-        <is>
-          <t>-7.9</t>
-        </is>
-      </c>
-      <c r="V38" s="23" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
-      <c r="W38" s="23" t="inlineStr">
-        <is>
-          <t>+10.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>San José State @ Eastern Michigan</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>27-21</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>-15.8</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr">
-        <is>
-          <t>+14.3</t>
-        </is>
-      </c>
-      <c r="H39" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I39" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>-10.1</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>+8.6</t>
-        </is>
-      </c>
-      <c r="L39" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M39" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N39" s="23" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="O39" s="23" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="P39" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q39" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R39" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S39" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T39" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U39" s="23" t="inlineStr">
-        <is>
-          <t>+6.4</t>
-        </is>
-      </c>
-      <c r="V39" s="23" t="inlineStr">
-        <is>
-          <t>+7.8</t>
-        </is>
-      </c>
-      <c r="W39" s="23" t="inlineStr">
-        <is>
-          <t>+8.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>UNLV @ Hawai'i</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>21-6</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="H40" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I40" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>+4.6</t>
-        </is>
-      </c>
-      <c r="L40" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M40" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N40" s="23" t="inlineStr">
-        <is>
-          <t>+4.4</t>
-        </is>
-      </c>
-      <c r="O40" s="23" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="P40" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q40" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge) (seed week)</t>
-        </is>
-      </c>
-      <c r="R40" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S40" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T40" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U40" s="23" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
-      <c r="V40" s="23" t="inlineStr">
-        <is>
-          <t>+12.4</t>
-        </is>
-      </c>
-      <c r="W40" s="23" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Northern Illinois @ Iowa</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>0-40</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>-31.8</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>+40.0</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>-28.3</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I41" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>-24.3</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>-7.4</t>
-        </is>
-      </c>
-      <c r="L41" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M41" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N41" s="23" t="inlineStr">
-        <is>
-          <t>-41.0</t>
-        </is>
-      </c>
-      <c r="O41" s="23" t="inlineStr">
-        <is>
-          <t>+9.2</t>
-        </is>
-      </c>
-      <c r="P41" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q41" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
-        </is>
-      </c>
-      <c r="R41" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S41" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U41" s="23" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
-      <c r="V41" s="23" t="inlineStr">
-        <is>
-          <t>+4.9</t>
-        </is>
-      </c>
-      <c r="W41" s="23" t="inlineStr">
-        <is>
-          <t>+15.8</t>
+      <c r="AB41" s="22" t="inlineStr">
+        <is>
+          <t>Massey CLV Pts (Cum.)</t>
         </is>
       </c>
     </row>
@@ -7646,32 +7553,32 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Western Kentucky @ Nevada</t>
+          <t>Duquesne @ Air Force</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>14-49</t>
+          <t>0-34</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>-30.0</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>+35.0</t>
+          <t>+34.0</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>+3.3</t>
+          <t>-17.0</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="H42" s="23" t="inlineStr">
@@ -7679,19 +7586,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="I42" s="25" t="inlineStr">
+      <c r="I42" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>+6.7</t>
+          <t>-28.3</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="L42" s="23" t="inlineStr">
@@ -7699,19 +7606,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="M42" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="M42" s="24" t="inlineStr">
+        <is>
+          <t>Loss (no real edge)</t>
         </is>
       </c>
       <c r="N42" s="23" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-36.5</t>
         </is>
       </c>
       <c r="O42" s="23" t="inlineStr">
         <is>
-          <t>+2.7</t>
+          <t>+6.5</t>
         </is>
       </c>
       <c r="P42" s="23" t="inlineStr">
@@ -7719,39 +7626,64 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q42" s="24" t="inlineStr">
+      <c r="Q42" s="25" t="inlineStr">
         <is>
           <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R42" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S42" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T42" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U42" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V42" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S42" s="23" t="inlineStr">
+      <c r="W42" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U42" s="23" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="V42" s="23" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="W42" s="23" t="inlineStr">
-        <is>
-          <t>+18.5</t>
+      <c r="X42" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Y42" s="23" t="inlineStr">
+        <is>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="Z42" s="23" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="AA42" s="23" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+      <c r="AB42" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -7761,32 +7693,32 @@
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Central Michigan @ New Mexico</t>
+          <t>Wyoming @ Colorado State</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>7-38</t>
+          <t>13-35</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>-11.2</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>+31.0</t>
+          <t>+22.0</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>-17.5</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
-          <t>+6.2</t>
+          <t>+5.1</t>
         </is>
       </c>
       <c r="H43" s="23" t="inlineStr">
@@ -7794,19 +7726,19 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="I43" s="24" t="inlineStr">
+      <c r="I43" s="25" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>-10.6</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="L43" s="23" t="inlineStr">
@@ -7814,19 +7746,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="M43" s="25" t="inlineStr">
+      <c r="M43" s="24" t="inlineStr">
         <is>
           <t>Loss (no real edge)</t>
         </is>
       </c>
       <c r="N43" s="23" t="inlineStr">
         <is>
-          <t>-15.6</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="O43" s="23" t="inlineStr">
         <is>
-          <t>+4.3</t>
+          <t>+3.7</t>
         </is>
       </c>
       <c r="P43" s="23" t="inlineStr">
@@ -7834,39 +7766,64 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q43" s="24" t="inlineStr">
+      <c r="Q43" s="25" t="inlineStr">
         <is>
           <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S43" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T43" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U43" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V43" s="23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S43" s="23" t="inlineStr">
+      <c r="W43" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T43" s="24" t="inlineStr">
+      <c r="X43" s="25" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U43" s="23" t="inlineStr">
-        <is>
-          <t>+5.9</t>
-        </is>
-      </c>
-      <c r="V43" s="23" t="inlineStr">
-        <is>
-          <t>-2.2</t>
-        </is>
-      </c>
-      <c r="W43" s="23" t="inlineStr">
-        <is>
-          <t>+22.9</t>
+      <c r="Y43" s="23" t="inlineStr">
+        <is>
+          <t>-7.9</t>
+        </is>
+      </c>
+      <c r="Z43" s="23" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="AA43" s="23" t="inlineStr">
+        <is>
+          <t>+10.2</t>
+        </is>
+      </c>
+      <c r="AB43" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -7876,112 +7833,137 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Fordham @ North Dakota State</t>
+          <t>San José State @ Eastern Michigan</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>0-38</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>-41.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>+38.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>-40.9</t>
+          <t>-15.8</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>+14.3</t>
         </is>
       </c>
       <c r="H44" s="23" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>+9.0</t>
+        </is>
+      </c>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M44" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N44" s="23" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="O44" s="23" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="P44" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>-34.8</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr">
-        <is>
-          <t>-6.7</t>
-        </is>
-      </c>
-      <c r="L44" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M44" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N44" s="23" t="inlineStr">
-        <is>
-          <t>-58.5</t>
-        </is>
-      </c>
-      <c r="O44" s="23" t="inlineStr">
-        <is>
-          <t>+17.0</t>
-        </is>
-      </c>
-      <c r="P44" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
       <c r="Q44" s="25" t="inlineStr">
         <is>
-          <t>Loss (seed week)</t>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R44" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S44" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T44" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U44" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V44" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S44" s="23" t="inlineStr">
+      <c r="W44" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T44" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U44" s="23" t="inlineStr">
-        <is>
-          <t>+5.3</t>
-        </is>
-      </c>
-      <c r="V44" s="23" t="inlineStr">
-        <is>
-          <t>-8.9</t>
-        </is>
-      </c>
-      <c r="W44" s="23" t="inlineStr">
-        <is>
-          <t>+39.8</t>
+      <c r="X44" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Y44" s="23" t="inlineStr">
+        <is>
+          <t>+6.4</t>
+        </is>
+      </c>
+      <c r="Z44" s="23" t="inlineStr">
+        <is>
+          <t>+7.2</t>
+        </is>
+      </c>
+      <c r="AA44" s="23" t="inlineStr">
+        <is>
+          <t>+8.2</t>
+        </is>
+      </c>
+      <c r="AB44" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -7991,112 +7973,137 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Jacksonville State @ North Dakota State</t>
+          <t>UNLV @ Hawai'i</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>7-33</t>
+          <t>21-6</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>+2.8</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>+26.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>-18.4</t>
+          <t>+2.9</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>+11.6</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I45" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>+4.6</t>
+        </is>
+      </c>
+      <c r="L45" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I45" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="inlineStr">
-        <is>
-          <t>+8.3</t>
-        </is>
-      </c>
-      <c r="L45" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
       <c r="M45" s="24" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Loss</t>
         </is>
       </c>
       <c r="N45" s="23" t="inlineStr">
         <is>
-          <t>-25.5</t>
+          <t>+4.4</t>
         </is>
       </c>
       <c r="O45" s="23" t="inlineStr">
         <is>
-          <t>+18.7</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="P45" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q45" s="24" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q45" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge) (seed week)</t>
         </is>
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S45" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T45" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U45" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V45" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W45" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S45" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T45" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U45" s="23" t="inlineStr">
-        <is>
-          <t>+16.9</t>
-        </is>
-      </c>
-      <c r="V45" s="23" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="W45" s="23" t="inlineStr">
-        <is>
-          <t>+58.5</t>
+      <c r="X45" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="Y45" s="23" t="inlineStr">
+        <is>
+          <t>+6.2</t>
+        </is>
+      </c>
+      <c r="Z45" s="23" t="inlineStr">
+        <is>
+          <t>+11.8</t>
+        </is>
+      </c>
+      <c r="AA45" s="23" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+      <c r="AB45" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -8106,32 +8113,32 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>UTEP @ Oklahoma</t>
+          <t>Northern Illinois @ Iowa</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>0-51</t>
+          <t>0-40</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>-40.8</t>
+          <t>-31.8</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>+51.0</t>
+          <t>+40.0</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>-34.8</t>
+          <t>-28.3</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="H46" s="23" t="inlineStr">
@@ -8139,19 +8146,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="I46" s="25" t="inlineStr">
+      <c r="I46" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>-32.8</t>
+          <t>-25.4</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="L46" s="23" t="inlineStr">
@@ -8159,19 +8166,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="M46" s="25" t="inlineStr">
+      <c r="M46" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="N46" s="23" t="inlineStr">
         <is>
-          <t>-44.4</t>
+          <t>-41.0</t>
         </is>
       </c>
       <c r="O46" s="23" t="inlineStr">
         <is>
-          <t>+3.6</t>
+          <t>+9.2</t>
         </is>
       </c>
       <c r="P46" s="23" t="inlineStr">
@@ -8179,39 +8186,64 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q46" s="24" t="inlineStr">
+      <c r="Q46" s="25" t="inlineStr">
         <is>
           <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R46" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S46" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T46" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U46" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V46" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S46" s="23" t="inlineStr">
+      <c r="W46" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T46" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U46" s="23" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
-      <c r="V46" s="23" t="inlineStr">
-        <is>
-          <t>-8.6</t>
-        </is>
-      </c>
-      <c r="W46" s="23" t="inlineStr">
-        <is>
-          <t>+62.1</t>
+      <c r="X46" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="Y46" s="23" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
+      <c r="Z46" s="23" t="inlineStr">
+        <is>
+          <t>+5.4</t>
+        </is>
+      </c>
+      <c r="AA46" s="23" t="inlineStr">
+        <is>
+          <t>+15.8</t>
+        </is>
+      </c>
+      <c r="AB46" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -8221,32 +8253,32 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>Hawai'i @ Stanford</t>
+          <t>Western Kentucky @ Nevada</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>27-37</t>
+          <t>14-49</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>+10.0</t>
+          <t>+35.0</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+3.3</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="H47" s="23" t="inlineStr">
@@ -8254,19 +8286,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="I47" s="25" t="inlineStr">
+      <c r="I47" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>+7.3</t>
         </is>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>-5.3</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="L47" s="23" t="inlineStr">
@@ -8274,19 +8306,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="M47" s="25" t="inlineStr">
+      <c r="M47" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="N47" s="23" t="inlineStr">
         <is>
-          <t>-11.2</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="O47" s="23" t="inlineStr">
         <is>
-          <t>+6.4</t>
+          <t>+2.7</t>
         </is>
       </c>
       <c r="P47" s="23" t="inlineStr">
@@ -8294,39 +8326,64 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q47" s="24" t="inlineStr">
+      <c r="Q47" s="25" t="inlineStr">
         <is>
           <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S47" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T47" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U47" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V47" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S47" s="23" t="inlineStr">
+      <c r="W47" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T47" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U47" s="23" t="inlineStr">
-        <is>
-          <t>+7.7</t>
-        </is>
-      </c>
-      <c r="V47" s="23" t="inlineStr">
-        <is>
-          <t>-14.0</t>
-        </is>
-      </c>
-      <c r="W47" s="23" t="inlineStr">
-        <is>
-          <t>+68.5</t>
+      <c r="X47" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Y47" s="23" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="Z47" s="23" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="AA47" s="23" t="inlineStr">
+        <is>
+          <t>+18.5</t>
+        </is>
+      </c>
+      <c r="AB47" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -8336,27 +8393,27 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Memphis @ UNLV</t>
+          <t>Central Michigan @ New Mexico</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>7-38</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-11.2</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>+31.0</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-17.5</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
@@ -8371,17 +8428,17 @@
       </c>
       <c r="I48" s="25" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>+1.4</t>
+          <t>+0.3</t>
         </is>
       </c>
       <c r="L48" s="23" t="inlineStr">
@@ -8391,57 +8448,82 @@
       </c>
       <c r="M48" s="25" t="inlineStr">
         <is>
-          <t>Loss (no real edge)</t>
+          <t>Win (no real edge)</t>
         </is>
       </c>
       <c r="N48" s="23" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>-15.6</t>
         </is>
       </c>
       <c r="O48" s="23" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>+4.3</t>
         </is>
       </c>
       <c r="P48" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q48" s="24" t="inlineStr">
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q48" s="25" t="inlineStr">
         <is>
           <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R48" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S48" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T48" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U48" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V48" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S48" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T48" s="24" t="inlineStr">
+      <c r="W48" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" s="25" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U48" s="23" t="inlineStr">
-        <is>
-          <t>+13.9</t>
-        </is>
-      </c>
-      <c r="V48" s="23" t="inlineStr">
-        <is>
-          <t>-12.5</t>
-        </is>
-      </c>
-      <c r="W48" s="23" t="inlineStr">
-        <is>
-          <t>+62.2</t>
+      <c r="Y48" s="23" t="inlineStr">
+        <is>
+          <t>+5.9</t>
+        </is>
+      </c>
+      <c r="Z48" s="23" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="AA48" s="23" t="inlineStr">
+        <is>
+          <t>+22.9</t>
+        </is>
+      </c>
+      <c r="AB48" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -8451,687 +8533,837 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>San José State @ USC</t>
+          <t>Jacksonville State @ North Dakota State</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>26-42</t>
+          <t>7-33</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>-37.2</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>+16.0</t>
+          <t>+26.0</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>-34.6</t>
+          <t>-18.4</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>+11.6</t>
         </is>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I49" s="24" t="inlineStr">
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I49" s="25" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>-34.3</t>
+          <t>-14.4</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>+7.7</t>
         </is>
       </c>
       <c r="L49" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M49" s="24" t="inlineStr">
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M49" s="25" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
       <c r="N49" s="23" t="inlineStr">
         <is>
-          <t>-30.3</t>
+          <t>-25.5</t>
         </is>
       </c>
       <c r="O49" s="23" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>+18.7</t>
         </is>
       </c>
       <c r="P49" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q49" s="24" t="inlineStr">
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q49" s="25" t="inlineStr">
         <is>
           <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S49" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T49" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U49" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V49" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S49" s="23" t="inlineStr">
+      <c r="W49" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T49" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U49" s="23" t="inlineStr">
-        <is>
-          <t>+11.2</t>
-        </is>
-      </c>
-      <c r="V49" s="23" t="inlineStr">
-        <is>
-          <t>-15.5</t>
-        </is>
-      </c>
-      <c r="W49" s="23" t="inlineStr">
-        <is>
-          <t>+55.2</t>
+      <c r="X49" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Y49" s="23" t="inlineStr">
+        <is>
+          <t>+17.6</t>
+        </is>
+      </c>
+      <c r="Z49" s="23" t="inlineStr">
+        <is>
+          <t>+6.3</t>
+        </is>
+      </c>
+      <c r="AA49" s="23" t="inlineStr">
+        <is>
+          <t>+41.6</t>
+        </is>
+      </c>
+      <c r="AB49" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>North Dakota State @ Air Force</t>
+          <t>Fordham @ North Dakota State</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>38-32</t>
+          <t>0-38</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>+1.8</t>
+          <t>-41.5</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>+38.0</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
+          <t>-40.9</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I50" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="L50" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M50" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N50" s="23" t="inlineStr">
+        <is>
+          <t>-58.5</t>
+        </is>
+      </c>
+      <c r="O50" s="23" t="inlineStr">
+        <is>
           <t>+17.0</t>
         </is>
       </c>
-      <c r="G50" s="23" t="inlineStr">
-        <is>
-          <t>-15.3</t>
-        </is>
-      </c>
-      <c r="H50" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>+14.3</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
-        <is>
-          <t>-12.5</t>
-        </is>
-      </c>
-      <c r="L50" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M50" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N50" s="23" t="inlineStr">
-        <is>
-          <t>+17.9</t>
-        </is>
-      </c>
-      <c r="O50" s="23" t="inlineStr">
-        <is>
-          <t>-16.2</t>
-        </is>
-      </c>
       <c r="P50" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="Q50" s="24" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Loss (seed week)</t>
         </is>
       </c>
       <c r="R50" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S50" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T50" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U50" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V50" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S50" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T50" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U50" s="23" t="inlineStr">
-        <is>
-          <t>-4.1</t>
-        </is>
-      </c>
-      <c r="V50" s="23" t="inlineStr">
-        <is>
-          <t>-28.0</t>
-        </is>
-      </c>
       <c r="W50" s="23" t="inlineStr">
         <is>
-          <t>+39.0</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X50" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="Y50" s="23" t="inlineStr">
+        <is>
+          <t>+16.9</t>
+        </is>
+      </c>
+      <c r="Z50" s="23" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="AA50" s="23" t="inlineStr">
+        <is>
+          <t>+58.5</t>
+        </is>
+      </c>
+      <c r="AB50" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>New Mexico State @ Hawai'i</t>
+          <t>UTEP @ Oklahoma</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>19-29</t>
+          <t>0-51</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-40.8</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>+10.0</t>
+          <t>+51.0</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>-14.1</t>
+          <t>-34.8</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>+6.6</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J51" s="23" t="inlineStr">
+        <is>
+          <t>-32.8</t>
+        </is>
+      </c>
+      <c r="K51" s="23" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="L51" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M51" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N51" s="23" t="inlineStr">
+        <is>
+          <t>-44.4</t>
+        </is>
+      </c>
+      <c r="O51" s="23" t="inlineStr">
+        <is>
+          <t>+3.6</t>
+        </is>
+      </c>
+      <c r="P51" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I51" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J51" s="23" t="inlineStr">
-        <is>
-          <t>-12.9</t>
-        </is>
-      </c>
-      <c r="K51" s="23" t="inlineStr">
-        <is>
-          <t>+5.4</t>
-        </is>
-      </c>
-      <c r="L51" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M51" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N51" s="23" t="inlineStr">
-        <is>
-          <t>-7.6</t>
-        </is>
-      </c>
-      <c r="O51" s="23" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
-      <c r="P51" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q51" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
+      <c r="Q51" s="25" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S51" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T51" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U51" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V51" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S51" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T51" s="24" t="inlineStr">
+      <c r="W51" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X51" s="25" t="inlineStr">
         <is>
           <t>Gamma</t>
         </is>
       </c>
-      <c r="U51" s="23" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="V51" s="23" t="inlineStr">
-        <is>
-          <t>-22.5</t>
-        </is>
-      </c>
-      <c r="W51" s="23" t="inlineStr">
-        <is>
-          <t>+39.1</t>
+      <c r="Y51" s="23" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
+      <c r="Z51" s="23" t="inlineStr">
+        <is>
+          <t>-8.2</t>
+        </is>
+      </c>
+      <c r="AA51" s="23" t="inlineStr">
+        <is>
+          <t>+62.1</t>
+        </is>
+      </c>
+      <c r="AB51" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Montana State @ Nevada</t>
+          <t>Hawai'i @ Stanford</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
-          <t>20-7</t>
+          <t>27-37</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>+10.0</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>-17.2</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
-          <t>+22.2</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="H52" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>+1.1</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr">
+        <is>
+          <t>-5.8</t>
+        </is>
+      </c>
+      <c r="L52" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M52" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N52" s="23" t="inlineStr">
+        <is>
+          <t>-11.2</t>
+        </is>
+      </c>
+      <c r="O52" s="23" t="inlineStr">
+        <is>
+          <t>+6.4</t>
+        </is>
+      </c>
+      <c r="P52" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I52" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J52" s="23" t="inlineStr">
-        <is>
-          <t>-13.2</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="inlineStr">
-        <is>
-          <t>+18.2</t>
-        </is>
-      </c>
-      <c r="L52" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M52" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N52" s="23" t="inlineStr">
-        <is>
-          <t>-33.6</t>
-        </is>
-      </c>
-      <c r="O52" s="23" t="inlineStr">
-        <is>
-          <t>+38.6</t>
-        </is>
-      </c>
-      <c r="P52" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
       <c r="Q52" s="25" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R52" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S52" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T52" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U52" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V52" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S52" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U52" s="23" t="inlineStr">
-        <is>
-          <t>+24.8</t>
-        </is>
-      </c>
-      <c r="V52" s="23" t="inlineStr">
-        <is>
-          <t>-4.4</t>
-        </is>
-      </c>
       <c r="W52" s="23" t="inlineStr">
         <is>
-          <t>+77.8</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X52" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="Y52" s="23" t="inlineStr">
+        <is>
+          <t>+7.7</t>
+        </is>
+      </c>
+      <c r="Z52" s="23" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
+      <c r="AA52" s="23" t="inlineStr">
+        <is>
+          <t>+68.5</t>
+        </is>
+      </c>
+      <c r="AB52" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>Mercyhurst @ New Mexico</t>
+          <t>Memphis @ UNLV</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>7-70</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>-42.2</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>+63.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>-17.0</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>-25.2</t>
+          <t>+6.2</t>
         </is>
       </c>
       <c r="H53" s="23" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>-7.4</t>
+        </is>
+      </c>
+      <c r="K53" s="23" t="inlineStr">
+        <is>
+          <t>+2.6</t>
+        </is>
+      </c>
+      <c r="L53" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M53" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N53" s="23" t="inlineStr">
+        <is>
+          <t>+1.6</t>
+        </is>
+      </c>
+      <c r="O53" s="23" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
+      <c r="P53" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I53" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="J53" s="23" t="inlineStr">
-        <is>
-          <t>-27.7</t>
-        </is>
-      </c>
-      <c r="K53" s="23" t="inlineStr">
-        <is>
-          <t>-14.6</t>
-        </is>
-      </c>
-      <c r="L53" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M53" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N53" s="23" t="inlineStr">
-        <is>
-          <t>-45.6</t>
-        </is>
-      </c>
-      <c r="O53" s="23" t="inlineStr">
-        <is>
-          <t>+3.3</t>
-        </is>
-      </c>
-      <c r="P53" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q53" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="Q53" s="25" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R53" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S53" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T53" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U53" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V53" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S53" s="23" t="inlineStr">
+      <c r="W53" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T53" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U53" s="23" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="V53" s="23" t="inlineStr">
-        <is>
-          <t>-18.9</t>
-        </is>
-      </c>
-      <c r="W53" s="23" t="inlineStr">
-        <is>
-          <t>+81.1</t>
+      <c r="X53" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Y53" s="23" t="inlineStr">
+        <is>
+          <t>+13.9</t>
+        </is>
+      </c>
+      <c r="Z53" s="23" t="inlineStr">
+        <is>
+          <t>-11.4</t>
+        </is>
+      </c>
+      <c r="AA53" s="23" t="inlineStr">
+        <is>
+          <t>+62.2</t>
+        </is>
+      </c>
+      <c r="AB53" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>UNLV @ North Texas</t>
+          <t>San José State @ USC</t>
         </is>
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>6-44</t>
+          <t>26-42</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>+2.8</t>
+          <t>-37.2</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>+38.0</t>
+          <t>+16.0</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-34.6</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>+6.3</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="H54" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I54" s="24" t="inlineStr">
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I54" s="25" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>+1.1</t>
+          <t>-35.3</t>
         </is>
       </c>
       <c r="K54" s="23" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="L54" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M54" s="24" t="inlineStr">
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M54" s="25" t="inlineStr">
         <is>
           <t>Win (no real edge)</t>
         </is>
       </c>
       <c r="N54" s="23" t="inlineStr">
         <is>
-          <t>-5.3</t>
+          <t>-30.3</t>
         </is>
       </c>
       <c r="O54" s="23" t="inlineStr">
         <is>
-          <t>+8.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="P54" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q54" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q54" s="25" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R54" s="23" t="inlineStr">
         <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S54" s="23" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T54" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="U54" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="V54" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S54" s="23" t="inlineStr">
+      <c r="W54" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T54" s="24" t="inlineStr">
+      <c r="X54" s="25" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U54" s="23" t="inlineStr">
-        <is>
-          <t>+5.9</t>
-        </is>
-      </c>
-      <c r="V54" s="23" t="inlineStr">
-        <is>
-          <t>-17.3</t>
-        </is>
-      </c>
-      <c r="W54" s="23" t="inlineStr">
-        <is>
-          <t>+89.1</t>
+      <c r="Y54" s="23" t="inlineStr">
+        <is>
+          <t>+11.2</t>
+        </is>
+      </c>
+      <c r="Z54" s="23" t="inlineStr">
+        <is>
+          <t>-13.3</t>
+        </is>
+      </c>
+      <c r="AA54" s="23" t="inlineStr">
+        <is>
+          <t>+55.2</t>
+        </is>
+      </c>
+      <c r="AB54" s="23" t="inlineStr">
+        <is>
+          <t>+0.0</t>
         </is>
       </c>
     </row>
@@ -9141,112 +9373,137 @@
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>Illinois State @ Northern Illinois</t>
+          <t>North Dakota State @ Air Force</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
-          <t>28-24</t>
+          <t>38-32</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>+1.8</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>+17.0</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>+17.5</t>
+          <t>-15.3</t>
         </is>
       </c>
       <c r="H55" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I55" s="25" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>-15.7</t>
+          <t>+14.7</t>
         </is>
       </c>
       <c r="K55" s="23" t="inlineStr">
         <is>
-          <t>+18.2</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="L55" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="M55" s="25" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="N55" s="23" t="inlineStr">
         <is>
-          <t>-23.3</t>
+          <t>+17.9</t>
         </is>
       </c>
       <c r="O55" s="23" t="inlineStr">
         <is>
-          <t>+25.8</t>
+          <t>-16.2</t>
         </is>
       </c>
       <c r="P55" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="Q55" s="25" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="R55" s="23" t="inlineStr">
         <is>
+          <t>+1.9</t>
+        </is>
+      </c>
+      <c r="S55" s="23" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="T55" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="U55" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="V55" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S55" s="23" t="inlineStr">
+      <c r="W55" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T55" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U55" s="23" t="inlineStr">
-        <is>
-          <t>+23.4</t>
-        </is>
-      </c>
-      <c r="V55" s="23" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
-      <c r="W55" s="23" t="inlineStr">
-        <is>
-          <t>+114.9</t>
+      <c r="X55" s="25" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="Y55" s="23" t="inlineStr">
+        <is>
+          <t>-4.1</t>
+        </is>
+      </c>
+      <c r="Z55" s="23" t="inlineStr">
+        <is>
+          <t>-26.3</t>
+        </is>
+      </c>
+      <c r="AA55" s="23" t="inlineStr">
+        <is>
+          <t>+39.0</t>
+        </is>
+      </c>
+      <c r="AB55" s="23" t="inlineStr">
+        <is>
+          <t>-0.2</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9513,17 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Cal Poly @ San José State</t>
+          <t>New Mexico State @ Hawai'i</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>19-29</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>-21.5</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
@@ -9276,92 +9533,117 @@
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>-19.9</t>
+          <t>-14.1</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>+6.6</t>
         </is>
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I56" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>-13.3</t>
+        </is>
+      </c>
+      <c r="K56" s="23" t="inlineStr">
+        <is>
+          <t>+5.8</t>
+        </is>
+      </c>
+      <c r="L56" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M56" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N56" s="23" t="inlineStr">
+        <is>
+          <t>-7.6</t>
+        </is>
+      </c>
+      <c r="O56" s="23" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
+      <c r="P56" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q56" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="R56" s="23" t="inlineStr">
+        <is>
+          <t>+7.2</t>
+        </is>
+      </c>
+      <c r="S56" s="23" t="inlineStr">
+        <is>
+          <t>-14.7</t>
+        </is>
+      </c>
+      <c r="T56" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I56" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="J56" s="23" t="inlineStr">
-        <is>
-          <t>-27.7</t>
-        </is>
-      </c>
-      <c r="K56" s="23" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
-      <c r="L56" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M56" s="25" t="inlineStr">
+      <c r="U56" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="N56" s="23" t="inlineStr">
-        <is>
-          <t>-30.7</t>
-        </is>
-      </c>
-      <c r="O56" s="23" t="inlineStr">
-        <is>
-          <t>+9.2</t>
-        </is>
-      </c>
-      <c r="P56" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q56" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="R56" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S56" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T56" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U56" s="23" t="inlineStr">
-        <is>
-          <t>+21.8</t>
-        </is>
-      </c>
       <c r="V56" s="23" t="inlineStr">
         <is>
-          <t>+7.1</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W56" s="23" t="inlineStr">
         <is>
-          <t>+124.1</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Y56" s="23" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="Z56" s="23" t="inlineStr">
+        <is>
+          <t>-20.5</t>
+        </is>
+      </c>
+      <c r="AA56" s="23" t="inlineStr">
+        <is>
+          <t>+39.1</t>
+        </is>
+      </c>
+      <c r="AB56" s="23" t="inlineStr">
+        <is>
+          <t>-14.9</t>
         </is>
       </c>
     </row>
@@ -9371,112 +9653,137 @@
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>Texas Southern @ UTEP</t>
+          <t>Montana State @ Nevada</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
-          <t>10-51</t>
+          <t>20-7</t>
         </is>
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>-27.2</t>
+          <t>+5.0</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>+41.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>-14.6</t>
+          <t>-17.2</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>+22.2</t>
         </is>
       </c>
       <c r="H57" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I57" s="25" t="inlineStr">
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>-20.3</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="K57" s="23" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>+16.6</t>
         </is>
       </c>
       <c r="L57" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M57" s="25" t="inlineStr">
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M57" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="N57" s="23" t="inlineStr">
         <is>
-          <t>-19.8</t>
+          <t>-33.6</t>
         </is>
       </c>
       <c r="O57" s="23" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>+38.6</t>
         </is>
       </c>
       <c r="P57" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q57" s="25" t="inlineStr">
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q57" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
       <c r="R57" s="23" t="inlineStr">
         <is>
+          <t>-11.8</t>
+        </is>
+      </c>
+      <c r="S57" s="23" t="inlineStr">
+        <is>
+          <t>+16.8</t>
+        </is>
+      </c>
+      <c r="T57" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="U57" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="V57" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S57" s="23" t="inlineStr">
+      <c r="W57" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T57" s="24" t="inlineStr">
+      <c r="X57" s="25" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U57" s="23" t="inlineStr">
-        <is>
-          <t>+9.2</t>
-        </is>
-      </c>
-      <c r="V57" s="23" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
-      <c r="W57" s="23" t="inlineStr">
-        <is>
-          <t>+116.6</t>
+      <c r="Y57" s="23" t="inlineStr">
+        <is>
+          <t>+24.8</t>
+        </is>
+      </c>
+      <c r="Z57" s="23" t="inlineStr">
+        <is>
+          <t>-3.9</t>
+        </is>
+      </c>
+      <c r="AA57" s="23" t="inlineStr">
+        <is>
+          <t>+77.8</t>
+        </is>
+      </c>
+      <c r="AB57" s="23" t="inlineStr">
+        <is>
+          <t>+1.8</t>
         </is>
       </c>
     </row>
@@ -9486,32 +9793,32 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Northern Colorado @ Wyoming</t>
+          <t>Mercyhurst @ New Mexico</t>
         </is>
       </c>
       <c r="C58" s="23" t="inlineStr">
         <is>
-          <t>13-21</t>
+          <t>7-70</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>-23.5</t>
+          <t>-42.2</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>+8.0</t>
+          <t>+63.0</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>-16.3</t>
+          <t>-17.0</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-25.2</t>
         </is>
       </c>
       <c r="H58" s="23" t="inlineStr">
@@ -9521,227 +9828,277 @@
       </c>
       <c r="I58" s="24" t="inlineStr">
         <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>-28.0</t>
+        </is>
+      </c>
+      <c r="K58" s="23" t="inlineStr">
+        <is>
+          <t>-14.3</t>
+        </is>
+      </c>
+      <c r="L58" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M58" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N58" s="23" t="inlineStr">
+        <is>
+          <t>-45.6</t>
+        </is>
+      </c>
+      <c r="O58" s="23" t="inlineStr">
+        <is>
+          <t>+3.3</t>
+        </is>
+      </c>
+      <c r="P58" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q58" s="25" t="inlineStr">
+        <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="J58" s="23" t="inlineStr">
-        <is>
-          <t>-21.9</t>
-        </is>
-      </c>
-      <c r="K58" s="23" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="L58" s="23" t="inlineStr">
+      <c r="R58" s="23" t="inlineStr">
+        <is>
+          <t>-20.6</t>
+        </is>
+      </c>
+      <c r="S58" s="23" t="inlineStr">
+        <is>
+          <t>-21.6</t>
+        </is>
+      </c>
+      <c r="T58" s="23" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="M58" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="N58" s="23" t="inlineStr">
-        <is>
-          <t>-27.6</t>
-        </is>
-      </c>
-      <c r="O58" s="23" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
-      <c r="P58" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q58" s="25" t="inlineStr">
+      <c r="U58" s="24" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="R58" s="23" t="inlineStr">
+      <c r="V58" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S58" s="23" t="inlineStr">
+      <c r="W58" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T58" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U58" s="23" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
-      <c r="V58" s="23" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="W58" s="23" t="inlineStr">
-        <is>
-          <t>+120.7</t>
+      <c r="X58" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Y58" s="23" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="Z58" s="23" t="inlineStr">
+        <is>
+          <t>-18.2</t>
+        </is>
+      </c>
+      <c r="AA58" s="23" t="inlineStr">
+        <is>
+          <t>+81.1</t>
+        </is>
+      </c>
+      <c r="AB58" s="23" t="inlineStr">
+        <is>
+          <t>-19.8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>Northern Illinois @ Arizona</t>
+          <t>UNLV @ North Texas</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>17-42</t>
+          <t>6-44</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
         <is>
-          <t>-34.5</t>
+          <t>+2.8</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>+25.0</t>
+          <t>+38.0</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>-26.3</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>+6.3</t>
         </is>
       </c>
       <c r="H59" s="23" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I59" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
+      <c r="K59" s="23" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
+      <c r="L59" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M59" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N59" s="23" t="inlineStr">
+        <is>
+          <t>-5.3</t>
+        </is>
+      </c>
+      <c r="O59" s="23" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
+      <c r="P59" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q59" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R59" s="23" t="inlineStr">
+        <is>
+          <t>+5.7</t>
+        </is>
+      </c>
+      <c r="S59" s="23" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T59" s="23" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I59" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J59" s="23" t="inlineStr">
-        <is>
-          <t>-23.8</t>
-        </is>
-      </c>
-      <c r="K59" s="23" t="inlineStr">
-        <is>
-          <t>-10.7</t>
-        </is>
-      </c>
-      <c r="L59" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M59" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N59" s="23" t="inlineStr">
-        <is>
-          <t>-30.9</t>
-        </is>
-      </c>
-      <c r="O59" s="23" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="P59" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q59" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="R59" s="23" t="inlineStr">
+      <c r="U59" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="V59" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S59" s="23" t="inlineStr">
+      <c r="W59" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T59" s="24" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="U59" s="23" t="inlineStr">
-        <is>
-          <t>-6.2</t>
-        </is>
-      </c>
-      <c r="V59" s="23" t="inlineStr">
-        <is>
-          <t>-12.2</t>
-        </is>
-      </c>
-      <c r="W59" s="23" t="inlineStr">
-        <is>
-          <t>+117.1</t>
+      <c r="X59" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Y59" s="23" t="inlineStr">
+        <is>
+          <t>+5.9</t>
+        </is>
+      </c>
+      <c r="Z59" s="23" t="inlineStr">
+        <is>
+          <t>-16.8</t>
+        </is>
+      </c>
+      <c r="AA59" s="23" t="inlineStr">
+        <is>
+          <t>+89.1</t>
+        </is>
+      </c>
+      <c r="AB59" s="23" t="inlineStr">
+        <is>
+          <t>-22.7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Wyoming @ Central Michigan</t>
+          <t>Illinois State @ Northern Illinois</t>
         </is>
       </c>
       <c r="C60" s="23" t="inlineStr">
         <is>
-          <t>10-24</t>
+          <t>28-24</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
         <is>
-          <t>+1.8</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>+14.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>-9.5</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
-          <t>+11.3</t>
+          <t>+17.5</t>
         </is>
       </c>
       <c r="H60" s="23" t="inlineStr">
@@ -9751,327 +10108,402 @@
       </c>
       <c r="I60" s="24" t="inlineStr">
         <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J60" s="23" t="inlineStr">
+        <is>
+          <t>-16.3</t>
+        </is>
+      </c>
+      <c r="K60" s="23" t="inlineStr">
+        <is>
+          <t>+18.8</t>
+        </is>
+      </c>
+      <c r="L60" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M60" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N60" s="23" t="inlineStr">
+        <is>
+          <t>-23.3</t>
+        </is>
+      </c>
+      <c r="O60" s="23" t="inlineStr">
+        <is>
+          <t>+25.8</t>
+        </is>
+      </c>
+      <c r="P60" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q60" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R60" s="23" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
+      <c r="S60" s="23" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T60" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="U60" s="25" t="inlineStr">
+        <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="J60" s="23" t="inlineStr">
-        <is>
-          <t>-7.8</t>
-        </is>
-      </c>
-      <c r="K60" s="23" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
-      <c r="L60" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M60" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N60" s="23" t="inlineStr">
-        <is>
-          <t>-9.3</t>
-        </is>
-      </c>
-      <c r="O60" s="23" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
-      <c r="P60" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q60" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="R60" s="23" t="inlineStr">
+      <c r="V60" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S60" s="23" t="inlineStr">
+      <c r="W60" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T60" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U60" s="23" t="inlineStr">
-        <is>
-          <t>+5.1</t>
-        </is>
-      </c>
-      <c r="V60" s="23" t="inlineStr">
-        <is>
-          <t>-2.7</t>
-        </is>
-      </c>
-      <c r="W60" s="23" t="inlineStr">
-        <is>
-          <t>+128.1</t>
+      <c r="X60" s="25" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="Y60" s="23" t="inlineStr">
+        <is>
+          <t>+23.4</t>
+        </is>
+      </c>
+      <c r="Z60" s="23" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="AA60" s="23" t="inlineStr">
+        <is>
+          <t>+114.9</t>
+        </is>
+      </c>
+      <c r="AB60" s="23" t="inlineStr">
+        <is>
+          <t>-25.2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>UTEP @ Michigan</t>
+          <t>Cal Poly @ San José State</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
         <is>
-          <t>17-52</t>
+          <t>20-30</t>
         </is>
       </c>
       <c r="D61" s="23" t="inlineStr">
         <is>
-          <t>-34.5</t>
+          <t>-21.5</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>+35.0</t>
+          <t>+10.0</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>-35.0</t>
+          <t>-19.9</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="H61" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I61" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
+        <is>
+          <t>-27.6</t>
+        </is>
+      </c>
+      <c r="K61" s="23" t="inlineStr">
+        <is>
+          <t>+6.1</t>
+        </is>
+      </c>
+      <c r="L61" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I61" s="24" t="inlineStr">
-        <is>
-          <t>Win (no real edge)</t>
-        </is>
-      </c>
-      <c r="J61" s="23" t="inlineStr">
-        <is>
-          <t>-30.8</t>
-        </is>
-      </c>
-      <c r="K61" s="23" t="inlineStr">
-        <is>
-          <t>-3.7</t>
-        </is>
-      </c>
-      <c r="L61" s="23" t="inlineStr">
+      <c r="M61" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N61" s="23" t="inlineStr">
+        <is>
+          <t>-30.7</t>
+        </is>
+      </c>
+      <c r="O61" s="23" t="inlineStr">
+        <is>
+          <t>+9.2</t>
+        </is>
+      </c>
+      <c r="P61" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q61" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R61" s="23" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="S61" s="23" t="inlineStr">
+        <is>
+          <t>-15.0</t>
+        </is>
+      </c>
+      <c r="T61" s="23" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="M61" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="N61" s="23" t="inlineStr">
-        <is>
-          <t>-29.7</t>
-        </is>
-      </c>
-      <c r="O61" s="23" t="inlineStr">
-        <is>
-          <t>-4.8</t>
-        </is>
-      </c>
-      <c r="P61" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q61" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="R61" s="23" t="inlineStr">
+      <c r="U61" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V61" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S61" s="23" t="inlineStr">
+      <c r="W61" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T61" s="24" t="inlineStr">
+      <c r="X61" s="25" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="U61" s="23" t="inlineStr">
-        <is>
-          <t>+5.6</t>
-        </is>
-      </c>
-      <c r="V61" s="23" t="inlineStr">
-        <is>
-          <t>-6.4</t>
-        </is>
-      </c>
-      <c r="W61" s="23" t="inlineStr">
-        <is>
-          <t>+123.3</t>
+      <c r="Y61" s="23" t="inlineStr">
+        <is>
+          <t>+21.8</t>
+        </is>
+      </c>
+      <c r="Z61" s="23" t="inlineStr">
+        <is>
+          <t>+8.1</t>
+        </is>
+      </c>
+      <c r="AA61" s="23" t="inlineStr">
+        <is>
+          <t>+124.1</t>
+        </is>
+      </c>
+      <c r="AB61" s="23" t="inlineStr">
+        <is>
+          <t>-40.2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Nevada @ Middle Tennessee</t>
+          <t>Texas Southern @ UTEP</t>
         </is>
       </c>
       <c r="C62" s="23" t="inlineStr">
         <is>
-          <t>20-27</t>
+          <t>10-51</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t>+3.8</t>
+          <t>-27.2</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>+7.0</t>
+          <t>+41.0</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-14.6</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
         <is>
-          <t>+7.3</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="H62" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Loss</t>
         </is>
       </c>
       <c r="J62" s="23" t="inlineStr">
         <is>
-          <t>+2.9</t>
+          <t>-19.9</t>
         </is>
       </c>
       <c r="K62" s="23" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="L62" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="M62" s="24" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Loss</t>
         </is>
       </c>
       <c r="N62" s="23" t="inlineStr">
         <is>
-          <t>+2.9</t>
+          <t>-19.8</t>
         </is>
       </c>
       <c r="O62" s="23" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="P62" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="Q62" s="24" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Loss</t>
         </is>
       </c>
       <c r="R62" s="23" t="inlineStr">
         <is>
+          <t>+7.8</t>
+        </is>
+      </c>
+      <c r="S62" s="23" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="T62" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="U62" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="V62" s="23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S62" s="23" t="inlineStr">
+      <c r="W62" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T62" s="24" t="inlineStr">
+      <c r="X62" s="25" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U62" s="23" t="inlineStr">
-        <is>
-          <t>+12.9</t>
-        </is>
-      </c>
-      <c r="V62" s="23" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
-      <c r="W62" s="23" t="inlineStr">
-        <is>
-          <t>+124.2</t>
+      <c r="Y62" s="23" t="inlineStr">
+        <is>
+          <t>+9.2</t>
+        </is>
+      </c>
+      <c r="Z62" s="23" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
+      <c r="AA62" s="23" t="inlineStr">
+        <is>
+          <t>+116.6</t>
+        </is>
+      </c>
+      <c r="AB62" s="23" t="inlineStr">
+        <is>
+          <t>-75.2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>New Mexico @ Oklahoma</t>
+          <t>Northern Colorado @ Wyoming</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
         <is>
-          <t>6-14</t>
+          <t>13-21</t>
         </is>
       </c>
       <c r="D63" s="23" t="inlineStr">
         <is>
-          <t>-21.2</t>
+          <t>-23.5</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
@@ -10081,7 +10513,7 @@
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>-14.1</t>
+          <t>-16.3</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -10094,19 +10526,19 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="I63" s="24" t="inlineStr">
+      <c r="I63" s="25" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
       <c r="J63" s="23" t="inlineStr">
         <is>
-          <t>-14.4</t>
+          <t>-22.1</t>
         </is>
       </c>
       <c r="K63" s="23" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="L63" s="23" t="inlineStr">
@@ -10114,289 +10546,84 @@
           <t>Away</t>
         </is>
       </c>
-      <c r="M63" s="24" t="inlineStr">
+      <c r="M63" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="N63" s="23" t="inlineStr">
+        <is>
+          <t>-27.6</t>
+        </is>
+      </c>
+      <c r="O63" s="23" t="inlineStr">
+        <is>
+          <t>+4.1</t>
+        </is>
+      </c>
+      <c r="P63" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q63" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R63" s="23" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="S63" s="23" t="inlineStr">
+        <is>
+          <t>-24.0</t>
+        </is>
+      </c>
+      <c r="T63" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="U63" s="25" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="N63" s="23" t="inlineStr">
-        <is>
-          <t>-10.8</t>
-        </is>
-      </c>
-      <c r="O63" s="23" t="inlineStr">
-        <is>
-          <t>-10.4</t>
-        </is>
-      </c>
-      <c r="P63" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q63" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="R63" s="23" t="inlineStr">
+      <c r="V63" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S63" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T63" s="24" t="inlineStr">
+      <c r="W63" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X63" s="25" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U63" s="23" t="inlineStr">
-        <is>
-          <t>+5.7</t>
-        </is>
-      </c>
-      <c r="V63" s="23" t="inlineStr">
-        <is>
-          <t>-12.4</t>
-        </is>
-      </c>
-      <c r="W63" s="23" t="inlineStr">
-        <is>
-          <t>+113.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B64" s="23" t="inlineStr">
-        <is>
-          <t>North Dakota State @ Sacramento State</t>
-        </is>
-      </c>
-      <c r="C64" s="23" t="inlineStr">
-        <is>
-          <t>31-10</t>
-        </is>
-      </c>
-      <c r="D64" s="23" t="inlineStr">
-        <is>
-          <t>+25.5</t>
-        </is>
-      </c>
-      <c r="E64" s="23" t="inlineStr">
-        <is>
-          <t>-21.0</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>+13.0</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
-      <c r="H64" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I64" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J64" s="23" t="inlineStr">
-        <is>
-          <t>+19.8</t>
-        </is>
-      </c>
-      <c r="K64" s="23" t="inlineStr">
-        <is>
-          <t>+5.7</t>
-        </is>
-      </c>
-      <c r="L64" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M64" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N64" s="23" t="inlineStr">
-        <is>
-          <t>+35.9</t>
-        </is>
-      </c>
-      <c r="O64" s="23" t="inlineStr">
-        <is>
-          <t>-10.4</t>
-        </is>
-      </c>
-      <c r="P64" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="Q64" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="R64" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S64" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T64" s="24" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="U64" s="23" t="inlineStr">
-        <is>
-          <t>+18.2</t>
-        </is>
-      </c>
-      <c r="V64" s="23" t="inlineStr">
-        <is>
-          <t>-6.7</t>
-        </is>
-      </c>
-      <c r="W64" s="23" t="inlineStr">
-        <is>
-          <t>+103.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B65" s="23" t="inlineStr">
-        <is>
-          <t>Fresno State @ San José State</t>
-        </is>
-      </c>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>26-10</t>
-        </is>
-      </c>
-      <c r="D65" s="23" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
-      <c r="E65" s="23" t="inlineStr">
-        <is>
-          <t>-16.0</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
-      <c r="H65" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I65" s="25" t="inlineStr">
-        <is>
-          <t>Loss (no real edge)</t>
-        </is>
-      </c>
-      <c r="J65" s="23" t="inlineStr">
-        <is>
-          <t>+10.1</t>
-        </is>
-      </c>
-      <c r="K65" s="23" t="inlineStr">
-        <is>
-          <t>-6.1</t>
-        </is>
-      </c>
-      <c r="L65" s="23" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="M65" s="24" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N65" s="23" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
-      <c r="O65" s="23" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
-      <c r="P65" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q65" s="25" t="inlineStr">
-        <is>
-          <t>Loss</t>
-        </is>
-      </c>
-      <c r="R65" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S65" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T65" s="24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="U65" s="23" t="inlineStr">
-        <is>
-          <t>+19.1</t>
-        </is>
-      </c>
-      <c r="V65" s="23" t="inlineStr">
-        <is>
-          <t>-12.8</t>
-        </is>
-      </c>
-      <c r="W65" s="23" t="inlineStr">
-        <is>
-          <t>+106.2</t>
+      <c r="Y63" s="23" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="Z63" s="23" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="AA63" s="23" t="inlineStr">
+        <is>
+          <t>+120.7</t>
+        </is>
+      </c>
+      <c r="AB63" s="23" t="inlineStr">
+        <is>
+          <t>-99.2</t>
         </is>
       </c>
     </row>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="F2" t="n">
         <v>13.5</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-7.8</v>
+        <v>-7.7</v>
       </c>
       <c r="F3" t="n">
         <v>-10</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="F5" t="n">
         <v>12.8</v>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -982,7 +982,7 @@
         <v>47.8</v>
       </c>
       <c r="J2" t="n">
-        <v>50.8</v>
+        <v>52.2</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -1026,7 +1026,7 @@
         <v>-7.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-10</v>
+        <v>-10.5</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -1040,7 +1040,7 @@
         <v>46.1</v>
       </c>
       <c r="J3" t="n">
-        <v>56</v>
+        <v>55.5</v>
       </c>
       <c r="K3" s="6">
         <f>I3-J3</f>
@@ -1096,7 +1096,7 @@
         <v>44.9</v>
       </c>
       <c r="J4" t="n">
-        <v>45.8</v>
+        <v>44.5</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -1138,7 +1138,7 @@
         <v>18.7</v>
       </c>
       <c r="F5" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
@@ -1213,7 +1213,7 @@
         <v>50.9</v>
       </c>
       <c r="J6" t="n">
-        <v>53.5</v>
+        <v>55.5</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -1274,7 +1274,7 @@
         <v>46.6</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="K7" s="10">
         <f>I7-J7</f>
@@ -5636,7 +5636,7 @@
         <v>1760.7</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>4.2</v>
+        <v>10.6</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>0.156824607490598</v>
@@ -5673,7 +5673,7 @@
         <v>1583.6</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-2.7</v>
+        <v>-3.3</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>-0.05248930944528065</v>
@@ -5710,7 +5710,7 @@
         <v>1575.5</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.1020851442163246</v>
@@ -5747,7 +5747,7 @@
         <v>1506.1</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>-5.8</v>
+        <v>-7.1</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.03294096360944201</v>
@@ -5784,7 +5784,7 @@
         <v>1489.8</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>-0.1</v>
+        <v>-2.8</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.3168724868895267</v>
@@ -5821,7 +5821,7 @@
         <v>1399.2</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>-13.7</v>
+        <v>-15</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.04058174869502743</v>
@@ -5858,7 +5858,7 @@
         <v>1385.2</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-16.9</v>
+        <v>-19.7</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>-0.1421253070922879</v>
@@ -5895,7 +5895,7 @@
         <v>1428.8</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>-12.5</v>
+        <v>-13.9</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>0.08220884405806574</v>
@@ -5932,7 +5932,7 @@
         <v>1393.9</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-7.6</v>
+        <v>-9.6</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.07825850329211136</v>
@@ -5969,7 +5969,7 @@
         <v>1375.4</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>-16.2</v>
+        <v>-19.7</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>-0.1670547546022537</v>
@@ -5998,7 +5998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB63"/>
+  <dimension ref="A1:AB70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6121,46 +6121,46 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>8618</v>
+        <v>8693</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="I6" s="23" t="n">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t>71/185 (38%)</t>
+          <t>98/260 (38%)</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
         <is>
-          <t>+731.7</t>
+          <t>+807.5</t>
         </is>
       </c>
     </row>
@@ -6171,46 +6171,46 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>+38.8%</t>
+          <t>+31.7%</t>
         </is>
       </c>
       <c r="I7" s="23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>5/22 (23%)</t>
+          <t>7/29 (24%)</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
         <is>
-          <t>+120.7</t>
+          <t>+106.1</t>
         </is>
       </c>
     </row>
@@ -6221,46 +6221,46 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>8618</v>
+        <v>8693</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>8548</v>
+        <v>8622</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>4273</v>
+        <v>4316</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>4275</v>
+        <v>4306</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="I8" s="23" t="n">
-        <v>6762</v>
+        <v>6826</v>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr">
         <is>
-          <t>2633/8618 (31%)</t>
+          <t>2653/8693 (31%)</t>
         </is>
       </c>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t>+5565.3</t>
+          <t>+5473.7</t>
         </is>
       </c>
     </row>
@@ -6271,46 +6271,46 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F9" s="23" t="n">
         <v>12</v>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="I9" s="23" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>302/978 (31%)</t>
+          <t>297/985 (30%)</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
         <is>
-          <t>+591.7</t>
+          <t>+608.7</t>
         </is>
       </c>
     </row>
@@ -6321,46 +6321,46 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>8618</v>
+        <v>8693</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>8548</v>
+        <v>8622</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>4261</v>
+        <v>4333</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4287</v>
+        <v>4289</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="I10" s="23" t="n">
-        <v>6695</v>
+        <v>6762</v>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>3102/8618 (36%)</t>
+          <t>3097/8693 (36%)</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t>+566.3</t>
+          <t>+98.7</t>
         </is>
       </c>
     </row>
@@ -6371,46 +6371,46 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F11" s="23" t="n">
         <v>12</v>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="I11" s="23" t="n">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>342/978 (35%)</t>
+          <t>340/985 (35%)</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t>+907.7</t>
+          <t>+785.8</t>
         </is>
       </c>
     </row>
@@ -6421,46 +6421,46 @@
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>8618</v>
+        <v>8693</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>7369</v>
+        <v>7443</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>3730</v>
+        <v>3761</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>3639</v>
+        <v>3682</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
+          <t>50.5%</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>-3.5%</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>5678</v>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
           <t>50.6%</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>-3.4%</t>
-        </is>
-      </c>
-      <c r="I12" s="23" t="n">
-        <v>5613</v>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t>50.6%</t>
-        </is>
-      </c>
       <c r="K12" s="23" t="inlineStr">
         <is>
-          <t>2812/7429 (38%)</t>
+          <t>2845/7504 (38%)</t>
         </is>
       </c>
       <c r="L12" s="23" t="inlineStr">
         <is>
-          <t>-10178.7</t>
+          <t>-10816.4</t>
         </is>
       </c>
     </row>
@@ -6471,46 +6471,46 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F13" s="23" t="n">
         <v>10</v>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="I13" s="23" t="n">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K13" s="23" t="inlineStr">
         <is>
-          <t>329/835 (39%)</t>
+          <t>341/842 (40%)</t>
         </is>
       </c>
       <c r="L13" s="23" t="inlineStr">
         <is>
-          <t>-178.4</t>
+          <t>-206.1</t>
         </is>
       </c>
     </row>
@@ -6590,46 +6590,46 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="I17" s="23" t="n">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>71/185 (38%)</t>
+          <t>98/260 (38%)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
         <is>
-          <t>+731.7</t>
+          <t>+807.5</t>
         </is>
       </c>
     </row>
@@ -6640,46 +6640,46 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>+38.8%</t>
+          <t>+31.7%</t>
         </is>
       </c>
       <c r="I18" s="23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>5/22 (23%)</t>
+          <t>7/29 (24%)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
-          <t>+120.7</t>
+          <t>+106.1</t>
         </is>
       </c>
     </row>
@@ -6690,46 +6690,46 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="I19" s="23" t="n">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
         <is>
-          <t>52/185 (28%)</t>
+          <t>66/260 (25%)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
-          <t>-529.7</t>
+          <t>-621.2</t>
         </is>
       </c>
     </row>
@@ -6740,46 +6740,46 @@
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>+11.9%</t>
         </is>
       </c>
       <c r="I20" s="23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>5/22 (23%)</t>
+          <t>7/29 (24%)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+19.1</t>
         </is>
       </c>
     </row>
@@ -6790,46 +6790,46 @@
         </is>
       </c>
       <c r="B21" s="23" t="n">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="C21" s="23" t="n">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="I21" s="23" t="n">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
         <is>
-          <t>54/185 (29%)</t>
+          <t>77/260 (30%)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
         <is>
-          <t>-344.2</t>
+          <t>-592.6</t>
         </is>
       </c>
     </row>
@@ -6840,46 +6840,46 @@
         </is>
       </c>
       <c r="B22" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E22" s="23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="I22" s="23" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>10/22 (45%)</t>
+          <t>12/29 (41%)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-14.1</t>
         </is>
       </c>
     </row>
@@ -6890,46 +6890,46 @@
         </is>
       </c>
       <c r="B23" s="23" t="n">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E23" s="23" t="n">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="I23" s="23" t="n">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="K23" s="23" t="inlineStr">
         <is>
-          <t>8/86 (9%)</t>
+          <t>19/161 (12%)</t>
         </is>
       </c>
       <c r="L23" s="23" t="inlineStr">
         <is>
-          <t>-1344.9</t>
+          <t>-1982.6</t>
         </is>
       </c>
     </row>
@@ -6940,53 +6940,53 @@
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C24" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="D24" s="23" t="n">
-        <v>4</v>
-      </c>
       <c r="E24" s="23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>+7.4%</t>
         </is>
       </c>
       <c r="I24" s="23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
         <is>
-          <t>2/9 (22%)</t>
+          <t>3/16 (19%)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
         <is>
-          <t>-99.2</t>
+          <t>-126.9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.0% of all graded games. Ridge agrees with the live model (Gamma) in 48.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 60.0% of games it has a rating for. Massey agrees with the live model (Gamma) in 34.9% of games it has a rating for.</t>
+          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.5% of all graded games. Ridge agrees with the live model (Gamma) in 53.1% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 62.7% of games it has a rating for. Massey agrees with the live model (Gamma) in 45.3% of games it has a rating for.</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+13.5</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -7082,37 +7082,37 @@
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>+9.3</t>
+          <t>+9.8</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>+3.7</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -7142,32 +7142,32 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.7</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -7192,37 +7192,37 @@
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>+1.2</t>
+          <t>+1.1</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>+1.9</t>
+          <t>+1.4</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+11.2</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -7247,37 +7247,37 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>+12.1</t>
+          <t>+12.2</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>+18.8</t>
+          <t>+18.7</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+10.5</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>+1.8</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
@@ -7312,27 +7312,27 @@
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pick'em</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+5.5</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>+0.7</t>
+          <t>+0.8</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
@@ -7367,27 +7367,27 @@
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I36" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -7593,12 +7593,12 @@
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>-28.3</t>
+          <t>-28.4</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="L42" s="23" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z42" s="23" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AA42" s="23" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="L43" s="23" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="Z43" s="23" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AA43" s="23" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
         <is>
-          <t>+9.0</t>
+          <t>+8.0</t>
         </is>
       </c>
       <c r="L44" s="23" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="Z44" s="23" t="inlineStr">
         <is>
-          <t>+7.2</t>
+          <t>+5.6</t>
         </is>
       </c>
       <c r="AA44" s="23" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>+4.6</t>
+          <t>+4.1</t>
         </is>
       </c>
       <c r="L45" s="23" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="Z45" s="23" t="inlineStr">
         <is>
-          <t>+11.8</t>
+          <t>+9.7</t>
         </is>
       </c>
       <c r="AA45" s="23" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>-25.4</t>
+          <t>-24.4</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="L46" s="23" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="Z46" s="23" t="inlineStr">
         <is>
-          <t>+5.4</t>
+          <t>+2.4</t>
         </is>
       </c>
       <c r="AA46" s="23" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>+7.3</t>
+          <t>+7.0</t>
         </is>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>-7.1</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="L47" s="23" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="Z47" s="23" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AA47" s="23" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>+0.3</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="L48" s="23" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="Z48" s="23" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AA48" s="23" t="inlineStr">
@@ -8533,82 +8533,82 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>Jacksonville State @ North Dakota State</t>
+          <t>Fordham @ North Dakota State</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>7-33</t>
+          <t>0-38</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-41.5</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>+26.0</t>
+          <t>+38.0</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>-18.4</t>
+          <t>-40.9</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>+11.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I49" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>-35.3</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>-6.2</t>
+        </is>
+      </c>
+      <c r="L49" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M49" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N49" s="23" t="inlineStr">
+        <is>
+          <t>-58.5</t>
+        </is>
+      </c>
+      <c r="O49" s="23" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="P49" s="23" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I49" s="25" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>-14.4</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="inlineStr">
-        <is>
-          <t>+7.7</t>
-        </is>
-      </c>
-      <c r="L49" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M49" s="25" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N49" s="23" t="inlineStr">
-        <is>
-          <t>-25.5</t>
-        </is>
-      </c>
-      <c r="O49" s="23" t="inlineStr">
-        <is>
-          <t>+18.7</t>
-        </is>
-      </c>
-      <c r="P49" s="23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q49" s="25" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
+      <c r="Q49" s="24" t="inlineStr">
+        <is>
+          <t>Loss (seed week)</t>
         </is>
       </c>
       <c r="R49" s="23" t="inlineStr">
@@ -8638,27 +8638,27 @@
       </c>
       <c r="W49" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X49" s="25" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="Y49" s="23" t="inlineStr">
         <is>
-          <t>+17.6</t>
+          <t>+5.3</t>
         </is>
       </c>
       <c r="Z49" s="23" t="inlineStr">
         <is>
-          <t>+6.3</t>
+          <t>-10.2</t>
         </is>
       </c>
       <c r="AA49" s="23" t="inlineStr">
         <is>
-          <t>+41.6</t>
+          <t>+39.8</t>
         </is>
       </c>
       <c r="AB49" s="23" t="inlineStr">
@@ -8673,57 +8673,57 @@
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Fordham @ North Dakota State</t>
+          <t>Jacksonville State @ North Dakota State</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>0-38</t>
+          <t>7-33</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>-41.5</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>+38.0</t>
+          <t>+26.0</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>-40.9</t>
+          <t>-18.4</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>+11.6</t>
         </is>
       </c>
       <c r="H50" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I50" s="25" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>-35.0</t>
+          <t>-15.0</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>+8.3</t>
         </is>
       </c>
       <c r="L50" s="23" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="M50" s="25" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="N50" s="23" t="inlineStr">
         <is>
-          <t>-58.5</t>
+          <t>-25.5</t>
         </is>
       </c>
       <c r="O50" s="23" t="inlineStr">
         <is>
-          <t>+17.0</t>
+          <t>+18.7</t>
         </is>
       </c>
       <c r="P50" s="23" t="inlineStr">
@@ -8746,9 +8746,9 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q50" s="24" t="inlineStr">
-        <is>
-          <t>Loss (seed week)</t>
+      <c r="Q50" s="25" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R50" s="23" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="W50" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X50" s="25" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="Y50" s="23" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="Z50" s="23" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AA50" s="23" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>-32.8</t>
+          <t>-31.9</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-8.8</t>
         </is>
       </c>
       <c r="L51" s="23" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="Z51" s="23" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-10.7</t>
         </is>
       </c>
       <c r="AA51" s="23" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>+1.1</t>
+          <t>+1.7</t>
         </is>
       </c>
       <c r="K52" s="23" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="L52" s="23" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="Z52" s="23" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-17.2</t>
         </is>
       </c>
       <c r="AA52" s="23" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="J53" s="23" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="K53" s="23" t="inlineStr">
         <is>
-          <t>+2.6</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="L53" s="23" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="M53" s="24" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Loss (no real edge)</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="Z53" s="23" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-15.6</t>
         </is>
       </c>
       <c r="AA53" s="23" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>-35.3</t>
+          <t>-35.8</t>
         </is>
       </c>
       <c r="K54" s="23" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="L54" s="23" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="Z54" s="23" t="inlineStr">
         <is>
-          <t>-13.3</t>
+          <t>-17.1</t>
         </is>
       </c>
       <c r="AA54" s="23" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>+14.7</t>
+          <t>+14.5</t>
         </is>
       </c>
       <c r="K55" s="23" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-12.8</t>
         </is>
       </c>
       <c r="L55" s="23" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="Z55" s="23" t="inlineStr">
         <is>
-          <t>-26.3</t>
+          <t>-29.8</t>
         </is>
       </c>
       <c r="AA55" s="23" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="J56" s="23" t="inlineStr">
         <is>
-          <t>-13.3</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="K56" s="23" t="inlineStr">
         <is>
-          <t>+5.8</t>
+          <t>+5.4</t>
         </is>
       </c>
       <c r="L56" s="23" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="Z56" s="23" t="inlineStr">
         <is>
-          <t>-20.5</t>
+          <t>-24.4</t>
         </is>
       </c>
       <c r="AA56" s="23" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="K57" s="23" t="inlineStr">
         <is>
-          <t>+16.6</t>
+          <t>+16.4</t>
         </is>
       </c>
       <c r="L57" s="23" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="Z57" s="23" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="AA57" s="23" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="J58" s="23" t="inlineStr">
         <is>
-          <t>-28.0</t>
+          <t>-27.5</t>
         </is>
       </c>
       <c r="K58" s="23" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.7</t>
         </is>
       </c>
       <c r="L58" s="23" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="Z58" s="23" t="inlineStr">
         <is>
-          <t>-18.2</t>
+          <t>-22.8</t>
         </is>
       </c>
       <c r="AA58" s="23" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="J59" s="23" t="inlineStr">
         <is>
-          <t>+1.4</t>
+          <t>+1.6</t>
         </is>
       </c>
       <c r="K59" s="23" t="inlineStr">
         <is>
-          <t>+1.3</t>
+          <t>+1.1</t>
         </is>
       </c>
       <c r="L59" s="23" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="Z59" s="23" t="inlineStr">
         <is>
-          <t>-16.8</t>
+          <t>-21.7</t>
         </is>
       </c>
       <c r="AA59" s="23" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="J60" s="23" t="inlineStr">
         <is>
-          <t>-16.3</t>
+          <t>-15.7</t>
         </is>
       </c>
       <c r="K60" s="23" t="inlineStr">
         <is>
-          <t>+18.8</t>
+          <t>+18.2</t>
         </is>
       </c>
       <c r="L60" s="23" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z60" s="23" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="AA60" s="23" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="J61" s="23" t="inlineStr">
         <is>
-          <t>-27.6</t>
+          <t>-27.9</t>
         </is>
       </c>
       <c r="K61" s="23" t="inlineStr">
         <is>
-          <t>+6.1</t>
+          <t>+6.4</t>
         </is>
       </c>
       <c r="L61" s="23" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="Z61" s="23" t="inlineStr">
         <is>
-          <t>+8.1</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="AA61" s="23" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="J62" s="23" t="inlineStr">
         <is>
-          <t>-19.9</t>
+          <t>-20.5</t>
         </is>
       </c>
       <c r="K62" s="23" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="L62" s="23" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="Z62" s="23" t="inlineStr">
         <is>
-          <t>+0.7</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AA62" s="23" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="J63" s="23" t="inlineStr">
         <is>
-          <t>-22.1</t>
+          <t>-21.8</t>
         </is>
       </c>
       <c r="K63" s="23" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="L63" s="23" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="Z63" s="23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="AA63" s="23" t="inlineStr">
@@ -10624,6 +10624,986 @@
       <c r="AB63" s="23" t="inlineStr">
         <is>
           <t>-99.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t>Northern Illinois @ Arizona</t>
+        </is>
+      </c>
+      <c r="C64" s="23" t="inlineStr">
+        <is>
+          <t>17-42</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="inlineStr">
+        <is>
+          <t>-34.5</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
+        <is>
+          <t>+25.0</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>-26.3</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr">
+        <is>
+          <t>-8.2</t>
+        </is>
+      </c>
+      <c r="H64" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I64" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J64" s="23" t="inlineStr">
+        <is>
+          <t>-20.9</t>
+        </is>
+      </c>
+      <c r="K64" s="23" t="inlineStr">
+        <is>
+          <t>-13.6</t>
+        </is>
+      </c>
+      <c r="L64" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M64" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N64" s="23" t="inlineStr">
+        <is>
+          <t>-30.9</t>
+        </is>
+      </c>
+      <c r="O64" s="23" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="P64" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q64" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R64" s="23" t="inlineStr">
+        <is>
+          <t>-19.0</t>
+        </is>
+      </c>
+      <c r="S64" s="23" t="inlineStr">
+        <is>
+          <t>-15.5</t>
+        </is>
+      </c>
+      <c r="T64" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="U64" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V64" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Y64" s="23" t="inlineStr">
+        <is>
+          <t>-6.2</t>
+        </is>
+      </c>
+      <c r="Z64" s="23" t="inlineStr">
+        <is>
+          <t>-19.0</t>
+        </is>
+      </c>
+      <c r="AA64" s="23" t="inlineStr">
+        <is>
+          <t>+117.1</t>
+        </is>
+      </c>
+      <c r="AB64" s="23" t="inlineStr">
+        <is>
+          <t>-114.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>Wyoming @ Central Michigan</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>10-24</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
+        <is>
+          <t>+1.8</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>+14.0</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>+11.3</t>
+        </is>
+      </c>
+      <c r="H65" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I65" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
+        <is>
+          <t>-8.6</t>
+        </is>
+      </c>
+      <c r="K65" s="23" t="inlineStr">
+        <is>
+          <t>+10.4</t>
+        </is>
+      </c>
+      <c r="L65" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M65" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N65" s="23" t="inlineStr">
+        <is>
+          <t>-9.3</t>
+        </is>
+      </c>
+      <c r="O65" s="23" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
+      <c r="P65" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q65" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R65" s="23" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="S65" s="23" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="T65" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="U65" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V65" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" s="25" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="Y65" s="23" t="inlineStr">
+        <is>
+          <t>+5.1</t>
+        </is>
+      </c>
+      <c r="Z65" s="23" t="inlineStr">
+        <is>
+          <t>-8.7</t>
+        </is>
+      </c>
+      <c r="AA65" s="23" t="inlineStr">
+        <is>
+          <t>+128.1</t>
+        </is>
+      </c>
+      <c r="AB65" s="23" t="inlineStr">
+        <is>
+          <t>-110.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>UTEP @ Michigan</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>17-52</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
+        <is>
+          <t>-34.5</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>+35.0</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I66" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J66" s="23" t="inlineStr">
+        <is>
+          <t>-32.4</t>
+        </is>
+      </c>
+      <c r="K66" s="23" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
+      <c r="L66" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M66" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="N66" s="23" t="inlineStr">
+        <is>
+          <t>-29.7</t>
+        </is>
+      </c>
+      <c r="O66" s="23" t="inlineStr">
+        <is>
+          <t>-4.8</t>
+        </is>
+      </c>
+      <c r="P66" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q66" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R66" s="23" t="inlineStr">
+        <is>
+          <t>-11.8</t>
+        </is>
+      </c>
+      <c r="S66" s="23" t="inlineStr">
+        <is>
+          <t>-22.7</t>
+        </is>
+      </c>
+      <c r="T66" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="U66" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="V66" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W66" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X66" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="Y66" s="23" t="inlineStr">
+        <is>
+          <t>+5.6</t>
+        </is>
+      </c>
+      <c r="Z66" s="23" t="inlineStr">
+        <is>
+          <t>-10.8</t>
+        </is>
+      </c>
+      <c r="AA66" s="23" t="inlineStr">
+        <is>
+          <t>+123.3</t>
+        </is>
+      </c>
+      <c r="AB66" s="23" t="inlineStr">
+        <is>
+          <t>-133.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>Nevada @ Middle Tennessee</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>20-27</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>+3.8</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>+7.3</t>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I67" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
+      <c r="K67" s="23" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="L67" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M67" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N67" s="23" t="inlineStr">
+        <is>
+          <t>+2.9</t>
+        </is>
+      </c>
+      <c r="O67" s="23" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
+      <c r="P67" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q67" s="25" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="R67" s="23" t="inlineStr">
+        <is>
+          <t>-4.9</t>
+        </is>
+      </c>
+      <c r="S67" s="23" t="inlineStr">
+        <is>
+          <t>+8.7</t>
+        </is>
+      </c>
+      <c r="T67" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="U67" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V67" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W67" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X67" s="25" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="Y67" s="23" t="inlineStr">
+        <is>
+          <t>+12.9</t>
+        </is>
+      </c>
+      <c r="Z67" s="23" t="inlineStr">
+        <is>
+          <t>-8.3</t>
+        </is>
+      </c>
+      <c r="AA67" s="23" t="inlineStr">
+        <is>
+          <t>+124.2</t>
+        </is>
+      </c>
+      <c r="AB67" s="23" t="inlineStr">
+        <is>
+          <t>-124.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t>New Mexico @ Oklahoma</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>6-14</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>-21.2</t>
+        </is>
+      </c>
+      <c r="E68" s="23" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>-14.1</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr">
+        <is>
+          <t>-7.2</t>
+        </is>
+      </c>
+      <c r="H68" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I68" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J68" s="23" t="inlineStr">
+        <is>
+          <t>-14.9</t>
+        </is>
+      </c>
+      <c r="K68" s="23" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
+      <c r="L68" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M68" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N68" s="23" t="inlineStr">
+        <is>
+          <t>-10.8</t>
+        </is>
+      </c>
+      <c r="O68" s="23" t="inlineStr">
+        <is>
+          <t>-10.4</t>
+        </is>
+      </c>
+      <c r="P68" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q68" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R68" s="23" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
+      <c r="S68" s="23" t="inlineStr">
+        <is>
+          <t>-21.6</t>
+        </is>
+      </c>
+      <c r="T68" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="U68" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V68" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W68" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Y68" s="23" t="inlineStr">
+        <is>
+          <t>+5.7</t>
+        </is>
+      </c>
+      <c r="Z68" s="23" t="inlineStr">
+        <is>
+          <t>-14.6</t>
+        </is>
+      </c>
+      <c r="AA68" s="23" t="inlineStr">
+        <is>
+          <t>+113.8</t>
+        </is>
+      </c>
+      <c r="AB68" s="23" t="inlineStr">
+        <is>
+          <t>-146.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>North Dakota State @ Sacramento State</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>31-10</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>+25.5</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="inlineStr">
+        <is>
+          <t>-21.0</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>+13.0</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t>+12.5</t>
+        </is>
+      </c>
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I69" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
+        <is>
+          <t>+17.7</t>
+        </is>
+      </c>
+      <c r="K69" s="23" t="inlineStr">
+        <is>
+          <t>+7.8</t>
+        </is>
+      </c>
+      <c r="L69" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M69" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N69" s="23" t="inlineStr">
+        <is>
+          <t>+35.9</t>
+        </is>
+      </c>
+      <c r="O69" s="23" t="inlineStr">
+        <is>
+          <t>-10.4</t>
+        </is>
+      </c>
+      <c r="P69" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="Q69" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R69" s="23" t="inlineStr">
+        <is>
+          <t>+12.2</t>
+        </is>
+      </c>
+      <c r="S69" s="23" t="inlineStr">
+        <is>
+          <t>+13.3</t>
+        </is>
+      </c>
+      <c r="T69" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="U69" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V69" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W69" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X69" s="25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Y69" s="23" t="inlineStr">
+        <is>
+          <t>+18.2</t>
+        </is>
+      </c>
+      <c r="Z69" s="23" t="inlineStr">
+        <is>
+          <t>-6.8</t>
+        </is>
+      </c>
+      <c r="AA69" s="23" t="inlineStr">
+        <is>
+          <t>+103.3</t>
+        </is>
+      </c>
+      <c r="AB69" s="23" t="inlineStr">
+        <is>
+          <t>-133.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>Fresno State @ San José State</t>
+        </is>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>26-10</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="inlineStr">
+        <is>
+          <t>-16.0</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
+      <c r="H70" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>Loss (no real edge)</t>
+        </is>
+      </c>
+      <c r="J70" s="23" t="inlineStr">
+        <is>
+          <t>+11.4</t>
+        </is>
+      </c>
+      <c r="K70" s="23" t="inlineStr">
+        <is>
+          <t>-7.4</t>
+        </is>
+      </c>
+      <c r="L70" s="23" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M70" s="25" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N70" s="23" t="inlineStr">
+        <is>
+          <t>+1.2</t>
+        </is>
+      </c>
+      <c r="O70" s="23" t="inlineStr">
+        <is>
+          <t>+2.8</t>
+        </is>
+      </c>
+      <c r="P70" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q70" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="R70" s="23" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="S70" s="23" t="inlineStr">
+        <is>
+          <t>+6.2</t>
+        </is>
+      </c>
+      <c r="T70" s="23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="U70" s="24" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="V70" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" s="25" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="Y70" s="23" t="inlineStr">
+        <is>
+          <t>+19.1</t>
+        </is>
+      </c>
+      <c r="Z70" s="23" t="inlineStr">
+        <is>
+          <t>-14.1</t>
+        </is>
+      </c>
+      <c r="AA70" s="23" t="inlineStr">
+        <is>
+          <t>+106.1</t>
+        </is>
+      </c>
+      <c r="AB70" s="23" t="inlineStr">
+        <is>
+          <t>-126.9</t>
         </is>
       </c>
     </row>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="2" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="3" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Team Profiles" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Model Comparison" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Power Ratings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MW Team ATS" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -21,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="22">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -132,6 +135,45 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
@@ -158,13 +200,8 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -200,7 +237,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -255,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -292,6 +344,20 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17146,10 +17212,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W139"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="5"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -17157,126 +17223,126 @@
     <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="15.5" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="V1" s="23" t="inlineStr">
+      <c r="V1" s="30" t="inlineStr">
         <is>
           <t>Matchup Spread Calculator</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Indiana</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n">
+      <c r="B2" s="31" t="n">
         <v>97</v>
       </c>
-      <c r="C2" s="24" t="n">
+      <c r="C2" s="31" t="n">
         <v>99.7</v>
       </c>
-      <c r="D2" s="24" t="n">
+      <c r="D2" s="31" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="E2" s="24" t="n">
+      <c r="E2" s="31" t="n">
         <v>96.7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Ohio State</t>
         </is>
       </c>
-      <c r="B3" s="24" t="n">
+      <c r="B3" s="31" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="C3" s="24" t="n">
+      <c r="C3" s="31" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="D3" s="24" t="n">
+      <c r="D3" s="31" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="E3" s="24" t="n">
+      <c r="E3" s="31" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="V3" s="24" t="inlineStr">
+      <c r="V3" s="31" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="W3" s="25" t="inlineStr"/>
+      <c r="W3" s="25" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="31" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="31" t="n">
         <v>94.3</v>
       </c>
-      <c r="D4" s="24" t="n">
+      <c r="D4" s="31" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="E4" s="24" t="n">
+      <c r="E4" s="31" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="V4" s="24" t="inlineStr">
+      <c r="V4" s="31" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="W4" s="25" t="inlineStr"/>
+      <c r="W4" s="25" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Oregon</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="31" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="31" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="31" t="n">
         <v>89.7</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="31" t="n">
         <v>89.7</v>
       </c>
-      <c r="V5" s="24" t="inlineStr">
+      <c r="V5" s="31" t="inlineStr">
         <is>
           <t>Neutral Site? (Y/N)</t>
         </is>
@@ -17288,2582 +17354,4073 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Notre Dame</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="31" t="n">
         <v>88.5</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="31" t="n">
         <v>89.5</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="31" t="n">
         <v>89</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="31" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="31" t="n">
         <v>83.5</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="31" t="n">
         <v>85.8</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="31" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="31" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="V7" s="24" t="inlineStr">
+      <c r="V7" s="31" t="inlineStr">
         <is>
           <t>HFA (model constant)</t>
         </is>
       </c>
-      <c r="W7" s="24" t="n">
+      <c r="W7" s="31" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Texas Tech</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="31" t="n">
         <v>87.3</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="31" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="31" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="31" t="n">
         <v>85.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Texas</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="31" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="31" t="n">
         <v>86</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="31" t="n">
         <v>86.5</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="31" t="n">
         <v>85.2</v>
       </c>
-      <c r="V9" s="26" t="inlineStr">
+      <c r="V9" s="32" t="inlineStr">
         <is>
           <t>Predicted Spread (Home)</t>
         </is>
       </c>
-      <c r="W9" s="26">
+      <c r="W9" s="32">
         <f>IF(OR(W3="",W4=""),"",INDEX($E$2:$E$139,MATCH(W4,$A$2:$A$139,0))-INDEX($E$2:$E$139,MATCH(W3,$A$2:$A$139,0))-IF(UPPER(W5)="Y",0,W7))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Iowa</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="31" t="n">
         <v>81.2</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="31" t="n">
         <v>80.2</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="31" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="31" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="V10" s="27" t="inlineStr">
+      <c r="V10" s="33" t="inlineStr">
         <is>
           <t>(negative = home team favored, e.g. "Home -6.5")</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Ole Miss</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="31" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="31" t="n">
         <v>84</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="31" t="n">
         <v>84.5</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="31" t="n">
         <v>84.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Utah</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="31" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="31" t="n">
         <v>83.5</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="31" t="n">
         <v>84.2</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="31" t="n">
         <v>84.2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Alabama</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="31" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="31" t="n">
         <v>82.3</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="31" t="n">
         <v>82.2</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="31" t="n">
         <v>82.2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Texas A&amp;M</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="31" t="n">
         <v>82.8</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="31" t="n">
         <v>84.3</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="31" t="n">
         <v>81.7</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="31" t="n">
         <v>81.7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Penn State</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="31" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="31" t="n">
         <v>80.3</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="31" t="n">
         <v>81.2</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="31" t="n">
         <v>81.2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>South Carolina</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="31" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="31" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Tennessee</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="31" t="n">
         <v>76.8</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="31" t="n">
         <v>77.8</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="31" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="31" t="n">
         <v>80.2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="31" t="n">
         <v>79.2</v>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="31" t="n">
         <v>83.2</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="31" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="31" t="n">
         <v>80.09999999999999</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Washington</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="31" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="31" t="n">
         <v>78.3</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="31" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Oklahoma</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="31" t="n">
         <v>81.2</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="31" t="n">
         <v>79.5</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="31" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>LSU</t>
         </is>
       </c>
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="31" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C21" s="24" t="n">
+      <c r="C21" s="31" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="31" t="n">
         <v>79.7</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="31" t="n">
         <v>79.7</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="31" t="n">
         <v>75.3</v>
       </c>
-      <c r="C22" s="24" t="n">
+      <c r="C22" s="31" t="n">
         <v>74.7</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="31" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="E22" s="24" t="n">
+      <c r="E22" s="31" t="n">
         <v>79.09999999999999</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Vanderbilt</t>
         </is>
       </c>
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="31" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="31" t="n">
         <v>78.8</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="31" t="n">
         <v>78.8</v>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="31" t="n">
         <v>78.8</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Florida</t>
         </is>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="31" t="n">
         <v>75.2</v>
       </c>
-      <c r="C24" s="24" t="n">
+      <c r="C24" s="31" t="n">
         <v>79</v>
       </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="31" t="n">
         <v>78.7</v>
       </c>
-      <c r="E24" s="24" t="n">
+      <c r="E24" s="31" t="n">
         <v>78.7</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>BYU</t>
         </is>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="31" t="n">
         <v>78.3</v>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="31" t="n">
         <v>79</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="31" t="n">
         <v>78.5</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="31" t="n">
         <v>78.5</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>Louisville</t>
         </is>
       </c>
-      <c r="B26" s="24" t="n">
+      <c r="B26" s="31" t="n">
         <v>74.7</v>
       </c>
-      <c r="C26" s="24" t="n">
+      <c r="C26" s="31" t="n">
         <v>78.8</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D26" s="31" t="n">
         <v>79.8</v>
       </c>
-      <c r="E26" s="24" t="n">
+      <c r="E26" s="31" t="n">
         <v>77.90000000000001</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>SMU</t>
         </is>
       </c>
-      <c r="B27" s="24" t="n">
+      <c r="B27" s="31" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="C27" s="24" t="n">
+      <c r="C27" s="31" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="31" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="E27" s="31" t="n">
         <v>77.90000000000001</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>USC</t>
         </is>
       </c>
-      <c r="B28" s="24" t="n">
+      <c r="B28" s="31" t="n">
         <v>78</v>
       </c>
-      <c r="C28" s="24" t="n">
+      <c r="C28" s="31" t="n">
         <v>77.5</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="31" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="E28" s="24" t="n">
+      <c r="E28" s="31" t="n">
         <v>77.40000000000001</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>James Madison</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="31" t="n">
         <v>67.8</v>
       </c>
-      <c r="C29" s="24" t="n">
+      <c r="C29" s="31" t="n">
         <v>76.8</v>
       </c>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="31" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="31" t="n">
         <v>77.09999999999999</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>Nebraska</t>
         </is>
       </c>
-      <c r="B30" s="24" t="n">
+      <c r="B30" s="31" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="C30" s="24" t="n">
+      <c r="C30" s="31" t="n">
         <v>74.7</v>
       </c>
-      <c r="D30" s="24" t="n">
+      <c r="D30" s="31" t="n">
         <v>76.3</v>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E30" s="31" t="n">
         <v>76.3</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B31" s="24" t="n">
+      <c r="B31" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="C31" s="24" t="n">
+      <c r="C31" s="31" t="n">
         <v>74.8</v>
       </c>
-      <c r="D31" s="24" t="n">
+      <c r="D31" s="31" t="n">
         <v>76.2</v>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="31" t="n">
         <v>76.2</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>North Dakota State</t>
         </is>
       </c>
-      <c r="B32" s="24" t="n">
+      <c r="B32" s="31" t="n">
         <v>79.5</v>
       </c>
-      <c r="C32" s="24" t="n">
+      <c r="C32" s="31" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="D32" s="24" t="n">
+      <c r="D32" s="31" t="n">
         <v>76</v>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E32" s="31" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="B33" s="24" t="n">
+      <c r="B33" s="31" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="C33" s="24" t="n">
+      <c r="C33" s="31" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="D33" s="24" t="n">
+      <c r="D33" s="31" t="n">
         <v>75.8</v>
       </c>
-      <c r="E33" s="24" t="n">
+      <c r="E33" s="31" t="n">
         <v>75.8</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>TCU</t>
         </is>
       </c>
-      <c r="B34" s="24" t="n">
+      <c r="B34" s="31" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="C34" s="24" t="n">
+      <c r="C34" s="31" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="D34" s="24" t="n">
+      <c r="D34" s="31" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="E34" s="24" t="n">
+      <c r="E34" s="31" t="n">
         <v>75.09999999999999</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>Wake Forest</t>
         </is>
       </c>
-      <c r="B35" s="24" t="n">
+      <c r="B35" s="31" t="n">
         <v>71</v>
       </c>
-      <c r="C35" s="24" t="n">
+      <c r="C35" s="31" t="n">
         <v>69.8</v>
       </c>
-      <c r="D35" s="24" t="n">
+      <c r="D35" s="31" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E35" s="24" t="n">
+      <c r="E35" s="31" t="n">
         <v>74.59999999999999</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>NC State</t>
         </is>
       </c>
-      <c r="B36" s="24" t="n">
+      <c r="B36" s="31" t="n">
         <v>67.2</v>
       </c>
-      <c r="C36" s="24" t="n">
+      <c r="C36" s="31" t="n">
         <v>74.2</v>
       </c>
-      <c r="D36" s="24" t="n">
+      <c r="D36" s="31" t="n">
         <v>74.3</v>
       </c>
-      <c r="E36" s="24" t="n">
+      <c r="E36" s="31" t="n">
         <v>74.3</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>Missouri</t>
         </is>
       </c>
-      <c r="B37" s="24" t="n">
+      <c r="B37" s="31" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="C37" s="24" t="n">
+      <c r="C37" s="31" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="D37" s="24" t="n">
+      <c r="D37" s="31" t="n">
         <v>74</v>
       </c>
-      <c r="E37" s="24" t="n">
+      <c r="E37" s="31" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>Michigan</t>
         </is>
       </c>
-      <c r="B38" s="24" t="n">
+      <c r="B38" s="31" t="n">
         <v>71.2</v>
       </c>
-      <c r="C38" s="24" t="n">
+      <c r="C38" s="31" t="n">
         <v>72.90000000000001</v>
       </c>
-      <c r="D38" s="24" t="n">
+      <c r="D38" s="31" t="n">
         <v>73.90000000000001</v>
       </c>
-      <c r="E38" s="24" t="n">
+      <c r="E38" s="31" t="n">
         <v>73.90000000000001</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Illinois</t>
         </is>
       </c>
-      <c r="B39" s="24" t="n">
+      <c r="B39" s="31" t="n">
         <v>71</v>
       </c>
-      <c r="C39" s="24" t="n">
+      <c r="C39" s="31" t="n">
         <v>71.2</v>
       </c>
-      <c r="D39" s="24" t="n">
+      <c r="D39" s="31" t="n">
         <v>74.3</v>
       </c>
-      <c r="E39" s="24" t="n">
+      <c r="E39" s="31" t="n">
         <v>73.8</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t>Northwestern</t>
         </is>
       </c>
-      <c r="B40" s="24" t="n">
+      <c r="B40" s="31" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="C40" s="24" t="n">
+      <c r="C40" s="31" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="D40" s="24" t="n">
+      <c r="D40" s="31" t="n">
         <v>71.5</v>
       </c>
-      <c r="E40" s="24" t="n">
+      <c r="E40" s="31" t="n">
         <v>73.59999999999999</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>Kansas State</t>
         </is>
       </c>
-      <c r="B41" s="24" t="n">
+      <c r="B41" s="31" t="n">
         <v>70.7</v>
       </c>
-      <c r="C41" s="24" t="n">
+      <c r="C41" s="31" t="n">
         <v>73.2</v>
       </c>
-      <c r="D41" s="24" t="n">
+      <c r="D41" s="31" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="E41" s="24" t="n">
+      <c r="E41" s="31" t="n">
         <v>73.40000000000001</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>Cincinnati</t>
         </is>
       </c>
-      <c r="B42" s="24" t="n">
+      <c r="B42" s="31" t="n">
         <v>69.3</v>
       </c>
-      <c r="C42" s="24" t="n">
+      <c r="C42" s="31" t="n">
         <v>74</v>
       </c>
-      <c r="D42" s="24" t="n">
+      <c r="D42" s="31" t="n">
         <v>73</v>
       </c>
-      <c r="E42" s="24" t="n">
+      <c r="E42" s="31" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
       </c>
-      <c r="B43" s="24" t="n">
+      <c r="B43" s="31" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="C43" s="24" t="n">
+      <c r="C43" s="31" t="n">
         <v>72.7</v>
       </c>
-      <c r="D43" s="24" t="n">
+      <c r="D43" s="31" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E43" s="24" t="n">
+      <c r="E43" s="31" t="n">
         <v>72.59999999999999</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t>Boise State</t>
         </is>
       </c>
-      <c r="B44" s="24" t="n">
+      <c r="B44" s="31" t="n">
         <v>70.2</v>
       </c>
-      <c r="C44" s="24" t="n">
+      <c r="C44" s="31" t="n">
         <v>71.8</v>
       </c>
-      <c r="D44" s="24" t="n">
+      <c r="D44" s="31" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="E44" s="24" t="n">
+      <c r="E44" s="31" t="n">
         <v>72.40000000000001</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t>New Mexico</t>
         </is>
       </c>
-      <c r="B45" s="24" t="n">
+      <c r="B45" s="31" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="C45" s="24" t="n">
+      <c r="C45" s="31" t="n">
         <v>72.7</v>
       </c>
-      <c r="D45" s="24" t="n">
+      <c r="D45" s="31" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="E45" s="24" t="n">
+      <c r="E45" s="31" t="n">
         <v>72.09999999999999</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="31" t="inlineStr">
         <is>
           <t>South Florida</t>
         </is>
       </c>
-      <c r="B46" s="24" t="n">
+      <c r="B46" s="31" t="n">
         <v>68.2</v>
       </c>
-      <c r="C46" s="24" t="n">
+      <c r="C46" s="31" t="n">
         <v>68.3</v>
       </c>
-      <c r="D46" s="24" t="n">
+      <c r="D46" s="31" t="n">
         <v>72</v>
       </c>
-      <c r="E46" s="24" t="n">
+      <c r="E46" s="31" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>Baylor</t>
         </is>
       </c>
-      <c r="B47" s="24" t="n">
+      <c r="B47" s="31" t="n">
         <v>66.8</v>
       </c>
-      <c r="C47" s="24" t="n">
+      <c r="C47" s="31" t="n">
         <v>71.2</v>
       </c>
-      <c r="D47" s="24" t="n">
+      <c r="D47" s="31" t="n">
         <v>71.5</v>
       </c>
-      <c r="E47" s="24" t="n">
+      <c r="E47" s="31" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t>Iowa State</t>
         </is>
       </c>
-      <c r="B48" s="24" t="n">
+      <c r="B48" s="31" t="n">
         <v>68.3</v>
       </c>
-      <c r="C48" s="24" t="n">
+      <c r="C48" s="31" t="n">
         <v>69.3</v>
       </c>
-      <c r="D48" s="24" t="n">
+      <c r="D48" s="31" t="n">
         <v>71.8</v>
       </c>
-      <c r="E48" s="24" t="n">
+      <c r="E48" s="31" t="n">
         <v>71.8</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>Auburn</t>
         </is>
       </c>
-      <c r="B49" s="24" t="n">
+      <c r="B49" s="31" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="C49" s="24" t="n">
+      <c r="C49" s="31" t="n">
         <v>71.2</v>
       </c>
-      <c r="D49" s="24" t="n">
+      <c r="D49" s="31" t="n">
         <v>71.5</v>
       </c>
-      <c r="E49" s="24" t="n">
+      <c r="E49" s="31" t="n">
         <v>71.5</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="31" t="inlineStr">
         <is>
           <t>Mississippi State</t>
         </is>
       </c>
-      <c r="B50" s="24" t="n">
+      <c r="B50" s="31" t="n">
         <v>68.8</v>
       </c>
-      <c r="C50" s="24" t="n">
+      <c r="C50" s="31" t="n">
         <v>71.3</v>
       </c>
-      <c r="D50" s="24" t="n">
+      <c r="D50" s="31" t="n">
         <v>71.3</v>
       </c>
-      <c r="E50" s="24" t="n">
+      <c r="E50" s="31" t="n">
         <v>71.3</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Georgia Tech</t>
         </is>
       </c>
-      <c r="B51" s="24" t="n">
+      <c r="B51" s="31" t="n">
         <v>67.7</v>
       </c>
-      <c r="C51" s="24" t="n">
+      <c r="C51" s="31" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="D51" s="24" t="n">
+      <c r="D51" s="31" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E51" s="31" t="n">
         <v>69.59999999999999</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Minnesota</t>
         </is>
       </c>
-      <c r="B52" s="24" t="n">
+      <c r="B52" s="31" t="n">
         <v>69.8</v>
       </c>
-      <c r="C52" s="24" t="n">
+      <c r="C52" s="31" t="n">
         <v>67.2</v>
       </c>
-      <c r="D52" s="24" t="n">
+      <c r="D52" s="31" t="n">
         <v>69.5</v>
       </c>
-      <c r="E52" s="24" t="n">
+      <c r="E52" s="31" t="n">
         <v>69.5</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>Clemson</t>
         </is>
       </c>
-      <c r="B53" s="24" t="n">
+      <c r="B53" s="31" t="n">
         <v>67.8</v>
       </c>
-      <c r="C53" s="24" t="n">
+      <c r="C53" s="31" t="n">
         <v>68.2</v>
       </c>
-      <c r="D53" s="24" t="n">
+      <c r="D53" s="31" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="E53" s="24" t="n">
+      <c r="E53" s="31" t="n">
         <v>69.3</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="A54" s="31" t="inlineStr">
         <is>
           <t>Western Michigan</t>
         </is>
       </c>
-      <c r="B54" s="24" t="n">
+      <c r="B54" s="31" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="C54" s="24" t="n">
+      <c r="C54" s="31" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="D54" s="24" t="n">
+      <c r="D54" s="31" t="n">
         <v>69.3</v>
       </c>
-      <c r="E54" s="24" t="n">
+      <c r="E54" s="31" t="n">
         <v>69.3</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="B55" s="24" t="n">
+      <c r="B55" s="31" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="C55" s="24" t="n">
+      <c r="C55" s="31" t="n">
         <v>67.2</v>
       </c>
-      <c r="D55" s="24" t="n">
+      <c r="D55" s="31" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="E55" s="24" t="n">
+      <c r="E55" s="31" t="n">
         <v>68.90000000000001</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="31" t="inlineStr">
         <is>
           <t>Kentucky</t>
         </is>
       </c>
-      <c r="B56" s="24" t="n">
+      <c r="B56" s="31" t="n">
         <v>66.5</v>
       </c>
-      <c r="C56" s="24" t="n">
+      <c r="C56" s="31" t="n">
         <v>65.2</v>
       </c>
-      <c r="D56" s="24" t="n">
+      <c r="D56" s="31" t="n">
         <v>67.7</v>
       </c>
-      <c r="E56" s="24" t="n">
+      <c r="E56" s="31" t="n">
         <v>68.7</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="31" t="inlineStr">
         <is>
           <t>Toledo</t>
         </is>
       </c>
-      <c r="B57" s="24" t="n">
+      <c r="B57" s="31" t="n">
         <v>62.1</v>
       </c>
-      <c r="C57" s="24" t="n">
+      <c r="C57" s="31" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="D57" s="24" t="n">
+      <c r="D57" s="31" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="E57" s="24" t="n">
+      <c r="E57" s="31" t="n">
         <v>68.59999999999999</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="31" t="inlineStr">
         <is>
           <t>Old Dominion</t>
         </is>
       </c>
-      <c r="B58" s="24" t="n">
+      <c r="B58" s="31" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="C58" s="24" t="n">
+      <c r="C58" s="31" t="n">
         <v>69.5</v>
       </c>
-      <c r="D58" s="24" t="n">
+      <c r="D58" s="31" t="n">
         <v>68.5</v>
       </c>
-      <c r="E58" s="24" t="n">
+      <c r="E58" s="31" t="n">
         <v>68.5</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="31" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="B59" s="24" t="n">
+      <c r="B59" s="31" t="n">
         <v>68.2</v>
       </c>
-      <c r="C59" s="24" t="n">
+      <c r="C59" s="31" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="D59" s="24" t="n">
+      <c r="D59" s="31" t="n">
         <v>68.2</v>
       </c>
-      <c r="E59" s="24" t="n">
+      <c r="E59" s="31" t="n">
         <v>68.2</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="31" t="inlineStr">
         <is>
           <t>Navy</t>
         </is>
       </c>
-      <c r="B60" s="24" t="n">
+      <c r="B60" s="31" t="n">
         <v>72.2</v>
       </c>
-      <c r="C60" s="24" t="n">
+      <c r="C60" s="31" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="D60" s="24" t="n">
+      <c r="D60" s="31" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="E60" s="24" t="n">
+      <c r="E60" s="31" t="n">
         <v>67.8</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>Washington State</t>
         </is>
       </c>
-      <c r="B61" s="24" t="n">
+      <c r="B61" s="31" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="C61" s="24" t="n">
+      <c r="C61" s="31" t="n">
         <v>63.7</v>
       </c>
-      <c r="D61" s="24" t="n">
+      <c r="D61" s="31" t="n">
         <v>67.8</v>
       </c>
-      <c r="E61" s="24" t="n">
+      <c r="E61" s="31" t="n">
         <v>67.8</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>Arizona State</t>
         </is>
       </c>
-      <c r="B62" s="24" t="n">
+      <c r="B62" s="31" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="C62" s="24" t="n">
+      <c r="C62" s="31" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="D62" s="24" t="n">
+      <c r="D62" s="31" t="n">
         <v>67.7</v>
       </c>
-      <c r="E62" s="24" t="n">
+      <c r="E62" s="31" t="n">
         <v>67.7</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>Virginia Tech</t>
         </is>
       </c>
-      <c r="B63" s="24" t="n">
+      <c r="B63" s="31" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="C63" s="24" t="n">
+      <c r="C63" s="31" t="n">
         <v>67.5</v>
       </c>
-      <c r="D63" s="24" t="n">
+      <c r="D63" s="31" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="E63" s="24" t="n">
+      <c r="E63" s="31" t="n">
         <v>67.5</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t>Michigan State</t>
         </is>
       </c>
-      <c r="B64" s="24" t="n">
+      <c r="B64" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="C64" s="24" t="n">
+      <c r="C64" s="31" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="D64" s="24" t="n">
+      <c r="D64" s="31" t="n">
         <v>67.5</v>
       </c>
-      <c r="E64" s="24" t="n">
+      <c r="E64" s="31" t="n">
         <v>67.5</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="31" t="inlineStr">
         <is>
           <t>Florida State</t>
         </is>
       </c>
-      <c r="B65" s="24" t="n">
+      <c r="B65" s="31" t="n">
         <v>67.2</v>
       </c>
-      <c r="C65" s="24" t="n">
+      <c r="C65" s="31" t="n">
         <v>67.2</v>
       </c>
-      <c r="D65" s="24" t="n">
+      <c r="D65" s="31" t="n">
         <v>67.3</v>
       </c>
-      <c r="E65" s="24" t="n">
+      <c r="E65" s="31" t="n">
         <v>67.3</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="31" t="inlineStr">
         <is>
           <t>Rutgers</t>
         </is>
       </c>
-      <c r="B66" s="24" t="n">
+      <c r="B66" s="31" t="n">
         <v>61.1</v>
       </c>
-      <c r="C66" s="24" t="n">
+      <c r="C66" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="D66" s="24" t="n">
+      <c r="D66" s="31" t="n">
         <v>62.1</v>
       </c>
-      <c r="E66" s="24" t="n">
+      <c r="E66" s="31" t="n">
         <v>67.09999999999999</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="31" t="inlineStr">
         <is>
           <t>UCLA</t>
         </is>
       </c>
-      <c r="B67" s="24" t="n">
+      <c r="B67" s="31" t="n">
         <v>63.8</v>
       </c>
-      <c r="C67" s="24" t="n">
+      <c r="C67" s="31" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="D67" s="24" t="n">
+      <c r="D67" s="31" t="n">
         <v>66.7</v>
       </c>
-      <c r="E67" s="24" t="n">
+      <c r="E67" s="31" t="n">
         <v>66.7</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="31" t="inlineStr">
         <is>
           <t>West Virginia</t>
         </is>
       </c>
-      <c r="B68" s="24" t="n">
+      <c r="B68" s="31" t="n">
         <v>58.2</v>
       </c>
-      <c r="C68" s="24" t="n">
+      <c r="C68" s="31" t="n">
         <v>63.2</v>
       </c>
-      <c r="D68" s="24" t="n">
+      <c r="D68" s="31" t="n">
         <v>66.3</v>
       </c>
-      <c r="E68" s="24" t="n">
+      <c r="E68" s="31" t="n">
         <v>66.3</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="24" t="inlineStr">
+      <c r="A69" s="31" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="B69" s="24" t="n">
+      <c r="B69" s="31" t="n">
         <v>65.7</v>
       </c>
-      <c r="C69" s="24" t="n">
+      <c r="C69" s="31" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="D69" s="24" t="n">
+      <c r="D69" s="31" t="n">
         <v>65.7</v>
       </c>
-      <c r="E69" s="24" t="n">
+      <c r="E69" s="31" t="n">
         <v>65.7</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="A70" s="31" t="inlineStr">
         <is>
           <t>UTSA</t>
         </is>
       </c>
-      <c r="B70" s="24" t="n">
+      <c r="B70" s="31" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="C70" s="24" t="n">
+      <c r="C70" s="31" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="D70" s="24" t="n">
+      <c r="D70" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="E70" s="24" t="n">
+      <c r="E70" s="31" t="n">
         <v>65.59999999999999</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="inlineStr">
+      <c r="A71" s="31" t="inlineStr">
         <is>
           <t>Maryland</t>
         </is>
       </c>
-      <c r="B71" s="24" t="n">
+      <c r="B71" s="31" t="n">
         <v>62.3</v>
       </c>
-      <c r="C71" s="24" t="n">
+      <c r="C71" s="31" t="n">
         <v>65.2</v>
       </c>
-      <c r="D71" s="24" t="n">
+      <c r="D71" s="31" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="E71" s="24" t="n">
+      <c r="E71" s="31" t="n">
         <v>65.09999999999999</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="inlineStr">
+      <c r="A72" s="31" t="inlineStr">
         <is>
           <t>North Texas</t>
         </is>
       </c>
-      <c r="B72" s="24" t="n">
+      <c r="B72" s="31" t="n">
         <v>63.9</v>
       </c>
-      <c r="C72" s="24" t="n">
+      <c r="C72" s="31" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="D72" s="24" t="n">
+      <c r="D72" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="E72" s="24" t="n">
+      <c r="E72" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24" t="inlineStr">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>North Carolina</t>
         </is>
       </c>
-      <c r="B73" s="24" t="n">
+      <c r="B73" s="31" t="n">
         <v>61.3</v>
       </c>
-      <c r="C73" s="24" t="n">
+      <c r="C73" s="31" t="n">
         <v>64.7</v>
       </c>
-      <c r="D73" s="24" t="n">
+      <c r="D73" s="31" t="n">
         <v>64.5</v>
       </c>
-      <c r="E73" s="24" t="n">
+      <c r="E73" s="31" t="n">
         <v>64.5</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24" t="inlineStr">
+      <c r="A74" s="31" t="inlineStr">
         <is>
           <t>Army</t>
         </is>
       </c>
-      <c r="B74" s="24" t="n">
+      <c r="B74" s="31" t="n">
         <v>64.5</v>
       </c>
-      <c r="C74" s="24" t="n">
+      <c r="C74" s="31" t="n">
         <v>64.5</v>
       </c>
-      <c r="D74" s="24" t="n">
+      <c r="D74" s="31" t="n">
         <v>64.5</v>
       </c>
-      <c r="E74" s="24" t="n">
+      <c r="E74" s="31" t="n">
         <v>64.3</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="24" t="inlineStr">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>Colorado</t>
         </is>
       </c>
-      <c r="B75" s="24" t="n">
+      <c r="B75" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="C75" s="24" t="n">
+      <c r="C75" s="31" t="n">
         <v>68</v>
       </c>
-      <c r="D75" s="24" t="n">
+      <c r="D75" s="31" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="E75" s="24" t="n">
+      <c r="E75" s="31" t="n">
         <v>64.2</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="inlineStr">
+      <c r="A76" s="31" t="inlineStr">
         <is>
           <t>Arkansas</t>
         </is>
       </c>
-      <c r="B76" s="24" t="n">
+      <c r="B76" s="31" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="C76" s="24" t="n">
+      <c r="C76" s="31" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="D76" s="24" t="n">
+      <c r="D76" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="E76" s="24" t="n">
+      <c r="E76" s="31" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="inlineStr">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>East Carolina</t>
         </is>
       </c>
-      <c r="B77" s="24" t="n">
+      <c r="B77" s="31" t="n">
         <v>64.8</v>
       </c>
-      <c r="C77" s="24" t="n">
+      <c r="C77" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="D77" s="24" t="n">
+      <c r="D77" s="31" t="n">
         <v>63.9</v>
       </c>
-      <c r="E77" s="24" t="n">
+      <c r="E77" s="31" t="n">
         <v>63.9</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="24" t="inlineStr">
+      <c r="A78" s="31" t="inlineStr">
         <is>
           <t>Texas State</t>
         </is>
       </c>
-      <c r="B78" s="24" t="n">
+      <c r="B78" s="31" t="n">
         <v>60.5</v>
       </c>
-      <c r="C78" s="24" t="n">
+      <c r="C78" s="31" t="n">
         <v>60.7</v>
       </c>
-      <c r="D78" s="24" t="n">
+      <c r="D78" s="31" t="n">
         <v>63.2</v>
       </c>
-      <c r="E78" s="24" t="n">
+      <c r="E78" s="31" t="n">
         <v>63.2</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="24" t="inlineStr">
+      <c r="A79" s="31" t="inlineStr">
         <is>
           <t>UCF</t>
         </is>
       </c>
-      <c r="B79" s="24" t="n">
+      <c r="B79" s="31" t="n">
         <v>62.3</v>
       </c>
-      <c r="C79" s="24" t="n">
+      <c r="C79" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="D79" s="24" t="n">
+      <c r="D79" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="E79" s="24" t="n">
+      <c r="E79" s="31" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="24" t="inlineStr">
+      <c r="A80" s="31" t="inlineStr">
         <is>
           <t>Tulane</t>
         </is>
       </c>
-      <c r="B80" s="24" t="n">
+      <c r="B80" s="31" t="n">
         <v>63.9</v>
       </c>
-      <c r="C80" s="24" t="n">
+      <c r="C80" s="31" t="n">
         <v>63.1</v>
       </c>
-      <c r="D80" s="24" t="n">
+      <c r="D80" s="31" t="n">
         <v>62.9</v>
       </c>
-      <c r="E80" s="24" t="n">
+      <c r="E80" s="31" t="n">
         <v>62.9</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="24" t="inlineStr">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="B81" s="24" t="n">
+      <c r="B81" s="31" t="n">
         <v>60.4</v>
       </c>
-      <c r="C81" s="24" t="n">
+      <c r="C81" s="31" t="n">
         <v>59.8</v>
       </c>
-      <c r="D81" s="24" t="n">
+      <c r="D81" s="31" t="n">
         <v>63.5</v>
       </c>
-      <c r="E81" s="24" t="n">
+      <c r="E81" s="31" t="n">
         <v>62.6</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="24" t="inlineStr">
+      <c r="A82" s="31" t="inlineStr">
         <is>
           <t>Liberty</t>
         </is>
       </c>
-      <c r="B82" s="24" t="n">
+      <c r="B82" s="31" t="n">
         <v>57.2</v>
       </c>
-      <c r="C82" s="24" t="n">
+      <c r="C82" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="D82" s="24" t="n">
+      <c r="D82" s="31" t="n">
         <v>60.5</v>
       </c>
-      <c r="E82" s="24" t="n">
+      <c r="E82" s="31" t="n">
         <v>61.7</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="24" t="inlineStr">
+      <c r="A83" s="31" t="inlineStr">
         <is>
           <t>Oklahoma State</t>
         </is>
       </c>
-      <c r="B83" s="24" t="n">
+      <c r="B83" s="31" t="n">
         <v>50.2</v>
       </c>
-      <c r="C83" s="24" t="n">
+      <c r="C83" s="31" t="n">
         <v>54.5</v>
       </c>
-      <c r="D83" s="24" t="n">
+      <c r="D83" s="31" t="n">
         <v>61.5</v>
       </c>
-      <c r="E83" s="24" t="n">
+      <c r="E83" s="31" t="n">
         <v>61.5</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="24" t="inlineStr">
+      <c r="A84" s="31" t="inlineStr">
         <is>
           <t>Utah State</t>
         </is>
       </c>
-      <c r="B84" s="24" t="n">
+      <c r="B84" s="31" t="n">
         <v>60.9</v>
       </c>
-      <c r="C84" s="24" t="n">
+      <c r="C84" s="31" t="n">
         <v>61.7</v>
       </c>
-      <c r="D84" s="24" t="n">
+      <c r="D84" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="E84" s="24" t="n">
+      <c r="E84" s="31" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24" t="inlineStr">
+      <c r="A85" s="31" t="inlineStr">
         <is>
           <t>Miami (OH)</t>
         </is>
       </c>
-      <c r="B85" s="24" t="n">
+      <c r="B85" s="31" t="n">
         <v>55.2</v>
       </c>
-      <c r="C85" s="24" t="n">
+      <c r="C85" s="31" t="n">
         <v>59.9</v>
       </c>
-      <c r="D85" s="24" t="n">
+      <c r="D85" s="31" t="n">
         <v>60.9</v>
       </c>
-      <c r="E85" s="24" t="n">
+      <c r="E85" s="31" t="n">
         <v>60.9</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="24" t="inlineStr">
+      <c r="A86" s="31" t="inlineStr">
         <is>
           <t>UNLV</t>
         </is>
       </c>
-      <c r="B86" s="24" t="n">
+      <c r="B86" s="31" t="n">
         <v>62.6</v>
       </c>
-      <c r="C86" s="24" t="n">
+      <c r="C86" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="D86" s="24" t="n">
+      <c r="D86" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="E86" s="24" t="n">
+      <c r="E86" s="31" t="n">
         <v>60.8</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="24" t="inlineStr">
+      <c r="A87" s="31" t="inlineStr">
         <is>
           <t>Oregon State</t>
         </is>
       </c>
-      <c r="B87" s="24" t="n">
+      <c r="B87" s="31" t="n">
         <v>54.3</v>
       </c>
-      <c r="C87" s="24" t="n">
+      <c r="C87" s="31" t="n">
         <v>56.5</v>
       </c>
-      <c r="D87" s="24" t="n">
+      <c r="D87" s="31" t="n">
         <v>60.8</v>
       </c>
-      <c r="E87" s="24" t="n">
+      <c r="E87" s="31" t="n">
         <v>60.8</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="24" t="inlineStr">
+      <c r="A88" s="31" t="inlineStr">
         <is>
           <t>Fresno State</t>
         </is>
       </c>
-      <c r="B88" s="24" t="n">
+      <c r="B88" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C88" s="24" t="n">
+      <c r="C88" s="31" t="n">
         <v>59.2</v>
       </c>
-      <c r="D88" s="24" t="n">
+      <c r="D88" s="31" t="n">
         <v>60.2</v>
       </c>
-      <c r="E88" s="24" t="n">
+      <c r="E88" s="31" t="n">
         <v>60.2</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24" t="inlineStr">
+      <c r="A89" s="31" t="inlineStr">
         <is>
           <t>San Diego State</t>
         </is>
       </c>
-      <c r="B89" s="24" t="n">
+      <c r="B89" s="31" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="C89" s="24" t="n">
+      <c r="C89" s="31" t="n">
         <v>62.4</v>
       </c>
-      <c r="D89" s="24" t="n">
+      <c r="D89" s="31" t="n">
         <v>62.2</v>
       </c>
-      <c r="E89" s="24" t="n">
+      <c r="E89" s="31" t="n">
         <v>60.2</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="24" t="inlineStr">
+      <c r="A90" s="31" t="inlineStr">
         <is>
           <t>Stanford</t>
         </is>
       </c>
-      <c r="B90" s="24" t="n">
+      <c r="B90" s="31" t="n">
         <v>61.4</v>
       </c>
-      <c r="C90" s="24" t="n">
+      <c r="C90" s="31" t="n">
         <v>61.4</v>
       </c>
-      <c r="D90" s="24" t="n">
+      <c r="D90" s="31" t="n">
         <v>59.9</v>
       </c>
-      <c r="E90" s="24" t="n">
+      <c r="E90" s="31" t="n">
         <v>59.9</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="24" t="inlineStr">
+      <c r="A91" s="31" t="inlineStr">
         <is>
           <t>Tulsa</t>
         </is>
       </c>
-      <c r="B91" s="24" t="n">
+      <c r="B91" s="31" t="n">
         <v>55.3</v>
       </c>
-      <c r="C91" s="24" t="n">
+      <c r="C91" s="31" t="n">
         <v>54.8</v>
       </c>
-      <c r="D91" s="24" t="n">
+      <c r="D91" s="31" t="n">
         <v>59.9</v>
       </c>
-      <c r="E91" s="24" t="n">
+      <c r="E91" s="31" t="n">
         <v>59.9</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="24" t="inlineStr">
+      <c r="A92" s="31" t="inlineStr">
         <is>
           <t>Air Force</t>
         </is>
       </c>
-      <c r="B92" s="24" t="n">
+      <c r="B92" s="31" t="n">
         <v>57.5</v>
       </c>
-      <c r="C92" s="24" t="n">
+      <c r="C92" s="31" t="n">
         <v>59.1</v>
       </c>
-      <c r="D92" s="24" t="n">
+      <c r="D92" s="31" t="n">
         <v>59.1</v>
       </c>
-      <c r="E92" s="24" t="n">
+      <c r="E92" s="31" t="n">
         <v>59.1</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="inlineStr">
+      <c r="A93" s="31" t="inlineStr">
         <is>
           <t>Arkansas State</t>
         </is>
       </c>
-      <c r="B93" s="24" t="n">
+      <c r="B93" s="31" t="n">
         <v>54.6</v>
       </c>
-      <c r="C93" s="24" t="n">
+      <c r="C93" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="D93" s="24" t="n">
+      <c r="D93" s="31" t="n">
         <v>59.1</v>
       </c>
-      <c r="E93" s="24" t="n">
+      <c r="E93" s="31" t="n">
         <v>59.1</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="24" t="inlineStr">
+      <c r="A94" s="31" t="inlineStr">
         <is>
           <t>Temple</t>
         </is>
       </c>
-      <c r="B94" s="24" t="n">
+      <c r="B94" s="31" t="n">
         <v>56.9</v>
       </c>
-      <c r="C94" s="24" t="n">
+      <c r="C94" s="31" t="n">
         <v>57.5</v>
       </c>
-      <c r="D94" s="24" t="n">
+      <c r="D94" s="31" t="n">
         <v>58.5</v>
       </c>
-      <c r="E94" s="24" t="n">
+      <c r="E94" s="31" t="n">
         <v>58.7</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="24" t="inlineStr">
+      <c r="A95" s="31" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="B95" s="24" t="n">
+      <c r="B95" s="31" t="n">
         <v>56.1</v>
       </c>
-      <c r="C95" s="24" t="n">
+      <c r="C95" s="31" t="n">
         <v>57.6</v>
       </c>
-      <c r="D95" s="24" t="n">
+      <c r="D95" s="31" t="n">
         <v>58.3</v>
       </c>
-      <c r="E95" s="24" t="n">
+      <c r="E95" s="31" t="n">
         <v>58.3</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="24" t="inlineStr">
+      <c r="A96" s="31" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="B96" s="24" t="n">
+      <c r="B96" s="31" t="n">
         <v>58.8</v>
       </c>
-      <c r="C96" s="24" t="n">
+      <c r="C96" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="D96" s="24" t="n">
+      <c r="D96" s="31" t="n">
         <v>58.2</v>
       </c>
-      <c r="E96" s="24" t="n">
+      <c r="E96" s="31" t="n">
         <v>58.2</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="24" t="inlineStr">
+      <c r="A97" s="31" t="inlineStr">
         <is>
           <t>Boston College</t>
         </is>
       </c>
-      <c r="B97" s="24" t="n">
+      <c r="B97" s="31" t="n">
         <v>57.5</v>
       </c>
-      <c r="C97" s="24" t="n">
+      <c r="C97" s="31" t="n">
         <v>56.6</v>
       </c>
-      <c r="D97" s="24" t="n">
+      <c r="D97" s="31" t="n">
         <v>57.9</v>
       </c>
-      <c r="E97" s="24" t="n">
+      <c r="E97" s="31" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="24" t="inlineStr">
+      <c r="A98" s="31" t="inlineStr">
         <is>
           <t>Jacksonville State</t>
         </is>
       </c>
-      <c r="B98" s="24" t="n">
+      <c r="B98" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C98" s="24" t="n">
+      <c r="C98" s="31" t="n">
         <v>57.7</v>
       </c>
-      <c r="D98" s="24" t="n">
+      <c r="D98" s="31" t="n">
         <v>57.9</v>
       </c>
-      <c r="E98" s="24" t="n">
+      <c r="E98" s="31" t="n">
         <v>57.9</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="24" t="inlineStr">
+      <c r="A99" s="31" t="inlineStr">
         <is>
           <t>Purdue</t>
         </is>
       </c>
-      <c r="B99" s="24" t="n">
+      <c r="B99" s="31" t="n">
         <v>56.7</v>
       </c>
-      <c r="C99" s="24" t="n">
+      <c r="C99" s="31" t="n">
         <v>57.9</v>
       </c>
-      <c r="D99" s="24" t="n">
+      <c r="D99" s="31" t="n">
         <v>57.2</v>
       </c>
-      <c r="E99" s="24" t="n">
+      <c r="E99" s="31" t="n">
         <v>57.2</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="24" t="inlineStr">
+      <c r="A100" s="31" t="inlineStr">
         <is>
           <t>UConn</t>
         </is>
       </c>
-      <c r="B100" s="24" t="n">
+      <c r="B100" s="31" t="n">
         <v>57.3</v>
       </c>
-      <c r="C100" s="24" t="n">
+      <c r="C100" s="31" t="n">
         <v>54.5</v>
       </c>
-      <c r="D100" s="24" t="n">
+      <c r="D100" s="31" t="n">
         <v>57.1</v>
       </c>
-      <c r="E100" s="24" t="n">
+      <c r="E100" s="31" t="n">
         <v>57.1</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="inlineStr">
+      <c r="A101" s="31" t="inlineStr">
         <is>
           <t>Central Michigan</t>
         </is>
       </c>
-      <c r="B101" s="24" t="n">
+      <c r="B101" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C101" s="24" t="n">
+      <c r="C101" s="31" t="n">
         <v>56.2</v>
       </c>
-      <c r="D101" s="24" t="n">
+      <c r="D101" s="31" t="n">
         <v>57.1</v>
       </c>
-      <c r="E101" s="24" t="n">
+      <c r="E101" s="31" t="n">
         <v>57.1</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="inlineStr">
+      <c r="A102" s="31" t="inlineStr">
         <is>
           <t>Louisiana Tech</t>
         </is>
       </c>
-      <c r="B102" s="24" t="n">
+      <c r="B102" s="31" t="n">
         <v>58.3</v>
       </c>
-      <c r="C102" s="24" t="n">
+      <c r="C102" s="31" t="n">
         <v>57.3</v>
       </c>
-      <c r="D102" s="24" t="n">
+      <c r="D102" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="E102" s="24" t="n">
+      <c r="E102" s="31" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="24" t="inlineStr">
+      <c r="A103" s="31" t="inlineStr">
         <is>
           <t>Syracuse</t>
         </is>
       </c>
-      <c r="B103" s="24" t="n">
+      <c r="B103" s="31" t="n">
         <v>55.7</v>
       </c>
-      <c r="C103" s="24" t="n">
+      <c r="C103" s="31" t="n">
         <v>56.3</v>
       </c>
-      <c r="D103" s="24" t="n">
+      <c r="D103" s="31" t="n">
         <v>56.8</v>
       </c>
-      <c r="E103" s="24" t="n">
+      <c r="E103" s="31" t="n">
         <v>56.8</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="24" t="inlineStr">
+      <c r="A104" s="31" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="B104" s="24" t="n">
+      <c r="B104" s="31" t="n">
         <v>53.1</v>
       </c>
-      <c r="C104" s="24" t="n">
+      <c r="C104" s="31" t="n">
         <v>55.9</v>
       </c>
-      <c r="D104" s="24" t="n">
+      <c r="D104" s="31" t="n">
         <v>56.8</v>
       </c>
-      <c r="E104" s="24" t="n">
+      <c r="E104" s="31" t="n">
         <v>56.8</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="24" t="inlineStr">
+      <c r="A105" s="31" t="inlineStr">
         <is>
           <t>Colorado State</t>
         </is>
       </c>
-      <c r="B105" s="24" t="n">
+      <c r="B105" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C105" s="24" t="n">
+      <c r="C105" s="31" t="n">
         <v>55.7</v>
       </c>
-      <c r="D105" s="24" t="n">
+      <c r="D105" s="31" t="n">
         <v>56.1</v>
       </c>
-      <c r="E105" s="24" t="n">
+      <c r="E105" s="31" t="n">
         <v>56.5</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="24" t="inlineStr">
+      <c r="A106" s="31" t="inlineStr">
         <is>
           <t>Georgia Southern</t>
         </is>
       </c>
-      <c r="B106" s="24" t="n">
+      <c r="B106" s="31" t="n">
         <v>56.1</v>
       </c>
-      <c r="C106" s="24" t="n">
+      <c r="C106" s="31" t="n">
         <v>55.8</v>
       </c>
-      <c r="D106" s="24" t="n">
+      <c r="D106" s="31" t="n">
         <v>55.6</v>
       </c>
-      <c r="E106" s="24" t="n">
+      <c r="E106" s="31" t="n">
         <v>55.6</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="24" t="inlineStr">
+      <c r="A107" s="31" t="inlineStr">
         <is>
           <t>Florida International</t>
         </is>
       </c>
-      <c r="B107" s="24" t="n">
+      <c r="B107" s="31" t="n">
         <v>55.5</v>
       </c>
-      <c r="C107" s="24" t="n">
+      <c r="C107" s="31" t="n">
         <v>56.4</v>
       </c>
-      <c r="D107" s="24" t="n">
+      <c r="D107" s="31" t="n">
         <v>55.5</v>
       </c>
-      <c r="E107" s="24" t="n">
+      <c r="E107" s="31" t="n">
         <v>55.5</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="24" t="inlineStr">
+      <c r="A108" s="31" t="inlineStr">
         <is>
           <t>Hawai'i</t>
         </is>
       </c>
-      <c r="B108" s="24" t="n">
+      <c r="B108" s="31" t="n">
         <v>54.2</v>
       </c>
-      <c r="C108" s="24" t="n">
+      <c r="C108" s="31" t="n">
         <v>55.4</v>
       </c>
-      <c r="D108" s="24" t="n">
+      <c r="D108" s="31" t="n">
         <v>55.4</v>
       </c>
-      <c r="E108" s="24" t="n">
+      <c r="E108" s="31" t="n">
         <v>55.4</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="24" t="inlineStr">
+      <c r="A109" s="31" t="inlineStr">
         <is>
           <t>Louisiana</t>
         </is>
       </c>
-      <c r="B109" s="24" t="n">
+      <c r="B109" s="31" t="n">
         <v>54.3</v>
       </c>
-      <c r="C109" s="24" t="n">
+      <c r="C109" s="31" t="n">
         <v>54.7</v>
       </c>
-      <c r="D109" s="24" t="n">
+      <c r="D109" s="31" t="n">
         <v>55.2</v>
       </c>
-      <c r="E109" s="24" t="n">
+      <c r="E109" s="31" t="n">
         <v>55.2</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="24" t="inlineStr">
+      <c r="A110" s="31" t="inlineStr">
         <is>
           <t>Missouri State</t>
         </is>
       </c>
-      <c r="B110" s="24" t="n">
+      <c r="B110" s="31" t="n">
         <v>50.7</v>
       </c>
-      <c r="C110" s="24" t="n">
+      <c r="C110" s="31" t="n">
         <v>55.6</v>
       </c>
-      <c r="D110" s="24" t="n">
+      <c r="D110" s="31" t="n">
         <v>54.7</v>
       </c>
-      <c r="E110" s="24" t="n">
+      <c r="E110" s="31" t="n">
         <v>54.7</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="24" t="inlineStr">
+      <c r="A111" s="31" t="inlineStr">
         <is>
           <t>Western Kentucky</t>
         </is>
       </c>
-      <c r="B111" s="24" t="n">
+      <c r="B111" s="31" t="n">
         <v>56.1</v>
       </c>
-      <c r="C111" s="24" t="n">
+      <c r="C111" s="31" t="n">
         <v>53.9</v>
       </c>
-      <c r="D111" s="24" t="n">
+      <c r="D111" s="31" t="n">
         <v>54.6</v>
       </c>
-      <c r="E111" s="24" t="n">
+      <c r="E111" s="31" t="n">
         <v>54.6</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="24" t="inlineStr">
+      <c r="A112" s="31" t="inlineStr">
         <is>
           <t>Coastal Carolina</t>
         </is>
       </c>
-      <c r="B112" s="24" t="n">
+      <c r="B112" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C112" s="24" t="n">
+      <c r="C112" s="31" t="n">
         <v>56.1</v>
       </c>
-      <c r="D112" s="24" t="n">
+      <c r="D112" s="31" t="n">
         <v>55.4</v>
       </c>
-      <c r="E112" s="24" t="n">
+      <c r="E112" s="31" t="n">
         <v>54.2</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="24" t="inlineStr">
+      <c r="A113" s="31" t="inlineStr">
         <is>
           <t>Florida Atlantic</t>
         </is>
       </c>
-      <c r="B113" s="24" t="n">
+      <c r="B113" s="31" t="n">
         <v>50.4</v>
       </c>
-      <c r="C113" s="24" t="n">
+      <c r="C113" s="31" t="n">
         <v>53.3</v>
       </c>
-      <c r="D113" s="24" t="n">
+      <c r="D113" s="31" t="n">
         <v>54.2</v>
       </c>
-      <c r="E113" s="24" t="n">
+      <c r="E113" s="31" t="n">
         <v>54.2</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="24" t="inlineStr">
+      <c r="A114" s="31" t="inlineStr">
         <is>
           <t>UAB</t>
         </is>
       </c>
-      <c r="B114" s="24" t="n">
+      <c r="B114" s="31" t="n">
         <v>52.6</v>
       </c>
-      <c r="C114" s="24" t="n">
+      <c r="C114" s="31" t="n">
         <v>52.2</v>
       </c>
-      <c r="D114" s="24" t="n">
+      <c r="D114" s="31" t="n">
         <v>51.8</v>
       </c>
-      <c r="E114" s="24" t="n">
+      <c r="E114" s="31" t="n">
         <v>53.3</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="24" t="inlineStr">
+      <c r="A115" s="31" t="inlineStr">
         <is>
           <t>San José State</t>
         </is>
       </c>
-      <c r="B115" s="24" t="n">
+      <c r="B115" s="31" t="n">
         <v>51.7</v>
       </c>
-      <c r="C115" s="24" t="n">
+      <c r="C115" s="31" t="n">
         <v>53.9</v>
       </c>
-      <c r="D115" s="24" t="n">
+      <c r="D115" s="31" t="n">
         <v>52.9</v>
       </c>
-      <c r="E115" s="24" t="n">
+      <c r="E115" s="31" t="n">
         <v>52.9</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="24" t="inlineStr">
+      <c r="A116" s="31" t="inlineStr">
         <is>
           <t>Nevada</t>
         </is>
       </c>
-      <c r="B116" s="24" t="n">
+      <c r="B116" s="31" t="n">
         <v>54.6</v>
       </c>
-      <c r="C116" s="24" t="n">
+      <c r="C116" s="31" t="n">
         <v>54.2</v>
       </c>
-      <c r="D116" s="24" t="n">
+      <c r="D116" s="31" t="n">
         <v>52.9</v>
       </c>
-      <c r="E116" s="24" t="n">
+      <c r="E116" s="31" t="n">
         <v>52.9</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="24" t="inlineStr">
+      <c r="A117" s="31" t="inlineStr">
         <is>
           <t>Marshall</t>
         </is>
       </c>
-      <c r="B117" s="24" t="n">
+      <c r="B117" s="31" t="n">
         <v>52.1</v>
       </c>
-      <c r="C117" s="24" t="n">
+      <c r="C117" s="31" t="n">
         <v>51.8</v>
       </c>
-      <c r="D117" s="24" t="n">
+      <c r="D117" s="31" t="n">
         <v>52.7</v>
       </c>
-      <c r="E117" s="24" t="n">
+      <c r="E117" s="31" t="n">
         <v>52.7</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="24" t="inlineStr">
+      <c r="A118" s="31" t="inlineStr">
         <is>
           <t>Kennesaw State</t>
         </is>
       </c>
-      <c r="B118" s="24" t="n">
+      <c r="B118" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C118" s="24" t="n">
+      <c r="C118" s="31" t="n">
         <v>53.7</v>
       </c>
-      <c r="D118" s="24" t="n">
+      <c r="D118" s="31" t="n">
         <v>52.6</v>
       </c>
-      <c r="E118" s="24" t="n">
+      <c r="E118" s="31" t="n">
         <v>52.6</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="24" t="inlineStr">
+      <c r="A119" s="31" t="inlineStr">
         <is>
           <t>South Alabama</t>
         </is>
       </c>
-      <c r="B119" s="24" t="n">
+      <c r="B119" s="31" t="n">
         <v>51.6</v>
       </c>
-      <c r="C119" s="24" t="n">
+      <c r="C119" s="31" t="n">
         <v>52.5</v>
       </c>
-      <c r="D119" s="24" t="n">
+      <c r="D119" s="31" t="n">
         <v>53.3</v>
       </c>
-      <c r="E119" s="24" t="n">
+      <c r="E119" s="31" t="n">
         <v>52.4</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="24" t="inlineStr">
+      <c r="A120" s="31" t="inlineStr">
         <is>
           <t>App State</t>
         </is>
       </c>
-      <c r="B120" s="24" t="n">
+      <c r="B120" s="31" t="n">
         <v>49.2</v>
       </c>
-      <c r="C120" s="24" t="n">
+      <c r="C120" s="31" t="n">
         <v>51.1</v>
       </c>
-      <c r="D120" s="24" t="n">
+      <c r="D120" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="E120" s="24" t="n">
+      <c r="E120" s="31" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="24" t="inlineStr">
+      <c r="A121" s="31" t="inlineStr">
         <is>
           <t>Wyoming</t>
         </is>
       </c>
-      <c r="B121" s="24" t="n">
+      <c r="B121" s="31" t="n">
         <v>48.6</v>
       </c>
-      <c r="C121" s="24" t="n">
+      <c r="C121" s="31" t="n">
         <v>50.9</v>
       </c>
-      <c r="D121" s="24" t="n">
+      <c r="D121" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="E121" s="24" t="n">
+      <c r="E121" s="31" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="24" t="inlineStr">
+      <c r="A122" s="31" t="inlineStr">
         <is>
           <t>Southern Miss</t>
         </is>
       </c>
-      <c r="B122" s="24" t="n">
+      <c r="B122" s="31" t="n">
         <v>54.4</v>
       </c>
-      <c r="C122" s="24" t="n">
+      <c r="C122" s="31" t="n">
         <v>52.5</v>
       </c>
-      <c r="D122" s="24" t="n">
+      <c r="D122" s="31" t="n">
         <v>49.9</v>
       </c>
-      <c r="E122" s="24" t="n">
+      <c r="E122" s="31" t="n">
         <v>49.9</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="24" t="inlineStr">
+      <c r="A123" s="31" t="inlineStr">
         <is>
           <t>Buffalo</t>
         </is>
       </c>
-      <c r="B123" s="24" t="n">
+      <c r="B123" s="31" t="n">
         <v>51.5</v>
       </c>
-      <c r="C123" s="24" t="n">
+      <c r="C123" s="31" t="n">
         <v>50.6</v>
       </c>
-      <c r="D123" s="24" t="n">
+      <c r="D123" s="31" t="n">
         <v>49.8</v>
       </c>
-      <c r="E123" s="24" t="n">
+      <c r="E123" s="31" t="n">
         <v>49.8</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="24" t="inlineStr">
+      <c r="A124" s="31" t="inlineStr">
         <is>
           <t>Georgia State</t>
         </is>
       </c>
-      <c r="B124" s="24" t="n">
+      <c r="B124" s="31" t="n">
         <v>47.4</v>
       </c>
-      <c r="C124" s="24" t="n">
+      <c r="C124" s="31" t="n">
         <v>49.7</v>
       </c>
-      <c r="D124" s="24" t="n">
+      <c r="D124" s="31" t="n">
         <v>49.6</v>
       </c>
-      <c r="E124" s="24" t="n">
+      <c r="E124" s="31" t="n">
         <v>49.6</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="24" t="inlineStr">
+      <c r="A125" s="31" t="inlineStr">
         <is>
           <t>Akron</t>
         </is>
       </c>
-      <c r="B125" s="24" t="n">
+      <c r="B125" s="31" t="n">
         <v>48.5</v>
       </c>
-      <c r="C125" s="24" t="n">
+      <c r="C125" s="31" t="n">
         <v>53.7</v>
       </c>
-      <c r="D125" s="24" t="n">
+      <c r="D125" s="31" t="n">
         <v>51.4</v>
       </c>
-      <c r="E125" s="24" t="n">
+      <c r="E125" s="31" t="n">
         <v>49.6</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="24" t="inlineStr">
+      <c r="A126" s="31" t="inlineStr">
         <is>
           <t>New Mexico State</t>
         </is>
       </c>
-      <c r="B126" s="24" t="n">
+      <c r="B126" s="31" t="n">
         <v>50.6</v>
       </c>
-      <c r="C126" s="24" t="n">
+      <c r="C126" s="31" t="n">
         <v>49.5</v>
       </c>
-      <c r="D126" s="24" t="n">
+      <c r="D126" s="31" t="n">
         <v>49.5</v>
       </c>
-      <c r="E126" s="24" t="n">
+      <c r="E126" s="31" t="n">
         <v>49.5</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="24" t="inlineStr">
+      <c r="A127" s="31" t="inlineStr">
         <is>
           <t>Sam Houston</t>
         </is>
       </c>
-      <c r="B127" s="24" t="n">
+      <c r="B127" s="31" t="n">
         <v>41.1</v>
       </c>
-      <c r="C127" s="24" t="n">
+      <c r="C127" s="31" t="n">
         <v>41.7</v>
       </c>
-      <c r="D127" s="24" t="n">
+      <c r="D127" s="31" t="n">
         <v>49.8</v>
       </c>
-      <c r="E127" s="24" t="n">
+      <c r="E127" s="31" t="n">
         <v>49.4</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="24" t="inlineStr">
+      <c r="A128" s="31" t="inlineStr">
         <is>
           <t>Eastern Michigan</t>
         </is>
       </c>
-      <c r="B128" s="24" t="n">
+      <c r="B128" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="C128" s="24" t="n">
+      <c r="C128" s="31" t="n">
         <v>46.4</v>
       </c>
-      <c r="D128" s="24" t="n">
+      <c r="D128" s="31" t="n">
         <v>44.7</v>
       </c>
-      <c r="E128" s="24" t="n">
+      <c r="E128" s="31" t="n">
         <v>49.3</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="24" t="inlineStr">
+      <c r="A129" s="31" t="inlineStr">
         <is>
           <t>Kent State</t>
         </is>
       </c>
-      <c r="B129" s="24" t="n">
+      <c r="B129" s="31" t="n">
         <v>45.6</v>
       </c>
-      <c r="C129" s="24" t="n">
+      <c r="C129" s="31" t="n">
         <v>49.5</v>
       </c>
-      <c r="D129" s="24" t="n">
+      <c r="D129" s="31" t="n">
         <v>47.8</v>
       </c>
-      <c r="E129" s="24" t="n">
+      <c r="E129" s="31" t="n">
         <v>48.9</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="24" t="inlineStr">
+      <c r="A130" s="31" t="inlineStr">
         <is>
           <t>Middle Tennessee</t>
         </is>
       </c>
-      <c r="B130" s="24" t="n">
+      <c r="B130" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C130" s="24" t="n">
+      <c r="C130" s="31" t="n">
         <v>47.4</v>
       </c>
-      <c r="D130" s="24" t="n">
+      <c r="D130" s="31" t="n">
         <v>48.7</v>
       </c>
-      <c r="E130" s="24" t="n">
+      <c r="E130" s="31" t="n">
         <v>48.7</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="24" t="inlineStr">
+      <c r="A131" s="31" t="inlineStr">
         <is>
           <t>Rice</t>
         </is>
       </c>
-      <c r="B131" s="24" t="n">
+      <c r="B131" s="31" t="n">
         <v>46.8</v>
       </c>
-      <c r="C131" s="24" t="n">
+      <c r="C131" s="31" t="n">
         <v>45.8</v>
       </c>
-      <c r="D131" s="24" t="n">
+      <c r="D131" s="31" t="n">
         <v>47.7</v>
       </c>
-      <c r="E131" s="24" t="n">
+      <c r="E131" s="31" t="n">
         <v>47.7</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="24" t="inlineStr">
+      <c r="A132" s="31" t="inlineStr">
         <is>
           <t>Massachusetts</t>
         </is>
       </c>
-      <c r="B132" s="24" t="n">
+      <c r="B132" s="31" t="n">
         <v>37.6</v>
       </c>
-      <c r="C132" s="24" t="n">
+      <c r="C132" s="31" t="n">
         <v>42.9</v>
       </c>
-      <c r="D132" s="24" t="n">
+      <c r="D132" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="E132" s="24" t="n">
+      <c r="E132" s="31" t="n">
         <v>47.2</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="24" t="inlineStr">
+      <c r="A133" s="31" t="inlineStr">
         <is>
           <t>UTEP</t>
         </is>
       </c>
-      <c r="B133" s="24" t="n">
+      <c r="B133" s="31" t="n">
         <v>40.8</v>
       </c>
-      <c r="C133" s="24" t="n">
+      <c r="C133" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="D133" s="24" t="n">
+      <c r="D133" s="31" t="n">
         <v>46.3</v>
       </c>
-      <c r="E133" s="24" t="n">
+      <c r="E133" s="31" t="n">
         <v>46.3</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="24" t="inlineStr">
+      <c r="A134" s="31" t="inlineStr">
         <is>
           <t>Northern Illinois</t>
         </is>
       </c>
-      <c r="B134" s="24" t="n">
+      <c r="B134" s="31" t="n">
         <v>44.3</v>
       </c>
-      <c r="C134" s="24" t="n">
+      <c r="C134" s="31" t="n">
         <v>45.8</v>
       </c>
-      <c r="D134" s="24" t="n">
+      <c r="D134" s="31" t="n">
         <v>45.9</v>
       </c>
-      <c r="E134" s="24" t="n">
+      <c r="E134" s="31" t="n">
         <v>45.9</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="24" t="inlineStr">
+      <c r="A135" s="31" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="B135" s="24" t="n">
+      <c r="B135" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C135" s="24" t="n">
+      <c r="C135" s="31" t="n">
         <v>44.9</v>
       </c>
-      <c r="D135" s="24" t="n">
+      <c r="D135" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="E135" s="24" t="n">
+      <c r="E135" s="31" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="24" t="inlineStr">
+      <c r="A136" s="31" t="inlineStr">
         <is>
           <t>UL Monroe</t>
         </is>
       </c>
-      <c r="B136" s="24" t="n">
+      <c r="B136" s="31" t="n">
         <v>42.9</v>
       </c>
-      <c r="C136" s="24" t="n">
+      <c r="C136" s="31" t="n">
         <v>43.3</v>
       </c>
-      <c r="D136" s="24" t="n">
+      <c r="D136" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="E136" s="24" t="n">
+      <c r="E136" s="31" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="24" t="inlineStr">
+      <c r="A137" s="31" t="inlineStr">
         <is>
           <t>Ball State</t>
         </is>
       </c>
-      <c r="B137" s="24" t="n">
+      <c r="B137" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C137" s="24" t="n">
+      <c r="C137" s="31" t="n">
         <v>47.5</v>
       </c>
-      <c r="D137" s="24" t="n">
+      <c r="D137" s="31" t="n">
         <v>44.9</v>
       </c>
-      <c r="E137" s="24" t="n">
+      <c r="E137" s="31" t="n">
         <v>43.9</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="24" t="inlineStr">
+      <c r="A138" s="31" t="inlineStr">
         <is>
           <t>Bowling Green</t>
         </is>
       </c>
-      <c r="B138" s="24" t="n">
+      <c r="B138" s="31" t="n">
         <v>48.8</v>
       </c>
-      <c r="C138" s="24" t="n">
+      <c r="C138" s="31" t="n">
         <v>46.2</v>
       </c>
-      <c r="D138" s="24" t="n">
+      <c r="D138" s="31" t="n">
         <v>43.7</v>
       </c>
-      <c r="E138" s="24" t="n">
+      <c r="E138" s="31" t="n">
         <v>43.7</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="24" t="inlineStr">
+      <c r="A139" s="31" t="inlineStr">
         <is>
           <t>Sacramento State</t>
         </is>
       </c>
-      <c r="B139" s="24" t="n">
+      <c r="B139" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C139" s="24" t="n">
+      <c r="C139" s="31" t="n">
         <v>37.9</v>
       </c>
-      <c r="D139" s="24" t="n">
+      <c r="D139" s="31" t="n">
         <v>39.8</v>
       </c>
-      <c r="E139" s="24" t="n">
+      <c r="E139" s="31" t="n">
         <v>39.8</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=$A$2:$A$139</formula1>
-    </dataValidation>
-    <dataValidation sqref="W4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=$A$2:$A$139</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="W3:W4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>$A$2:$A$139</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>MW Team ATS -- 2026 Season (graded vs. the real market line, not any model)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>ATS Record (C-L-P)</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>Cover %</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>1-1-0</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Hawai'i</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>1-2-0</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>1-2-0</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>3-0-0</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>2-2-0</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Northern Illinois</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>1-2-0</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>San José State</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>2-2-0</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>2-2-0</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>UTEP</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>1-2-0</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>0-3-0</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Opponent</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Team's Spread</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>Result (Margin)</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>ATS Result</t>
+        </is>
+      </c>
+      <c r="I16" s="35" t="inlineStr">
+        <is>
+          <t>Cover Margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Duquesne</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>34</v>
+      </c>
+      <c r="H17" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="n">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Hawai'i</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Stanford</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H19" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I19" s="31" t="n">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Hawai'i</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G20" s="31" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H20" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I20" s="31" t="n">
+        <v>-12.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>Hawai'i</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>New Mexico State</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="G21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I21" s="31" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>Western Kentucky</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G22" s="31" t="n">
+        <v>35</v>
+      </c>
+      <c r="H22" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I22" s="31" t="n">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Montana State</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="31" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H23" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I23" s="31" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Middle Tennessee</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="G24" s="31" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H24" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I24" s="31" t="n">
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Central Michigan</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="G25" s="31" t="n">
+        <v>31</v>
+      </c>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I25" s="31" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>Mercyhurst</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="n">
+        <v>-42.2</v>
+      </c>
+      <c r="G26" s="31" t="n">
+        <v>63</v>
+      </c>
+      <c r="H26" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I26" s="31" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G27" s="31" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H27" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I27" s="31" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>Jacksonville State</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="G28" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="H28" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I28" s="31" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Fordham</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>-41.5</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="H29" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I29" s="31" t="n">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G30" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I30" s="31" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Sacramento State</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="G31" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="H31" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I31" s="31" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Northern Illinois</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G32" s="31" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H32" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I32" s="31" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>Northern Illinois</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>Illinois State</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G33" s="31" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H33" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I33" s="31" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>Northern Illinois</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G34" s="31" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H34" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I34" s="31" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>San José State</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G35" s="31" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H35" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I35" s="31" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>San José State</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>Eastern Michigan</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G36" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I36" s="31" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>San José State</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Cal Poly</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I37" s="31" t="n">
+        <v>-11.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>San José State</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="inlineStr">
+        <is>
+          <t>Fresno State</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F38" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H38" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I38" s="31" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F39" s="31" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H39" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I39" s="31" t="n">
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>Hawai'i</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I40" s="31" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>-38</v>
+      </c>
+      <c r="H41" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I41" s="31" t="n">
+        <v>-40.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="H42" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I42" s="31" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>UTEP</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F43" s="31" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="G43" s="31" t="n">
+        <v>-51</v>
+      </c>
+      <c r="H43" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I43" s="31" t="n">
+        <v>-10.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>UTEP</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>Texas Southern</t>
+        </is>
+      </c>
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="n">
+        <v>-27.2</v>
+      </c>
+      <c r="G44" s="31" t="n">
+        <v>41</v>
+      </c>
+      <c r="H44" s="36" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="I44" s="31" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>UTEP</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G45" s="31" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H45" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I45" s="31" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>Colorado State</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G46" s="31" t="n">
+        <v>-22</v>
+      </c>
+      <c r="H46" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I46" s="31" t="n">
+        <v>-19.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>Northern Colorado</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="G47" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I47" s="31" t="n">
+        <v>-15.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>Central Michigan</t>
+        </is>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G48" s="31" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H48" s="37" t="inlineStr">
+        <is>
+          <t>No Cover</t>
+        </is>
+      </c>
+      <c r="I48" s="31" t="n">
+        <v>-15.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="J6" t="n">
         <v>56.2</v>
@@ -1348,7 +1348,7 @@
         <v/>
       </c>
       <c r="I7" s="10" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>50.5</v>
@@ -17475,20 +17475,20 @@
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>Ole Miss</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="B10" s="35" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="C10" s="35" t="n">
-        <v>84</v>
+        <v>83.5</v>
       </c>
       <c r="D10" s="35" t="n">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="E10" s="35" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="V10" s="37" t="inlineStr">
         <is>
@@ -17499,58 +17499,58 @@
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="B11" s="35" t="n">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="C11" s="35" t="n">
-        <v>83.5</v>
+        <v>80.2</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>84.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>84.3</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="B12" s="35" t="n">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C12" s="35" t="n">
-        <v>80.2</v>
+        <v>82.3</v>
       </c>
       <c r="D12" s="35" t="n">
-        <v>84.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="E12" s="35" t="n">
-        <v>83.7</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B13" s="35" t="n">
-        <v>80.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="C13" s="35" t="n">
-        <v>82.3</v>
+        <v>83.2</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>82.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E13" s="35" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="14">
@@ -17575,226 +17575,226 @@
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Penn State</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="B15" s="35" t="n">
-        <v>80.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="C15" s="35" t="n">
-        <v>80.3</v>
+        <v>79</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>81.2</v>
+        <v>78.7</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>81.2</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Ole Miss</t>
         </is>
       </c>
       <c r="B16" s="35" t="n">
-        <v>75.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="C16" s="35" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D16" s="35" t="n">
-        <v>81</v>
+        <v>84.5</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="B17" s="35" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C17" s="35" t="n">
-        <v>74.8</v>
+        <v>81</v>
       </c>
       <c r="D17" s="35" t="n">
-        <v>76.2</v>
+        <v>81</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="B18" s="35" t="n">
-        <v>76.8</v>
+        <v>75</v>
       </c>
       <c r="C18" s="35" t="n">
-        <v>77.8</v>
+        <v>74.8</v>
       </c>
       <c r="D18" s="35" t="n">
-        <v>78.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="E18" s="35" t="n">
-        <v>80.2</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Penn State</t>
         </is>
       </c>
       <c r="B19" s="35" t="n">
-        <v>79.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C19" s="35" t="n">
-        <v>83.2</v>
+        <v>80.3</v>
       </c>
       <c r="D19" s="35" t="n">
-        <v>80.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="E19" s="35" t="n">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B20" s="35" t="n">
-        <v>79.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="C20" s="35" t="n">
-        <v>78.3</v>
+        <v>77.8</v>
       </c>
       <c r="D20" s="35" t="n">
-        <v>80</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E20" s="35" t="n">
-        <v>80</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B21" s="35" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="C21" s="35" t="n">
-        <v>80.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="D21" s="35" t="n">
-        <v>79.7</v>
+        <v>80</v>
       </c>
       <c r="E21" s="35" t="n">
-        <v>79.7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="B22" s="35" t="n">
-        <v>75.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C22" s="35" t="n">
-        <v>74.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D22" s="35" t="n">
-        <v>74.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="E22" s="35" t="n">
-        <v>79.09999999999999</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B23" s="35" t="n">
-        <v>80.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="C23" s="35" t="n">
-        <v>78.8</v>
+        <v>74.7</v>
       </c>
       <c r="D23" s="35" t="n">
-        <v>78.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E23" s="35" t="n">
-        <v>78.8</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="B24" s="35" t="n">
-        <v>75.2</v>
+        <v>78.3</v>
       </c>
       <c r="C24" s="35" t="n">
         <v>79</v>
       </c>
       <c r="D24" s="35" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="E24" s="35" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="B25" s="35" t="n">
-        <v>78.3</v>
+        <v>74.7</v>
       </c>
       <c r="C25" s="35" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="D25" s="35" t="n">
-        <v>78.5</v>
+        <v>79.8</v>
       </c>
       <c r="E25" s="35" t="n">
-        <v>78.5</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="B26" s="35" t="n">
-        <v>74.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C26" s="35" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D26" s="35" t="n">
-        <v>79.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E26" s="35" t="n">
         <v>77.90000000000001</v>
@@ -17803,17 +17803,17 @@
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B27" s="35" t="n">
-        <v>75.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="C27" s="35" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="D27" s="35" t="n">
-        <v>77.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="E27" s="35" t="n">
         <v>77.90000000000001</v>
@@ -17822,36 +17822,36 @@
     <row r="28">
       <c r="A28" s="35" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="B28" s="35" t="n">
-        <v>81.2</v>
+        <v>78</v>
       </c>
       <c r="C28" s="35" t="n">
-        <v>79.5</v>
+        <v>77.5</v>
       </c>
       <c r="D28" s="35" t="n">
-        <v>80</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E28" s="35" t="n">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="35" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="B29" s="35" t="n">
-        <v>78</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C29" s="35" t="n">
-        <v>77.5</v>
+        <v>78.8</v>
       </c>
       <c r="D29" s="35" t="n">
-        <v>77.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="E29" s="35" t="n">
         <v>77.40000000000001</v>
@@ -17860,39 +17860,39 @@
     <row r="30">
       <c r="A30" s="35" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B30" s="35" t="n">
-        <v>67.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C30" s="35" t="n">
-        <v>76.8</v>
+        <v>74.7</v>
       </c>
       <c r="D30" s="35" t="n">
-        <v>77.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="E30" s="35" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="35" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B31" s="35" t="n">
-        <v>72.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="C31" s="35" t="n">
-        <v>74.7</v>
+        <v>76.8</v>
       </c>
       <c r="D31" s="35" t="n">
-        <v>76.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>76.3</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -17930,7 +17930,7 @@
         <v>75.8</v>
       </c>
       <c r="E33" s="35" t="n">
-        <v>75.8</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="34">
@@ -18126,58 +18126,58 @@
     <row r="44">
       <c r="A44" s="35" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="B44" s="35" t="n">
-        <v>73.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="C44" s="35" t="n">
-        <v>72.7</v>
+        <v>71.2</v>
       </c>
       <c r="D44" s="35" t="n">
-        <v>72.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E44" s="35" t="n">
-        <v>72.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="35" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="B45" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C45" s="35" t="n">
         <v>72.7</v>
       </c>
       <c r="D45" s="35" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E45" s="35" t="n">
-        <v>72.3</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="35" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B46" s="35" t="n">
-        <v>68.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C46" s="35" t="n">
-        <v>68.3</v>
+        <v>72.7</v>
       </c>
       <c r="D46" s="35" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E46" s="35" t="n">
-        <v>72</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="47">
@@ -18221,36 +18221,36 @@
     <row r="49">
       <c r="A49" s="35" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="B49" s="35" t="n">
-        <v>69.40000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="C49" s="35" t="n">
-        <v>71.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D49" s="35" t="n">
-        <v>71.5</v>
+        <v>66.7</v>
       </c>
       <c r="E49" s="35" t="n">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="35" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Mississippi State</t>
         </is>
       </c>
       <c r="B50" s="35" t="n">
-        <v>63.8</v>
+        <v>68.8</v>
       </c>
       <c r="C50" s="35" t="n">
-        <v>65.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="D50" s="35" t="n">
-        <v>66.7</v>
+        <v>71.3</v>
       </c>
       <c r="E50" s="35" t="n">
         <v>71.3</v>
@@ -18259,20 +18259,20 @@
     <row r="51">
       <c r="A51" s="35" t="inlineStr">
         <is>
-          <t>Mississippi State</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="B51" s="35" t="n">
-        <v>68.8</v>
+        <v>68.2</v>
       </c>
       <c r="C51" s="35" t="n">
-        <v>71.3</v>
+        <v>68.3</v>
       </c>
       <c r="D51" s="35" t="n">
-        <v>71.3</v>
+        <v>72</v>
       </c>
       <c r="E51" s="35" t="n">
-        <v>71.3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
@@ -18316,58 +18316,58 @@
     <row r="54">
       <c r="A54" s="35" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B54" s="35" t="n">
-        <v>69.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="C54" s="35" t="n">
         <v>67.2</v>
       </c>
       <c r="D54" s="35" t="n">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E54" s="35" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="35" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="B55" s="35" t="n">
-        <v>67.8</v>
+        <v>69.8</v>
       </c>
       <c r="C55" s="35" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D55" s="35" t="n">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="E55" s="35" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="35" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="B56" s="35" t="n">
-        <v>64.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="C56" s="35" t="n">
-        <v>67.2</v>
+        <v>68.2</v>
       </c>
       <c r="D56" s="35" t="n">
-        <v>68.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E56" s="35" t="n">
-        <v>68.90000000000001</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="57">
@@ -18525,20 +18525,20 @@
     <row r="65">
       <c r="A65" s="35" t="inlineStr">
         <is>
-          <t>Michigan State</t>
+          <t>East Carolina</t>
         </is>
       </c>
       <c r="B65" s="35" t="n">
-        <v>66</v>
+        <v>64.8</v>
       </c>
       <c r="C65" s="35" t="n">
-        <v>66.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="D65" s="35" t="n">
-        <v>67.5</v>
+        <v>63.9</v>
       </c>
       <c r="E65" s="35" t="n">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="66">
@@ -18582,191 +18582,191 @@
     <row r="68">
       <c r="A68" s="35" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="B68" s="35" t="n">
-        <v>58.2</v>
+        <v>66</v>
       </c>
       <c r="C68" s="35" t="n">
-        <v>63.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D68" s="35" t="n">
-        <v>66.3</v>
+        <v>67.5</v>
       </c>
       <c r="E68" s="35" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B69" s="35" t="n">
-        <v>65.7</v>
+        <v>58.2</v>
       </c>
       <c r="C69" s="35" t="n">
-        <v>65.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="D69" s="35" t="n">
-        <v>65.7</v>
+        <v>66.3</v>
       </c>
       <c r="E69" s="35" t="n">
-        <v>65.7</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="inlineStr">
         <is>
-          <t>UTSA</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B70" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="C70" s="35" t="n">
-        <v>66.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D70" s="35" t="n">
-        <v>66</v>
+        <v>65.7</v>
       </c>
       <c r="E70" s="35" t="n">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>UTSA</t>
         </is>
       </c>
       <c r="B71" s="35" t="n">
-        <v>62.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C71" s="35" t="n">
-        <v>63</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D71" s="35" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E71" s="35" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="B72" s="35" t="n">
-        <v>63.9</v>
+        <v>62.3</v>
       </c>
       <c r="C72" s="35" t="n">
-        <v>67.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="D72" s="35" t="n">
-        <v>64.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E72" s="35" t="n">
-        <v>64.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="35" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="B73" s="35" t="n">
-        <v>61.3</v>
+        <v>63.9</v>
       </c>
       <c r="C73" s="35" t="n">
-        <v>64.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D73" s="35" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E73" s="35" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="inlineStr">
         <is>
-          <t>Army</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="B74" s="35" t="n">
-        <v>64.5</v>
+        <v>61.3</v>
       </c>
       <c r="C74" s="35" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D74" s="35" t="n">
         <v>64.5</v>
       </c>
       <c r="E74" s="35" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Army</t>
         </is>
       </c>
       <c r="B75" s="35" t="n">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="C75" s="35" t="n">
-        <v>68</v>
+        <v>64.5</v>
       </c>
       <c r="D75" s="35" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="E75" s="35" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="B76" s="35" t="n">
-        <v>66.90000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C76" s="35" t="n">
-        <v>65.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="D76" s="35" t="n">
-        <v>64</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E76" s="35" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="35" t="inlineStr">
         <is>
-          <t>East Carolina</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B77" s="35" t="n">
-        <v>64.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="C77" s="35" t="n">
-        <v>63</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D77" s="35" t="n">
-        <v>63.9</v>
+        <v>64</v>
       </c>
       <c r="E77" s="35" t="n">
-        <v>63.9</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78">
@@ -19114,36 +19114,36 @@
     <row r="96">
       <c r="A96" s="35" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="B96" s="35" t="n">
-        <v>56.1</v>
+        <v>57.5</v>
       </c>
       <c r="C96" s="35" t="n">
-        <v>57.6</v>
+        <v>56.6</v>
       </c>
       <c r="D96" s="35" t="n">
-        <v>58.3</v>
+        <v>57.9</v>
       </c>
       <c r="E96" s="35" t="n">
-        <v>58.3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="35" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Florida International</t>
         </is>
       </c>
       <c r="B97" s="35" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="C97" s="35" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="D97" s="35" t="n">
-        <v>57.9</v>
+        <v>55.5</v>
       </c>
       <c r="E97" s="35" t="n">
         <v>58</v>
@@ -19266,77 +19266,77 @@
     <row r="104">
       <c r="A104" s="35" t="inlineStr">
         <is>
-          <t>Colorado State</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B104" s="35" t="n">
-        <v>51</v>
+        <v>56.1</v>
       </c>
       <c r="C104" s="35" t="n">
-        <v>55.7</v>
+        <v>57.6</v>
       </c>
       <c r="D104" s="35" t="n">
-        <v>56.1</v>
+        <v>58.3</v>
       </c>
       <c r="E104" s="35" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="35" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Colorado State</t>
         </is>
       </c>
       <c r="B105" s="35" t="n">
-        <v>56.7</v>
+        <v>51</v>
       </c>
       <c r="C105" s="35" t="n">
-        <v>57.9</v>
+        <v>55.7</v>
       </c>
       <c r="D105" s="35" t="n">
-        <v>57.2</v>
+        <v>56.1</v>
       </c>
       <c r="E105" s="35" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="35" t="inlineStr">
         <is>
-          <t>Georgia Southern</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="B106" s="35" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="C106" s="35" t="n">
-        <v>55.8</v>
+        <v>57.9</v>
       </c>
       <c r="D106" s="35" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="E106" s="35" t="n">
-        <v>55.6</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="35" t="inlineStr">
         <is>
-          <t>Florida International</t>
+          <t>Georgia Southern</t>
         </is>
       </c>
       <c r="B107" s="35" t="n">
-        <v>55.5</v>
+        <v>56.1</v>
       </c>
       <c r="C107" s="35" t="n">
-        <v>56.4</v>
+        <v>55.8</v>
       </c>
       <c r="D107" s="35" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="E107" s="35" t="n">
-        <v>55.5</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="108">
@@ -19836,33 +19836,33 @@
     <row r="134">
       <c r="A134" s="35" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Bowling Green</t>
         </is>
       </c>
       <c r="B134" s="35" t="n">
-        <v>44</v>
+        <v>48.8</v>
       </c>
       <c r="C134" s="35" t="n">
-        <v>44.9</v>
+        <v>46.2</v>
       </c>
       <c r="D134" s="35" t="n">
-        <v>45</v>
+        <v>43.7</v>
       </c>
       <c r="E134" s="35" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="35" t="inlineStr">
         <is>
-          <t>UL Monroe</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B135" s="35" t="n">
-        <v>42.9</v>
+        <v>44</v>
       </c>
       <c r="C135" s="35" t="n">
-        <v>43.3</v>
+        <v>44.9</v>
       </c>
       <c r="D135" s="35" t="n">
         <v>45</v>
@@ -19874,58 +19874,58 @@
     <row r="136">
       <c r="A136" s="35" t="inlineStr">
         <is>
-          <t>Northern Illinois</t>
+          <t>UL Monroe</t>
         </is>
       </c>
       <c r="B136" s="35" t="n">
-        <v>44.3</v>
+        <v>42.9</v>
       </c>
       <c r="C136" s="35" t="n">
-        <v>45.8</v>
+        <v>43.3</v>
       </c>
       <c r="D136" s="35" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="E136" s="35" t="n">
-        <v>44.2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="35" t="inlineStr">
         <is>
-          <t>Ball State</t>
+          <t>Northern Illinois</t>
         </is>
       </c>
       <c r="B137" s="35" t="n">
-        <v>43</v>
+        <v>44.3</v>
       </c>
       <c r="C137" s="35" t="n">
-        <v>47.5</v>
+        <v>45.8</v>
       </c>
       <c r="D137" s="35" t="n">
-        <v>44.9</v>
+        <v>45.9</v>
       </c>
       <c r="E137" s="35" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="35" t="inlineStr">
         <is>
-          <t>Bowling Green</t>
+          <t>Ball State</t>
         </is>
       </c>
       <c r="B138" s="35" t="n">
-        <v>48.8</v>
+        <v>43</v>
       </c>
       <c r="C138" s="35" t="n">
-        <v>46.2</v>
+        <v>47.5</v>
       </c>
       <c r="D138" s="35" t="n">
-        <v>43.7</v>
+        <v>44.9</v>
       </c>
       <c r="E138" s="35" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="139">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -17341,7 +17341,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="E4" s="35" t="n">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V4" s="35" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>89.7</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="7">
@@ -17499,77 +17499,77 @@
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="B11" s="35" t="n">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C11" s="35" t="n">
-        <v>80.2</v>
+        <v>82.3</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>84.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>83.7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="B12" s="35" t="n">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="C12" s="35" t="n">
-        <v>82.3</v>
+        <v>80.2</v>
       </c>
       <c r="D12" s="35" t="n">
-        <v>82.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E12" s="35" t="n">
-        <v>82.2</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="B13" s="35" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C13" s="35" t="n">
-        <v>83.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>80.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="E13" s="35" t="n">
-        <v>81.8</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B14" s="35" t="n">
-        <v>82.8</v>
+        <v>79.2</v>
       </c>
       <c r="C14" s="35" t="n">
-        <v>84.3</v>
+        <v>83.2</v>
       </c>
       <c r="D14" s="35" t="n">
-        <v>81.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E14" s="35" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="15">
@@ -17613,115 +17613,115 @@
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="B17" s="35" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="C17" s="35" t="n">
-        <v>81</v>
+        <v>74.8</v>
       </c>
       <c r="D17" s="35" t="n">
-        <v>81</v>
+        <v>76.2</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Penn State</t>
         </is>
       </c>
       <c r="B18" s="35" t="n">
-        <v>75</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C18" s="35" t="n">
-        <v>74.8</v>
+        <v>80.3</v>
       </c>
       <c r="D18" s="35" t="n">
-        <v>76.2</v>
+        <v>81.2</v>
       </c>
       <c r="E18" s="35" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>Penn State</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B19" s="35" t="n">
-        <v>80.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="C19" s="35" t="n">
-        <v>80.3</v>
+        <v>77.8</v>
       </c>
       <c r="D19" s="35" t="n">
-        <v>81.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E19" s="35" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B20" s="35" t="n">
-        <v>76.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C20" s="35" t="n">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="D20" s="35" t="n">
-        <v>78.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="E20" s="35" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>79.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C21" s="35" t="n">
-        <v>78.3</v>
+        <v>81</v>
       </c>
       <c r="D21" s="35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" s="35" t="n">
-        <v>80</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B22" s="35" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="C22" s="35" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E22" s="35" t="n">
         <v>79.09999999999999</v>
-      </c>
-      <c r="C22" s="35" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>79.7</v>
       </c>
     </row>
     <row r="23">
@@ -17746,55 +17746,55 @@
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="B24" s="35" t="n">
-        <v>78.3</v>
+        <v>82.8</v>
       </c>
       <c r="C24" s="35" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="E24" s="35" t="n">
         <v>79</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="E24" s="35" t="n">
-        <v>78.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="B25" s="35" t="n">
-        <v>74.7</v>
+        <v>78.3</v>
       </c>
       <c r="C25" s="35" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="D25" s="35" t="n">
-        <v>79.8</v>
+        <v>78.5</v>
       </c>
       <c r="E25" s="35" t="n">
-        <v>77.90000000000001</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="B26" s="35" t="n">
-        <v>75.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C26" s="35" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="D26" s="35" t="n">
-        <v>77.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="E26" s="35" t="n">
         <v>77.90000000000001</v>
@@ -17803,17 +17803,17 @@
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="B27" s="35" t="n">
-        <v>81.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C27" s="35" t="n">
-        <v>79.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D27" s="35" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E27" s="35" t="n">
         <v>77.90000000000001</v>
@@ -17822,77 +17822,77 @@
     <row r="28">
       <c r="A28" s="35" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B28" s="35" t="n">
-        <v>78</v>
+        <v>81.2</v>
       </c>
       <c r="C28" s="35" t="n">
-        <v>77.5</v>
+        <v>79.5</v>
       </c>
       <c r="D28" s="35" t="n">
-        <v>77.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="E28" s="35" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="35" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="B29" s="35" t="n">
-        <v>80.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="C29" s="35" t="n">
-        <v>78.8</v>
+        <v>77.5</v>
       </c>
       <c r="D29" s="35" t="n">
-        <v>78.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E29" s="35" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="35" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="B30" s="35" t="n">
-        <v>72.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C30" s="35" t="n">
-        <v>74.7</v>
+        <v>78.8</v>
       </c>
       <c r="D30" s="35" t="n">
-        <v>76.3</v>
+        <v>78.8</v>
       </c>
       <c r="E30" s="35" t="n">
-        <v>77.2</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="35" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B31" s="35" t="n">
-        <v>67.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C31" s="35" t="n">
-        <v>76.8</v>
+        <v>74.7</v>
       </c>
       <c r="D31" s="35" t="n">
-        <v>77.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="32">
@@ -17993,131 +17993,131 @@
     <row r="37">
       <c r="A37" s="35" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="B37" s="35" t="n">
-        <v>67.2</v>
+        <v>71</v>
       </c>
       <c r="C37" s="35" t="n">
-        <v>74.2</v>
+        <v>71.2</v>
       </c>
       <c r="D37" s="35" t="n">
         <v>74.3</v>
       </c>
       <c r="E37" s="35" t="n">
-        <v>74.3</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="35" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="B38" s="35" t="n">
-        <v>74.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C38" s="35" t="n">
-        <v>74.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D38" s="35" t="n">
-        <v>74</v>
+        <v>71.5</v>
       </c>
       <c r="E38" s="35" t="n">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="35" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B39" s="35" t="n">
-        <v>71</v>
+        <v>69.3</v>
       </c>
       <c r="C39" s="35" t="n">
-        <v>71.2</v>
+        <v>74</v>
       </c>
       <c r="D39" s="35" t="n">
-        <v>74.3</v>
+        <v>73</v>
       </c>
       <c r="E39" s="35" t="n">
-        <v>73.8</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="35" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="B40" s="35" t="n">
-        <v>68.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C40" s="35" t="n">
-        <v>68.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="D40" s="35" t="n">
-        <v>71.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E40" s="35" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="35" t="inlineStr">
         <is>
-          <t>Kansas State</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="B41" s="35" t="n">
-        <v>70.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C41" s="35" t="n">
-        <v>73.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D41" s="35" t="n">
-        <v>73.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E41" s="35" t="n">
-        <v>73.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="35" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Kansas State</t>
         </is>
       </c>
       <c r="B42" s="35" t="n">
-        <v>69.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="C42" s="35" t="n">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="D42" s="35" t="n">
-        <v>75.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E42" s="35" t="n">
-        <v>73.09999999999999</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="35" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="B43" s="35" t="n">
-        <v>69.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C43" s="35" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="D43" s="35" t="n">
         <v>74</v>
-      </c>
-      <c r="D43" s="35" t="n">
-        <v>73</v>
       </c>
       <c r="E43" s="35" t="n">
         <v>73</v>
@@ -18126,17 +18126,17 @@
     <row r="44">
       <c r="A44" s="35" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="B44" s="35" t="n">
-        <v>69.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="C44" s="35" t="n">
-        <v>71.2</v>
+        <v>74.2</v>
       </c>
       <c r="D44" s="35" t="n">
-        <v>71.5</v>
+        <v>74.3</v>
       </c>
       <c r="E44" s="35" t="n">
         <v>72.90000000000001</v>
@@ -18145,20 +18145,20 @@
     <row r="45">
       <c r="A45" s="35" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="B45" s="35" t="n">
-        <v>73.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="C45" s="35" t="n">
-        <v>72.7</v>
+        <v>71.2</v>
       </c>
       <c r="D45" s="35" t="n">
-        <v>72.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E45" s="35" t="n">
-        <v>72.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -18183,74 +18183,74 @@
     <row r="47">
       <c r="A47" s="35" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Mississippi State</t>
         </is>
       </c>
       <c r="B47" s="35" t="n">
-        <v>66.8</v>
+        <v>68.8</v>
       </c>
       <c r="C47" s="35" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="D47" s="35" t="n">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="E47" s="35" t="n">
-        <v>72</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="35" t="inlineStr">
         <is>
-          <t>Iowa State</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="B48" s="35" t="n">
-        <v>68.3</v>
+        <v>66.8</v>
       </c>
       <c r="C48" s="35" t="n">
-        <v>69.3</v>
+        <v>71.2</v>
       </c>
       <c r="D48" s="35" t="n">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="E48" s="35" t="n">
-        <v>71.7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="35" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Iowa State</t>
         </is>
       </c>
       <c r="B49" s="35" t="n">
-        <v>63.8</v>
+        <v>68.3</v>
       </c>
       <c r="C49" s="35" t="n">
-        <v>65.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="D49" s="35" t="n">
-        <v>66.7</v>
+        <v>71.8</v>
       </c>
       <c r="E49" s="35" t="n">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="35" t="inlineStr">
         <is>
-          <t>Mississippi State</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="B50" s="35" t="n">
-        <v>68.8</v>
+        <v>63.8</v>
       </c>
       <c r="C50" s="35" t="n">
-        <v>71.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D50" s="35" t="n">
-        <v>71.3</v>
+        <v>66.7</v>
       </c>
       <c r="E50" s="35" t="n">
         <v>71.3</v>
@@ -18278,17 +18278,17 @@
     <row r="52">
       <c r="A52" s="35" t="inlineStr">
         <is>
-          <t>Florida State</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="B52" s="35" t="n">
-        <v>67.2</v>
+        <v>63.9</v>
       </c>
       <c r="C52" s="35" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D52" s="35" t="n">
-        <v>67.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E52" s="35" t="n">
         <v>69.7</v>
@@ -18297,36 +18297,36 @@
     <row r="53">
       <c r="A53" s="35" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Florida State</t>
         </is>
       </c>
       <c r="B53" s="35" t="n">
-        <v>67.7</v>
+        <v>67.2</v>
       </c>
       <c r="C53" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="D53" s="35" t="n">
-        <v>69.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="E53" s="35" t="n">
-        <v>69.59999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="35" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="B54" s="35" t="n">
-        <v>64.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="C54" s="35" t="n">
-        <v>67.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D54" s="35" t="n">
-        <v>68.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E54" s="35" t="n">
         <v>69.59999999999999</v>
@@ -18335,150 +18335,150 @@
     <row r="55">
       <c r="A55" s="35" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B55" s="35" t="n">
-        <v>69.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="C55" s="35" t="n">
         <v>67.2</v>
       </c>
       <c r="D55" s="35" t="n">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E55" s="35" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="35" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="B56" s="35" t="n">
-        <v>67.8</v>
+        <v>69.8</v>
       </c>
       <c r="C56" s="35" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D56" s="35" t="n">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="E56" s="35" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="35" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="B57" s="35" t="n">
-        <v>66.5</v>
+        <v>67.8</v>
       </c>
       <c r="C57" s="35" t="n">
-        <v>65.2</v>
+        <v>68.2</v>
       </c>
       <c r="D57" s="35" t="n">
-        <v>67.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E57" s="35" t="n">
-        <v>68.7</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="35" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Texas State</t>
         </is>
       </c>
       <c r="B58" s="35" t="n">
-        <v>62.1</v>
+        <v>60.5</v>
       </c>
       <c r="C58" s="35" t="n">
-        <v>67.59999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="D58" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="E58" s="35" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="35" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B59" s="35" t="n">
-        <v>72.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="C59" s="35" t="n">
-        <v>69.5</v>
+        <v>65.2</v>
       </c>
       <c r="D59" s="35" t="n">
-        <v>68.5</v>
+        <v>67.7</v>
       </c>
       <c r="E59" s="35" t="n">
-        <v>68.5</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="35" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="B60" s="35" t="n">
-        <v>68.2</v>
+        <v>62.1</v>
       </c>
       <c r="C60" s="35" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="D60" s="35" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="D60" s="35" t="n">
-        <v>68.2</v>
-      </c>
       <c r="E60" s="35" t="n">
-        <v>68.2</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="35" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B61" s="35" t="n">
-        <v>72.2</v>
+        <v>68.2</v>
       </c>
       <c r="C61" s="35" t="n">
-        <v>69.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D61" s="35" t="n">
-        <v>69.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="E61" s="35" t="n">
-        <v>67.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="35" t="inlineStr">
         <is>
-          <t>Washington State</t>
+          <t>Navy</t>
         </is>
       </c>
       <c r="B62" s="35" t="n">
-        <v>66.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C62" s="35" t="n">
-        <v>63.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D62" s="35" t="n">
-        <v>67.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E62" s="35" t="n">
         <v>67.8</v>
@@ -18544,267 +18544,267 @@
     <row r="66">
       <c r="A66" s="35" t="inlineStr">
         <is>
-          <t>Rutgers</t>
+          <t>Washington State</t>
         </is>
       </c>
       <c r="B66" s="35" t="n">
-        <v>61.1</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="C66" s="35" t="n">
-        <v>62</v>
+        <v>63.7</v>
       </c>
       <c r="D66" s="35" t="n">
-        <v>62.1</v>
+        <v>67.8</v>
       </c>
       <c r="E66" s="35" t="n">
-        <v>67.09999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="35" t="inlineStr">
         <is>
-          <t>Western Michigan</t>
+          <t>Rutgers</t>
         </is>
       </c>
       <c r="B67" s="35" t="n">
-        <v>68.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="C67" s="35" t="n">
-        <v>71.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="D67" s="35" t="n">
-        <v>69.3</v>
+        <v>62.1</v>
       </c>
       <c r="E67" s="35" t="n">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="35" t="inlineStr">
         <is>
-          <t>Michigan State</t>
+          <t>Western Michigan</t>
         </is>
       </c>
       <c r="B68" s="35" t="n">
-        <v>66</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C68" s="35" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="D68" s="35" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="E68" s="35" t="n">
         <v>66.90000000000001</v>
-      </c>
-      <c r="D68" s="35" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E68" s="35" t="n">
-        <v>66.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="B69" s="35" t="n">
-        <v>58.2</v>
+        <v>66</v>
       </c>
       <c r="C69" s="35" t="n">
-        <v>63.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D69" s="35" t="n">
-        <v>66.3</v>
+        <v>67.5</v>
       </c>
       <c r="E69" s="35" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="B70" s="35" t="n">
-        <v>65.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C70" s="35" t="n">
-        <v>65.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="D70" s="35" t="n">
-        <v>65.7</v>
+        <v>68.5</v>
       </c>
       <c r="E70" s="35" t="n">
-        <v>65.7</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="inlineStr">
         <is>
-          <t>UTSA</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B71" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="C71" s="35" t="n">
-        <v>66.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D71" s="35" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E71" s="35" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B72" s="35" t="n">
-        <v>62.3</v>
+        <v>65.7</v>
       </c>
       <c r="C72" s="35" t="n">
-        <v>63</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D72" s="35" t="n">
-        <v>63</v>
+        <v>65.7</v>
       </c>
       <c r="E72" s="35" t="n">
-        <v>65.09999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="35" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>UTSA</t>
         </is>
       </c>
       <c r="B73" s="35" t="n">
-        <v>63.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C73" s="35" t="n">
-        <v>67.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D73" s="35" t="n">
-        <v>64.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="E73" s="35" t="n">
-        <v>64.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="B74" s="35" t="n">
-        <v>61.3</v>
+        <v>62.3</v>
       </c>
       <c r="C74" s="35" t="n">
-        <v>64.7</v>
+        <v>63</v>
       </c>
       <c r="D74" s="35" t="n">
-        <v>64.5</v>
+        <v>63</v>
       </c>
       <c r="E74" s="35" t="n">
-        <v>64.5</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="inlineStr">
         <is>
-          <t>Army</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="B75" s="35" t="n">
-        <v>64.5</v>
+        <v>61.3</v>
       </c>
       <c r="C75" s="35" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="D75" s="35" t="n">
         <v>64.5</v>
       </c>
       <c r="E75" s="35" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Army</t>
         </is>
       </c>
       <c r="B76" s="35" t="n">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="C76" s="35" t="n">
-        <v>68</v>
+        <v>64.5</v>
       </c>
       <c r="D76" s="35" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="E76" s="35" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="35" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B77" s="35" t="n">
-        <v>66.90000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="C77" s="35" t="n">
-        <v>65.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="D77" s="35" t="n">
-        <v>64</v>
+        <v>66.3</v>
       </c>
       <c r="E77" s="35" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="35" t="inlineStr">
         <is>
-          <t>Texas State</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="B78" s="35" t="n">
-        <v>60.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C78" s="35" t="n">
-        <v>60.7</v>
+        <v>68</v>
       </c>
       <c r="D78" s="35" t="n">
-        <v>63.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E78" s="35" t="n">
-        <v>63.2</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="35" t="inlineStr">
         <is>
-          <t>Tulane</t>
+          <t>Oklahoma State</t>
         </is>
       </c>
       <c r="B79" s="35" t="n">
-        <v>63.9</v>
+        <v>50.2</v>
       </c>
       <c r="C79" s="35" t="n">
-        <v>63.1</v>
+        <v>54.5</v>
       </c>
       <c r="D79" s="35" t="n">
-        <v>62.9</v>
+        <v>61.5</v>
       </c>
       <c r="E79" s="35" t="n">
-        <v>62.9</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="80">
@@ -18829,77 +18829,77 @@
     <row r="81">
       <c r="A81" s="35" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Utah State</t>
         </is>
       </c>
       <c r="B81" s="35" t="n">
-        <v>57.2</v>
+        <v>60.9</v>
       </c>
       <c r="C81" s="35" t="n">
-        <v>58</v>
+        <v>61.7</v>
       </c>
       <c r="D81" s="35" t="n">
-        <v>60.5</v>
+        <v>61</v>
       </c>
       <c r="E81" s="35" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="35" t="inlineStr">
         <is>
-          <t>Oklahoma State</t>
+          <t>Tulane</t>
         </is>
       </c>
       <c r="B82" s="35" t="n">
-        <v>50.2</v>
+        <v>63.9</v>
       </c>
       <c r="C82" s="35" t="n">
-        <v>54.5</v>
+        <v>63.1</v>
       </c>
       <c r="D82" s="35" t="n">
-        <v>61.5</v>
+        <v>62.9</v>
       </c>
       <c r="E82" s="35" t="n">
-        <v>61.5</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="B83" s="35" t="n">
-        <v>58.8</v>
+        <v>57.2</v>
       </c>
       <c r="C83" s="35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D83" s="35" t="n">
-        <v>58.2</v>
+        <v>60.5</v>
       </c>
       <c r="E83" s="35" t="n">
-        <v>61.3</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="inlineStr">
         <is>
-          <t>Utah State</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B84" s="35" t="n">
-        <v>60.9</v>
+        <v>58.8</v>
       </c>
       <c r="C84" s="35" t="n">
-        <v>61.7</v>
+        <v>59</v>
       </c>
       <c r="D84" s="35" t="n">
-        <v>61</v>
+        <v>58.2</v>
       </c>
       <c r="E84" s="35" t="n">
-        <v>61</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="85">
@@ -19038,20 +19038,20 @@
     <row r="92">
       <c r="A92" s="35" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Western Kentucky</t>
         </is>
       </c>
       <c r="B92" s="35" t="n">
-        <v>55.3</v>
+        <v>56.1</v>
       </c>
       <c r="C92" s="35" t="n">
-        <v>54.8</v>
+        <v>53.9</v>
       </c>
       <c r="D92" s="35" t="n">
-        <v>59.9</v>
+        <v>54.6</v>
       </c>
       <c r="E92" s="35" t="n">
-        <v>59.9</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="93">
@@ -19089,7 +19089,7 @@
         <v>59.1</v>
       </c>
       <c r="E94" s="35" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="95">
@@ -19165,45 +19165,45 @@
         <v>57.9</v>
       </c>
       <c r="E98" s="35" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="35" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="B99" s="35" t="n">
-        <v>57.3</v>
+        <v>55.3</v>
       </c>
       <c r="C99" s="35" t="n">
-        <v>54.5</v>
+        <v>54.8</v>
       </c>
       <c r="D99" s="35" t="n">
-        <v>57.1</v>
+        <v>59.9</v>
       </c>
       <c r="E99" s="35" t="n">
-        <v>57.2</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="35" t="inlineStr">
         <is>
-          <t>Central Michigan</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="B100" s="35" t="n">
-        <v>55</v>
+        <v>57.3</v>
       </c>
       <c r="C100" s="35" t="n">
-        <v>56.2</v>
+        <v>54.5</v>
       </c>
       <c r="D100" s="35" t="n">
         <v>57.1</v>
       </c>
       <c r="E100" s="35" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="101">
@@ -19228,33 +19228,33 @@
     <row r="102">
       <c r="A102" s="35" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B102" s="35" t="n">
-        <v>55.7</v>
+        <v>54.3</v>
       </c>
       <c r="C102" s="35" t="n">
-        <v>56.3</v>
+        <v>54.7</v>
       </c>
       <c r="D102" s="35" t="n">
-        <v>56.8</v>
+        <v>55.2</v>
       </c>
       <c r="E102" s="35" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="35" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="B103" s="35" t="n">
-        <v>53.1</v>
+        <v>55.7</v>
       </c>
       <c r="C103" s="35" t="n">
-        <v>55.9</v>
+        <v>56.3</v>
       </c>
       <c r="D103" s="35" t="n">
         <v>56.8</v>
@@ -19342,93 +19342,93 @@
     <row r="108">
       <c r="A108" s="35" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Florida Atlantic</t>
         </is>
       </c>
       <c r="B108" s="35" t="n">
-        <v>54.3</v>
+        <v>50.4</v>
       </c>
       <c r="C108" s="35" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="D108" s="35" t="n">
-        <v>55.2</v>
+        <v>54.2</v>
       </c>
       <c r="E108" s="35" t="n">
-        <v>55.2</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="35" t="inlineStr">
         <is>
-          <t>Missouri State</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B109" s="35" t="n">
-        <v>50.7</v>
+        <v>53.1</v>
       </c>
       <c r="C109" s="35" t="n">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="D109" s="35" t="n">
-        <v>54.7</v>
+        <v>56.8</v>
       </c>
       <c r="E109" s="35" t="n">
-        <v>54.7</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="35" t="inlineStr">
         <is>
-          <t>Western Kentucky</t>
+          <t>Central Michigan</t>
         </is>
       </c>
       <c r="B110" s="35" t="n">
-        <v>56.1</v>
+        <v>55</v>
       </c>
       <c r="C110" s="35" t="n">
-        <v>53.9</v>
+        <v>56.2</v>
       </c>
       <c r="D110" s="35" t="n">
-        <v>54.6</v>
+        <v>57.1</v>
       </c>
       <c r="E110" s="35" t="n">
-        <v>54.6</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="35" t="inlineStr">
         <is>
-          <t>Coastal Carolina</t>
+          <t>Missouri State</t>
         </is>
       </c>
       <c r="B111" s="35" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="C111" s="35" t="n">
-        <v>56.1</v>
+        <v>55.6</v>
       </c>
       <c r="D111" s="35" t="n">
-        <v>55.4</v>
+        <v>54.7</v>
       </c>
       <c r="E111" s="35" t="n">
-        <v>54.2</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="35" t="inlineStr">
         <is>
-          <t>Florida Atlantic</t>
+          <t>Coastal Carolina</t>
         </is>
       </c>
       <c r="B112" s="35" t="n">
-        <v>50.4</v>
+        <v>51</v>
       </c>
       <c r="C112" s="35" t="n">
-        <v>53.3</v>
+        <v>56.1</v>
       </c>
       <c r="D112" s="35" t="n">
-        <v>54.2</v>
+        <v>55.4</v>
       </c>
       <c r="E112" s="35" t="n">
         <v>54.2</v>
@@ -19545,7 +19545,7 @@
         <v>52.6</v>
       </c>
       <c r="E118" s="35" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="119">
@@ -19570,77 +19570,77 @@
     <row r="120">
       <c r="A120" s="35" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>App State</t>
         </is>
       </c>
       <c r="B120" s="35" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="C120" s="35" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="D120" s="35" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E120" s="35" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="35" t="inlineStr">
         <is>
-          <t>Georgia State</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B121" s="35" t="n">
-        <v>47.4</v>
+        <v>48.6</v>
       </c>
       <c r="C121" s="35" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="D121" s="35" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E121" s="35" t="n">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="35" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Georgia State</t>
         </is>
       </c>
       <c r="B122" s="35" t="n">
-        <v>51.5</v>
+        <v>47.4</v>
       </c>
       <c r="C122" s="35" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="D122" s="35" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="E122" s="35" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="35" t="inlineStr">
         <is>
-          <t>App State</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="B123" s="35" t="n">
-        <v>49.2</v>
+        <v>51.5</v>
       </c>
       <c r="C123" s="35" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="D123" s="35" t="n">
-        <v>51</v>
+        <v>49.8</v>
       </c>
       <c r="E123" s="35" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="124">
@@ -19659,7 +19659,7 @@
         <v>49.9</v>
       </c>
       <c r="E124" s="35" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125">
@@ -19855,77 +19855,77 @@
     <row r="135">
       <c r="A135" s="35" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Northern Illinois</t>
         </is>
       </c>
       <c r="B135" s="35" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
       <c r="C135" s="35" t="n">
-        <v>44.9</v>
+        <v>45.8</v>
       </c>
       <c r="D135" s="35" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="E135" s="35" t="n">
-        <v>45</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="35" t="inlineStr">
         <is>
-          <t>UL Monroe</t>
+          <t>Ball State</t>
         </is>
       </c>
       <c r="B136" s="35" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="C136" s="35" t="n">
-        <v>43.3</v>
+        <v>47.5</v>
       </c>
       <c r="D136" s="35" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="E136" s="35" t="n">
-        <v>45</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="35" t="inlineStr">
         <is>
-          <t>Northern Illinois</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B137" s="35" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="C137" s="35" t="n">
-        <v>45.8</v>
+        <v>44.9</v>
       </c>
       <c r="D137" s="35" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="E137" s="35" t="n">
-        <v>44.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="35" t="inlineStr">
         <is>
-          <t>Ball State</t>
+          <t>UL Monroe</t>
         </is>
       </c>
       <c r="B138" s="35" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="C138" s="35" t="n">
-        <v>47.5</v>
+        <v>43.3</v>
       </c>
       <c r="D138" s="35" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="E138" s="35" t="n">
-        <v>43.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="139">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deene\Mountain Dub Handicapping\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E43BEDF-AE36-40AF-AEA3-18C866DD2CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BDA28C-B9EF-4C07-9B16-E533F78130FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6827,9 +6827,6 @@
       <c r="E57" t="s">
         <v>73</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
       <c r="G57">
         <v>116</v>
       </c>
@@ -12388,11 +12385,11 @@
     </row>
     <row r="450" spans="10:13" x14ac:dyDescent="0.35">
       <c r="J450" s="12" t="str">
-        <f t="shared" ref="J450:J513" si="14">IF(I450="","",I450-F450)</f>
+        <f t="shared" ref="J450:J500" si="14">IF(I450="","",I450-F450)</f>
         <v/>
       </c>
       <c r="L450" s="11">
-        <f t="shared" ref="L450:L513" si="15">IF(K450="W",IF(G450&lt;0,H450*100/ABS(G450),H450*G450/100),IF(K450="L",-H450,0))</f>
+        <f t="shared" ref="L450:L500" si="15">IF(K450="W",IF(G450&lt;0,H450*100/ABS(G450),H450*G450/100),IF(K450="L",-H450,0))</f>
         <v>0</v>
       </c>
       <c r="M450" s="11">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -938,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="C88" s="33" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D88" s="33" t="n">
         <v>83</v>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -862,3430 +862,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.5" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B1" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D1" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E1" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F1" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G1" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H1" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I1" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J1" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K1" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L1" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M1" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N1" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O1" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P1" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q1" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B2" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C2" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D2" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E2" s="35" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="F2" s="35" t="inlineStr">
-        <is>
-          <t>Virginia Tech</t>
-        </is>
-      </c>
-      <c r="G2" s="35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H2" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I2" s="40" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="J2" s="35" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="K2" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="35" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M2" s="35" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="N2" s="40" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="O2" s="35" t="n"/>
-      <c r="P2" s="35" t="n"/>
-      <c r="Q2" s="35" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C3" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D3" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E3" s="35" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="F3" s="35" t="inlineStr">
-        <is>
-          <t>Clemson</t>
-        </is>
-      </c>
-      <c r="G3" s="35" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="H3" s="35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I3" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J3" s="35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K3" s="35" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="L3" s="35" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="M3" s="35" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="N3" s="35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O3" s="35" t="n"/>
-      <c r="P3" s="35" t="n"/>
-      <c r="Q3" s="35" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C4" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D4" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E4" s="35" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="F4" s="35" t="inlineStr">
-        <is>
-          <t>Florida State</t>
-        </is>
-      </c>
-      <c r="G4" s="35" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H4" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I4" s="40" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J4" s="35" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="K4" s="35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L4" s="35" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="M4" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N4" s="35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O4" s="35" t="n"/>
-      <c r="P4" s="35" t="n"/>
-      <c r="Q4" s="35" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C5" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E5" s="35" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="F5" s="35" t="inlineStr">
-        <is>
-          <t>NC State</t>
-        </is>
-      </c>
-      <c r="G5" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H5" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I5" s="40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J5" s="35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K5" s="35" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="L5" s="35" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M5" s="35" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="N5" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O5" s="35" t="n"/>
-      <c r="P5" s="35" t="n"/>
-      <c r="Q5" s="35" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C6" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D6" s="35" t="inlineStr">
-        <is>
-          <t>FBS Independents</t>
-        </is>
-      </c>
-      <c r="E6" s="35" t="inlineStr">
-        <is>
-          <t>Notre Dame</t>
-        </is>
-      </c>
-      <c r="F6" s="35" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
-        </is>
-      </c>
-      <c r="G6" s="35" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H6" s="35" t="n">
-        <v>21</v>
-      </c>
-      <c r="I6" s="40" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="J6" s="35" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K6" s="35" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L6" s="35" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="M6" s="35" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N6" s="35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O6" s="35" t="n"/>
-      <c r="P6" s="35" t="n"/>
-      <c r="Q6" s="35" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E7" s="35" t="inlineStr">
-        <is>
-          <t>Boston College</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="inlineStr">
-        <is>
-          <t>SMU</t>
-        </is>
-      </c>
-      <c r="G7" s="35" t="n">
-        <v>-23.1</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>-21</v>
-      </c>
-      <c r="I7" s="40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J7" s="35" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="K7" s="35" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L7" s="35" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="M7" s="35" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="N7" s="40" t="n">
-        <v>-7</v>
-      </c>
-      <c r="O7" s="35" t="n"/>
-      <c r="P7" s="35" t="n"/>
-      <c r="Q7" s="35" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D8" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="inlineStr">
-        <is>
-          <t>Stanford</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="inlineStr">
-        <is>
-          <t>Wake Forest</t>
-        </is>
-      </c>
-      <c r="G8" s="35" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="H8" s="35" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="35" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="K8" s="35" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="L8" s="35" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="M8" s="35" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N8" s="40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O8" s="35" t="n"/>
-      <c r="P8" s="35" t="n"/>
-      <c r="Q8" s="35" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E9" s="35" t="inlineStr">
-        <is>
-          <t>North Texas</t>
-        </is>
-      </c>
-      <c r="F9" s="35" t="inlineStr">
-        <is>
-          <t>Tulsa</t>
-        </is>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="I9" s="40" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="J9" s="35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K9" s="35" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L9" s="35" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="M9" s="35" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="N9" s="35" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="O9" s="35" t="n"/>
-      <c r="P9" s="35" t="n"/>
-      <c r="Q9" s="35" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C10" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D10" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E10" s="35" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="F10" s="35" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="G10" s="35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H10" s="35" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="I10" s="40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J10" s="35" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K10" s="35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L10" s="35" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="M10" s="35" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N10" s="35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O10" s="35" t="n"/>
-      <c r="P10" s="35" t="n"/>
-      <c r="Q10" s="35" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="inlineStr">
-        <is>
-          <t>SWAC</t>
-        </is>
-      </c>
-      <c r="E11" s="35" t="inlineStr">
-        <is>
-          <t>Texas Southern</t>
-        </is>
-      </c>
-      <c r="F11" s="35" t="inlineStr">
-        <is>
-          <t>Florida Atlantic</t>
-        </is>
-      </c>
-      <c r="G11" s="35" t="n">
-        <v>-31.3</v>
-      </c>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
-      <c r="J11" s="35" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="K11" s="35" t="n">
-        <v>-21.1</v>
-      </c>
-      <c r="L11" s="35" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="M11" s="35" t="n"/>
-      <c r="N11" s="35" t="n"/>
-      <c r="O11" s="35" t="n"/>
-      <c r="P11" s="35" t="n"/>
-      <c r="Q11" s="35" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C12" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E12" s="35" t="inlineStr">
-        <is>
-          <t>UTSA</t>
-        </is>
-      </c>
-      <c r="F12" s="35" t="inlineStr">
-        <is>
-          <t>Rice</t>
-        </is>
-      </c>
-      <c r="G12" s="35" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H12" s="35" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I12" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="J12" s="35" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K12" s="35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L12" s="35" t="n">
-        <v>55</v>
-      </c>
-      <c r="M12" s="35" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N12" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O12" s="35" t="n"/>
-      <c r="P12" s="35" t="n"/>
-      <c r="Q12" s="35" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E13" s="35" t="inlineStr">
-        <is>
-          <t>Temple</t>
-        </is>
-      </c>
-      <c r="F13" s="35" t="inlineStr">
-        <is>
-          <t>South Florida</t>
-        </is>
-      </c>
-      <c r="G13" s="35" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I13" s="40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J13" s="35" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="K13" s="35" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="L13" s="35" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="M13" s="35" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="N13" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="O13" s="35" t="n"/>
-      <c r="P13" s="35" t="n"/>
-      <c r="Q13" s="35" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="inlineStr">
-        <is>
-          <t>Southern</t>
-        </is>
-      </c>
-      <c r="E14" s="35" t="inlineStr">
-        <is>
-          <t>Samford</t>
-        </is>
-      </c>
-      <c r="F14" s="35" t="inlineStr">
-        <is>
-          <t>UAB</t>
-        </is>
-      </c>
-      <c r="G14" s="35" t="n">
-        <v>-32.3</v>
-      </c>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="K14" s="35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L14" s="35" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="M14" s="35" t="n"/>
-      <c r="N14" s="35" t="n"/>
-      <c r="O14" s="35" t="n"/>
-      <c r="P14" s="35" t="n"/>
-      <c r="Q14" s="35" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="inlineStr">
-        <is>
-          <t>Texas Tech</t>
-        </is>
-      </c>
-      <c r="F15" s="35" t="inlineStr">
-        <is>
-          <t>Colorado</t>
-        </is>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" s="40" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J15" s="35" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="K15" s="35" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L15" s="35" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="M15" s="35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N15" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O15" s="35" t="n"/>
-      <c r="P15" s="35" t="n"/>
-      <c r="Q15" s="35" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>UCF</t>
-        </is>
-      </c>
-      <c r="F16" s="35" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="G16" s="35" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="H16" s="35" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="I16" s="35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J16" s="35" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="K16" s="35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L16" s="35" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="M16" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N16" s="40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O16" s="35" t="n"/>
-      <c r="P16" s="35" t="n"/>
-      <c r="Q16" s="35" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E17" s="35" t="inlineStr">
-        <is>
-          <t>West Virginia</t>
-        </is>
-      </c>
-      <c r="F17" s="35" t="inlineStr">
-        <is>
-          <t>Iowa State</t>
-        </is>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I17" s="40" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J17" s="35" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="K17" s="35" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="L17" s="35" t="n">
-        <v>49</v>
-      </c>
-      <c r="M17" s="35" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N17" s="40" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="O17" s="35" t="n"/>
-      <c r="P17" s="35" t="n"/>
-      <c r="Q17" s="35" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D18" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="E18" s="35" t="inlineStr">
-        <is>
-          <t>Middle Tennessee</t>
-        </is>
-      </c>
-      <c r="F18" s="35" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="G18" s="35" t="n">
-        <v>-21.2</v>
-      </c>
-      <c r="H18" s="35" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="I18" s="40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J18" s="35" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="K18" s="35" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="L18" s="35" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="M18" s="35" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="N18" s="40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O18" s="35" t="n"/>
-      <c r="P18" s="35" t="n"/>
-      <c r="Q18" s="35" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>BYU</t>
-        </is>
-      </c>
-      <c r="F19" s="35" t="inlineStr">
-        <is>
-          <t>TCU</t>
-        </is>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I19" s="40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K19" s="35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="L19" s="35" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="M19" s="35" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N19" s="40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O19" s="35" t="n"/>
-      <c r="P19" s="35" t="n"/>
-      <c r="Q19" s="35" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D20" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E20" s="35" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="F20" s="35" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="G20" s="35" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="H20" s="35" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I20" s="35" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J20" s="35" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K20" s="35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L20" s="35" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="M20" s="35" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="N20" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O20" s="35" t="n"/>
-      <c r="P20" s="35" t="n"/>
-      <c r="Q20" s="35" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>Baylor</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="inlineStr">
-        <is>
-          <t>Arizona State</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I21" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="L21" s="35" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="M21" s="35" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="N21" s="40" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O21" s="35" t="n"/>
-      <c r="P21" s="35" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>Purdue</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>Illinois</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I22" s="40" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="M22" s="35" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="N22" s="35" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>Ohio State</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N23" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="L24" s="35" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="M24" s="35" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="N24" s="35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="L25" s="35" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="M25" s="35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="N25" s="35" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="35" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Penn State</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>Northwestern</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I26" s="35" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K26" s="35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L26" s="35" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="M26" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N26" s="40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="35" t="n"/>
-      <c r="Q26" s="35" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>USC</t>
-        </is>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="I27" s="40" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="K27" s="35" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="L27" s="35" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="M27" s="35" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="N27" s="40" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="O27" s="35" t="n"/>
-      <c r="P27" s="35" t="n"/>
-      <c r="Q27" s="35" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C28" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D28" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="inlineStr">
-        <is>
-          <t>Michigan State</t>
-        </is>
-      </c>
-      <c r="F28" s="35" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="G28" s="35" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="H28" s="35" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I28" s="40" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J28" s="35" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="K28" s="35" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="L28" s="35" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="M28" s="35" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="N28" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O28" s="35" t="n"/>
-      <c r="P28" s="35" t="n"/>
-      <c r="Q28" s="35" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D29" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="F29" s="35" t="inlineStr">
-        <is>
-          <t>Rutgers</t>
-        </is>
-      </c>
-      <c r="G29" s="35" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I29" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J29" s="35" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="K29" s="35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L29" s="35" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="M29" s="35" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N29" s="40" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="O29" s="35" t="n"/>
-      <c r="P29" s="35" t="n"/>
-      <c r="Q29" s="35" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="D30" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="inlineStr">
-        <is>
-          <t>Liberty</t>
-        </is>
-      </c>
-      <c r="F30" s="35" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-      <c r="G30" s="35" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="I30" s="40" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J30" s="35" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="K30" s="35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L30" s="35" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="M30" s="35" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="N30" s="35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O30" s="35" t="n"/>
-      <c r="P30" s="35" t="n"/>
-      <c r="Q30" s="35" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="D31" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="E31" s="35" t="inlineStr">
-        <is>
-          <t>Western Kentucky</t>
-        </is>
-      </c>
-      <c r="F31" s="35" t="inlineStr">
-        <is>
-          <t>New Mexico State</t>
-        </is>
-      </c>
-      <c r="G31" s="35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H31" s="35" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I31" s="40" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J31" s="35" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K31" s="35" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L31" s="35" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="M31" s="35" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="N31" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="O31" s="35" t="n"/>
-      <c r="P31" s="35" t="n"/>
-      <c r="Q31" s="35" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
-        <is>
-          <t>FBS Independents</t>
-        </is>
-      </c>
-      <c r="D32" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E32" s="35" t="inlineStr">
-        <is>
-          <t>Syracuse</t>
-        </is>
-      </c>
-      <c r="F32" s="35" t="inlineStr">
-        <is>
-          <t>UConn</t>
-        </is>
-      </c>
-      <c r="G32" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="H32" s="35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I32" s="40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J32" s="35" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="K32" s="35" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L32" s="35" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="M32" s="35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N32" s="40" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O32" s="35" t="n"/>
-      <c r="P32" s="35" t="n"/>
-      <c r="Q32" s="35" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D33" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E33" s="35" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="F33" s="35" t="inlineStr">
-        <is>
-          <t>Ball State</t>
-        </is>
-      </c>
-      <c r="G33" s="35" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H33" s="35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I33" s="35" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J33" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="K33" s="35" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="L33" s="35" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="M33" s="35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="N33" s="35" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="O33" s="35" t="n"/>
-      <c r="P33" s="35" t="n"/>
-      <c r="Q33" s="35" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D34" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E34" s="35" t="inlineStr">
-        <is>
-          <t>Western Michigan</t>
-        </is>
-      </c>
-      <c r="F34" s="35" t="inlineStr">
-        <is>
-          <t>Buffalo</t>
-        </is>
-      </c>
-      <c r="G34" s="35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H34" s="35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I34" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="35" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K34" s="35" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="L34" s="35" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="M34" s="35" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="N34" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O34" s="35" t="n"/>
-      <c r="P34" s="35" t="n"/>
-      <c r="Q34" s="35" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D35" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E35" s="35" t="inlineStr">
-        <is>
-          <t>Akron</t>
-        </is>
-      </c>
-      <c r="F35" s="35" t="inlineStr">
-        <is>
-          <t>Central Michigan</t>
-        </is>
-      </c>
-      <c r="G35" s="35" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="H35" s="35" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I35" s="40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J35" s="35" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="K35" s="35" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="L35" s="35" t="n">
-        <v>47</v>
-      </c>
-      <c r="M35" s="35" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="N35" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O35" s="35" t="n"/>
-      <c r="P35" s="35" t="n"/>
-      <c r="Q35" s="35" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D36" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E36" s="35" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="F36" s="35" t="inlineStr">
-        <is>
-          <t>Kent State</t>
-        </is>
-      </c>
-      <c r="G36" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="H36" s="35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I36" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="J36" s="35" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="K36" s="35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L36" s="35" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M36" s="35" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="N36" s="40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O36" s="35" t="n"/>
-      <c r="P36" s="35" t="n"/>
-      <c r="Q36" s="35" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D37" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E37" s="35" t="inlineStr">
-        <is>
-          <t>Eastern Michigan</t>
-        </is>
-      </c>
-      <c r="F37" s="35" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-      <c r="G37" s="35" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="H37" s="35" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="I37" s="40" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="J37" s="35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K37" s="35" t="n">
-        <v>-24.6</v>
-      </c>
-      <c r="L37" s="35" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="M37" s="35" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="N37" s="35" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O37" s="35" t="n"/>
-      <c r="P37" s="35" t="n"/>
-      <c r="Q37" s="35" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D38" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E38" s="35" t="inlineStr">
-        <is>
-          <t>Bowling Green</t>
-        </is>
-      </c>
-      <c r="F38" s="35" t="inlineStr">
-        <is>
-          <t>Miami (OH)</t>
-        </is>
-      </c>
-      <c r="G38" s="35" t="n">
-        <v>-20</v>
-      </c>
-      <c r="H38" s="35" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="I38" s="40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J38" s="35" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="K38" s="35" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="L38" s="35" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="M38" s="35" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="N38" s="40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O38" s="35" t="n"/>
-      <c r="P38" s="35" t="n"/>
-      <c r="Q38" s="35" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D39" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E39" s="35" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="F39" s="35" t="inlineStr">
-        <is>
-          <t>Air Force</t>
-        </is>
-      </c>
-      <c r="G39" s="35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H39" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I39" s="40" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="J39" s="35" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="K39" s="35" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="L39" s="35" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="M39" s="35" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="N39" s="40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O39" s="35" t="n"/>
-      <c r="P39" s="35" t="n"/>
-      <c r="Q39" s="35" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D40" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="E40" s="35" t="inlineStr">
-        <is>
-          <t>UTEP</t>
-        </is>
-      </c>
-      <c r="F40" s="35" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-      <c r="G40" s="35" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="H40" s="35" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="I40" s="40" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J40" s="35" t="n">
-        <v>-22.1</v>
-      </c>
-      <c r="K40" s="35" t="n">
-        <v>-28.2</v>
-      </c>
-      <c r="L40" s="35" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="M40" s="35" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="N40" s="40" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="O40" s="35" t="n"/>
-      <c r="P40" s="35" t="n"/>
-      <c r="Q40" s="35" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D41" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="E41" s="35" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="F41" s="35" t="inlineStr">
-        <is>
-          <t>North Dakota State</t>
-        </is>
-      </c>
-      <c r="G41" s="35" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="H41" s="35" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="I41" s="40" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J41" s="35" t="n">
-        <v>-22</v>
-      </c>
-      <c r="K41" s="35" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="L41" s="35" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="M41" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N41" s="35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O41" s="35" t="n"/>
-      <c r="P41" s="35" t="n"/>
-      <c r="Q41" s="35" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D42" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E42" s="35" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F42" s="35" t="inlineStr">
-        <is>
-          <t>UNLV</t>
-        </is>
-      </c>
-      <c r="G42" s="35" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="H42" s="35" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="I42" s="40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J42" s="35" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="K42" s="35" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="L42" s="35" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="M42" s="35" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="N42" s="40" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="O42" s="35" t="n"/>
-      <c r="P42" s="35" t="n"/>
-      <c r="Q42" s="35" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B43" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D43" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="E43" s="35" t="inlineStr">
-        <is>
-          <t>San José State</t>
-        </is>
-      </c>
-      <c r="F43" s="35" t="inlineStr">
-        <is>
-          <t>Hawai'i</t>
-        </is>
-      </c>
-      <c r="G43" s="35" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="H43" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I43" s="40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J43" s="35" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="K43" s="35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L43" s="35" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="M43" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N43" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O43" s="35" t="n"/>
-      <c r="P43" s="35" t="n"/>
-      <c r="Q43" s="35" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C44" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D44" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E44" s="35" t="inlineStr">
-        <is>
-          <t>Utah State</t>
-        </is>
-      </c>
-      <c r="F44" s="35" t="inlineStr">
-        <is>
-          <t>Boise State</t>
-        </is>
-      </c>
-      <c r="G44" s="35" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="H44" s="35" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="I44" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="J44" s="35" t="n">
-        <v>-18.4</v>
-      </c>
-      <c r="K44" s="35" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="L44" s="35" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="M44" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N44" s="40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O44" s="35" t="n"/>
-      <c r="P44" s="35" t="n"/>
-      <c r="Q44" s="35" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C45" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D45" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E45" s="35" t="inlineStr">
-        <is>
-          <t>Oregon State</t>
-        </is>
-      </c>
-      <c r="F45" s="35" t="inlineStr">
-        <is>
-          <t>Colorado State</t>
-        </is>
-      </c>
-      <c r="G45" s="35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H45" s="35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I45" s="40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J45" s="35" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="K45" s="35" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L45" s="35" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="M45" s="35" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="N45" s="40" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="O45" s="35" t="n"/>
-      <c r="P45" s="35" t="n"/>
-      <c r="Q45" s="35" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C46" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D46" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E46" s="35" t="inlineStr">
-        <is>
-          <t>Texas State</t>
-        </is>
-      </c>
-      <c r="F46" s="35" t="inlineStr">
-        <is>
-          <t>San Diego State</t>
-        </is>
-      </c>
-      <c r="G46" s="35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H46" s="35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I46" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J46" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K46" s="35" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="L46" s="35" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="M46" s="35" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="N46" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="O46" s="35" t="n"/>
-      <c r="P46" s="35" t="n"/>
-      <c r="Q46" s="35" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B47" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C47" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D47" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E47" s="35" t="inlineStr">
-        <is>
-          <t>Fresno State</t>
-        </is>
-      </c>
-      <c r="F47" s="35" t="inlineStr">
-        <is>
-          <t>Washington State</t>
-        </is>
-      </c>
-      <c r="G47" s="35" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="H47" s="35" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I47" s="40" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J47" s="35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K47" s="35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L47" s="35" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="M47" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N47" s="40" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="O47" s="35" t="n"/>
-      <c r="P47" s="35" t="n"/>
-      <c r="Q47" s="35" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B48" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C48" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D48" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E48" s="35" t="inlineStr">
-        <is>
-          <t>Vanderbilt</t>
-        </is>
-      </c>
-      <c r="F48" s="35" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
-      <c r="G48" s="35" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="H48" s="35" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I48" s="40" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="J48" s="35" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="K48" s="35" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="L48" s="35" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="M48" s="35" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="N48" s="40" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="O48" s="35" t="n"/>
-      <c r="P48" s="35" t="n"/>
-      <c r="Q48" s="35" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B49" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C49" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D49" s="35" t="inlineStr">
-        <is>
-          <t>Southland</t>
-        </is>
-      </c>
-      <c r="E49" s="35" t="inlineStr">
-        <is>
-          <t>McNeese</t>
-        </is>
-      </c>
-      <c r="F49" s="35" t="inlineStr">
-        <is>
-          <t>LSU</t>
-        </is>
-      </c>
-      <c r="G49" s="35" t="n">
-        <v>-61.5</v>
-      </c>
-      <c r="H49" s="35" t="n"/>
-      <c r="I49" s="35" t="n"/>
-      <c r="J49" s="35" t="n">
-        <v>-40.8</v>
-      </c>
-      <c r="K49" s="35" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="L49" s="35" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="M49" s="35" t="n"/>
-      <c r="N49" s="35" t="n"/>
-      <c r="O49" s="35" t="n"/>
-      <c r="P49" s="35" t="n"/>
-      <c r="Q49" s="35" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B50" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C50" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D50" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E50" s="35" t="inlineStr">
-        <is>
-          <t>Alabama</t>
-        </is>
-      </c>
-      <c r="F50" s="35" t="inlineStr">
-        <is>
-          <t>Mississippi State</t>
-        </is>
-      </c>
-      <c r="G50" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="H50" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="I50" s="40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J50" s="35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="K50" s="35" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L50" s="35" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="M50" s="35" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="N50" s="40" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="O50" s="35" t="n"/>
-      <c r="P50" s="35" t="n"/>
-      <c r="Q50" s="35" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B51" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C51" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D51" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E51" s="35" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="F51" s="35" t="inlineStr">
-        <is>
-          <t>Missouri</t>
-        </is>
-      </c>
-      <c r="G51" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H51" s="35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I51" s="40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J51" s="35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K51" s="35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L51" s="35" t="n">
-        <v>51</v>
-      </c>
-      <c r="M51" s="35" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="N51" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="O51" s="35" t="n"/>
-      <c r="P51" s="35" t="n"/>
-      <c r="Q51" s="35" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B52" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C52" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D52" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E52" s="35" t="inlineStr">
-        <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="F52" s="35" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
-        </is>
-      </c>
-      <c r="G52" s="35" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="H52" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I52" s="40" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J52" s="35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K52" s="35" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="L52" s="35" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="M52" s="35" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N52" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="O52" s="35" t="n"/>
-      <c r="P52" s="35" t="n"/>
-      <c r="Q52" s="35" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B53" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C53" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D53" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E53" s="35" t="inlineStr">
-        <is>
-          <t>Auburn</t>
-        </is>
-      </c>
-      <c r="F53" s="35" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-      <c r="G53" s="35" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="H53" s="35" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I53" s="40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J53" s="35" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="K53" s="35" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L53" s="35" t="n">
-        <v>48</v>
-      </c>
-      <c r="M53" s="35" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N53" s="40" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="O53" s="35" t="n"/>
-      <c r="P53" s="35" t="n"/>
-      <c r="Q53" s="35" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B54" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C54" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D54" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E54" s="35" t="inlineStr">
-        <is>
-          <t>Arkansas</t>
-        </is>
-      </c>
-      <c r="F54" s="35" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M</t>
-        </is>
-      </c>
-      <c r="G54" s="35" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="H54" s="35" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I54" s="40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J54" s="35" t="n">
-        <v>-17</v>
-      </c>
-      <c r="K54" s="35" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="L54" s="35" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="M54" s="35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N54" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O54" s="35" t="n"/>
-      <c r="P54" s="35" t="n"/>
-      <c r="Q54" s="35" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B55" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C55" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D55" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E55" s="35" t="inlineStr">
-        <is>
-          <t>Georgia Southern</t>
-        </is>
-      </c>
-      <c r="F55" s="35" t="inlineStr">
-        <is>
-          <t>Coastal Carolina</t>
-        </is>
-      </c>
-      <c r="G55" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H55" s="35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I55" s="40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J55" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K55" s="35" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="L55" s="35" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="M55" s="35" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N55" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O55" s="35" t="n"/>
-      <c r="P55" s="35" t="n"/>
-      <c r="Q55" s="35" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B56" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C56" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D56" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E56" s="35" t="inlineStr">
-        <is>
-          <t>Old Dominion</t>
-        </is>
-      </c>
-      <c r="F56" s="35" t="inlineStr">
-        <is>
-          <t>Georgia State</t>
-        </is>
-      </c>
-      <c r="G56" s="35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H56" s="35" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="I56" s="40" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="J56" s="35" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="K56" s="35" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="L56" s="35" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="M56" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N56" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O56" s="35" t="n"/>
-      <c r="P56" s="35" t="n"/>
-      <c r="Q56" s="35" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B57" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C57" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D57" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E57" s="35" t="inlineStr">
-        <is>
-          <t>Marshall</t>
-        </is>
-      </c>
-      <c r="F57" s="35" t="inlineStr">
-        <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="G57" s="35" t="n">
-        <v>-28.8</v>
-      </c>
-      <c r="H57" s="35" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="I57" s="40" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J57" s="35" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="K57" s="35" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="L57" s="35" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="M57" s="35" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="N57" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O57" s="35" t="n"/>
-      <c r="P57" s="35" t="n"/>
-      <c r="Q57" s="35" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B58" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C58" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D58" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E58" s="35" t="inlineStr">
-        <is>
-          <t>Army</t>
-        </is>
-      </c>
-      <c r="F58" s="35" t="inlineStr">
-        <is>
-          <t>Louisiana Tech</t>
-        </is>
-      </c>
-      <c r="G58" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H58" s="35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I58" s="35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J58" s="35" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="K58" s="35" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="L58" s="35" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M58" s="35" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N58" s="40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O58" s="35" t="n"/>
-      <c r="P58" s="35" t="n"/>
-      <c r="Q58" s="35" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B59" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C59" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D59" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E59" s="35" t="inlineStr">
-        <is>
-          <t>UL Monroe</t>
-        </is>
-      </c>
-      <c r="F59" s="35" t="inlineStr">
-        <is>
-          <t>South Alabama</t>
-        </is>
-      </c>
-      <c r="G59" s="35" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="H59" s="35" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I59" s="35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J59" s="35" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K59" s="35" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L59" s="35" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="M59" s="35" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="N59" s="35" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="O59" s="35" t="n"/>
-      <c r="P59" s="35" t="n"/>
-      <c r="Q59" s="35" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B60" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C60" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D60" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E60" s="35" t="inlineStr">
-        <is>
-          <t>Arkansas State</t>
-        </is>
-      </c>
-      <c r="F60" s="35" t="inlineStr">
-        <is>
-          <t>Louisiana</t>
-        </is>
-      </c>
-      <c r="G60" s="35" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="H60" s="35" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I60" s="40" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J60" s="35" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="K60" s="35" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="L60" s="35" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="M60" s="35" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N60" s="40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O60" s="35" t="n"/>
-      <c r="P60" s="35" t="n"/>
-      <c r="Q60" s="35" t="n"/>
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games found for season 2026, week 5.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q60"/>
@@ -4299,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4735,604 +1316,11 @@
       </c>
     </row>
     <row r="21" ht="26.5" customHeight="1">
-      <c r="A21" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C21" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D21" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E21" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F21" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G21" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H21" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I21" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J21" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K21" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L21" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M21" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N21" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O21" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P21" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q21" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>Virginia Tech</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I22" s="40" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M22" s="35" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="N22" s="40" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>Clemson</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I23" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="N23" s="35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>Florida State</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L24" s="35" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="M24" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N24" s="35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="inlineStr">
-        <is>
-          <t>NC State</t>
-        </is>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="L25" s="35" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M25" s="35" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="N25" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="35" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>FBS Independents</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Notre Dame</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>21</v>
-      </c>
-      <c r="I26" s="40" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K26" s="35" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L26" s="35" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="M26" s="35" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N26" s="35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="35" t="n"/>
-      <c r="Q26" s="35" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>Boston College</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>SMU</t>
-        </is>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>-23.1</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>-21</v>
-      </c>
-      <c r="I27" s="40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="K27" s="35" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L27" s="35" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="M27" s="35" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="N27" s="40" t="n">
-        <v>-7</v>
-      </c>
-      <c r="O27" s="35" t="n"/>
-      <c r="P27" s="35" t="n"/>
-      <c r="Q27" s="35" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C28" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D28" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="inlineStr">
-        <is>
-          <t>Stanford</t>
-        </is>
-      </c>
-      <c r="F28" s="35" t="inlineStr">
-        <is>
-          <t>Wake Forest</t>
-        </is>
-      </c>
-      <c r="G28" s="35" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="H28" s="35" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="I28" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="35" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="K28" s="35" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="L28" s="35" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="M28" s="35" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N28" s="40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O28" s="35" t="n"/>
-      <c r="P28" s="35" t="n"/>
-      <c r="Q28" s="35" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>FBS Independents</t>
-        </is>
-      </c>
-      <c r="D29" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
-        <is>
-          <t>Syracuse</t>
-        </is>
-      </c>
-      <c r="F29" s="35" t="inlineStr">
-        <is>
-          <t>UConn</t>
-        </is>
-      </c>
-      <c r="G29" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I29" s="40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J29" s="35" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="K29" s="35" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L29" s="35" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="M29" s="35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N29" s="40" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O29" s="35" t="n"/>
-      <c r="P29" s="35" t="n"/>
-      <c r="Q29" s="35" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D30" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F30" s="35" t="inlineStr">
-        <is>
-          <t>UNLV</t>
-        </is>
-      </c>
-      <c r="G30" s="35" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="I30" s="40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J30" s="35" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="K30" s="35" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="L30" s="35" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="M30" s="35" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="N30" s="40" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="O30" s="35" t="n"/>
-      <c r="P30" s="35" t="n"/>
-      <c r="Q30" s="35" t="n"/>
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve ACC.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A21:Q30"/>
@@ -5346,7 +1334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5700,531 +1688,11 @@
       </c>
     </row>
     <row r="18" ht="26.5" customHeight="1">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E18" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F18" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G18" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H18" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J18" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K18" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L18" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M18" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N18" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O18" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P18" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q18" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>North Texas</t>
-        </is>
-      </c>
-      <c r="F19" s="35" t="inlineStr">
-        <is>
-          <t>Tulsa</t>
-        </is>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="I19" s="40" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K19" s="35" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L19" s="35" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="M19" s="35" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="N19" s="35" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="O19" s="35" t="n"/>
-      <c r="P19" s="35" t="n"/>
-      <c r="Q19" s="35" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D20" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E20" s="35" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="F20" s="35" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="G20" s="35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H20" s="35" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="I20" s="40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J20" s="35" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K20" s="35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L20" s="35" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="M20" s="35" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N20" s="35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O20" s="35" t="n"/>
-      <c r="P20" s="35" t="n"/>
-      <c r="Q20" s="35" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="inlineStr">
-        <is>
-          <t>SWAC</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>Texas Southern</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="inlineStr">
-        <is>
-          <t>Florida Atlantic</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>-31.3</v>
-      </c>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
-      <c r="J21" s="35" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>-21.1</v>
-      </c>
-      <c r="L21" s="35" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="M21" s="35" t="n"/>
-      <c r="N21" s="35" t="n"/>
-      <c r="O21" s="35" t="n"/>
-      <c r="P21" s="35" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>UTSA</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>Rice</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I22" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>55</v>
-      </c>
-      <c r="M22" s="35" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N22" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>Temple</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>South Florida</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="N23" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>Southern</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Samford</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>UAB</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>-32.3</v>
-      </c>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="35" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L24" s="35" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="M24" s="35" t="n"/>
-      <c r="N24" s="35" t="n"/>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="inlineStr">
-        <is>
-          <t>Air Force</t>
-        </is>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="L25" s="35" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="M25" s="35" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="N25" s="40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="35" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Army</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>Louisiana Tech</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I26" s="35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="K26" s="35" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="L26" s="35" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M26" s="35" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N26" s="40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="35" t="n"/>
-      <c r="Q26" s="35" t="n"/>
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve American Athletic.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A18:Q26"/>
@@ -6238,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6652,490 +2120,11 @@
       </c>
     </row>
     <row r="20" ht="26.5" customHeight="1">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F20" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H20" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J20" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K20" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L20" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M20" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N20" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O20" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P20" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q20" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>Texas Tech</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="inlineStr">
-        <is>
-          <t>Colorado</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="I21" s="40" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L21" s="35" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="M21" s="35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N21" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O21" s="35" t="n"/>
-      <c r="P21" s="35" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>UCF</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="I22" s="35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="M22" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N22" s="40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>West Virginia</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>Iowa State</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>49</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N23" s="40" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Middle Tennessee</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>-21.2</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="L24" s="35" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="M24" s="35" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="N24" s="40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>BYU</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="inlineStr">
-        <is>
-          <t>TCU</t>
-        </is>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="L25" s="35" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="M25" s="35" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N25" s="40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="35" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I26" s="35" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K26" s="35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L26" s="35" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="M26" s="35" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="N26" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="35" t="n"/>
-      <c r="Q26" s="35" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>Baylor</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>Arizona State</t>
-        </is>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I27" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="K27" s="35" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="L27" s="35" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="M27" s="35" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="N27" s="40" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O27" s="35" t="n"/>
-      <c r="P27" s="35" t="n"/>
-      <c r="Q27" s="35" t="n"/>
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve Big 12.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A20:Q27"/>
@@ -7149,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7607,547 +2596,11 @@
       </c>
     </row>
     <row r="22" ht="26.5" customHeight="1">
-      <c r="A22" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E22" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F22" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G22" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H22" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I22" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J22" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K22" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L22" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M22" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N22" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O22" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P22" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q22" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>Purdue</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>Illinois</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="N23" s="35" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Ohio State</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L24" s="35" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="M24" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N24" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="inlineStr">
-        <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="L25" s="35" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="M25" s="35" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="N25" s="35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="35" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="I26" s="40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="K26" s="35" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="L26" s="35" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="M26" s="35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="N26" s="35" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="35" t="n"/>
-      <c r="Q26" s="35" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>Penn State</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>Northwestern</t>
-        </is>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I27" s="35" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K27" s="35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L27" s="35" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="M27" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N27" s="40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O27" s="35" t="n"/>
-      <c r="P27" s="35" t="n"/>
-      <c r="Q27" s="35" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C28" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D28" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="F28" s="35" t="inlineStr">
-        <is>
-          <t>USC</t>
-        </is>
-      </c>
-      <c r="G28" s="35" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="H28" s="35" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="I28" s="40" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="J28" s="35" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="K28" s="35" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="L28" s="35" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="M28" s="35" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="N28" s="40" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="O28" s="35" t="n"/>
-      <c r="P28" s="35" t="n"/>
-      <c r="Q28" s="35" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D29" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
-        <is>
-          <t>Michigan State</t>
-        </is>
-      </c>
-      <c r="F29" s="35" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="G29" s="35" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I29" s="40" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J29" s="35" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="K29" s="35" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="L29" s="35" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="M29" s="35" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="N29" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O29" s="35" t="n"/>
-      <c r="P29" s="35" t="n"/>
-      <c r="Q29" s="35" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="D30" s="35" t="inlineStr">
-        <is>
-          <t>Big Ten</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="F30" s="35" t="inlineStr">
-        <is>
-          <t>Rutgers</t>
-        </is>
-      </c>
-      <c r="G30" s="35" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I30" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J30" s="35" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="K30" s="35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L30" s="35" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="M30" s="35" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N30" s="40" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="O30" s="35" t="n"/>
-      <c r="P30" s="35" t="n"/>
-      <c r="Q30" s="35" t="n"/>
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve Big Ten.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A22:Q30"/>
@@ -8161,7 +2614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8427,262 +2880,11 @@
       </c>
     </row>
     <row r="14" ht="26.5" customHeight="1">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E14" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F14" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G14" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H14" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I14" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J14" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K14" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L14" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M14" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N14" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O14" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P14" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q14" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>Big 12</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="inlineStr">
-        <is>
-          <t>Middle Tennessee</t>
-        </is>
-      </c>
-      <c r="F15" s="35" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>-21.2</v>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="I15" s="40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J15" s="35" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="K15" s="35" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="L15" s="35" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="M15" s="35" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="N15" s="40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O15" s="35" t="n"/>
-      <c r="P15" s="35" t="n"/>
-      <c r="Q15" s="35" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>Liberty</t>
-        </is>
-      </c>
-      <c r="F16" s="35" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-      <c r="G16" s="35" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H16" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J16" s="35" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="K16" s="35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L16" s="35" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="M16" s="35" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="N16" s="35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O16" s="35" t="n"/>
-      <c r="P16" s="35" t="n"/>
-      <c r="Q16" s="35" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="inlineStr">
-        <is>
-          <t>Conference USA</t>
-        </is>
-      </c>
-      <c r="E17" s="35" t="inlineStr">
-        <is>
-          <t>Western Kentucky</t>
-        </is>
-      </c>
-      <c r="F17" s="35" t="inlineStr">
-        <is>
-          <t>New Mexico State</t>
-        </is>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I17" s="40" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J17" s="35" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K17" s="35" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L17" s="35" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="M17" s="35" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="N17" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="O17" s="35" t="n"/>
-      <c r="P17" s="35" t="n"/>
-      <c r="Q17" s="35" t="n"/>
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve Conference USA.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A14:Q17"/>
@@ -8696,7 +2898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8798,205 +3000,11 @@
       </c>
     </row>
     <row r="6" ht="26.5" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D6" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E6" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F6" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G6" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H6" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J6" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K6" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L6" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M6" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N6" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O6" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P6" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q6" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>FBS Independents</t>
-        </is>
-      </c>
-      <c r="E7" s="35" t="inlineStr">
-        <is>
-          <t>Notre Dame</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
-        </is>
-      </c>
-      <c r="G7" s="35" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>21</v>
-      </c>
-      <c r="I7" s="40" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="J7" s="35" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K7" s="35" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L7" s="35" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="M7" s="35" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N7" s="35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O7" s="35" t="n"/>
-      <c r="P7" s="35" t="n"/>
-      <c r="Q7" s="35" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="inlineStr">
-        <is>
-          <t>FBS Independents</t>
-        </is>
-      </c>
-      <c r="D8" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="inlineStr">
-        <is>
-          <t>Syracuse</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="inlineStr">
-        <is>
-          <t>UConn</t>
-        </is>
-      </c>
-      <c r="G8" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="H8" s="35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J8" s="35" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="K8" s="35" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L8" s="35" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="M8" s="35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N8" s="40" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O8" s="35" t="n"/>
-      <c r="P8" s="35" t="n"/>
-      <c r="Q8" s="35" t="n"/>
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve FBS Independents.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A6:Q8"/>
@@ -9010,7 +3018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9342,433 +3350,11 @@
       </c>
     </row>
     <row r="17" ht="26.5" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D17" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E17" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F17" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G17" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H17" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I17" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J17" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K17" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L17" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M17" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N17" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O17" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P17" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q17" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D18" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E18" s="35" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="F18" s="35" t="inlineStr">
-        <is>
-          <t>Ball State</t>
-        </is>
-      </c>
-      <c r="G18" s="35" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H18" s="35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I18" s="35" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J18" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="K18" s="35" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="L18" s="35" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="M18" s="35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="N18" s="35" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="O18" s="35" t="n"/>
-      <c r="P18" s="35" t="n"/>
-      <c r="Q18" s="35" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>Western Michigan</t>
-        </is>
-      </c>
-      <c r="F19" s="35" t="inlineStr">
-        <is>
-          <t>Buffalo</t>
-        </is>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I19" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K19" s="35" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="L19" s="35" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="M19" s="35" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="N19" s="35" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O19" s="35" t="n"/>
-      <c r="P19" s="35" t="n"/>
-      <c r="Q19" s="35" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D20" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E20" s="35" t="inlineStr">
-        <is>
-          <t>Akron</t>
-        </is>
-      </c>
-      <c r="F20" s="35" t="inlineStr">
-        <is>
-          <t>Central Michigan</t>
-        </is>
-      </c>
-      <c r="G20" s="35" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="H20" s="35" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I20" s="40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" s="35" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="K20" s="35" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="L20" s="35" t="n">
-        <v>47</v>
-      </c>
-      <c r="M20" s="35" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="N20" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O20" s="35" t="n"/>
-      <c r="P20" s="35" t="n"/>
-      <c r="Q20" s="35" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="inlineStr">
-        <is>
-          <t>Kent State</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I21" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L21" s="35" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M21" s="35" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="N21" s="40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O21" s="35" t="n"/>
-      <c r="P21" s="35" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>Eastern Michigan</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="I22" s="40" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>-24.6</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="M22" s="35" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="N22" s="35" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>Mid-American</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>Bowling Green</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>Miami (OH)</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>-20</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="N23" s="40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve Mid-American.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A17:Q23"/>
@@ -9782,7 +3368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10056,376 +3642,11 @@
       </c>
     </row>
     <row r="14" ht="26.5" customHeight="1">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E14" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F14" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G14" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H14" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I14" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J14" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K14" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L14" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M14" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N14" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O14" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P14" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q14" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="F15" s="35" t="inlineStr">
-        <is>
-          <t>Air Force</t>
-        </is>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I15" s="40" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="J15" s="35" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="K15" s="35" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="L15" s="35" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="M15" s="35" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="N15" s="40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O15" s="35" t="n"/>
-      <c r="P15" s="35" t="n"/>
-      <c r="Q15" s="35" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>UTEP</t>
-        </is>
-      </c>
-      <c r="F16" s="35" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-      <c r="G16" s="35" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="H16" s="35" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J16" s="35" t="n">
-        <v>-22.1</v>
-      </c>
-      <c r="K16" s="35" t="n">
-        <v>-28.2</v>
-      </c>
-      <c r="L16" s="35" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="M16" s="35" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="N16" s="40" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="O16" s="35" t="n"/>
-      <c r="P16" s="35" t="n"/>
-      <c r="Q16" s="35" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="E17" s="35" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="F17" s="35" t="inlineStr">
-        <is>
-          <t>North Dakota State</t>
-        </is>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="I17" s="40" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J17" s="35" t="n">
-        <v>-22</v>
-      </c>
-      <c r="K17" s="35" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="L17" s="35" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="M17" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N17" s="35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O17" s="35" t="n"/>
-      <c r="P17" s="35" t="n"/>
-      <c r="Q17" s="35" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D18" s="35" t="inlineStr">
-        <is>
-          <t>ACC</t>
-        </is>
-      </c>
-      <c r="E18" s="35" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F18" s="35" t="inlineStr">
-        <is>
-          <t>UNLV</t>
-        </is>
-      </c>
-      <c r="G18" s="35" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="H18" s="35" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="I18" s="40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J18" s="35" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="K18" s="35" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="L18" s="35" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="M18" s="35" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="N18" s="40" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="O18" s="35" t="n"/>
-      <c r="P18" s="35" t="n"/>
-      <c r="Q18" s="35" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>Mountain West</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>San José State</t>
-        </is>
-      </c>
-      <c r="F19" s="35" t="inlineStr">
-        <is>
-          <t>Hawai'i</t>
-        </is>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I19" s="40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="K19" s="35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L19" s="35" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="M19" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N19" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O19" s="35" t="n"/>
-      <c r="P19" s="35" t="n"/>
-      <c r="Q19" s="35" t="n"/>
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve Mountain West.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A14:Q19"/>
@@ -10439,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10661,319 +3882,11 @@
       </c>
     </row>
     <row r="12" ht="26.5" customHeight="1">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E12" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F12" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G12" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H12" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I12" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J12" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K12" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L12" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M12" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N12" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O12" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P12" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q12" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E13" s="35" t="inlineStr">
-        <is>
-          <t>Utah State</t>
-        </is>
-      </c>
-      <c r="F13" s="35" t="inlineStr">
-        <is>
-          <t>Boise State</t>
-        </is>
-      </c>
-      <c r="G13" s="35" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="I13" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="J13" s="35" t="n">
-        <v>-18.4</v>
-      </c>
-      <c r="K13" s="35" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="L13" s="35" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="M13" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N13" s="40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O13" s="35" t="n"/>
-      <c r="P13" s="35" t="n"/>
-      <c r="Q13" s="35" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E14" s="35" t="inlineStr">
-        <is>
-          <t>Oregon State</t>
-        </is>
-      </c>
-      <c r="F14" s="35" t="inlineStr">
-        <is>
-          <t>Colorado State</t>
-        </is>
-      </c>
-      <c r="G14" s="35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H14" s="35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I14" s="40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J14" s="35" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="K14" s="35" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L14" s="35" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="M14" s="35" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="N14" s="40" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="O14" s="35" t="n"/>
-      <c r="P14" s="35" t="n"/>
-      <c r="Q14" s="35" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="inlineStr">
-        <is>
-          <t>Texas State</t>
-        </is>
-      </c>
-      <c r="F15" s="35" t="inlineStr">
-        <is>
-          <t>San Diego State</t>
-        </is>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I15" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J15" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K15" s="35" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="L15" s="35" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="M15" s="35" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="N15" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="O15" s="35" t="n"/>
-      <c r="P15" s="35" t="n"/>
-      <c r="Q15" s="35" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>Pac-12</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>Fresno State</t>
-        </is>
-      </c>
-      <c r="F16" s="35" t="inlineStr">
-        <is>
-          <t>Washington State</t>
-        </is>
-      </c>
-      <c r="G16" s="35" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="H16" s="35" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J16" s="35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K16" s="35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L16" s="35" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="M16" s="35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N16" s="40" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="O16" s="35" t="n"/>
-      <c r="P16" s="35" t="n"/>
-      <c r="Q16" s="35" t="n"/>
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve Pac-12.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A12:Q16"/>
@@ -11091,7 +4004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11505,482 +4418,11 @@
       </c>
     </row>
     <row r="20" ht="26.5" customHeight="1">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F20" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H20" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J20" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K20" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L20" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M20" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N20" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O20" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P20" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q20" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>Vanderbilt</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I21" s="40" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="L21" s="35" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="M21" s="35" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="N21" s="40" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="O21" s="35" t="n"/>
-      <c r="P21" s="35" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>Southland</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>McNeese</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>LSU</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>-61.5</v>
-      </c>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="35" t="n"/>
-      <c r="J22" s="35" t="n">
-        <v>-40.8</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="M22" s="35" t="n"/>
-      <c r="N22" s="35" t="n"/>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>Alabama</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>Mississippi State</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="N23" s="40" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>Missouri</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L24" s="35" t="n">
-        <v>51</v>
-      </c>
-      <c r="M24" s="35" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="N24" s="40" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
-        </is>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="L25" s="35" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="M25" s="35" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N25" s="35" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="35" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Auburn</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I26" s="40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J26" s="35" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="K26" s="35" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L26" s="35" t="n">
-        <v>48</v>
-      </c>
-      <c r="M26" s="35" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N26" s="40" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="35" t="n"/>
-      <c r="Q26" s="35" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>Arkansas</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M</t>
-        </is>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I27" s="40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>-17</v>
-      </c>
-      <c r="K27" s="35" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="L27" s="35" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="M27" s="35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N27" s="35" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O27" s="35" t="n"/>
-      <c r="P27" s="35" t="n"/>
-      <c r="Q27" s="35" t="n"/>
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve SEC.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A20:Q27"/>
@@ -11994,7 +4436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12340,433 +4782,11 @@
       </c>
     </row>
     <row r="18" ht="26.5" customHeight="1">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>Home Conf</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>Away Conf</t>
-        </is>
-      </c>
-      <c r="E18" s="39" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="F18" s="39" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="G18" s="39" t="inlineStr">
-        <is>
-          <t>Model Line (Home)</t>
-        </is>
-      </c>
-      <c r="H18" s="39" t="inlineStr">
-        <is>
-          <t>Market Line (Home)</t>
-        </is>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>Spread Edge (pts)</t>
-        </is>
-      </c>
-      <c r="J18" s="39" t="inlineStr">
-        <is>
-          <t>Ridge Line (Home)</t>
-        </is>
-      </c>
-      <c r="K18" s="39" t="inlineStr">
-        <is>
-          <t>Massey Line (Home)</t>
-        </is>
-      </c>
-      <c r="L18" s="39" t="inlineStr">
-        <is>
-          <t>Model Total</t>
-        </is>
-      </c>
-      <c r="M18" s="39" t="inlineStr">
-        <is>
-          <t>Market Total</t>
-        </is>
-      </c>
-      <c r="N18" s="39" t="inlineStr">
-        <is>
-          <t>Total Edge (pts)</t>
-        </is>
-      </c>
-      <c r="O18" s="39" t="inlineStr">
-        <is>
-          <t>Away Pts</t>
-        </is>
-      </c>
-      <c r="P18" s="39" t="inlineStr">
-        <is>
-          <t>Home Pts</t>
-        </is>
-      </c>
-      <c r="Q18" s="39" t="inlineStr">
-        <is>
-          <t>Model Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>Georgia Southern</t>
-        </is>
-      </c>
-      <c r="F19" s="35" t="inlineStr">
-        <is>
-          <t>Coastal Carolina</t>
-        </is>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I19" s="40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K19" s="35" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="L19" s="35" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="M19" s="35" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N19" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O19" s="35" t="n"/>
-      <c r="P19" s="35" t="n"/>
-      <c r="Q19" s="35" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D20" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E20" s="35" t="inlineStr">
-        <is>
-          <t>Old Dominion</t>
-        </is>
-      </c>
-      <c r="F20" s="35" t="inlineStr">
-        <is>
-          <t>Georgia State</t>
-        </is>
-      </c>
-      <c r="G20" s="35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H20" s="35" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="I20" s="40" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="J20" s="35" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="K20" s="35" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="L20" s="35" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="M20" s="35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N20" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O20" s="35" t="n"/>
-      <c r="P20" s="35" t="n"/>
-      <c r="Q20" s="35" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>Marshall</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="inlineStr">
-        <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>-28.8</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="I21" s="40" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="L21" s="35" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="M21" s="35" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="N21" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O21" s="35" t="n"/>
-      <c r="P21" s="35" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>American Athletic</t>
-        </is>
-      </c>
-      <c r="E22" s="35" t="inlineStr">
-        <is>
-          <t>Army</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>Louisiana Tech</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I22" s="35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M22" s="35" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N22" s="40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>UL Monroe</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>South Alabama</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I23" s="35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="M23" s="35" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="N23" s="35" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
-        <is>
-          <t>Sun Belt</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Arkansas State</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>Louisiana</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J24" s="35" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="L24" s="35" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="M24" s="35" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N24" s="40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>No FBS games this week involve Sun Belt.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A18:Q24"/>
@@ -12923,7 +4943,7 @@
         <v>55.1</v>
       </c>
       <c r="J2" t="n">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -12967,7 +4987,7 @@
         <v>-30.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-18.5</v>
+        <v>-18.2</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -13023,7 +5043,7 @@
         <v>-5.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
@@ -13037,7 +5057,7 @@
         <v>45.6</v>
       </c>
       <c r="J4" t="n">
-        <v>52.8</v>
+        <v>53.5</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -13079,7 +5099,7 @@
         <v>-31.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-22.8</v>
+        <v>-22.5</v>
       </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
@@ -13093,7 +5113,7 @@
         <v>43.7</v>
       </c>
       <c r="J5" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="K5" s="6">
         <f>I5-J5</f>
@@ -23759,7 +15779,7 @@
         <v>93.8</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>93.8</v>
+        <v>94</v>
       </c>
       <c r="V3" s="35" t="inlineStr">
         <is>
@@ -23892,7 +15912,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="E8" s="35" t="n">
-        <v>85.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -24020,7 +16040,7 @@
         <v>84.5</v>
       </c>
       <c r="E14" s="35" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -24058,23 +16078,23 @@
         <v>78.90000000000001</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="B17" s="35" t="n">
-        <v>79.2</v>
+        <v>75.2</v>
       </c>
       <c r="C17" s="35" t="n">
-        <v>81.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D17" s="35" t="n">
-        <v>77.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="E17" s="35" t="n">
         <v>79.5</v>
@@ -24083,20 +16103,20 @@
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B18" s="35" t="n">
-        <v>75.2</v>
+        <v>79.2</v>
       </c>
       <c r="C18" s="35" t="n">
-        <v>76.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D18" s="35" t="n">
-        <v>76.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E18" s="35" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="19">
@@ -24216,96 +16236,96 @@
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="B25" s="35" t="n">
-        <v>78</v>
+        <v>74.7</v>
       </c>
       <c r="C25" s="35" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="D25" s="35" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E25" s="35" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="B26" s="35" t="n">
-        <v>75.3</v>
+        <v>78</v>
       </c>
       <c r="C26" s="35" t="n">
-        <v>74.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D26" s="35" t="n">
-        <v>74.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E26" s="35" t="n">
-        <v>76.59999999999999</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B27" s="35" t="n">
-        <v>79.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="C27" s="35" t="n">
-        <v>78.2</v>
+        <v>74.7</v>
       </c>
       <c r="D27" s="35" t="n">
-        <v>77.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E27" s="35" t="n">
-        <v>76.3</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="35" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B28" s="35" t="n">
-        <v>67.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C28" s="35" t="n">
-        <v>73.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="D28" s="35" t="n">
-        <v>74.2</v>
+        <v>77.5</v>
       </c>
       <c r="E28" s="35" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="35" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B29" s="35" t="n">
-        <v>74.7</v>
+        <v>67.8</v>
       </c>
       <c r="C29" s="35" t="n">
-        <v>77.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D29" s="35" t="n">
-        <v>77.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="E29" s="35" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -24368,17 +16388,17 @@
     <row r="33">
       <c r="A33" s="35" t="inlineStr">
         <is>
-          <t>Wake Forest</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="B33" s="35" t="n">
-        <v>71</v>
+        <v>71.2</v>
       </c>
       <c r="C33" s="35" t="n">
-        <v>69.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D33" s="35" t="n">
-        <v>72.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="E33" s="35" t="n">
         <v>74.09999999999999</v>
@@ -24387,74 +16407,74 @@
     <row r="34">
       <c r="A34" s="35" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="B34" s="35" t="n">
-        <v>71.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="C34" s="35" t="n">
-        <v>72.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D34" s="35" t="n">
-        <v>73.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E34" s="35" t="n">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="35" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Kansas State</t>
         </is>
       </c>
       <c r="B35" s="35" t="n">
-        <v>68.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="C35" s="35" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D35" s="35" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="D35" s="35" t="n">
-        <v>73.59999999999999</v>
-      </c>
       <c r="E35" s="35" t="n">
-        <v>73.2</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="35" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Wake Forest</t>
         </is>
       </c>
       <c r="B36" s="35" t="n">
-        <v>73.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="C36" s="35" t="n">
-        <v>72.7</v>
+        <v>69.8</v>
       </c>
       <c r="D36" s="35" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="E36" s="35" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="35" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="B37" s="35" t="n">
-        <v>68.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C37" s="35" t="n">
-        <v>68.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="D37" s="35" t="n">
-        <v>71.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E37" s="35" t="n">
         <v>72.8</v>
@@ -24463,20 +16483,20 @@
     <row r="38">
       <c r="A38" s="35" t="inlineStr">
         <is>
-          <t>Kansas State</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="B38" s="35" t="n">
-        <v>70.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C38" s="35" t="n">
-        <v>73.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D38" s="35" t="n">
-        <v>73.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E38" s="35" t="n">
-        <v>72.7</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="39">
@@ -24539,17 +16559,17 @@
     <row r="42">
       <c r="A42" s="35" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Mississippi State</t>
         </is>
       </c>
       <c r="B42" s="35" t="n">
-        <v>71</v>
+        <v>68.8</v>
       </c>
       <c r="C42" s="35" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="D42" s="35" t="n">
-        <v>72</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E42" s="35" t="n">
         <v>71.90000000000001</v>
@@ -24558,17 +16578,17 @@
     <row r="43">
       <c r="A43" s="35" t="inlineStr">
         <is>
-          <t>Mississippi State</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="B43" s="35" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C43" s="35" t="n">
-        <v>71.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D43" s="35" t="n">
-        <v>70.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E43" s="35" t="n">
         <v>71.90000000000001</v>
@@ -24577,20 +16597,20 @@
     <row r="44">
       <c r="A44" s="35" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="B44" s="35" t="n">
-        <v>69.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="C44" s="35" t="n">
-        <v>72.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="D44" s="35" t="n">
-        <v>73.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="E44" s="35" t="n">
-        <v>71.90000000000001</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="45">
@@ -24647,7 +16667,7 @@
         <v>70.5</v>
       </c>
       <c r="E47" s="35" t="n">
-        <v>71.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -24742,7 +16762,7 @@
         <v>68.09999999999999</v>
       </c>
       <c r="E52" s="35" t="n">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="53">
@@ -24805,36 +16825,36 @@
     <row r="56">
       <c r="A56" s="35" t="inlineStr">
         <is>
-          <t>Texas State</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="B56" s="35" t="n">
-        <v>60.5</v>
+        <v>68.2</v>
       </c>
       <c r="C56" s="35" t="n">
-        <v>61.5</v>
+        <v>68.3</v>
       </c>
       <c r="D56" s="35" t="n">
-        <v>64.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="E56" s="35" t="n">
-        <v>67.59999999999999</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="35" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>Texas State</t>
         </is>
       </c>
       <c r="B57" s="35" t="n">
-        <v>68.2</v>
+        <v>60.5</v>
       </c>
       <c r="C57" s="35" t="n">
-        <v>68.3</v>
+        <v>61.5</v>
       </c>
       <c r="D57" s="35" t="n">
-        <v>69.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E57" s="35" t="n">
         <v>67.59999999999999</v>
@@ -24913,7 +16933,7 @@
         <v>64.8</v>
       </c>
       <c r="E61" s="35" t="n">
-        <v>66.8</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -25413,17 +17433,17 @@
     <row r="88">
       <c r="A88" s="35" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B88" s="35" t="n">
-        <v>60.4</v>
+        <v>58.8</v>
       </c>
       <c r="C88" s="35" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="D88" s="35" t="n">
-        <v>60.6</v>
+        <v>58.2</v>
       </c>
       <c r="E88" s="35" t="n">
         <v>59.6</v>
@@ -25432,17 +17452,17 @@
     <row r="89">
       <c r="A89" s="35" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Oklahoma State</t>
         </is>
       </c>
       <c r="B89" s="35" t="n">
-        <v>58.8</v>
+        <v>50.2</v>
       </c>
       <c r="C89" s="35" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D89" s="35" t="n">
-        <v>58.2</v>
+        <v>57.8</v>
       </c>
       <c r="E89" s="35" t="n">
         <v>59.6</v>
@@ -25451,20 +17471,20 @@
     <row r="90">
       <c r="A90" s="35" t="inlineStr">
         <is>
-          <t>Oklahoma State</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B90" s="35" t="n">
-        <v>50.2</v>
+        <v>60.4</v>
       </c>
       <c r="C90" s="35" t="n">
-        <v>54</v>
+        <v>59.8</v>
       </c>
       <c r="D90" s="35" t="n">
-        <v>57.8</v>
+        <v>60.6</v>
       </c>
       <c r="E90" s="35" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="91">
@@ -26243,7 +18263,7 @@
         <v>45.5</v>
       </c>
       <c r="E131" s="35" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="132">
@@ -26281,7 +18301,7 @@
         <v>43.7</v>
       </c>
       <c r="E133" s="35" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="134">
@@ -26357,7 +18377,7 @@
         <v>42.1</v>
       </c>
       <c r="E137" s="35" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="138">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -4800,7 +4800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9065,6 +9065,38 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Liberty @ Delaware</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
       <c r="J60" s="12">
         <f>IF(I60="","",I60-F60)</f>
         <v/>
@@ -9079,6 +9111,38 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Alabama @ Mississippi State</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
       <c r="J61" s="12">
         <f>IF(I61="","",I61-F61)</f>
         <v/>
@@ -9093,7 +9157,38 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="n"/>
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Marshall @ James Madison</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
       <c r="J62" s="12">
         <f>IF(I62="","",I62-F62)</f>
         <v/>
@@ -9108,6 +9203,35 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pittsburgh @ Virginia Tech</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>116</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
       <c r="J63" s="12">
         <f>IF(I63="","",I63-F63)</f>
         <v/>
@@ -22490,7 +22614,7 @@
         </is>
       </c>
       <c r="C88" s="35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D88" s="35" t="n">
         <v>83</v>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1442,7 +1442,7 @@
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>UAB</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="B5" s="35" t="n">
@@ -1455,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="35" t="n">
         <v>2</v>
@@ -1464,40 +1464,42 @@
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>Army</t>
+          <t>UAB</t>
         </is>
       </c>
       <c r="B6" s="35" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="35" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>0.5</v>
       </c>
       <c r="E6" s="35" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Army</t>
         </is>
       </c>
       <c r="B7" s="35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="35" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E7" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="35" t="n">
         <v>1</v>
@@ -1506,7 +1508,7 @@
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B8" s="35" t="n">
@@ -1546,18 +1548,20 @@
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>East Carolina</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="B10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="35" t="n"/>
       <c r="E10" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="35" t="n">
         <v>2</v>
@@ -1566,7 +1570,7 @@
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>East Carolina</t>
         </is>
       </c>
       <c r="B11" s="35" t="n">
@@ -2700,27 +2704,29 @@
     <row r="4">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>New Mexico State</t>
         </is>
       </c>
       <c r="B4" s="35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="35" t="n"/>
+      <c r="D4" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="35" t="n">
         <v>3</v>
-      </c>
-      <c r="F4" s="35" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="B5" s="35" t="n">
@@ -2731,16 +2737,16 @@
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>Florida International</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B6" s="35" t="n">
@@ -2760,18 +2766,16 @@
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>Middle Tennessee</t>
+          <t>Florida International</t>
         </is>
       </c>
       <c r="B7" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="D7" s="35" t="n"/>
       <c r="E7" s="35" t="n">
         <v>2</v>
       </c>
@@ -2782,27 +2786,29 @@
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>Kennesaw State</t>
+          <t>Middle Tennessee</t>
         </is>
       </c>
       <c r="B8" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="35" t="n"/>
       <c r="E8" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>Missouri State</t>
+          <t>Kennesaw State</t>
         </is>
       </c>
       <c r="B9" s="35" t="n">
@@ -2822,7 +2828,7 @@
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>New Mexico State</t>
+          <t>Missouri State</t>
         </is>
       </c>
       <c r="B10" s="35" t="n">
@@ -2869,14 +2875,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="35" t="n"/>
       <c r="E12" s="35" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="26.5" customHeight="1">
@@ -4800,7 +4808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4929,7 +4937,7 @@
         <v>5.2</v>
       </c>
       <c r="F2" t="n">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
       <c r="G2" s="6">
         <f>F2-E2</f>
@@ -4943,7 +4951,7 @@
         <v>55.1</v>
       </c>
       <c r="J2" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -4987,7 +4995,7 @@
         <v>-30.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-18.2</v>
+        <v>-17.2</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -5001,7 +5009,7 @@
         <v>46.7</v>
       </c>
       <c r="J3" t="n">
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
       <c r="K3" s="6">
         <f>I3-J3</f>
@@ -5043,7 +5051,7 @@
         <v>-5.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5</v>
+        <v>-2.8</v>
       </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
@@ -5113,7 +5121,7 @@
         <v>43.7</v>
       </c>
       <c r="J5" t="n">
-        <v>48.5</v>
+        <v>47.8</v>
       </c>
       <c r="K5" s="6">
         <f>I5-J5</f>
@@ -5174,7 +5182,7 @@
         <v>48.5</v>
       </c>
       <c r="J6" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -15832,6 +15840,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
@@ -15862,6 +15871,11 @@
           <t>Week 4</t>
         </is>
       </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
       <c r="V1" s="34" t="inlineStr">
         <is>
           <t>Matchup Spread Calculator</t>
@@ -15886,6 +15900,9 @@
       <c r="E2" s="35" t="n">
         <v>94.90000000000001</v>
       </c>
+      <c r="F2" s="35" t="n">
+        <v>94.59999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="35" t="inlineStr">
@@ -15905,6 +15922,9 @@
       <c r="E3" s="35" t="n">
         <v>94</v>
       </c>
+      <c r="F3" s="35" t="n">
+        <v>94</v>
+      </c>
       <c r="V3" s="35" t="inlineStr">
         <is>
           <t>Home Team</t>
@@ -15934,6 +15954,9 @@
       <c r="E4" s="35" t="n">
         <v>90.40000000000001</v>
       </c>
+      <c r="F4" s="35" t="n">
+        <v>90.40000000000001</v>
+      </c>
       <c r="V4" s="35" t="inlineStr">
         <is>
           <t>Away Team</t>
@@ -15963,6 +15986,9 @@
       <c r="E5" s="35" t="n">
         <v>89.40000000000001</v>
       </c>
+      <c r="F5" s="35" t="n">
+        <v>89.40000000000001</v>
+      </c>
       <c r="V5" s="35" t="inlineStr">
         <is>
           <t>Neutral Site? (Y/N)</t>
@@ -15992,6 +16018,9 @@
       <c r="E6" s="35" t="n">
         <v>89</v>
       </c>
+      <c r="F6" s="35" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -16011,6 +16040,9 @@
       <c r="E7" s="35" t="n">
         <v>88</v>
       </c>
+      <c r="F7" s="35" t="n">
+        <v>88</v>
+      </c>
       <c r="V7" s="35" t="inlineStr">
         <is>
           <t>HFA (model constant)</t>
@@ -16038,53 +16070,62 @@
       <c r="E8" s="35" t="n">
         <v>85.59999999999999</v>
       </c>
+      <c r="F8" s="35" t="n">
+        <v>85.59999999999999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="B9" s="35" t="n">
-        <v>87.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="C9" s="35" t="n">
-        <v>85.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="D9" s="35" t="n">
-        <v>84.7</v>
+        <v>84.2</v>
       </c>
       <c r="E9" s="35" t="n">
         <v>84.3</v>
       </c>
+      <c r="F9" s="35" t="n">
+        <v>84.3</v>
+      </c>
       <c r="V9" s="36" t="inlineStr">
         <is>
           <t>Predicted Spread (Home)</t>
         </is>
       </c>
       <c r="W9" s="36">
-        <f>IF(OR(W3="",W4=""),"",INDEX($E$2:$E$139,MATCH(W4,$A$2:$A$139,0))-INDEX($E$2:$E$139,MATCH(W3,$A$2:$A$139,0))-IF(UPPER(W5)="Y",0,W7))</f>
+        <f>IF(OR(W3="",W4=""),"",INDEX($F$2:$F$139,MATCH(W4,$A$2:$A$139,0))-INDEX($F$2:$F$139,MATCH(W3,$A$2:$A$139,0))-IF(UPPER(W5)="Y",0,W7))</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="B10" s="35" t="n">
-        <v>81.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="C10" s="35" t="n">
-        <v>83.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D10" s="35" t="n">
-        <v>84.2</v>
+        <v>84.7</v>
       </c>
       <c r="E10" s="35" t="n">
         <v>84.3</v>
       </c>
+      <c r="F10" s="35" t="n">
+        <v>84.3</v>
+      </c>
       <c r="V10" s="37" t="inlineStr">
         <is>
           <t>(negative = home team favored, e.g. "Home -6.5")</t>
@@ -16109,6 +16150,9 @@
       <c r="E11" s="35" t="n">
         <v>83.90000000000001</v>
       </c>
+      <c r="F11" s="35" t="n">
+        <v>83.90000000000001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
@@ -16128,6 +16172,9 @@
       <c r="E12" s="35" t="n">
         <v>82.5</v>
       </c>
+      <c r="F12" s="35" t="n">
+        <v>82.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
@@ -16147,6 +16194,9 @@
       <c r="E13" s="35" t="n">
         <v>81.3</v>
       </c>
+      <c r="F13" s="35" t="n">
+        <v>81.40000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
@@ -16166,6 +16216,9 @@
       <c r="E14" s="35" t="n">
         <v>81.09999999999999</v>
       </c>
+      <c r="F14" s="35" t="n">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
@@ -16185,6 +16238,9 @@
       <c r="E15" s="35" t="n">
         <v>80.2</v>
       </c>
+      <c r="F15" s="35" t="n">
+        <v>80.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -16204,6 +16260,9 @@
       <c r="E16" s="35" t="n">
         <v>79.7</v>
       </c>
+      <c r="F16" s="35" t="n">
+        <v>79.7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
@@ -16223,6 +16282,9 @@
       <c r="E17" s="35" t="n">
         <v>79.5</v>
       </c>
+      <c r="F17" s="35" t="n">
+        <v>79.59999999999999</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
@@ -16242,6 +16304,9 @@
       <c r="E18" s="35" t="n">
         <v>79.5</v>
       </c>
+      <c r="F18" s="35" t="n">
+        <v>79.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
@@ -16261,6 +16326,9 @@
       <c r="E19" s="35" t="n">
         <v>78.90000000000001</v>
       </c>
+      <c r="F19" s="35" t="n">
+        <v>78.90000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
@@ -16280,6 +16348,9 @@
       <c r="E20" s="35" t="n">
         <v>78.2</v>
       </c>
+      <c r="F20" s="35" t="n">
+        <v>78.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -16299,6 +16370,9 @@
       <c r="E21" s="35" t="n">
         <v>78.09999999999999</v>
       </c>
+      <c r="F21" s="35" t="n">
+        <v>78.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -16318,6 +16392,9 @@
       <c r="E22" s="35" t="n">
         <v>77.7</v>
       </c>
+      <c r="F22" s="35" t="n">
+        <v>77.59999999999999</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -16337,6 +16414,9 @@
       <c r="E23" s="35" t="n">
         <v>77.5</v>
       </c>
+      <c r="F23" s="35" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
@@ -16356,6 +16436,9 @@
       <c r="E24" s="35" t="n">
         <v>77.5</v>
       </c>
+      <c r="F24" s="35" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
@@ -16375,6 +16458,9 @@
       <c r="E25" s="35" t="n">
         <v>77.2</v>
       </c>
+      <c r="F25" s="35" t="n">
+        <v>77.2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
@@ -16394,6 +16480,9 @@
       <c r="E26" s="35" t="n">
         <v>77</v>
       </c>
+      <c r="F26" s="35" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
@@ -16413,6 +16502,9 @@
       <c r="E27" s="35" t="n">
         <v>76.59999999999999</v>
       </c>
+      <c r="F27" s="35" t="n">
+        <v>76.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="35" t="inlineStr">
@@ -16432,6 +16524,9 @@
       <c r="E28" s="35" t="n">
         <v>76.3</v>
       </c>
+      <c r="F28" s="35" t="n">
+        <v>76.3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="35" t="inlineStr">
@@ -16451,6 +16546,9 @@
       <c r="E29" s="35" t="n">
         <v>76.09999999999999</v>
       </c>
+      <c r="F29" s="35" t="n">
+        <v>76.2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="35" t="inlineStr">
@@ -16470,6 +16568,9 @@
       <c r="E30" s="35" t="n">
         <v>76</v>
       </c>
+      <c r="F30" s="35" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="35" t="inlineStr">
@@ -16489,6 +16590,9 @@
       <c r="E31" s="35" t="n">
         <v>75.3</v>
       </c>
+      <c r="F31" s="35" t="n">
+        <v>75.3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="35" t="inlineStr">
@@ -16508,6 +16612,9 @@
       <c r="E32" s="35" t="n">
         <v>74.40000000000001</v>
       </c>
+      <c r="F32" s="35" t="n">
+        <v>74.40000000000001</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="35" t="inlineStr">
@@ -16527,6 +16634,9 @@
       <c r="E33" s="35" t="n">
         <v>74.09999999999999</v>
       </c>
+      <c r="F33" s="35" t="n">
+        <v>74.09999999999999</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="35" t="inlineStr">
@@ -16546,6 +16656,9 @@
       <c r="E34" s="35" t="n">
         <v>73.2</v>
       </c>
+      <c r="F34" s="35" t="n">
+        <v>73.2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="35" t="inlineStr">
@@ -16565,6 +16678,9 @@
       <c r="E35" s="35" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="F35" s="35" t="n">
+        <v>72.90000000000001</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="35" t="inlineStr">
@@ -16584,6 +16700,9 @@
       <c r="E36" s="35" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="F36" s="35" t="n">
+        <v>72.90000000000001</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="35" t="inlineStr">
@@ -16603,6 +16722,9 @@
       <c r="E37" s="35" t="n">
         <v>72.8</v>
       </c>
+      <c r="F37" s="35" t="n">
+        <v>72.8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="35" t="inlineStr">
@@ -16622,6 +16744,9 @@
       <c r="E38" s="35" t="n">
         <v>72.8</v>
       </c>
+      <c r="F38" s="35" t="n">
+        <v>72.8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="35" t="inlineStr">
@@ -16641,6 +16766,9 @@
       <c r="E39" s="35" t="n">
         <v>72.7</v>
       </c>
+      <c r="F39" s="35" t="n">
+        <v>72.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="35" t="inlineStr">
@@ -16660,6 +16788,9 @@
       <c r="E40" s="35" t="n">
         <v>72.40000000000001</v>
       </c>
+      <c r="F40" s="35" t="n">
+        <v>72.40000000000001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="35" t="inlineStr">
@@ -16679,6 +16810,9 @@
       <c r="E41" s="35" t="n">
         <v>72.2</v>
       </c>
+      <c r="F41" s="35" t="n">
+        <v>72.3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="35" t="inlineStr">
@@ -16698,6 +16832,9 @@
       <c r="E42" s="35" t="n">
         <v>71.90000000000001</v>
       </c>
+      <c r="F42" s="35" t="n">
+        <v>71.90000000000001</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="35" t="inlineStr">
@@ -16717,6 +16854,9 @@
       <c r="E43" s="35" t="n">
         <v>71.90000000000001</v>
       </c>
+      <c r="F43" s="35" t="n">
+        <v>71.90000000000001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="35" t="inlineStr">
@@ -16736,6 +16876,9 @@
       <c r="E44" s="35" t="n">
         <v>71.7</v>
       </c>
+      <c r="F44" s="35" t="n">
+        <v>71.8</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="35" t="inlineStr">
@@ -16755,6 +16898,9 @@
       <c r="E45" s="35" t="n">
         <v>71.7</v>
       </c>
+      <c r="F45" s="35" t="n">
+        <v>71.7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="35" t="inlineStr">
@@ -16774,6 +16920,9 @@
       <c r="E46" s="35" t="n">
         <v>71.40000000000001</v>
       </c>
+      <c r="F46" s="35" t="n">
+        <v>71.40000000000001</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="35" t="inlineStr">
@@ -16793,6 +16942,9 @@
       <c r="E47" s="35" t="n">
         <v>70.90000000000001</v>
       </c>
+      <c r="F47" s="35" t="n">
+        <v>70.90000000000001</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="35" t="inlineStr">
@@ -16812,6 +16964,9 @@
       <c r="E48" s="35" t="n">
         <v>70.7</v>
       </c>
+      <c r="F48" s="35" t="n">
+        <v>70.7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="35" t="inlineStr">
@@ -16831,6 +16986,9 @@
       <c r="E49" s="35" t="n">
         <v>70.40000000000001</v>
       </c>
+      <c r="F49" s="35" t="n">
+        <v>70.2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="35" t="inlineStr">
@@ -16850,6 +17008,9 @@
       <c r="E50" s="35" t="n">
         <v>70.2</v>
       </c>
+      <c r="F50" s="35" t="n">
+        <v>70.2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="35" t="inlineStr">
@@ -16869,6 +17030,9 @@
       <c r="E51" s="35" t="n">
         <v>69.40000000000001</v>
       </c>
+      <c r="F51" s="35" t="n">
+        <v>69.40000000000001</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="35" t="inlineStr">
@@ -16888,6 +17052,9 @@
       <c r="E52" s="35" t="n">
         <v>68.8</v>
       </c>
+      <c r="F52" s="35" t="n">
+        <v>68.8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="35" t="inlineStr">
@@ -16907,6 +17074,9 @@
       <c r="E53" s="35" t="n">
         <v>68.59999999999999</v>
       </c>
+      <c r="F53" s="35" t="n">
+        <v>68.59999999999999</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="35" t="inlineStr">
@@ -16926,6 +17096,9 @@
       <c r="E54" s="35" t="n">
         <v>67.8</v>
       </c>
+      <c r="F54" s="35" t="n">
+        <v>67.8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="35" t="inlineStr">
@@ -16945,6 +17118,9 @@
       <c r="E55" s="35" t="n">
         <v>67.7</v>
       </c>
+      <c r="F55" s="35" t="n">
+        <v>67.7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="35" t="inlineStr">
@@ -16964,6 +17140,9 @@
       <c r="E56" s="35" t="n">
         <v>67.7</v>
       </c>
+      <c r="F56" s="35" t="n">
+        <v>67.7</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="35" t="inlineStr">
@@ -16983,6 +17162,9 @@
       <c r="E57" s="35" t="n">
         <v>67.59999999999999</v>
       </c>
+      <c r="F57" s="35" t="n">
+        <v>67.5</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="35" t="inlineStr">
@@ -17002,6 +17184,9 @@
       <c r="E58" s="35" t="n">
         <v>67.3</v>
       </c>
+      <c r="F58" s="35" t="n">
+        <v>67.2</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="35" t="inlineStr">
@@ -17021,6 +17206,9 @@
       <c r="E59" s="35" t="n">
         <v>67.2</v>
       </c>
+      <c r="F59" s="35" t="n">
+        <v>67.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="35" t="inlineStr">
@@ -17040,118 +17228,139 @@
       <c r="E60" s="35" t="n">
         <v>67.09999999999999</v>
       </c>
+      <c r="F60" s="35" t="n">
+        <v>67.09999999999999</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="35" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="B61" s="35" t="n">
-        <v>63.9</v>
+        <v>66</v>
       </c>
       <c r="C61" s="35" t="n">
-        <v>67.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D61" s="35" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="E61" s="35" t="n">
-        <v>66.90000000000001</v>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F61" s="35" t="n">
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="35" t="inlineStr">
         <is>
-          <t>Michigan State</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="B62" s="35" t="n">
-        <v>66</v>
+        <v>62.1</v>
       </c>
       <c r="C62" s="35" t="n">
-        <v>66.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D62" s="35" t="n">
-        <v>67.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E62" s="35" t="n">
-        <v>66.40000000000001</v>
+        <v>66.3</v>
+      </c>
+      <c r="F62" s="35" t="n">
+        <v>66.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="B63" s="35" t="n">
-        <v>62.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C63" s="35" t="n">
-        <v>65</v>
+        <v>69.5</v>
       </c>
       <c r="D63" s="35" t="n">
-        <v>64.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="E63" s="35" t="n">
         <v>66.3</v>
       </c>
+      <c r="F63" s="35" t="n">
+        <v>66.3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B64" s="35" t="n">
-        <v>72.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="C64" s="35" t="n">
-        <v>69.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D64" s="35" t="n">
-        <v>68.5</v>
+        <v>64</v>
       </c>
       <c r="E64" s="35" t="n">
-        <v>66.3</v>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="F64" s="35" t="n">
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="35" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="B65" s="35" t="n">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="C65" s="35" t="n">
-        <v>65.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="D65" s="35" t="n">
-        <v>64</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E65" s="35" t="n">
-        <v>66</v>
+        <v>65.8</v>
+      </c>
+      <c r="F65" s="35" t="n">
+        <v>65.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="35" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="B66" s="35" t="n">
-        <v>67.7</v>
+        <v>63.9</v>
       </c>
       <c r="C66" s="35" t="n">
-        <v>66.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D66" s="35" t="n">
-        <v>67.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="E66" s="35" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="F66" s="35" t="n">
         <v>65.8</v>
       </c>
     </row>
@@ -17173,6 +17382,9 @@
       <c r="E67" s="35" t="n">
         <v>65.7</v>
       </c>
+      <c r="F67" s="35" t="n">
+        <v>65.7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="35" t="inlineStr">
@@ -17192,6 +17404,9 @@
       <c r="E68" s="35" t="n">
         <v>65.40000000000001</v>
       </c>
+      <c r="F68" s="35" t="n">
+        <v>65.40000000000001</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="inlineStr">
@@ -17211,6 +17426,9 @@
       <c r="E69" s="35" t="n">
         <v>65.09999999999999</v>
       </c>
+      <c r="F69" s="35" t="n">
+        <v>65.09999999999999</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="inlineStr">
@@ -17230,6 +17448,9 @@
       <c r="E70" s="35" t="n">
         <v>65.09999999999999</v>
       </c>
+      <c r="F70" s="35" t="n">
+        <v>65.09999999999999</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="inlineStr">
@@ -17249,44 +17470,53 @@
       <c r="E71" s="35" t="n">
         <v>64.7</v>
       </c>
+      <c r="F71" s="35" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="inlineStr">
         <is>
-          <t>Rutgers</t>
+          <t>UTSA</t>
         </is>
       </c>
       <c r="B72" s="35" t="n">
-        <v>61.1</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C72" s="35" t="n">
-        <v>62</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D72" s="35" t="n">
-        <v>62.1</v>
+        <v>65.2</v>
       </c>
       <c r="E72" s="35" t="n">
         <v>64.7</v>
       </c>
+      <c r="F72" s="35" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="35" t="inlineStr">
         <is>
-          <t>UTSA</t>
+          <t>Rutgers</t>
         </is>
       </c>
       <c r="B73" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="C73" s="35" t="n">
-        <v>65.59999999999999</v>
+        <v>62</v>
       </c>
       <c r="D73" s="35" t="n">
-        <v>65.2</v>
+        <v>62.1</v>
       </c>
       <c r="E73" s="35" t="n">
         <v>64.7</v>
       </c>
+      <c r="F73" s="35" t="n">
+        <v>64.3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="inlineStr">
@@ -17306,6 +17536,9 @@
       <c r="E74" s="35" t="n">
         <v>64.2</v>
       </c>
+      <c r="F74" s="35" t="n">
+        <v>64.2</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="inlineStr">
@@ -17325,6 +17558,9 @@
       <c r="E75" s="35" t="n">
         <v>63.9</v>
       </c>
+      <c r="F75" s="35" t="n">
+        <v>63.9</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="inlineStr">
@@ -17344,6 +17580,9 @@
       <c r="E76" s="35" t="n">
         <v>62.3</v>
       </c>
+      <c r="F76" s="35" t="n">
+        <v>62.3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="35" t="inlineStr">
@@ -17363,6 +17602,9 @@
       <c r="E77" s="35" t="n">
         <v>62.2</v>
       </c>
+      <c r="F77" s="35" t="n">
+        <v>62.2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="35" t="inlineStr">
@@ -17382,6 +17624,9 @@
       <c r="E78" s="35" t="n">
         <v>61.7</v>
       </c>
+      <c r="F78" s="35" t="n">
+        <v>61.7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="35" t="inlineStr">
@@ -17401,6 +17646,9 @@
       <c r="E79" s="35" t="n">
         <v>61.5</v>
       </c>
+      <c r="F79" s="35" t="n">
+        <v>61.5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="35" t="inlineStr">
@@ -17420,6 +17668,9 @@
       <c r="E80" s="35" t="n">
         <v>61.4</v>
       </c>
+      <c r="F80" s="35" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="35" t="inlineStr">
@@ -17439,44 +17690,53 @@
       <c r="E81" s="35" t="n">
         <v>61.4</v>
       </c>
+      <c r="F81" s="35" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="35" t="inlineStr">
         <is>
-          <t>UNLV</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B82" s="35" t="n">
-        <v>62.6</v>
+        <v>58.2</v>
       </c>
       <c r="C82" s="35" t="n">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="D82" s="35" t="n">
-        <v>59</v>
+        <v>63.4</v>
       </c>
       <c r="E82" s="35" t="n">
         <v>60.9</v>
       </c>
+      <c r="F82" s="35" t="n">
+        <v>60.9</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>UNLV</t>
         </is>
       </c>
       <c r="B83" s="35" t="n">
-        <v>58.2</v>
+        <v>62.6</v>
       </c>
       <c r="C83" s="35" t="n">
-        <v>60.5</v>
+        <v>59</v>
       </c>
       <c r="D83" s="35" t="n">
-        <v>63.4</v>
+        <v>59</v>
       </c>
       <c r="E83" s="35" t="n">
         <v>60.9</v>
       </c>
+      <c r="F83" s="35" t="n">
+        <v>60.9</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="inlineStr">
@@ -17496,6 +17756,9 @@
       <c r="E84" s="35" t="n">
         <v>60.2</v>
       </c>
+      <c r="F84" s="35" t="n">
+        <v>60.2</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="35" t="inlineStr">
@@ -17515,6 +17778,9 @@
       <c r="E85" s="35" t="n">
         <v>60.1</v>
       </c>
+      <c r="F85" s="35" t="n">
+        <v>60.1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="35" t="inlineStr">
@@ -17534,6 +17800,9 @@
       <c r="E86" s="35" t="n">
         <v>59.9</v>
       </c>
+      <c r="F86" s="35" t="n">
+        <v>59.9</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="35" t="inlineStr">
@@ -17553,62 +17822,74 @@
       <c r="E87" s="35" t="n">
         <v>59.7</v>
       </c>
+      <c r="F87" s="35" t="n">
+        <v>59.7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="35" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Oklahoma State</t>
         </is>
       </c>
       <c r="B88" s="35" t="n">
-        <v>58.8</v>
+        <v>50.2</v>
       </c>
       <c r="C88" s="35" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D88" s="35" t="n">
-        <v>58.2</v>
+        <v>57.8</v>
       </c>
       <c r="E88" s="35" t="n">
         <v>59.6</v>
       </c>
+      <c r="F88" s="35" t="n">
+        <v>59.6</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="35" t="inlineStr">
         <is>
-          <t>Oklahoma State</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B89" s="35" t="n">
-        <v>50.2</v>
+        <v>60.4</v>
       </c>
       <c r="C89" s="35" t="n">
-        <v>54</v>
+        <v>59.8</v>
       </c>
       <c r="D89" s="35" t="n">
-        <v>57.8</v>
+        <v>60.5</v>
       </c>
       <c r="E89" s="35" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F89" s="35" t="n">
         <v>59.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="35" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B90" s="35" t="n">
-        <v>60.4</v>
+        <v>58.8</v>
       </c>
       <c r="C90" s="35" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="D90" s="35" t="n">
-        <v>60.6</v>
+        <v>58.2</v>
       </c>
       <c r="E90" s="35" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
+      </c>
+      <c r="F90" s="35" t="n">
+        <v>59.4</v>
       </c>
     </row>
     <row r="91">
@@ -17629,6 +17910,9 @@
       <c r="E91" s="35" t="n">
         <v>59.2</v>
       </c>
+      <c r="F91" s="35" t="n">
+        <v>59.1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="35" t="inlineStr">
@@ -17648,6 +17932,9 @@
       <c r="E92" s="35" t="n">
         <v>58.7</v>
       </c>
+      <c r="F92" s="35" t="n">
+        <v>58.7</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="35" t="inlineStr">
@@ -17667,6 +17954,9 @@
       <c r="E93" s="35" t="n">
         <v>58.5</v>
       </c>
+      <c r="F93" s="35" t="n">
+        <v>58.5</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="35" t="inlineStr">
@@ -17686,43 +17976,52 @@
       <c r="E94" s="35" t="n">
         <v>58</v>
       </c>
+      <c r="F94" s="35" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="35" t="inlineStr">
         <is>
-          <t>Western Kentucky</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B95" s="35" t="n">
-        <v>56.1</v>
+        <v>54.3</v>
       </c>
       <c r="C95" s="35" t="n">
-        <v>53.9</v>
+        <v>54.8</v>
       </c>
       <c r="D95" s="35" t="n">
-        <v>54.4</v>
+        <v>55.3</v>
       </c>
       <c r="E95" s="35" t="n">
-        <v>57.1</v>
+        <v>57</v>
+      </c>
+      <c r="F95" s="35" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="35" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="B96" s="35" t="n">
-        <v>54.3</v>
+        <v>55.3</v>
       </c>
       <c r="C96" s="35" t="n">
-        <v>54.8</v>
+        <v>55.4</v>
       </c>
       <c r="D96" s="35" t="n">
-        <v>55.3</v>
+        <v>58.2</v>
       </c>
       <c r="E96" s="35" t="n">
-        <v>57</v>
+        <v>55.9</v>
+      </c>
+      <c r="F96" s="35" t="n">
+        <v>56.9</v>
       </c>
     </row>
     <row r="97">
@@ -17743,6 +18042,9 @@
       <c r="E97" s="35" t="n">
         <v>56.8</v>
       </c>
+      <c r="F97" s="35" t="n">
+        <v>56.8</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="35" t="inlineStr">
@@ -17762,6 +18064,9 @@
       <c r="E98" s="35" t="n">
         <v>56.7</v>
       </c>
+      <c r="F98" s="35" t="n">
+        <v>56.7</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="35" t="inlineStr">
@@ -17781,6 +18086,9 @@
       <c r="E99" s="35" t="n">
         <v>56.6</v>
       </c>
+      <c r="F99" s="35" t="n">
+        <v>56.6</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="35" t="inlineStr">
@@ -17800,6 +18108,9 @@
       <c r="E100" s="35" t="n">
         <v>56.5</v>
       </c>
+      <c r="F100" s="35" t="n">
+        <v>56.5</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="35" t="inlineStr">
@@ -17819,6 +18130,9 @@
       <c r="E101" s="35" t="n">
         <v>56</v>
       </c>
+      <c r="F101" s="35" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="35" t="inlineStr">
@@ -17838,6 +18152,9 @@
       <c r="E102" s="35" t="n">
         <v>55.9</v>
       </c>
+      <c r="F102" s="35" t="n">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="35" t="inlineStr">
@@ -17857,6 +18174,9 @@
       <c r="E103" s="35" t="n">
         <v>55.8</v>
       </c>
+      <c r="F103" s="35" t="n">
+        <v>55.8</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="35" t="inlineStr">
@@ -17876,6 +18196,9 @@
       <c r="E104" s="35" t="n">
         <v>55.6</v>
       </c>
+      <c r="F104" s="35" t="n">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="35" t="inlineStr">
@@ -17895,81 +18218,96 @@
       <c r="E105" s="35" t="n">
         <v>55.2</v>
       </c>
+      <c r="F105" s="35" t="n">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="35" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="B106" s="35" t="n">
-        <v>55.3</v>
+        <v>57.3</v>
       </c>
       <c r="C106" s="35" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="D106" s="35" t="n">
-        <v>57.6</v>
+        <v>57.3</v>
       </c>
       <c r="E106" s="35" t="n">
-        <v>55.2</v>
+        <v>54.4</v>
+      </c>
+      <c r="F106" s="35" t="n">
+        <v>54.4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="35" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Colorado State</t>
         </is>
       </c>
       <c r="B107" s="35" t="n">
-        <v>57.3</v>
+        <v>51</v>
       </c>
       <c r="C107" s="35" t="n">
-        <v>54.7</v>
+        <v>53.6</v>
       </c>
       <c r="D107" s="35" t="n">
-        <v>57.3</v>
+        <v>53.8</v>
       </c>
       <c r="E107" s="35" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
+      </c>
+      <c r="F107" s="35" t="n">
+        <v>54.3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="35" t="inlineStr">
         <is>
-          <t>Colorado State</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B108" s="35" t="n">
-        <v>51</v>
+        <v>53.1</v>
       </c>
       <c r="C108" s="35" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="D108" s="35" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="E108" s="35" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
+      </c>
+      <c r="F108" s="35" t="n">
+        <v>54.2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="35" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Western Kentucky</t>
         </is>
       </c>
       <c r="B109" s="35" t="n">
-        <v>53.1</v>
+        <v>56.1</v>
       </c>
       <c r="C109" s="35" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
       <c r="D109" s="35" t="n">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="E109" s="35" t="n">
-        <v>54.2</v>
+        <v>57.1</v>
+      </c>
+      <c r="F109" s="35" t="n">
+        <v>53.9</v>
       </c>
     </row>
     <row r="110">
@@ -17990,6 +18328,9 @@
       <c r="E110" s="35" t="n">
         <v>53.9</v>
       </c>
+      <c r="F110" s="35" t="n">
+        <v>53.5</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="35" t="inlineStr">
@@ -18009,6 +18350,9 @@
       <c r="E111" s="35" t="n">
         <v>53.3</v>
       </c>
+      <c r="F111" s="35" t="n">
+        <v>53.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="35" t="inlineStr">
@@ -18028,6 +18372,9 @@
       <c r="E112" s="35" t="n">
         <v>53.2</v>
       </c>
+      <c r="F112" s="35" t="n">
+        <v>53.2</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="35" t="inlineStr">
@@ -18047,6 +18394,9 @@
       <c r="E113" s="35" t="n">
         <v>53.1</v>
       </c>
+      <c r="F113" s="35" t="n">
+        <v>53.1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="35" t="inlineStr">
@@ -18066,6 +18416,9 @@
       <c r="E114" s="35" t="n">
         <v>52.5</v>
       </c>
+      <c r="F114" s="35" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="35" t="inlineStr">
@@ -18085,6 +18438,9 @@
       <c r="E115" s="35" t="n">
         <v>52.3</v>
       </c>
+      <c r="F115" s="35" t="n">
+        <v>52.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="35" t="inlineStr">
@@ -18104,6 +18460,9 @@
       <c r="E116" s="35" t="n">
         <v>52.1</v>
       </c>
+      <c r="F116" s="35" t="n">
+        <v>52.1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="35" t="inlineStr">
@@ -18123,138 +18482,162 @@
       <c r="E117" s="35" t="n">
         <v>51.9</v>
       </c>
+      <c r="F117" s="35" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="35" t="inlineStr">
         <is>
-          <t>Coastal Carolina</t>
+          <t>New Mexico State</t>
         </is>
       </c>
       <c r="B118" s="35" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="C118" s="35" t="n">
-        <v>54.1</v>
+        <v>49.5</v>
       </c>
       <c r="D118" s="35" t="n">
-        <v>53</v>
+        <v>49.5</v>
       </c>
       <c r="E118" s="35" t="n">
-        <v>51.7</v>
+        <v>49.1</v>
+      </c>
+      <c r="F118" s="35" t="n">
+        <v>51.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="35" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Coastal Carolina</t>
         </is>
       </c>
       <c r="B119" s="35" t="n">
-        <v>52.1</v>
+        <v>51</v>
       </c>
       <c r="C119" s="35" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="D119" s="35" t="n">
+        <v>53</v>
+      </c>
+      <c r="E119" s="35" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F119" s="35" t="n">
         <v>51.8</v>
-      </c>
-      <c r="D119" s="35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E119" s="35" t="n">
-        <v>51.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="35" t="inlineStr">
         <is>
-          <t>Southern Miss</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B120" s="35" t="n">
-        <v>54.4</v>
+        <v>52.1</v>
       </c>
       <c r="C120" s="35" t="n">
-        <v>52.7</v>
+        <v>51.8</v>
       </c>
       <c r="D120" s="35" t="n">
-        <v>50.1</v>
+        <v>52.5</v>
       </c>
       <c r="E120" s="35" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F120" s="35" t="n">
         <v>51.3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="35" t="inlineStr">
         <is>
-          <t>Georgia State</t>
+          <t>Southern Miss</t>
         </is>
       </c>
       <c r="B121" s="35" t="n">
-        <v>47.4</v>
+        <v>54.4</v>
       </c>
       <c r="C121" s="35" t="n">
-        <v>49.7</v>
+        <v>52.7</v>
       </c>
       <c r="D121" s="35" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="E121" s="35" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
+      </c>
+      <c r="F121" s="35" t="n">
+        <v>51.3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="35" t="inlineStr">
         <is>
-          <t>San José State</t>
+          <t>Georgia State</t>
         </is>
       </c>
       <c r="B122" s="35" t="n">
-        <v>51.7</v>
+        <v>47.4</v>
       </c>
       <c r="C122" s="35" t="n">
-        <v>51.6</v>
+        <v>49.7</v>
       </c>
       <c r="D122" s="35" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="E122" s="35" t="n">
-        <v>50.4</v>
+        <v>51.2</v>
+      </c>
+      <c r="F122" s="35" t="n">
+        <v>51.2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="35" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>San José State</t>
         </is>
       </c>
       <c r="B123" s="35" t="n">
-        <v>48.6</v>
+        <v>51.7</v>
       </c>
       <c r="C123" s="35" t="n">
-        <v>48.8</v>
+        <v>51.6</v>
       </c>
       <c r="D123" s="35" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="E123" s="35" t="n">
-        <v>49.6</v>
+        <v>50.4</v>
+      </c>
+      <c r="F123" s="35" t="n">
+        <v>50.4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="35" t="inlineStr">
         <is>
-          <t>New Mexico State</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B124" s="35" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="C124" s="35" t="n">
-        <v>49.5</v>
+        <v>48.8</v>
       </c>
       <c r="D124" s="35" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="E124" s="35" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
+      </c>
+      <c r="F124" s="35" t="n">
+        <v>49.6</v>
       </c>
     </row>
     <row r="125">
@@ -18275,6 +18658,9 @@
       <c r="E125" s="35" t="n">
         <v>48.8</v>
       </c>
+      <c r="F125" s="35" t="n">
+        <v>48.6</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="35" t="inlineStr">
@@ -18294,42 +18680,51 @@
       <c r="E126" s="35" t="n">
         <v>48.5</v>
       </c>
+      <c r="F126" s="35" t="n">
+        <v>48.5</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="35" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="B127" s="35" t="n">
-        <v>48.5</v>
+        <v>46.8</v>
       </c>
       <c r="C127" s="35" t="n">
-        <v>51.5</v>
+        <v>45.8</v>
       </c>
       <c r="D127" s="35" t="n">
-        <v>49.3</v>
+        <v>47.4</v>
       </c>
       <c r="E127" s="35" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
+      </c>
+      <c r="F127" s="35" t="n">
+        <v>47.3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="35" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="B128" s="35" t="n">
-        <v>46.8</v>
+        <v>48.5</v>
       </c>
       <c r="C128" s="35" t="n">
-        <v>45.8</v>
+        <v>51.5</v>
       </c>
       <c r="D128" s="35" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="E128" s="35" t="n">
         <v>47.4</v>
       </c>
-      <c r="E128" s="35" t="n">
+      <c r="F128" s="35" t="n">
         <v>47.3</v>
       </c>
     </row>
@@ -18351,80 +18746,95 @@
       <c r="E129" s="35" t="n">
         <v>46.8</v>
       </c>
+      <c r="F129" s="35" t="n">
+        <v>46.4</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="35" t="inlineStr">
         <is>
-          <t>Sam Houston</t>
+          <t>Kent State</t>
         </is>
       </c>
       <c r="B130" s="35" t="n">
-        <v>41.1</v>
+        <v>45.6</v>
       </c>
       <c r="C130" s="35" t="n">
-        <v>41.7</v>
+        <v>47.5</v>
       </c>
       <c r="D130" s="35" t="n">
-        <v>47</v>
+        <v>45.5</v>
       </c>
       <c r="E130" s="35" t="n">
-        <v>46.7</v>
+        <v>46.3</v>
+      </c>
+      <c r="F130" s="35" t="n">
+        <v>46.3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="35" t="inlineStr">
         <is>
-          <t>Kent State</t>
+          <t>Sam Houston</t>
         </is>
       </c>
       <c r="B131" s="35" t="n">
-        <v>45.6</v>
+        <v>41.1</v>
       </c>
       <c r="C131" s="35" t="n">
-        <v>47.5</v>
+        <v>41.1</v>
       </c>
       <c r="D131" s="35" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="E131" s="35" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
+      </c>
+      <c r="F131" s="35" t="n">
+        <v>46.2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="35" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Bowling Green</t>
         </is>
       </c>
       <c r="B132" s="35" t="n">
-        <v>37.6</v>
+        <v>48.8</v>
       </c>
       <c r="C132" s="35" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="D132" s="35" t="n">
-        <v>41.1</v>
+        <v>43.7</v>
       </c>
       <c r="E132" s="35" t="n">
-        <v>45.6</v>
+        <v>45.4</v>
+      </c>
+      <c r="F132" s="35" t="n">
+        <v>45.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="35" t="inlineStr">
         <is>
-          <t>Bowling Green</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B133" s="35" t="n">
-        <v>48.8</v>
+        <v>37.6</v>
       </c>
       <c r="C133" s="35" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="D133" s="35" t="n">
-        <v>43.7</v>
+        <v>41.1</v>
       </c>
       <c r="E133" s="35" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F133" s="35" t="n">
         <v>45.4</v>
       </c>
     </row>
@@ -18446,6 +18856,9 @@
       <c r="E134" s="35" t="n">
         <v>43.3</v>
       </c>
+      <c r="F134" s="35" t="n">
+        <v>43.3</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="35" t="inlineStr">
@@ -18465,6 +18878,9 @@
       <c r="E135" s="35" t="n">
         <v>42.6</v>
       </c>
+      <c r="F135" s="35" t="n">
+        <v>42.6</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="35" t="inlineStr">
@@ -18484,6 +18900,9 @@
       <c r="E136" s="35" t="n">
         <v>42.3</v>
       </c>
+      <c r="F136" s="35" t="n">
+        <v>42.3</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="35" t="inlineStr">
@@ -18503,6 +18922,9 @@
       <c r="E137" s="35" t="n">
         <v>41.2</v>
       </c>
+      <c r="F137" s="35" t="n">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="35" t="inlineStr">
@@ -18522,6 +18944,9 @@
       <c r="E138" s="35" t="n">
         <v>40.7</v>
       </c>
+      <c r="F138" s="35" t="n">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="35" t="inlineStr">
@@ -18540,6 +18965,9 @@
       </c>
       <c r="E139" s="35" t="n">
         <v>37.3</v>
+      </c>
+      <c r="F139" s="35" t="n">
+        <v>37.2</v>
       </c>
     </row>
   </sheetData>
@@ -20895,10 +21323,10 @@
         <v>1622.5</v>
       </c>
       <c r="F24" s="35" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" s="42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -21111,10 +21539,10 @@
         <v>1415.3</v>
       </c>
       <c r="F32" s="35" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G32" s="42" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33">
@@ -21714,34 +22142,34 @@
     <row r="55">
       <c r="A55" s="35" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="B55" s="35" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C55" s="35" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="D55" s="35" t="n">
         <v>50</v>
       </c>
       <c r="E55" s="35" t="n">
-        <v>1656.2</v>
+        <v>1625.5</v>
       </c>
       <c r="F55" s="35" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G55" s="35" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="35" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="B56" s="35" t="inlineStr">
@@ -21756,19 +22184,19 @@
         <v>51</v>
       </c>
       <c r="E56" s="35" t="n">
-        <v>1597.5</v>
+        <v>1656.2</v>
       </c>
       <c r="F56" s="35" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G56" s="35" t="n">
-        <v>2</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="35" t="inlineStr">
         <is>
-          <t>App State</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B57" s="35" t="inlineStr">
@@ -21777,84 +22205,84 @@
         </is>
       </c>
       <c r="C57" s="35" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="D57" s="35" t="n">
         <v>52</v>
       </c>
       <c r="E57" s="35" t="n">
-        <v>1505.1</v>
+        <v>1597.5</v>
       </c>
       <c r="F57" s="35" t="n">
-        <v>87</v>
-      </c>
-      <c r="G57" s="42" t="n">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="G57" s="35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="35" t="inlineStr">
         <is>
-          <t>Idaho State</t>
+          <t>App State</t>
         </is>
       </c>
       <c r="B58" s="35" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C58" s="35" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="D58" s="35" t="n">
         <v>53</v>
       </c>
       <c r="E58" s="35" t="n">
-        <v>1459.7</v>
+        <v>1505.1</v>
       </c>
       <c r="F58" s="35" t="n">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="G58" s="42" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="35" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Idaho State</t>
         </is>
       </c>
       <c r="B59" s="35" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="C59" s="35" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="D59" s="35" t="n">
         <v>54</v>
       </c>
       <c r="E59" s="35" t="n">
-        <v>1596.4</v>
+        <v>1459.7</v>
       </c>
       <c r="F59" s="35" t="n">
-        <v>54</v>
-      </c>
-      <c r="G59" s="35" t="n">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="G59" s="42" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="35" t="inlineStr">
         <is>
-          <t>Montana State</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="B60" s="35" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C60" s="35" t="n">
@@ -21864,24 +22292,24 @@
         <v>55</v>
       </c>
       <c r="E60" s="35" t="n">
-        <v>1505.4</v>
+        <v>1596.4</v>
       </c>
       <c r="F60" s="35" t="n">
-        <v>86</v>
-      </c>
-      <c r="G60" s="42" t="n">
-        <v>31</v>
+        <v>54</v>
+      </c>
+      <c r="G60" s="35" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="35" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Montana State</t>
         </is>
       </c>
       <c r="B61" s="35" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="C61" s="35" t="n">
@@ -21891,19 +22319,19 @@
         <v>56</v>
       </c>
       <c r="E61" s="35" t="n">
-        <v>1622.7</v>
+        <v>1505.4</v>
       </c>
       <c r="F61" s="35" t="n">
-        <v>37</v>
-      </c>
-      <c r="G61" s="35" t="n">
-        <v>-19</v>
+        <v>85</v>
+      </c>
+      <c r="G61" s="42" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="35" t="inlineStr">
         <is>
-          <t>Georgia State</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B62" s="35" t="inlineStr">
@@ -21918,132 +22346,132 @@
         <v>57</v>
       </c>
       <c r="E62" s="35" t="n">
-        <v>1440.6</v>
+        <v>1622.7</v>
       </c>
       <c r="F62" s="35" t="n">
-        <v>143</v>
-      </c>
-      <c r="G62" s="42" t="n">
-        <v>86</v>
+        <v>38</v>
+      </c>
+      <c r="G62" s="35" t="n">
+        <v>-19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="inlineStr">
         <is>
-          <t>Tarleton State</t>
+          <t>Georgia State</t>
         </is>
       </c>
       <c r="B63" s="35" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C63" s="35" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="D63" s="35" t="n">
         <v>58</v>
       </c>
       <c r="E63" s="35" t="n">
-        <v>1505.7</v>
+        <v>1440.6</v>
       </c>
       <c r="F63" s="35" t="n">
+        <v>143</v>
+      </c>
+      <c r="G63" s="42" t="n">
         <v>85</v>
-      </c>
-      <c r="G63" s="42" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Tarleton State</t>
         </is>
       </c>
       <c r="B64" s="35" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="C64" s="35" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="D64" s="35" t="n">
         <v>59</v>
       </c>
       <c r="E64" s="35" t="n">
-        <v>1461.8</v>
+        <v>1505.7</v>
       </c>
       <c r="F64" s="35" t="n">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="G64" s="42" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="35" t="inlineStr">
         <is>
-          <t>Illinois State</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C65" s="35" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="D65" s="35" t="n">
         <v>60</v>
       </c>
       <c r="E65" s="35" t="n">
-        <v>1460.9</v>
+        <v>1461.8</v>
       </c>
       <c r="F65" s="35" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G65" s="42" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="35" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Illinois State</t>
         </is>
       </c>
       <c r="B66" s="35" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="C66" s="35" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="D66" s="35" t="n">
         <v>61</v>
       </c>
       <c r="E66" s="35" t="n">
-        <v>1640</v>
+        <v>1460.9</v>
       </c>
       <c r="F66" s="35" t="n">
-        <v>32</v>
-      </c>
-      <c r="G66" s="35" t="n">
-        <v>-29</v>
+        <v>116</v>
+      </c>
+      <c r="G66" s="42" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="35" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B67" s="35" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C67" s="35" t="n">
@@ -22053,46 +22481,46 @@
         <v>62</v>
       </c>
       <c r="E67" s="35" t="n">
-        <v>1503.2</v>
+        <v>1640</v>
       </c>
       <c r="F67" s="35" t="n">
-        <v>89</v>
-      </c>
-      <c r="G67" s="42" t="n">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="G67" s="35" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="35" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="B68" s="35" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C68" s="35" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="D68" s="35" t="n">
         <v>63</v>
       </c>
       <c r="E68" s="35" t="n">
-        <v>1553</v>
+        <v>1503.2</v>
       </c>
       <c r="F68" s="35" t="n">
-        <v>72</v>
-      </c>
-      <c r="G68" s="35" t="n">
-        <v>9</v>
+        <v>88</v>
+      </c>
+      <c r="G68" s="42" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="35" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B69" s="35" t="inlineStr">
@@ -22101,25 +22529,25 @@
         </is>
       </c>
       <c r="C69" s="35" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="D69" s="35" t="n">
         <v>64</v>
       </c>
       <c r="E69" s="35" t="n">
-        <v>1515.8</v>
+        <v>1553</v>
       </c>
       <c r="F69" s="35" t="n">
-        <v>83</v>
-      </c>
-      <c r="G69" s="42" t="n">
-        <v>19</v>
+        <v>72</v>
+      </c>
+      <c r="G69" s="35" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="35" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B70" s="35" t="inlineStr">
@@ -22128,25 +22556,25 @@
         </is>
       </c>
       <c r="C70" s="35" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D70" s="35" t="n">
         <v>65</v>
       </c>
       <c r="E70" s="35" t="n">
-        <v>1667.5</v>
+        <v>1515.8</v>
       </c>
       <c r="F70" s="35" t="n">
-        <v>24</v>
-      </c>
-      <c r="G70" s="35" t="n">
-        <v>-41</v>
+        <v>82</v>
+      </c>
+      <c r="G70" s="42" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B71" s="35" t="inlineStr">
@@ -22161,24 +22589,24 @@
         <v>66</v>
       </c>
       <c r="E71" s="35" t="n">
-        <v>1565.6</v>
+        <v>1667.5</v>
       </c>
       <c r="F71" s="35" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="G71" s="35" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="35" t="inlineStr">
         <is>
-          <t>UNLV</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="B72" s="35" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C72" s="35" t="n">
@@ -22188,73 +22616,73 @@
         <v>67</v>
       </c>
       <c r="E72" s="35" t="n">
-        <v>1606.6</v>
+        <v>1565.6</v>
       </c>
       <c r="F72" s="35" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G72" s="35" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="35" t="inlineStr">
         <is>
-          <t>The Citadel</t>
+          <t>UNLV</t>
         </is>
       </c>
       <c r="B73" s="35" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C73" s="35" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="D73" s="35" t="n">
         <v>68</v>
       </c>
       <c r="E73" s="35" t="n">
-        <v>1459.6</v>
+        <v>1606.6</v>
       </c>
       <c r="F73" s="35" t="n">
-        <v>119</v>
-      </c>
-      <c r="G73" s="42" t="n">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="G73" s="35" t="n">
+        <v>-23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="35" t="inlineStr">
         <is>
-          <t>Arizona State</t>
+          <t>The Citadel</t>
         </is>
       </c>
       <c r="B74" s="35" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="C74" s="35" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="D74" s="35" t="n">
         <v>69</v>
       </c>
       <c r="E74" s="35" t="n">
-        <v>1606</v>
+        <v>1459.6</v>
       </c>
       <c r="F74" s="35" t="n">
-        <v>47</v>
-      </c>
-      <c r="G74" s="35" t="n">
-        <v>-22</v>
+        <v>119</v>
+      </c>
+      <c r="G74" s="42" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="35" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Arizona State</t>
         </is>
       </c>
       <c r="B75" s="35" t="inlineStr">
@@ -22263,57 +22691,57 @@
         </is>
       </c>
       <c r="C75" s="35" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="D75" s="35" t="n">
         <v>70</v>
       </c>
       <c r="E75" s="35" t="n">
-        <v>1573.7</v>
+        <v>1606</v>
       </c>
       <c r="F75" s="35" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G75" s="35" t="n">
-        <v>-6</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="35" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="B76" s="35" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C76" s="35" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="D76" s="35" t="n">
         <v>71</v>
       </c>
       <c r="E76" s="35" t="n">
-        <v>1600.6</v>
+        <v>1573.7</v>
       </c>
       <c r="F76" s="35" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="G76" s="35" t="n">
-        <v>-20</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="35" t="inlineStr">
         <is>
-          <t>Jacksonville State</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="B77" s="35" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C77" s="35" t="n">
@@ -22323,19 +22751,19 @@
         <v>72</v>
       </c>
       <c r="E77" s="35" t="n">
-        <v>1579.4</v>
+        <v>1600.6</v>
       </c>
       <c r="F77" s="35" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G77" s="35" t="n">
-        <v>-11</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="35" t="inlineStr">
         <is>
-          <t>Michigan State</t>
+          <t>Jacksonville State</t>
         </is>
       </c>
       <c r="B78" s="35" t="inlineStr">
@@ -22344,46 +22772,46 @@
         </is>
       </c>
       <c r="C78" s="35" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="D78" s="35" t="n">
         <v>73</v>
       </c>
       <c r="E78" s="35" t="n">
-        <v>1471.5</v>
+        <v>1579.4</v>
       </c>
       <c r="F78" s="35" t="n">
-        <v>110</v>
-      </c>
-      <c r="G78" s="42" t="n">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="G78" s="35" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="35" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Michigan State</t>
         </is>
       </c>
       <c r="B79" s="35" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C79" s="35" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="D79" s="35" t="n">
         <v>74</v>
       </c>
       <c r="E79" s="35" t="n">
-        <v>1430.6</v>
+        <v>1471.5</v>
       </c>
       <c r="F79" s="35" t="n">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="G79" s="42" t="n">
-        <v>87</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80">
@@ -22434,10 +22862,10 @@
         <v>1502.2</v>
       </c>
       <c r="F81" s="35" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G81" s="35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -22470,7 +22898,7 @@
     <row r="83">
       <c r="A83" s="35" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Utah State</t>
         </is>
       </c>
       <c r="B83" s="35" t="inlineStr">
@@ -22485,100 +22913,100 @@
         <v>78</v>
       </c>
       <c r="E83" s="35" t="n">
-        <v>1621.2</v>
+        <v>1466.7</v>
       </c>
       <c r="F83" s="35" t="n">
-        <v>39</v>
-      </c>
-      <c r="G83" s="35" t="n">
-        <v>-39</v>
+        <v>113</v>
+      </c>
+      <c r="G83" s="42" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="35" t="inlineStr">
         <is>
-          <t>Utah State</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="B84" s="35" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C84" s="35" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="D84" s="35" t="n">
         <v>79</v>
       </c>
       <c r="E84" s="35" t="n">
-        <v>1466.7</v>
+        <v>1638.9</v>
       </c>
       <c r="F84" s="35" t="n">
-        <v>113</v>
-      </c>
-      <c r="G84" s="42" t="n">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="G84" s="35" t="n">
+        <v>-46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="35" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Army</t>
         </is>
       </c>
       <c r="B85" s="35" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C85" s="35" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="D85" s="35" t="n">
         <v>80</v>
       </c>
       <c r="E85" s="35" t="n">
-        <v>1638.9</v>
+        <v>1610.1</v>
       </c>
       <c r="F85" s="35" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G85" s="35" t="n">
-        <v>-47</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="35" t="inlineStr">
         <is>
-          <t>Army</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="B86" s="35" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C86" s="35" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="D86" s="35" t="n">
         <v>81</v>
       </c>
       <c r="E86" s="35" t="n">
-        <v>1610.1</v>
+        <v>1460</v>
       </c>
       <c r="F86" s="35" t="n">
-        <v>43</v>
-      </c>
-      <c r="G86" s="35" t="n">
-        <v>-38</v>
+        <v>117</v>
+      </c>
+      <c r="G86" s="42" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="35" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Texas State</t>
         </is>
       </c>
       <c r="B87" s="35" t="inlineStr">
@@ -22587,25 +23015,25 @@
         </is>
       </c>
       <c r="C87" s="35" t="n">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="D87" s="35" t="n">
         <v>82</v>
       </c>
       <c r="E87" s="35" t="n">
-        <v>1460</v>
+        <v>1588.2</v>
       </c>
       <c r="F87" s="35" t="n">
-        <v>117</v>
-      </c>
-      <c r="G87" s="42" t="n">
-        <v>35</v>
+        <v>58</v>
+      </c>
+      <c r="G87" s="35" t="n">
+        <v>-24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="35" t="inlineStr">
         <is>
-          <t>Texas State</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="B88" s="35" t="inlineStr">
@@ -22614,25 +23042,25 @@
         </is>
       </c>
       <c r="C88" s="35" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D88" s="35" t="n">
         <v>83</v>
       </c>
       <c r="E88" s="35" t="n">
-        <v>1588.2</v>
+        <v>1658.8</v>
       </c>
       <c r="F88" s="35" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="G88" s="35" t="n">
-        <v>-25</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="35" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B89" s="35" t="inlineStr">
@@ -22641,25 +23069,25 @@
         </is>
       </c>
       <c r="C89" s="35" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="D89" s="35" t="n">
         <v>84</v>
       </c>
       <c r="E89" s="35" t="n">
-        <v>1658.8</v>
+        <v>1504.3</v>
       </c>
       <c r="F89" s="35" t="n">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="G89" s="35" t="n">
-        <v>-59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="35" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>South Alabama</t>
         </is>
       </c>
       <c r="B90" s="35" t="inlineStr">
@@ -22668,25 +23096,25 @@
         </is>
       </c>
       <c r="C90" s="35" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="D90" s="35" t="n">
         <v>85</v>
       </c>
       <c r="E90" s="35" t="n">
-        <v>1504.3</v>
+        <v>1493.6</v>
       </c>
       <c r="F90" s="35" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G90" s="35" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="35" t="inlineStr">
         <is>
-          <t>South Alabama</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="B91" s="35" t="inlineStr">
@@ -22701,19 +23129,19 @@
         <v>86</v>
       </c>
       <c r="E91" s="35" t="n">
-        <v>1493.6</v>
+        <v>1592.5</v>
       </c>
       <c r="F91" s="35" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G91" s="35" t="n">
-        <v>9</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="35" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>East Carolina</t>
         </is>
       </c>
       <c r="B92" s="35" t="inlineStr">
@@ -22722,79 +23150,79 @@
         </is>
       </c>
       <c r="C92" s="35" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="D92" s="35" t="n">
         <v>87</v>
       </c>
       <c r="E92" s="35" t="n">
-        <v>1592.5</v>
+        <v>1593.3</v>
       </c>
       <c r="F92" s="35" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G92" s="35" t="n">
-        <v>-30</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="35" t="inlineStr">
         <is>
-          <t>East Carolina</t>
+          <t>SE Louisiana</t>
         </is>
       </c>
       <c r="B93" s="35" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C93" s="35" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D93" s="35" t="n">
         <v>88</v>
       </c>
       <c r="E93" s="35" t="n">
-        <v>1593.3</v>
+        <v>1412.1</v>
       </c>
       <c r="F93" s="35" t="n">
-        <v>55</v>
-      </c>
-      <c r="G93" s="35" t="n">
-        <v>-33</v>
+        <v>202</v>
+      </c>
+      <c r="G93" s="42" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="35" t="inlineStr">
         <is>
-          <t>SE Louisiana</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B94" s="35" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C94" s="35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="D94" s="35" t="n">
         <v>89</v>
       </c>
       <c r="E94" s="35" t="n">
-        <v>1412.1</v>
+        <v>1496</v>
       </c>
       <c r="F94" s="35" t="n">
-        <v>201</v>
-      </c>
-      <c r="G94" s="42" t="n">
-        <v>112</v>
+        <v>93</v>
+      </c>
+      <c r="G94" s="35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="35" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Arkansas State</t>
         </is>
       </c>
       <c r="B95" s="35" t="inlineStr">
@@ -22803,25 +23231,25 @@
         </is>
       </c>
       <c r="C95" s="35" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="D95" s="35" t="n">
         <v>90</v>
       </c>
       <c r="E95" s="35" t="n">
-        <v>1496</v>
+        <v>1509.2</v>
       </c>
       <c r="F95" s="35" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G95" s="35" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="35" t="inlineStr">
         <is>
-          <t>Arkansas State</t>
+          <t>Western Michigan</t>
         </is>
       </c>
       <c r="B96" s="35" t="inlineStr">
@@ -22836,24 +23264,24 @@
         <v>91</v>
       </c>
       <c r="E96" s="35" t="n">
-        <v>1509.2</v>
+        <v>1579.5</v>
       </c>
       <c r="F96" s="35" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="G96" s="35" t="n">
-        <v>-7</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="35" t="inlineStr">
         <is>
-          <t>Western Michigan</t>
+          <t>Tennessee State</t>
         </is>
       </c>
       <c r="B97" s="35" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C97" s="35" t="n">
@@ -22863,127 +23291,127 @@
         <v>92</v>
       </c>
       <c r="E97" s="35" t="n">
-        <v>1579.5</v>
+        <v>1447.4</v>
       </c>
       <c r="F97" s="35" t="n">
-        <v>60</v>
-      </c>
-      <c r="G97" s="35" t="n">
-        <v>-32</v>
+        <v>132</v>
+      </c>
+      <c r="G97" s="42" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="35" t="inlineStr">
         <is>
-          <t>Tennessee State</t>
+          <t>Miami (OH)</t>
         </is>
       </c>
       <c r="B98" s="35" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C98" s="35" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="D98" s="35" t="n">
         <v>93</v>
       </c>
       <c r="E98" s="35" t="n">
-        <v>1447.4</v>
+        <v>1536.7</v>
       </c>
       <c r="F98" s="35" t="n">
-        <v>132</v>
-      </c>
-      <c r="G98" s="42" t="n">
-        <v>39</v>
+        <v>76</v>
+      </c>
+      <c r="G98" s="35" t="n">
+        <v>-17</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="35" t="inlineStr">
         <is>
-          <t>Miami (OH)</t>
+          <t>Florida A&amp;M</t>
         </is>
       </c>
       <c r="B99" s="35" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C99" s="35" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="D99" s="35" t="n">
         <v>94</v>
       </c>
       <c r="E99" s="35" t="n">
-        <v>1536.7</v>
+        <v>1414.3</v>
       </c>
       <c r="F99" s="35" t="n">
-        <v>76</v>
-      </c>
-      <c r="G99" s="35" t="n">
-        <v>-18</v>
+        <v>191</v>
+      </c>
+      <c r="G99" s="42" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="35" t="inlineStr">
         <is>
-          <t>Florida A&amp;M</t>
+          <t>Central Michigan</t>
         </is>
       </c>
       <c r="B100" s="35" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C100" s="35" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="D100" s="35" t="n">
         <v>95</v>
       </c>
       <c r="E100" s="35" t="n">
-        <v>1414.3</v>
+        <v>1466.3</v>
       </c>
       <c r="F100" s="35" t="n">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="G100" s="42" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="35" t="inlineStr">
         <is>
-          <t>Central Michigan</t>
+          <t>Abilene Christian</t>
         </is>
       </c>
       <c r="B101" s="35" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C101" s="35" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="D101" s="35" t="n">
         <v>96</v>
       </c>
       <c r="E101" s="35" t="n">
-        <v>1466.3</v>
+        <v>1414.3</v>
       </c>
       <c r="F101" s="35" t="n">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="G101" s="42" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="35" t="inlineStr">
         <is>
-          <t>Abilene Christian</t>
+          <t>UC Davis</t>
         </is>
       </c>
       <c r="B102" s="35" t="inlineStr">
@@ -22992,25 +23420,25 @@
         </is>
       </c>
       <c r="C102" s="35" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="D102" s="35" t="n">
         <v>97</v>
       </c>
       <c r="E102" s="35" t="n">
-        <v>1414.3</v>
+        <v>1449.9</v>
       </c>
       <c r="F102" s="35" t="n">
-        <v>191</v>
+        <v>129</v>
       </c>
       <c r="G102" s="42" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="35" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B103" s="35" t="inlineStr">
@@ -23025,19 +23453,19 @@
         <v>98</v>
       </c>
       <c r="E103" s="35" t="n">
-        <v>1449.9</v>
+        <v>1459.1</v>
       </c>
       <c r="F103" s="35" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G103" s="42" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="35" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="B104" s="35" t="inlineStr">
@@ -23052,24 +23480,24 @@
         <v>99</v>
       </c>
       <c r="E104" s="35" t="n">
-        <v>1459.1</v>
+        <v>1411.5</v>
       </c>
       <c r="F104" s="35" t="n">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="G104" s="42" t="n">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="35" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>San José State</t>
         </is>
       </c>
       <c r="B105" s="35" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C105" s="35" t="n">
@@ -23079,40 +23507,40 @@
         <v>100</v>
       </c>
       <c r="E105" s="35" t="n">
-        <v>1411.5</v>
+        <v>1428.8</v>
       </c>
       <c r="F105" s="35" t="n">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="G105" s="42" t="n">
-        <v>103</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="35" t="inlineStr">
         <is>
-          <t>San José State</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="B106" s="35" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C106" s="35" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="D106" s="35" t="n">
         <v>101</v>
       </c>
       <c r="E106" s="35" t="n">
-        <v>1428.8</v>
+        <v>1426.3</v>
       </c>
       <c r="F106" s="35" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G106" s="42" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107">
@@ -23244,10 +23672,10 @@
         <v>1406.9</v>
       </c>
       <c r="F111" s="35" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G111" s="42" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112">
@@ -23298,10 +23726,10 @@
         <v>1519.1</v>
       </c>
       <c r="F113" s="35" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G113" s="35" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="114">
@@ -23460,10 +23888,10 @@
         <v>1412.3</v>
       </c>
       <c r="F119" s="35" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G119" s="42" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="120">
@@ -23487,10 +23915,10 @@
         <v>1429.6</v>
       </c>
       <c r="F120" s="35" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G120" s="42" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="121">
@@ -23568,10 +23996,10 @@
         <v>1427.9</v>
       </c>
       <c r="F123" s="35" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G123" s="42" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124">
@@ -23595,10 +24023,10 @@
         <v>1422.7</v>
       </c>
       <c r="F124" s="35" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G124" s="42" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125">
@@ -23730,10 +24158,10 @@
         <v>1414.2</v>
       </c>
       <c r="F129" s="35" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G129" s="42" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130">
@@ -23757,10 +24185,10 @@
         <v>1418.5</v>
       </c>
       <c r="F130" s="35" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G130" s="42" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="131">
@@ -23811,10 +24239,10 @@
         <v>1422.8</v>
       </c>
       <c r="F132" s="35" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G132" s="42" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="133">
@@ -23892,10 +24320,10 @@
         <v>1429.2</v>
       </c>
       <c r="F135" s="35" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G135" s="42" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136">
@@ -23973,10 +24401,10 @@
         <v>1405.5</v>
       </c>
       <c r="F138" s="35" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G138" s="42" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="139">
@@ -24000,10 +24428,10 @@
         <v>1413.9</v>
       </c>
       <c r="F139" s="35" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G139" s="42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140">
@@ -24027,10 +24455,10 @@
         <v>1403.3</v>
       </c>
       <c r="F140" s="35" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G140" s="42" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="141">
@@ -24054,10 +24482,10 @@
         <v>1409.5</v>
       </c>
       <c r="F141" s="35" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G141" s="42" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="142">
@@ -24081,10 +24509,10 @@
         <v>1428.8</v>
       </c>
       <c r="F142" s="35" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G142" s="42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="143">
@@ -24108,10 +24536,10 @@
         <v>1420.7</v>
       </c>
       <c r="F143" s="35" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G143" s="42" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144">
@@ -24162,10 +24590,10 @@
         <v>1491.6</v>
       </c>
       <c r="F145" s="35" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G145" s="35" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="146">
@@ -24189,10 +24617,10 @@
         <v>1411.7</v>
       </c>
       <c r="F146" s="35" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G146" s="42" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="147">
@@ -24243,10 +24671,10 @@
         <v>1412.8</v>
       </c>
       <c r="F148" s="35" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G148" s="42" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149">
@@ -24297,10 +24725,10 @@
         <v>1398.8</v>
       </c>
       <c r="F150" s="35" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G150" s="42" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="151">
@@ -24378,10 +24806,10 @@
         <v>1414.9</v>
       </c>
       <c r="F153" s="35" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G153" s="42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="154">
@@ -24432,10 +24860,10 @@
         <v>1488.5</v>
       </c>
       <c r="F155" s="35" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G155" s="35" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="156">
@@ -24459,10 +24887,10 @@
         <v>1429.6</v>
       </c>
       <c r="F156" s="35" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G156" s="35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157">
@@ -24486,10 +24914,10 @@
         <v>1387.5</v>
       </c>
       <c r="F157" s="35" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G157" s="42" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="158">
@@ -24513,10 +24941,10 @@
         <v>1400.8</v>
       </c>
       <c r="F158" s="35" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G158" s="42" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="159">
@@ -24675,10 +25103,10 @@
         <v>1520.2</v>
       </c>
       <c r="F164" s="35" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G164" s="35" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
     </row>
     <row r="165">
@@ -24702,10 +25130,10 @@
         <v>1402.8</v>
       </c>
       <c r="F165" s="35" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G165" s="42" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="166">
@@ -24729,10 +25157,10 @@
         <v>1417.1</v>
       </c>
       <c r="F166" s="35" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G166" s="42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167">
@@ -24783,10 +25211,10 @@
         <v>1391.8</v>
       </c>
       <c r="F168" s="35" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G168" s="42" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="169">
@@ -24810,10 +25238,10 @@
         <v>1411.1</v>
       </c>
       <c r="F169" s="35" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G169" s="42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="170">
@@ -24891,10 +25319,10 @@
         <v>1422</v>
       </c>
       <c r="F172" s="35" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G172" s="35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173">
@@ -24945,10 +25373,10 @@
         <v>1404.2</v>
       </c>
       <c r="F174" s="35" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G174" s="42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="175">
@@ -24972,10 +25400,10 @@
         <v>1413.6</v>
       </c>
       <c r="F175" s="35" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G175" s="42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176">
@@ -24999,10 +25427,10 @@
         <v>1624</v>
       </c>
       <c r="F176" s="35" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G176" s="35" t="n">
-        <v>-135</v>
+        <v>-134</v>
       </c>
     </row>
     <row r="177">
@@ -25026,10 +25454,10 @@
         <v>1418.7</v>
       </c>
       <c r="F177" s="35" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G177" s="35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178">
@@ -25053,10 +25481,10 @@
         <v>1420.6</v>
       </c>
       <c r="F178" s="35" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G178" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179">
@@ -25080,10 +25508,10 @@
         <v>1416.7</v>
       </c>
       <c r="F179" s="35" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G179" s="35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180">
@@ -25134,10 +25562,10 @@
         <v>1393.9</v>
       </c>
       <c r="F181" s="35" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G181" s="42" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="182">
@@ -25188,10 +25616,10 @@
         <v>1412.2</v>
       </c>
       <c r="F183" s="35" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G183" s="42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184">
@@ -25242,10 +25670,10 @@
         <v>1388</v>
       </c>
       <c r="F185" s="35" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G185" s="42" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="186">
@@ -25269,10 +25697,10 @@
         <v>1395</v>
       </c>
       <c r="F186" s="35" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G186" s="42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187">
@@ -25323,10 +25751,10 @@
         <v>1417.9</v>
       </c>
       <c r="F188" s="35" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G188" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -25350,10 +25778,10 @@
         <v>1397.7</v>
       </c>
       <c r="F189" s="35" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G189" s="42" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="190">
@@ -25377,10 +25805,10 @@
         <v>1501.2</v>
       </c>
       <c r="F190" s="35" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G190" s="35" t="n">
-        <v>-94</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="191">
@@ -25404,10 +25832,10 @@
         <v>1413.3</v>
       </c>
       <c r="F191" s="35" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G191" s="35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192">
@@ -25566,43 +25994,43 @@
         <v>1427.1</v>
       </c>
       <c r="F197" s="35" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G197" s="35" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="35" t="inlineStr">
         <is>
-          <t>Western Kentucky</t>
+          <t>Gardner-Webb</t>
         </is>
       </c>
       <c r="B198" s="35" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C198" s="35" t="n">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
       <c r="D198" s="35" t="n">
         <v>193</v>
       </c>
       <c r="E198" s="35" t="n">
-        <v>1521.5</v>
+        <v>1421.6</v>
       </c>
       <c r="F198" s="35" t="n">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="G198" s="35" t="n">
-        <v>-114</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="35" t="inlineStr">
         <is>
-          <t>Gardner-Webb</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B199" s="35" t="inlineStr">
@@ -25611,25 +26039,25 @@
         </is>
       </c>
       <c r="C199" s="35" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="D199" s="35" t="n">
         <v>194</v>
       </c>
       <c r="E199" s="35" t="n">
-        <v>1421.6</v>
+        <v>1501</v>
       </c>
       <c r="F199" s="35" t="n">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="G199" s="35" t="n">
-        <v>-16</v>
+        <v>-103</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="35" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Houston Christian</t>
         </is>
       </c>
       <c r="B200" s="35" t="inlineStr">
@@ -25638,25 +26066,25 @@
         </is>
       </c>
       <c r="C200" s="35" t="n">
-        <v>-0.79</v>
+        <v>-0.8</v>
       </c>
       <c r="D200" s="35" t="n">
         <v>195</v>
       </c>
       <c r="E200" s="35" t="n">
-        <v>1501</v>
+        <v>1392.6</v>
       </c>
       <c r="F200" s="35" t="n">
-        <v>92</v>
-      </c>
-      <c r="G200" s="35" t="n">
-        <v>-103</v>
+        <v>230</v>
+      </c>
+      <c r="G200" s="42" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="35" t="inlineStr">
         <is>
-          <t>Houston Christian</t>
+          <t>Duquesne</t>
         </is>
       </c>
       <c r="B201" s="35" t="inlineStr">
@@ -25671,19 +26099,19 @@
         <v>196</v>
       </c>
       <c r="E201" s="35" t="n">
-        <v>1392.6</v>
+        <v>1359.3</v>
       </c>
       <c r="F201" s="35" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="G201" s="42" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="35" t="inlineStr">
         <is>
-          <t>Duquesne</t>
+          <t>West Georgia</t>
         </is>
       </c>
       <c r="B202" s="35" t="inlineStr">
@@ -25692,25 +26120,25 @@
         </is>
       </c>
       <c r="C202" s="35" t="n">
-        <v>-0.8</v>
+        <v>-0.82</v>
       </c>
       <c r="D202" s="35" t="n">
         <v>197</v>
       </c>
       <c r="E202" s="35" t="n">
-        <v>1359.3</v>
+        <v>1442.3</v>
       </c>
       <c r="F202" s="35" t="n">
-        <v>247</v>
-      </c>
-      <c r="G202" s="42" t="n">
-        <v>50</v>
+        <v>141</v>
+      </c>
+      <c r="G202" s="35" t="n">
+        <v>-56</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="35" t="inlineStr">
         <is>
-          <t>West Georgia</t>
+          <t>Long Island University</t>
         </is>
       </c>
       <c r="B203" s="35" t="inlineStr">
@@ -25719,73 +26147,73 @@
         </is>
       </c>
       <c r="C203" s="35" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="D203" s="35" t="n">
         <v>198</v>
       </c>
       <c r="E203" s="35" t="n">
-        <v>1442.3</v>
+        <v>1409.7</v>
       </c>
       <c r="F203" s="35" t="n">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="G203" s="35" t="n">
-        <v>-57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="35" t="inlineStr">
         <is>
-          <t>Long Island University</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="B204" s="35" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C204" s="35" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="D204" s="35" t="n">
         <v>199</v>
       </c>
       <c r="E204" s="35" t="n">
-        <v>1409.7</v>
+        <v>1413.7</v>
       </c>
       <c r="F204" s="35" t="n">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G204" s="35" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="35" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>New Mexico State</t>
         </is>
       </c>
       <c r="B205" s="35" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C205" s="35" t="n">
-        <v>-0.84</v>
+        <v>-0.88</v>
       </c>
       <c r="D205" s="35" t="n">
         <v>200</v>
       </c>
       <c r="E205" s="35" t="n">
-        <v>1413.7</v>
+        <v>1423</v>
       </c>
       <c r="F205" s="35" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="G205" s="35" t="n">
-        <v>-6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="206">
@@ -25836,10 +26264,10 @@
         <v>1520.6</v>
       </c>
       <c r="F207" s="35" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G207" s="35" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
     </row>
     <row r="208">
@@ -25890,10 +26318,10 @@
         <v>1388.5</v>
       </c>
       <c r="F209" s="35" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G209" s="42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="210">
@@ -26025,10 +26453,10 @@
         <v>1499.6</v>
       </c>
       <c r="F214" s="35" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G214" s="35" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
     </row>
     <row r="215">
@@ -26052,10 +26480,10 @@
         <v>1402.2</v>
       </c>
       <c r="F215" s="35" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G215" s="35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216">
@@ -26079,10 +26507,10 @@
         <v>1399.2</v>
       </c>
       <c r="F216" s="35" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G216" s="35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217">
@@ -26133,10 +26561,10 @@
         <v>1491.5</v>
       </c>
       <c r="F218" s="35" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G218" s="35" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
     </row>
     <row r="219">
@@ -26160,10 +26588,10 @@
         <v>1396.1</v>
       </c>
       <c r="F219" s="35" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G219" s="35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220">
@@ -26187,10 +26615,10 @@
         <v>1427.8</v>
       </c>
       <c r="F220" s="35" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G220" s="35" t="n">
-        <v>-46</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="221">
@@ -26295,10 +26723,10 @@
         <v>1393.2</v>
       </c>
       <c r="F224" s="35" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G224" s="35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225">
@@ -26322,10 +26750,10 @@
         <v>1419.1</v>
       </c>
       <c r="F225" s="35" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G225" s="35" t="n">
-        <v>-39</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="226">
@@ -26376,10 +26804,10 @@
         <v>1406.7</v>
       </c>
       <c r="F227" s="35" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G227" s="35" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="228">
@@ -26457,10 +26885,10 @@
         <v>1389.7</v>
       </c>
       <c r="F230" s="35" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G230" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -26484,16 +26912,16 @@
         <v>1414.7</v>
       </c>
       <c r="F231" s="35" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G231" s="35" t="n">
-        <v>-37</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="35" t="inlineStr">
         <is>
-          <t>New Mexico State</t>
+          <t>Kennesaw State</t>
         </is>
       </c>
       <c r="B232" s="35" t="inlineStr">
@@ -26502,30 +26930,30 @@
         </is>
       </c>
       <c r="C232" s="35" t="n">
-        <v>-1.31</v>
+        <v>-1.34</v>
       </c>
       <c r="D232" s="35" t="n">
         <v>227</v>
       </c>
       <c r="E232" s="35" t="n">
-        <v>1387.2</v>
+        <v>1480.8</v>
       </c>
       <c r="F232" s="35" t="n">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="G232" s="35" t="n">
-        <v>8</v>
+        <v>-126</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="35" t="inlineStr">
         <is>
-          <t>Kennesaw State</t>
+          <t>Western Kentucky</t>
         </is>
       </c>
       <c r="B233" s="35" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="C233" s="35" t="n">
@@ -26535,13 +26963,13 @@
         <v>228</v>
       </c>
       <c r="E233" s="35" t="n">
-        <v>1480.8</v>
+        <v>1485.6</v>
       </c>
       <c r="F233" s="35" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G233" s="35" t="n">
-        <v>-127</v>
+        <v>-128</v>
       </c>
     </row>
     <row r="234">
@@ -26673,10 +27101,10 @@
         <v>1404.9</v>
       </c>
       <c r="F238" s="35" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G238" s="35" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
     </row>
   </sheetData>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -862,11 +862,3470 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.5" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games found for season 2026, week 5.</t>
-        </is>
-      </c>
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D1" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E1" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F1" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G1" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H1" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I1" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J1" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K1" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L1" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M1" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N1" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O1" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P1" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q1" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="F2" s="35" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+      <c r="G2" s="35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="35" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I2" s="40" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J2" s="35" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="K2" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="35" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M2" s="35" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="N2" s="40" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="O2" s="35" t="n"/>
+      <c r="P2" s="35" t="n"/>
+      <c r="Q2" s="35" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>Clemson</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H3" s="35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="J3" s="35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K3" s="35" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="L3" s="35" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="M3" s="35" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="N3" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O3" s="35" t="n"/>
+      <c r="P3" s="35" t="n"/>
+      <c r="Q3" s="35" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>Florida State</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H4" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I4" s="40" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="J4" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="K4" s="35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L4" s="35" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="M4" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="N4" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O4" s="35" t="n"/>
+      <c r="P4" s="35" t="n"/>
+      <c r="Q4" s="35" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
+        <is>
+          <t>NC State</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K5" s="35" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="L5" s="35" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="M5" s="35" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="N5" s="35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O5" s="35" t="n"/>
+      <c r="P5" s="35" t="n"/>
+      <c r="Q5" s="35" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>FBS Independents</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>Notre Dame</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="J6" s="35" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K6" s="35" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L6" s="35" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="M6" s="35" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="N6" s="35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O6" s="35" t="n"/>
+      <c r="P6" s="35" t="n"/>
+      <c r="Q6" s="35" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>Boston College</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>SMU</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="K7" s="35" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L7" s="35" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="M7" s="35" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="N7" s="40" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="O7" s="35" t="n"/>
+      <c r="P7" s="35" t="n"/>
+      <c r="Q7" s="35" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>Stanford</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>Wake Forest</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="K8" s="35" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="L8" s="35" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="M8" s="35" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N8" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O8" s="35" t="n"/>
+      <c r="P8" s="35" t="n"/>
+      <c r="Q8" s="35" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
+        <is>
+          <t>Tulsa</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K9" s="35" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L9" s="35" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="M9" s="35" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="N9" s="35" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O9" s="35" t="n">
+        <v>45</v>
+      </c>
+      <c r="P9" s="35" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="40" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I10" s="40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J10" s="35" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K10" s="35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L10" s="35" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="M10" s="35" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="N10" s="40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O10" s="35" t="n"/>
+      <c r="P10" s="35" t="n"/>
+      <c r="Q10" s="35" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>SWAC</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>Texas Southern</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Florida Atlantic</t>
+        </is>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>-44.2</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="J11" s="35" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="K11" s="35" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="L11" s="35" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="M11" s="35" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="N11" s="40" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="O11" s="35" t="n"/>
+      <c r="P11" s="35" t="n"/>
+      <c r="Q11" s="35" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>UTSA</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="J12" s="35" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K12" s="35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L12" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="M12" s="35" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="N12" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="O12" s="35" t="n"/>
+      <c r="P12" s="35" t="n"/>
+      <c r="Q12" s="35" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>South Florida</t>
+        </is>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J13" s="35" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K13" s="35" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="L13" s="35" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="M13" s="35" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="N13" s="40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O13" s="35" t="n"/>
+      <c r="P13" s="35" t="n"/>
+      <c r="Q13" s="35" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>Southern</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>Samford</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>UAB</t>
+        </is>
+      </c>
+      <c r="G14" s="35" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" s="35" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="K14" s="35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L14" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="M14" s="35" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N14" s="40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O14" s="35" t="n"/>
+      <c r="P14" s="35" t="n"/>
+      <c r="Q14" s="35" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>Texas Tech</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L15" s="35" t="n">
+        <v>49</v>
+      </c>
+      <c r="M15" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N15" s="35" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>UCF</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="I16" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L16" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="M16" s="35" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="N16" s="40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>Iowa State</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I17" s="40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="K17" s="35" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="L17" s="35" t="n">
+        <v>49</v>
+      </c>
+      <c r="M17" s="35" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="N17" s="40" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="35" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>Middle Tennessee</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="K18" s="35" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="L18" s="35" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="M18" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N18" s="40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O18" s="35" t="n"/>
+      <c r="P18" s="35" t="n"/>
+      <c r="Q18" s="35" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>BYU</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>TCU</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L19" s="35" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="N19" s="40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O19" s="35" t="n"/>
+      <c r="P19" s="35" t="n"/>
+      <c r="Q19" s="35" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I20" s="35" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K20" s="35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L20" s="35" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="M20" s="35" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="N20" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O20" s="35" t="n"/>
+      <c r="P20" s="35" t="n"/>
+      <c r="Q20" s="35" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Baylor</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Arizona State</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="N21" s="40" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>Purdue</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>Ohio State</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N23" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="M24" s="35" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="N24" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M25" s="35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N25" s="35" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Penn State</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>Northwestern</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="M26" s="35" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="N26" s="40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="I27" s="40" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="K27" s="35" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="L27" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="M27" s="35" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="N27" s="40" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="35" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>Michigan State</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="I28" s="40" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="J28" s="35" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K28" s="35" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="L28" s="35" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="M28" s="35" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="N28" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O28" s="35" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="35" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>Rutgers</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J29" s="35" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K29" s="35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L29" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="M29" s="35" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="N29" s="40" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O29" s="35" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="35" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I30" s="40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J30" s="35" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K30" s="35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L30" s="35" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="M30" s="35" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="N30" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O30" s="35" t="n"/>
+      <c r="P30" s="35" t="n"/>
+      <c r="Q30" s="35" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>Western Kentucky</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>New Mexico State</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="I31" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J31" s="35" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K31" s="35" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L31" s="35" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M31" s="35" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="N31" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O31" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="P31" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q31" s="40" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>FBS Independents</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>Syracuse</t>
+        </is>
+      </c>
+      <c r="F32" s="35" t="inlineStr">
+        <is>
+          <t>UConn</t>
+        </is>
+      </c>
+      <c r="G32" s="35" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H32" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J32" s="35" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="K32" s="35" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L32" s="35" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="M32" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N32" s="40" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="O32" s="35" t="n"/>
+      <c r="P32" s="35" t="n"/>
+      <c r="Q32" s="35" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>Ball State</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H33" s="35" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I33" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J33" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="K33" s="35" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L33" s="35" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="M33" s="35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N33" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O33" s="35" t="n"/>
+      <c r="P33" s="35" t="n"/>
+      <c r="Q33" s="35" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>Western Michigan</t>
+        </is>
+      </c>
+      <c r="F34" s="35" t="inlineStr">
+        <is>
+          <t>Buffalo</t>
+        </is>
+      </c>
+      <c r="G34" s="35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H34" s="35" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J34" s="35" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K34" s="35" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L34" s="35" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="M34" s="35" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="N34" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="O34" s="35" t="n"/>
+      <c r="P34" s="35" t="n"/>
+      <c r="Q34" s="35" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="F35" s="35" t="inlineStr">
+        <is>
+          <t>Central Michigan</t>
+        </is>
+      </c>
+      <c r="G35" s="35" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="H35" s="35" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I35" s="40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J35" s="35" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="K35" s="35" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L35" s="35" t="n">
+        <v>47</v>
+      </c>
+      <c r="M35" s="35" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N35" s="35" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="O35" s="35" t="n"/>
+      <c r="P35" s="35" t="n"/>
+      <c r="Q35" s="35" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="F36" s="35" t="inlineStr">
+        <is>
+          <t>Kent State</t>
+        </is>
+      </c>
+      <c r="G36" s="35" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I36" s="40" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="J36" s="35" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K36" s="35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L36" s="35" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="M36" s="35" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="N36" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O36" s="35" t="n"/>
+      <c r="P36" s="35" t="n"/>
+      <c r="Q36" s="35" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>Eastern Michigan</t>
+        </is>
+      </c>
+      <c r="F37" s="35" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="G37" s="35" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="H37" s="35" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="I37" s="40" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="J37" s="35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K37" s="35" t="n">
+        <v>-24.6</v>
+      </c>
+      <c r="L37" s="35" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="M37" s="35" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="N37" s="35" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O37" s="35" t="n"/>
+      <c r="P37" s="35" t="n"/>
+      <c r="Q37" s="35" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="inlineStr">
+        <is>
+          <t>Miami (OH)</t>
+        </is>
+      </c>
+      <c r="G38" s="35" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="H38" s="35" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="I38" s="40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J38" s="35" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="K38" s="35" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="L38" s="35" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="M38" s="35" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="N38" s="40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O38" s="35" t="n"/>
+      <c r="P38" s="35" t="n"/>
+      <c r="Q38" s="35" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="F39" s="35" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="G39" s="35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="I39" s="40" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="J39" s="35" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="K39" s="35" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="L39" s="35" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="M39" s="35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N39" s="40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O39" s="35" t="n"/>
+      <c r="P39" s="35" t="n"/>
+      <c r="Q39" s="35" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>UTEP</t>
+        </is>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="G40" s="35" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="I40" s="40" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J40" s="35" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K40" s="35" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="L40" s="35" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="M40" s="35" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="N40" s="40" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O40" s="35" t="n"/>
+      <c r="P40" s="35" t="n"/>
+      <c r="Q40" s="35" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="F41" s="35" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="G41" s="35" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="I41" s="40" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J41" s="35" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K41" s="35" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="L41" s="35" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="M41" s="35" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="N41" s="40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O41" s="35" t="n"/>
+      <c r="P41" s="35" t="n"/>
+      <c r="Q41" s="35" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="F42" s="35" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="G42" s="35" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I42" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J42" s="35" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="K42" s="35" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L42" s="35" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="M42" s="35" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N42" s="40" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="O42" s="35" t="n"/>
+      <c r="P42" s="35" t="n"/>
+      <c r="Q42" s="35" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
+        <is>
+          <t>San José State</t>
+        </is>
+      </c>
+      <c r="F43" s="35" t="inlineStr">
+        <is>
+          <t>Hawai'i</t>
+        </is>
+      </c>
+      <c r="G43" s="35" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I43" s="40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J43" s="35" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="K43" s="35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L43" s="35" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="M43" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N43" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O43" s="35" t="n"/>
+      <c r="P43" s="35" t="n"/>
+      <c r="Q43" s="35" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C44" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="inlineStr">
+        <is>
+          <t>Utah State</t>
+        </is>
+      </c>
+      <c r="F44" s="35" t="inlineStr">
+        <is>
+          <t>Boise State</t>
+        </is>
+      </c>
+      <c r="G44" s="35" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="H44" s="35" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="I44" s="40" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="J44" s="35" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="K44" s="35" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="L44" s="35" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M44" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="N44" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O44" s="35" t="n"/>
+      <c r="P44" s="35" t="n"/>
+      <c r="Q44" s="35" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C45" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>Oregon State</t>
+        </is>
+      </c>
+      <c r="F45" s="35" t="inlineStr">
+        <is>
+          <t>Colorado State</t>
+        </is>
+      </c>
+      <c r="G45" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H45" s="35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I45" s="40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J45" s="35" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K45" s="35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L45" s="35" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="M45" s="35" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="N45" s="40" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O45" s="35" t="n"/>
+      <c r="P45" s="35" t="n"/>
+      <c r="Q45" s="35" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C46" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>Texas State</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>San Diego State</t>
+        </is>
+      </c>
+      <c r="G46" s="35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H46" s="35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I46" s="40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J46" s="35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K46" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L46" s="35" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="M46" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="N46" s="40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O46" s="35" t="n"/>
+      <c r="P46" s="35" t="n"/>
+      <c r="Q46" s="35" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C47" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
+        <is>
+          <t>Fresno State</t>
+        </is>
+      </c>
+      <c r="F47" s="35" t="inlineStr">
+        <is>
+          <t>Washington State</t>
+        </is>
+      </c>
+      <c r="G47" s="35" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="H47" s="35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I47" s="40" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J47" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K47" s="35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L47" s="35" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="M47" s="35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N47" s="40" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O47" s="35" t="n"/>
+      <c r="P47" s="35" t="n"/>
+      <c r="Q47" s="35" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C48" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>Vanderbilt</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G48" s="35" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="H48" s="35" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="I48" s="40" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="J48" s="35" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="K48" s="35" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="L48" s="35" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="M48" s="35" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="N48" s="35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O48" s="35" t="n"/>
+      <c r="P48" s="35" t="n"/>
+      <c r="Q48" s="35" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C49" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="inlineStr">
+        <is>
+          <t>Southland</t>
+        </is>
+      </c>
+      <c r="E49" s="35" t="inlineStr">
+        <is>
+          <t>McNeese</t>
+        </is>
+      </c>
+      <c r="F49" s="35" t="inlineStr">
+        <is>
+          <t>LSU</t>
+        </is>
+      </c>
+      <c r="G49" s="35" t="n">
+        <v>-61.5</v>
+      </c>
+      <c r="H49" s="35" t="n">
+        <v>-52.8</v>
+      </c>
+      <c r="I49" s="40" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J49" s="35" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="K49" s="35" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="L49" s="35" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M49" s="35" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="N49" s="40" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O49" s="35" t="n"/>
+      <c r="P49" s="35" t="n"/>
+      <c r="Q49" s="35" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C50" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="F50" s="35" t="inlineStr">
+        <is>
+          <t>Mississippi State</t>
+        </is>
+      </c>
+      <c r="G50" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I50" s="40" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J50" s="35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K50" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L50" s="35" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="M50" s="35" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="N50" s="40" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="O50" s="35" t="n"/>
+      <c r="P50" s="35" t="n"/>
+      <c r="Q50" s="35" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H51" s="35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I51" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J51" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K51" s="35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L51" s="35" t="n">
+        <v>51</v>
+      </c>
+      <c r="M51" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="N51" s="40" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="O51" s="35" t="n"/>
+      <c r="P51" s="35" t="n"/>
+      <c r="Q51" s="35" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B52" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E52" s="35" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="F52" s="35" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="G52" s="35" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="H52" s="35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I52" s="40" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J52" s="35" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K52" s="35" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="L52" s="35" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="M52" s="35" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N52" s="40" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="O52" s="35" t="n"/>
+      <c r="P52" s="35" t="n"/>
+      <c r="Q52" s="35" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B53" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C53" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E53" s="35" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="F53" s="35" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="G53" s="35" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="H53" s="35" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I53" s="40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J53" s="35" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K53" s="35" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L53" s="35" t="n">
+        <v>48</v>
+      </c>
+      <c r="M53" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="N53" s="40" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="O53" s="35" t="n"/>
+      <c r="P53" s="35" t="n"/>
+      <c r="Q53" s="35" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B54" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C54" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M</t>
+        </is>
+      </c>
+      <c r="G54" s="35" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H54" s="35" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I54" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="35" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K54" s="35" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="L54" s="35" t="n">
+        <v>49</v>
+      </c>
+      <c r="M54" s="35" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="N54" s="35" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O54" s="35" t="n"/>
+      <c r="P54" s="35" t="n"/>
+      <c r="Q54" s="35" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B55" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
+        <is>
+          <t>Georgia Southern</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>Coastal Carolina</t>
+        </is>
+      </c>
+      <c r="G55" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H55" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I55" s="35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J55" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K55" s="35" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="L55" s="35" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M55" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="N55" s="35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O55" s="35" t="n"/>
+      <c r="P55" s="35" t="n"/>
+      <c r="Q55" s="35" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C56" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>Old Dominion</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>Georgia State</t>
+        </is>
+      </c>
+      <c r="G56" s="35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H56" s="35" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I56" s="40" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="J56" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K56" s="35" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="L56" s="35" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="M56" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="N56" s="40" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O56" s="35" t="n"/>
+      <c r="P56" s="35" t="n"/>
+      <c r="Q56" s="35" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C57" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D57" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>Marshall</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
+        <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="G57" s="35" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="H57" s="35" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="I57" s="40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J57" s="35" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="K57" s="35" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="L57" s="35" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="M57" s="35" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N57" s="35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O57" s="35" t="n"/>
+      <c r="P57" s="35" t="n"/>
+      <c r="Q57" s="35" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B58" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C58" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D58" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
+        <is>
+          <t>Army</t>
+        </is>
+      </c>
+      <c r="F58" s="35" t="inlineStr">
+        <is>
+          <t>Louisiana Tech</t>
+        </is>
+      </c>
+      <c r="G58" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H58" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I58" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J58" s="35" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="K58" s="35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L58" s="35" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="M58" s="35" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="N58" s="40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O58" s="35" t="n"/>
+      <c r="P58" s="35" t="n"/>
+      <c r="Q58" s="35" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C59" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D59" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
+        <is>
+          <t>UL Monroe</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>South Alabama</t>
+        </is>
+      </c>
+      <c r="G59" s="35" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="H59" s="35" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I59" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J59" s="35" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="K59" s="35" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L59" s="35" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="M59" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="N59" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="O59" s="35" t="n"/>
+      <c r="P59" s="35" t="n"/>
+      <c r="Q59" s="35" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C60" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D60" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E60" s="35" t="inlineStr">
+        <is>
+          <t>Arkansas State</t>
+        </is>
+      </c>
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="G60" s="35" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="H60" s="35" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I60" s="40" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="J60" s="35" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="K60" s="35" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="L60" s="35" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M60" s="35" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="N60" s="40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O60" s="35" t="n"/>
+      <c r="P60" s="35" t="n"/>
+      <c r="Q60" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q60"/>
@@ -880,7 +4339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1316,11 +4775,604 @@
       </c>
     </row>
     <row r="21" ht="26.5" customHeight="1">
-      <c r="A21" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve ACC.</t>
-        </is>
-      </c>
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F21" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G21" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H21" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I21" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J21" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K21" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L21" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M21" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N21" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O21" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P21" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q21" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Clemson</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="N23" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>Florida State</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="M24" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="N24" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>NC State</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I25" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="M25" s="35" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="N25" s="35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>FBS Independents</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Notre Dame</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="M26" s="35" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="N26" s="35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>Boston College</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>SMU</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="K27" s="35" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L27" s="35" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="M27" s="35" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="N27" s="40" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="35" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>Stanford</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>Wake Forest</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J28" s="35" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="K28" s="35" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="L28" s="35" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="M28" s="35" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N28" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O28" s="35" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="35" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>FBS Independents</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>Syracuse</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>UConn</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" s="40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J29" s="35" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="K29" s="35" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L29" s="35" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="M29" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N29" s="40" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="O29" s="35" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="35" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I30" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J30" s="35" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="K30" s="35" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L30" s="35" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="M30" s="35" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N30" s="40" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="O30" s="35" t="n"/>
+      <c r="P30" s="35" t="n"/>
+      <c r="Q30" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A21:Q30"/>
@@ -1334,7 +5386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1692,11 +5744,555 @@
       </c>
     </row>
     <row r="18" ht="26.5" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve American Athletic.</t>
-        </is>
-      </c>
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H18" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I18" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J18" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K18" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L18" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M18" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N18" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O18" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P18" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q18" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>Tulsa</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L19" s="35" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="N19" s="35" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O19" s="35" t="n">
+        <v>45</v>
+      </c>
+      <c r="P19" s="35" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="40" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K20" s="35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L20" s="35" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="M20" s="35" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="N20" s="40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O20" s="35" t="n"/>
+      <c r="P20" s="35" t="n"/>
+      <c r="Q20" s="35" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>SWAC</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Texas Southern</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Florida Atlantic</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>-44.2</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="N21" s="40" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>UTSA</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="N22" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>South Florida</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="N23" s="40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>Southern</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Samford</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>UAB</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="I24" s="35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="M24" s="35" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N24" s="40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="M25" s="35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N25" s="40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Army</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>Louisiana Tech</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="M26" s="35" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="N26" s="40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A18:Q26"/>
@@ -1710,7 +6306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2124,11 +6720,490 @@
       </c>
     </row>
     <row r="20" ht="26.5" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve Big 12.</t>
-        </is>
-      </c>
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G20" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H20" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I20" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J20" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K20" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M20" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N20" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O20" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P20" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q20" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Texas Tech</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <v>49</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N21" s="35" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>UCF</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Iowa State</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>49</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="N23" s="40" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Middle Tennessee</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="I24" s="35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="M24" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N24" s="40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>BYU</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>TCU</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="M25" s="35" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="N25" s="40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="M26" s="35" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="N26" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>Baylor</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>Arizona State</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K27" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="L27" s="35" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="M27" s="35" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="N27" s="40" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A20:Q27"/>
@@ -2142,7 +7217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2600,11 +7675,547 @@
       </c>
     </row>
     <row r="22" ht="26.5" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve Big Ten.</t>
-        </is>
-      </c>
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F22" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G22" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H22" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I22" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J22" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K22" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L22" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M22" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N22" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O22" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P22" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q22" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>Purdue</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N23" s="40" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Ohio State</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="M24" s="35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N24" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="M25" s="35" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="N25" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M26" s="35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N26" s="35" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>Penn State</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>Northwestern</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K27" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L27" s="35" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="M27" s="35" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="N27" s="40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="35" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="I28" s="40" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="J28" s="35" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="K28" s="35" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="L28" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="M28" s="35" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="N28" s="40" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O28" s="35" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="35" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>Michigan State</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="I29" s="40" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="J29" s="35" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K29" s="35" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="L29" s="35" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="M29" s="35" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="N29" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O29" s="35" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="35" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>Big Ten</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>Rutgers</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J30" s="35" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K30" s="35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L30" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="M30" s="35" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="N30" s="40" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O30" s="35" t="n"/>
+      <c r="P30" s="35" t="n"/>
+      <c r="Q30" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A22:Q30"/>
@@ -2618,7 +8229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2888,9 +8499,268 @@
       </c>
     </row>
     <row r="14" ht="26.5" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve Conference USA.</t>
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H14" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I14" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J14" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K14" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L14" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M14" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N14" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O14" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P14" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q14" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>Big 12</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>Middle Tennessee</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="L15" s="35" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="M15" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N15" s="40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L16" s="35" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="M16" s="35" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="N16" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Conference USA</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>Western Kentucky</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>New Mexico State</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="I17" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K17" s="35" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L17" s="35" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M17" s="35" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="N17" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O17" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="P17" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q17" s="40" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
     </row>
@@ -2906,7 +8776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3008,11 +8878,205 @@
       </c>
     </row>
     <row r="6" ht="26.5" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve FBS Independents.</t>
-        </is>
-      </c>
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H6" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I6" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J6" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K6" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L6" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M6" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N6" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O6" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P6" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q6" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>FBS Independents</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>Notre Dame</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K7" s="35" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L7" s="35" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="M7" s="35" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="N7" s="35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O7" s="35" t="n"/>
+      <c r="P7" s="35" t="n"/>
+      <c r="Q7" s="35" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>FBS Independents</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>Syracuse</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>UConn</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="K8" s="35" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L8" s="35" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="M8" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N8" s="40" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="O8" s="35" t="n"/>
+      <c r="P8" s="35" t="n"/>
+      <c r="Q8" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:Q8"/>
@@ -3026,7 +9090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3358,11 +9422,433 @@
       </c>
     </row>
     <row r="17" ht="26.5" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve Mid-American.</t>
-        </is>
-      </c>
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E17" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F17" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G17" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H17" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I17" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J17" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K17" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L17" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M17" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N17" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O17" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P17" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q17" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>Ball State</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" s="35" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L18" s="35" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="M18" s="35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N18" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O18" s="35" t="n"/>
+      <c r="P18" s="35" t="n"/>
+      <c r="Q18" s="35" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>Western Michigan</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>Buffalo</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L19" s="35" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="N19" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="O19" s="35" t="n"/>
+      <c r="P19" s="35" t="n"/>
+      <c r="Q19" s="35" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Central Michigan</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="K20" s="35" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L20" s="35" t="n">
+        <v>47</v>
+      </c>
+      <c r="M20" s="35" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N20" s="35" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="O20" s="35" t="n"/>
+      <c r="P20" s="35" t="n"/>
+      <c r="Q20" s="35" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Kent State</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="N21" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>Eastern Michigan</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>-24.6</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="N22" s="35" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>Mid-American</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Miami (OH)</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="N23" s="40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A17:Q23"/>
@@ -3376,7 +9862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3650,11 +10136,376 @@
       </c>
     </row>
     <row r="14" ht="26.5" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve Mountain West.</t>
-        </is>
-      </c>
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H14" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I14" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J14" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K14" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L14" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M14" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N14" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O14" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P14" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q14" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="L15" s="35" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="M15" s="35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N15" s="40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>UTEP</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="L16" s="35" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="M16" s="35" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="N16" s="40" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>North Dakota State</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="I17" s="40" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K17" s="35" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="L17" s="35" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="M17" s="35" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="N17" s="40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="35" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I18" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="K18" s="35" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L18" s="35" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="M18" s="35" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N18" s="40" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="O18" s="35" t="n"/>
+      <c r="P18" s="35" t="n"/>
+      <c r="Q18" s="35" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>Mountain West</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>San José State</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>Hawai'i</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L19" s="35" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N19" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O19" s="35" t="n"/>
+      <c r="P19" s="35" t="n"/>
+      <c r="Q19" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A14:Q19"/>
@@ -3668,7 +10519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3890,11 +10741,319 @@
       </c>
     </row>
     <row r="12" ht="26.5" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve Pac-12.</t>
-        </is>
-      </c>
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I12" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J12" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K12" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L12" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M12" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N12" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O12" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P12" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q12" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>Utah State</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>Boise State</t>
+        </is>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="J13" s="35" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="K13" s="35" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="L13" s="35" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M13" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="N13" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O13" s="35" t="n"/>
+      <c r="P13" s="35" t="n"/>
+      <c r="Q13" s="35" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>Oregon State</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>Colorado State</t>
+        </is>
+      </c>
+      <c r="G14" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J14" s="35" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K14" s="35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L14" s="35" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="M14" s="35" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="N14" s="40" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O14" s="35" t="n"/>
+      <c r="P14" s="35" t="n"/>
+      <c r="Q14" s="35" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>Texas State</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>San Diego State</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L15" s="35" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="M15" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="N15" s="40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Pac-12</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>Fresno State</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Washington State</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L16" s="35" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="M16" s="35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N16" s="40" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A12:Q16"/>
@@ -4012,7 +11171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4426,11 +11585,490 @@
       </c>
     </row>
     <row r="20" ht="26.5" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve SEC.</t>
-        </is>
-      </c>
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G20" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H20" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I20" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J20" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K20" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M20" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N20" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O20" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P20" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q20" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Vanderbilt</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="N21" s="35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>Southland</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>McNeese</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>LSU</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>-61.5</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>-52.8</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Mississippi State</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="N23" s="40" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>51</v>
+      </c>
+      <c r="M24" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="N24" s="40" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="M25" s="35" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N25" s="40" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <v>48</v>
+      </c>
+      <c r="M26" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="N26" s="40" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I27" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K27" s="35" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="L27" s="35" t="n">
+        <v>49</v>
+      </c>
+      <c r="M27" s="35" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="N27" s="35" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A20:Q27"/>
@@ -4444,7 +12082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4790,11 +12428,433 @@
       </c>
     </row>
     <row r="18" ht="26.5" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>No FBS games this week involve Sun Belt.</t>
-        </is>
-      </c>
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Home Conf</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>Away Conf</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t>Away Team</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>Home Team</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="inlineStr">
+        <is>
+          <t>Model Line (Home)</t>
+        </is>
+      </c>
+      <c r="H18" s="39" t="inlineStr">
+        <is>
+          <t>Market Line (Home)</t>
+        </is>
+      </c>
+      <c r="I18" s="39" t="inlineStr">
+        <is>
+          <t>Spread Edge (pts)</t>
+        </is>
+      </c>
+      <c r="J18" s="39" t="inlineStr">
+        <is>
+          <t>Ridge Line (Home)</t>
+        </is>
+      </c>
+      <c r="K18" s="39" t="inlineStr">
+        <is>
+          <t>Massey Line (Home)</t>
+        </is>
+      </c>
+      <c r="L18" s="39" t="inlineStr">
+        <is>
+          <t>Model Total</t>
+        </is>
+      </c>
+      <c r="M18" s="39" t="inlineStr">
+        <is>
+          <t>Market Total</t>
+        </is>
+      </c>
+      <c r="N18" s="39" t="inlineStr">
+        <is>
+          <t>Total Edge (pts)</t>
+        </is>
+      </c>
+      <c r="O18" s="39" t="inlineStr">
+        <is>
+          <t>Away Pts</t>
+        </is>
+      </c>
+      <c r="P18" s="39" t="inlineStr">
+        <is>
+          <t>Home Pts</t>
+        </is>
+      </c>
+      <c r="Q18" s="39" t="inlineStr">
+        <is>
+          <t>Model Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>Georgia Southern</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>Coastal Carolina</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="L19" s="35" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="N19" s="35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O19" s="35" t="n"/>
+      <c r="P19" s="35" t="n"/>
+      <c r="Q19" s="35" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>Old Dominion</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Georgia State</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K20" s="35" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="L20" s="35" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="M20" s="35" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="N20" s="40" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O20" s="35" t="n"/>
+      <c r="P20" s="35" t="n"/>
+      <c r="Q20" s="35" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Marshall</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N21" s="35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>American Athletic</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>Army</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Louisiana Tech</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>UL Monroe</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>South Alabama</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="N23" s="35" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>Sun Belt</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Arkansas State</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M24" s="35" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="N24" s="40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A18:Q24"/>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -928,11 +928,11 @@
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>196-166-5</t>
+          <t>196-168-5</t>
         </is>
       </c>
       <c r="C3" s="40" t="n">
-        <v>0.541</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="4">
@@ -943,7 +943,7 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>17-18-1</t>
+          <t>18-19-1</t>
         </is>
       </c>
       <c r="C4" s="40" t="n">
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="G7" s="37" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="H7" s="37" t="n">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="I7" s="42" t="n">
-        <v>-7.5</v>
+        <v>-6.6</v>
       </c>
       <c r="J7" s="37" t="n">
         <v>-1.4</v>
@@ -1085,10 +1085,10 @@
         <v>51.2</v>
       </c>
       <c r="M7" s="37" t="n">
-        <v>53.2</v>
+        <v>54.5</v>
       </c>
       <c r="N7" s="42" t="n">
-        <v>-2</v>
+        <v>-3.3</v>
       </c>
       <c r="O7" s="37" t="n">
         <v>35</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="G8" s="37" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="H8" s="37" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>-2.3</v>
+        <v>16.5</v>
+      </c>
+      <c r="I8" s="37" t="n">
+        <v>-1.1</v>
       </c>
       <c r="J8" s="37" t="n">
         <v>8.199999999999999</v>
@@ -1150,10 +1150,10 @@
         <v>47.3</v>
       </c>
       <c r="M8" s="37" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="N8" s="37" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="O8" s="37" t="n"/>
       <c r="P8" s="37" t="n"/>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="G9" s="37" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="H9" s="37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I9" s="37" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>2.9</v>
       </c>
       <c r="J9" s="37" t="n">
         <v>-0.8</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="G10" s="37" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H10" s="37" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I10" s="37" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J10" s="37" t="n">
         <v>1.4</v>
@@ -1272,10 +1272,10 @@
         <v>57.3</v>
       </c>
       <c r="M10" s="37" t="n">
-        <v>57</v>
+        <v>58.2</v>
       </c>
       <c r="N10" s="37" t="n">
-        <v>0.3</v>
+        <v>-1</v>
       </c>
       <c r="O10" s="37" t="n">
         <v>28</v>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="G11" s="37" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="H11" s="37" t="n">
-        <v>21</v>
-      </c>
-      <c r="I11" s="37" t="n">
-        <v>1.1</v>
+        <v>21.5</v>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>2</v>
       </c>
       <c r="J11" s="37" t="n">
         <v>11.2</v>
@@ -1384,13 +1384,13 @@
         </is>
       </c>
       <c r="G12" s="37" t="n">
-        <v>-21.9</v>
+        <v>-21.8</v>
       </c>
       <c r="H12" s="37" t="n">
         <v>-21.5</v>
       </c>
       <c r="I12" s="37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J12" s="37" t="n">
         <v>-19.4</v>
@@ -1402,10 +1402,10 @@
         <v>48.3</v>
       </c>
       <c r="M12" s="37" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="N12" s="42" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="O12" s="37" t="n">
         <v>16</v>
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="G13" s="37" t="n">
-        <v>-24.8</v>
+        <v>-25.8</v>
       </c>
       <c r="H13" s="37" t="n">
-        <v>-14.5</v>
+        <v>-14</v>
       </c>
       <c r="I13" s="42" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="J13" s="37" t="n">
         <v>-7.7</v>
@@ -1467,10 +1467,10 @@
         <v>56.1</v>
       </c>
       <c r="M13" s="37" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N13" s="37" t="n">
-        <v>1.8</v>
+        <v>53.5</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>2.6</v>
       </c>
       <c r="O13" s="37" t="n">
         <v>3</v>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="G14" s="37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H14" s="37" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="42" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="J14" s="37" t="n">
         <v>4.4</v>
@@ -1582,10 +1582,10 @@
         <v>23.8</v>
       </c>
       <c r="H15" s="37" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="I15" s="42" t="n">
-        <v>-4.3</v>
+        <v>-3.3</v>
       </c>
       <c r="J15" s="37" t="n">
         <v>17.5</v>
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="G16" s="37" t="n">
-        <v>-31.3</v>
+        <v>-31.2</v>
       </c>
       <c r="H16" s="37" t="n">
-        <v>-45.8</v>
+        <v>-44.2</v>
       </c>
       <c r="I16" s="42" t="n">
-        <v>-14.5</v>
+        <v>-13</v>
       </c>
       <c r="J16" s="37" t="n">
         <v>-18.2</v>
@@ -1662,10 +1662,10 @@
         <v>56.5</v>
       </c>
       <c r="M16" s="37" t="n">
-        <v>62</v>
+        <v>61.2</v>
       </c>
       <c r="N16" s="42" t="n">
-        <v>-5.5</v>
+        <v>-4.7</v>
       </c>
       <c r="O16" s="37" t="n"/>
       <c r="P16" s="37" t="n"/>
@@ -1719,10 +1719,10 @@
         <v>55.1</v>
       </c>
       <c r="M17" s="37" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="N17" s="37" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="O17" s="37" t="n"/>
       <c r="P17" s="37" t="n"/>
@@ -1761,10 +1761,10 @@
         <v>-13.2</v>
       </c>
       <c r="H18" s="37" t="n">
-        <v>-5.5</v>
+        <v>-6</v>
       </c>
       <c r="I18" s="42" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J18" s="37" t="n">
         <v>-14.2</v>
@@ -1776,10 +1776,10 @@
         <v>58.3</v>
       </c>
       <c r="M18" s="37" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="N18" s="42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O18" s="37" t="n"/>
       <c r="P18" s="37" t="n"/>
@@ -1833,10 +1833,10 @@
         <v>57.5</v>
       </c>
       <c r="M19" s="37" t="n">
-        <v>54.2</v>
+        <v>52.8</v>
       </c>
       <c r="N19" s="42" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="O19" s="37" t="n">
         <v>14</v>
@@ -1898,10 +1898,10 @@
         <v>49</v>
       </c>
       <c r="M20" s="37" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="N20" s="37" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="O20" s="37" t="n"/>
       <c r="P20" s="37" t="n"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="G21" s="37" t="n">
-        <v>-12.9</v>
+        <v>-12.8</v>
       </c>
       <c r="H21" s="37" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="I21" s="42" t="n">
-        <v>2.4</v>
+        <v>-11.2</v>
+      </c>
+      <c r="I21" s="37" t="n">
+        <v>1.5</v>
       </c>
       <c r="J21" s="37" t="n">
         <v>-12</v>
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="G22" s="37" t="n">
-        <v>-13.3</v>
+        <v>-13.4</v>
       </c>
       <c r="H22" s="37" t="n">
         <v>-3</v>
       </c>
       <c r="I22" s="42" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J22" s="37" t="n">
         <v>-5.6</v>
@@ -2017,7 +2017,7 @@
         <v>-6.3</v>
       </c>
       <c r="L22" s="37" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="M22" s="37" t="n">
         <v>53.2</v>
@@ -2070,10 +2070,10 @@
         <v>-29.9</v>
       </c>
       <c r="H23" s="37" t="n">
-        <v>-21</v>
+        <v>-19.8</v>
       </c>
       <c r="I23" s="42" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="J23" s="37" t="n">
         <v>-19.5</v>
@@ -2085,10 +2085,10 @@
         <v>54.2</v>
       </c>
       <c r="M23" s="37" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N23" s="42" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O23" s="37" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>2.4</v>
       </c>
       <c r="H24" s="37" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="I24" s="42" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J24" s="37" t="n">
         <v>8.800000000000001</v>
@@ -2150,10 +2150,10 @@
         <v>52.4</v>
       </c>
       <c r="M24" s="37" t="n">
-        <v>48.8</v>
+        <v>47.8</v>
       </c>
       <c r="N24" s="42" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="O24" s="37" t="n"/>
       <c r="P24" s="37" t="n"/>
@@ -2192,10 +2192,10 @@
         <v>-5.9</v>
       </c>
       <c r="H25" s="37" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="I25" s="37" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="J25" s="37" t="n">
         <v>-11</v>
@@ -2207,10 +2207,10 @@
         <v>55.7</v>
       </c>
       <c r="M25" s="37" t="n">
-        <v>56</v>
+        <v>55.5</v>
       </c>
       <c r="N25" s="37" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O25" s="37" t="n"/>
       <c r="P25" s="37" t="n"/>
@@ -2249,10 +2249,10 @@
         <v>-2.3</v>
       </c>
       <c r="H26" s="37" t="n">
-        <v>-3.5</v>
+        <v>-3.8</v>
       </c>
       <c r="I26" s="37" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="J26" s="37" t="n">
         <v>-4</v>
@@ -2264,10 +2264,10 @@
         <v>46.8</v>
       </c>
       <c r="M26" s="37" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N26" s="37" t="n">
-        <v>-1.7</v>
+        <v>49.2</v>
+      </c>
+      <c r="N26" s="42" t="n">
+        <v>-2.4</v>
       </c>
       <c r="O26" s="37" t="n"/>
       <c r="P26" s="37" t="n"/>
@@ -2306,10 +2306,10 @@
         <v>-14.7</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10</v>
       </c>
       <c r="I27" s="42" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J27" s="37" t="n">
         <v>-16.6</v>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="G28" s="37" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H28" s="37" t="n">
         <v>14.2</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>7.1</v>
@@ -2386,10 +2386,10 @@
         <v>45.9</v>
       </c>
       <c r="M28" s="37" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="N28" s="37" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="O28" s="37" t="n">
         <v>31</v>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="G29" s="37" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="H29" s="37" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I29" s="42" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J29" s="37" t="n">
         <v>5</v>
@@ -2451,10 +2451,10 @@
         <v>43.8</v>
       </c>
       <c r="M29" s="37" t="n">
-        <v>42.2</v>
+        <v>43.5</v>
       </c>
       <c r="N29" s="37" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="O29" s="37" t="n">
         <v>14</v>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="G30" s="37" t="n">
-        <v>-19</v>
+        <v>-21.4</v>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-15</v>
+        <v>-14.5</v>
       </c>
       <c r="I30" s="42" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="J30" s="37" t="n">
         <v>-13</v>
@@ -2521,9 +2521,17 @@
       <c r="N30" s="37" t="n">
         <v>-0.3</v>
       </c>
-      <c r="O30" s="37" t="n"/>
-      <c r="P30" s="37" t="n"/>
-      <c r="Q30" s="37" t="n"/>
+      <c r="O30" s="37" t="n">
+        <v>23</v>
+      </c>
+      <c r="P30" s="37" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q30" s="42" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="37" t="n">
@@ -2555,13 +2563,13 @@
         </is>
       </c>
       <c r="G31" s="37" t="n">
-        <v>-1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="H31" s="37" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I31" s="42" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J31" s="37" t="n">
         <v>0.6</v>
@@ -2573,10 +2581,10 @@
         <v>49.9</v>
       </c>
       <c r="M31" s="37" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="N31" s="42" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O31" s="37" t="n">
         <v>13</v>
@@ -2620,13 +2628,13 @@
         </is>
       </c>
       <c r="G32" s="37" t="n">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="H32" s="37" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="I32" s="42" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="J32" s="37" t="n">
         <v>-5.4</v>
@@ -2677,13 +2685,13 @@
         </is>
       </c>
       <c r="G33" s="37" t="n">
-        <v>-10</v>
+        <v>-10.2</v>
       </c>
       <c r="H33" s="37" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="I33" s="37" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J33" s="37" t="n">
         <v>-9.6</v>
@@ -2692,7 +2700,7 @@
         <v>-9.4</v>
       </c>
       <c r="L33" s="37" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="M33" s="37" t="n">
         <v>43.2</v>
@@ -2745,10 +2753,10 @@
         <v>26.2</v>
       </c>
       <c r="H34" s="37" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I34" s="42" t="n">
-        <v>-2</v>
+        <v>24.5</v>
+      </c>
+      <c r="I34" s="37" t="n">
+        <v>-1.7</v>
       </c>
       <c r="J34" s="37" t="n">
         <v>18.7</v>
@@ -2799,13 +2807,13 @@
         </is>
       </c>
       <c r="G35" s="37" t="n">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="H35" s="37" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I35" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J35" s="37" t="n">
         <v>-0.4</v>
@@ -2817,10 +2825,10 @@
         <v>51</v>
       </c>
       <c r="M35" s="37" t="n">
-        <v>51.5</v>
+        <v>49.8</v>
       </c>
       <c r="N35" s="37" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="O35" s="37" t="n">
         <v>30</v>
@@ -2828,9 +2836,9 @@
       <c r="P35" s="37" t="n">
         <v>14</v>
       </c>
-      <c r="Q35" s="43" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="Q35" s="42" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
     </row>
@@ -2929,13 +2937,13 @@
         </is>
       </c>
       <c r="G37" s="37" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="H37" s="37" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I37" s="42" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J37" s="37" t="n">
         <v>-9.800000000000001</v>
@@ -2944,13 +2952,13 @@
         <v>-1.9</v>
       </c>
       <c r="L37" s="37" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="M37" s="37" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N37" s="42" t="n">
-        <v>-3.1</v>
+        <v>-2.5</v>
       </c>
       <c r="O37" s="37" t="n">
         <v>42</v>
@@ -2994,13 +3002,13 @@
         </is>
       </c>
       <c r="G38" s="37" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="H38" s="37" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I38" s="42" t="n">
-        <v>2.3</v>
+        <v>20.5</v>
+      </c>
+      <c r="I38" s="37" t="n">
+        <v>1.5</v>
       </c>
       <c r="J38" s="37" t="n">
         <v>12</v>
@@ -3012,10 +3020,10 @@
         <v>52.4</v>
       </c>
       <c r="M38" s="37" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="N38" s="37" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="O38" s="37" t="n">
         <v>39</v>
@@ -3059,13 +3067,13 @@
         </is>
       </c>
       <c r="G39" s="37" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H39" s="37" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="I39" s="42" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J39" s="37" t="n">
         <v>10.3</v>
@@ -3124,13 +3132,13 @@
         </is>
       </c>
       <c r="G40" s="37" t="n">
-        <v>-12.7</v>
+        <v>-13.4</v>
       </c>
       <c r="H40" s="37" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="I40" s="42" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="J40" s="37" t="n">
         <v>-6.3</v>
@@ -3189,13 +3197,13 @@
         </is>
       </c>
       <c r="G41" s="37" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H41" s="37" t="n">
         <v>3.5</v>
       </c>
       <c r="I41" s="42" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="J41" s="37" t="n">
         <v>11</v>
@@ -3254,13 +3262,13 @@
         </is>
       </c>
       <c r="G42" s="37" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H42" s="37" t="n">
         <v>-5.8</v>
       </c>
       <c r="I42" s="42" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="J42" s="37" t="n">
         <v>1.4</v>
@@ -3272,10 +3280,10 @@
         <v>48.3</v>
       </c>
       <c r="M42" s="37" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="N42" s="37" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="O42" s="37" t="n">
         <v>38</v>
@@ -3322,10 +3330,10 @@
         <v>-20.1</v>
       </c>
       <c r="H43" s="37" t="n">
-        <v>-11.2</v>
+        <v>-13.5</v>
       </c>
       <c r="I43" s="42" t="n">
-        <v>8.9</v>
+        <v>6.6</v>
       </c>
       <c r="J43" s="37" t="n">
         <v>-13.8</v>
@@ -3337,10 +3345,10 @@
         <v>48.6</v>
       </c>
       <c r="M43" s="37" t="n">
-        <v>42.2</v>
+        <v>43.5</v>
       </c>
       <c r="N43" s="42" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="O43" s="37" t="n">
         <v>24</v>
@@ -3384,13 +3392,13 @@
         </is>
       </c>
       <c r="G44" s="37" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="H44" s="37" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="I44" s="42" t="n">
-        <v>-5</v>
+        <v>-6.4</v>
       </c>
       <c r="J44" s="37" t="n">
         <v>-8.6</v>
@@ -3402,10 +3410,10 @@
         <v>54.9</v>
       </c>
       <c r="M44" s="37" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="N44" s="42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O44" s="37" t="n">
         <v>9</v>
@@ -3449,16 +3457,16 @@
         </is>
       </c>
       <c r="G45" s="37" t="n">
-        <v>-37.6</v>
+        <v>-37.3</v>
       </c>
       <c r="H45" s="37" t="n">
-        <v>-23.2</v>
+        <v>-22.5</v>
       </c>
       <c r="I45" s="42" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="J45" s="37" t="n">
-        <v>-22.1</v>
+        <v>-22.2</v>
       </c>
       <c r="K45" s="37" t="n">
         <v>-28.2</v>
@@ -3514,13 +3522,13 @@
         </is>
       </c>
       <c r="G46" s="37" t="n">
-        <v>-31.2</v>
+        <v>-30.7</v>
       </c>
       <c r="H46" s="37" t="n">
         <v>-17.2</v>
       </c>
       <c r="I46" s="42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J46" s="37" t="n">
         <v>-22</v>
@@ -3579,13 +3587,13 @@
         </is>
       </c>
       <c r="G47" s="37" t="n">
-        <v>-7.4</v>
+        <v>-6.8</v>
       </c>
       <c r="H47" s="37" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="I47" s="42" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J47" s="37" t="n">
         <v>-15.5</v>
@@ -3594,13 +3602,13 @@
         <v>-3.1</v>
       </c>
       <c r="L47" s="37" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="M47" s="37" t="n">
-        <v>52.2</v>
+        <v>53.5</v>
       </c>
       <c r="N47" s="42" t="n">
-        <v>-6.7</v>
+        <v>-8</v>
       </c>
       <c r="O47" s="37" t="n">
         <v>31</v>
@@ -3647,10 +3655,10 @@
         <v>-6.8</v>
       </c>
       <c r="H48" s="37" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="I48" s="42" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J48" s="37" t="n">
         <v>-6.8</v>
@@ -3662,10 +3670,10 @@
         <v>48.5</v>
       </c>
       <c r="M48" s="37" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="N48" s="42" t="n">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
       <c r="O48" s="37" t="n"/>
       <c r="P48" s="37" t="n"/>
@@ -3704,10 +3712,10 @@
         <v>-14.8</v>
       </c>
       <c r="H49" s="37" t="n">
-        <v>-19.5</v>
+        <v>-18.5</v>
       </c>
       <c r="I49" s="42" t="n">
-        <v>-4.7</v>
+        <v>-3.7</v>
       </c>
       <c r="J49" s="37" t="n">
         <v>-18.5</v>
@@ -3761,10 +3769,10 @@
         <v>1.6</v>
       </c>
       <c r="H50" s="37" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I50" s="42" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J50" s="37" t="n">
         <v>-1.3</v>
@@ -3776,10 +3784,10 @@
         <v>56.2</v>
       </c>
       <c r="M50" s="37" t="n">
-        <v>61.5</v>
+        <v>62.2</v>
       </c>
       <c r="N50" s="42" t="n">
-        <v>-5.3</v>
+        <v>-6</v>
       </c>
       <c r="O50" s="37" t="n"/>
       <c r="P50" s="37" t="n"/>
@@ -3818,10 +3826,10 @@
         <v>3.8</v>
       </c>
       <c r="H51" s="37" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="I51" s="42" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J51" s="37" t="n">
         <v>2.7</v>
@@ -3875,10 +3883,10 @@
         <v>-7.8</v>
       </c>
       <c r="H52" s="37" t="n">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I52" s="42" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="J52" s="37" t="n">
         <v>2.4</v>
@@ -3890,10 +3898,10 @@
         <v>41.4</v>
       </c>
       <c r="M52" s="37" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="N52" s="42" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="O52" s="37" t="n"/>
       <c r="P52" s="37" t="n"/>
@@ -3929,13 +3937,13 @@
         </is>
       </c>
       <c r="G53" s="37" t="n">
-        <v>-15.8</v>
+        <v>-17.2</v>
       </c>
       <c r="H53" s="37" t="n">
-        <v>-25.5</v>
+        <v>-25.2</v>
       </c>
       <c r="I53" s="42" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8</v>
       </c>
       <c r="J53" s="37" t="n">
         <v>-20.6</v>
@@ -3947,10 +3955,10 @@
         <v>48.9</v>
       </c>
       <c r="M53" s="37" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="N53" s="37" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="O53" s="37" t="n">
         <v>14</v>
@@ -3997,10 +4005,10 @@
         <v>-61.5</v>
       </c>
       <c r="H54" s="37" t="n">
-        <v>-53.2</v>
+        <v>-52.8</v>
       </c>
       <c r="I54" s="42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J54" s="37" t="n">
         <v>-40.8</v>
@@ -4012,10 +4020,10 @@
         <v>57.7</v>
       </c>
       <c r="M54" s="37" t="n">
-        <v>62</v>
+        <v>61.5</v>
       </c>
       <c r="N54" s="42" t="n">
-        <v>-4.3</v>
+        <v>-3.8</v>
       </c>
       <c r="O54" s="37" t="n"/>
       <c r="P54" s="37" t="n"/>
@@ -4051,13 +4059,13 @@
         </is>
       </c>
       <c r="G55" s="37" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="H55" s="37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I55" s="42" t="n">
-        <v>-6.7</v>
+        <v>-6</v>
       </c>
       <c r="J55" s="37" t="n">
         <v>12.2</v>
@@ -4069,10 +4077,10 @@
         <v>55.4</v>
       </c>
       <c r="M55" s="37" t="n">
-        <v>62</v>
+        <v>60.2</v>
       </c>
       <c r="N55" s="42" t="n">
-        <v>-6.6</v>
+        <v>-4.8</v>
       </c>
       <c r="O55" s="37" t="n">
         <v>56</v>
@@ -4131,13 +4139,13 @@
         <v>4.7</v>
       </c>
       <c r="L56" s="37" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M56" s="37" t="n">
-        <v>57.8</v>
+        <v>57.5</v>
       </c>
       <c r="N56" s="42" t="n">
-        <v>-6.7</v>
+        <v>-6.4</v>
       </c>
       <c r="O56" s="37" t="n">
         <v>17</v>
@@ -4181,13 +4189,13 @@
         </is>
       </c>
       <c r="G57" s="37" t="n">
-        <v>-12.9</v>
+        <v>-12.7</v>
       </c>
       <c r="H57" s="37" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="I57" s="42" t="n">
-        <v>10.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" s="37" t="n">
         <v>-4</v>
@@ -4199,14 +4207,22 @@
         <v>51.8</v>
       </c>
       <c r="M57" s="37" t="n">
-        <v>53</v>
-      </c>
-      <c r="N57" s="37" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O57" s="37" t="n"/>
-      <c r="P57" s="37" t="n"/>
-      <c r="Q57" s="37" t="n"/>
+        <v>54.2</v>
+      </c>
+      <c r="N57" s="42" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="O57" s="37" t="n">
+        <v>35</v>
+      </c>
+      <c r="P57" s="37" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="43" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="37" t="n">
@@ -4238,13 +4254,13 @@
         </is>
       </c>
       <c r="G58" s="37" t="n">
-        <v>-12.5</v>
+        <v>-12.9</v>
       </c>
       <c r="H58" s="37" t="n">
-        <v>-6.2</v>
+        <v>-7</v>
       </c>
       <c r="I58" s="42" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="J58" s="37" t="n">
         <v>-14.1</v>
@@ -4256,10 +4272,10 @@
         <v>48</v>
       </c>
       <c r="M58" s="37" t="n">
-        <v>54.2</v>
+        <v>53.8</v>
       </c>
       <c r="N58" s="42" t="n">
-        <v>-6.2</v>
+        <v>-5.7</v>
       </c>
       <c r="O58" s="37" t="n">
         <v>14</v>
@@ -4306,10 +4322,10 @@
         <v>-17</v>
       </c>
       <c r="H59" s="37" t="n">
-        <v>-13.8</v>
+        <v>-14</v>
       </c>
       <c r="I59" s="42" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J59" s="37" t="n">
         <v>-16.9</v>
@@ -4363,10 +4379,10 @@
         <v>0.2</v>
       </c>
       <c r="H60" s="37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I60" s="42" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
+      </c>
+      <c r="I60" s="37" t="n">
+        <v>1.3</v>
       </c>
       <c r="J60" s="37" t="n">
         <v>0.4</v>
@@ -4378,10 +4394,10 @@
         <v>55.7</v>
       </c>
       <c r="M60" s="37" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N60" s="42" t="n">
-        <v>2.2</v>
+        <v>53.8</v>
+      </c>
+      <c r="N60" s="37" t="n">
+        <v>1.9</v>
       </c>
       <c r="O60" s="37" t="n"/>
       <c r="P60" s="37" t="n"/>
@@ -4420,10 +4436,10 @@
         <v>2.1</v>
       </c>
       <c r="H61" s="37" t="n">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="I61" s="42" t="n">
-        <v>-4.1</v>
+        <v>-4.6</v>
       </c>
       <c r="J61" s="37" t="n">
         <v>-0.3</v>
@@ -4482,13 +4498,13 @@
         </is>
       </c>
       <c r="G62" s="37" t="n">
-        <v>-29.6</v>
+        <v>-29.7</v>
       </c>
       <c r="H62" s="37" t="n">
-        <v>-16.2</v>
+        <v>-19.2</v>
       </c>
       <c r="I62" s="42" t="n">
-        <v>13.3</v>
+        <v>10.5</v>
       </c>
       <c r="J62" s="37" t="n">
         <v>-12.4</v>
@@ -4500,10 +4516,10 @@
         <v>56.3</v>
       </c>
       <c r="M62" s="37" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="N62" s="37" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="O62" s="37" t="n">
         <v>17</v>
@@ -4550,10 +4566,10 @@
         <v>3.5</v>
       </c>
       <c r="H63" s="37" t="n">
-        <v>-0.2</v>
+        <v>1.5</v>
       </c>
       <c r="I63" s="42" t="n">
-        <v>-3.7</v>
+        <v>-2</v>
       </c>
       <c r="J63" s="37" t="n">
         <v>-8.1</v>
@@ -4565,10 +4581,10 @@
         <v>53.3</v>
       </c>
       <c r="M63" s="37" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="N63" s="42" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="O63" s="37" t="n"/>
       <c r="P63" s="37" t="n"/>
@@ -4607,10 +4623,10 @@
         <v>-15.6</v>
       </c>
       <c r="H64" s="37" t="n">
-        <v>-13.8</v>
+        <v>-14</v>
       </c>
       <c r="I64" s="37" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J64" s="37" t="n">
         <v>-21.1</v>
@@ -4622,10 +4638,10 @@
         <v>56.6</v>
       </c>
       <c r="M64" s="37" t="n">
-        <v>57</v>
+        <v>57.5</v>
       </c>
       <c r="N64" s="37" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="O64" s="37" t="n"/>
       <c r="P64" s="37" t="n"/>
@@ -4664,10 +4680,10 @@
         <v>-4.3</v>
       </c>
       <c r="H65" s="37" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="I65" s="37" t="n">
-        <v>-1.4</v>
+        <v>-6.5</v>
+      </c>
+      <c r="I65" s="42" t="n">
+        <v>-2.2</v>
       </c>
       <c r="J65" s="37" t="n">
         <v>-7.4</v>
@@ -4679,10 +4695,10 @@
         <v>51.5</v>
       </c>
       <c r="M65" s="37" t="n">
-        <v>49</v>
+        <v>47.8</v>
       </c>
       <c r="N65" s="42" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="O65" s="37" t="n"/>
       <c r="P65" s="37" t="n"/>
@@ -5306,13 +5322,13 @@
         </is>
       </c>
       <c r="G27" s="37" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="I27" s="42" t="n">
-        <v>-7.5</v>
+        <v>-6.6</v>
       </c>
       <c r="J27" s="37" t="n">
         <v>-1.4</v>
@@ -5324,10 +5340,10 @@
         <v>51.2</v>
       </c>
       <c r="M27" s="37" t="n">
-        <v>53.2</v>
+        <v>54.5</v>
       </c>
       <c r="N27" s="42" t="n">
-        <v>-2</v>
+        <v>-3.3</v>
       </c>
       <c r="O27" s="37" t="n">
         <v>35</v>
@@ -5371,13 +5387,13 @@
         </is>
       </c>
       <c r="G28" s="37" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="H28" s="37" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I28" s="42" t="n">
-        <v>-2.3</v>
+        <v>16.5</v>
+      </c>
+      <c r="I28" s="37" t="n">
+        <v>-1.1</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>8.199999999999999</v>
@@ -5389,10 +5405,10 @@
         <v>47.3</v>
       </c>
       <c r="M28" s="37" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="N28" s="37" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="O28" s="37" t="n"/>
       <c r="P28" s="37" t="n"/>
@@ -5428,13 +5444,13 @@
         </is>
       </c>
       <c r="G29" s="37" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="H29" s="37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I29" s="37" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
+      </c>
+      <c r="I29" s="42" t="n">
+        <v>2.9</v>
       </c>
       <c r="J29" s="37" t="n">
         <v>-0.8</v>
@@ -5493,13 +5509,13 @@
         </is>
       </c>
       <c r="G30" s="37" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H30" s="37" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I30" s="37" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J30" s="37" t="n">
         <v>1.4</v>
@@ -5511,10 +5527,10 @@
         <v>57.3</v>
       </c>
       <c r="M30" s="37" t="n">
-        <v>57</v>
+        <v>58.2</v>
       </c>
       <c r="N30" s="37" t="n">
-        <v>0.3</v>
+        <v>-1</v>
       </c>
       <c r="O30" s="37" t="n">
         <v>28</v>
@@ -5558,13 +5574,13 @@
         </is>
       </c>
       <c r="G31" s="37" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="H31" s="37" t="n">
-        <v>21</v>
-      </c>
-      <c r="I31" s="37" t="n">
-        <v>1.1</v>
+        <v>21.5</v>
+      </c>
+      <c r="I31" s="42" t="n">
+        <v>2</v>
       </c>
       <c r="J31" s="37" t="n">
         <v>11.2</v>
@@ -5623,13 +5639,13 @@
         </is>
       </c>
       <c r="G32" s="37" t="n">
-        <v>-21.9</v>
+        <v>-21.8</v>
       </c>
       <c r="H32" s="37" t="n">
         <v>-21.5</v>
       </c>
       <c r="I32" s="37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J32" s="37" t="n">
         <v>-19.4</v>
@@ -5641,10 +5657,10 @@
         <v>48.3</v>
       </c>
       <c r="M32" s="37" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="N32" s="42" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="O32" s="37" t="n">
         <v>16</v>
@@ -5688,13 +5704,13 @@
         </is>
       </c>
       <c r="G33" s="37" t="n">
-        <v>-24.8</v>
+        <v>-25.8</v>
       </c>
       <c r="H33" s="37" t="n">
-        <v>-14.5</v>
+        <v>-14</v>
       </c>
       <c r="I33" s="42" t="n">
-        <v>10.3</v>
+        <v>11.8</v>
       </c>
       <c r="J33" s="37" t="n">
         <v>-7.7</v>
@@ -5706,10 +5722,10 @@
         <v>56.1</v>
       </c>
       <c r="M33" s="37" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N33" s="37" t="n">
-        <v>1.8</v>
+        <v>53.5</v>
+      </c>
+      <c r="N33" s="42" t="n">
+        <v>2.6</v>
       </c>
       <c r="O33" s="37" t="n">
         <v>3</v>
@@ -5753,13 +5769,13 @@
         </is>
       </c>
       <c r="G34" s="37" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="H34" s="37" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I34" s="42" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J34" s="37" t="n">
         <v>-9.800000000000001</v>
@@ -5768,13 +5784,13 @@
         <v>-1.9</v>
       </c>
       <c r="L34" s="37" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="M34" s="37" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N34" s="42" t="n">
-        <v>-3.1</v>
+        <v>-2.5</v>
       </c>
       <c r="O34" s="37" t="n">
         <v>42</v>
@@ -5818,13 +5834,13 @@
         </is>
       </c>
       <c r="G35" s="37" t="n">
-        <v>-7.4</v>
+        <v>-6.8</v>
       </c>
       <c r="H35" s="37" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="I35" s="42" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J35" s="37" t="n">
         <v>-15.5</v>
@@ -5833,13 +5849,13 @@
         <v>-3.1</v>
       </c>
       <c r="L35" s="37" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="M35" s="37" t="n">
-        <v>52.2</v>
+        <v>53.5</v>
       </c>
       <c r="N35" s="42" t="n">
-        <v>-6.7</v>
+        <v>-8</v>
       </c>
       <c r="O35" s="37" t="n">
         <v>31</v>
@@ -6397,13 +6413,13 @@
         </is>
       </c>
       <c r="G24" s="37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H24" s="37" t="n">
         <v>2</v>
       </c>
       <c r="I24" s="42" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="J24" s="37" t="n">
         <v>4.4</v>
@@ -6465,10 +6481,10 @@
         <v>23.8</v>
       </c>
       <c r="H25" s="37" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="I25" s="42" t="n">
-        <v>-4.3</v>
+        <v>-3.3</v>
       </c>
       <c r="J25" s="37" t="n">
         <v>17.5</v>
@@ -6527,13 +6543,13 @@
         </is>
       </c>
       <c r="G26" s="37" t="n">
-        <v>-31.3</v>
+        <v>-31.2</v>
       </c>
       <c r="H26" s="37" t="n">
-        <v>-45.8</v>
+        <v>-44.2</v>
       </c>
       <c r="I26" s="42" t="n">
-        <v>-14.5</v>
+        <v>-13</v>
       </c>
       <c r="J26" s="37" t="n">
         <v>-18.2</v>
@@ -6545,10 +6561,10 @@
         <v>56.5</v>
       </c>
       <c r="M26" s="37" t="n">
-        <v>62</v>
+        <v>61.2</v>
       </c>
       <c r="N26" s="42" t="n">
-        <v>-5.5</v>
+        <v>-4.7</v>
       </c>
       <c r="O26" s="37" t="n"/>
       <c r="P26" s="37" t="n"/>
@@ -6602,10 +6618,10 @@
         <v>55.1</v>
       </c>
       <c r="M27" s="37" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="N27" s="37" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="O27" s="37" t="n"/>
       <c r="P27" s="37" t="n"/>
@@ -6644,10 +6660,10 @@
         <v>-13.2</v>
       </c>
       <c r="H28" s="37" t="n">
-        <v>-5.5</v>
+        <v>-6</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>-14.2</v>
@@ -6659,10 +6675,10 @@
         <v>58.3</v>
       </c>
       <c r="M28" s="37" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="N28" s="42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O28" s="37" t="n"/>
       <c r="P28" s="37" t="n"/>
@@ -6716,10 +6732,10 @@
         <v>57.5</v>
       </c>
       <c r="M29" s="37" t="n">
-        <v>54.2</v>
+        <v>52.8</v>
       </c>
       <c r="N29" s="42" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="O29" s="37" t="n">
         <v>14</v>
@@ -6763,13 +6779,13 @@
         </is>
       </c>
       <c r="G30" s="37" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="I30" s="42" t="n">
-        <v>-5</v>
+        <v>-6.4</v>
       </c>
       <c r="J30" s="37" t="n">
         <v>-8.6</v>
@@ -6781,10 +6797,10 @@
         <v>54.9</v>
       </c>
       <c r="M30" s="37" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="N30" s="42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O30" s="37" t="n">
         <v>9</v>
@@ -6831,10 +6847,10 @@
         <v>3.5</v>
       </c>
       <c r="H31" s="37" t="n">
-        <v>-0.2</v>
+        <v>1.5</v>
       </c>
       <c r="I31" s="42" t="n">
-        <v>-3.7</v>
+        <v>-2</v>
       </c>
       <c r="J31" s="37" t="n">
         <v>-8.1</v>
@@ -6846,10 +6862,10 @@
         <v>53.3</v>
       </c>
       <c r="M31" s="37" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="N31" s="42" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="O31" s="37" t="n"/>
       <c r="P31" s="37" t="n"/>
@@ -7469,10 +7485,10 @@
         <v>49</v>
       </c>
       <c r="M26" s="37" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="N26" s="37" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="O26" s="37" t="n"/>
       <c r="P26" s="37" t="n"/>
@@ -7508,13 +7524,13 @@
         </is>
       </c>
       <c r="G27" s="37" t="n">
-        <v>-12.9</v>
+        <v>-12.8</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="I27" s="42" t="n">
-        <v>2.4</v>
+        <v>-11.2</v>
+      </c>
+      <c r="I27" s="37" t="n">
+        <v>1.5</v>
       </c>
       <c r="J27" s="37" t="n">
         <v>-12</v>
@@ -7573,13 +7589,13 @@
         </is>
       </c>
       <c r="G28" s="37" t="n">
-        <v>-13.3</v>
+        <v>-13.4</v>
       </c>
       <c r="H28" s="37" t="n">
         <v>-3</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>-5.6</v>
@@ -7588,7 +7604,7 @@
         <v>-6.3</v>
       </c>
       <c r="L28" s="37" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="M28" s="37" t="n">
         <v>53.2</v>
@@ -7641,10 +7657,10 @@
         <v>-29.9</v>
       </c>
       <c r="H29" s="37" t="n">
-        <v>-21</v>
+        <v>-19.8</v>
       </c>
       <c r="I29" s="42" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="J29" s="37" t="n">
         <v>-19.5</v>
@@ -7656,10 +7672,10 @@
         <v>54.2</v>
       </c>
       <c r="M29" s="37" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N29" s="42" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O29" s="37" t="n">
         <v>0</v>
@@ -7706,10 +7722,10 @@
         <v>2.4</v>
       </c>
       <c r="H30" s="37" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="I30" s="42" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J30" s="37" t="n">
         <v>8.800000000000001</v>
@@ -7721,10 +7737,10 @@
         <v>52.4</v>
       </c>
       <c r="M30" s="37" t="n">
-        <v>48.8</v>
+        <v>47.8</v>
       </c>
       <c r="N30" s="42" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="O30" s="37" t="n"/>
       <c r="P30" s="37" t="n"/>
@@ -7763,10 +7779,10 @@
         <v>-5.9</v>
       </c>
       <c r="H31" s="37" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="I31" s="37" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="J31" s="37" t="n">
         <v>-11</v>
@@ -7778,10 +7794,10 @@
         <v>55.7</v>
       </c>
       <c r="M31" s="37" t="n">
-        <v>56</v>
+        <v>55.5</v>
       </c>
       <c r="N31" s="37" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O31" s="37" t="n"/>
       <c r="P31" s="37" t="n"/>
@@ -7820,10 +7836,10 @@
         <v>-2.3</v>
       </c>
       <c r="H32" s="37" t="n">
-        <v>-3.5</v>
+        <v>-3.8</v>
       </c>
       <c r="I32" s="37" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="J32" s="37" t="n">
         <v>-4</v>
@@ -7835,10 +7851,10 @@
         <v>46.8</v>
       </c>
       <c r="M32" s="37" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N32" s="37" t="n">
-        <v>-1.7</v>
+        <v>49.2</v>
+      </c>
+      <c r="N32" s="42" t="n">
+        <v>-2.4</v>
       </c>
       <c r="O32" s="37" t="n"/>
       <c r="P32" s="37" t="n"/>
@@ -7910,11 +7926,11 @@
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>30-36-1</t>
+          <t>31-36-1</t>
         </is>
       </c>
       <c r="C3" s="40" t="n">
-        <v>0.455</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="4">
@@ -7925,11 +7941,11 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>1-4-0</t>
+          <t>2-4-0</t>
         </is>
       </c>
       <c r="C4" s="40" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="6">
@@ -7974,7 +7990,7 @@
     <row r="8">
       <c r="A8" s="37" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B8" s="37" t="n">
@@ -7987,7 +8003,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="37" t="n">
         <v>0</v>
@@ -7996,7 +8012,7 @@
     <row r="9">
       <c r="A9" s="37" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="B9" s="37" t="n">
@@ -8012,13 +8028,13 @@
         <v>4</v>
       </c>
       <c r="F9" s="37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="37" t="inlineStr">
         <is>
-          <t>Ohio State</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="B10" s="37" t="n">
@@ -8040,7 +8056,7 @@
     <row r="11">
       <c r="A11" s="37" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Ohio State</t>
         </is>
       </c>
       <c r="B11" s="37" t="n">
@@ -8062,11 +8078,11 @@
     <row r="12">
       <c r="A12" s="37" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B12" s="37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="37" t="n">
         <v>0</v>
@@ -8078,13 +8094,13 @@
         <v>4</v>
       </c>
       <c r="F12" s="37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="37" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="B13" s="37" t="n">
@@ -8282,14 +8298,14 @@
     <row r="22" ht="26.5" customHeight="1">
       <c r="A22" s="37" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="B22" s="37" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="37" t="n">
         <v>0</v>
@@ -8298,13 +8314,13 @@
         <v>2</v>
       </c>
       <c r="F22" s="37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="37" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B23" s="37" t="n">
@@ -8487,10 +8503,10 @@
         <v>-14.7</v>
       </c>
       <c r="H28" s="37" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>-16.6</v>
@@ -8549,13 +8565,13 @@
         </is>
       </c>
       <c r="G29" s="37" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H29" s="37" t="n">
         <v>14.2</v>
       </c>
       <c r="I29" s="42" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J29" s="37" t="n">
         <v>7.1</v>
@@ -8567,10 +8583,10 @@
         <v>45.9</v>
       </c>
       <c r="M29" s="37" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="N29" s="37" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="O29" s="37" t="n">
         <v>31</v>
@@ -8614,13 +8630,13 @@
         </is>
       </c>
       <c r="G30" s="37" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="H30" s="37" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I30" s="42" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J30" s="37" t="n">
         <v>5</v>
@@ -8632,10 +8648,10 @@
         <v>43.8</v>
       </c>
       <c r="M30" s="37" t="n">
-        <v>42.2</v>
+        <v>43.5</v>
       </c>
       <c r="N30" s="37" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="O30" s="37" t="n">
         <v>14</v>
@@ -8679,13 +8695,13 @@
         </is>
       </c>
       <c r="G31" s="37" t="n">
-        <v>-19</v>
+        <v>-21.4</v>
       </c>
       <c r="H31" s="37" t="n">
-        <v>-15</v>
+        <v>-14.5</v>
       </c>
       <c r="I31" s="42" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="J31" s="37" t="n">
         <v>-13</v>
@@ -8702,9 +8718,17 @@
       <c r="N31" s="37" t="n">
         <v>-0.3</v>
       </c>
-      <c r="O31" s="37" t="n"/>
-      <c r="P31" s="37" t="n"/>
-      <c r="Q31" s="37" t="n"/>
+      <c r="O31" s="37" t="n">
+        <v>23</v>
+      </c>
+      <c r="P31" s="37" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q31" s="42" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="n">
@@ -8736,13 +8760,13 @@
         </is>
       </c>
       <c r="G32" s="37" t="n">
-        <v>-1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="H32" s="37" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I32" s="42" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="37" t="n">
         <v>0.6</v>
@@ -8754,10 +8778,10 @@
         <v>49.9</v>
       </c>
       <c r="M32" s="37" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="N32" s="42" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O32" s="37" t="n">
         <v>13</v>
@@ -8801,13 +8825,13 @@
         </is>
       </c>
       <c r="G33" s="37" t="n">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="H33" s="37" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="I33" s="42" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="J33" s="37" t="n">
         <v>-5.4</v>
@@ -8858,13 +8882,13 @@
         </is>
       </c>
       <c r="G34" s="37" t="n">
-        <v>-10</v>
+        <v>-10.2</v>
       </c>
       <c r="H34" s="37" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="I34" s="37" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J34" s="37" t="n">
         <v>-9.6</v>
@@ -8873,7 +8897,7 @@
         <v>-9.4</v>
       </c>
       <c r="L34" s="37" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="M34" s="37" t="n">
         <v>43.2</v>
@@ -8926,10 +8950,10 @@
         <v>26.2</v>
       </c>
       <c r="H35" s="37" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I35" s="42" t="n">
-        <v>-2</v>
+        <v>24.5</v>
+      </c>
+      <c r="I35" s="37" t="n">
+        <v>-1.7</v>
       </c>
       <c r="J35" s="37" t="n">
         <v>18.7</v>
@@ -9409,10 +9433,10 @@
         <v>-29.9</v>
       </c>
       <c r="H20" s="37" t="n">
-        <v>-21</v>
+        <v>-19.8</v>
       </c>
       <c r="I20" s="42" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="J20" s="37" t="n">
         <v>-19.5</v>
@@ -9424,10 +9448,10 @@
         <v>54.2</v>
       </c>
       <c r="M20" s="37" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N20" s="42" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O20" s="37" t="n">
         <v>0</v>
@@ -9471,13 +9495,13 @@
         </is>
       </c>
       <c r="G21" s="37" t="n">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="H21" s="37" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I21" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J21" s="37" t="n">
         <v>-0.4</v>
@@ -9489,10 +9513,10 @@
         <v>51</v>
       </c>
       <c r="M21" s="37" t="n">
-        <v>51.5</v>
+        <v>49.8</v>
       </c>
       <c r="N21" s="37" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="O21" s="37" t="n">
         <v>30</v>
@@ -9500,9 +9524,9 @@
       <c r="P21" s="37" t="n">
         <v>14</v>
       </c>
-      <c r="Q21" s="43" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="Q21" s="42" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
     </row>
@@ -9855,13 +9879,13 @@
         </is>
       </c>
       <c r="G12" s="37" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="H12" s="37" t="n">
-        <v>21</v>
-      </c>
-      <c r="I12" s="37" t="n">
-        <v>1.1</v>
+        <v>21.5</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>2</v>
       </c>
       <c r="J12" s="37" t="n">
         <v>11.2</v>
@@ -9920,13 +9944,13 @@
         </is>
       </c>
       <c r="G13" s="37" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="H13" s="37" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I13" s="42" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J13" s="37" t="n">
         <v>-9.800000000000001</v>
@@ -9935,13 +9959,13 @@
         <v>-1.9</v>
       </c>
       <c r="L13" s="37" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="M13" s="37" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N13" s="42" t="n">
-        <v>-3.1</v>
+        <v>-2.5</v>
       </c>
       <c r="O13" s="37" t="n">
         <v>42</v>
@@ -10485,13 +10509,13 @@
         </is>
       </c>
       <c r="G23" s="37" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="H23" s="37" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I23" s="42" t="n">
-        <v>2.3</v>
+        <v>20.5</v>
+      </c>
+      <c r="I23" s="37" t="n">
+        <v>1.5</v>
       </c>
       <c r="J23" s="37" t="n">
         <v>12</v>
@@ -10503,10 +10527,10 @@
         <v>52.4</v>
       </c>
       <c r="M23" s="37" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="N23" s="37" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="O23" s="37" t="n">
         <v>39</v>
@@ -10550,13 +10574,13 @@
         </is>
       </c>
       <c r="G24" s="37" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H24" s="37" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="I24" s="42" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J24" s="37" t="n">
         <v>10.3</v>
@@ -10615,13 +10639,13 @@
         </is>
       </c>
       <c r="G25" s="37" t="n">
-        <v>-12.7</v>
+        <v>-13.4</v>
       </c>
       <c r="H25" s="37" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="I25" s="42" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="J25" s="37" t="n">
         <v>-6.3</v>
@@ -10680,13 +10704,13 @@
         </is>
       </c>
       <c r="G26" s="37" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H26" s="37" t="n">
         <v>3.5</v>
       </c>
       <c r="I26" s="42" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="J26" s="37" t="n">
         <v>11</v>
@@ -10745,13 +10769,13 @@
         </is>
       </c>
       <c r="G27" s="37" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H27" s="37" t="n">
         <v>-5.8</v>
       </c>
       <c r="I27" s="42" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="J27" s="37" t="n">
         <v>1.4</v>
@@ -10763,10 +10787,10 @@
         <v>48.3</v>
       </c>
       <c r="M27" s="37" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="N27" s="37" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="O27" s="37" t="n">
         <v>38</v>
@@ -10813,10 +10837,10 @@
         <v>-20.1</v>
       </c>
       <c r="H28" s="37" t="n">
-        <v>-11.2</v>
+        <v>-13.5</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>8.9</v>
+        <v>6.6</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>-13.8</v>
@@ -10828,10 +10852,10 @@
         <v>48.6</v>
       </c>
       <c r="M28" s="37" t="n">
-        <v>42.2</v>
+        <v>43.5</v>
       </c>
       <c r="N28" s="42" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="O28" s="37" t="n">
         <v>24</v>
@@ -11305,13 +11329,13 @@
         </is>
       </c>
       <c r="G20" s="37" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="H20" s="37" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="I20" s="42" t="n">
-        <v>-5</v>
+        <v>-6.4</v>
       </c>
       <c r="J20" s="37" t="n">
         <v>-8.6</v>
@@ -11323,10 +11347,10 @@
         <v>54.9</v>
       </c>
       <c r="M20" s="37" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="N20" s="42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O20" s="37" t="n">
         <v>9</v>
@@ -11370,16 +11394,16 @@
         </is>
       </c>
       <c r="G21" s="37" t="n">
-        <v>-37.6</v>
+        <v>-37.3</v>
       </c>
       <c r="H21" s="37" t="n">
-        <v>-23.2</v>
+        <v>-22.5</v>
       </c>
       <c r="I21" s="42" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="J21" s="37" t="n">
-        <v>-22.1</v>
+        <v>-22.2</v>
       </c>
       <c r="K21" s="37" t="n">
         <v>-28.2</v>
@@ -11435,13 +11459,13 @@
         </is>
       </c>
       <c r="G22" s="37" t="n">
-        <v>-31.2</v>
+        <v>-30.7</v>
       </c>
       <c r="H22" s="37" t="n">
         <v>-17.2</v>
       </c>
       <c r="I22" s="42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J22" s="37" t="n">
         <v>-22</v>
@@ -11500,13 +11524,13 @@
         </is>
       </c>
       <c r="G23" s="37" t="n">
-        <v>-7.4</v>
+        <v>-6.8</v>
       </c>
       <c r="H23" s="37" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="I23" s="42" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J23" s="37" t="n">
         <v>-15.5</v>
@@ -11515,13 +11539,13 @@
         <v>-3.1</v>
       </c>
       <c r="L23" s="37" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="M23" s="37" t="n">
-        <v>52.2</v>
+        <v>53.5</v>
       </c>
       <c r="N23" s="42" t="n">
-        <v>-6.7</v>
+        <v>-8</v>
       </c>
       <c r="O23" s="37" t="n">
         <v>31</v>
@@ -11568,10 +11592,10 @@
         <v>-6.8</v>
       </c>
       <c r="H24" s="37" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="I24" s="42" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J24" s="37" t="n">
         <v>-6.8</v>
@@ -11583,10 +11607,10 @@
         <v>48.5</v>
       </c>
       <c r="M24" s="37" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="N24" s="42" t="n">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
       <c r="O24" s="37" t="n"/>
       <c r="P24" s="37" t="n"/>
@@ -11999,10 +12023,10 @@
         <v>-14.8</v>
       </c>
       <c r="H18" s="37" t="n">
-        <v>-19.5</v>
+        <v>-18.5</v>
       </c>
       <c r="I18" s="42" t="n">
-        <v>-4.7</v>
+        <v>-3.7</v>
       </c>
       <c r="J18" s="37" t="n">
         <v>-18.5</v>
@@ -12056,10 +12080,10 @@
         <v>1.6</v>
       </c>
       <c r="H19" s="37" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I19" s="42" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J19" s="37" t="n">
         <v>-1.3</v>
@@ -12071,10 +12095,10 @@
         <v>56.2</v>
       </c>
       <c r="M19" s="37" t="n">
-        <v>61.5</v>
+        <v>62.2</v>
       </c>
       <c r="N19" s="42" t="n">
-        <v>-5.3</v>
+        <v>-6</v>
       </c>
       <c r="O19" s="37" t="n"/>
       <c r="P19" s="37" t="n"/>
@@ -12113,10 +12137,10 @@
         <v>3.8</v>
       </c>
       <c r="H20" s="37" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="I20" s="42" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J20" s="37" t="n">
         <v>2.7</v>
@@ -12170,10 +12194,10 @@
         <v>-7.8</v>
       </c>
       <c r="H21" s="37" t="n">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I21" s="42" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="J21" s="37" t="n">
         <v>2.4</v>
@@ -12185,10 +12209,10 @@
         <v>41.4</v>
       </c>
       <c r="M21" s="37" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="N21" s="42" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="O21" s="37" t="n"/>
       <c r="P21" s="37" t="n"/>
@@ -12364,11 +12388,11 @@
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>28-27-0</t>
+          <t>27-29-0</t>
         </is>
       </c>
       <c r="C3" s="40" t="n">
-        <v>0.509</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="4">
@@ -12379,11 +12403,11 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>4-0-0</t>
+          <t>4-1-0</t>
         </is>
       </c>
       <c r="C4" s="40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -12516,7 +12540,7 @@
     <row r="12">
       <c r="A12" s="37" t="inlineStr">
         <is>
-          <t>Mississippi State</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B12" s="37" t="n">
@@ -12538,17 +12562,17 @@
     <row r="13">
       <c r="A13" s="37" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Mississippi State</t>
         </is>
       </c>
       <c r="B13" s="37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="E13" s="37" t="n">
         <v>4</v>
@@ -12560,7 +12584,7 @@
     <row r="14">
       <c r="A14" s="37" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="B14" s="37" t="n">
@@ -12582,7 +12606,7 @@
     <row r="15">
       <c r="A15" s="37" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B15" s="37" t="n">
@@ -12595,7 +12619,7 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="37" t="n">
         <v>1</v>
@@ -12736,7 +12760,7 @@
     <row r="22">
       <c r="A22" s="37" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="B22" s="37" t="n">
@@ -12758,14 +12782,14 @@
     <row r="23">
       <c r="A23" s="37" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="B23" s="37" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="37" t="n">
         <v>0</v>
@@ -12774,7 +12798,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -12894,13 +12918,13 @@
         </is>
       </c>
       <c r="G26" s="37" t="n">
-        <v>-15.8</v>
+        <v>-17.2</v>
       </c>
       <c r="H26" s="37" t="n">
-        <v>-25.5</v>
+        <v>-25.2</v>
       </c>
       <c r="I26" s="42" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8</v>
       </c>
       <c r="J26" s="37" t="n">
         <v>-20.6</v>
@@ -12912,10 +12936,10 @@
         <v>48.9</v>
       </c>
       <c r="M26" s="37" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="N26" s="37" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="O26" s="37" t="n">
         <v>14</v>
@@ -12962,10 +12986,10 @@
         <v>-61.5</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>-53.2</v>
+        <v>-52.8</v>
       </c>
       <c r="I27" s="42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J27" s="37" t="n">
         <v>-40.8</v>
@@ -12977,10 +13001,10 @@
         <v>57.7</v>
       </c>
       <c r="M27" s="37" t="n">
-        <v>62</v>
+        <v>61.5</v>
       </c>
       <c r="N27" s="42" t="n">
-        <v>-4.3</v>
+        <v>-3.8</v>
       </c>
       <c r="O27" s="37" t="n"/>
       <c r="P27" s="37" t="n"/>
@@ -13016,13 +13040,13 @@
         </is>
       </c>
       <c r="G28" s="37" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="H28" s="37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I28" s="42" t="n">
-        <v>-6.7</v>
+        <v>-6</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>12.2</v>
@@ -13034,10 +13058,10 @@
         <v>55.4</v>
       </c>
       <c r="M28" s="37" t="n">
-        <v>62</v>
+        <v>60.2</v>
       </c>
       <c r="N28" s="42" t="n">
-        <v>-6.6</v>
+        <v>-4.8</v>
       </c>
       <c r="O28" s="37" t="n">
         <v>56</v>
@@ -13096,13 +13120,13 @@
         <v>4.7</v>
       </c>
       <c r="L29" s="37" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M29" s="37" t="n">
-        <v>57.8</v>
+        <v>57.5</v>
       </c>
       <c r="N29" s="42" t="n">
-        <v>-6.7</v>
+        <v>-6.4</v>
       </c>
       <c r="O29" s="37" t="n">
         <v>17</v>
@@ -13146,13 +13170,13 @@
         </is>
       </c>
       <c r="G30" s="37" t="n">
-        <v>-12.9</v>
+        <v>-12.7</v>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="I30" s="42" t="n">
-        <v>10.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J30" s="37" t="n">
         <v>-4</v>
@@ -13164,14 +13188,22 @@
         <v>51.8</v>
       </c>
       <c r="M30" s="37" t="n">
-        <v>53</v>
-      </c>
-      <c r="N30" s="37" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O30" s="37" t="n"/>
-      <c r="P30" s="37" t="n"/>
-      <c r="Q30" s="37" t="n"/>
+        <v>54.2</v>
+      </c>
+      <c r="N30" s="42" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="O30" s="37" t="n">
+        <v>35</v>
+      </c>
+      <c r="P30" s="37" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q30" s="43" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="37" t="n">
@@ -13203,13 +13235,13 @@
         </is>
       </c>
       <c r="G31" s="37" t="n">
-        <v>-12.5</v>
+        <v>-12.9</v>
       </c>
       <c r="H31" s="37" t="n">
-        <v>-6.2</v>
+        <v>-7</v>
       </c>
       <c r="I31" s="42" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="J31" s="37" t="n">
         <v>-14.1</v>
@@ -13221,10 +13253,10 @@
         <v>48</v>
       </c>
       <c r="M31" s="37" t="n">
-        <v>54.2</v>
+        <v>53.8</v>
       </c>
       <c r="N31" s="42" t="n">
-        <v>-6.2</v>
+        <v>-5.7</v>
       </c>
       <c r="O31" s="37" t="n">
         <v>14</v>
@@ -13271,10 +13303,10 @@
         <v>-17</v>
       </c>
       <c r="H32" s="37" t="n">
-        <v>-13.8</v>
+        <v>-14</v>
       </c>
       <c r="I32" s="42" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J32" s="37" t="n">
         <v>-16.9</v>
@@ -13830,10 +13862,10 @@
         <v>0.2</v>
       </c>
       <c r="H24" s="37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I24" s="42" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
+      </c>
+      <c r="I24" s="37" t="n">
+        <v>1.3</v>
       </c>
       <c r="J24" s="37" t="n">
         <v>0.4</v>
@@ -13845,10 +13877,10 @@
         <v>55.7</v>
       </c>
       <c r="M24" s="37" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N24" s="42" t="n">
-        <v>2.2</v>
+        <v>53.8</v>
+      </c>
+      <c r="N24" s="37" t="n">
+        <v>1.9</v>
       </c>
       <c r="O24" s="37" t="n"/>
       <c r="P24" s="37" t="n"/>
@@ -13887,10 +13919,10 @@
         <v>2.1</v>
       </c>
       <c r="H25" s="37" t="n">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="I25" s="42" t="n">
-        <v>-4.1</v>
+        <v>-4.6</v>
       </c>
       <c r="J25" s="37" t="n">
         <v>-0.3</v>
@@ -13949,13 +13981,13 @@
         </is>
       </c>
       <c r="G26" s="37" t="n">
-        <v>-29.6</v>
+        <v>-29.7</v>
       </c>
       <c r="H26" s="37" t="n">
-        <v>-16.2</v>
+        <v>-19.2</v>
       </c>
       <c r="I26" s="42" t="n">
-        <v>13.3</v>
+        <v>10.5</v>
       </c>
       <c r="J26" s="37" t="n">
         <v>-12.4</v>
@@ -13967,10 +13999,10 @@
         <v>56.3</v>
       </c>
       <c r="M26" s="37" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="N26" s="37" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="O26" s="37" t="n">
         <v>17</v>
@@ -14017,10 +14049,10 @@
         <v>3.5</v>
       </c>
       <c r="H27" s="37" t="n">
-        <v>-0.2</v>
+        <v>1.5</v>
       </c>
       <c r="I27" s="42" t="n">
-        <v>-3.7</v>
+        <v>-2</v>
       </c>
       <c r="J27" s="37" t="n">
         <v>-8.1</v>
@@ -14032,10 +14064,10 @@
         <v>53.3</v>
       </c>
       <c r="M27" s="37" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="N27" s="42" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="O27" s="37" t="n"/>
       <c r="P27" s="37" t="n"/>
@@ -14074,10 +14106,10 @@
         <v>-15.6</v>
       </c>
       <c r="H28" s="37" t="n">
-        <v>-13.8</v>
+        <v>-14</v>
       </c>
       <c r="I28" s="37" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J28" s="37" t="n">
         <v>-21.1</v>
@@ -14089,10 +14121,10 @@
         <v>56.6</v>
       </c>
       <c r="M28" s="37" t="n">
-        <v>57</v>
+        <v>57.5</v>
       </c>
       <c r="N28" s="37" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="O28" s="37" t="n"/>
       <c r="P28" s="37" t="n"/>
@@ -14131,10 +14163,10 @@
         <v>-4.3</v>
       </c>
       <c r="H29" s="37" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="I29" s="37" t="n">
-        <v>-1.4</v>
+        <v>-6.5</v>
+      </c>
+      <c r="I29" s="42" t="n">
+        <v>-2.2</v>
       </c>
       <c r="J29" s="37" t="n">
         <v>-7.4</v>
@@ -14146,10 +14178,10 @@
         <v>51.5</v>
       </c>
       <c r="M29" s="37" t="n">
-        <v>49</v>
+        <v>47.8</v>
       </c>
       <c r="N29" s="42" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="O29" s="37" t="n"/>
       <c r="P29" s="37" t="n"/>
@@ -14293,10 +14325,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="G2" s="6">
         <f>F2-E2</f>
@@ -14310,7 +14342,7 @@
         <v>54.9</v>
       </c>
       <c r="J2" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -14351,7 +14383,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-31.2</v>
+        <v>-30.7</v>
       </c>
       <c r="F3" t="n">
         <v>-17.2</v>
@@ -14407,10 +14439,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-7.4</v>
+        <v>-6.8</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="G4" s="6">
         <f>F4-E4</f>
@@ -14421,10 +14453,10 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="n">
-        <v>52.2</v>
+        <v>53.5</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -14463,10 +14495,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-37.6</v>
+        <v>-37.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-23.2</v>
+        <v>-22.5</v>
       </c>
       <c r="G5" s="6">
         <f>F5-E5</f>
@@ -14527,7 +14559,7 @@
         <v>-6.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="G6" s="6">
         <f>F6-E6</f>
@@ -14541,7 +14573,7 @@
         <v>48.5</v>
       </c>
       <c r="J6" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -24998,10 +25030,10 @@
         <v>7.8</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0.1678349346428817</v>
+        <v>0.156824607490598</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>-0.181694328952023</v>
+        <v>-0.1560976801881319</v>
       </c>
       <c r="H2" s="9" t="n">
         <v>117</v>
@@ -25035,10 +25067,10 @@
         <v>-2.4</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.06510813285458766</v>
+        <v>0.0529135687229341</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.04498009596690349</v>
+        <v>0.07570992671064915</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>63</v>
@@ -25072,10 +25104,10 @@
         <v>7.7</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.1847788819920051</v>
+        <v>0.1625145914195359</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>-0.1769707647780528</v>
+        <v>-0.1458178721495771</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>87</v>
@@ -25146,10 +25178,10 @@
         <v>-3.4</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.1897182411253068</v>
+        <v>0.2974661943078536</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.0006029415712754172</v>
+        <v>0.004400601889996306</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>141</v>
@@ -25183,10 +25215,10 @@
         <v>-12.7</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.07614824835866943</v>
+        <v>0.1562028838199938</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.141371716108203</v>
+        <v>0.1233751116920913</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>114</v>
@@ -25331,10 +25363,10 @@
         <v>-24</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>-0.2049394058109931</v>
+        <v>-0.1789529945845773</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.2564665617671945</v>
+        <v>0.2519532316649529</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>92</v>
@@ -25410,42 +25442,42 @@
     <row r="2">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Ohio State</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="B2" s="37" t="n">
-        <v>93.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="C2" s="37" t="n">
-        <v>92.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="D2" s="37" t="n">
-        <v>94</v>
+        <v>96.5</v>
       </c>
       <c r="E2" s="37" t="n">
-        <v>94.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F2" s="37" t="n">
-        <v>94.7</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Ohio State</t>
         </is>
       </c>
       <c r="B3" s="37" t="n">
-        <v>97</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="C3" s="37" t="n">
-        <v>97</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D3" s="37" t="n">
-        <v>96.5</v>
+        <v>93.8</v>
       </c>
       <c r="E3" s="37" t="n">
-        <v>94.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="F3" s="37" t="n">
         <v>94.5</v>
@@ -25474,13 +25506,13 @@
         <v>91.7</v>
       </c>
       <c r="D4" s="37" t="n">
-        <v>88.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="E4" s="37" t="n">
-        <v>89.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F4" s="37" t="n">
-        <v>89.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="V4" s="37" t="inlineStr">
         <is>
@@ -25512,7 +25544,7 @@
         <v>89</v>
       </c>
       <c r="F5" s="37" t="n">
-        <v>89.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="V5" s="37" t="inlineStr">
         <is>
@@ -25566,7 +25598,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="F7" s="37" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="V7" s="37" t="inlineStr">
         <is>
@@ -25587,16 +25619,16 @@
         <v>80.90000000000001</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D8" s="37" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E8" s="37" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F8" s="37" t="n">
-        <v>86.09999999999999</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="9">
@@ -25615,10 +25647,10 @@
         <v>86.40000000000001</v>
       </c>
       <c r="E9" s="37" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F9" s="37" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="V9" s="38" t="inlineStr">
         <is>
@@ -25670,10 +25702,10 @@
         <v>85.09999999999999</v>
       </c>
       <c r="D11" s="37" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="E11" s="37" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="F11" s="37" t="n">
         <v>84.3</v>
@@ -25704,45 +25736,45 @@
     <row r="13">
       <c r="A13" s="37" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Ole Miss</t>
         </is>
       </c>
       <c r="B13" s="37" t="n">
-        <v>81.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="C13" s="37" t="n">
-        <v>80.2</v>
+        <v>84</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>82.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="E13" s="37" t="n">
-        <v>81.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F13" s="37" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="37" t="inlineStr">
         <is>
-          <t>Ole Miss</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="B14" s="37" t="n">
-        <v>84.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="C14" s="37" t="n">
-        <v>84</v>
+        <v>80.2</v>
       </c>
       <c r="D14" s="37" t="n">
-        <v>84.5</v>
+        <v>81.7</v>
       </c>
       <c r="E14" s="37" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="F14" s="37" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="15">
@@ -25761,10 +25793,10 @@
         <v>78.90000000000001</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
       <c r="F15" s="37" t="n">
-        <v>80.2</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="16">
@@ -25824,10 +25856,10 @@
         <v>74.8</v>
       </c>
       <c r="D18" s="37" t="n">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="E18" s="37" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F18" s="37" t="n">
         <v>78.2</v>
@@ -25846,10 +25878,10 @@
         <v>69.8</v>
       </c>
       <c r="D19" s="37" t="n">
-        <v>73</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E19" s="37" t="n">
-        <v>73.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F19" s="37" t="n">
         <v>78</v>
@@ -25858,23 +25890,23 @@
     <row r="20">
       <c r="A20" s="37" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Penn State</t>
         </is>
       </c>
       <c r="B20" s="37" t="n">
-        <v>74.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C20" s="37" t="n">
-        <v>77.2</v>
+        <v>80.3</v>
       </c>
       <c r="D20" s="37" t="n">
-        <v>77.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="E20" s="37" t="n">
-        <v>77.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="F20" s="37" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="21">
@@ -25887,13 +25919,13 @@
         <v>81.2</v>
       </c>
       <c r="C21" s="37" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="D21" s="37" t="n">
         <v>79.7</v>
       </c>
       <c r="E21" s="37" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="F21" s="37" t="n">
         <v>77.59999999999999</v>
@@ -25902,23 +25934,23 @@
     <row r="22">
       <c r="A22" s="37" t="inlineStr">
         <is>
-          <t>Penn State</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="B22" s="37" t="n">
-        <v>80.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C22" s="37" t="n">
-        <v>80.3</v>
+        <v>77.2</v>
       </c>
       <c r="D22" s="37" t="n">
-        <v>81.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E22" s="37" t="n">
-        <v>80.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="F22" s="37" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -25940,139 +25972,139 @@
         <v>77.5</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="37" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="B24" s="37" t="n">
-        <v>80.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="C24" s="37" t="n">
-        <v>79.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D24" s="37" t="n">
-        <v>78.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E24" s="37" t="n">
-        <v>77.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="F24" s="37" t="n">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="37" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="B25" s="37" t="n">
-        <v>78</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C25" s="37" t="n">
-        <v>77.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="D25" s="37" t="n">
-        <v>77.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E25" s="37" t="n">
-        <v>77</v>
+        <v>77.5</v>
       </c>
       <c r="F25" s="37" t="n">
-        <v>77</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B26" s="37" t="n">
-        <v>75.3</v>
+        <v>67.8</v>
       </c>
       <c r="C26" s="37" t="n">
-        <v>74.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D26" s="37" t="n">
-        <v>74</v>
+        <v>74.2</v>
       </c>
       <c r="E26" s="37" t="n">
-        <v>76.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F26" s="37" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="37" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B27" s="37" t="n">
-        <v>67.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C27" s="37" t="n">
-        <v>73.5</v>
+        <v>74.7</v>
       </c>
       <c r="D27" s="37" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="E27" s="37" t="n">
-        <v>76.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="37" t="inlineStr">
         <is>
-          <t>North Dakota State</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B28" s="37" t="n">
-        <v>79.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C28" s="37" t="n">
-        <v>77.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="D28" s="37" t="n">
-        <v>76</v>
+        <v>77.5</v>
       </c>
       <c r="E28" s="37" t="n">
-        <v>76</v>
+        <v>76.3</v>
       </c>
       <c r="F28" s="37" t="n">
-        <v>76.40000000000001</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="37" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>North Dakota State</t>
         </is>
       </c>
       <c r="B29" s="37" t="n">
-        <v>79.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="C29" s="37" t="n">
-        <v>78.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D29" s="37" t="n">
-        <v>77.5</v>
+        <v>76</v>
       </c>
       <c r="E29" s="37" t="n">
-        <v>76.3</v>
+        <v>76</v>
       </c>
       <c r="F29" s="37" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -26091,10 +26123,10 @@
         <v>76.3</v>
       </c>
       <c r="E30" s="37" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="F30" s="37" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -26122,42 +26154,42 @@
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B32" s="37" t="n">
-        <v>68.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="C32" s="37" t="n">
-        <v>68.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D32" s="37" t="n">
-        <v>71.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E32" s="37" t="n">
-        <v>72.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F32" s="37" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="B33" s="37" t="n">
-        <v>72.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C33" s="37" t="n">
-        <v>74.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D33" s="37" t="n">
-        <v>74.3</v>
+        <v>71.2</v>
       </c>
       <c r="E33" s="37" t="n">
-        <v>75.3</v>
+        <v>72.8</v>
       </c>
       <c r="F33" s="37" t="n">
         <v>75.2</v>
@@ -26179,7 +26211,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="E34" s="37" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="F34" s="37" t="n">
         <v>75.09999999999999</v>
@@ -26217,16 +26249,16 @@
         <v>68.90000000000001</v>
       </c>
       <c r="C36" s="37" t="n">
-        <v>73.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D36" s="37" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E36" s="37" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="F36" s="37" t="n">
         <v>73.3</v>
-      </c>
-      <c r="F36" s="37" t="n">
-        <v>73.5</v>
       </c>
     </row>
     <row r="37">
@@ -26239,57 +26271,57 @@
         <v>71.2</v>
       </c>
       <c r="C37" s="37" t="n">
-        <v>73</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D37" s="37" t="n">
-        <v>73.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="E37" s="37" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>73.09999999999999</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="37" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Kansas State</t>
         </is>
       </c>
       <c r="B38" s="37" t="n">
-        <v>66.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="C38" s="37" t="n">
-        <v>71.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="D38" s="37" t="n">
-        <v>70.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E38" s="37" t="n">
-        <v>70.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="37" t="inlineStr">
         <is>
-          <t>Kansas State</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B39" s="37" t="n">
-        <v>70.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C39" s="37" t="n">
-        <v>73.2</v>
+        <v>71</v>
       </c>
       <c r="D39" s="37" t="n">
-        <v>73.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E39" s="37" t="n">
-        <v>72.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F39" s="37" t="n">
         <v>72.90000000000001</v>
@@ -26380,7 +26412,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -26440,13 +26472,13 @@
         <v>67.2</v>
       </c>
       <c r="D46" s="37" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="E46" s="37" t="n">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>71.09999999999999</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47">
@@ -26468,7 +26500,7 @@
         <v>71.7</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>70.90000000000001</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48">
@@ -26506,13 +26538,13 @@
         <v>72.09999999999999</v>
       </c>
       <c r="D49" s="37" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E49" s="37" t="n">
         <v>70.7</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -26528,10 +26560,10 @@
         <v>65.40000000000001</v>
       </c>
       <c r="D50" s="37" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="E50" s="37" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="F50" s="37" t="n">
         <v>70.09999999999999</v>
@@ -26556,7 +26588,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="F51" s="37" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
@@ -26572,13 +26604,13 @@
         <v>64.3</v>
       </c>
       <c r="D52" s="37" t="n">
-        <v>65.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E52" s="37" t="n">
-        <v>66.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="53">
@@ -26594,7 +26626,7 @@
         <v>71.2</v>
       </c>
       <c r="D53" s="37" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="E53" s="37" t="n">
         <v>71.7</v>
@@ -26666,7 +26698,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="F56" s="37" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="57">
@@ -26694,23 +26726,23 @@
     <row r="58">
       <c r="A58" s="37" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="B58" s="37" t="n">
-        <v>68.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C58" s="37" t="n">
-        <v>68.3</v>
+        <v>67.5</v>
       </c>
       <c r="D58" s="37" t="n">
-        <v>69.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E58" s="37" t="n">
-        <v>67.7</v>
+        <v>67.2</v>
       </c>
       <c r="F58" s="37" t="n">
-        <v>67.7</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -26738,45 +26770,45 @@
     <row r="60">
       <c r="A60" s="37" t="inlineStr">
         <is>
-          <t>Texas State</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="B60" s="37" t="n">
-        <v>60.5</v>
+        <v>68.2</v>
       </c>
       <c r="C60" s="37" t="n">
-        <v>61.5</v>
+        <v>68.3</v>
       </c>
       <c r="D60" s="37" t="n">
-        <v>64.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="E60" s="37" t="n">
-        <v>67.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="F60" s="37" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="37" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Texas State</t>
         </is>
       </c>
       <c r="B61" s="37" t="n">
-        <v>64.40000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="C61" s="37" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D61" s="37" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="E61" s="37" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F61" s="37" t="n">
         <v>67.5</v>
-      </c>
-      <c r="D61" s="37" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="E61" s="37" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="F61" s="37" t="n">
-        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -26798,7 +26830,7 @@
         <v>67.8</v>
       </c>
       <c r="F62" s="37" t="n">
-        <v>66.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -26855,57 +26887,57 @@
         <v>63.9</v>
       </c>
       <c r="C65" s="37" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D65" s="37" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="E65" s="37" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F65" s="37" t="n">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="37" t="inlineStr">
         <is>
-          <t>East Carolina</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="B66" s="37" t="n">
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="C66" s="37" t="n">
-        <v>63.1</v>
+        <v>65</v>
       </c>
       <c r="D66" s="37" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="E66" s="37" t="n">
-        <v>65.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="F66" s="37" t="n">
-        <v>65.09999999999999</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="37" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>East Carolina</t>
         </is>
       </c>
       <c r="B67" s="37" t="n">
-        <v>62.1</v>
+        <v>64.8</v>
       </c>
       <c r="C67" s="37" t="n">
-        <v>65</v>
+        <v>63.1</v>
       </c>
       <c r="D67" s="37" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="E67" s="37" t="n">
-        <v>66.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F67" s="37" t="n">
         <v>65.09999999999999</v>
@@ -27018,7 +27050,7 @@
         <v>62.3</v>
       </c>
       <c r="F72" s="37" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -27059,10 +27091,10 @@
         <v>67.2</v>
       </c>
       <c r="E74" s="37" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F74" s="37" t="n">
-        <v>63.7</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="75">
@@ -27075,16 +27107,16 @@
         <v>66</v>
       </c>
       <c r="C75" s="37" t="n">
-        <v>66.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D75" s="37" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="E75" s="37" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F75" s="37" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="76">
@@ -27112,67 +27144,67 @@
     <row r="77">
       <c r="A77" s="37" t="inlineStr">
         <is>
-          <t>UNLV</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="B77" s="37" t="n">
-        <v>62.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C77" s="37" t="n">
-        <v>59.2</v>
+        <v>69.5</v>
       </c>
       <c r="D77" s="37" t="n">
-        <v>59.2</v>
+        <v>68.5</v>
       </c>
       <c r="E77" s="37" t="n">
-        <v>61.2</v>
+        <v>66.3</v>
       </c>
       <c r="F77" s="37" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="37" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Tulane</t>
         </is>
       </c>
       <c r="B78" s="37" t="n">
-        <v>72.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="C78" s="37" t="n">
-        <v>69.5</v>
+        <v>63.1</v>
       </c>
       <c r="D78" s="37" t="n">
-        <v>68.5</v>
+        <v>62.9</v>
       </c>
       <c r="E78" s="37" t="n">
-        <v>66.3</v>
+        <v>61.7</v>
       </c>
       <c r="F78" s="37" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="37" t="inlineStr">
         <is>
-          <t>Tulane</t>
+          <t>UNLV</t>
         </is>
       </c>
       <c r="B79" s="37" t="n">
-        <v>63.9</v>
+        <v>62.6</v>
       </c>
       <c r="C79" s="37" t="n">
-        <v>63.1</v>
+        <v>59</v>
       </c>
       <c r="D79" s="37" t="n">
-        <v>62.9</v>
+        <v>59</v>
       </c>
       <c r="E79" s="37" t="n">
-        <v>61.7</v>
+        <v>60.9</v>
       </c>
       <c r="F79" s="37" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="80">
@@ -27185,7 +27217,7 @@
         <v>58.2</v>
       </c>
       <c r="C80" s="37" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
       <c r="D80" s="37" t="n">
         <v>63.4</v>
@@ -27244,42 +27276,42 @@
     <row r="83">
       <c r="A83" s="37" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="B83" s="37" t="n">
-        <v>62.3</v>
+        <v>57.2</v>
       </c>
       <c r="C83" s="37" t="n">
-        <v>64.90000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="D83" s="37" t="n">
-        <v>64.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="E83" s="37" t="n">
-        <v>60.2</v>
+        <v>59.2</v>
       </c>
       <c r="F83" s="37" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="37" t="inlineStr">
         <is>
-          <t>Air Force</t>
+          <t>Fresno State</t>
         </is>
       </c>
       <c r="B84" s="37" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="C84" s="37" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="D84" s="37" t="n">
-        <v>59.1</v>
+        <v>60</v>
       </c>
       <c r="E84" s="37" t="n">
-        <v>58.8</v>
+        <v>60.1</v>
       </c>
       <c r="F84" s="37" t="n">
         <v>60.1</v>
@@ -27288,64 +27320,64 @@
     <row r="85">
       <c r="A85" s="37" t="inlineStr">
         <is>
-          <t>Fresno State</t>
+          <t>Oregon State</t>
         </is>
       </c>
       <c r="B85" s="37" t="n">
-        <v>56</v>
+        <v>54.3</v>
       </c>
       <c r="C85" s="37" t="n">
-        <v>59.2</v>
+        <v>56.5</v>
       </c>
       <c r="D85" s="37" t="n">
-        <v>60</v>
+        <v>59.6</v>
       </c>
       <c r="E85" s="37" t="n">
-        <v>60.1</v>
+        <v>59.9</v>
       </c>
       <c r="F85" s="37" t="n">
-        <v>60.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="37" t="inlineStr">
         <is>
-          <t>Oregon State</t>
+          <t>San Diego State</t>
         </is>
       </c>
       <c r="B86" s="37" t="n">
-        <v>54.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="C86" s="37" t="n">
-        <v>56.5</v>
+        <v>62.6</v>
       </c>
       <c r="D86" s="37" t="n">
-        <v>59.6</v>
+        <v>62</v>
       </c>
       <c r="E86" s="37" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="F86" s="37" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="37" t="inlineStr">
         <is>
-          <t>San Diego State</t>
+          <t>Air Force</t>
         </is>
       </c>
       <c r="B87" s="37" t="n">
-        <v>64.59999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="C87" s="37" t="n">
-        <v>62.6</v>
+        <v>59.1</v>
       </c>
       <c r="D87" s="37" t="n">
-        <v>62</v>
+        <v>59.1</v>
       </c>
       <c r="E87" s="37" t="n">
-        <v>59.7</v>
+        <v>58.7</v>
       </c>
       <c r="F87" s="37" t="n">
         <v>59.7</v>
@@ -27376,42 +27408,42 @@
     <row r="89">
       <c r="A89" s="37" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B89" s="37" t="n">
-        <v>57.2</v>
+        <v>62.3</v>
       </c>
       <c r="C89" s="37" t="n">
-        <v>55.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D89" s="37" t="n">
-        <v>58</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E89" s="37" t="n">
-        <v>59.2</v>
+        <v>60.2</v>
       </c>
       <c r="F89" s="37" t="n">
-        <v>59.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="37" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B90" s="37" t="n">
-        <v>56.7</v>
+        <v>60.4</v>
       </c>
       <c r="C90" s="37" t="n">
-        <v>57.9</v>
+        <v>59.8</v>
       </c>
       <c r="D90" s="37" t="n">
-        <v>57</v>
+        <v>60.5</v>
       </c>
       <c r="E90" s="37" t="n">
-        <v>56.5</v>
+        <v>59.5</v>
       </c>
       <c r="F90" s="37" t="n">
         <v>58.8</v>
@@ -27420,23 +27452,23 @@
     <row r="91">
       <c r="A91" s="37" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="B91" s="37" t="n">
-        <v>60.4</v>
+        <v>56.7</v>
       </c>
       <c r="C91" s="37" t="n">
-        <v>59.4</v>
+        <v>57.9</v>
       </c>
       <c r="D91" s="37" t="n">
-        <v>60.2</v>
+        <v>57</v>
       </c>
       <c r="E91" s="37" t="n">
-        <v>59.2</v>
+        <v>56.5</v>
       </c>
       <c r="F91" s="37" t="n">
-        <v>58.5</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="92">
@@ -27458,7 +27490,7 @@
         <v>59.6</v>
       </c>
       <c r="F92" s="37" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="93">
@@ -27508,133 +27540,133 @@
     <row r="95">
       <c r="A95" s="37" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B95" s="37" t="n">
-        <v>61.4</v>
+        <v>54.3</v>
       </c>
       <c r="C95" s="37" t="n">
-        <v>61.4</v>
+        <v>54.8</v>
       </c>
       <c r="D95" s="37" t="n">
-        <v>59.9</v>
+        <v>55.3</v>
       </c>
       <c r="E95" s="37" t="n">
-        <v>61.4</v>
+        <v>57</v>
       </c>
       <c r="F95" s="37" t="n">
-        <v>57.2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="37" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="B96" s="37" t="n">
-        <v>55.7</v>
+        <v>55.3</v>
       </c>
       <c r="C96" s="37" t="n">
-        <v>56.6</v>
+        <v>55.4</v>
       </c>
       <c r="D96" s="37" t="n">
-        <v>57.4</v>
+        <v>58.2</v>
       </c>
       <c r="E96" s="37" t="n">
-        <v>57.4</v>
+        <v>55.9</v>
       </c>
       <c r="F96" s="37" t="n">
-        <v>57.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="37" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="B97" s="37" t="n">
-        <v>54.3</v>
+        <v>55.7</v>
       </c>
       <c r="C97" s="37" t="n">
-        <v>54.8</v>
+        <v>56.3</v>
       </c>
       <c r="D97" s="37" t="n">
-        <v>55.3</v>
+        <v>56.8</v>
       </c>
       <c r="E97" s="37" t="n">
-        <v>57</v>
+        <v>56.8</v>
       </c>
       <c r="F97" s="37" t="n">
-        <v>57</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="37" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Louisiana Tech</t>
         </is>
       </c>
       <c r="B98" s="37" t="n">
-        <v>55.3</v>
+        <v>58.3</v>
       </c>
       <c r="C98" s="37" t="n">
-        <v>55.4</v>
+        <v>57.3</v>
       </c>
       <c r="D98" s="37" t="n">
-        <v>58.2</v>
+        <v>56.7</v>
       </c>
       <c r="E98" s="37" t="n">
-        <v>55.9</v>
+        <v>56.7</v>
       </c>
       <c r="F98" s="37" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="37" t="inlineStr">
         <is>
-          <t>Louisiana Tech</t>
+          <t>Arkansas State</t>
         </is>
       </c>
       <c r="B99" s="37" t="n">
-        <v>58.3</v>
+        <v>54.6</v>
       </c>
       <c r="C99" s="37" t="n">
-        <v>57.3</v>
+        <v>58.5</v>
       </c>
       <c r="D99" s="37" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="E99" s="37" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="F99" s="37" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="37" t="inlineStr">
         <is>
-          <t>Arkansas State</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="B100" s="37" t="n">
-        <v>54.6</v>
+        <v>61.4</v>
       </c>
       <c r="C100" s="37" t="n">
-        <v>58.5</v>
+        <v>61.4</v>
       </c>
       <c r="D100" s="37" t="n">
-        <v>56.6</v>
+        <v>59.9</v>
       </c>
       <c r="E100" s="37" t="n">
-        <v>56.6</v>
+        <v>61.4</v>
       </c>
       <c r="F100" s="37" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="101">
@@ -27675,10 +27707,10 @@
         <v>55.1</v>
       </c>
       <c r="E102" s="37" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="F102" s="37" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="103">
@@ -27728,64 +27760,64 @@
     <row r="105">
       <c r="A105" s="37" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Florida International</t>
         </is>
       </c>
       <c r="B105" s="37" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="C105" s="37" t="n">
-        <v>57.4</v>
+        <v>56.4</v>
       </c>
       <c r="D105" s="37" t="n">
-        <v>57.8</v>
+        <v>55.5</v>
       </c>
       <c r="E105" s="37" t="n">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="F105" s="37" t="n">
-        <v>55.5</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="37" t="inlineStr">
         <is>
-          <t>Florida International</t>
+          <t>Central Michigan</t>
         </is>
       </c>
       <c r="B106" s="37" t="n">
-        <v>55.5</v>
+        <v>55</v>
       </c>
       <c r="C106" s="37" t="n">
-        <v>56.4</v>
+        <v>53.8</v>
       </c>
       <c r="D106" s="37" t="n">
-        <v>55.5</v>
+        <v>54.6</v>
       </c>
       <c r="E106" s="37" t="n">
-        <v>55.6</v>
+        <v>53.1</v>
       </c>
       <c r="F106" s="37" t="n">
-        <v>55.3</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="37" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B107" s="37" t="n">
-        <v>57.3</v>
+        <v>56.1</v>
       </c>
       <c r="C107" s="37" t="n">
-        <v>54.7</v>
+        <v>57.4</v>
       </c>
       <c r="D107" s="37" t="n">
-        <v>57.3</v>
+        <v>57.8</v>
       </c>
       <c r="E107" s="37" t="n">
-        <v>54.4</v>
+        <v>55.9</v>
       </c>
       <c r="F107" s="37" t="n">
         <v>54.6</v>
@@ -27794,23 +27826,23 @@
     <row r="108">
       <c r="A108" s="37" t="inlineStr">
         <is>
-          <t>Central Michigan</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="B108" s="37" t="n">
-        <v>55</v>
+        <v>57.3</v>
       </c>
       <c r="C108" s="37" t="n">
-        <v>53.8</v>
+        <v>54.7</v>
       </c>
       <c r="D108" s="37" t="n">
-        <v>54.6</v>
+        <v>57.3</v>
       </c>
       <c r="E108" s="37" t="n">
-        <v>53</v>
+        <v>54.4</v>
       </c>
       <c r="F108" s="37" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="109">
@@ -28005,10 +28037,10 @@
         <v>51.8</v>
       </c>
       <c r="E117" s="37" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="F117" s="37" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="118">
@@ -28049,7 +28081,7 @@
         <v>49.5</v>
       </c>
       <c r="E119" s="37" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F119" s="37" t="n">
         <v>51.9</v>
@@ -28115,10 +28147,10 @@
         <v>52.5</v>
       </c>
       <c r="E122" s="37" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="F122" s="37" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="123">
@@ -28162,48 +28194,48 @@
         <v>48.8</v>
       </c>
       <c r="F124" s="37" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="37" t="inlineStr">
         <is>
-          <t>Eastern Michigan</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B125" s="37" t="n">
-        <v>47.2</v>
+        <v>48.6</v>
       </c>
       <c r="C125" s="37" t="n">
-        <v>46.4</v>
+        <v>48.8</v>
       </c>
       <c r="D125" s="37" t="n">
-        <v>44.8</v>
+        <v>47.5</v>
       </c>
       <c r="E125" s="37" t="n">
-        <v>47.4</v>
+        <v>49.6</v>
       </c>
       <c r="F125" s="37" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="37" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Eastern Michigan</t>
         </is>
       </c>
       <c r="B126" s="37" t="n">
-        <v>48.6</v>
+        <v>47.2</v>
       </c>
       <c r="C126" s="37" t="n">
-        <v>48.8</v>
+        <v>46.4</v>
       </c>
       <c r="D126" s="37" t="n">
-        <v>47.5</v>
+        <v>44.4</v>
       </c>
       <c r="E126" s="37" t="n">
-        <v>49.6</v>
+        <v>46.8</v>
       </c>
       <c r="F126" s="37" t="n">
         <v>49.2</v>
@@ -28244,13 +28276,13 @@
         <v>47.5</v>
       </c>
       <c r="D128" s="37" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="E128" s="37" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="F128" s="37" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="129">
@@ -28291,10 +28323,10 @@
         <v>49.3</v>
       </c>
       <c r="E130" s="37" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="F130" s="37" t="n">
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="131">
@@ -28344,20 +28376,20 @@
     <row r="133">
       <c r="A133" s="37" t="inlineStr">
         <is>
-          <t>Ball State</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B133" s="37" t="n">
-        <v>43</v>
+        <v>37.6</v>
       </c>
       <c r="C133" s="37" t="n">
-        <v>45</v>
+        <v>41.2</v>
       </c>
       <c r="D133" s="37" t="n">
-        <v>42.1</v>
+        <v>41.1</v>
       </c>
       <c r="E133" s="37" t="n">
-        <v>41.3</v>
+        <v>45.6</v>
       </c>
       <c r="F133" s="37" t="n">
         <v>42.6</v>
@@ -28388,23 +28420,23 @@
     <row r="135">
       <c r="A135" s="37" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Ball State</t>
         </is>
       </c>
       <c r="B135" s="37" t="n">
-        <v>37.6</v>
+        <v>43</v>
       </c>
       <c r="C135" s="37" t="n">
+        <v>45</v>
+      </c>
+      <c r="D135" s="37" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E135" s="37" t="n">
         <v>41.2</v>
       </c>
-      <c r="D135" s="37" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="E135" s="37" t="n">
-        <v>45.6</v>
-      </c>
       <c r="F135" s="37" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="136">
@@ -28470,7 +28502,7 @@
         <v>42.3</v>
       </c>
       <c r="F138" s="37" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="139">
@@ -28888,7 +28920,7 @@
         </is>
       </c>
       <c r="F20" s="37" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="G20" s="37" t="n">
         <v>5</v>
@@ -28899,7 +28931,7 @@
         </is>
       </c>
       <c r="I20" s="37" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21">
@@ -29395,7 +29427,7 @@
         </is>
       </c>
       <c r="F33" s="37" t="n">
-        <v>-23.2</v>
+        <v>-22.5</v>
       </c>
       <c r="G33" s="37" t="n">
         <v>54</v>
@@ -29406,7 +29438,7 @@
         </is>
       </c>
       <c r="I33" s="37" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="34">
@@ -30097,7 +30129,7 @@
         </is>
       </c>
       <c r="F51" s="37" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="G51" s="37" t="n">
         <v>8</v>
@@ -30108,7 +30140,7 @@
         </is>
       </c>
       <c r="I51" s="37" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="52">
@@ -30292,7 +30324,7 @@
         </is>
       </c>
       <c r="F56" s="37" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="G56" s="37" t="n">
         <v>-54</v>
@@ -30303,7 +30335,7 @@
         </is>
       </c>
       <c r="I56" s="37" t="n">
-        <v>-30.8</v>
+        <v>-31.5</v>
       </c>
     </row>
     <row r="57">
@@ -30821,34 +30853,34 @@
     <row r="15">
       <c r="A15" s="37" t="inlineStr">
         <is>
-          <t>Ohio State</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="C15" s="37" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="D15" s="37" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>1832.7</v>
+        <v>1634.9</v>
       </c>
       <c r="F15" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="37" t="n">
-        <v>-8</v>
+        <v>35</v>
+      </c>
+      <c r="G15" s="44" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="37" t="inlineStr">
         <is>
-          <t>Wake Forest</t>
+          <t>Ohio State</t>
         </is>
       </c>
       <c r="B16" s="37" t="inlineStr">
@@ -30857,52 +30889,52 @@
         </is>
       </c>
       <c r="C16" s="37" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="D16" s="37" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="37" t="n">
-        <v>1594.7</v>
+        <v>1832.7</v>
       </c>
       <c r="F16" s="37" t="n">
-        <v>54</v>
-      </c>
-      <c r="G16" s="44" t="n">
-        <v>43</v>
+        <v>2</v>
+      </c>
+      <c r="G16" s="37" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Wake Forest</t>
         </is>
       </c>
       <c r="B17" s="37" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C17" s="37" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="D17" s="37" t="n">
         <v>12</v>
       </c>
       <c r="E17" s="37" t="n">
-        <v>1686.3</v>
+        <v>1594.7</v>
       </c>
       <c r="F17" s="37" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" s="37" t="n">
-        <v>4</v>
+        <v>54</v>
+      </c>
+      <c r="G17" s="44" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="37" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="B18" s="37" t="inlineStr">
@@ -30911,25 +30943,25 @@
         </is>
       </c>
       <c r="C18" s="37" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="D18" s="37" t="n">
         <v>13</v>
       </c>
       <c r="E18" s="37" t="n">
-        <v>1783.6</v>
+        <v>1686.3</v>
       </c>
       <c r="F18" s="37" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G18" s="37" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="37" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B19" s="37" t="inlineStr">
@@ -30938,133 +30970,133 @@
         </is>
       </c>
       <c r="C19" s="37" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="D19" s="37" t="n">
         <v>14</v>
       </c>
       <c r="E19" s="37" t="n">
-        <v>1668.8</v>
+        <v>1579.4</v>
       </c>
       <c r="F19" s="37" t="n">
-        <v>22</v>
-      </c>
-      <c r="G19" s="37" t="n">
-        <v>8</v>
+        <v>63</v>
+      </c>
+      <c r="G19" s="44" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="37" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="C20" s="37" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="D20" s="37" t="n">
         <v>15</v>
       </c>
       <c r="E20" s="37" t="n">
-        <v>1671.9</v>
+        <v>1783.6</v>
       </c>
       <c r="F20" s="37" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G20" s="37" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="37" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="B21" s="37" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C21" s="37" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="D21" s="37" t="n">
         <v>16</v>
       </c>
       <c r="E21" s="37" t="n">
-        <v>1645.8</v>
+        <v>1668.8</v>
       </c>
       <c r="F21" s="37" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G21" s="37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="37" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C22" s="37" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="D22" s="37" t="n">
         <v>17</v>
       </c>
       <c r="E22" s="37" t="n">
-        <v>1837.5</v>
+        <v>1671.9</v>
       </c>
       <c r="F22" s="37" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G22" s="37" t="n">
-        <v>-16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="37" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="B23" s="37" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="C23" s="37" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="D23" s="37" t="n">
         <v>18</v>
       </c>
       <c r="E23" s="37" t="n">
-        <v>1611.8</v>
+        <v>1645.8</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>44</v>
-      </c>
-      <c r="G23" s="44" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="G23" s="37" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="37" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="B24" s="37" t="inlineStr">
@@ -31073,25 +31105,25 @@
         </is>
       </c>
       <c r="C24" s="37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="D24" s="37" t="n">
         <v>19</v>
       </c>
       <c r="E24" s="37" t="n">
-        <v>1749.4</v>
+        <v>1837.5</v>
       </c>
       <c r="F24" s="37" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G24" s="37" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="37" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="B25" s="37" t="inlineStr">
@@ -31100,25 +31132,25 @@
         </is>
       </c>
       <c r="C25" s="37" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="D25" s="37" t="n">
         <v>20</v>
       </c>
       <c r="E25" s="37" t="n">
-        <v>1685</v>
+        <v>1611.8</v>
       </c>
       <c r="F25" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="G25" s="37" t="n">
-        <v>-2</v>
+        <v>44</v>
+      </c>
+      <c r="G25" s="44" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="B26" s="37" t="inlineStr">
@@ -31127,79 +31159,79 @@
         </is>
       </c>
       <c r="C26" s="37" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="D26" s="37" t="n">
         <v>21</v>
       </c>
       <c r="E26" s="37" t="n">
-        <v>1622.5</v>
+        <v>1749.4</v>
       </c>
       <c r="F26" s="37" t="n">
-        <v>38</v>
-      </c>
-      <c r="G26" s="44" t="n">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="G26" s="37" t="n">
+        <v>-10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="37" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C27" s="37" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="D27" s="37" t="n">
         <v>22</v>
       </c>
       <c r="E27" s="37" t="n">
-        <v>1592.8</v>
+        <v>1685</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>56</v>
-      </c>
-      <c r="G27" s="44" t="n">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G27" s="37" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="37" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="C28" s="37" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="D28" s="37" t="n">
         <v>23</v>
       </c>
       <c r="E28" s="37" t="n">
-        <v>1669.5</v>
+        <v>1592.8</v>
       </c>
       <c r="F28" s="37" t="n">
-        <v>21</v>
-      </c>
-      <c r="G28" s="37" t="n">
-        <v>-2</v>
+        <v>56</v>
+      </c>
+      <c r="G28" s="44" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="37" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="B29" s="37" t="inlineStr">
@@ -31208,25 +31240,25 @@
         </is>
       </c>
       <c r="C29" s="37" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="D29" s="37" t="n">
         <v>24</v>
       </c>
       <c r="E29" s="37" t="n">
-        <v>1554.7</v>
+        <v>1669.5</v>
       </c>
       <c r="F29" s="37" t="n">
-        <v>69</v>
-      </c>
-      <c r="G29" s="44" t="n">
-        <v>45</v>
+        <v>21</v>
+      </c>
+      <c r="G29" s="37" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="37" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="B30" s="37" t="inlineStr">
@@ -31235,25 +31267,25 @@
         </is>
       </c>
       <c r="C30" s="37" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="D30" s="37" t="n">
         <v>25</v>
       </c>
       <c r="E30" s="37" t="n">
-        <v>1685.4</v>
+        <v>1554.7</v>
       </c>
       <c r="F30" s="37" t="n">
-        <v>17</v>
-      </c>
-      <c r="G30" s="37" t="n">
-        <v>-8</v>
+        <v>69</v>
+      </c>
+      <c r="G30" s="44" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="37" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B31" s="37" t="inlineStr">
@@ -31262,79 +31294,79 @@
         </is>
       </c>
       <c r="C31" s="37" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="D31" s="37" t="n">
         <v>26</v>
       </c>
       <c r="E31" s="37" t="n">
-        <v>1570.7</v>
+        <v>1685.4</v>
       </c>
       <c r="F31" s="37" t="n">
-        <v>65</v>
-      </c>
-      <c r="G31" s="44" t="n">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="G31" s="37" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C32" s="37" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="D32" s="37" t="n">
         <v>27</v>
       </c>
       <c r="E32" s="37" t="n">
-        <v>1738.1</v>
+        <v>1570.7</v>
       </c>
       <c r="F32" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="G32" s="37" t="n">
-        <v>-15</v>
+        <v>65</v>
+      </c>
+      <c r="G32" s="44" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="C33" s="37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="D33" s="37" t="n">
         <v>28</v>
       </c>
       <c r="E33" s="37" t="n">
-        <v>1562.1</v>
+        <v>1738.1</v>
       </c>
       <c r="F33" s="37" t="n">
-        <v>67</v>
-      </c>
-      <c r="G33" s="44" t="n">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="G33" s="37" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="37" t="inlineStr">
         <is>
-          <t>Ole Miss</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="B34" s="37" t="inlineStr">
@@ -31343,25 +31375,25 @@
         </is>
       </c>
       <c r="C34" s="37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="D34" s="37" t="n">
         <v>29</v>
       </c>
       <c r="E34" s="37" t="n">
-        <v>1734.2</v>
+        <v>1562.1</v>
       </c>
       <c r="F34" s="37" t="n">
-        <v>13</v>
-      </c>
-      <c r="G34" s="37" t="n">
-        <v>-16</v>
+        <v>67</v>
+      </c>
+      <c r="G34" s="44" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="37" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Ole Miss</t>
         </is>
       </c>
       <c r="B35" s="37" t="inlineStr">
@@ -31370,25 +31402,25 @@
         </is>
       </c>
       <c r="C35" s="37" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="D35" s="37" t="n">
         <v>30</v>
       </c>
       <c r="E35" s="37" t="n">
-        <v>1646.5</v>
+        <v>1734.2</v>
       </c>
       <c r="F35" s="37" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G35" s="37" t="n">
-        <v>-4</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="37" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="B36" s="37" t="inlineStr">
@@ -31397,30 +31429,30 @@
         </is>
       </c>
       <c r="C36" s="37" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="D36" s="37" t="n">
         <v>31</v>
       </c>
       <c r="E36" s="37" t="n">
-        <v>1634.3</v>
+        <v>1646.5</v>
       </c>
       <c r="F36" s="37" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G36" s="37" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="37" t="inlineStr">
         <is>
-          <t>Boise State</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="B37" s="37" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C37" s="37" t="n">
@@ -31430,46 +31462,46 @@
         <v>32</v>
       </c>
       <c r="E37" s="37" t="n">
-        <v>1673.6</v>
+        <v>1634.3</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G37" s="37" t="n">
-        <v>-13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="37" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Boise State</t>
         </is>
       </c>
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C38" s="37" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="D38" s="37" t="n">
         <v>33</v>
       </c>
       <c r="E38" s="37" t="n">
-        <v>1619.5</v>
+        <v>1673.6</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G38" s="37" t="n">
-        <v>6</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="37" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B39" s="37" t="inlineStr">
@@ -31484,73 +31516,73 @@
         <v>34</v>
       </c>
       <c r="E39" s="37" t="n">
-        <v>1616.2</v>
+        <v>1619.5</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G39" s="37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="37" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C40" s="37" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="D40" s="37" t="n">
         <v>35</v>
       </c>
       <c r="E40" s="37" t="n">
-        <v>1727</v>
+        <v>1616.2</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G40" s="37" t="n">
-        <v>-21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="37" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="B41" s="37" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="C41" s="37" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="D41" s="37" t="n">
         <v>36</v>
       </c>
       <c r="E41" s="37" t="n">
-        <v>1696.3</v>
+        <v>1727</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G41" s="37" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="37" t="inlineStr">
         <is>
-          <t>Florida Atlantic</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="B42" s="37" t="inlineStr">
@@ -31559,25 +31591,25 @@
         </is>
       </c>
       <c r="C42" s="37" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="D42" s="37" t="n">
         <v>37</v>
       </c>
       <c r="E42" s="37" t="n">
-        <v>1475.5</v>
+        <v>1696.3</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>105</v>
-      </c>
-      <c r="G42" s="44" t="n">
-        <v>68</v>
+        <v>15</v>
+      </c>
+      <c r="G42" s="37" t="n">
+        <v>-22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="37" t="inlineStr">
         <is>
-          <t>Fresno State</t>
+          <t>Florida Atlantic</t>
         </is>
       </c>
       <c r="B43" s="37" t="inlineStr">
@@ -31586,25 +31618,25 @@
         </is>
       </c>
       <c r="C43" s="37" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="D43" s="37" t="n">
         <v>38</v>
       </c>
       <c r="E43" s="37" t="n">
-        <v>1609.2</v>
+        <v>1475.5</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>48</v>
-      </c>
-      <c r="G43" s="37" t="n">
-        <v>10</v>
+        <v>105</v>
+      </c>
+      <c r="G43" s="44" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="37" t="inlineStr">
         <is>
-          <t>Georgia State</t>
+          <t>Fresno State</t>
         </is>
       </c>
       <c r="B44" s="37" t="inlineStr">
@@ -31619,46 +31651,46 @@
         <v>39</v>
       </c>
       <c r="E44" s="37" t="n">
-        <v>1480</v>
+        <v>1609.2</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>103</v>
-      </c>
-      <c r="G44" s="44" t="n">
-        <v>64</v>
+        <v>48</v>
+      </c>
+      <c r="G44" s="37" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="37" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Georgia State</t>
         </is>
       </c>
       <c r="B45" s="37" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C45" s="37" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="D45" s="37" t="n">
         <v>40</v>
       </c>
       <c r="E45" s="37" t="n">
-        <v>1608.9</v>
+        <v>1480</v>
       </c>
       <c r="F45" s="37" t="n">
-        <v>49</v>
-      </c>
-      <c r="G45" s="37" t="n">
-        <v>9</v>
+        <v>103</v>
+      </c>
+      <c r="G45" s="44" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="37" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="B46" s="37" t="inlineStr">
@@ -31667,19 +31699,19 @@
         </is>
       </c>
       <c r="C46" s="37" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="D46" s="37" t="n">
         <v>41</v>
       </c>
       <c r="E46" s="37" t="n">
-        <v>1571.9</v>
+        <v>1608.9</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>63</v>
-      </c>
-      <c r="G46" s="44" t="n">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="G46" s="37" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -31703,10 +31735,10 @@
         <v>1456.2</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G47" s="44" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
@@ -32000,10 +32032,10 @@
         <v>1625.5</v>
       </c>
       <c r="F58" s="37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G58" s="37" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="59">
@@ -32702,10 +32734,10 @@
         <v>1449.3</v>
       </c>
       <c r="F84" s="37" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G84" s="44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85">
@@ -33026,10 +33058,10 @@
         <v>1452.4</v>
       </c>
       <c r="F96" s="37" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G96" s="44" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97">
@@ -33107,10 +33139,10 @@
         <v>1447.4</v>
       </c>
       <c r="F99" s="37" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G99" s="44" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100">
@@ -33188,10 +33220,10 @@
         <v>1449.9</v>
       </c>
       <c r="F102" s="37" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G102" s="44" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103">
@@ -33350,10 +33382,10 @@
         <v>1456.6</v>
       </c>
       <c r="F108" s="37" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G108" s="44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
@@ -33458,10 +33490,10 @@
         <v>1456.2</v>
       </c>
       <c r="F112" s="37" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G112" s="44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113">
@@ -33485,10 +33517,10 @@
         <v>1444.8</v>
       </c>
       <c r="F113" s="37" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G113" s="44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114">
@@ -33539,10 +33571,10 @@
         <v>1445.5</v>
       </c>
       <c r="F115" s="37" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G115" s="44" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116">
@@ -33647,10 +33679,10 @@
         <v>1447.5</v>
       </c>
       <c r="F119" s="37" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G119" s="44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120">
@@ -33971,10 +34003,10 @@
         <v>1451</v>
       </c>
       <c r="F131" s="37" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G131" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -34466,12 +34498,12 @@
     <row r="150">
       <c r="A150" s="37" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Prairie View A&amp;M</t>
         </is>
       </c>
       <c r="B150" s="37" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C150" s="37" t="n">
@@ -34481,19 +34513,19 @@
         <v>145</v>
       </c>
       <c r="E150" s="37" t="n">
-        <v>1457.2</v>
+        <v>1414.9</v>
       </c>
       <c r="F150" s="37" t="n">
-        <v>122</v>
-      </c>
-      <c r="G150" s="37" t="n">
-        <v>-23</v>
+        <v>189</v>
+      </c>
+      <c r="G150" s="44" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="37" t="inlineStr">
         <is>
-          <t>Prairie View A&amp;M</t>
+          <t>Central Arkansas</t>
         </is>
       </c>
       <c r="B151" s="37" t="inlineStr">
@@ -34502,57 +34534,57 @@
         </is>
       </c>
       <c r="C151" s="37" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="D151" s="37" t="n">
         <v>146</v>
       </c>
       <c r="E151" s="37" t="n">
-        <v>1414.9</v>
+        <v>1433.8</v>
       </c>
       <c r="F151" s="37" t="n">
-        <v>189</v>
-      </c>
-      <c r="G151" s="44" t="n">
-        <v>43</v>
+        <v>156</v>
+      </c>
+      <c r="G151" s="37" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="37" t="inlineStr">
         <is>
-          <t>Central Arkansas</t>
+          <t>Florida International</t>
         </is>
       </c>
       <c r="B152" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C152" s="37" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="D152" s="37" t="n">
         <v>147</v>
       </c>
       <c r="E152" s="37" t="n">
-        <v>1433.8</v>
+        <v>1488.5</v>
       </c>
       <c r="F152" s="37" t="n">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="G152" s="37" t="n">
-        <v>9</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="37" t="inlineStr">
         <is>
-          <t>Florida International</t>
+          <t>East Tennessee State</t>
         </is>
       </c>
       <c r="B153" s="37" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C153" s="37" t="n">
@@ -34562,19 +34594,19 @@
         <v>148</v>
       </c>
       <c r="E153" s="37" t="n">
-        <v>1488.5</v>
+        <v>1429.6</v>
       </c>
       <c r="F153" s="37" t="n">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="G153" s="37" t="n">
-        <v>-50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="37" t="inlineStr">
         <is>
-          <t>East Tennessee State</t>
+          <t>Western Illinois</t>
         </is>
       </c>
       <c r="B154" s="37" t="inlineStr">
@@ -34589,19 +34621,19 @@
         <v>149</v>
       </c>
       <c r="E154" s="37" t="n">
-        <v>1429.6</v>
+        <v>1387.5</v>
       </c>
       <c r="F154" s="37" t="n">
-        <v>162</v>
-      </c>
-      <c r="G154" s="37" t="n">
-        <v>13</v>
+        <v>233</v>
+      </c>
+      <c r="G154" s="44" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="37" t="inlineStr">
         <is>
-          <t>Western Illinois</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="B155" s="37" t="inlineStr">
@@ -34610,25 +34642,25 @@
         </is>
       </c>
       <c r="C155" s="37" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="D155" s="37" t="n">
         <v>150</v>
       </c>
       <c r="E155" s="37" t="n">
-        <v>1387.5</v>
+        <v>1400.8</v>
       </c>
       <c r="F155" s="37" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="G155" s="44" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="37" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>Bethune-Cookman</t>
         </is>
       </c>
       <c r="B156" s="37" t="inlineStr">
@@ -34643,19 +34675,19 @@
         <v>151</v>
       </c>
       <c r="E156" s="37" t="n">
-        <v>1400.8</v>
+        <v>1379</v>
       </c>
       <c r="F156" s="37" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="G156" s="44" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="37" t="inlineStr">
         <is>
-          <t>Bethune-Cookman</t>
+          <t>North Alabama</t>
         </is>
       </c>
       <c r="B157" s="37" t="inlineStr">
@@ -34670,19 +34702,19 @@
         <v>152</v>
       </c>
       <c r="E157" s="37" t="n">
-        <v>1379</v>
+        <v>1434.2</v>
       </c>
       <c r="F157" s="37" t="n">
-        <v>239</v>
-      </c>
-      <c r="G157" s="44" t="n">
-        <v>87</v>
+        <v>154</v>
+      </c>
+      <c r="G157" s="37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="37" t="inlineStr">
         <is>
-          <t>North Alabama</t>
+          <t>Weber State</t>
         </is>
       </c>
       <c r="B158" s="37" t="inlineStr">
@@ -34691,30 +34723,30 @@
         </is>
       </c>
       <c r="C158" s="37" t="n">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="D158" s="37" t="n">
         <v>153</v>
       </c>
       <c r="E158" s="37" t="n">
-        <v>1434.2</v>
+        <v>1433.7</v>
       </c>
       <c r="F158" s="37" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G158" s="37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="37" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>UAlbany</t>
         </is>
       </c>
       <c r="B159" s="37" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C159" s="37" t="n">
@@ -34724,24 +34756,24 @@
         <v>154</v>
       </c>
       <c r="E159" s="37" t="n">
-        <v>1538.4</v>
+        <v>1435.7</v>
       </c>
       <c r="F159" s="37" t="n">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="G159" s="37" t="n">
-        <v>-79</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="37" t="inlineStr">
         <is>
-          <t>Weber State</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B160" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C160" s="37" t="n">
@@ -34751,19 +34783,19 @@
         <v>155</v>
       </c>
       <c r="E160" s="37" t="n">
-        <v>1433.7</v>
+        <v>1520.2</v>
       </c>
       <c r="F160" s="37" t="n">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="G160" s="37" t="n">
-        <v>2</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="37" t="inlineStr">
         <is>
-          <t>UAlbany</t>
+          <t>Hampton</t>
         </is>
       </c>
       <c r="B161" s="37" t="inlineStr">
@@ -34772,52 +34804,52 @@
         </is>
       </c>
       <c r="C161" s="37" t="n">
-        <v>-0.45</v>
+        <v>-0.48</v>
       </c>
       <c r="D161" s="37" t="n">
         <v>156</v>
       </c>
       <c r="E161" s="37" t="n">
-        <v>1435.7</v>
+        <v>1402.8</v>
       </c>
       <c r="F161" s="37" t="n">
-        <v>152</v>
-      </c>
-      <c r="G161" s="37" t="n">
-        <v>-4</v>
+        <v>218</v>
+      </c>
+      <c r="G161" s="44" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="37" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="B162" s="37" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C162" s="37" t="n">
-        <v>-0.45</v>
+        <v>-0.48</v>
       </c>
       <c r="D162" s="37" t="n">
         <v>157</v>
       </c>
       <c r="E162" s="37" t="n">
-        <v>1520.2</v>
+        <v>1417.1</v>
       </c>
       <c r="F162" s="37" t="n">
-        <v>81</v>
-      </c>
-      <c r="G162" s="37" t="n">
-        <v>-76</v>
+        <v>187</v>
+      </c>
+      <c r="G162" s="44" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="37" t="inlineStr">
         <is>
-          <t>Hampton</t>
+          <t>Mississippi Valley State</t>
         </is>
       </c>
       <c r="B163" s="37" t="inlineStr">
@@ -34832,24 +34864,24 @@
         <v>158</v>
       </c>
       <c r="E163" s="37" t="n">
-        <v>1402.8</v>
+        <v>1435.2</v>
       </c>
       <c r="F163" s="37" t="n">
-        <v>218</v>
-      </c>
-      <c r="G163" s="44" t="n">
-        <v>60</v>
+        <v>153</v>
+      </c>
+      <c r="G163" s="37" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="37" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Portland State</t>
         </is>
       </c>
       <c r="B164" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C164" s="37" t="n">
@@ -34859,19 +34891,19 @@
         <v>159</v>
       </c>
       <c r="E164" s="37" t="n">
-        <v>1417.1</v>
+        <v>1391.8</v>
       </c>
       <c r="F164" s="37" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="G164" s="44" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="37" t="inlineStr">
         <is>
-          <t>Mississippi Valley State</t>
+          <t>VMI</t>
         </is>
       </c>
       <c r="B165" s="37" t="inlineStr">
@@ -34886,46 +34918,46 @@
         <v>160</v>
       </c>
       <c r="E165" s="37" t="n">
-        <v>1435.2</v>
+        <v>1411.1</v>
       </c>
       <c r="F165" s="37" t="n">
-        <v>153</v>
-      </c>
-      <c r="G165" s="37" t="n">
-        <v>-7</v>
+        <v>205</v>
+      </c>
+      <c r="G165" s="44" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="37" t="inlineStr">
         <is>
-          <t>Portland State</t>
+          <t>Colgate</t>
         </is>
       </c>
       <c r="B166" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C166" s="37" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="D166" s="37" t="n">
         <v>161</v>
       </c>
       <c r="E166" s="37" t="n">
-        <v>1391.8</v>
+        <v>1422</v>
       </c>
       <c r="F166" s="37" t="n">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="G166" s="44" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="37" t="inlineStr">
         <is>
-          <t>VMI</t>
+          <t>Alcorn State</t>
         </is>
       </c>
       <c r="B167" s="37" t="inlineStr">
@@ -34934,52 +34966,52 @@
         </is>
       </c>
       <c r="C167" s="37" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
       <c r="D167" s="37" t="n">
         <v>162</v>
       </c>
       <c r="E167" s="37" t="n">
-        <v>1411.1</v>
+        <v>1384.2</v>
       </c>
       <c r="F167" s="37" t="n">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="G167" s="44" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="37" t="inlineStr">
         <is>
-          <t>Colgate</t>
+          <t>Norfolk State</t>
         </is>
       </c>
       <c r="B168" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C168" s="37" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="D168" s="37" t="n">
         <v>163</v>
       </c>
       <c r="E168" s="37" t="n">
-        <v>1422</v>
+        <v>1404.2</v>
       </c>
       <c r="F168" s="37" t="n">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="G168" s="44" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="37" t="inlineStr">
         <is>
-          <t>Alcorn State</t>
+          <t>Cal Poly</t>
         </is>
       </c>
       <c r="B169" s="37" t="inlineStr">
@@ -34994,46 +35026,46 @@
         <v>164</v>
       </c>
       <c r="E169" s="37" t="n">
-        <v>1384.2</v>
+        <v>1413.6</v>
       </c>
       <c r="F169" s="37" t="n">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="G169" s="44" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="37" t="inlineStr">
         <is>
-          <t>Norfolk State</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="B170" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C170" s="37" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="D170" s="37" t="n">
         <v>165</v>
       </c>
       <c r="E170" s="37" t="n">
-        <v>1404.2</v>
+        <v>1624</v>
       </c>
       <c r="F170" s="37" t="n">
-        <v>213</v>
-      </c>
-      <c r="G170" s="44" t="n">
-        <v>48</v>
+        <v>38</v>
+      </c>
+      <c r="G170" s="37" t="n">
+        <v>-127</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="37" t="inlineStr">
         <is>
-          <t>Cal Poly</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="B171" s="37" t="inlineStr">
@@ -35042,25 +35074,25 @@
         </is>
       </c>
       <c r="C171" s="37" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="D171" s="37" t="n">
         <v>166</v>
       </c>
       <c r="E171" s="37" t="n">
-        <v>1413.6</v>
+        <v>1418.7</v>
       </c>
       <c r="F171" s="37" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="G171" s="44" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="37" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B172" s="37" t="inlineStr">
@@ -35075,19 +35107,19 @@
         <v>167</v>
       </c>
       <c r="E172" s="37" t="n">
-        <v>1624</v>
+        <v>1521.7</v>
       </c>
       <c r="F172" s="37" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G172" s="37" t="n">
-        <v>-130</v>
+        <v>-89</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="37" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Samford</t>
         </is>
       </c>
       <c r="B173" s="37" t="inlineStr">
@@ -35096,52 +35128,52 @@
         </is>
       </c>
       <c r="C173" s="37" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="D173" s="37" t="n">
         <v>168</v>
       </c>
       <c r="E173" s="37" t="n">
-        <v>1418.7</v>
+        <v>1420.6</v>
       </c>
       <c r="F173" s="37" t="n">
-        <v>184</v>
-      </c>
-      <c r="G173" s="44" t="n">
-        <v>16</v>
+        <v>182</v>
+      </c>
+      <c r="G173" s="37" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="37" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>East Texas A&amp;M</t>
         </is>
       </c>
       <c r="B174" s="37" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C174" s="37" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="D174" s="37" t="n">
         <v>169</v>
       </c>
       <c r="E174" s="37" t="n">
-        <v>1521.7</v>
+        <v>1420.6</v>
       </c>
       <c r="F174" s="37" t="n">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="G174" s="37" t="n">
-        <v>-91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="37" t="inlineStr">
         <is>
-          <t>Samford</t>
+          <t>Southern Utah</t>
         </is>
       </c>
       <c r="B175" s="37" t="inlineStr">
@@ -35156,19 +35188,19 @@
         <v>170</v>
       </c>
       <c r="E175" s="37" t="n">
-        <v>1420.6</v>
+        <v>1416.7</v>
       </c>
       <c r="F175" s="37" t="n">
-        <v>182</v>
-      </c>
-      <c r="G175" s="37" t="n">
-        <v>12</v>
+        <v>188</v>
+      </c>
+      <c r="G175" s="44" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="37" t="inlineStr">
         <is>
-          <t>East Texas A&amp;M</t>
+          <t>Indiana State</t>
         </is>
       </c>
       <c r="B176" s="37" t="inlineStr">
@@ -35177,25 +35209,25 @@
         </is>
       </c>
       <c r="C176" s="37" t="n">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="D176" s="37" t="n">
         <v>171</v>
       </c>
       <c r="E176" s="37" t="n">
-        <v>1420.6</v>
+        <v>1393.9</v>
       </c>
       <c r="F176" s="37" t="n">
-        <v>183</v>
-      </c>
-      <c r="G176" s="37" t="n">
-        <v>12</v>
+        <v>226</v>
+      </c>
+      <c r="G176" s="44" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="37" t="inlineStr">
         <is>
-          <t>Southern Utah</t>
+          <t>Northern Colorado</t>
         </is>
       </c>
       <c r="B177" s="37" t="inlineStr">
@@ -35204,52 +35236,52 @@
         </is>
       </c>
       <c r="C177" s="37" t="n">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="D177" s="37" t="n">
         <v>172</v>
       </c>
       <c r="E177" s="37" t="n">
-        <v>1416.7</v>
+        <v>1425.1</v>
       </c>
       <c r="F177" s="37" t="n">
-        <v>188</v>
-      </c>
-      <c r="G177" s="44" t="n">
-        <v>16</v>
+        <v>175</v>
+      </c>
+      <c r="G177" s="37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="37" t="inlineStr">
         <is>
-          <t>Indiana State</t>
+          <t>Towson</t>
         </is>
       </c>
       <c r="B178" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C178" s="37" t="n">
-        <v>-0.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D178" s="37" t="n">
         <v>173</v>
       </c>
       <c r="E178" s="37" t="n">
-        <v>1393.9</v>
+        <v>1412.2</v>
       </c>
       <c r="F178" s="37" t="n">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="G178" s="44" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="37" t="inlineStr">
         <is>
-          <t>Northern Colorado</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="B179" s="37" t="inlineStr">
@@ -35258,25 +35290,25 @@
         </is>
       </c>
       <c r="C179" s="37" t="n">
-        <v>-0.55</v>
+        <v>-0.58</v>
       </c>
       <c r="D179" s="37" t="n">
         <v>174</v>
       </c>
       <c r="E179" s="37" t="n">
-        <v>1425.1</v>
+        <v>1467.1</v>
       </c>
       <c r="F179" s="37" t="n">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="G179" s="37" t="n">
-        <v>1</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="37" t="inlineStr">
         <is>
-          <t>Towson</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="B180" s="37" t="inlineStr">
@@ -35285,25 +35317,25 @@
         </is>
       </c>
       <c r="C180" s="37" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="D180" s="37" t="n">
         <v>175</v>
       </c>
       <c r="E180" s="37" t="n">
-        <v>1412.2</v>
+        <v>1388</v>
       </c>
       <c r="F180" s="37" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="G180" s="44" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="37" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Stony Brook</t>
         </is>
       </c>
       <c r="B181" s="37" t="inlineStr">
@@ -35312,25 +35344,25 @@
         </is>
       </c>
       <c r="C181" s="37" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="D181" s="37" t="n">
         <v>176</v>
       </c>
       <c r="E181" s="37" t="n">
-        <v>1467.1</v>
+        <v>1395</v>
       </c>
       <c r="F181" s="37" t="n">
-        <v>111</v>
-      </c>
-      <c r="G181" s="37" t="n">
-        <v>-65</v>
+        <v>225</v>
+      </c>
+      <c r="G181" s="44" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="37" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Wagner</t>
         </is>
       </c>
       <c r="B182" s="37" t="inlineStr">
@@ -35339,25 +35371,25 @@
         </is>
       </c>
       <c r="C182" s="37" t="n">
-        <v>-0.58</v>
+        <v>-0.61</v>
       </c>
       <c r="D182" s="37" t="n">
         <v>177</v>
       </c>
       <c r="E182" s="37" t="n">
-        <v>1388</v>
+        <v>1353.5</v>
       </c>
       <c r="F182" s="37" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="G182" s="44" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="37" t="inlineStr">
         <is>
-          <t>Stony Brook</t>
+          <t>Wofford</t>
         </is>
       </c>
       <c r="B183" s="37" t="inlineStr">
@@ -35366,30 +35398,30 @@
         </is>
       </c>
       <c r="C183" s="37" t="n">
-        <v>-0.59</v>
+        <v>-0.61</v>
       </c>
       <c r="D183" s="37" t="n">
         <v>178</v>
       </c>
       <c r="E183" s="37" t="n">
-        <v>1395</v>
+        <v>1417.9</v>
       </c>
       <c r="F183" s="37" t="n">
-        <v>225</v>
-      </c>
-      <c r="G183" s="44" t="n">
-        <v>47</v>
+        <v>186</v>
+      </c>
+      <c r="G183" s="37" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="37" t="inlineStr">
         <is>
-          <t>Wagner</t>
+          <t>North Carolina A&amp;T</t>
         </is>
       </c>
       <c r="B184" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C184" s="37" t="n">
@@ -35399,24 +35431,24 @@
         <v>179</v>
       </c>
       <c r="E184" s="37" t="n">
-        <v>1353.5</v>
+        <v>1397.7</v>
       </c>
       <c r="F184" s="37" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="G184" s="44" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="37" t="inlineStr">
         <is>
-          <t>Wofford</t>
+          <t>Louisiana Tech</t>
         </is>
       </c>
       <c r="B185" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C185" s="37" t="n">
@@ -35426,127 +35458,127 @@
         <v>180</v>
       </c>
       <c r="E185" s="37" t="n">
-        <v>1417.9</v>
+        <v>1501.2</v>
       </c>
       <c r="F185" s="37" t="n">
-        <v>186</v>
+        <v>90</v>
       </c>
       <c r="G185" s="37" t="n">
-        <v>6</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="37" t="inlineStr">
         <is>
-          <t>North Carolina A&amp;T</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="B186" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C186" s="37" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="D186" s="37" t="n">
         <v>181</v>
       </c>
       <c r="E186" s="37" t="n">
-        <v>1397.7</v>
+        <v>1413.3</v>
       </c>
       <c r="F186" s="37" t="n">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="G186" s="44" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="37" t="inlineStr">
         <is>
-          <t>Louisiana Tech</t>
+          <t>Texas Southern</t>
         </is>
       </c>
       <c r="B187" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C187" s="37" t="n">
-        <v>-0.61</v>
+        <v>-0.63</v>
       </c>
       <c r="D187" s="37" t="n">
         <v>182</v>
       </c>
       <c r="E187" s="37" t="n">
-        <v>1501.2</v>
+        <v>1378.6</v>
       </c>
       <c r="F187" s="37" t="n">
-        <v>90</v>
-      </c>
-      <c r="G187" s="37" t="n">
-        <v>-92</v>
+        <v>240</v>
+      </c>
+      <c r="G187" s="44" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="37" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B188" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C188" s="37" t="n">
-        <v>-0.62</v>
+        <v>-0.65</v>
       </c>
       <c r="D188" s="37" t="n">
         <v>183</v>
       </c>
       <c r="E188" s="37" t="n">
-        <v>1413.3</v>
+        <v>1465.7</v>
       </c>
       <c r="F188" s="37" t="n">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="G188" s="37" t="n">
-        <v>14</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="37" t="inlineStr">
         <is>
-          <t>Texas Southern</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="B189" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C189" s="37" t="n">
-        <v>-0.63</v>
+        <v>-0.65</v>
       </c>
       <c r="D189" s="37" t="n">
         <v>184</v>
       </c>
       <c r="E189" s="37" t="n">
-        <v>1378.6</v>
+        <v>1444.8</v>
       </c>
       <c r="F189" s="37" t="n">
-        <v>240</v>
-      </c>
-      <c r="G189" s="44" t="n">
-        <v>56</v>
+        <v>138</v>
+      </c>
+      <c r="G189" s="37" t="n">
+        <v>-46</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="37" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Kent State</t>
         </is>
       </c>
       <c r="B190" s="37" t="inlineStr">
@@ -35561,51 +35593,51 @@
         <v>185</v>
       </c>
       <c r="E190" s="37" t="n">
-        <v>1465.7</v>
+        <v>1398.4</v>
       </c>
       <c r="F190" s="37" t="n">
-        <v>114</v>
-      </c>
-      <c r="G190" s="37" t="n">
-        <v>-71</v>
+        <v>223</v>
+      </c>
+      <c r="G190" s="44" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="37" t="inlineStr">
         <is>
-          <t>Kent State</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="B191" s="37" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C191" s="37" t="n">
-        <v>-0.65</v>
+        <v>-0.68</v>
       </c>
       <c r="D191" s="37" t="n">
         <v>186</v>
       </c>
       <c r="E191" s="37" t="n">
-        <v>1398.4</v>
+        <v>1381.4</v>
       </c>
       <c r="F191" s="37" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="G191" s="44" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="37" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>UT Martin</t>
         </is>
       </c>
       <c r="B192" s="37" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C192" s="37" t="n">
@@ -35615,51 +35647,51 @@
         <v>187</v>
       </c>
       <c r="E192" s="37" t="n">
-        <v>1381.4</v>
+        <v>1383.9</v>
       </c>
       <c r="F192" s="37" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G192" s="44" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="37" t="inlineStr">
         <is>
-          <t>UT Martin</t>
+          <t>Sacred Heart</t>
         </is>
       </c>
       <c r="B193" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C193" s="37" t="n">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="D193" s="37" t="n">
         <v>188</v>
       </c>
       <c r="E193" s="37" t="n">
-        <v>1383.9</v>
+        <v>1427.1</v>
       </c>
       <c r="F193" s="37" t="n">
-        <v>236</v>
-      </c>
-      <c r="G193" s="44" t="n">
-        <v>48</v>
+        <v>169</v>
+      </c>
+      <c r="G193" s="37" t="n">
+        <v>-19</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="37" t="inlineStr">
         <is>
-          <t>Sacred Heart</t>
+          <t>Eastern Michigan</t>
         </is>
       </c>
       <c r="B194" s="37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C194" s="37" t="n">
@@ -35669,46 +35701,46 @@
         <v>189</v>
       </c>
       <c r="E194" s="37" t="n">
-        <v>1427.1</v>
+        <v>1455.9</v>
       </c>
       <c r="F194" s="37" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="G194" s="37" t="n">
-        <v>-20</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="37" t="inlineStr">
         <is>
-          <t>Eastern Michigan</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="B195" s="37" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C195" s="37" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="D195" s="37" t="n">
         <v>190</v>
       </c>
       <c r="E195" s="37" t="n">
-        <v>1455.9</v>
+        <v>1439.6</v>
       </c>
       <c r="F195" s="37" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="G195" s="37" t="n">
-        <v>-64</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="37" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B196" s="37" t="inlineStr">
@@ -35717,25 +35749,25 @@
         </is>
       </c>
       <c r="C196" s="37" t="n">
-        <v>-0.71</v>
+        <v>-0.75</v>
       </c>
       <c r="D196" s="37" t="n">
         <v>191</v>
       </c>
       <c r="E196" s="37" t="n">
-        <v>1439.6</v>
+        <v>1425.6</v>
       </c>
       <c r="F196" s="37" t="n">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="G196" s="37" t="n">
-        <v>-43</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="37" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B197" s="37" t="inlineStr">
@@ -35744,106 +35776,106 @@
         </is>
       </c>
       <c r="C197" s="37" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="D197" s="37" t="n">
         <v>192</v>
       </c>
       <c r="E197" s="37" t="n">
-        <v>1425.6</v>
+        <v>1465.8</v>
       </c>
       <c r="F197" s="37" t="n">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="G197" s="37" t="n">
-        <v>-19</v>
+        <v>-79</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="37" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Gardner-Webb</t>
         </is>
       </c>
       <c r="B198" s="37" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C198" s="37" t="n">
-        <v>-0.76</v>
+        <v>-0.78</v>
       </c>
       <c r="D198" s="37" t="n">
         <v>193</v>
       </c>
       <c r="E198" s="37" t="n">
-        <v>1465.8</v>
+        <v>1421.6</v>
       </c>
       <c r="F198" s="37" t="n">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="G198" s="37" t="n">
-        <v>-80</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="37" t="inlineStr">
         <is>
-          <t>Gardner-Webb</t>
+          <t>Middle Tennessee</t>
         </is>
       </c>
       <c r="B199" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C199" s="37" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="D199" s="37" t="n">
         <v>194</v>
       </c>
       <c r="E199" s="37" t="n">
-        <v>1421.6</v>
+        <v>1378.1</v>
       </c>
       <c r="F199" s="37" t="n">
-        <v>180</v>
-      </c>
-      <c r="G199" s="37" t="n">
-        <v>-14</v>
+        <v>242</v>
+      </c>
+      <c r="G199" s="44" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="37" t="inlineStr">
         <is>
-          <t>Middle Tennessee</t>
+          <t>Houston Christian</t>
         </is>
       </c>
       <c r="B200" s="37" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C200" s="37" t="n">
-        <v>-0.79</v>
+        <v>-0.8</v>
       </c>
       <c r="D200" s="37" t="n">
         <v>195</v>
       </c>
       <c r="E200" s="37" t="n">
-        <v>1378.1</v>
+        <v>1392.6</v>
       </c>
       <c r="F200" s="37" t="n">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="G200" s="44" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="37" t="inlineStr">
         <is>
-          <t>Houston Christian</t>
+          <t>Duquesne</t>
         </is>
       </c>
       <c r="B201" s="37" t="inlineStr">
@@ -35858,19 +35890,19 @@
         <v>196</v>
       </c>
       <c r="E201" s="37" t="n">
-        <v>1392.6</v>
+        <v>1359.3</v>
       </c>
       <c r="F201" s="37" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="G201" s="44" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="37" t="inlineStr">
         <is>
-          <t>Duquesne</t>
+          <t>West Georgia</t>
         </is>
       </c>
       <c r="B202" s="37" t="inlineStr">
@@ -35879,25 +35911,25 @@
         </is>
       </c>
       <c r="C202" s="37" t="n">
-        <v>-0.8</v>
+        <v>-0.82</v>
       </c>
       <c r="D202" s="37" t="n">
         <v>197</v>
       </c>
       <c r="E202" s="37" t="n">
-        <v>1359.3</v>
+        <v>1442.3</v>
       </c>
       <c r="F202" s="37" t="n">
-        <v>246</v>
-      </c>
-      <c r="G202" s="44" t="n">
-        <v>49</v>
+        <v>142</v>
+      </c>
+      <c r="G202" s="37" t="n">
+        <v>-55</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="37" t="inlineStr">
         <is>
-          <t>West Georgia</t>
+          <t>Long Island University</t>
         </is>
       </c>
       <c r="B203" s="37" t="inlineStr">
@@ -35906,79 +35938,79 @@
         </is>
       </c>
       <c r="C203" s="37" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="D203" s="37" t="n">
         <v>198</v>
       </c>
       <c r="E203" s="37" t="n">
-        <v>1442.3</v>
+        <v>1409.7</v>
       </c>
       <c r="F203" s="37" t="n">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="G203" s="37" t="n">
-        <v>-56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="37" t="inlineStr">
         <is>
-          <t>Long Island University</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="B204" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C204" s="37" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="D204" s="37" t="n">
         <v>199</v>
       </c>
       <c r="E204" s="37" t="n">
-        <v>1409.7</v>
+        <v>1413.7</v>
       </c>
       <c r="F204" s="37" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="G204" s="37" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="37" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>New Mexico State</t>
         </is>
       </c>
       <c r="B205" s="37" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C205" s="37" t="n">
-        <v>-0.84</v>
+        <v>-0.88</v>
       </c>
       <c r="D205" s="37" t="n">
         <v>200</v>
       </c>
       <c r="E205" s="37" t="n">
-        <v>1413.7</v>
+        <v>1423</v>
       </c>
       <c r="F205" s="37" t="n">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="G205" s="37" t="n">
-        <v>-5</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="37" t="inlineStr">
         <is>
-          <t>New Mexico State</t>
+          <t>Miami (OH)</t>
         </is>
       </c>
       <c r="B206" s="37" t="inlineStr">
@@ -35993,24 +36025,24 @@
         <v>201</v>
       </c>
       <c r="E206" s="37" t="n">
-        <v>1423</v>
+        <v>1513.8</v>
       </c>
       <c r="F206" s="37" t="n">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="G206" s="37" t="n">
-        <v>-25</v>
+        <v>-118</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="37" t="inlineStr">
         <is>
-          <t>Miami (OH)</t>
+          <t>Nicholls</t>
         </is>
       </c>
       <c r="B207" s="37" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C207" s="37" t="n">
@@ -36020,132 +36052,132 @@
         <v>202</v>
       </c>
       <c r="E207" s="37" t="n">
-        <v>1513.8</v>
+        <v>1366.1</v>
       </c>
       <c r="F207" s="37" t="n">
-        <v>83</v>
-      </c>
-      <c r="G207" s="37" t="n">
-        <v>-119</v>
+        <v>244</v>
+      </c>
+      <c r="G207" s="44" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="37" t="inlineStr">
         <is>
-          <t>Nicholls</t>
+          <t>Washington State</t>
         </is>
       </c>
       <c r="B208" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C208" s="37" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="D208" s="37" t="n">
         <v>203</v>
       </c>
       <c r="E208" s="37" t="n">
-        <v>1366.1</v>
+        <v>1520.6</v>
       </c>
       <c r="F208" s="37" t="n">
-        <v>244</v>
-      </c>
-      <c r="G208" s="44" t="n">
-        <v>41</v>
+        <v>80</v>
+      </c>
+      <c r="G208" s="37" t="n">
+        <v>-123</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="37" t="inlineStr">
         <is>
-          <t>Washington State</t>
+          <t>Maine</t>
         </is>
       </c>
       <c r="B209" s="37" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="C209" s="37" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="D209" s="37" t="n">
         <v>204</v>
       </c>
       <c r="E209" s="37" t="n">
-        <v>1520.6</v>
+        <v>1388.5</v>
       </c>
       <c r="F209" s="37" t="n">
-        <v>80</v>
-      </c>
-      <c r="G209" s="37" t="n">
-        <v>-124</v>
+        <v>231</v>
+      </c>
+      <c r="G209" s="44" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="37" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="B210" s="37" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C210" s="37" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="D210" s="37" t="n">
         <v>205</v>
       </c>
       <c r="E210" s="37" t="n">
-        <v>1388.5</v>
+        <v>1571.5</v>
       </c>
       <c r="F210" s="37" t="n">
-        <v>231</v>
-      </c>
-      <c r="G210" s="44" t="n">
-        <v>26</v>
+        <v>64</v>
+      </c>
+      <c r="G210" s="37" t="n">
+        <v>-141</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="37" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Missouri State</t>
         </is>
       </c>
       <c r="B211" s="37" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C211" s="37" t="n">
-        <v>-0.93</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D211" s="37" t="n">
         <v>206</v>
       </c>
       <c r="E211" s="37" t="n">
-        <v>1571.5</v>
+        <v>1447</v>
       </c>
       <c r="F211" s="37" t="n">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="G211" s="37" t="n">
-        <v>-142</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="37" t="inlineStr">
         <is>
-          <t>Missouri State</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="B212" s="37" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C212" s="37" t="n">
@@ -36155,13 +36187,13 @@
         <v>207</v>
       </c>
       <c r="E212" s="37" t="n">
-        <v>1447</v>
+        <v>1530.9</v>
       </c>
       <c r="F212" s="37" t="n">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="G212" s="37" t="n">
-        <v>-73</v>
+        <v>-131</v>
       </c>
     </row>
     <row r="213">
@@ -36185,10 +36217,10 @@
         <v>1445.5</v>
       </c>
       <c r="F213" s="37" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G213" s="37" t="n">
-        <v>-72</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="214">
@@ -36374,10 +36406,10 @@
         <v>1446.5</v>
       </c>
       <c r="F220" s="37" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G220" s="37" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
     </row>
     <row r="221">
@@ -36725,10 +36757,10 @@
         <v>1532.4</v>
       </c>
       <c r="F233" s="37" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G233" s="37" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="234">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -25250,7 +25250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -13946,26 +13946,26 @@
       </c>
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>33-26-1</t>
+          <t>33-27-1</t>
         </is>
       </c>
       <c r="C3" s="41" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="38" t="inlineStr">
         <is>
-          <t>Weekly ATS (Wk 5)</t>
+          <t>Weekly ATS (Wk 6)</t>
         </is>
       </c>
       <c r="B4" s="38" t="inlineStr">
         <is>
-          <t>3-3-0</t>
+          <t>0-1-0</t>
         </is>
       </c>
       <c r="C4" s="41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.6" customHeight="1">
@@ -14098,7 +14098,7 @@
     <row r="12">
       <c r="A12" s="38" t="inlineStr">
         <is>
-          <t>Georgia Southern</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B12" s="38" t="n">
@@ -14111,69 +14111,71 @@
         <v>1</v>
       </c>
       <c r="E12" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="38" t="n">
         <v>2</v>
-      </c>
-      <c r="F12" s="38" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="38" t="inlineStr">
         <is>
-          <t>App State</t>
+          <t>Georgia Southern</t>
         </is>
       </c>
       <c r="B13" s="38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="38" t="n"/>
+      <c r="D13" s="38" t="n">
+        <v>1</v>
+      </c>
       <c r="E13" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="38" t="n">
         <v>3</v>
-      </c>
-      <c r="F13" s="38" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="38" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>App State</t>
         </is>
       </c>
       <c r="B14" s="38" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="D14" s="38" t="n"/>
       <c r="E14" s="38" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="38" t="inlineStr">
         <is>
-          <t>Louisiana Tech</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B15" s="38" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="38" t="n"/>
       <c r="E15" s="38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>2</v>
@@ -14182,7 +14184,7 @@
     <row r="16">
       <c r="A16" s="38" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Louisiana Tech</t>
         </is>
       </c>
       <c r="B16" s="38" t="n">
@@ -14224,34 +14226,36 @@
     <row r="18" ht="26.45" customHeight="1">
       <c r="A18" s="38" t="inlineStr">
         <is>
-          <t>Southern Miss</t>
+          <t>Coastal Carolina</t>
         </is>
       </c>
       <c r="B18" s="38" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="38" t="n"/>
       <c r="E18" s="38" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="38" t="inlineStr">
         <is>
-          <t>Coastal Carolina</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="B19" s="38" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="38" t="n">
         <v>0</v>
@@ -14266,14 +14270,14 @@
     <row r="20">
       <c r="A20" s="38" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Southern Miss</t>
         </is>
       </c>
       <c r="B20" s="38" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="38" t="n">
         <v>0</v>
@@ -14454,9 +14458,17 @@
       <c r="N25" s="38" t="n">
         <v>0.3</v>
       </c>
-      <c r="O25" s="38" t="n"/>
-      <c r="P25" s="38" t="n"/>
-      <c r="Q25" s="38" t="n"/>
+      <c r="O25" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="P25" s="38" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q25" s="43" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="38" t="n">
@@ -25448,7 +25460,7 @@
         <v/>
       </c>
       <c r="I3" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="J3" t="n">
         <v>43.5</v>
@@ -25560,7 +25572,7 @@
         <v/>
       </c>
       <c r="I5" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="J5" t="n">
         <v>49.5</v>
@@ -36639,6 +36651,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
@@ -36674,6 +36687,11 @@
           <t>Week 5</t>
         </is>
       </c>
+      <c r="G1" s="36" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
       <c r="V1" s="37" t="inlineStr">
         <is>
           <t>Matchup Spread Calculator</t>
@@ -36701,6 +36719,9 @@
       <c r="F2" s="38" t="n">
         <v>94.59999999999999</v>
       </c>
+      <c r="G2" s="38" t="n">
+        <v>94.59999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="38" t="inlineStr">
@@ -36723,6 +36744,9 @@
       <c r="F3" s="38" t="n">
         <v>94.2</v>
       </c>
+      <c r="G3" s="38" t="n">
+        <v>94.3</v>
+      </c>
       <c r="V3" s="38" t="inlineStr">
         <is>
           <t>Home Team</t>
@@ -36755,6 +36779,9 @@
       <c r="F4" s="38" t="n">
         <v>90.40000000000001</v>
       </c>
+      <c r="G4" s="38" t="n">
+        <v>90.5</v>
+      </c>
       <c r="V4" s="38" t="inlineStr">
         <is>
           <t>Away Team</t>
@@ -36787,6 +36814,9 @@
       <c r="F5" s="38" t="n">
         <v>89.2</v>
       </c>
+      <c r="G5" s="38" t="n">
+        <v>89.2</v>
+      </c>
       <c r="V5" s="38" t="inlineStr">
         <is>
           <t>Neutral Site? (Y/N)</t>
@@ -36819,6 +36849,9 @@
       <c r="F6" s="38" t="n">
         <v>88</v>
       </c>
+      <c r="G6" s="38" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="38" t="inlineStr">
@@ -36841,6 +36874,9 @@
       <c r="F7" s="38" t="n">
         <v>87.8</v>
       </c>
+      <c r="G7" s="38" t="n">
+        <v>87.8</v>
+      </c>
       <c r="V7" s="38" t="inlineStr">
         <is>
           <t>HFA (model constant)</t>
@@ -36871,6 +36907,9 @@
       <c r="F8" s="38" t="n">
         <v>85.8</v>
       </c>
+      <c r="G8" s="38" t="n">
+        <v>85.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="38" t="inlineStr">
@@ -36893,13 +36932,16 @@
       <c r="F9" s="38" t="n">
         <v>85.7</v>
       </c>
+      <c r="G9" s="38" t="n">
+        <v>85.7</v>
+      </c>
       <c r="V9" s="39" t="inlineStr">
         <is>
           <t>Predicted Spread (Home)</t>
         </is>
       </c>
       <c r="W9" s="39">
-        <f>IF(OR(W3="",W4=""),"",INDEX($F$2:$F$139,MATCH(W4,$A$2:$A$139,0))-INDEX($F$2:$F$139,MATCH(W3,$A$2:$A$139,0))-IF(UPPER(W5)="Y",0,W7))</f>
+        <f>IF(OR(W3="",W4=""),"",INDEX($G$2:$G$139,MATCH(W4,$A$2:$A$139,0))-INDEX($G$2:$G$139,MATCH(W3,$A$2:$A$139,0))-IF(UPPER(W5)="Y",0,W7))</f>
         <v/>
       </c>
     </row>
@@ -36924,6 +36966,9 @@
       <c r="F10" s="38" t="n">
         <v>84.5</v>
       </c>
+      <c r="G10" s="38" t="n">
+        <v>84.5</v>
+      </c>
       <c r="V10" s="40" t="inlineStr">
         <is>
           <t>(negative = home team favored, e.g. "Home -6.5")</t>
@@ -36951,6 +36996,9 @@
       <c r="F11" s="38" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="G11" s="38" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="38" t="inlineStr">
@@ -36973,6 +37021,9 @@
       <c r="F12" s="38" t="n">
         <v>83</v>
       </c>
+      <c r="G12" s="38" t="n">
+        <v>83.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="38" t="inlineStr">
@@ -36995,6 +37046,9 @@
       <c r="F13" s="38" t="n">
         <v>81.2</v>
       </c>
+      <c r="G13" s="38" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="38" t="inlineStr">
@@ -37017,6 +37071,9 @@
       <c r="F14" s="38" t="n">
         <v>81.09999999999999</v>
       </c>
+      <c r="G14" s="38" t="n">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="38" t="inlineStr">
@@ -37039,6 +37096,9 @@
       <c r="F15" s="38" t="n">
         <v>80.7</v>
       </c>
+      <c r="G15" s="38" t="n">
+        <v>80.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="38" t="inlineStr">
@@ -37061,6 +37121,9 @@
       <c r="F16" s="38" t="n">
         <v>80.40000000000001</v>
       </c>
+      <c r="G16" s="38" t="n">
+        <v>80.40000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="38" t="inlineStr">
@@ -37083,6 +37146,9 @@
       <c r="F17" s="38" t="n">
         <v>79.8</v>
       </c>
+      <c r="G17" s="38" t="n">
+        <v>79.8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="38" t="inlineStr">
@@ -37105,6 +37171,9 @@
       <c r="F18" s="38" t="n">
         <v>78.8</v>
       </c>
+      <c r="G18" s="38" t="n">
+        <v>78.8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="38" t="inlineStr">
@@ -37127,6 +37196,9 @@
       <c r="F19" s="38" t="n">
         <v>78.2</v>
       </c>
+      <c r="G19" s="38" t="n">
+        <v>78.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="38" t="inlineStr">
@@ -37149,6 +37221,9 @@
       <c r="F20" s="38" t="n">
         <v>78</v>
       </c>
+      <c r="G20" s="38" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="38" t="inlineStr">
@@ -37171,6 +37246,9 @@
       <c r="F21" s="38" t="n">
         <v>77.8</v>
       </c>
+      <c r="G21" s="38" t="n">
+        <v>77.8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="38" t="inlineStr">
@@ -37193,6 +37271,9 @@
       <c r="F22" s="38" t="n">
         <v>77.59999999999999</v>
       </c>
+      <c r="G22" s="38" t="n">
+        <v>77.59999999999999</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="38" t="inlineStr">
@@ -37215,6 +37296,9 @@
       <c r="F23" s="38" t="n">
         <v>77.59999999999999</v>
       </c>
+      <c r="G23" s="38" t="n">
+        <v>77.59999999999999</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="38" t="inlineStr">
@@ -37237,6 +37321,9 @@
       <c r="F24" s="38" t="n">
         <v>77.5</v>
       </c>
+      <c r="G24" s="38" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="38" t="inlineStr">
@@ -37259,6 +37346,9 @@
       <c r="F25" s="38" t="n">
         <v>77.40000000000001</v>
       </c>
+      <c r="G25" s="38" t="n">
+        <v>77.40000000000001</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="38" t="inlineStr">
@@ -37281,6 +37371,9 @@
       <c r="F26" s="38" t="n">
         <v>76.90000000000001</v>
       </c>
+      <c r="G26" s="38" t="n">
+        <v>76.90000000000001</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
@@ -37303,50 +37396,59 @@
       <c r="F27" s="38" t="n">
         <v>76.59999999999999</v>
       </c>
+      <c r="G27" s="38" t="n">
+        <v>76.59999999999999</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B28" s="38" t="n">
-        <v>73.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="C28" s="38" t="n">
-        <v>72.7</v>
+        <v>73.5</v>
       </c>
       <c r="D28" s="38" t="n">
-        <v>72.5</v>
+        <v>74.2</v>
       </c>
       <c r="E28" s="38" t="n">
-        <v>73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F28" s="38" t="n">
         <v>76.5</v>
       </c>
+      <c r="G28" s="38" t="n">
+        <v>76.59999999999999</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="B29" s="38" t="n">
-        <v>67.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C29" s="38" t="n">
-        <v>73.5</v>
+        <v>72.7</v>
       </c>
       <c r="D29" s="38" t="n">
-        <v>74.2</v>
+        <v>72.5</v>
       </c>
       <c r="E29" s="38" t="n">
-        <v>76.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="F29" s="38" t="n">
         <v>76.5</v>
       </c>
+      <c r="G29" s="38" t="n">
+        <v>76.5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="inlineStr">
@@ -37369,6 +37471,9 @@
       <c r="F30" s="38" t="n">
         <v>76.3</v>
       </c>
+      <c r="G30" s="38" t="n">
+        <v>76.3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="38" t="inlineStr">
@@ -37391,6 +37496,9 @@
       <c r="F31" s="38" t="n">
         <v>76.2</v>
       </c>
+      <c r="G31" s="38" t="n">
+        <v>76.2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="38" t="inlineStr">
@@ -37413,6 +37521,9 @@
       <c r="F32" s="38" t="n">
         <v>76.09999999999999</v>
       </c>
+      <c r="G32" s="38" t="n">
+        <v>76.09999999999999</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="38" t="inlineStr">
@@ -37435,6 +37546,9 @@
       <c r="F33" s="38" t="n">
         <v>75.2</v>
       </c>
+      <c r="G33" s="38" t="n">
+        <v>75.3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="38" t="inlineStr">
@@ -37457,6 +37571,9 @@
       <c r="F34" s="38" t="n">
         <v>75.2</v>
       </c>
+      <c r="G34" s="38" t="n">
+        <v>75.2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="38" t="inlineStr">
@@ -37479,6 +37596,9 @@
       <c r="F35" s="38" t="n">
         <v>75.09999999999999</v>
       </c>
+      <c r="G35" s="38" t="n">
+        <v>75.09999999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="38" t="inlineStr">
@@ -37501,6 +37621,9 @@
       <c r="F36" s="38" t="n">
         <v>74.8</v>
       </c>
+      <c r="G36" s="38" t="n">
+        <v>74.8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="38" t="inlineStr">
@@ -37523,6 +37646,9 @@
       <c r="F37" s="38" t="n">
         <v>73.7</v>
       </c>
+      <c r="G37" s="38" t="n">
+        <v>73.8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="38" t="inlineStr">
@@ -37545,6 +37671,9 @@
       <c r="F38" s="38" t="n">
         <v>73.7</v>
       </c>
+      <c r="G38" s="38" t="n">
+        <v>73.7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="38" t="inlineStr">
@@ -37567,6 +37696,9 @@
       <c r="F39" s="38" t="n">
         <v>73.09999999999999</v>
       </c>
+      <c r="G39" s="38" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="38" t="inlineStr">
@@ -37589,6 +37721,9 @@
       <c r="F40" s="38" t="n">
         <v>73.09999999999999</v>
       </c>
+      <c r="G40" s="38" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="38" t="inlineStr">
@@ -37611,6 +37746,9 @@
       <c r="F41" s="38" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="G41" s="38" t="n">
+        <v>72.90000000000001</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="38" t="inlineStr">
@@ -37633,6 +37771,9 @@
       <c r="F42" s="38" t="n">
         <v>72.8</v>
       </c>
+      <c r="G42" s="38" t="n">
+        <v>72.8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="38" t="inlineStr">
@@ -37655,6 +37796,9 @@
       <c r="F43" s="38" t="n">
         <v>72.09999999999999</v>
       </c>
+      <c r="G43" s="38" t="n">
+        <v>72.09999999999999</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="38" t="inlineStr">
@@ -37677,6 +37821,9 @@
       <c r="F44" s="38" t="n">
         <v>71.5</v>
       </c>
+      <c r="G44" s="38" t="n">
+        <v>71.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="38" t="inlineStr">
@@ -37699,6 +37846,9 @@
       <c r="F45" s="38" t="n">
         <v>71.40000000000001</v>
       </c>
+      <c r="G45" s="38" t="n">
+        <v>71.40000000000001</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="38" t="inlineStr">
@@ -37721,6 +37871,9 @@
       <c r="F46" s="38" t="n">
         <v>71.3</v>
       </c>
+      <c r="G46" s="38" t="n">
+        <v>71.3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="38" t="inlineStr">
@@ -37743,6 +37896,9 @@
       <c r="F47" s="38" t="n">
         <v>71.09999999999999</v>
       </c>
+      <c r="G47" s="38" t="n">
+        <v>71.09999999999999</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="38" t="inlineStr">
@@ -37765,6 +37921,9 @@
       <c r="F48" s="38" t="n">
         <v>71</v>
       </c>
+      <c r="G48" s="38" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="38" t="inlineStr">
@@ -37787,6 +37946,9 @@
       <c r="F49" s="38" t="n">
         <v>70.3</v>
       </c>
+      <c r="G49" s="38" t="n">
+        <v>70.3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="38" t="inlineStr">
@@ -37809,6 +37971,9 @@
       <c r="F50" s="38" t="n">
         <v>70.2</v>
       </c>
+      <c r="G50" s="38" t="n">
+        <v>70.2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="38" t="inlineStr">
@@ -37831,6 +37996,9 @@
       <c r="F51" s="38" t="n">
         <v>69.7</v>
       </c>
+      <c r="G51" s="38" t="n">
+        <v>69.7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="38" t="inlineStr">
@@ -37853,6 +38021,9 @@
       <c r="F52" s="38" t="n">
         <v>69.5</v>
       </c>
+      <c r="G52" s="38" t="n">
+        <v>69.5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="38" t="inlineStr">
@@ -37875,6 +38046,9 @@
       <c r="F53" s="38" t="n">
         <v>69.3</v>
       </c>
+      <c r="G53" s="38" t="n">
+        <v>69.3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="38" t="inlineStr">
@@ -37897,6 +38071,9 @@
       <c r="F54" s="38" t="n">
         <v>68.5</v>
       </c>
+      <c r="G54" s="38" t="n">
+        <v>68.5</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="38" t="inlineStr">
@@ -37919,6 +38096,9 @@
       <c r="F55" s="38" t="n">
         <v>68.3</v>
       </c>
+      <c r="G55" s="38" t="n">
+        <v>68.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="38" t="inlineStr">
@@ -37941,6 +38121,9 @@
       <c r="F56" s="38" t="n">
         <v>68.2</v>
       </c>
+      <c r="G56" s="38" t="n">
+        <v>68.2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="38" t="inlineStr">
@@ -37963,6 +38146,9 @@
       <c r="F57" s="38" t="n">
         <v>67.3</v>
       </c>
+      <c r="G57" s="38" t="n">
+        <v>67.3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="38" t="inlineStr">
@@ -37985,6 +38171,9 @@
       <c r="F58" s="38" t="n">
         <v>67</v>
       </c>
+      <c r="G58" s="38" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="38" t="inlineStr">
@@ -38007,6 +38196,9 @@
       <c r="F59" s="38" t="n">
         <v>66.90000000000001</v>
       </c>
+      <c r="G59" s="38" t="n">
+        <v>66.90000000000001</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="38" t="inlineStr">
@@ -38029,6 +38221,9 @@
       <c r="F60" s="38" t="n">
         <v>66.40000000000001</v>
       </c>
+      <c r="G60" s="38" t="n">
+        <v>66.40000000000001</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="38" t="inlineStr">
@@ -38051,6 +38246,9 @@
       <c r="F61" s="38" t="n">
         <v>65.8</v>
       </c>
+      <c r="G61" s="38" t="n">
+        <v>65.8</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="38" t="inlineStr">
@@ -38073,6 +38271,9 @@
       <c r="F62" s="38" t="n">
         <v>65.59999999999999</v>
       </c>
+      <c r="G62" s="38" t="n">
+        <v>65.7</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="38" t="inlineStr">
@@ -38095,6 +38296,9 @@
       <c r="F63" s="38" t="n">
         <v>65.2</v>
       </c>
+      <c r="G63" s="38" t="n">
+        <v>65.2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="38" t="inlineStr">
@@ -38117,6 +38321,9 @@
       <c r="F64" s="38" t="n">
         <v>65.09999999999999</v>
       </c>
+      <c r="G64" s="38" t="n">
+        <v>65.09999999999999</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="38" t="inlineStr">
@@ -38139,6 +38346,9 @@
       <c r="F65" s="38" t="n">
         <v>65</v>
       </c>
+      <c r="G65" s="38" t="n">
+        <v>65.09999999999999</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="38" t="inlineStr">
@@ -38161,6 +38371,9 @@
       <c r="F66" s="38" t="n">
         <v>64.7</v>
       </c>
+      <c r="G66" s="38" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="38" t="inlineStr">
@@ -38183,6 +38396,9 @@
       <c r="F67" s="38" t="n">
         <v>64.7</v>
       </c>
+      <c r="G67" s="38" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="38" t="inlineStr">
@@ -38205,6 +38421,9 @@
       <c r="F68" s="38" t="n">
         <v>64.5</v>
       </c>
+      <c r="G68" s="38" t="n">
+        <v>64.5</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="38" t="inlineStr">
@@ -38227,6 +38446,9 @@
       <c r="F69" s="38" t="n">
         <v>64.09999999999999</v>
       </c>
+      <c r="G69" s="38" t="n">
+        <v>64.09999999999999</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="38" t="inlineStr">
@@ -38249,6 +38471,9 @@
       <c r="F70" s="38" t="n">
         <v>63.9</v>
       </c>
+      <c r="G70" s="38" t="n">
+        <v>63.9</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="38" t="inlineStr">
@@ -38271,6 +38496,9 @@
       <c r="F71" s="38" t="n">
         <v>63.6</v>
       </c>
+      <c r="G71" s="38" t="n">
+        <v>63.7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="38" t="inlineStr">
@@ -38293,6 +38521,9 @@
       <c r="F72" s="38" t="n">
         <v>63.6</v>
       </c>
+      <c r="G72" s="38" t="n">
+        <v>63.6</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="38" t="inlineStr">
@@ -38315,6 +38546,9 @@
       <c r="F73" s="38" t="n">
         <v>62.6</v>
       </c>
+      <c r="G73" s="38" t="n">
+        <v>62.6</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="38" t="inlineStr">
@@ -38337,6 +38571,9 @@
       <c r="F74" s="38" t="n">
         <v>62.5</v>
       </c>
+      <c r="G74" s="38" t="n">
+        <v>62.6</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="38" t="inlineStr">
@@ -38359,6 +38596,9 @@
       <c r="F75" s="38" t="n">
         <v>62.5</v>
       </c>
+      <c r="G75" s="38" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="38" t="inlineStr">
@@ -38381,6 +38621,9 @@
       <c r="F76" s="38" t="n">
         <v>62.2</v>
       </c>
+      <c r="G76" s="38" t="n">
+        <v>62.2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="38" t="inlineStr">
@@ -38403,6 +38646,9 @@
       <c r="F77" s="38" t="n">
         <v>62</v>
       </c>
+      <c r="G77" s="38" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="38" t="inlineStr">
@@ -38425,6 +38671,9 @@
       <c r="F78" s="38" t="n">
         <v>61.7</v>
       </c>
+      <c r="G78" s="38" t="n">
+        <v>61.7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="38" t="inlineStr">
@@ -38447,6 +38696,9 @@
       <c r="F79" s="38" t="n">
         <v>61.7</v>
       </c>
+      <c r="G79" s="38" t="n">
+        <v>61.7</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="38" t="inlineStr">
@@ -38469,6 +38721,9 @@
       <c r="F80" s="38" t="n">
         <v>61.6</v>
       </c>
+      <c r="G80" s="38" t="n">
+        <v>61.7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="38" t="inlineStr">
@@ -38491,6 +38746,9 @@
       <c r="F81" s="38" t="n">
         <v>61.6</v>
       </c>
+      <c r="G81" s="38" t="n">
+        <v>61.6</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="38" t="inlineStr">
@@ -38513,6 +38771,9 @@
       <c r="F82" s="38" t="n">
         <v>61.4</v>
       </c>
+      <c r="G82" s="38" t="n">
+        <v>61.5</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="38" t="inlineStr">
@@ -38535,6 +38796,9 @@
       <c r="F83" s="38" t="n">
         <v>61.4</v>
       </c>
+      <c r="G83" s="38" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="38" t="inlineStr">
@@ -38557,6 +38821,9 @@
       <c r="F84" s="38" t="n">
         <v>61.3</v>
       </c>
+      <c r="G84" s="38" t="n">
+        <v>61.3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="38" t="inlineStr">
@@ -38579,6 +38846,9 @@
       <c r="F85" s="38" t="n">
         <v>60.7</v>
       </c>
+      <c r="G85" s="38" t="n">
+        <v>60.7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="38" t="inlineStr">
@@ -38601,6 +38871,9 @@
       <c r="F86" s="38" t="n">
         <v>60.6</v>
       </c>
+      <c r="G86" s="38" t="n">
+        <v>60.6</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="38" t="inlineStr">
@@ -38623,6 +38896,9 @@
       <c r="F87" s="38" t="n">
         <v>59.7</v>
       </c>
+      <c r="G87" s="38" t="n">
+        <v>59.7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="38" t="inlineStr">
@@ -38645,6 +38921,9 @@
       <c r="F88" s="38" t="n">
         <v>59.6</v>
       </c>
+      <c r="G88" s="38" t="n">
+        <v>59.6</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="38" t="inlineStr">
@@ -38667,6 +38946,9 @@
       <c r="F89" s="38" t="n">
         <v>59.5</v>
       </c>
+      <c r="G89" s="38" t="n">
+        <v>59.5</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="38" t="inlineStr">
@@ -38689,92 +38971,107 @@
       <c r="F90" s="38" t="n">
         <v>59.3</v>
       </c>
+      <c r="G90" s="38" t="n">
+        <v>59.3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="38" t="inlineStr">
         <is>
-          <t>Florida Atlantic</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="B91" s="38" t="n">
-        <v>50.4</v>
+        <v>56.7</v>
       </c>
       <c r="C91" s="38" t="n">
-        <v>53.3</v>
+        <v>57.9</v>
       </c>
       <c r="D91" s="38" t="n">
-        <v>54.2</v>
+        <v>57</v>
       </c>
       <c r="E91" s="38" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="F91" s="38" t="n">
         <v>58.6</v>
       </c>
+      <c r="G91" s="38" t="n">
+        <v>58.6</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="38" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B92" s="38" t="n">
-        <v>56.7</v>
+        <v>58.8</v>
       </c>
       <c r="C92" s="38" t="n">
-        <v>57.9</v>
+        <v>59</v>
       </c>
       <c r="D92" s="38" t="n">
-        <v>57</v>
+        <v>58.2</v>
       </c>
       <c r="E92" s="38" t="n">
-        <v>56.5</v>
+        <v>59.6</v>
       </c>
       <c r="F92" s="38" t="n">
-        <v>58.6</v>
+        <v>58.4</v>
+      </c>
+      <c r="G92" s="38" t="n">
+        <v>58.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="38" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B93" s="38" t="n">
-        <v>58.8</v>
+        <v>60.4</v>
       </c>
       <c r="C93" s="38" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="D93" s="38" t="n">
-        <v>58.2</v>
+        <v>60.2</v>
       </c>
       <c r="E93" s="38" t="n">
-        <v>59.6</v>
+        <v>59.2</v>
       </c>
       <c r="F93" s="38" t="n">
         <v>58.4</v>
       </c>
+      <c r="G93" s="38" t="n">
+        <v>58.4</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="38" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Florida Atlantic</t>
         </is>
       </c>
       <c r="B94" s="38" t="n">
-        <v>60.4</v>
+        <v>50.4</v>
       </c>
       <c r="C94" s="38" t="n">
-        <v>59.4</v>
+        <v>53.3</v>
       </c>
       <c r="D94" s="38" t="n">
-        <v>60.2</v>
+        <v>54.2</v>
       </c>
       <c r="E94" s="38" t="n">
-        <v>59.2</v>
+        <v>55.8</v>
       </c>
       <c r="F94" s="38" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="G94" s="38" t="n">
         <v>58.4</v>
       </c>
     </row>
@@ -38799,6 +39096,9 @@
       <c r="F95" s="38" t="n">
         <v>58</v>
       </c>
+      <c r="G95" s="38" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="38" t="inlineStr">
@@ -38821,6 +39121,9 @@
       <c r="F96" s="38" t="n">
         <v>57.5</v>
       </c>
+      <c r="G96" s="38" t="n">
+        <v>57.5</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="38" t="inlineStr">
@@ -38843,6 +39146,9 @@
       <c r="F97" s="38" t="n">
         <v>57.4</v>
       </c>
+      <c r="G97" s="38" t="n">
+        <v>57.4</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="38" t="inlineStr">
@@ -38865,6 +39171,9 @@
       <c r="F98" s="38" t="n">
         <v>57.2</v>
       </c>
+      <c r="G98" s="38" t="n">
+        <v>57.2</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="38" t="inlineStr">
@@ -38887,6 +39196,9 @@
       <c r="F99" s="38" t="n">
         <v>56.8</v>
       </c>
+      <c r="G99" s="38" t="n">
+        <v>56.9</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="38" t="inlineStr">
@@ -38909,6 +39221,9 @@
       <c r="F100" s="38" t="n">
         <v>56.7</v>
       </c>
+      <c r="G100" s="38" t="n">
+        <v>56.7</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="38" t="inlineStr">
@@ -38931,6 +39246,9 @@
       <c r="F101" s="38" t="n">
         <v>56.5</v>
       </c>
+      <c r="G101" s="38" t="n">
+        <v>56.6</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="38" t="inlineStr">
@@ -38953,6 +39271,9 @@
       <c r="F102" s="38" t="n">
         <v>56.1</v>
       </c>
+      <c r="G102" s="38" t="n">
+        <v>56.1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="38" t="inlineStr">
@@ -38975,137 +39296,158 @@
       <c r="F103" s="38" t="n">
         <v>56</v>
       </c>
+      <c r="G103" s="38" t="n">
+        <v>56.1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="38" t="inlineStr">
         <is>
-          <t>Georgia State</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B104" s="38" t="n">
-        <v>47.4</v>
+        <v>53.1</v>
       </c>
       <c r="C104" s="38" t="n">
-        <v>49.7</v>
+        <v>53.7</v>
       </c>
       <c r="D104" s="38" t="n">
-        <v>49.6</v>
+        <v>54.6</v>
       </c>
       <c r="E104" s="38" t="n">
-        <v>51.2</v>
+        <v>54.2</v>
       </c>
       <c r="F104" s="38" t="n">
-        <v>55.9</v>
+        <v>54.2</v>
+      </c>
+      <c r="G104" s="38" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="38" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Georgia State</t>
         </is>
       </c>
       <c r="B105" s="38" t="n">
-        <v>56.1</v>
+        <v>47.4</v>
       </c>
       <c r="C105" s="38" t="n">
-        <v>57.4</v>
+        <v>49.7</v>
       </c>
       <c r="D105" s="38" t="n">
-        <v>57.8</v>
+        <v>49.6</v>
       </c>
       <c r="E105" s="38" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F105" s="38" t="n">
         <v>55.9</v>
       </c>
-      <c r="F105" s="38" t="n">
-        <v>55.5</v>
+      <c r="G105" s="38" t="n">
+        <v>55.9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="38" t="inlineStr">
         <is>
-          <t>Florida International</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B106" s="38" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="C106" s="38" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="D106" s="38" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E106" s="38" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F106" s="38" t="n">
         <v>55.5</v>
       </c>
-      <c r="C106" s="38" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="D106" s="38" t="n">
+      <c r="G106" s="38" t="n">
         <v>55.5</v>
-      </c>
-      <c r="E106" s="38" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F106" s="38" t="n">
-        <v>55.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="38" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Florida International</t>
         </is>
       </c>
       <c r="B107" s="38" t="n">
-        <v>57.3</v>
+        <v>55.5</v>
       </c>
       <c r="C107" s="38" t="n">
-        <v>54.4</v>
+        <v>56.4</v>
       </c>
       <c r="D107" s="38" t="n">
-        <v>57</v>
+        <v>55.5</v>
       </c>
       <c r="E107" s="38" t="n">
-        <v>54.2</v>
+        <v>55.6</v>
       </c>
       <c r="F107" s="38" t="n">
-        <v>54.9</v>
+        <v>55.3</v>
+      </c>
+      <c r="G107" s="38" t="n">
+        <v>55.3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="38" t="inlineStr">
         <is>
-          <t>Central Michigan</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="B108" s="38" t="n">
-        <v>55</v>
+        <v>57.3</v>
       </c>
       <c r="C108" s="38" t="n">
-        <v>53.8</v>
+        <v>54.4</v>
       </c>
       <c r="D108" s="38" t="n">
-        <v>54.6</v>
+        <v>57</v>
       </c>
       <c r="E108" s="38" t="n">
-        <v>53</v>
+        <v>54.2</v>
       </c>
       <c r="F108" s="38" t="n">
-        <v>54.5</v>
+        <v>54.9</v>
+      </c>
+      <c r="G108" s="38" t="n">
+        <v>54.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="38" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Central Michigan</t>
         </is>
       </c>
       <c r="B109" s="38" t="n">
-        <v>53.1</v>
+        <v>55</v>
       </c>
       <c r="C109" s="38" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="D109" s="38" t="n">
         <v>54.6</v>
       </c>
       <c r="E109" s="38" t="n">
-        <v>54.2</v>
+        <v>53</v>
       </c>
       <c r="F109" s="38" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
+      </c>
+      <c r="G109" s="38" t="n">
+        <v>54.5</v>
       </c>
     </row>
     <row r="110">
@@ -39129,6 +39471,9 @@
       <c r="F110" s="38" t="n">
         <v>53.9</v>
       </c>
+      <c r="G110" s="38" t="n">
+        <v>53.9</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="38" t="inlineStr">
@@ -39151,6 +39496,9 @@
       <c r="F111" s="38" t="n">
         <v>53.8</v>
       </c>
+      <c r="G111" s="38" t="n">
+        <v>53.7</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="38" t="inlineStr">
@@ -39173,6 +39521,9 @@
       <c r="F112" s="38" t="n">
         <v>53.5</v>
       </c>
+      <c r="G112" s="38" t="n">
+        <v>53.5</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="38" t="inlineStr">
@@ -39195,6 +39546,9 @@
       <c r="F113" s="38" t="n">
         <v>52.9</v>
       </c>
+      <c r="G113" s="38" t="n">
+        <v>52.9</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="38" t="inlineStr">
@@ -39217,6 +39571,9 @@
       <c r="F114" s="38" t="n">
         <v>52.6</v>
       </c>
+      <c r="G114" s="38" t="n">
+        <v>52.7</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="38" t="inlineStr">
@@ -39239,6 +39596,9 @@
       <c r="F115" s="38" t="n">
         <v>52.5</v>
       </c>
+      <c r="G115" s="38" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="38" t="inlineStr">
@@ -39261,6 +39621,9 @@
       <c r="F116" s="38" t="n">
         <v>52.4</v>
       </c>
+      <c r="G116" s="38" t="n">
+        <v>52.4</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="38" t="inlineStr">
@@ -39283,6 +39646,9 @@
       <c r="F117" s="38" t="n">
         <v>52</v>
       </c>
+      <c r="G117" s="38" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="38" t="inlineStr">
@@ -39305,6 +39671,9 @@
       <c r="F118" s="38" t="n">
         <v>51.9</v>
       </c>
+      <c r="G118" s="38" t="n">
+        <v>51.9</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="38" t="inlineStr">
@@ -39327,6 +39696,9 @@
       <c r="F119" s="38" t="n">
         <v>51.8</v>
       </c>
+      <c r="G119" s="38" t="n">
+        <v>51.8</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="38" t="inlineStr">
@@ -39349,114 +39721,132 @@
       <c r="F120" s="38" t="n">
         <v>51.6</v>
       </c>
+      <c r="G120" s="38" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="38" t="inlineStr">
         <is>
-          <t>Southern Miss</t>
+          <t>San José State</t>
         </is>
       </c>
       <c r="B121" s="38" t="n">
-        <v>54.4</v>
+        <v>51.7</v>
       </c>
       <c r="C121" s="38" t="n">
-        <v>52.7</v>
+        <v>51.6</v>
       </c>
       <c r="D121" s="38" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="E121" s="38" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="F121" s="38" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
+      </c>
+      <c r="G121" s="38" t="n">
+        <v>51.1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="38" t="inlineStr">
         <is>
-          <t>San José State</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B122" s="38" t="n">
-        <v>51.7</v>
+        <v>52.1</v>
       </c>
       <c r="C122" s="38" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="D122" s="38" t="n">
-        <v>50.5</v>
+        <v>52.5</v>
       </c>
       <c r="E122" s="38" t="n">
-        <v>50.4</v>
+        <v>51.5</v>
       </c>
       <c r="F122" s="38" t="n">
-        <v>51.1</v>
+        <v>51</v>
+      </c>
+      <c r="G122" s="38" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="38" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="B123" s="38" t="n">
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="C123" s="38" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="D123" s="38" t="n">
-        <v>52.5</v>
+        <v>49.7</v>
       </c>
       <c r="E123" s="38" t="n">
-        <v>51.5</v>
+        <v>48.8</v>
       </c>
       <c r="F123" s="38" t="n">
-        <v>51</v>
+        <v>50.2</v>
+      </c>
+      <c r="G123" s="38" t="n">
+        <v>50.2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="38" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Eastern Michigan</t>
         </is>
       </c>
       <c r="B124" s="38" t="n">
-        <v>51.5</v>
+        <v>47.2</v>
       </c>
       <c r="C124" s="38" t="n">
-        <v>50.6</v>
+        <v>46.4</v>
       </c>
       <c r="D124" s="38" t="n">
-        <v>49.7</v>
+        <v>44.8</v>
       </c>
       <c r="E124" s="38" t="n">
-        <v>48.8</v>
+        <v>47.4</v>
       </c>
       <c r="F124" s="38" t="n">
-        <v>50.2</v>
+        <v>49.4</v>
+      </c>
+      <c r="G124" s="38" t="n">
+        <v>49.4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="38" t="inlineStr">
         <is>
-          <t>Eastern Michigan</t>
+          <t>Southern Miss</t>
         </is>
       </c>
       <c r="B125" s="38" t="n">
-        <v>47.2</v>
+        <v>54.4</v>
       </c>
       <c r="C125" s="38" t="n">
-        <v>46.4</v>
+        <v>52.7</v>
       </c>
       <c r="D125" s="38" t="n">
-        <v>44.8</v>
+        <v>50.1</v>
       </c>
       <c r="E125" s="38" t="n">
-        <v>47.4</v>
+        <v>51.2</v>
       </c>
       <c r="F125" s="38" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G125" s="38" t="n">
         <v>49.4</v>
       </c>
     </row>
@@ -39481,6 +39871,9 @@
       <c r="F126" s="38" t="n">
         <v>49.2</v>
       </c>
+      <c r="G126" s="38" t="n">
+        <v>49.2</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="38" t="inlineStr">
@@ -39503,6 +39896,9 @@
       <c r="F127" s="38" t="n">
         <v>48.8</v>
       </c>
+      <c r="G127" s="38" t="n">
+        <v>48.8</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="38" t="inlineStr">
@@ -39525,6 +39921,9 @@
       <c r="F128" s="38" t="n">
         <v>47</v>
       </c>
+      <c r="G128" s="38" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="38" t="inlineStr">
@@ -39547,6 +39946,9 @@
       <c r="F129" s="38" t="n">
         <v>46.2</v>
       </c>
+      <c r="G129" s="38" t="n">
+        <v>46.2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="38" t="inlineStr">
@@ -39569,6 +39971,9 @@
       <c r="F130" s="38" t="n">
         <v>45.8</v>
       </c>
+      <c r="G130" s="38" t="n">
+        <v>45.8</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="38" t="inlineStr">
@@ -39591,6 +39996,9 @@
       <c r="F131" s="38" t="n">
         <v>45.3</v>
       </c>
+      <c r="G131" s="38" t="n">
+        <v>45.4</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="38" t="inlineStr">
@@ -39613,6 +40021,9 @@
       <c r="F132" s="38" t="n">
         <v>44.1</v>
       </c>
+      <c r="G132" s="38" t="n">
+        <v>44.1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="38" t="inlineStr">
@@ -39635,6 +40046,9 @@
       <c r="F133" s="38" t="n">
         <v>42.9</v>
       </c>
+      <c r="G133" s="38" t="n">
+        <v>42.9</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="38" t="inlineStr">
@@ -39657,6 +40071,9 @@
       <c r="F134" s="38" t="n">
         <v>42.6</v>
       </c>
+      <c r="G134" s="38" t="n">
+        <v>42.6</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="38" t="inlineStr">
@@ -39679,6 +40096,9 @@
       <c r="F135" s="38" t="n">
         <v>42.5</v>
       </c>
+      <c r="G135" s="38" t="n">
+        <v>42.5</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="38" t="inlineStr">
@@ -39701,6 +40121,9 @@
       <c r="F136" s="38" t="n">
         <v>40.5</v>
       </c>
+      <c r="G136" s="38" t="n">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="38" t="inlineStr">
@@ -39723,6 +40146,9 @@
       <c r="F137" s="38" t="n">
         <v>40.1</v>
       </c>
+      <c r="G137" s="38" t="n">
+        <v>40.2</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="38" t="inlineStr">
@@ -39745,6 +40171,9 @@
       <c r="F138" s="38" t="n">
         <v>39.5</v>
       </c>
+      <c r="G138" s="38" t="n">
+        <v>39.3</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="38" t="inlineStr">
@@ -39765,6 +40194,9 @@
         <v>37.3</v>
       </c>
       <c r="F139" s="38" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G139" s="38" t="n">
         <v>37.2</v>
       </c>
     </row>
@@ -43324,10 +43756,10 @@
         <v>1521.6</v>
       </c>
       <c r="F57" s="38" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G57" s="45" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
@@ -43783,10 +44215,10 @@
         <v>1528.5</v>
       </c>
       <c r="F74" s="38" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G74" s="38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
@@ -44467,34 +44899,34 @@
     <row r="100">
       <c r="A100" s="38" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B100" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C100" s="38" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="D100" s="38" t="n">
         <v>95</v>
       </c>
       <c r="E100" s="38" t="n">
-        <v>1449.9</v>
+        <v>1535.2</v>
       </c>
       <c r="F100" s="38" t="n">
-        <v>128</v>
-      </c>
-      <c r="G100" s="45" t="n">
-        <v>33</v>
+        <v>75</v>
+      </c>
+      <c r="G100" s="38" t="n">
+        <v>-20</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="38" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>UC Davis</t>
         </is>
       </c>
       <c r="B101" s="38" t="inlineStr">
@@ -44509,19 +44941,19 @@
         <v>96</v>
       </c>
       <c r="E101" s="38" t="n">
-        <v>1459.1</v>
+        <v>1449.9</v>
       </c>
       <c r="F101" s="38" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G101" s="45" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="38" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B102" s="38" t="inlineStr">
@@ -44536,51 +44968,51 @@
         <v>97</v>
       </c>
       <c r="E102" s="38" t="n">
-        <v>1411.5</v>
+        <v>1459.1</v>
       </c>
       <c r="F102" s="38" t="n">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="G102" s="45" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="38" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="B103" s="38" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C103" s="38" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="D103" s="38" t="n">
         <v>98</v>
       </c>
       <c r="E103" s="38" t="n">
-        <v>1426.3</v>
+        <v>1411.5</v>
       </c>
       <c r="F103" s="38" t="n">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="G103" s="45" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="38" t="inlineStr">
         <is>
-          <t>Utah Tech</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="B104" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C104" s="38" t="n">
@@ -44590,19 +45022,19 @@
         <v>99</v>
       </c>
       <c r="E104" s="38" t="n">
-        <v>1439.6</v>
+        <v>1426.3</v>
       </c>
       <c r="F104" s="38" t="n">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="G104" s="45" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="38" t="inlineStr">
         <is>
-          <t>Eastern Washington</t>
+          <t>Utah Tech</t>
         </is>
       </c>
       <c r="B105" s="38" t="inlineStr">
@@ -44611,25 +45043,25 @@
         </is>
       </c>
       <c r="C105" s="38" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="D105" s="38" t="n">
         <v>100</v>
       </c>
       <c r="E105" s="38" t="n">
-        <v>1433.4</v>
+        <v>1439.6</v>
       </c>
       <c r="F105" s="38" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G105" s="45" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="38" t="inlineStr">
         <is>
-          <t>William &amp; Mary</t>
+          <t>Eastern Washington</t>
         </is>
       </c>
       <c r="B106" s="38" t="inlineStr">
@@ -44644,19 +45076,19 @@
         <v>101</v>
       </c>
       <c r="E106" s="38" t="n">
-        <v>1440</v>
+        <v>1433.4</v>
       </c>
       <c r="F106" s="38" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G106" s="45" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="38" t="inlineStr">
         <is>
-          <t>McNeese</t>
+          <t>William &amp; Mary</t>
         </is>
       </c>
       <c r="B107" s="38" t="inlineStr">
@@ -44665,25 +45097,25 @@
         </is>
       </c>
       <c r="C107" s="38" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="D107" s="38" t="n">
         <v>102</v>
       </c>
       <c r="E107" s="38" t="n">
-        <v>1417.4</v>
+        <v>1440</v>
       </c>
       <c r="F107" s="38" t="n">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="G107" s="45" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="38" t="inlineStr">
         <is>
-          <t>Austin Peay</t>
+          <t>McNeese</t>
         </is>
       </c>
       <c r="B108" s="38" t="inlineStr">
@@ -44692,25 +45124,25 @@
         </is>
       </c>
       <c r="C108" s="38" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="D108" s="38" t="n">
         <v>103</v>
       </c>
       <c r="E108" s="38" t="n">
-        <v>1470.1</v>
+        <v>1417.4</v>
       </c>
       <c r="F108" s="38" t="n">
-        <v>109</v>
-      </c>
-      <c r="G108" s="38" t="n">
-        <v>6</v>
+        <v>186</v>
+      </c>
+      <c r="G108" s="45" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="38" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Austin Peay</t>
         </is>
       </c>
       <c r="B109" s="38" t="inlineStr">
@@ -44725,19 +45157,19 @@
         <v>104</v>
       </c>
       <c r="E109" s="38" t="n">
-        <v>1456.2</v>
+        <v>1470.1</v>
       </c>
       <c r="F109" s="38" t="n">
-        <v>122</v>
-      </c>
-      <c r="G109" s="45" t="n">
-        <v>18</v>
+        <v>109</v>
+      </c>
+      <c r="G109" s="38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="38" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="B110" s="38" t="inlineStr">
@@ -44746,30 +45178,30 @@
         </is>
       </c>
       <c r="C110" s="38" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="D110" s="38" t="n">
         <v>105</v>
       </c>
       <c r="E110" s="38" t="n">
-        <v>1444.8</v>
+        <v>1456.2</v>
       </c>
       <c r="F110" s="38" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G110" s="45" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="38" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="B111" s="38" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C111" s="38" t="n">
@@ -44779,24 +45211,24 @@
         <v>106</v>
       </c>
       <c r="E111" s="38" t="n">
-        <v>1464.9</v>
+        <v>1444.8</v>
       </c>
       <c r="F111" s="38" t="n">
-        <v>113</v>
-      </c>
-      <c r="G111" s="38" t="n">
-        <v>7</v>
+        <v>139</v>
+      </c>
+      <c r="G111" s="45" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="38" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="B112" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C112" s="38" t="n">
@@ -44806,24 +45238,24 @@
         <v>107</v>
       </c>
       <c r="E112" s="38" t="n">
-        <v>1445.5</v>
+        <v>1464.9</v>
       </c>
       <c r="F112" s="38" t="n">
-        <v>138</v>
-      </c>
-      <c r="G112" s="45" t="n">
-        <v>31</v>
+        <v>113</v>
+      </c>
+      <c r="G112" s="38" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="38" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="B113" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C113" s="38" t="n">
@@ -44833,24 +45265,24 @@
         <v>108</v>
       </c>
       <c r="E113" s="38" t="n">
-        <v>1447</v>
+        <v>1445.5</v>
       </c>
       <c r="F113" s="38" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G113" s="45" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="38" t="inlineStr">
         <is>
-          <t>Delaware State</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="B114" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C114" s="38" t="n">
@@ -44860,19 +45292,19 @@
         <v>109</v>
       </c>
       <c r="E114" s="38" t="n">
-        <v>1412.3</v>
+        <v>1447</v>
       </c>
       <c r="F114" s="38" t="n">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="G114" s="45" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="38" t="inlineStr">
         <is>
-          <t>Grambling</t>
+          <t>Delaware State</t>
         </is>
       </c>
       <c r="B115" s="38" t="inlineStr">
@@ -44881,25 +45313,25 @@
         </is>
       </c>
       <c r="C115" s="38" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="D115" s="38" t="n">
         <v>110</v>
       </c>
       <c r="E115" s="38" t="n">
-        <v>1429.6</v>
+        <v>1412.3</v>
       </c>
       <c r="F115" s="38" t="n">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="G115" s="45" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="38" t="inlineStr">
         <is>
-          <t>Bucknell</t>
+          <t>Grambling</t>
         </is>
       </c>
       <c r="B116" s="38" t="inlineStr">
@@ -44914,19 +45346,19 @@
         <v>111</v>
       </c>
       <c r="E116" s="38" t="n">
-        <v>1431.1</v>
+        <v>1429.6</v>
       </c>
       <c r="F116" s="38" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G116" s="45" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="38" t="inlineStr">
         <is>
-          <t>Northern Arizona</t>
+          <t>Bucknell</t>
         </is>
       </c>
       <c r="B117" s="38" t="inlineStr">
@@ -44941,19 +45373,19 @@
         <v>112</v>
       </c>
       <c r="E117" s="38" t="n">
-        <v>1447.5</v>
+        <v>1431.1</v>
       </c>
       <c r="F117" s="38" t="n">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="G117" s="45" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="38" t="inlineStr">
         <is>
-          <t>Arkansas-Pine Bluff</t>
+          <t>Northern Arizona</t>
         </is>
       </c>
       <c r="B118" s="38" t="inlineStr">
@@ -44968,19 +45400,19 @@
         <v>113</v>
       </c>
       <c r="E118" s="38" t="n">
-        <v>1422.7</v>
+        <v>1447.5</v>
       </c>
       <c r="F118" s="38" t="n">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G118" s="45" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="38" t="inlineStr">
         <is>
-          <t>Southeast Missouri State</t>
+          <t>Arkansas-Pine Bluff</t>
         </is>
       </c>
       <c r="B119" s="38" t="inlineStr">
@@ -44989,25 +45421,25 @@
         </is>
       </c>
       <c r="C119" s="38" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="D119" s="38" t="n">
         <v>114</v>
       </c>
       <c r="E119" s="38" t="n">
-        <v>1436.8</v>
+        <v>1422.7</v>
       </c>
       <c r="F119" s="38" t="n">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="G119" s="45" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="38" t="inlineStr">
         <is>
-          <t>Bryant</t>
+          <t>Southeast Missouri State</t>
         </is>
       </c>
       <c r="B120" s="38" t="inlineStr">
@@ -45016,30 +45448,30 @@
         </is>
       </c>
       <c r="C120" s="38" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="D120" s="38" t="n">
         <v>115</v>
       </c>
       <c r="E120" s="38" t="n">
-        <v>1434.1</v>
+        <v>1436.8</v>
       </c>
       <c r="F120" s="38" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G120" s="45" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="38" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Bryant</t>
         </is>
       </c>
       <c r="B121" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C121" s="38" t="n">
@@ -45049,24 +45481,24 @@
         <v>116</v>
       </c>
       <c r="E121" s="38" t="n">
-        <v>1489.6</v>
+        <v>1434.1</v>
       </c>
       <c r="F121" s="38" t="n">
-        <v>99</v>
-      </c>
-      <c r="G121" s="38" t="n">
-        <v>-17</v>
+        <v>156</v>
+      </c>
+      <c r="G121" s="45" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="38" t="inlineStr">
         <is>
-          <t>Southern Illinois</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B122" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C122" s="38" t="n">
@@ -45076,19 +45508,19 @@
         <v>117</v>
       </c>
       <c r="E122" s="38" t="n">
-        <v>1436.5</v>
+        <v>1489.6</v>
       </c>
       <c r="F122" s="38" t="n">
-        <v>152</v>
-      </c>
-      <c r="G122" s="45" t="n">
-        <v>35</v>
+        <v>99</v>
+      </c>
+      <c r="G122" s="38" t="n">
+        <v>-18</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="38" t="inlineStr">
         <is>
-          <t>Morgan State</t>
+          <t>Southern Illinois</t>
         </is>
       </c>
       <c r="B123" s="38" t="inlineStr">
@@ -45097,25 +45529,25 @@
         </is>
       </c>
       <c r="C123" s="38" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="D123" s="38" t="n">
         <v>118</v>
       </c>
       <c r="E123" s="38" t="n">
-        <v>1414.2</v>
+        <v>1436.5</v>
       </c>
       <c r="F123" s="38" t="n">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="G123" s="45" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="38" t="inlineStr">
         <is>
-          <t>Eastern Illinois</t>
+          <t>Morgan State</t>
         </is>
       </c>
       <c r="B124" s="38" t="inlineStr">
@@ -45130,19 +45562,19 @@
         <v>119</v>
       </c>
       <c r="E124" s="38" t="n">
-        <v>1418.5</v>
+        <v>1414.2</v>
       </c>
       <c r="F124" s="38" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G124" s="45" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="38" t="inlineStr">
         <is>
-          <t>Monmouth</t>
+          <t>Eastern Illinois</t>
         </is>
       </c>
       <c r="B125" s="38" t="inlineStr">
@@ -45151,30 +45583,30 @@
         </is>
       </c>
       <c r="C125" s="38" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="D125" s="38" t="n">
         <v>120</v>
       </c>
       <c r="E125" s="38" t="n">
-        <v>1438.9</v>
+        <v>1418.5</v>
       </c>
       <c r="F125" s="38" t="n">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="G125" s="45" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="38" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Monmouth</t>
         </is>
       </c>
       <c r="B126" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C126" s="38" t="n">
@@ -45184,24 +45616,24 @@
         <v>121</v>
       </c>
       <c r="E126" s="38" t="n">
-        <v>1644.9</v>
+        <v>1438.9</v>
       </c>
       <c r="F126" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="G126" s="45" t="n">
         <v>29</v>
-      </c>
-      <c r="G126" s="38" t="n">
-        <v>-92</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="38" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="B127" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C127" s="38" t="n">
@@ -45211,19 +45643,19 @@
         <v>122</v>
       </c>
       <c r="E127" s="38" t="n">
-        <v>1422.8</v>
+        <v>1644.9</v>
       </c>
       <c r="F127" s="38" t="n">
-        <v>175</v>
-      </c>
-      <c r="G127" s="45" t="n">
-        <v>53</v>
+        <v>29</v>
+      </c>
+      <c r="G127" s="38" t="n">
+        <v>-93</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="38" t="inlineStr">
         <is>
-          <t>UT Rio Grande Valley</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="B128" s="38" t="inlineStr">
@@ -45238,19 +45670,19 @@
         <v>123</v>
       </c>
       <c r="E128" s="38" t="n">
-        <v>1480.7</v>
+        <v>1422.8</v>
       </c>
       <c r="F128" s="38" t="n">
-        <v>104</v>
-      </c>
-      <c r="G128" s="38" t="n">
-        <v>-19</v>
+        <v>175</v>
+      </c>
+      <c r="G128" s="45" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="38" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>UT Rio Grande Valley</t>
         </is>
       </c>
       <c r="B129" s="38" t="inlineStr">
@@ -45265,24 +45697,24 @@
         <v>124</v>
       </c>
       <c r="E129" s="38" t="n">
-        <v>1451</v>
+        <v>1480.7</v>
       </c>
       <c r="F129" s="38" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="G129" s="38" t="n">
-        <v>3</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="38" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="B130" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C130" s="38" t="n">
@@ -45292,46 +45724,46 @@
         <v>125</v>
       </c>
       <c r="E130" s="38" t="n">
-        <v>1451.6</v>
+        <v>1451</v>
       </c>
       <c r="F130" s="38" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G130" s="38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="38" t="inlineStr">
         <is>
-          <t>North Carolina Central</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="B131" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C131" s="38" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="D131" s="38" t="n">
         <v>126</v>
       </c>
       <c r="E131" s="38" t="n">
-        <v>1429.2</v>
+        <v>1451.6</v>
       </c>
       <c r="F131" s="38" t="n">
-        <v>165</v>
-      </c>
-      <c r="G131" s="45" t="n">
-        <v>39</v>
+        <v>126</v>
+      </c>
+      <c r="G131" s="38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="38" t="inlineStr">
         <is>
-          <t>Incarnate Word</t>
+          <t>North Carolina Central</t>
         </is>
       </c>
       <c r="B132" s="38" t="inlineStr">
@@ -45340,25 +45772,25 @@
         </is>
       </c>
       <c r="C132" s="38" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="D132" s="38" t="n">
         <v>127</v>
       </c>
       <c r="E132" s="38" t="n">
-        <v>1441.2</v>
+        <v>1429.2</v>
       </c>
       <c r="F132" s="38" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G132" s="45" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="38" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Incarnate Word</t>
         </is>
       </c>
       <c r="B133" s="38" t="inlineStr">
@@ -45373,19 +45805,19 @@
         <v>128</v>
       </c>
       <c r="E133" s="38" t="n">
-        <v>1425.1</v>
+        <v>1441.2</v>
       </c>
       <c r="F133" s="38" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G133" s="45" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="38" t="inlineStr">
         <is>
-          <t>Lafayette</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B134" s="38" t="inlineStr">
@@ -45400,19 +45832,19 @@
         <v>129</v>
       </c>
       <c r="E134" s="38" t="n">
-        <v>1405.5</v>
+        <v>1425.1</v>
       </c>
       <c r="F134" s="38" t="n">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="G134" s="45" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="38" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Lafayette</t>
         </is>
       </c>
       <c r="B135" s="38" t="inlineStr">
@@ -45421,25 +45853,25 @@
         </is>
       </c>
       <c r="C135" s="38" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="D135" s="38" t="n">
         <v>130</v>
       </c>
       <c r="E135" s="38" t="n">
-        <v>1413.9</v>
+        <v>1405.5</v>
       </c>
       <c r="F135" s="38" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="G135" s="45" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="38" t="inlineStr">
         <is>
-          <t>Central Connecticut</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="B136" s="38" t="inlineStr">
@@ -45454,19 +45886,19 @@
         <v>131</v>
       </c>
       <c r="E136" s="38" t="n">
-        <v>1403.3</v>
+        <v>1413.9</v>
       </c>
       <c r="F136" s="38" t="n">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="G136" s="45" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="38" t="inlineStr">
         <is>
-          <t>Eastern Kentucky</t>
+          <t>Central Connecticut</t>
         </is>
       </c>
       <c r="B137" s="38" t="inlineStr">
@@ -45475,30 +45907,30 @@
         </is>
       </c>
       <c r="C137" s="38" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="D137" s="38" t="n">
         <v>132</v>
       </c>
       <c r="E137" s="38" t="n">
-        <v>1409.5</v>
+        <v>1403.3</v>
       </c>
       <c r="F137" s="38" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G137" s="45" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="38" t="inlineStr">
         <is>
-          <t>Bowling Green</t>
+          <t>Eastern Kentucky</t>
         </is>
       </c>
       <c r="B138" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C138" s="38" t="n">
@@ -45508,24 +45940,24 @@
         <v>133</v>
       </c>
       <c r="E138" s="38" t="n">
-        <v>1400.7</v>
+        <v>1409.5</v>
       </c>
       <c r="F138" s="38" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="G138" s="45" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="38" t="inlineStr">
         <is>
-          <t>Army</t>
+          <t>Bowling Green</t>
         </is>
       </c>
       <c r="B139" s="38" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C139" s="38" t="n">
@@ -45535,51 +45967,51 @@
         <v>134</v>
       </c>
       <c r="E139" s="38" t="n">
-        <v>1598</v>
+        <v>1400.7</v>
       </c>
       <c r="F139" s="38" t="n">
-        <v>53</v>
-      </c>
-      <c r="G139" s="38" t="n">
-        <v>-81</v>
+        <v>219</v>
+      </c>
+      <c r="G139" s="45" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="38" t="inlineStr">
         <is>
-          <t>Alabama State</t>
+          <t>Army</t>
         </is>
       </c>
       <c r="B140" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C140" s="38" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="D140" s="38" t="n">
         <v>135</v>
       </c>
       <c r="E140" s="38" t="n">
-        <v>1428.8</v>
+        <v>1598</v>
       </c>
       <c r="F140" s="38" t="n">
-        <v>166</v>
-      </c>
-      <c r="G140" s="45" t="n">
-        <v>31</v>
+        <v>53</v>
+      </c>
+      <c r="G140" s="38" t="n">
+        <v>-82</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="38" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Alabama State</t>
         </is>
       </c>
       <c r="B141" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C141" s="38" t="n">
@@ -45589,24 +46021,24 @@
         <v>136</v>
       </c>
       <c r="E141" s="38" t="n">
-        <v>1426.7</v>
+        <v>1428.8</v>
       </c>
       <c r="F141" s="38" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G141" s="45" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="38" t="inlineStr">
         <is>
-          <t>Western Carolina</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="B142" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C142" s="38" t="n">
@@ -45616,19 +46048,19 @@
         <v>137</v>
       </c>
       <c r="E142" s="38" t="n">
-        <v>1420.7</v>
+        <v>1426.7</v>
       </c>
       <c r="F142" s="38" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="G142" s="45" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="38" t="inlineStr">
         <is>
-          <t>Mercer</t>
+          <t>Western Carolina</t>
         </is>
       </c>
       <c r="B143" s="38" t="inlineStr">
@@ -45637,25 +46069,25 @@
         </is>
       </c>
       <c r="C143" s="38" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
       <c r="D143" s="38" t="n">
         <v>138</v>
       </c>
       <c r="E143" s="38" t="n">
-        <v>1430.9</v>
+        <v>1420.7</v>
       </c>
       <c r="F143" s="38" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G143" s="45" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="38" t="inlineStr">
         <is>
-          <t>South Dakota State</t>
+          <t>Mercer</t>
         </is>
       </c>
       <c r="B144" s="38" t="inlineStr">
@@ -45670,19 +46102,19 @@
         <v>139</v>
       </c>
       <c r="E144" s="38" t="n">
-        <v>1491.6</v>
+        <v>1430.9</v>
       </c>
       <c r="F144" s="38" t="n">
-        <v>97</v>
-      </c>
-      <c r="G144" s="38" t="n">
-        <v>-42</v>
+        <v>162</v>
+      </c>
+      <c r="G144" s="45" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="38" t="inlineStr">
         <is>
-          <t>Charleston Southern</t>
+          <t>South Dakota State</t>
         </is>
       </c>
       <c r="B145" s="38" t="inlineStr">
@@ -45691,25 +46123,25 @@
         </is>
       </c>
       <c r="C145" s="38" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="D145" s="38" t="n">
         <v>140</v>
       </c>
       <c r="E145" s="38" t="n">
-        <v>1411.7</v>
+        <v>1491.6</v>
       </c>
       <c r="F145" s="38" t="n">
-        <v>202</v>
-      </c>
-      <c r="G145" s="45" t="n">
-        <v>62</v>
+        <v>97</v>
+      </c>
+      <c r="G145" s="38" t="n">
+        <v>-43</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="38" t="inlineStr">
         <is>
-          <t>Northwestern State</t>
+          <t>Charleston Southern</t>
         </is>
       </c>
       <c r="B146" s="38" t="inlineStr">
@@ -45718,25 +46150,25 @@
         </is>
       </c>
       <c r="C146" s="38" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="D146" s="38" t="n">
         <v>141</v>
       </c>
       <c r="E146" s="38" t="n">
-        <v>1382.5</v>
+        <v>1411.7</v>
       </c>
       <c r="F146" s="38" t="n">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="G146" s="45" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="38" t="inlineStr">
         <is>
-          <t>Lamar</t>
+          <t>Northwestern State</t>
         </is>
       </c>
       <c r="B147" s="38" t="inlineStr">
@@ -45751,19 +46183,19 @@
         <v>142</v>
       </c>
       <c r="E147" s="38" t="n">
-        <v>1412.8</v>
+        <v>1382.5</v>
       </c>
       <c r="F147" s="38" t="n">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="G147" s="45" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="38" t="inlineStr">
         <is>
-          <t>Youngstown State</t>
+          <t>Lamar</t>
         </is>
       </c>
       <c r="B148" s="38" t="inlineStr">
@@ -45772,25 +46204,25 @@
         </is>
       </c>
       <c r="C148" s="38" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="D148" s="38" t="n">
         <v>143</v>
       </c>
       <c r="E148" s="38" t="n">
-        <v>1425.9</v>
+        <v>1412.8</v>
       </c>
       <c r="F148" s="38" t="n">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="G148" s="45" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="38" t="inlineStr">
         <is>
-          <t>Holy Cross</t>
+          <t>Youngstown State</t>
         </is>
       </c>
       <c r="B149" s="38" t="inlineStr">
@@ -45805,19 +46237,19 @@
         <v>144</v>
       </c>
       <c r="E149" s="38" t="n">
-        <v>1444.4</v>
+        <v>1425.9</v>
       </c>
       <c r="F149" s="38" t="n">
-        <v>141</v>
-      </c>
-      <c r="G149" s="38" t="n">
-        <v>-3</v>
+        <v>170</v>
+      </c>
+      <c r="G149" s="45" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="38" t="inlineStr">
         <is>
-          <t>Prairie View A&amp;M</t>
+          <t>Holy Cross</t>
         </is>
       </c>
       <c r="B150" s="38" t="inlineStr">
@@ -45826,57 +46258,57 @@
         </is>
       </c>
       <c r="C150" s="38" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="D150" s="38" t="n">
         <v>145</v>
       </c>
       <c r="E150" s="38" t="n">
-        <v>1414.9</v>
+        <v>1444.4</v>
       </c>
       <c r="F150" s="38" t="n">
-        <v>189</v>
-      </c>
-      <c r="G150" s="45" t="n">
-        <v>44</v>
+        <v>141</v>
+      </c>
+      <c r="G150" s="38" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="38" t="inlineStr">
         <is>
-          <t>Texas State</t>
+          <t>Prairie View A&amp;M</t>
         </is>
       </c>
       <c r="B151" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C151" s="38" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="D151" s="38" t="n">
         <v>146</v>
       </c>
       <c r="E151" s="38" t="n">
-        <v>1576.6</v>
+        <v>1414.9</v>
       </c>
       <c r="F151" s="38" t="n">
-        <v>62</v>
-      </c>
-      <c r="G151" s="38" t="n">
-        <v>-84</v>
+        <v>189</v>
+      </c>
+      <c r="G151" s="45" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="38" t="inlineStr">
         <is>
-          <t>Central Arkansas</t>
+          <t>Texas State</t>
         </is>
       </c>
       <c r="B152" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C152" s="38" t="n">
@@ -45886,51 +46318,51 @@
         <v>147</v>
       </c>
       <c r="E152" s="38" t="n">
-        <v>1433.8</v>
+        <v>1576.6</v>
       </c>
       <c r="F152" s="38" t="n">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="G152" s="38" t="n">
-        <v>10</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="38" t="inlineStr">
         <is>
-          <t>Florida International</t>
+          <t>Central Arkansas</t>
         </is>
       </c>
       <c r="B153" s="38" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C153" s="38" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="D153" s="38" t="n">
         <v>148</v>
       </c>
       <c r="E153" s="38" t="n">
-        <v>1488.5</v>
+        <v>1433.8</v>
       </c>
       <c r="F153" s="38" t="n">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="G153" s="38" t="n">
-        <v>-48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="38" t="inlineStr">
         <is>
-          <t>East Tennessee State</t>
+          <t>Florida International</t>
         </is>
       </c>
       <c r="B154" s="38" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C154" s="38" t="n">
@@ -45940,19 +46372,19 @@
         <v>149</v>
       </c>
       <c r="E154" s="38" t="n">
-        <v>1429.6</v>
+        <v>1488.5</v>
       </c>
       <c r="F154" s="38" t="n">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="G154" s="38" t="n">
-        <v>14</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="38" t="inlineStr">
         <is>
-          <t>Western Illinois</t>
+          <t>East Tennessee State</t>
         </is>
       </c>
       <c r="B155" s="38" t="inlineStr">
@@ -45967,19 +46399,19 @@
         <v>150</v>
       </c>
       <c r="E155" s="38" t="n">
-        <v>1387.5</v>
+        <v>1429.6</v>
       </c>
       <c r="F155" s="38" t="n">
-        <v>233</v>
-      </c>
-      <c r="G155" s="45" t="n">
-        <v>83</v>
+        <v>163</v>
+      </c>
+      <c r="G155" s="38" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="38" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>Western Illinois</t>
         </is>
       </c>
       <c r="B156" s="38" t="inlineStr">
@@ -45988,25 +46420,25 @@
         </is>
       </c>
       <c r="C156" s="38" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="D156" s="38" t="n">
         <v>151</v>
       </c>
       <c r="E156" s="38" t="n">
-        <v>1400.8</v>
+        <v>1387.5</v>
       </c>
       <c r="F156" s="38" t="n">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="G156" s="45" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="38" t="inlineStr">
         <is>
-          <t>Bethune-Cookman</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="B157" s="38" t="inlineStr">
@@ -46021,19 +46453,19 @@
         <v>152</v>
       </c>
       <c r="E157" s="38" t="n">
-        <v>1379</v>
+        <v>1400.8</v>
       </c>
       <c r="F157" s="38" t="n">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="G157" s="45" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="38" t="inlineStr">
         <is>
-          <t>North Alabama</t>
+          <t>Bethune-Cookman</t>
         </is>
       </c>
       <c r="B158" s="38" t="inlineStr">
@@ -46048,19 +46480,19 @@
         <v>153</v>
       </c>
       <c r="E158" s="38" t="n">
-        <v>1434.2</v>
+        <v>1379</v>
       </c>
       <c r="F158" s="38" t="n">
-        <v>155</v>
-      </c>
-      <c r="G158" s="38" t="n">
-        <v>2</v>
+        <v>239</v>
+      </c>
+      <c r="G158" s="45" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="38" t="inlineStr">
         <is>
-          <t>Weber State</t>
+          <t>North Alabama</t>
         </is>
       </c>
       <c r="B159" s="38" t="inlineStr">
@@ -46069,25 +46501,25 @@
         </is>
       </c>
       <c r="C159" s="38" t="n">
-        <v>-0.45</v>
+        <v>-0.43</v>
       </c>
       <c r="D159" s="38" t="n">
         <v>154</v>
       </c>
       <c r="E159" s="38" t="n">
-        <v>1433.7</v>
+        <v>1434.2</v>
       </c>
       <c r="F159" s="38" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G159" s="38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="38" t="inlineStr">
         <is>
-          <t>UAlbany</t>
+          <t>Weber State</t>
         </is>
       </c>
       <c r="B160" s="38" t="inlineStr">
@@ -46102,24 +46534,24 @@
         <v>155</v>
       </c>
       <c r="E160" s="38" t="n">
-        <v>1435.7</v>
+        <v>1433.7</v>
       </c>
       <c r="F160" s="38" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G160" s="38" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="38" t="inlineStr">
         <is>
-          <t>Arkansas State</t>
+          <t>UAlbany</t>
         </is>
       </c>
       <c r="B161" s="38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C161" s="38" t="n">
@@ -46129,24 +46561,24 @@
         <v>156</v>
       </c>
       <c r="E161" s="38" t="n">
-        <v>1500</v>
+        <v>1435.7</v>
       </c>
       <c r="F161" s="38" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="G161" s="38" t="n">
-        <v>-65</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="38" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Arkansas State</t>
         </is>
       </c>
       <c r="B162" s="38" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C162" s="38" t="n">
@@ -46156,13 +46588,13 @@
         <v>157</v>
       </c>
       <c r="E162" s="38" t="n">
-        <v>1520.2</v>
+        <v>1500</v>
       </c>
       <c r="F162" s="38" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G162" s="38" t="n">
-        <v>-77</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="163">
@@ -46213,10 +46645,10 @@
         <v>1402.8</v>
       </c>
       <c r="F164" s="38" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G164" s="45" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="165">
@@ -46294,10 +46726,10 @@
         <v>1391.8</v>
       </c>
       <c r="F167" s="38" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G167" s="45" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="168">
@@ -46402,10 +46834,10 @@
         <v>1404.2</v>
       </c>
       <c r="F171" s="38" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G171" s="45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="172">
@@ -46483,10 +46915,10 @@
         <v>1521.7</v>
       </c>
       <c r="F174" s="38" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G174" s="38" t="n">
-        <v>-91</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="175">
@@ -46591,10 +47023,10 @@
         <v>1393.9</v>
       </c>
       <c r="F178" s="38" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G178" s="45" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="179">
@@ -46753,10 +47185,10 @@
         <v>1395</v>
       </c>
       <c r="F184" s="38" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G184" s="45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185">
@@ -46834,10 +47266,10 @@
         <v>1397.7</v>
       </c>
       <c r="F187" s="38" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G187" s="45" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="188">
@@ -46942,10 +47374,10 @@
         <v>1398.4</v>
       </c>
       <c r="F191" s="38" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G191" s="45" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="192">
@@ -47239,10 +47671,10 @@
         <v>1392.6</v>
       </c>
       <c r="F202" s="38" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G202" s="45" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="203">
@@ -47536,10 +47968,10 @@
         <v>1530.9</v>
       </c>
       <c r="F213" s="38" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G213" s="38" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
     </row>
     <row r="214">
@@ -47617,10 +48049,10 @@
         <v>1402.2</v>
       </c>
       <c r="F216" s="38" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G216" s="38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
@@ -47644,10 +48076,10 @@
         <v>1399.2</v>
       </c>
       <c r="F217" s="38" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G217" s="38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218">
@@ -47761,7 +48193,7 @@
     <row r="222">
       <c r="A222" s="38" t="inlineStr">
         <is>
-          <t>Southern Miss</t>
+          <t>Sam Houston</t>
         </is>
       </c>
       <c r="B222" s="38" t="inlineStr">
@@ -47770,138 +48202,138 @@
         </is>
       </c>
       <c r="C222" s="38" t="n">
-        <v>-1.17</v>
+        <v>-1.23</v>
       </c>
       <c r="D222" s="38" t="n">
         <v>217</v>
       </c>
       <c r="E222" s="38" t="n">
-        <v>1406.7</v>
+        <v>1389.7</v>
       </c>
       <c r="F222" s="38" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="G222" s="38" t="n">
-        <v>-7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="38" t="inlineStr">
         <is>
-          <t>Sam Houston</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="B223" s="38" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="C223" s="38" t="n">
-        <v>-1.23</v>
+        <v>-1.27</v>
       </c>
       <c r="D223" s="38" t="n">
         <v>218</v>
       </c>
       <c r="E223" s="38" t="n">
-        <v>1389.7</v>
+        <v>1407.2</v>
       </c>
       <c r="F223" s="38" t="n">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="G223" s="38" t="n">
-        <v>12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="38" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Mercyhurst</t>
         </is>
       </c>
       <c r="B224" s="38" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C224" s="38" t="n">
-        <v>-1.27</v>
+        <v>-1.3</v>
       </c>
       <c r="D224" s="38" t="n">
         <v>219</v>
       </c>
       <c r="E224" s="38" t="n">
-        <v>1407.2</v>
+        <v>1414.7</v>
       </c>
       <c r="F224" s="38" t="n">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="G224" s="38" t="n">
-        <v>-12</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="38" t="inlineStr">
         <is>
-          <t>Mercyhurst</t>
+          <t>Washington State</t>
         </is>
       </c>
       <c r="B225" s="38" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="C225" s="38" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
       <c r="D225" s="38" t="n">
         <v>220</v>
       </c>
       <c r="E225" s="38" t="n">
-        <v>1414.7</v>
+        <v>1492.5</v>
       </c>
       <c r="F225" s="38" t="n">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="G225" s="38" t="n">
-        <v>-30</v>
+        <v>-125</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="38" t="inlineStr">
         <is>
-          <t>Washington State</t>
+          <t>Kennesaw State</t>
         </is>
       </c>
       <c r="B226" s="38" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C226" s="38" t="n">
-        <v>-1.32</v>
+        <v>-1.34</v>
       </c>
       <c r="D226" s="38" t="n">
         <v>221</v>
       </c>
       <c r="E226" s="38" t="n">
-        <v>1492.5</v>
+        <v>1480.8</v>
       </c>
       <c r="F226" s="38" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G226" s="38" t="n">
-        <v>-126</v>
+        <v>-118</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="38" t="inlineStr">
         <is>
-          <t>Kennesaw State</t>
+          <t>Western Kentucky</t>
         </is>
       </c>
       <c r="B227" s="38" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="C227" s="38" t="n">
@@ -47911,19 +48343,19 @@
         <v>222</v>
       </c>
       <c r="E227" s="38" t="n">
-        <v>1480.8</v>
+        <v>1485.6</v>
       </c>
       <c r="F227" s="38" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G227" s="38" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="38" t="inlineStr">
         <is>
-          <t>Western Kentucky</t>
+          <t>UTEP</t>
         </is>
       </c>
       <c r="B228" s="38" t="inlineStr">
@@ -47932,57 +48364,57 @@
         </is>
       </c>
       <c r="C228" s="38" t="n">
-        <v>-1.34</v>
+        <v>-1.41</v>
       </c>
       <c r="D228" s="38" t="n">
         <v>223</v>
       </c>
       <c r="E228" s="38" t="n">
-        <v>1485.6</v>
+        <v>1331.5</v>
       </c>
       <c r="F228" s="38" t="n">
-        <v>101</v>
-      </c>
-      <c r="G228" s="38" t="n">
-        <v>-122</v>
+        <v>250</v>
+      </c>
+      <c r="G228" s="45" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="38" t="inlineStr">
         <is>
-          <t>UTEP</t>
+          <t>Navy</t>
         </is>
       </c>
       <c r="B229" s="38" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C229" s="38" t="n">
-        <v>-1.41</v>
+        <v>-1.5</v>
       </c>
       <c r="D229" s="38" t="n">
         <v>224</v>
       </c>
       <c r="E229" s="38" t="n">
-        <v>1331.5</v>
+        <v>1581.9</v>
       </c>
       <c r="F229" s="38" t="n">
-        <v>250</v>
-      </c>
-      <c r="G229" s="45" t="n">
-        <v>26</v>
+        <v>59</v>
+      </c>
+      <c r="G229" s="38" t="n">
+        <v>-165</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="38" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B230" s="38" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="C230" s="38" t="n">
@@ -47992,67 +48424,67 @@
         <v>225</v>
       </c>
       <c r="E230" s="38" t="n">
-        <v>1581.9</v>
+        <v>1274.2</v>
       </c>
       <c r="F230" s="38" t="n">
-        <v>59</v>
-      </c>
-      <c r="G230" s="38" t="n">
-        <v>-166</v>
+        <v>252</v>
+      </c>
+      <c r="G230" s="45" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="38" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="B231" s="38" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="C231" s="38" t="n">
-        <v>-1.5</v>
+        <v>-1.53</v>
       </c>
       <c r="D231" s="38" t="n">
         <v>226</v>
       </c>
       <c r="E231" s="38" t="n">
-        <v>1274.2</v>
+        <v>1532.4</v>
       </c>
       <c r="F231" s="38" t="n">
-        <v>252</v>
-      </c>
-      <c r="G231" s="45" t="n">
-        <v>26</v>
+        <v>76</v>
+      </c>
+      <c r="G231" s="38" t="n">
+        <v>-150</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="38" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Southern Miss</t>
         </is>
       </c>
       <c r="B232" s="38" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="C232" s="38" t="n">
-        <v>-1.53</v>
+        <v>-1.55</v>
       </c>
       <c r="D232" s="38" t="n">
         <v>227</v>
       </c>
       <c r="E232" s="38" t="n">
-        <v>1532.4</v>
+        <v>1391.6</v>
       </c>
       <c r="F232" s="38" t="n">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="G232" s="38" t="n">
-        <v>-152</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -48157,10 +48589,10 @@
         <v>1404.9</v>
       </c>
       <c r="F236" s="38" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G236" s="38" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="237">
@@ -48336,26 +48768,26 @@
       </c>
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>207-178-5</t>
+          <t>207-179-5</t>
         </is>
       </c>
       <c r="C3" s="41" t="n">
-        <v>0.538</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="38" t="inlineStr">
         <is>
-          <t>Weekly ATS (Wk 5)</t>
+          <t>Weekly ATS (Wk 6)</t>
         </is>
       </c>
       <c r="B4" s="38" t="inlineStr">
         <is>
-          <t>28-30-1</t>
+          <t>0-1-0</t>
         </is>
       </c>
       <c r="C4" s="41" t="n">
-        <v>0.483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="26.45" customHeight="1">
@@ -51469,9 +51901,17 @@
       <c r="N60" s="38" t="n">
         <v>0.3</v>
       </c>
-      <c r="O60" s="38" t="n"/>
-      <c r="P60" s="38" t="n"/>
-      <c r="Q60" s="38" t="n"/>
+      <c r="O60" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="P60" s="38" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q60" s="43" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="38" t="n">

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1527,10 +1527,10 @@
         <v>-10.1</v>
       </c>
       <c r="H28" s="38" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="I28" s="43" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J28" s="38" t="n">
         <v>-6.4</v>
@@ -1542,10 +1542,10 @@
         <v>56.7</v>
       </c>
       <c r="M28" s="38" t="n">
-        <v>59.5</v>
+        <v>59.2</v>
       </c>
       <c r="N28" s="43" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="O28" s="38" t="n"/>
       <c r="P28" s="38" t="n"/>
@@ -1584,10 +1584,10 @@
         <v>4.5</v>
       </c>
       <c r="H29" s="38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29" s="43" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J29" s="38" t="n">
         <v>6.7</v>
@@ -1599,10 +1599,10 @@
         <v>47.2</v>
       </c>
       <c r="M29" s="38" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="N29" s="43" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="O29" s="38" t="n"/>
       <c r="P29" s="38" t="n"/>
@@ -1641,10 +1641,10 @@
         <v>8.4</v>
       </c>
       <c r="H30" s="38" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I30" s="38" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="J30" s="38" t="n">
         <v>7.6</v>
@@ -1656,10 +1656,10 @@
         <v>54.5</v>
       </c>
       <c r="M30" s="38" t="n">
-        <v>50</v>
+        <v>44.2</v>
       </c>
       <c r="N30" s="43" t="n">
-        <v>4.5</v>
+        <v>10.2</v>
       </c>
       <c r="O30" s="38" t="n"/>
       <c r="P30" s="38" t="n"/>
@@ -1713,10 +1713,10 @@
         <v>56.9</v>
       </c>
       <c r="M31" s="38" t="n">
-        <v>60</v>
+        <v>59.5</v>
       </c>
       <c r="N31" s="43" t="n">
-        <v>-3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="O31" s="38" t="n"/>
       <c r="P31" s="38" t="n"/>
@@ -1770,10 +1770,10 @@
         <v>49</v>
       </c>
       <c r="M32" s="38" t="n">
-        <v>47</v>
-      </c>
-      <c r="N32" s="43" t="n">
-        <v>2</v>
+        <v>47.2</v>
+      </c>
+      <c r="N32" s="38" t="n">
+        <v>1.8</v>
       </c>
       <c r="O32" s="38" t="n"/>
       <c r="P32" s="38" t="n"/>
@@ -1812,10 +1812,10 @@
         <v>-22.4</v>
       </c>
       <c r="H33" s="38" t="n">
-        <v>-9</v>
+        <v>-9.5</v>
       </c>
       <c r="I33" s="43" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="J33" s="38" t="n">
         <v>-4.2</v>
@@ -1827,10 +1827,10 @@
         <v>44.5</v>
       </c>
       <c r="M33" s="38" t="n">
-        <v>49.5</v>
+        <v>50.2</v>
       </c>
       <c r="N33" s="43" t="n">
-        <v>-5</v>
+        <v>-5.7</v>
       </c>
       <c r="O33" s="38" t="n"/>
       <c r="P33" s="38" t="n"/>
@@ -1869,10 +1869,10 @@
         <v>-34.6</v>
       </c>
       <c r="H34" s="38" t="n">
-        <v>-38</v>
+        <v>-38.2</v>
       </c>
       <c r="I34" s="43" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
       <c r="J34" s="38" t="n">
         <v>-38.8</v>
@@ -3144,10 +3144,10 @@
         <v>55.6</v>
       </c>
       <c r="M25" s="38" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="N25" s="43" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O25" s="38" t="n"/>
       <c r="P25" s="38" t="n"/>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="G26" s="38" t="n">
-        <v>-4.4</v>
+        <v>-4.5</v>
       </c>
       <c r="H26" s="38" t="n">
         <v>-3</v>
       </c>
       <c r="I26" s="38" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J26" s="38" t="n">
         <v>3.8</v>
@@ -3258,10 +3258,10 @@
         <v>47.1</v>
       </c>
       <c r="M27" s="38" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="N27" s="38" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="O27" s="38" t="n"/>
       <c r="P27" s="38" t="n"/>
@@ -3300,10 +3300,10 @@
         <v>-18.5</v>
       </c>
       <c r="H28" s="38" t="n">
-        <v>-14</v>
+        <v>-13.8</v>
       </c>
       <c r="I28" s="43" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J28" s="38" t="n">
         <v>-12.8</v>
@@ -3315,10 +3315,10 @@
         <v>56.8</v>
       </c>
       <c r="M28" s="38" t="n">
-        <v>57</v>
-      </c>
-      <c r="N28" s="38" t="n">
-        <v>-0.2</v>
+        <v>52.5</v>
+      </c>
+      <c r="N28" s="43" t="n">
+        <v>4.3</v>
       </c>
       <c r="O28" s="38" t="n"/>
       <c r="P28" s="38" t="n"/>
@@ -3372,10 +3372,10 @@
         <v>51.5</v>
       </c>
       <c r="M29" s="38" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="N29" s="43" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" s="38" t="n"/>
       <c r="P29" s="38" t="n"/>
@@ -3414,10 +3414,10 @@
         <v>-29.2</v>
       </c>
       <c r="H30" s="38" t="n">
-        <v>-27.5</v>
+        <v>-28.2</v>
       </c>
       <c r="I30" s="38" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J30" s="38" t="n">
         <v>-21</v>
@@ -3429,10 +3429,10 @@
         <v>56.5</v>
       </c>
       <c r="M30" s="38" t="n">
-        <v>58</v>
+        <v>57.8</v>
       </c>
       <c r="N30" s="38" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="O30" s="38" t="n"/>
       <c r="P30" s="38" t="n"/>
@@ -3471,10 +3471,10 @@
         <v>-8.9</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="I31" s="43" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J31" s="38" t="n">
         <v>-7.8</v>
@@ -4714,10 +4714,10 @@
         <v>-11.8</v>
       </c>
       <c r="H27" s="38" t="n">
-        <v>-12.2</v>
+        <v>-10</v>
       </c>
       <c r="I27" s="38" t="n">
-        <v>-0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J27" s="38" t="n">
         <v>-17.9</v>
@@ -4729,10 +4729,10 @@
         <v>50.5</v>
       </c>
       <c r="M27" s="38" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="N27" s="38" t="n">
-        <v>1.7</v>
+        <v>46.2</v>
+      </c>
+      <c r="N27" s="43" t="n">
+        <v>4.2</v>
       </c>
       <c r="O27" s="38" t="n"/>
       <c r="P27" s="38" t="n"/>
@@ -4786,10 +4786,10 @@
         <v>57.5</v>
       </c>
       <c r="M28" s="38" t="n">
-        <v>56</v>
-      </c>
-      <c r="N28" s="38" t="n">
-        <v>1.5</v>
+        <v>55.2</v>
+      </c>
+      <c r="N28" s="43" t="n">
+        <v>2.2</v>
       </c>
       <c r="O28" s="38" t="n"/>
       <c r="P28" s="38" t="n"/>
@@ -4828,10 +4828,10 @@
         <v>0.9</v>
       </c>
       <c r="H29" s="38" t="n">
-        <v>-9.5</v>
+        <v>-10.8</v>
       </c>
       <c r="I29" s="43" t="n">
-        <v>-10.4</v>
+        <v>-11.7</v>
       </c>
       <c r="J29" s="38" t="n">
         <v>1.5</v>
@@ -4843,10 +4843,10 @@
         <v>44.9</v>
       </c>
       <c r="M29" s="38" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="N29" s="43" t="n">
-        <v>-9.1</v>
+        <v>-8.6</v>
       </c>
       <c r="O29" s="38" t="n"/>
       <c r="P29" s="38" t="n"/>
@@ -4900,10 +4900,10 @@
         <v>54.1</v>
       </c>
       <c r="M30" s="38" t="n">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="N30" s="43" t="n">
-        <v>-6.9</v>
+        <v>-7.2</v>
       </c>
       <c r="O30" s="38" t="n"/>
       <c r="P30" s="38" t="n"/>
@@ -4942,10 +4942,10 @@
         <v>-16</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>-21</v>
+        <v>-20.8</v>
       </c>
       <c r="I31" s="43" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="J31" s="38" t="n">
         <v>-17.2</v>
@@ -4957,10 +4957,10 @@
         <v>47.9</v>
       </c>
       <c r="M31" s="38" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N31" s="43" t="n">
-        <v>-3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="O31" s="38" t="n"/>
       <c r="P31" s="38" t="n"/>
@@ -4999,10 +4999,10 @@
         <v>-18.3</v>
       </c>
       <c r="H32" s="38" t="n">
-        <v>-15.5</v>
+        <v>-15.8</v>
       </c>
       <c r="I32" s="43" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J32" s="38" t="n">
         <v>-20.3</v>
@@ -5014,10 +5014,10 @@
         <v>52.6</v>
       </c>
       <c r="M32" s="38" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="N32" s="38" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="O32" s="38" t="n"/>
       <c r="P32" s="38" t="n"/>
@@ -6236,10 +6236,10 @@
         <v>52.3</v>
       </c>
       <c r="M29" s="38" t="n">
-        <v>49.5</v>
+        <v>47.8</v>
       </c>
       <c r="N29" s="43" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O29" s="38" t="n"/>
       <c r="P29" s="38" t="n"/>
@@ -6278,10 +6278,10 @@
         <v>13.7</v>
       </c>
       <c r="H30" s="38" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I30" s="43" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="J30" s="38" t="n">
         <v>10.1</v>
@@ -6293,10 +6293,10 @@
         <v>54</v>
       </c>
       <c r="M30" s="38" t="n">
-        <v>51.2</v>
+        <v>48.8</v>
       </c>
       <c r="N30" s="43" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="O30" s="38" t="n"/>
       <c r="P30" s="38" t="n"/>
@@ -6335,10 +6335,10 @@
         <v>-36.7</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>-36</v>
+        <v>-36.8</v>
       </c>
       <c r="I31" s="38" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="J31" s="38" t="n">
         <v>-34.3</v>
@@ -6350,10 +6350,10 @@
         <v>53.2</v>
       </c>
       <c r="M31" s="38" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="N31" s="38" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="O31" s="38" t="n"/>
       <c r="P31" s="38" t="n"/>
@@ -6407,10 +6407,10 @@
         <v>47.7</v>
       </c>
       <c r="M32" s="38" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="N32" s="43" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="O32" s="38" t="n"/>
       <c r="P32" s="38" t="n"/>
@@ -6449,10 +6449,10 @@
         <v>-20.6</v>
       </c>
       <c r="H33" s="38" t="n">
-        <v>-12.2</v>
+        <v>-11.5</v>
       </c>
       <c r="I33" s="43" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="J33" s="38" t="n">
         <v>-20.4</v>
@@ -6464,10 +6464,10 @@
         <v>51.4</v>
       </c>
       <c r="M33" s="38" t="n">
-        <v>60.2</v>
+        <v>58.8</v>
       </c>
       <c r="N33" s="43" t="n">
-        <v>-8.9</v>
+        <v>-7.4</v>
       </c>
       <c r="O33" s="38" t="n"/>
       <c r="P33" s="38" t="n"/>
@@ -6506,10 +6506,10 @@
         <v>-3.7</v>
       </c>
       <c r="H34" s="38" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="I34" s="43" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="38" t="n">
         <v>6.3</v>
@@ -6521,10 +6521,10 @@
         <v>54.2</v>
       </c>
       <c r="M34" s="38" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N34" s="43" t="n">
-        <v>-2.1</v>
+        <v>54.8</v>
+      </c>
+      <c r="N34" s="38" t="n">
+        <v>-0.6</v>
       </c>
       <c r="O34" s="38" t="n"/>
       <c r="P34" s="38" t="n"/>
@@ -6563,10 +6563,10 @@
         <v>2</v>
       </c>
       <c r="H35" s="38" t="n">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="I35" s="43" t="n">
-        <v>-4.3</v>
+        <v>-5</v>
       </c>
       <c r="J35" s="38" t="n">
         <v>-1.1</v>
@@ -6635,10 +6635,10 @@
         <v>50.5</v>
       </c>
       <c r="M36" s="38" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="N36" s="38" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="O36" s="38" t="n"/>
       <c r="P36" s="38" t="n"/>
@@ -7723,10 +7723,10 @@
         <v>-7.5</v>
       </c>
       <c r="H21" s="38" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="I21" s="43" t="n">
-        <v>3</v>
+        <v>-7</v>
+      </c>
+      <c r="I21" s="38" t="n">
+        <v>0.5</v>
       </c>
       <c r="J21" s="38" t="n">
         <v>-6.3</v>
@@ -7738,10 +7738,10 @@
         <v>50.2</v>
       </c>
       <c r="M21" s="38" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="N21" s="43" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O21" s="38" t="n"/>
       <c r="P21" s="38" t="n"/>
@@ -7780,10 +7780,10 @@
         <v>1.5</v>
       </c>
       <c r="H22" s="38" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I22" s="38" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" s="38" t="n">
         <v>7.8</v>
@@ -7795,10 +7795,10 @@
         <v>54.2</v>
       </c>
       <c r="M22" s="38" t="n">
-        <v>49.8</v>
+        <v>48.8</v>
       </c>
       <c r="N22" s="43" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="O22" s="38" t="n"/>
       <c r="P22" s="38" t="n"/>
@@ -7837,10 +7837,10 @@
         <v>-17.3</v>
       </c>
       <c r="H23" s="38" t="n">
-        <v>-14</v>
+        <v>-13.5</v>
       </c>
       <c r="I23" s="43" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J23" s="38" t="n">
         <v>-14.8</v>
@@ -7894,10 +7894,10 @@
         <v>-4.4</v>
       </c>
       <c r="H24" s="38" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I24" s="38" t="n">
-        <v>1.9</v>
+        <v>-1.5</v>
+      </c>
+      <c r="I24" s="43" t="n">
+        <v>2.9</v>
       </c>
       <c r="J24" s="38" t="n">
         <v>-8.199999999999999</v>
@@ -8500,10 +8500,10 @@
         <v>-8.9</v>
       </c>
       <c r="H13" s="38" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="I13" s="43" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J13" s="38" t="n">
         <v>-7.8</v>
@@ -8557,10 +8557,10 @@
         <v>-34.6</v>
       </c>
       <c r="H14" s="38" t="n">
-        <v>-38</v>
+        <v>-38.2</v>
       </c>
       <c r="I14" s="43" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
       <c r="J14" s="38" t="n">
         <v>-38.8</v>
@@ -9344,10 +9344,10 @@
         <v>-36.7</v>
       </c>
       <c r="H24" s="38" t="n">
-        <v>-36</v>
+        <v>-36.8</v>
       </c>
       <c r="I24" s="38" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="J24" s="38" t="n">
         <v>-34.3</v>
@@ -9359,10 +9359,10 @@
         <v>53.2</v>
       </c>
       <c r="M24" s="38" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="N24" s="38" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="O24" s="38" t="n"/>
       <c r="P24" s="38" t="n"/>
@@ -9401,10 +9401,10 @@
         <v>-0.4</v>
       </c>
       <c r="H25" s="38" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I25" s="43" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J25" s="38" t="n">
         <v>3.6</v>
@@ -9416,10 +9416,10 @@
         <v>49.8</v>
       </c>
       <c r="M25" s="38" t="n">
-        <v>52</v>
-      </c>
-      <c r="N25" s="43" t="n">
-        <v>-2.2</v>
+        <v>51.5</v>
+      </c>
+      <c r="N25" s="38" t="n">
+        <v>-1.7</v>
       </c>
       <c r="O25" s="38" t="n"/>
       <c r="P25" s="38" t="n"/>
@@ -9473,10 +9473,10 @@
         <v>46.1</v>
       </c>
       <c r="M26" s="38" t="n">
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
       <c r="N26" s="38" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="38" t="n"/>
       <c r="P26" s="38" t="n"/>
@@ -9515,10 +9515,10 @@
         <v>14.5</v>
       </c>
       <c r="H27" s="38" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I27" s="43" t="n">
-        <v>-12.5</v>
+        <v>-12</v>
       </c>
       <c r="J27" s="38" t="n">
         <v>8.199999999999999</v>
@@ -9530,10 +9530,10 @@
         <v>52.6</v>
       </c>
       <c r="M27" s="38" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="N27" s="43" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="O27" s="38" t="n"/>
       <c r="P27" s="38" t="n"/>
@@ -9587,10 +9587,10 @@
         <v>51.1</v>
       </c>
       <c r="M28" s="38" t="n">
-        <v>47</v>
+        <v>46.2</v>
       </c>
       <c r="N28" s="43" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O28" s="38" t="n"/>
       <c r="P28" s="38" t="n"/>
@@ -9629,10 +9629,10 @@
         <v>-18.9</v>
       </c>
       <c r="H29" s="38" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I29" s="38" t="n">
-        <v>-1.1</v>
+        <v>-21</v>
+      </c>
+      <c r="I29" s="43" t="n">
+        <v>-2.1</v>
       </c>
       <c r="J29" s="38" t="n">
         <v>-14.1</v>
@@ -9644,10 +9644,10 @@
         <v>47.6</v>
       </c>
       <c r="M29" s="38" t="n">
-        <v>55</v>
+        <v>54.8</v>
       </c>
       <c r="N29" s="43" t="n">
-        <v>-7.4</v>
+        <v>-7.2</v>
       </c>
       <c r="O29" s="38" t="n"/>
       <c r="P29" s="38" t="n"/>
@@ -9686,10 +9686,10 @@
         <v>-20.7</v>
       </c>
       <c r="H30" s="38" t="n">
-        <v>-14</v>
+        <v>-13.8</v>
       </c>
       <c r="I30" s="43" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J30" s="38" t="n">
         <v>-18.8</v>
@@ -10665,10 +10665,10 @@
         <v>-16</v>
       </c>
       <c r="H21" s="38" t="n">
-        <v>-21</v>
+        <v>-20.8</v>
       </c>
       <c r="I21" s="43" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="J21" s="38" t="n">
         <v>-17.2</v>
@@ -10680,10 +10680,10 @@
         <v>47.9</v>
       </c>
       <c r="M21" s="38" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N21" s="43" t="n">
-        <v>-3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="O21" s="38" t="n"/>
       <c r="P21" s="38" t="n"/>
@@ -10737,10 +10737,10 @@
         <v>41.3</v>
       </c>
       <c r="M22" s="38" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="N22" s="43" t="n">
-        <v>-5.7</v>
+        <v>-5.5</v>
       </c>
       <c r="O22" s="38" t="n"/>
       <c r="P22" s="38" t="n"/>
@@ -10779,10 +10779,10 @@
         <v>-5.9</v>
       </c>
       <c r="H23" s="38" t="n">
-        <v>-6.5</v>
+        <v>-6</v>
       </c>
       <c r="I23" s="38" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="J23" s="38" t="n">
         <v>1.5</v>
@@ -10794,10 +10794,10 @@
         <v>45.6</v>
       </c>
       <c r="M23" s="38" t="n">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="N23" s="43" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O23" s="38" t="n"/>
       <c r="P23" s="38" t="n"/>
@@ -10851,10 +10851,10 @@
         <v>43.9</v>
       </c>
       <c r="M24" s="38" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="N24" s="43" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
       <c r="O24" s="38" t="n"/>
       <c r="P24" s="38" t="n"/>
@@ -11765,10 +11765,10 @@
         <v>-5.1</v>
       </c>
       <c r="H19" s="38" t="n">
-        <v>-14</v>
+        <v>-15.5</v>
       </c>
       <c r="I19" s="43" t="n">
-        <v>-8.9</v>
+        <v>-10.4</v>
       </c>
       <c r="J19" s="38" t="n">
         <v>-1.6</v>
@@ -11780,10 +11780,10 @@
         <v>47.8</v>
       </c>
       <c r="M19" s="38" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="N19" s="43" t="n">
-        <v>-7.2</v>
+        <v>-5.7</v>
       </c>
       <c r="O19" s="38" t="n"/>
       <c r="P19" s="38" t="n"/>
@@ -11822,10 +11822,10 @@
         <v>-3.2</v>
       </c>
       <c r="H20" s="38" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I20" s="38" t="n">
-        <v>-1.8</v>
+        <v>-5.5</v>
+      </c>
+      <c r="I20" s="43" t="n">
+        <v>-2.3</v>
       </c>
       <c r="J20" s="38" t="n">
         <v>-0.2</v>
@@ -11837,10 +11837,10 @@
         <v>40.4</v>
       </c>
       <c r="M20" s="38" t="n">
-        <v>42.5</v>
+        <v>44.2</v>
       </c>
       <c r="N20" s="43" t="n">
-        <v>-2.1</v>
+        <v>-3.9</v>
       </c>
       <c r="O20" s="38" t="n"/>
       <c r="P20" s="38" t="n"/>
@@ -11894,10 +11894,10 @@
         <v>48.3</v>
       </c>
       <c r="M21" s="38" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="N21" s="38" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O21" s="38" t="n"/>
       <c r="P21" s="38" t="n"/>
@@ -12862,10 +12862,10 @@
         <v>-0.6</v>
       </c>
       <c r="H27" s="38" t="n">
-        <v>0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I27" s="38" t="n">
-        <v>1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="J27" s="38" t="n">
         <v>2.6</v>
@@ -12877,10 +12877,10 @@
         <v>52.3</v>
       </c>
       <c r="M27" s="38" t="n">
-        <v>56</v>
-      </c>
-      <c r="N27" s="43" t="n">
-        <v>-3.7</v>
+        <v>51.5</v>
+      </c>
+      <c r="N27" s="38" t="n">
+        <v>0.8</v>
       </c>
       <c r="O27" s="38" t="n"/>
       <c r="P27" s="38" t="n"/>
@@ -12934,10 +12934,10 @@
         <v>52</v>
       </c>
       <c r="M28" s="38" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="N28" s="38" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="O28" s="38" t="n"/>
       <c r="P28" s="38" t="n"/>
@@ -12976,10 +12976,10 @@
         <v>0.3</v>
       </c>
       <c r="H29" s="38" t="n">
-        <v>-14</v>
+        <v>-11.2</v>
       </c>
       <c r="I29" s="43" t="n">
-        <v>-14.3</v>
+        <v>-11.5</v>
       </c>
       <c r="J29" s="38" t="n">
         <v>-9.199999999999999</v>
@@ -13033,10 +13033,10 @@
         <v>10.4</v>
       </c>
       <c r="H30" s="38" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I30" s="38" t="n">
-        <v>-0.7</v>
+        <v>-1.9</v>
       </c>
       <c r="J30" s="38" t="n">
         <v>6.8</v>
@@ -13048,10 +13048,10 @@
         <v>47.2</v>
       </c>
       <c r="M30" s="38" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="N30" s="43" t="n">
-        <v>-5.3</v>
+        <v>-4.6</v>
       </c>
       <c r="O30" s="38" t="n"/>
       <c r="P30" s="38" t="n"/>
@@ -13087,13 +13087,13 @@
         </is>
       </c>
       <c r="G31" s="38" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>-2.8</v>
+        <v>-3.5</v>
       </c>
       <c r="I31" s="43" t="n">
-        <v>-3.4</v>
+        <v>-4.2</v>
       </c>
       <c r="J31" s="38" t="n">
         <v>0.2</v>
@@ -13105,10 +13105,10 @@
         <v>46.4</v>
       </c>
       <c r="M31" s="38" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="N31" s="43" t="n">
-        <v>-3.1</v>
+        <v>-2.1</v>
       </c>
       <c r="O31" s="38" t="n"/>
       <c r="P31" s="38" t="n"/>
@@ -13147,10 +13147,10 @@
         <v>8.1</v>
       </c>
       <c r="H32" s="38" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I32" s="38" t="n">
-        <v>0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="J32" s="38" t="n">
         <v>16.9</v>
@@ -13162,10 +13162,10 @@
         <v>35.5</v>
       </c>
       <c r="M32" s="38" t="n">
-        <v>40.2</v>
+        <v>39.2</v>
       </c>
       <c r="N32" s="43" t="n">
-        <v>-4.7</v>
+        <v>-3.7</v>
       </c>
       <c r="O32" s="38" t="n"/>
       <c r="P32" s="38" t="n"/>
@@ -13219,10 +13219,10 @@
         <v>54.4</v>
       </c>
       <c r="M33" s="38" t="n">
-        <v>59</v>
-      </c>
-      <c r="N33" s="43" t="n">
-        <v>-4.6</v>
+        <v>56.2</v>
+      </c>
+      <c r="N33" s="38" t="n">
+        <v>-1.8</v>
       </c>
       <c r="O33" s="38" t="n"/>
       <c r="P33" s="38" t="n"/>
@@ -14435,13 +14435,13 @@
         </is>
       </c>
       <c r="G25" s="38" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="H25" s="38" t="n">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="I25" s="43" t="n">
-        <v>-3</v>
+        <v>-2.6</v>
       </c>
       <c r="J25" s="38" t="n">
         <v>-10.4</v>
@@ -14453,10 +14453,10 @@
         <v>49.5</v>
       </c>
       <c r="M25" s="38" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="N25" s="38" t="n">
-        <v>0.3</v>
+        <v>51.5</v>
+      </c>
+      <c r="N25" s="43" t="n">
+        <v>-2</v>
       </c>
       <c r="O25" s="38" t="n">
         <v>34</v>
@@ -14503,10 +14503,10 @@
         <v>-7.7</v>
       </c>
       <c r="H26" s="38" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I26" s="43" t="n">
-        <v>6.7</v>
+        <v>4.7</v>
       </c>
       <c r="J26" s="38" t="n">
         <v>-0.2</v>
@@ -14518,10 +14518,10 @@
         <v>60.5</v>
       </c>
       <c r="M26" s="38" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="N26" s="43" t="n">
-        <v>3</v>
+        <v>60.2</v>
+      </c>
+      <c r="N26" s="38" t="n">
+        <v>0.2</v>
       </c>
       <c r="O26" s="38" t="n"/>
       <c r="P26" s="38" t="n"/>
@@ -14560,10 +14560,10 @@
         <v>5.6</v>
       </c>
       <c r="H27" s="38" t="n">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="I27" s="43" t="n">
-        <v>-15.6</v>
+        <v>-15.1</v>
       </c>
       <c r="J27" s="38" t="n">
         <v>-8.6</v>
@@ -14575,10 +14575,10 @@
         <v>48.7</v>
       </c>
       <c r="M27" s="38" t="n">
-        <v>51</v>
-      </c>
-      <c r="N27" s="43" t="n">
-        <v>-2.3</v>
+        <v>49.5</v>
+      </c>
+      <c r="N27" s="38" t="n">
+        <v>-0.8</v>
       </c>
       <c r="O27" s="38" t="n"/>
       <c r="P27" s="38" t="n"/>
@@ -14632,10 +14632,10 @@
         <v>55.2</v>
       </c>
       <c r="M28" s="38" t="n">
-        <v>54</v>
-      </c>
-      <c r="N28" s="38" t="n">
-        <v>1.2</v>
+        <v>51.8</v>
+      </c>
+      <c r="N28" s="43" t="n">
+        <v>3.4</v>
       </c>
       <c r="O28" s="38" t="n"/>
       <c r="P28" s="38" t="n"/>
@@ -14689,10 +14689,10 @@
         <v>49.3</v>
       </c>
       <c r="M29" s="38" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="N29" s="38" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="O29" s="38" t="n"/>
       <c r="P29" s="38" t="n"/>
@@ -14730,8 +14730,12 @@
       <c r="G30" s="38" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H30" s="38" t="n"/>
-      <c r="I30" s="38" t="n"/>
+      <c r="H30" s="38" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I30" s="38" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J30" s="38" t="n">
         <v>-15.7</v>
       </c>
@@ -14741,8 +14745,12 @@
       <c r="L30" s="38" t="n">
         <v>60.7</v>
       </c>
-      <c r="M30" s="38" t="n"/>
-      <c r="N30" s="38" t="n"/>
+      <c r="M30" s="38" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="N30" s="43" t="n">
+        <v>2.2</v>
+      </c>
       <c r="O30" s="38" t="n"/>
       <c r="P30" s="38" t="n"/>
       <c r="Q30" s="38" t="n"/>
@@ -15365,46 +15373,46 @@
         </is>
       </c>
       <c r="B6" s="38" t="n">
-        <v>8823</v>
+        <v>8824</v>
       </c>
       <c r="C6" s="38" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>207</v>
       </c>
       <c r="E6" s="38" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="38" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="H6" s="38" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="I6" s="38" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>139/390 (36%)</t>
+          <t>141/391 (36%)</t>
         </is>
       </c>
       <c r="L6" s="38" t="inlineStr">
         <is>
-          <t>+1001.3</t>
+          <t>+998.6</t>
         </is>
       </c>
     </row>
@@ -15465,13 +15473,13 @@
         </is>
       </c>
       <c r="B8" s="38" t="n">
-        <v>8823</v>
+        <v>8824</v>
       </c>
       <c r="C8" s="38" t="n">
-        <v>8750</v>
+        <v>8751</v>
       </c>
       <c r="D8" s="38" t="n">
-        <v>4381</v>
+        <v>4382</v>
       </c>
       <c r="E8" s="38" t="n">
         <v>4369</v>
@@ -15499,12 +15507,12 @@
       </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>2687/8823 (30%)</t>
+          <t>2690/8824 (30%)</t>
         </is>
       </c>
       <c r="L8" s="38" t="inlineStr">
         <is>
-          <t>+5473.4</t>
+          <t>+5474.4</t>
         </is>
       </c>
     </row>
@@ -15549,7 +15557,7 @@
       </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>293/996 (29%)</t>
+          <t>296/996 (30%)</t>
         </is>
       </c>
       <c r="L9" s="38" t="inlineStr">
@@ -15565,46 +15573,46 @@
         </is>
       </c>
       <c r="B10" s="38" t="n">
-        <v>8823</v>
+        <v>8824</v>
       </c>
       <c r="C10" s="38" t="n">
-        <v>8750</v>
+        <v>8751</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>4377</v>
+        <v>4424</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>4373</v>
+        <v>4327</v>
       </c>
       <c r="F10" s="38" t="n">
         <v>73</v>
       </c>
       <c r="G10" s="38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="H10" s="38" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="I10" s="38" t="n">
-        <v>6860</v>
+        <v>6863</v>
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
-          <t>3143/8823 (36%)</t>
+          <t>3134/8824 (36%)</t>
         </is>
       </c>
       <c r="L10" s="38" t="inlineStr">
         <is>
-          <t>+125.2</t>
+          <t>+176.1</t>
         </is>
       </c>
     </row>
@@ -15621,30 +15629,30 @@
         <v>984</v>
       </c>
       <c r="D11" s="38" t="n">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="E11" s="38" t="n">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>12</v>
       </c>
       <c r="G11" s="38" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="H11" s="38" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="I11" s="38" t="n">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
@@ -15654,7 +15662,7 @@
       </c>
       <c r="L11" s="38" t="inlineStr">
         <is>
-          <t>+868.2</t>
+          <t>+905.8</t>
         </is>
       </c>
     </row>
@@ -15665,13 +15673,13 @@
         </is>
       </c>
       <c r="B12" s="38" t="n">
-        <v>8823</v>
+        <v>8824</v>
       </c>
       <c r="C12" s="38" t="n">
-        <v>7571</v>
+        <v>7572</v>
       </c>
       <c r="D12" s="38" t="n">
-        <v>3830</v>
+        <v>3831</v>
       </c>
       <c r="E12" s="38" t="n">
         <v>3741</v>
@@ -15699,7 +15707,7 @@
       </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
-          <t>2854/7634 (37%)</t>
+          <t>2859/7635 (37%)</t>
         </is>
       </c>
       <c r="L12" s="38" t="inlineStr">
@@ -15749,7 +15757,7 @@
       </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
-          <t>334/853 (39%)</t>
+          <t>331/853 (39%)</t>
         </is>
       </c>
       <c r="L13" s="38" t="inlineStr">
@@ -15834,46 +15842,46 @@
         </is>
       </c>
       <c r="B17" s="38" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C17" s="38" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D17" s="38" t="n">
         <v>207</v>
       </c>
       <c r="E17" s="38" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F17" s="38" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="38" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="H17" s="38" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="I17" s="38" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J17" s="38" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>139/390 (36%)</t>
+          <t>141/391 (36%)</t>
         </is>
       </c>
       <c r="L17" s="38" t="inlineStr">
         <is>
-          <t>+1001.3</t>
+          <t>+998.6</t>
         </is>
       </c>
     </row>
@@ -15934,13 +15942,13 @@
         </is>
       </c>
       <c r="B19" s="38" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C19" s="38" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D19" s="38" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E19" s="38" t="n">
         <v>199</v>
@@ -15950,12 +15958,12 @@
       </c>
       <c r="G19" s="38" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="H19" s="38" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="I19" s="38" t="n">
@@ -15968,12 +15976,12 @@
       </c>
       <c r="K19" s="38" t="inlineStr">
         <is>
-          <t>91/390 (23%)</t>
+          <t>91/391 (23%)</t>
         </is>
       </c>
       <c r="L19" s="38" t="inlineStr">
         <is>
-          <t>-621.6</t>
+          <t>-620.6</t>
         </is>
       </c>
     </row>
@@ -16034,46 +16042,46 @@
         </is>
       </c>
       <c r="B21" s="38" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C21" s="38" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D21" s="38" t="n">
         <v>186</v>
       </c>
       <c r="E21" s="38" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>5</v>
       </c>
       <c r="G21" s="38" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H21" s="38" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="I21" s="38" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J21" s="38" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>116/390 (30%)</t>
+          <t>113/391 (29%)</t>
         </is>
       </c>
       <c r="L21" s="38" t="inlineStr">
         <is>
-          <t>-613.2</t>
+          <t>-632.0</t>
         </is>
       </c>
     </row>
@@ -16090,40 +16098,40 @@
         <v>40</v>
       </c>
       <c r="D22" s="38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" s="38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F22" s="38" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="38" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H22" s="38" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="I22" s="38" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J22" s="38" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K22" s="38" t="inlineStr">
         <is>
-          <t>16/40 (40%)</t>
+          <t>17/40 (42%)</t>
         </is>
       </c>
       <c r="L22" s="38" t="inlineStr">
         <is>
-          <t>+19.5</t>
+          <t>+13.2</t>
         </is>
       </c>
     </row>
@@ -16134,13 +16142,13 @@
         </is>
       </c>
       <c r="B23" s="38" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C23" s="38" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D23" s="38" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E23" s="38" t="n">
         <v>153</v>
@@ -16150,12 +16158,12 @@
       </c>
       <c r="G23" s="38" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H23" s="38" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="I23" s="38" t="n">
@@ -16168,7 +16176,7 @@
       </c>
       <c r="K23" s="38" t="inlineStr">
         <is>
-          <t>44/291 (15%)</t>
+          <t>46/292 (16%)</t>
         </is>
       </c>
       <c r="L23" s="38" t="inlineStr">
@@ -16218,7 +16226,7 @@
       </c>
       <c r="K24" s="38" t="inlineStr">
         <is>
-          <t>7/27 (26%)</t>
+          <t>6/27 (22%)</t>
         </is>
       </c>
       <c r="L24" s="38" t="inlineStr">
@@ -16230,7 +16238,7 @@
     <row r="26">
       <c r="A26" s="40" t="inlineStr">
         <is>
-          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.1% of all graded games. Ridge agrees with the live model (Gamma) in 57.2% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 61.8% of games it has a rating for. Massey agrees with the live model (Gamma) in 49.5% of games it has a rating for.</t>
+          <t>Ridge and XGBoost (the two candidates) agree with each other in 77.4% of all graded games. Ridge agrees with the live model (Gamma) in 57.0% of games it has a rating for. XGBoost agrees with the live model (Gamma) in 62.9% of games it has a rating for. Massey agrees with the live model (Gamma) in 49.3% of games it has a rating for.</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16324,7 @@
       </c>
       <c r="C31" s="38" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="D31" s="38" t="inlineStr">
@@ -16326,14 +16334,14 @@
       </c>
       <c r="E31" s="38" t="inlineStr">
         <is>
+          <t>-9.4</t>
+        </is>
+      </c>
+      <c r="F31" s="38" t="inlineStr">
+        <is>
           <t>-6.9</t>
         </is>
       </c>
-      <c r="F31" s="38" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
       <c r="G31" s="38" t="inlineStr">
         <is>
           <t>Home (auto)</t>
@@ -16341,14 +16349,14 @@
       </c>
       <c r="H31" s="38" t="inlineStr">
         <is>
+          <t>Away (auto)</t>
+        </is>
+      </c>
+      <c r="I31" s="38" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I31" s="38" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
       <c r="J31" s="38" t="inlineStr">
         <is>
           <t>No</t>
@@ -16356,7 +16364,7 @@
       </c>
       <c r="K31" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16379,7 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>+2.8</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="D32" s="38" t="inlineStr">
@@ -16381,7 +16389,7 @@
       </c>
       <c r="E32" s="38" t="inlineStr">
         <is>
-          <t>+11.5</t>
+          <t>+10.1</t>
         </is>
       </c>
       <c r="F32" s="38" t="inlineStr">
@@ -16426,7 +16434,7 @@
       </c>
       <c r="C33" s="38" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="D33" s="38" t="inlineStr">
@@ -16436,7 +16444,7 @@
       </c>
       <c r="E33" s="38" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="F33" s="38" t="inlineStr">
@@ -16446,27 +16454,27 @@
       </c>
       <c r="G33" s="38" t="inlineStr">
         <is>
+          <t>Away (auto)</t>
+        </is>
+      </c>
+      <c r="H33" s="38" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I33" s="38" t="inlineStr">
+        <is>
           <t>Home (auto)</t>
         </is>
       </c>
-      <c r="H33" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I33" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
       <c r="J33" s="38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K33" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -16481,17 +16489,17 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-13.5</t>
         </is>
       </c>
       <c r="D34" s="38" t="inlineStr">
         <is>
-          <t>-14.8</t>
+          <t>-14.9</t>
         </is>
       </c>
       <c r="E34" s="38" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="F34" s="38" t="inlineStr">
@@ -16506,7 +16514,7 @@
       </c>
       <c r="H34" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="I34" s="38" t="inlineStr">
@@ -16536,7 +16544,7 @@
       </c>
       <c r="C35" s="38" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D35" s="38" t="inlineStr">
@@ -16546,7 +16554,7 @@
       </c>
       <c r="E35" s="38" t="inlineStr">
         <is>
-          <t>-8.7</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="F35" s="38" t="inlineStr">
@@ -16566,7 +16574,7 @@
       </c>
       <c r="I35" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J35" s="38" t="inlineStr">
@@ -16586,29 +16594,29 @@
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t>South Alabama @ Arkansas State</t>
+          <t>South Florida @ UTSA</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="D36" s="38" t="inlineStr">
         <is>
+          <t>-6.8</t>
+        </is>
+      </c>
+      <c r="E36" s="38" t="inlineStr">
+        <is>
+          <t>-7.1</t>
+        </is>
+      </c>
+      <c r="F36" s="38" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="E36" s="38" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="F36" s="38" t="inlineStr">
-        <is>
-          <t>-7.7</t>
-        </is>
-      </c>
       <c r="G36" s="38" t="inlineStr">
         <is>
           <t>Away (auto)</t>
@@ -16621,7 +16629,7 @@
       </c>
       <c r="I36" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J36" s="38" t="inlineStr">
@@ -16641,42 +16649,42 @@
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t>South Florida @ UTSA</t>
+          <t>South Alabama @ Arkansas State</t>
         </is>
       </c>
       <c r="C37" s="38" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D37" s="38" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="E37" s="38" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="F37" s="38" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-7.7</t>
         </is>
       </c>
       <c r="G37" s="38" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="H37" s="38" t="inlineStr">
+        <is>
           <t>Away (auto)</t>
         </is>
       </c>
-      <c r="H37" s="38" t="inlineStr">
-        <is>
-          <t>Away (auto)</t>
-        </is>
-      </c>
       <c r="I37" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J37" s="38" t="inlineStr">
@@ -16684,9 +16692,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K37" s="38" t="inlineStr">
-        <is>
-          <t>Tie</t>
+      <c r="K37" s="51" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -16701,7 +16709,7 @@
       </c>
       <c r="C38" s="38" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="D38" s="38" t="inlineStr">
@@ -16711,7 +16719,7 @@
       </c>
       <c r="E38" s="38" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="F38" s="38" t="inlineStr">
@@ -16756,7 +16764,7 @@
       </c>
       <c r="C39" s="38" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="D39" s="38" t="inlineStr">
@@ -16766,7 +16774,7 @@
       </c>
       <c r="E39" s="38" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="F39" s="38" t="inlineStr">
@@ -16786,7 +16794,7 @@
       </c>
       <c r="I39" s="38" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J39" s="38" t="inlineStr">
@@ -16806,44 +16814,44 @@
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t>Wyoming @ San José State</t>
+          <t>Iowa @ Washington</t>
         </is>
       </c>
       <c r="C40" s="38" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D40" s="38" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="E40" s="38" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="F40" s="38" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="G40" s="38" t="inlineStr">
         <is>
+          <t>Away (auto)</t>
+        </is>
+      </c>
+      <c r="H40" s="38" t="inlineStr">
+        <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="H40" s="38" t="inlineStr">
+      <c r="I40" s="38" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="I40" s="38" t="inlineStr">
-        <is>
-          <t>Away (auto)</t>
-        </is>
-      </c>
       <c r="J40" s="38" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16851,7 +16859,7 @@
       </c>
       <c r="K40" s="51" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -16861,44 +16869,44 @@
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t>Iowa @ Washington</t>
+          <t>Wyoming @ San José State</t>
         </is>
       </c>
       <c r="C41" s="38" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D41" s="38" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="E41" s="38" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="F41" s="38" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="G41" s="38" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="H41" s="38" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I41" s="38" t="inlineStr">
+        <is>
           <t>Away (auto)</t>
         </is>
       </c>
-      <c r="H41" s="38" t="inlineStr">
-        <is>
-          <t>Away (auto)</t>
-        </is>
-      </c>
-      <c r="I41" s="38" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
       <c r="J41" s="38" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16906,7 +16914,7 @@
       </c>
       <c r="K41" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -16921,7 +16929,7 @@
       </c>
       <c r="C42" s="38" t="inlineStr">
         <is>
-          <t>-12.2</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="D42" s="38" t="inlineStr">
@@ -16931,7 +16939,7 @@
       </c>
       <c r="E42" s="38" t="inlineStr">
         <is>
-          <t>-13.7</t>
+          <t>-13.6</t>
         </is>
       </c>
       <c r="F42" s="38" t="inlineStr">
@@ -16946,12 +16954,12 @@
       </c>
       <c r="H42" s="38" t="inlineStr">
         <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I42" s="38" t="inlineStr">
+        <is>
           <t>Home (auto)</t>
-        </is>
-      </c>
-      <c r="I42" s="38" t="inlineStr">
-        <is>
-          <t>Away (auto)</t>
         </is>
       </c>
       <c r="J42" s="38" t="inlineStr">
@@ -16971,27 +16979,27 @@
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t>Arizona @ West Virginia</t>
+          <t>Tulane @ Army</t>
         </is>
       </c>
       <c r="C43" s="38" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D43" s="38" t="inlineStr">
         <is>
-          <t>+10.5</t>
+          <t>+3.8</t>
         </is>
       </c>
       <c r="E43" s="38" t="inlineStr">
         <is>
-          <t>+6.4</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="F43" s="38" t="inlineStr">
         <is>
-          <t>+10.9</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="G43" s="38" t="inlineStr">
@@ -17001,17 +17009,17 @@
       </c>
       <c r="H43" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="I43" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J43" s="38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K43" s="51" t="inlineStr">
@@ -17026,47 +17034,47 @@
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t>Tulane @ Army</t>
+          <t>Wake Forest @ NC State</t>
         </is>
       </c>
       <c r="C44" s="38" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>+3.5</t>
         </is>
       </c>
       <c r="D44" s="38" t="inlineStr">
         <is>
+          <t>-5.7</t>
+        </is>
+      </c>
+      <c r="E44" s="38" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="F44" s="38" t="inlineStr">
+        <is>
           <t>+3.8</t>
         </is>
       </c>
-      <c r="E44" s="38" t="inlineStr">
-        <is>
-          <t>-4.9</t>
-        </is>
-      </c>
-      <c r="F44" s="38" t="inlineStr">
-        <is>
-          <t>-4.4</t>
-        </is>
-      </c>
       <c r="G44" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H44" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I44" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="J44" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K44" s="51" t="inlineStr">
@@ -17081,42 +17089,42 @@
       </c>
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t>UCF @ Oklahoma State</t>
+          <t>North Carolina @ Pittsburgh</t>
         </is>
       </c>
       <c r="C45" s="38" t="inlineStr">
         <is>
-          <t>-9.5</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D45" s="38" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-10.6</t>
         </is>
       </c>
       <c r="E45" s="38" t="inlineStr">
         <is>
-          <t>+2.4</t>
+          <t>-13.6</t>
         </is>
       </c>
       <c r="F45" s="38" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>-17.0</t>
         </is>
       </c>
       <c r="G45" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H45" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I45" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J45" s="38" t="inlineStr">
@@ -17126,7 +17134,7 @@
       </c>
       <c r="K45" s="51" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -17136,42 +17144,42 @@
       </c>
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t>North Carolina @ Pittsburgh</t>
+          <t>UCF @ Oklahoma State</t>
         </is>
       </c>
       <c r="C46" s="38" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-10.8</t>
         </is>
       </c>
       <c r="D46" s="38" t="inlineStr">
         <is>
-          <t>-10.6</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t>-13.1</t>
+          <t>+1.7</t>
         </is>
       </c>
       <c r="F46" s="38" t="inlineStr">
         <is>
-          <t>-17.0</t>
+          <t>+0.9</t>
         </is>
       </c>
       <c r="G46" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="H46" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I46" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J46" s="38" t="inlineStr">
@@ -17181,7 +17189,7 @@
       </c>
       <c r="K46" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -17191,27 +17199,27 @@
       </c>
       <c r="B47" s="38" t="inlineStr">
         <is>
-          <t>Indiana @ Nebraska</t>
+          <t>Arizona @ West Virginia</t>
         </is>
       </c>
       <c r="C47" s="38" t="inlineStr">
         <is>
-          <t>+8.0</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="D47" s="38" t="inlineStr">
         <is>
-          <t>+10.1</t>
+          <t>+10.5</t>
         </is>
       </c>
       <c r="E47" s="38" t="inlineStr">
         <is>
-          <t>+14.6</t>
+          <t>+5.7</t>
         </is>
       </c>
       <c r="F47" s="38" t="inlineStr">
         <is>
-          <t>+13.7</t>
+          <t>+10.9</t>
         </is>
       </c>
       <c r="G47" s="38" t="inlineStr">
@@ -17236,7 +17244,7 @@
       </c>
       <c r="K47" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -17246,52 +17254,52 @@
       </c>
       <c r="B48" s="38" t="inlineStr">
         <is>
-          <t>Wake Forest @ NC State</t>
+          <t>Sacramento State @ Bowling Green</t>
         </is>
       </c>
       <c r="C48" s="38" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="D48" s="38" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="E48" s="38" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-8.8</t>
         </is>
       </c>
       <c r="F48" s="38" t="inlineStr">
         <is>
-          <t>+3.8</t>
+          <t>-12.1</t>
         </is>
       </c>
       <c r="G48" s="38" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="H48" s="38" t="inlineStr">
+        <is>
+          <t>Home (auto)</t>
+        </is>
+      </c>
+      <c r="I48" s="38" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="H48" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="I48" s="38" t="inlineStr">
-        <is>
-          <t>Away (auto)</t>
-        </is>
-      </c>
       <c r="J48" s="38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K48" s="51" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -17301,27 +17309,27 @@
       </c>
       <c r="B49" s="38" t="inlineStr">
         <is>
-          <t>Sacramento State @ Bowling Green</t>
+          <t>Indiana @ Nebraska</t>
         </is>
       </c>
       <c r="C49" s="38" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>+7.5</t>
         </is>
       </c>
       <c r="D49" s="38" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>+10.1</t>
         </is>
       </c>
       <c r="E49" s="38" t="inlineStr">
         <is>
-          <t>-9.1</t>
+          <t>+14.8</t>
         </is>
       </c>
       <c r="F49" s="38" t="inlineStr">
         <is>
-          <t>-12.1</t>
+          <t>+13.7</t>
         </is>
       </c>
       <c r="G49" s="38" t="inlineStr">
@@ -17331,22 +17339,22 @@
       </c>
       <c r="H49" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I49" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J49" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K49" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17369,7 @@
       </c>
       <c r="C50" s="38" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="D50" s="38" t="inlineStr">
@@ -17371,12 +17379,12 @@
       </c>
       <c r="E50" s="38" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.9</t>
         </is>
       </c>
       <c r="F50" s="38" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>+0.7</t>
         </is>
       </c>
       <c r="G50" s="38" t="inlineStr">
@@ -17399,9 +17407,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K50" s="38" t="inlineStr">
-        <is>
-          <t>Tie</t>
+      <c r="K50" s="51" t="inlineStr">
+        <is>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17424,7 @@
       </c>
       <c r="C51" s="38" t="inlineStr">
         <is>
-          <t>-36.0</t>
+          <t>-36.8</t>
         </is>
       </c>
       <c r="D51" s="38" t="inlineStr">
@@ -17426,7 +17434,7 @@
       </c>
       <c r="E51" s="38" t="inlineStr">
         <is>
-          <t>-25.1</t>
+          <t>-24.4</t>
         </is>
       </c>
       <c r="F51" s="38" t="inlineStr">
@@ -17436,17 +17444,17 @@
       </c>
       <c r="G51" s="38" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="H51" s="38" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I51" s="38" t="inlineStr">
+        <is>
           <t>Away (auto)</t>
-        </is>
-      </c>
-      <c r="H51" s="38" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="I51" s="38" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J51" s="38" t="inlineStr">
@@ -17471,7 +17479,7 @@
       </c>
       <c r="C52" s="38" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-11.2</t>
         </is>
       </c>
       <c r="D52" s="38" t="inlineStr">
@@ -17481,7 +17489,7 @@
       </c>
       <c r="E52" s="38" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="F52" s="38" t="inlineStr">
@@ -17526,7 +17534,7 @@
       </c>
       <c r="C53" s="38" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="D53" s="38" t="inlineStr">
@@ -17536,7 +17544,7 @@
       </c>
       <c r="E53" s="38" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="F53" s="38" t="inlineStr">
@@ -17581,7 +17589,7 @@
       </c>
       <c r="C54" s="38" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="D54" s="38" t="inlineStr">
@@ -17631,27 +17639,27 @@
       </c>
       <c r="B55" s="38" t="inlineStr">
         <is>
-          <t>Eastern Michigan @ Akron</t>
+          <t>UCLA @ Oregon</t>
         </is>
       </c>
       <c r="C55" s="38" t="inlineStr">
         <is>
-          <t>+7.0</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="D55" s="38" t="inlineStr">
         <is>
-          <t>+3.6</t>
+          <t>-20.4</t>
         </is>
       </c>
       <c r="E55" s="38" t="inlineStr">
         <is>
-          <t>+4.9</t>
+          <t>-24.5</t>
         </is>
       </c>
       <c r="F55" s="38" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-20.6</t>
         </is>
       </c>
       <c r="G55" s="38" t="inlineStr">
@@ -17676,7 +17684,7 @@
       </c>
       <c r="K55" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -17686,27 +17694,27 @@
       </c>
       <c r="B56" s="38" t="inlineStr">
         <is>
-          <t>Virginia Tech @ California</t>
+          <t>Kent State @ Western Michigan</t>
         </is>
       </c>
       <c r="C56" s="38" t="inlineStr">
         <is>
-          <t>+9.0</t>
+          <t>-13.8</t>
         </is>
       </c>
       <c r="D56" s="38" t="inlineStr">
         <is>
-          <t>+6.7</t>
+          <t>-18.9</t>
         </is>
       </c>
       <c r="E56" s="38" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>-15.6</t>
         </is>
       </c>
       <c r="F56" s="38" t="inlineStr">
         <is>
-          <t>+4.5</t>
+          <t>-20.7</t>
         </is>
       </c>
       <c r="G56" s="38" t="inlineStr">
@@ -17716,14 +17724,14 @@
       </c>
       <c r="H56" s="38" t="inlineStr">
         <is>
+          <t>Home (auto)</t>
+        </is>
+      </c>
+      <c r="I56" s="38" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I56" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
       <c r="J56" s="38" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -17731,7 +17739,7 @@
       </c>
       <c r="K56" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17754,7 @@
       </c>
       <c r="C57" s="38" t="inlineStr">
         <is>
-          <t>+9.0</t>
+          <t>+7.5</t>
         </is>
       </c>
       <c r="D57" s="38" t="inlineStr">
@@ -17756,7 +17764,7 @@
       </c>
       <c r="E57" s="38" t="inlineStr">
         <is>
-          <t>+11.3</t>
+          <t>+11.1</t>
         </is>
       </c>
       <c r="F57" s="38" t="inlineStr">
@@ -17776,7 +17784,7 @@
       </c>
       <c r="I57" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="J57" s="38" t="inlineStr">
@@ -17811,7 +17819,7 @@
       </c>
       <c r="E58" s="38" t="inlineStr">
         <is>
-          <t>+8.4</t>
+          <t>+8.1</t>
         </is>
       </c>
       <c r="F58" s="38" t="inlineStr">
@@ -17866,7 +17874,7 @@
       </c>
       <c r="E59" s="38" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="F59" s="38" t="inlineStr">
@@ -17896,7 +17904,7 @@
       </c>
       <c r="K59" s="51" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -17921,7 +17929,7 @@
       </c>
       <c r="E60" s="38" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="F60" s="38" t="inlineStr">
@@ -18016,27 +18024,27 @@
       </c>
       <c r="B62" s="38" t="inlineStr">
         <is>
-          <t>Charlotte @ North Texas</t>
+          <t>Buffalo @ Toledo</t>
         </is>
       </c>
       <c r="C62" s="38" t="inlineStr">
         <is>
-          <t>-27.5</t>
+          <t>-21.0</t>
         </is>
       </c>
       <c r="D62" s="38" t="inlineStr">
         <is>
-          <t>-21.0</t>
+          <t>-14.1</t>
         </is>
       </c>
       <c r="E62" s="38" t="inlineStr">
         <is>
-          <t>-26.1</t>
+          <t>-13.8</t>
         </is>
       </c>
       <c r="F62" s="38" t="inlineStr">
         <is>
-          <t>-29.2</t>
+          <t>-18.9</t>
         </is>
       </c>
       <c r="G62" s="38" t="inlineStr">
@@ -18046,12 +18054,12 @@
       </c>
       <c r="H62" s="38" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I62" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J62" s="38" t="inlineStr">
@@ -18061,7 +18069,7 @@
       </c>
       <c r="K62" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -18071,42 +18079,42 @@
       </c>
       <c r="B63" s="38" t="inlineStr">
         <is>
-          <t>UCLA @ Oregon</t>
+          <t>Charlotte @ North Texas</t>
         </is>
       </c>
       <c r="C63" s="38" t="inlineStr">
         <is>
-          <t>-12.2</t>
+          <t>-28.2</t>
         </is>
       </c>
       <c r="D63" s="38" t="inlineStr">
         <is>
-          <t>-20.4</t>
+          <t>-21.0</t>
         </is>
       </c>
       <c r="E63" s="38" t="inlineStr">
         <is>
-          <t>-24.0</t>
+          <t>-26.0</t>
         </is>
       </c>
       <c r="F63" s="38" t="inlineStr">
         <is>
-          <t>-20.6</t>
+          <t>-29.2</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="H63" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I63" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J63" s="38" t="inlineStr">
@@ -18116,7 +18124,7 @@
       </c>
       <c r="K63" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -18126,42 +18134,42 @@
       </c>
       <c r="B64" s="38" t="inlineStr">
         <is>
-          <t>Buffalo @ Toledo</t>
+          <t>Virginia Tech @ California</t>
         </is>
       </c>
       <c r="C64" s="38" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>+10.0</t>
         </is>
       </c>
       <c r="D64" s="38" t="inlineStr">
         <is>
-          <t>-14.1</t>
+          <t>+6.7</t>
         </is>
       </c>
       <c r="E64" s="38" t="inlineStr">
         <is>
-          <t>-13.9</t>
+          <t>+3.8</t>
         </is>
       </c>
       <c r="F64" s="38" t="inlineStr">
         <is>
-          <t>-18.9</t>
+          <t>+4.5</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H64" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I64" s="38" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J64" s="38" t="inlineStr">
@@ -18171,7 +18179,7 @@
       </c>
       <c r="K64" s="51" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -18181,52 +18189,52 @@
       </c>
       <c r="B65" s="38" t="inlineStr">
         <is>
-          <t>Duke @ Georgia Tech</t>
+          <t>Eastern Michigan @ Akron</t>
         </is>
       </c>
       <c r="C65" s="38" t="inlineStr">
         <is>
-          <t>+7.0</t>
+          <t>+6.8</t>
         </is>
       </c>
       <c r="D65" s="38" t="inlineStr">
         <is>
-          <t>+7.6</t>
+          <t>+3.6</t>
         </is>
       </c>
       <c r="E65" s="38" t="inlineStr">
         <is>
-          <t>+5.8</t>
+          <t>+4.6</t>
         </is>
       </c>
       <c r="F65" s="38" t="inlineStr">
         <is>
-          <t>+8.4</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="H65" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I65" s="38" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J65" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K65" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -18251,7 +18259,7 @@
       </c>
       <c r="E66" s="38" t="inlineStr">
         <is>
-          <t>+7.5</t>
+          <t>+7.3</t>
         </is>
       </c>
       <c r="F66" s="38" t="inlineStr">
@@ -18291,52 +18299,52 @@
       </c>
       <c r="B67" s="38" t="inlineStr">
         <is>
-          <t>Stanford @ Notre Dame</t>
+          <t>Duke @ Georgia Tech</t>
         </is>
       </c>
       <c r="C67" s="38" t="inlineStr">
         <is>
-          <t>-38.0</t>
+          <t>+6.5</t>
         </is>
       </c>
       <c r="D67" s="38" t="inlineStr">
         <is>
-          <t>-38.8</t>
+          <t>+7.7</t>
         </is>
       </c>
       <c r="E67" s="38" t="inlineStr">
         <is>
-          <t>-38.0</t>
+          <t>+4.5</t>
         </is>
       </c>
       <c r="F67" s="38" t="inlineStr">
         <is>
-          <t>-34.6</t>
+          <t>+8.4</t>
         </is>
       </c>
       <c r="G67" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="H67" s="38" t="inlineStr">
         <is>
-          <t>Pick'em</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I67" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="J67" s="38" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K67" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
@@ -18346,47 +18354,47 @@
       </c>
       <c r="B68" s="38" t="inlineStr">
         <is>
-          <t>Kent State @ Western Michigan</t>
+          <t>Stanford @ Notre Dame</t>
         </is>
       </c>
       <c r="C68" s="38" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-38.2</t>
         </is>
       </c>
       <c r="D68" s="38" t="inlineStr">
         <is>
-          <t>-18.8</t>
+          <t>-38.8</t>
         </is>
       </c>
       <c r="E68" s="38" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>-37.9</t>
         </is>
       </c>
       <c r="F68" s="38" t="inlineStr">
         <is>
-          <t>-20.7</t>
+          <t>-34.6</t>
         </is>
       </c>
       <c r="G68" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="H68" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="I68" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J68" s="38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K68" s="51" t="inlineStr">
@@ -18406,7 +18414,7 @@
       </c>
       <c r="C69" s="38" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="D69" s="38" t="inlineStr">
@@ -18416,7 +18424,7 @@
       </c>
       <c r="E69" s="38" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="F69" s="38" t="inlineStr">
@@ -18471,7 +18479,7 @@
       </c>
       <c r="E70" s="38" t="inlineStr">
         <is>
-          <t>-12.5</t>
+          <t>-11.8</t>
         </is>
       </c>
       <c r="F70" s="38" t="inlineStr">
@@ -18486,7 +18494,7 @@
       </c>
       <c r="H70" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="I70" s="38" t="inlineStr">
@@ -18526,7 +18534,7 @@
       </c>
       <c r="E71" s="38" t="inlineStr">
         <is>
-          <t>+12.9</t>
+          <t>+13.8</t>
         </is>
       </c>
       <c r="F71" s="38" t="inlineStr">
@@ -18541,17 +18549,17 @@
       </c>
       <c r="H71" s="38" t="inlineStr">
         <is>
+          <t>Away (auto)</t>
+        </is>
+      </c>
+      <c r="I71" s="38" t="inlineStr">
+        <is>
           <t>Home (auto)</t>
         </is>
       </c>
-      <c r="I71" s="38" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
-        </is>
-      </c>
       <c r="J71" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K71" s="51" t="inlineStr">
@@ -18581,7 +18589,7 @@
       </c>
       <c r="E72" s="38" t="inlineStr">
         <is>
-          <t>-29.8</t>
+          <t>-29.9</t>
         </is>
       </c>
       <c r="F72" s="38" t="inlineStr">
@@ -18626,7 +18634,7 @@
       </c>
       <c r="C73" s="38" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-15.5</t>
         </is>
       </c>
       <c r="D73" s="38" t="inlineStr">
@@ -18636,7 +18644,7 @@
       </c>
       <c r="E73" s="38" t="inlineStr">
         <is>
-          <t>+2.6</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="F73" s="38" t="inlineStr">
@@ -18676,42 +18684,42 @@
       </c>
       <c r="B74" s="38" t="inlineStr">
         <is>
-          <t>North Dakota State @ UNLV</t>
+          <t>LSU @ Kentucky</t>
         </is>
       </c>
       <c r="C74" s="38" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>+8.5</t>
         </is>
       </c>
       <c r="D74" s="38" t="inlineStr">
         <is>
-          <t>+8.1</t>
+          <t>+6.8</t>
         </is>
       </c>
       <c r="E74" s="38" t="inlineStr">
         <is>
-          <t>+4.5</t>
+          <t>+7.2</t>
         </is>
       </c>
       <c r="F74" s="38" t="inlineStr">
         <is>
-          <t>+10.3</t>
+          <t>+10.4</t>
         </is>
       </c>
       <c r="G74" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="H74" s="38" t="inlineStr">
         <is>
+          <t>Home (auto)</t>
+        </is>
+      </c>
+      <c r="I74" s="38" t="inlineStr">
+        <is>
           <t>Away (auto)</t>
-        </is>
-      </c>
-      <c r="I74" s="38" t="inlineStr">
-        <is>
-          <t>Away</t>
         </is>
       </c>
       <c r="J74" s="38" t="inlineStr">
@@ -18731,52 +18739,52 @@
       </c>
       <c r="B75" s="38" t="inlineStr">
         <is>
-          <t>Coastal Carolina @ Marshall</t>
+          <t>North Dakota State @ UNLV</t>
         </is>
       </c>
       <c r="C75" s="38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="D75" s="38" t="inlineStr">
         <is>
-          <t>-15.7</t>
+          <t>+8.1</t>
         </is>
       </c>
       <c r="E75" s="38" t="inlineStr">
         <is>
-          <t>-13.5</t>
+          <t>+4.1</t>
         </is>
       </c>
       <c r="F75" s="38" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>+10.3</t>
         </is>
       </c>
       <c r="G75" s="38" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="H75" s="38" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away (auto)</t>
         </is>
       </c>
       <c r="I75" s="38" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="J75" s="38" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K75" s="38" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K75" s="51" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -18786,27 +18794,27 @@
       </c>
       <c r="B76" s="38" t="inlineStr">
         <is>
-          <t>LSU @ Kentucky</t>
+          <t>Nevada @ UTEP</t>
         </is>
       </c>
       <c r="C76" s="38" t="inlineStr">
         <is>
-          <t>+9.8</t>
+          <t>+9.5</t>
         </is>
       </c>
       <c r="D76" s="38" t="inlineStr">
         <is>
-          <t>+6.8</t>
+          <t>+5.0</t>
         </is>
       </c>
       <c r="E76" s="38" t="inlineStr">
         <is>
-          <t>+7.3</t>
+          <t>+6.0</t>
         </is>
       </c>
       <c r="F76" s="38" t="inlineStr">
         <is>
-          <t>+10.4</t>
+          <t>+8.5</t>
         </is>
       </c>
       <c r="G76" s="38" t="inlineStr">
@@ -18821,7 +18829,7 @@
       </c>
       <c r="I76" s="38" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J76" s="38" t="inlineStr">
@@ -18846,7 +18854,7 @@
       </c>
       <c r="C77" s="38" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-13.8</t>
         </is>
       </c>
       <c r="D77" s="38" t="inlineStr">
@@ -18856,7 +18864,7 @@
       </c>
       <c r="E77" s="38" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="F77" s="38" t="inlineStr">
@@ -18896,27 +18904,27 @@
       </c>
       <c r="B78" s="38" t="inlineStr">
         <is>
-          <t>Nevada @ UTEP</t>
+          <t>Coastal Carolina @ Marshall</t>
         </is>
       </c>
       <c r="C78" s="38" t="inlineStr">
         <is>
-          <t>+9.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D78" s="38" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>-15.7</t>
         </is>
       </c>
       <c r="E78" s="38" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="F78" s="38" t="inlineStr">
         <is>
-          <t>+8.5</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="G78" s="38" t="inlineStr">
@@ -18966,7 +18974,7 @@
       </c>
       <c r="E79" s="38" t="inlineStr">
         <is>
-          <t>+2.7</t>
+          <t>+4.0</t>
         </is>
       </c>
       <c r="F79" s="38" t="inlineStr">
@@ -19021,7 +19029,7 @@
       </c>
       <c r="E80" s="38" t="inlineStr">
         <is>
-          <t>+17.0</t>
+          <t>+17.1</t>
         </is>
       </c>
       <c r="F80" s="38" t="inlineStr">
@@ -19061,27 +19069,27 @@
       </c>
       <c r="B81" s="38" t="inlineStr">
         <is>
-          <t>Louisiana @ Louisiana Tech</t>
+          <t>Syracuse @ Virginia</t>
         </is>
       </c>
       <c r="C81" s="38" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="D81" s="38" t="inlineStr">
         <is>
-          <t>+4.3</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="E81" s="38" t="inlineStr">
         <is>
-          <t>+4.8</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="F81" s="38" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>-22.4</t>
         </is>
       </c>
       <c r="G81" s="38" t="inlineStr">
@@ -19096,7 +19104,7 @@
       </c>
       <c r="I81" s="38" t="inlineStr">
         <is>
-          <t>Home (auto)</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="J81" s="38" t="inlineStr">
@@ -19106,7 +19114,7 @@
       </c>
       <c r="K81" s="51" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>XGBoost</t>
         </is>
       </c>
     </row>
@@ -19121,7 +19129,7 @@
       </c>
       <c r="C82" s="38" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D82" s="38" t="inlineStr">
@@ -19131,7 +19139,7 @@
       </c>
       <c r="E82" s="38" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+1.6</t>
         </is>
       </c>
       <c r="F82" s="38" t="inlineStr">
@@ -19146,14 +19154,14 @@
       </c>
       <c r="H82" s="38" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I82" s="38" t="inlineStr">
+        <is>
           <t>Away (auto)</t>
         </is>
       </c>
-      <c r="I82" s="38" t="inlineStr">
-        <is>
-          <t>Home (auto)</t>
-        </is>
-      </c>
       <c r="J82" s="38" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -19161,7 +19169,7 @@
       </c>
       <c r="K82" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -19171,27 +19179,27 @@
       </c>
       <c r="B83" s="38" t="inlineStr">
         <is>
-          <t>Syracuse @ Virginia</t>
+          <t>Louisiana @ Louisiana Tech</t>
         </is>
       </c>
       <c r="C83" s="38" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="D83" s="38" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>+4.3</t>
         </is>
       </c>
       <c r="E83" s="38" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>+5.1</t>
         </is>
       </c>
       <c r="F83" s="38" t="inlineStr">
         <is>
-          <t>-22.4</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="G83" s="38" t="inlineStr">
@@ -19206,7 +19214,7 @@
       </c>
       <c r="I83" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Home (auto)</t>
         </is>
       </c>
       <c r="J83" s="38" t="inlineStr">
@@ -19214,9 +19222,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K83" s="38" t="inlineStr">
-        <is>
-          <t>Tie</t>
+      <c r="K83" s="51" t="inlineStr">
+        <is>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -19231,7 +19239,7 @@
       </c>
       <c r="C84" s="38" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D84" s="38" t="inlineStr">
@@ -19241,7 +19249,7 @@
       </c>
       <c r="E84" s="38" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="F84" s="38" t="inlineStr">
@@ -19256,7 +19264,7 @@
       </c>
       <c r="H84" s="38" t="inlineStr">
         <is>
-          <t>Away (auto)</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="I84" s="38" t="inlineStr">
@@ -19271,7 +19279,7 @@
       </c>
       <c r="K84" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Gamma</t>
         </is>
       </c>
     </row>
@@ -19291,12 +19299,12 @@
       </c>
       <c r="D85" s="38" t="inlineStr">
         <is>
-          <t>+11.3</t>
+          <t>+11.4</t>
         </is>
       </c>
       <c r="E85" s="38" t="inlineStr">
         <is>
-          <t>+10.2</t>
+          <t>+10.4</t>
         </is>
       </c>
       <c r="F85" s="38" t="inlineStr">
@@ -19341,7 +19349,7 @@
       </c>
       <c r="C86" s="38" t="inlineStr">
         <is>
-          <t>-21.0</t>
+          <t>-20.8</t>
         </is>
       </c>
       <c r="D86" s="38" t="inlineStr">
@@ -19351,7 +19359,7 @@
       </c>
       <c r="E86" s="38" t="inlineStr">
         <is>
-          <t>-15.4</t>
+          <t>-14.7</t>
         </is>
       </c>
       <c r="F86" s="38" t="inlineStr">
@@ -19396,7 +19404,7 @@
       </c>
       <c r="C87" s="38" t="inlineStr">
         <is>
-          <t>-15.5</t>
+          <t>-15.8</t>
         </is>
       </c>
       <c r="D87" s="38" t="inlineStr">
@@ -19406,7 +19414,7 @@
       </c>
       <c r="E87" s="38" t="inlineStr">
         <is>
-          <t>-19.6</t>
+          <t>-19.5</t>
         </is>
       </c>
       <c r="F87" s="38" t="inlineStr">
@@ -19461,7 +19469,7 @@
       </c>
       <c r="E88" s="38" t="inlineStr">
         <is>
-          <t>+2.6</t>
+          <t>+2.7</t>
         </is>
       </c>
       <c r="F88" s="38" t="inlineStr">
@@ -19697,12 +19705,12 @@
       </c>
       <c r="J94" s="38" t="inlineStr">
         <is>
-          <t>-28.0</t>
+          <t>-28.2</t>
         </is>
       </c>
       <c r="K94" s="38" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="L94" s="38" t="inlineStr">
@@ -19777,7 +19785,7 @@
       </c>
       <c r="Z94" s="38" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AA94" s="38" t="inlineStr">
@@ -19837,12 +19845,12 @@
       </c>
       <c r="J95" s="38" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="K95" s="38" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="L95" s="38" t="inlineStr">
@@ -19917,7 +19925,7 @@
       </c>
       <c r="Z95" s="38" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AA95" s="38" t="inlineStr">
@@ -19977,12 +19985,12 @@
       </c>
       <c r="J96" s="38" t="inlineStr">
         <is>
-          <t>-10.6</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="K96" s="38" t="inlineStr">
         <is>
-          <t>+9.1</t>
+          <t>+9.4</t>
         </is>
       </c>
       <c r="L96" s="38" t="inlineStr">
@@ -20057,7 +20065,7 @@
       </c>
       <c r="Z96" s="38" t="inlineStr">
         <is>
-          <t>+7.3</t>
+          <t>+8.1</t>
         </is>
       </c>
       <c r="AA96" s="38" t="inlineStr">
@@ -20117,12 +20125,12 @@
       </c>
       <c r="J97" s="38" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="K97" s="38" t="inlineStr">
         <is>
-          <t>+4.7</t>
+          <t>+4.8</t>
         </is>
       </c>
       <c r="L97" s="38" t="inlineStr">
@@ -20197,7 +20205,7 @@
       </c>
       <c r="Z97" s="38" t="inlineStr">
         <is>
-          <t>+12.0</t>
+          <t>+12.9</t>
         </is>
       </c>
       <c r="AA97" s="38" t="inlineStr">
@@ -20257,12 +20265,12 @@
       </c>
       <c r="J98" s="38" t="inlineStr">
         <is>
-          <t>-25.0</t>
+          <t>-25.2</t>
         </is>
       </c>
       <c r="K98" s="38" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="L98" s="38" t="inlineStr">
@@ -20337,7 +20345,7 @@
       </c>
       <c r="Z98" s="38" t="inlineStr">
         <is>
-          <t>+5.3</t>
+          <t>+6.3</t>
         </is>
       </c>
       <c r="AA98" s="38" t="inlineStr">
@@ -20397,12 +20405,12 @@
       </c>
       <c r="J99" s="38" t="inlineStr">
         <is>
-          <t>+7.0</t>
+          <t>+7.4</t>
         </is>
       </c>
       <c r="K99" s="38" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="L99" s="38" t="inlineStr">
@@ -20477,7 +20485,7 @@
       </c>
       <c r="Z99" s="38" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AA99" s="38" t="inlineStr">
@@ -20537,12 +20545,12 @@
       </c>
       <c r="J100" s="38" t="inlineStr">
         <is>
-          <t>-12.1</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="K100" s="38" t="inlineStr">
         <is>
-          <t>+0.9</t>
+          <t>+0.4</t>
         </is>
       </c>
       <c r="L100" s="38" t="inlineStr">
@@ -20617,7 +20625,7 @@
       </c>
       <c r="Z100" s="38" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AA100" s="38" t="inlineStr">
@@ -20637,57 +20645,57 @@
       </c>
       <c r="B101" s="38" t="inlineStr">
         <is>
-          <t>Fordham @ North Dakota State</t>
+          <t>Jacksonville State @ North Dakota State</t>
         </is>
       </c>
       <c r="C101" s="38" t="inlineStr">
         <is>
-          <t>0-38</t>
+          <t>7-33</t>
         </is>
       </c>
       <c r="D101" s="38" t="inlineStr">
         <is>
-          <t>-41.5</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="E101" s="38" t="inlineStr">
         <is>
-          <t>+38.0</t>
+          <t>+26.0</t>
         </is>
       </c>
       <c r="F101" s="38" t="inlineStr">
         <is>
-          <t>-40.9</t>
+          <t>-18.4</t>
         </is>
       </c>
       <c r="G101" s="38" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>+11.6</t>
         </is>
       </c>
       <c r="H101" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="I101" s="51" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="J101" s="38" t="inlineStr">
         <is>
-          <t>-35.2</t>
+          <t>-14.1</t>
         </is>
       </c>
       <c r="K101" s="38" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>+7.3</t>
         </is>
       </c>
       <c r="L101" s="38" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="M101" s="51" t="inlineStr">
@@ -20697,12 +20705,12 @@
       </c>
       <c r="N101" s="38" t="inlineStr">
         <is>
-          <t>-58.5</t>
+          <t>-25.5</t>
         </is>
       </c>
       <c r="O101" s="38" t="inlineStr">
         <is>
-          <t>+17.0</t>
+          <t>+18.7</t>
         </is>
       </c>
       <c r="P101" s="38" t="inlineStr">
@@ -20710,9 +20718,9 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="Q101" s="52" t="inlineStr">
-        <is>
-          <t>Loss (seed week)</t>
+      <c r="Q101" s="51" t="inlineStr">
+        <is>
+          <t>Win (seed week)</t>
         </is>
       </c>
       <c r="R101" s="38" t="inlineStr">
@@ -20742,27 +20750,27 @@
       </c>
       <c r="W101" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X101" s="51" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="Y101" s="38" t="inlineStr">
         <is>
-          <t>+5.3</t>
+          <t>+17.6</t>
         </is>
       </c>
       <c r="Z101" s="38" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>+6.9</t>
         </is>
       </c>
       <c r="AA101" s="38" t="inlineStr">
         <is>
-          <t>+39.8</t>
+          <t>+41.6</t>
         </is>
       </c>
       <c r="AB101" s="38" t="inlineStr">
@@ -20777,82 +20785,82 @@
       </c>
       <c r="B102" s="38" t="inlineStr">
         <is>
-          <t>Jacksonville State @ North Dakota State</t>
+          <t>Fordham @ North Dakota State</t>
         </is>
       </c>
       <c r="C102" s="38" t="inlineStr">
         <is>
-          <t>7-33</t>
+          <t>0-38</t>
         </is>
       </c>
       <c r="D102" s="38" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-41.5</t>
         </is>
       </c>
       <c r="E102" s="38" t="inlineStr">
         <is>
-          <t>+26.0</t>
+          <t>+38.0</t>
         </is>
       </c>
       <c r="F102" s="38" t="inlineStr">
         <is>
-          <t>-18.4</t>
+          <t>-40.9</t>
         </is>
       </c>
       <c r="G102" s="38" t="inlineStr">
         <is>
-          <t>+11.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="H102" s="38" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="I102" s="51" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
+        </is>
+      </c>
+      <c r="J102" s="38" t="inlineStr">
+        <is>
+          <t>-35.3</t>
+        </is>
+      </c>
+      <c r="K102" s="38" t="inlineStr">
+        <is>
+          <t>-6.2</t>
+        </is>
+      </c>
+      <c r="L102" s="38" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M102" s="51" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N102" s="38" t="inlineStr">
+        <is>
+          <t>-58.5</t>
+        </is>
+      </c>
+      <c r="O102" s="38" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="P102" s="38" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="I102" s="51" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="J102" s="38" t="inlineStr">
-        <is>
-          <t>-15.6</t>
-        </is>
-      </c>
-      <c r="K102" s="38" t="inlineStr">
-        <is>
-          <t>+8.9</t>
-        </is>
-      </c>
-      <c r="L102" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M102" s="51" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="N102" s="38" t="inlineStr">
-        <is>
-          <t>-25.5</t>
-        </is>
-      </c>
-      <c r="O102" s="38" t="inlineStr">
-        <is>
-          <t>+18.7</t>
-        </is>
-      </c>
-      <c r="P102" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q102" s="51" t="inlineStr">
-        <is>
-          <t>Win (seed week)</t>
+      <c r="Q102" s="52" t="inlineStr">
+        <is>
+          <t>Loss (seed week)</t>
         </is>
       </c>
       <c r="R102" s="38" t="inlineStr">
@@ -20882,12 +20890,12 @@
       </c>
       <c r="W102" s="38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X102" s="51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="Y102" s="38" t="inlineStr">
@@ -20897,7 +20905,7 @@
       </c>
       <c r="Z102" s="38" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+0.7</t>
         </is>
       </c>
       <c r="AA102" s="38" t="inlineStr">
@@ -20957,12 +20965,12 @@
       </c>
       <c r="J103" s="38" t="inlineStr">
         <is>
-          <t>-31.3</t>
+          <t>-30.9</t>
         </is>
       </c>
       <c r="K103" s="38" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-9.8</t>
         </is>
       </c>
       <c r="L103" s="38" t="inlineStr">
@@ -21037,7 +21045,7 @@
       </c>
       <c r="Z103" s="38" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-9.1</t>
         </is>
       </c>
       <c r="AA103" s="38" t="inlineStr">
@@ -21097,7 +21105,7 @@
       </c>
       <c r="J104" s="38" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+1.4</t>
         </is>
       </c>
       <c r="K104" s="38" t="inlineStr">
@@ -21177,7 +21185,7 @@
       </c>
       <c r="Z104" s="38" t="inlineStr">
         <is>
-          <t>-13.6</t>
+          <t>-15.2</t>
         </is>
       </c>
       <c r="AA104" s="38" t="inlineStr">
@@ -21237,12 +21245,12 @@
       </c>
       <c r="J105" s="38" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="K105" s="38" t="inlineStr">
         <is>
-          <t>+1.8</t>
+          <t>+2.6</t>
         </is>
       </c>
       <c r="L105" s="38" t="inlineStr">
@@ -21252,7 +21260,7 @@
       </c>
       <c r="M105" s="52" t="inlineStr">
         <is>
-          <t>Loss (no real edge)</t>
+          <t>Loss</t>
         </is>
       </c>
       <c r="N105" s="38" t="inlineStr">
@@ -21317,7 +21325,7 @@
       </c>
       <c r="Z105" s="38" t="inlineStr">
         <is>
-          <t>-11.8</t>
+          <t>-12.7</t>
         </is>
       </c>
       <c r="AA105" s="38" t="inlineStr">
@@ -21377,12 +21385,12 @@
       </c>
       <c r="J106" s="38" t="inlineStr">
         <is>
-          <t>-35.9</t>
+          <t>-35.5</t>
         </is>
       </c>
       <c r="K106" s="38" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="L106" s="38" t="inlineStr">
@@ -21457,7 +21465,7 @@
       </c>
       <c r="Z106" s="38" t="inlineStr">
         <is>
-          <t>-13.2</t>
+          <t>-14.4</t>
         </is>
       </c>
       <c r="AA106" s="38" t="inlineStr">
@@ -21517,12 +21525,12 @@
       </c>
       <c r="J107" s="38" t="inlineStr">
         <is>
-          <t>+14.6</t>
+          <t>+14.0</t>
         </is>
       </c>
       <c r="K107" s="38" t="inlineStr">
         <is>
-          <t>-12.8</t>
+          <t>-12.3</t>
         </is>
       </c>
       <c r="L107" s="38" t="inlineStr">
@@ -21597,7 +21605,7 @@
       </c>
       <c r="Z107" s="38" t="inlineStr">
         <is>
-          <t>-26.1</t>
+          <t>-26.7</t>
         </is>
       </c>
       <c r="AA107" s="38" t="inlineStr">
@@ -21657,12 +21665,12 @@
       </c>
       <c r="J108" s="38" t="inlineStr">
         <is>
-          <t>-12.2</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="K108" s="38" t="inlineStr">
         <is>
-          <t>+4.7</t>
+          <t>+5.1</t>
         </is>
       </c>
       <c r="L108" s="38" t="inlineStr">
@@ -21737,7 +21745,7 @@
       </c>
       <c r="Z108" s="38" t="inlineStr">
         <is>
-          <t>-21.4</t>
+          <t>-21.6</t>
         </is>
       </c>
       <c r="AA108" s="38" t="inlineStr">
@@ -21797,12 +21805,12 @@
       </c>
       <c r="J109" s="38" t="inlineStr">
         <is>
-          <t>-12.7</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="K109" s="38" t="inlineStr">
         <is>
-          <t>+17.7</t>
+          <t>+17.0</t>
         </is>
       </c>
       <c r="L109" s="38" t="inlineStr">
@@ -21877,7 +21885,7 @@
       </c>
       <c r="Z109" s="38" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AA109" s="38" t="inlineStr">
@@ -21937,12 +21945,12 @@
       </c>
       <c r="J110" s="38" t="inlineStr">
         <is>
-          <t>-27.2</t>
+          <t>-27.6</t>
         </is>
       </c>
       <c r="K110" s="38" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>-14.6</t>
         </is>
       </c>
       <c r="L110" s="38" t="inlineStr">
@@ -22017,7 +22025,7 @@
       </c>
       <c r="Z110" s="38" t="inlineStr">
         <is>
-          <t>-18.7</t>
+          <t>-19.2</t>
         </is>
       </c>
       <c r="AA110" s="38" t="inlineStr">
@@ -22077,7 +22085,7 @@
       </c>
       <c r="J111" s="38" t="inlineStr">
         <is>
-          <t>+0.8</t>
+          <t>+0.7</t>
         </is>
       </c>
       <c r="K111" s="38" t="inlineStr">
@@ -22092,7 +22100,7 @@
       </c>
       <c r="M111" s="51" t="inlineStr">
         <is>
-          <t>Win (no real edge)</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="N111" s="38" t="inlineStr">
@@ -22157,7 +22165,7 @@
       </c>
       <c r="Z111" s="38" t="inlineStr">
         <is>
-          <t>-16.7</t>
+          <t>-17.2</t>
         </is>
       </c>
       <c r="AA111" s="38" t="inlineStr">
@@ -22217,12 +22225,12 @@
       </c>
       <c r="J112" s="38" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>-15.5</t>
         </is>
       </c>
       <c r="K112" s="38" t="inlineStr">
         <is>
-          <t>+18.5</t>
+          <t>+18.0</t>
         </is>
       </c>
       <c r="L112" s="38" t="inlineStr">
@@ -22297,7 +22305,7 @@
       </c>
       <c r="Z112" s="38" t="inlineStr">
         <is>
-          <t>+1.7</t>
+          <t>+0.8</t>
         </is>
       </c>
       <c r="AA112" s="38" t="inlineStr">
@@ -22357,12 +22365,12 @@
       </c>
       <c r="J113" s="38" t="inlineStr">
         <is>
-          <t>-27.6</t>
+          <t>-27.8</t>
         </is>
       </c>
       <c r="K113" s="38" t="inlineStr">
         <is>
-          <t>+6.1</t>
+          <t>+6.3</t>
         </is>
       </c>
       <c r="L113" s="38" t="inlineStr">
@@ -22437,7 +22445,7 @@
       </c>
       <c r="Z113" s="38" t="inlineStr">
         <is>
-          <t>+7.9</t>
+          <t>+7.1</t>
         </is>
       </c>
       <c r="AA113" s="38" t="inlineStr">
@@ -22502,7 +22510,7 @@
       </c>
       <c r="K114" s="38" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="L114" s="38" t="inlineStr">
@@ -22577,7 +22585,7 @@
       </c>
       <c r="Z114" s="38" t="inlineStr">
         <is>
-          <t>+1.1</t>
+          <t>+0.3</t>
         </is>
       </c>
       <c r="AA114" s="38" t="inlineStr">
@@ -22637,12 +22645,12 @@
       </c>
       <c r="J115" s="38" t="inlineStr">
         <is>
-          <t>-22.0</t>
+          <t>-21.8</t>
         </is>
       </c>
       <c r="K115" s="38" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="L115" s="38" t="inlineStr">
@@ -22717,7 +22725,7 @@
       </c>
       <c r="Z115" s="38" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AA115" s="38" t="inlineStr">
@@ -22777,12 +22785,12 @@
       </c>
       <c r="J116" s="38" t="inlineStr">
         <is>
-          <t>-21.4</t>
+          <t>-20.8</t>
         </is>
       </c>
       <c r="K116" s="38" t="inlineStr">
         <is>
-          <t>-13.1</t>
+          <t>-13.7</t>
         </is>
       </c>
       <c r="L116" s="38" t="inlineStr">
@@ -22857,7 +22865,7 @@
       </c>
       <c r="Z116" s="38" t="inlineStr">
         <is>
-          <t>-13.5</t>
+          <t>-15.1</t>
         </is>
       </c>
       <c r="AA116" s="38" t="inlineStr">
@@ -22917,12 +22925,12 @@
       </c>
       <c r="J117" s="38" t="inlineStr">
         <is>
-          <t>-8.7</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="K117" s="38" t="inlineStr">
         <is>
-          <t>+10.4</t>
+          <t>+11.0</t>
         </is>
       </c>
       <c r="L117" s="38" t="inlineStr">
@@ -22997,7 +23005,7 @@
       </c>
       <c r="Z117" s="38" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="AA117" s="38" t="inlineStr">
@@ -23057,12 +23065,12 @@
       </c>
       <c r="J118" s="38" t="inlineStr">
         <is>
-          <t>-32.7</t>
+          <t>-32.0</t>
         </is>
       </c>
       <c r="K118" s="38" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="L118" s="38" t="inlineStr">
@@ -23072,7 +23080,7 @@
       </c>
       <c r="M118" s="52" t="inlineStr">
         <is>
-          <t>Loss (no real edge)</t>
+          <t>Loss</t>
         </is>
       </c>
       <c r="N118" s="38" t="inlineStr">
@@ -23137,7 +23145,7 @@
       </c>
       <c r="Z118" s="38" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AA118" s="38" t="inlineStr">
@@ -23277,7 +23285,7 @@
       </c>
       <c r="Z119" s="38" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-5.3</t>
         </is>
       </c>
       <c r="AA119" s="38" t="inlineStr">
@@ -23337,12 +23345,12 @@
       </c>
       <c r="J120" s="38" t="inlineStr">
         <is>
-          <t>-14.8</t>
+          <t>-14.4</t>
         </is>
       </c>
       <c r="K120" s="38" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="L120" s="38" t="inlineStr">
@@ -23417,7 +23425,7 @@
       </c>
       <c r="Z120" s="38" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-12.1</t>
         </is>
       </c>
       <c r="AA120" s="38" t="inlineStr">
@@ -23477,12 +23485,12 @@
       </c>
       <c r="J121" s="38" t="inlineStr">
         <is>
-          <t>+18.1</t>
+          <t>+17.8</t>
         </is>
       </c>
       <c r="K121" s="38" t="inlineStr">
         <is>
-          <t>+7.4</t>
+          <t>+7.7</t>
         </is>
       </c>
       <c r="L121" s="38" t="inlineStr">
@@ -23557,7 +23565,7 @@
       </c>
       <c r="Z121" s="38" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AA121" s="38" t="inlineStr">
@@ -23617,12 +23625,12 @@
       </c>
       <c r="J122" s="38" t="inlineStr">
         <is>
-          <t>+10.5</t>
+          <t>+11.5</t>
         </is>
       </c>
       <c r="K122" s="38" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="L122" s="38" t="inlineStr">
@@ -23697,7 +23705,7 @@
       </c>
       <c r="Z122" s="38" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AA122" s="38" t="inlineStr">
@@ -23757,12 +23765,12 @@
       </c>
       <c r="J123" s="38" t="inlineStr">
         <is>
-          <t>+8.3</t>
+          <t>+8.2</t>
         </is>
       </c>
       <c r="K123" s="38" t="inlineStr">
         <is>
-          <t>+5.2</t>
+          <t>+5.3</t>
         </is>
       </c>
       <c r="L123" s="38" t="inlineStr">
@@ -23837,7 +23845,7 @@
       </c>
       <c r="Z123" s="38" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AA123" s="38" t="inlineStr">
@@ -23897,12 +23905,12 @@
       </c>
       <c r="J124" s="38" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="K124" s="38" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="L124" s="38" t="inlineStr">
@@ -23977,7 +23985,7 @@
       </c>
       <c r="Z124" s="38" t="inlineStr">
         <is>
-          <t>-9.9</t>
+          <t>-13.5</t>
         </is>
       </c>
       <c r="AA124" s="38" t="inlineStr">
@@ -24037,12 +24045,12 @@
       </c>
       <c r="J125" s="38" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="K125" s="38" t="inlineStr">
         <is>
-          <t>+6.0</t>
+          <t>+5.3</t>
         </is>
       </c>
       <c r="L125" s="38" t="inlineStr">
@@ -24117,7 +24125,7 @@
       </c>
       <c r="Z125" s="38" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="AA125" s="38" t="inlineStr">
@@ -24177,22 +24185,22 @@
       </c>
       <c r="J126" s="38" t="inlineStr">
         <is>
-          <t>+9.9</t>
+          <t>+11.5</t>
         </is>
       </c>
       <c r="K126" s="38" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="L126" s="38" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="M126" s="52" t="inlineStr">
-        <is>
-          <t>Loss (no real edge)</t>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="M126" s="51" t="inlineStr">
+        <is>
+          <t>Win (no real edge)</t>
         </is>
       </c>
       <c r="N126" s="38" t="inlineStr">
@@ -24237,7 +24245,7 @@
       </c>
       <c r="V126" s="38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W126" s="38" t="inlineStr">
@@ -24247,7 +24255,7 @@
       </c>
       <c r="X126" s="51" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="Y126" s="38" t="inlineStr">
@@ -24257,7 +24265,7 @@
       </c>
       <c r="Z126" s="38" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="AA126" s="38" t="inlineStr">
@@ -24317,12 +24325,12 @@
       </c>
       <c r="J127" s="38" t="inlineStr">
         <is>
-          <t>+1.4</t>
+          <t>+1.8</t>
         </is>
       </c>
       <c r="K127" s="38" t="inlineStr">
         <is>
-          <t>+10.1</t>
+          <t>+9.7</t>
         </is>
       </c>
       <c r="L127" s="38" t="inlineStr">
@@ -24397,7 +24405,7 @@
       </c>
       <c r="Z127" s="38" t="inlineStr">
         <is>
-          <t>+7.9</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="AA127" s="38" t="inlineStr">
@@ -24457,12 +24465,12 @@
       </c>
       <c r="J128" s="38" t="inlineStr">
         <is>
-          <t>+0.7</t>
+          <t>+0.8</t>
         </is>
       </c>
       <c r="K128" s="38" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="L128" s="38" t="inlineStr">
@@ -24537,7 +24545,7 @@
       </c>
       <c r="Z128" s="38" t="inlineStr">
         <is>
-          <t>+9.5</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="AA128" s="38" t="inlineStr">
@@ -24597,12 +24605,12 @@
       </c>
       <c r="J129" s="38" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="K129" s="38" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="L129" s="38" t="inlineStr">
@@ -24677,7 +24685,7 @@
       </c>
       <c r="Z129" s="38" t="inlineStr">
         <is>
-          <t>+8.7</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="AA129" s="38" t="inlineStr">
@@ -24737,12 +24745,12 @@
       </c>
       <c r="J130" s="38" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="K130" s="38" t="inlineStr">
         <is>
-          <t>+3.9</t>
+          <t>+3.4</t>
         </is>
       </c>
       <c r="L130" s="38" t="inlineStr">
@@ -24817,7 +24825,7 @@
       </c>
       <c r="Z130" s="38" t="inlineStr">
         <is>
-          <t>+12.6</t>
+          <t>+6.0</t>
         </is>
       </c>
       <c r="AA130" s="38" t="inlineStr">
@@ -24877,7 +24885,7 @@
       </c>
       <c r="J131" s="38" t="inlineStr">
         <is>
-          <t>-21.1</t>
+          <t>-21.0</t>
         </is>
       </c>
       <c r="K131" s="38" t="inlineStr">
@@ -24957,7 +24965,7 @@
       </c>
       <c r="Z131" s="38" t="inlineStr">
         <is>
-          <t>+10.4</t>
+          <t>+3.7</t>
         </is>
       </c>
       <c r="AA131" s="38" t="inlineStr">
@@ -25017,64 +25025,64 @@
       </c>
       <c r="J132" s="38" t="inlineStr">
         <is>
-          <t>-20.9</t>
+          <t>-21.0</t>
         </is>
       </c>
       <c r="K132" s="38" t="inlineStr">
         <is>
+          <t>+3.7</t>
+        </is>
+      </c>
+      <c r="L132" s="38" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="M132" s="51" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="N132" s="38" t="inlineStr">
+        <is>
+          <t>-30.4</t>
+        </is>
+      </c>
+      <c r="O132" s="38" t="inlineStr">
+        <is>
+          <t>+13.1</t>
+        </is>
+      </c>
+      <c r="P132" s="38" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="Q132" s="51" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="R132" s="38" t="inlineStr">
+        <is>
+          <t>-20.8</t>
+        </is>
+      </c>
+      <c r="S132" s="38" t="inlineStr">
+        <is>
           <t>+3.6</t>
         </is>
       </c>
-      <c r="L132" s="38" t="inlineStr">
+      <c r="T132" s="38" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="M132" s="51" t="inlineStr">
+      <c r="U132" s="51" t="inlineStr">
         <is>
           <t>Win</t>
         </is>
       </c>
-      <c r="N132" s="38" t="inlineStr">
-        <is>
-          <t>-30.4</t>
-        </is>
-      </c>
-      <c r="O132" s="38" t="inlineStr">
-        <is>
-          <t>+13.1</t>
-        </is>
-      </c>
-      <c r="P132" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="Q132" s="51" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
-      <c r="R132" s="38" t="inlineStr">
-        <is>
-          <t>-20.8</t>
-        </is>
-      </c>
-      <c r="S132" s="38" t="inlineStr">
-        <is>
-          <t>+3.6</t>
-        </is>
-      </c>
-      <c r="T132" s="38" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="U132" s="51" t="inlineStr">
-        <is>
-          <t>Win</t>
-        </is>
-      </c>
       <c r="V132" s="38" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25097,7 +25105,7 @@
       </c>
       <c r="Z132" s="38" t="inlineStr">
         <is>
-          <t>+14.0</t>
+          <t>+7.4</t>
         </is>
       </c>
       <c r="AA132" s="38" t="inlineStr">
@@ -25157,12 +25165,12 @@
       </c>
       <c r="J133" s="38" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="K133" s="38" t="inlineStr">
         <is>
-          <t>+5.5</t>
+          <t>+5.8</t>
         </is>
       </c>
       <c r="L133" s="38" t="inlineStr">
@@ -25237,7 +25245,7 @@
       </c>
       <c r="Z133" s="38" t="inlineStr">
         <is>
-          <t>+19.5</t>
+          <t>+13.2</t>
         </is>
       </c>
       <c r="AA133" s="38" t="inlineStr">
@@ -25262,7 +25270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25405,7 +25413,7 @@
         <v>41.3</v>
       </c>
       <c r="J2" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="K2" s="6">
         <f>I2-J2</f>
@@ -25449,7 +25457,7 @@
         <v>-5.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.5</v>
+        <v>-6</v>
       </c>
       <c r="G3" s="6">
         <f>F3-E3</f>
@@ -25463,7 +25471,7 @@
         <v>45.7</v>
       </c>
       <c r="J3" t="n">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="K3" s="6">
         <f>I3-J3</f>
@@ -25519,7 +25527,7 @@
         <v>43.9</v>
       </c>
       <c r="J4" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="K4" s="6">
         <f>I4-J4</f>
@@ -25622,7 +25630,7 @@
         <v>-16</v>
       </c>
       <c r="F6" t="n">
-        <v>-21</v>
+        <v>-20.8</v>
       </c>
       <c r="G6" s="6">
         <f>F6-E6</f>
@@ -25636,7 +25644,7 @@
         <v>47.9</v>
       </c>
       <c r="J6" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="K6" s="6">
         <f>I6-J6</f>
@@ -37494,7 +37502,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G31" s="38" t="n">
         <v>76.2</v>
@@ -37519,10 +37527,10 @@
         <v>72.59999999999999</v>
       </c>
       <c r="F32" s="38" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="G32" s="38" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
@@ -37785,10 +37793,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="C43" s="38" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="D43" s="38" t="n">
         <v>71</v>
-      </c>
-      <c r="D43" s="38" t="n">
-        <v>71.09999999999999</v>
       </c>
       <c r="E43" s="38" t="n">
         <v>72.40000000000001</v>
@@ -39313,7 +39321,7 @@
         <v>53.7</v>
       </c>
       <c r="D104" s="38" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="E104" s="38" t="n">
         <v>54.2</v>
@@ -39322,7 +39330,7 @@
         <v>54.2</v>
       </c>
       <c r="G104" s="38" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="105">
@@ -39803,48 +39811,48 @@
     <row r="124">
       <c r="A124" s="38" t="inlineStr">
         <is>
-          <t>Eastern Michigan</t>
+          <t>Southern Miss</t>
         </is>
       </c>
       <c r="B124" s="38" t="n">
-        <v>47.2</v>
+        <v>54.4</v>
       </c>
       <c r="C124" s="38" t="n">
-        <v>46.4</v>
+        <v>52.8</v>
       </c>
       <c r="D124" s="38" t="n">
-        <v>44.8</v>
+        <v>50.2</v>
       </c>
       <c r="E124" s="38" t="n">
-        <v>47.4</v>
+        <v>51.3</v>
       </c>
       <c r="F124" s="38" t="n">
-        <v>49.4</v>
+        <v>51.3</v>
       </c>
       <c r="G124" s="38" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="38" t="inlineStr">
         <is>
-          <t>Southern Miss</t>
+          <t>Eastern Michigan</t>
         </is>
       </c>
       <c r="B125" s="38" t="n">
-        <v>54.4</v>
+        <v>47.2</v>
       </c>
       <c r="C125" s="38" t="n">
-        <v>52.7</v>
+        <v>46.4</v>
       </c>
       <c r="D125" s="38" t="n">
-        <v>50.1</v>
+        <v>44.8</v>
       </c>
       <c r="E125" s="38" t="n">
-        <v>51.2</v>
+        <v>47.4</v>
       </c>
       <c r="F125" s="38" t="n">
-        <v>51.2</v>
+        <v>49.4</v>
       </c>
       <c r="G125" s="38" t="n">
         <v>49.4</v>
@@ -48917,10 +48925,10 @@
         <v>-10.1</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="I8" s="43" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J8" s="38" t="n">
         <v>-6.4</v>
@@ -48932,10 +48940,10 @@
         <v>56.7</v>
       </c>
       <c r="M8" s="38" t="n">
-        <v>59.5</v>
+        <v>59.2</v>
       </c>
       <c r="N8" s="43" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="O8" s="38" t="n"/>
       <c r="P8" s="38" t="n"/>
@@ -48974,10 +48982,10 @@
         <v>4.5</v>
       </c>
       <c r="H9" s="38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="43" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J9" s="38" t="n">
         <v>6.7</v>
@@ -48989,10 +48997,10 @@
         <v>47.2</v>
       </c>
       <c r="M9" s="38" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="N9" s="43" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="O9" s="38" t="n"/>
       <c r="P9" s="38" t="n"/>
@@ -49031,10 +49039,10 @@
         <v>8.4</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I10" s="38" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="J10" s="38" t="n">
         <v>7.6</v>
@@ -49046,10 +49054,10 @@
         <v>54.5</v>
       </c>
       <c r="M10" s="38" t="n">
-        <v>50</v>
+        <v>44.2</v>
       </c>
       <c r="N10" s="43" t="n">
-        <v>4.5</v>
+        <v>10.2</v>
       </c>
       <c r="O10" s="38" t="n"/>
       <c r="P10" s="38" t="n"/>
@@ -49103,10 +49111,10 @@
         <v>56.9</v>
       </c>
       <c r="M11" s="38" t="n">
-        <v>60</v>
+        <v>59.5</v>
       </c>
       <c r="N11" s="43" t="n">
-        <v>-3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="O11" s="38" t="n"/>
       <c r="P11" s="38" t="n"/>
@@ -49160,10 +49168,10 @@
         <v>49</v>
       </c>
       <c r="M12" s="38" t="n">
-        <v>47</v>
-      </c>
-      <c r="N12" s="43" t="n">
-        <v>2</v>
+        <v>47.2</v>
+      </c>
+      <c r="N12" s="38" t="n">
+        <v>1.8</v>
       </c>
       <c r="O12" s="38" t="n"/>
       <c r="P12" s="38" t="n"/>
@@ -49202,10 +49210,10 @@
         <v>-22.4</v>
       </c>
       <c r="H13" s="38" t="n">
-        <v>-9</v>
+        <v>-9.5</v>
       </c>
       <c r="I13" s="43" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="J13" s="38" t="n">
         <v>-4.2</v>
@@ -49217,10 +49225,10 @@
         <v>44.5</v>
       </c>
       <c r="M13" s="38" t="n">
-        <v>49.5</v>
+        <v>50.2</v>
       </c>
       <c r="N13" s="43" t="n">
-        <v>-5</v>
+        <v>-5.7</v>
       </c>
       <c r="O13" s="38" t="n"/>
       <c r="P13" s="38" t="n"/>
@@ -49274,10 +49282,10 @@
         <v>55.6</v>
       </c>
       <c r="M14" s="38" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="N14" s="43" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O14" s="38" t="n"/>
       <c r="P14" s="38" t="n"/>
@@ -49313,13 +49321,13 @@
         </is>
       </c>
       <c r="G15" s="38" t="n">
-        <v>-4.4</v>
+        <v>-4.5</v>
       </c>
       <c r="H15" s="38" t="n">
         <v>-3</v>
       </c>
       <c r="I15" s="38" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" s="38" t="n">
         <v>3.8</v>
@@ -49388,10 +49396,10 @@
         <v>47.1</v>
       </c>
       <c r="M16" s="38" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="N16" s="38" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="O16" s="38" t="n"/>
       <c r="P16" s="38" t="n"/>
@@ -49430,10 +49438,10 @@
         <v>-18.5</v>
       </c>
       <c r="H17" s="38" t="n">
-        <v>-14</v>
+        <v>-13.8</v>
       </c>
       <c r="I17" s="43" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J17" s="38" t="n">
         <v>-12.8</v>
@@ -49445,10 +49453,10 @@
         <v>56.8</v>
       </c>
       <c r="M17" s="38" t="n">
-        <v>57</v>
-      </c>
-      <c r="N17" s="38" t="n">
-        <v>-0.2</v>
+        <v>52.5</v>
+      </c>
+      <c r="N17" s="43" t="n">
+        <v>4.3</v>
       </c>
       <c r="O17" s="38" t="n"/>
       <c r="P17" s="38" t="n"/>
@@ -49502,10 +49510,10 @@
         <v>51.5</v>
       </c>
       <c r="M18" s="38" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="N18" s="43" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O18" s="38" t="n"/>
       <c r="P18" s="38" t="n"/>
@@ -49544,10 +49552,10 @@
         <v>-29.2</v>
       </c>
       <c r="H19" s="38" t="n">
-        <v>-27.5</v>
+        <v>-28.2</v>
       </c>
       <c r="I19" s="38" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" s="38" t="n">
         <v>-21</v>
@@ -49559,10 +49567,10 @@
         <v>56.5</v>
       </c>
       <c r="M19" s="38" t="n">
-        <v>58</v>
+        <v>57.8</v>
       </c>
       <c r="N19" s="38" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="O19" s="38" t="n"/>
       <c r="P19" s="38" t="n"/>
@@ -49601,10 +49609,10 @@
         <v>-8.9</v>
       </c>
       <c r="H20" s="38" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="I20" s="43" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J20" s="38" t="n">
         <v>-7.8</v>
@@ -49658,10 +49666,10 @@
         <v>-11.8</v>
       </c>
       <c r="H21" s="38" t="n">
-        <v>-12.2</v>
+        <v>-10</v>
       </c>
       <c r="I21" s="38" t="n">
-        <v>-0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J21" s="38" t="n">
         <v>-17.9</v>
@@ -49673,10 +49681,10 @@
         <v>50.5</v>
       </c>
       <c r="M21" s="38" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="N21" s="38" t="n">
-        <v>1.7</v>
+        <v>46.2</v>
+      </c>
+      <c r="N21" s="43" t="n">
+        <v>4.2</v>
       </c>
       <c r="O21" s="38" t="n"/>
       <c r="P21" s="38" t="n"/>
@@ -49730,10 +49738,10 @@
         <v>57.5</v>
       </c>
       <c r="M22" s="38" t="n">
-        <v>56</v>
-      </c>
-      <c r="N22" s="38" t="n">
-        <v>1.5</v>
+        <v>55.2</v>
+      </c>
+      <c r="N22" s="43" t="n">
+        <v>2.2</v>
       </c>
       <c r="O22" s="38" t="n"/>
       <c r="P22" s="38" t="n"/>
@@ -49772,10 +49780,10 @@
         <v>0.9</v>
       </c>
       <c r="H23" s="38" t="n">
-        <v>-9.5</v>
+        <v>-10.8</v>
       </c>
       <c r="I23" s="43" t="n">
-        <v>-10.4</v>
+        <v>-11.7</v>
       </c>
       <c r="J23" s="38" t="n">
         <v>1.5</v>
@@ -49787,10 +49795,10 @@
         <v>44.9</v>
       </c>
       <c r="M23" s="38" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="N23" s="43" t="n">
-        <v>-9.1</v>
+        <v>-8.6</v>
       </c>
       <c r="O23" s="38" t="n"/>
       <c r="P23" s="38" t="n"/>
@@ -49844,10 +49852,10 @@
         <v>54.1</v>
       </c>
       <c r="M24" s="38" t="n">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="N24" s="43" t="n">
-        <v>-6.9</v>
+        <v>-7.2</v>
       </c>
       <c r="O24" s="38" t="n"/>
       <c r="P24" s="38" t="n"/>
@@ -49886,10 +49894,10 @@
         <v>-16</v>
       </c>
       <c r="H25" s="38" t="n">
-        <v>-21</v>
+        <v>-20.8</v>
       </c>
       <c r="I25" s="43" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="J25" s="38" t="n">
         <v>-17.2</v>
@@ -49901,10 +49909,10 @@
         <v>47.9</v>
       </c>
       <c r="M25" s="38" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="N25" s="43" t="n">
-        <v>-3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="O25" s="38" t="n"/>
       <c r="P25" s="38" t="n"/>
@@ -49943,10 +49951,10 @@
         <v>-18.3</v>
       </c>
       <c r="H26" s="38" t="n">
-        <v>-15.5</v>
+        <v>-15.8</v>
       </c>
       <c r="I26" s="43" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J26" s="38" t="n">
         <v>-20.3</v>
@@ -49958,10 +49966,10 @@
         <v>52.6</v>
       </c>
       <c r="M26" s="38" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="N26" s="38" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="O26" s="38" t="n"/>
       <c r="P26" s="38" t="n"/>
@@ -50015,10 +50023,10 @@
         <v>52.3</v>
       </c>
       <c r="M27" s="38" t="n">
-        <v>49.5</v>
+        <v>47.8</v>
       </c>
       <c r="N27" s="43" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O27" s="38" t="n"/>
       <c r="P27" s="38" t="n"/>
@@ -50057,10 +50065,10 @@
         <v>13.7</v>
       </c>
       <c r="H28" s="38" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I28" s="43" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="J28" s="38" t="n">
         <v>10.1</v>
@@ -50072,10 +50080,10 @@
         <v>54</v>
       </c>
       <c r="M28" s="38" t="n">
-        <v>51.2</v>
+        <v>48.8</v>
       </c>
       <c r="N28" s="43" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="O28" s="38" t="n"/>
       <c r="P28" s="38" t="n"/>
@@ -50114,10 +50122,10 @@
         <v>-36.7</v>
       </c>
       <c r="H29" s="38" t="n">
-        <v>-36</v>
+        <v>-36.8</v>
       </c>
       <c r="I29" s="38" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="J29" s="38" t="n">
         <v>-34.3</v>
@@ -50129,10 +50137,10 @@
         <v>53.2</v>
       </c>
       <c r="M29" s="38" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="N29" s="38" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="O29" s="38" t="n"/>
       <c r="P29" s="38" t="n"/>
@@ -50186,10 +50194,10 @@
         <v>47.7</v>
       </c>
       <c r="M30" s="38" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="N30" s="43" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="O30" s="38" t="n"/>
       <c r="P30" s="38" t="n"/>
@@ -50228,10 +50236,10 @@
         <v>-20.6</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>-12.2</v>
+        <v>-11.5</v>
       </c>
       <c r="I31" s="43" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="J31" s="38" t="n">
         <v>-20.4</v>
@@ -50243,10 +50251,10 @@
         <v>51.4</v>
       </c>
       <c r="M31" s="38" t="n">
-        <v>60.2</v>
+        <v>58.8</v>
       </c>
       <c r="N31" s="43" t="n">
-        <v>-8.9</v>
+        <v>-7.4</v>
       </c>
       <c r="O31" s="38" t="n"/>
       <c r="P31" s="38" t="n"/>
@@ -50285,10 +50293,10 @@
         <v>-3.7</v>
       </c>
       <c r="H32" s="38" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="I32" s="43" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="38" t="n">
         <v>6.3</v>
@@ -50300,10 +50308,10 @@
         <v>54.2</v>
       </c>
       <c r="M32" s="38" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N32" s="43" t="n">
-        <v>-2.1</v>
+        <v>54.8</v>
+      </c>
+      <c r="N32" s="38" t="n">
+        <v>-0.6</v>
       </c>
       <c r="O32" s="38" t="n"/>
       <c r="P32" s="38" t="n"/>
@@ -50342,10 +50350,10 @@
         <v>2</v>
       </c>
       <c r="H33" s="38" t="n">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="I33" s="43" t="n">
-        <v>-4.3</v>
+        <v>-5</v>
       </c>
       <c r="J33" s="38" t="n">
         <v>-1.1</v>
@@ -50414,10 +50422,10 @@
         <v>50.5</v>
       </c>
       <c r="M34" s="38" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="N34" s="38" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="O34" s="38" t="n"/>
       <c r="P34" s="38" t="n"/>
@@ -50456,10 +50464,10 @@
         <v>-7.5</v>
       </c>
       <c r="H35" s="38" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="I35" s="43" t="n">
-        <v>3</v>
+        <v>-7</v>
+      </c>
+      <c r="I35" s="38" t="n">
+        <v>0.5</v>
       </c>
       <c r="J35" s="38" t="n">
         <v>-6.3</v>
@@ -50471,10 +50479,10 @@
         <v>50.2</v>
       </c>
       <c r="M35" s="38" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="N35" s="43" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O35" s="38" t="n"/>
       <c r="P35" s="38" t="n"/>
@@ -50513,10 +50521,10 @@
         <v>1.5</v>
       </c>
       <c r="H36" s="38" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I36" s="38" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" s="38" t="n">
         <v>7.8</v>
@@ -50528,10 +50536,10 @@
         <v>54.2</v>
       </c>
       <c r="M36" s="38" t="n">
-        <v>49.8</v>
+        <v>48.8</v>
       </c>
       <c r="N36" s="43" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="O36" s="38" t="n"/>
       <c r="P36" s="38" t="n"/>
@@ -50570,10 +50578,10 @@
         <v>-17.3</v>
       </c>
       <c r="H37" s="38" t="n">
-        <v>-14</v>
+        <v>-13.5</v>
       </c>
       <c r="I37" s="43" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J37" s="38" t="n">
         <v>-14.8</v>
@@ -50627,10 +50635,10 @@
         <v>-4.4</v>
       </c>
       <c r="H38" s="38" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I38" s="38" t="n">
-        <v>1.9</v>
+        <v>-1.5</v>
+      </c>
+      <c r="I38" s="43" t="n">
+        <v>2.9</v>
       </c>
       <c r="J38" s="38" t="n">
         <v>-8.199999999999999</v>
@@ -50684,10 +50692,10 @@
         <v>-34.6</v>
       </c>
       <c r="H39" s="38" t="n">
-        <v>-38</v>
+        <v>-38.2</v>
       </c>
       <c r="I39" s="43" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
       <c r="J39" s="38" t="n">
         <v>-38.8</v>
@@ -50741,10 +50749,10 @@
         <v>-0.4</v>
       </c>
       <c r="H40" s="38" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I40" s="43" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J40" s="38" t="n">
         <v>3.6</v>
@@ -50756,10 +50764,10 @@
         <v>49.8</v>
       </c>
       <c r="M40" s="38" t="n">
-        <v>52</v>
-      </c>
-      <c r="N40" s="43" t="n">
-        <v>-2.2</v>
+        <v>51.5</v>
+      </c>
+      <c r="N40" s="38" t="n">
+        <v>-1.7</v>
       </c>
       <c r="O40" s="38" t="n"/>
       <c r="P40" s="38" t="n"/>
@@ -50813,10 +50821,10 @@
         <v>46.1</v>
       </c>
       <c r="M41" s="38" t="n">
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
       <c r="N41" s="38" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="38" t="n"/>
       <c r="P41" s="38" t="n"/>
@@ -50855,10 +50863,10 @@
         <v>14.5</v>
       </c>
       <c r="H42" s="38" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I42" s="43" t="n">
-        <v>-12.5</v>
+        <v>-12</v>
       </c>
       <c r="J42" s="38" t="n">
         <v>8.199999999999999</v>
@@ -50870,10 +50878,10 @@
         <v>52.6</v>
       </c>
       <c r="M42" s="38" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="N42" s="43" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="O42" s="38" t="n"/>
       <c r="P42" s="38" t="n"/>
@@ -50927,10 +50935,10 @@
         <v>51.1</v>
       </c>
       <c r="M43" s="38" t="n">
-        <v>47</v>
+        <v>46.2</v>
       </c>
       <c r="N43" s="43" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O43" s="38" t="n"/>
       <c r="P43" s="38" t="n"/>
@@ -50969,10 +50977,10 @@
         <v>-18.9</v>
       </c>
       <c r="H44" s="38" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I44" s="38" t="n">
-        <v>-1.1</v>
+        <v>-21</v>
+      </c>
+      <c r="I44" s="43" t="n">
+        <v>-2.1</v>
       </c>
       <c r="J44" s="38" t="n">
         <v>-14.1</v>
@@ -50984,10 +50992,10 @@
         <v>47.6</v>
       </c>
       <c r="M44" s="38" t="n">
-        <v>55</v>
+        <v>54.8</v>
       </c>
       <c r="N44" s="43" t="n">
-        <v>-7.4</v>
+        <v>-7.2</v>
       </c>
       <c r="O44" s="38" t="n"/>
       <c r="P44" s="38" t="n"/>
@@ -51026,10 +51034,10 @@
         <v>-20.7</v>
       </c>
       <c r="H45" s="38" t="n">
-        <v>-14</v>
+        <v>-13.8</v>
       </c>
       <c r="I45" s="43" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J45" s="38" t="n">
         <v>-18.8</v>
@@ -51098,10 +51106,10 @@
         <v>41.3</v>
       </c>
       <c r="M46" s="38" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="N46" s="43" t="n">
-        <v>-5.7</v>
+        <v>-5.5</v>
       </c>
       <c r="O46" s="38" t="n"/>
       <c r="P46" s="38" t="n"/>
@@ -51140,10 +51148,10 @@
         <v>-5.9</v>
       </c>
       <c r="H47" s="38" t="n">
-        <v>-6.5</v>
+        <v>-6</v>
       </c>
       <c r="I47" s="38" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="J47" s="38" t="n">
         <v>1.5</v>
@@ -51155,10 +51163,10 @@
         <v>45.6</v>
       </c>
       <c r="M47" s="38" t="n">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="N47" s="43" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O47" s="38" t="n"/>
       <c r="P47" s="38" t="n"/>
@@ -51212,10 +51220,10 @@
         <v>43.9</v>
       </c>
       <c r="M48" s="38" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="N48" s="43" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
       <c r="O48" s="38" t="n"/>
       <c r="P48" s="38" t="n"/>
@@ -51311,10 +51319,10 @@
         <v>-5.1</v>
       </c>
       <c r="H50" s="38" t="n">
-        <v>-14</v>
+        <v>-15.5</v>
       </c>
       <c r="I50" s="43" t="n">
-        <v>-8.9</v>
+        <v>-10.4</v>
       </c>
       <c r="J50" s="38" t="n">
         <v>-1.6</v>
@@ -51326,10 +51334,10 @@
         <v>47.8</v>
       </c>
       <c r="M50" s="38" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="N50" s="43" t="n">
-        <v>-7.2</v>
+        <v>-5.7</v>
       </c>
       <c r="O50" s="38" t="n"/>
       <c r="P50" s="38" t="n"/>
@@ -51368,10 +51376,10 @@
         <v>-3.2</v>
       </c>
       <c r="H51" s="38" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I51" s="38" t="n">
-        <v>-1.8</v>
+        <v>-5.5</v>
+      </c>
+      <c r="I51" s="43" t="n">
+        <v>-2.3</v>
       </c>
       <c r="J51" s="38" t="n">
         <v>-0.2</v>
@@ -51383,10 +51391,10 @@
         <v>40.4</v>
       </c>
       <c r="M51" s="38" t="n">
-        <v>42.5</v>
+        <v>44.2</v>
       </c>
       <c r="N51" s="43" t="n">
-        <v>-2.1</v>
+        <v>-3.9</v>
       </c>
       <c r="O51" s="38" t="n"/>
       <c r="P51" s="38" t="n"/>
@@ -51440,10 +51448,10 @@
         <v>48.3</v>
       </c>
       <c r="M52" s="38" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="N52" s="38" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O52" s="38" t="n"/>
       <c r="P52" s="38" t="n"/>
@@ -51482,10 +51490,10 @@
         <v>-0.6</v>
       </c>
       <c r="H53" s="38" t="n">
-        <v>0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I53" s="38" t="n">
-        <v>1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="J53" s="38" t="n">
         <v>2.6</v>
@@ -51497,10 +51505,10 @@
         <v>52.3</v>
       </c>
       <c r="M53" s="38" t="n">
-        <v>56</v>
-      </c>
-      <c r="N53" s="43" t="n">
-        <v>-3.7</v>
+        <v>51.5</v>
+      </c>
+      <c r="N53" s="38" t="n">
+        <v>0.8</v>
       </c>
       <c r="O53" s="38" t="n"/>
       <c r="P53" s="38" t="n"/>
@@ -51554,10 +51562,10 @@
         <v>52</v>
       </c>
       <c r="M54" s="38" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="N54" s="38" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="O54" s="38" t="n"/>
       <c r="P54" s="38" t="n"/>
@@ -51596,10 +51604,10 @@
         <v>0.3</v>
       </c>
       <c r="H55" s="38" t="n">
-        <v>-14</v>
+        <v>-11.2</v>
       </c>
       <c r="I55" s="43" t="n">
-        <v>-14.3</v>
+        <v>-11.5</v>
       </c>
       <c r="J55" s="38" t="n">
         <v>-9.199999999999999</v>
@@ -51653,10 +51661,10 @@
         <v>10.4</v>
       </c>
       <c r="H56" s="38" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I56" s="38" t="n">
-        <v>-0.7</v>
+        <v>-1.9</v>
       </c>
       <c r="J56" s="38" t="n">
         <v>6.8</v>
@@ -51668,10 +51676,10 @@
         <v>47.2</v>
       </c>
       <c r="M56" s="38" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="N56" s="43" t="n">
-        <v>-5.3</v>
+        <v>-4.6</v>
       </c>
       <c r="O56" s="38" t="n"/>
       <c r="P56" s="38" t="n"/>
@@ -51707,13 +51715,13 @@
         </is>
       </c>
       <c r="G57" s="38" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H57" s="38" t="n">
-        <v>-2.8</v>
+        <v>-3.5</v>
       </c>
       <c r="I57" s="43" t="n">
-        <v>-3.4</v>
+        <v>-4.2</v>
       </c>
       <c r="J57" s="38" t="n">
         <v>0.2</v>
@@ -51725,10 +51733,10 @@
         <v>46.4</v>
       </c>
       <c r="M57" s="38" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="N57" s="43" t="n">
-        <v>-3.1</v>
+        <v>-2.1</v>
       </c>
       <c r="O57" s="38" t="n"/>
       <c r="P57" s="38" t="n"/>
@@ -51767,10 +51775,10 @@
         <v>8.1</v>
       </c>
       <c r="H58" s="38" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I58" s="38" t="n">
-        <v>0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="J58" s="38" t="n">
         <v>16.9</v>
@@ -51782,10 +51790,10 @@
         <v>35.5</v>
       </c>
       <c r="M58" s="38" t="n">
-        <v>40.2</v>
+        <v>39.2</v>
       </c>
       <c r="N58" s="43" t="n">
-        <v>-4.7</v>
+        <v>-3.7</v>
       </c>
       <c r="O58" s="38" t="n"/>
       <c r="P58" s="38" t="n"/>
@@ -51839,10 +51847,10 @@
         <v>54.4</v>
       </c>
       <c r="M59" s="38" t="n">
-        <v>59</v>
-      </c>
-      <c r="N59" s="43" t="n">
-        <v>-4.6</v>
+        <v>56.2</v>
+      </c>
+      <c r="N59" s="38" t="n">
+        <v>-1.8</v>
       </c>
       <c r="O59" s="38" t="n"/>
       <c r="P59" s="38" t="n"/>
@@ -51878,13 +51886,13 @@
         </is>
       </c>
       <c r="G60" s="38" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="H60" s="38" t="n">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="I60" s="43" t="n">
-        <v>-3</v>
+        <v>-2.6</v>
       </c>
       <c r="J60" s="38" t="n">
         <v>-10.4</v>
@@ -51896,10 +51904,10 @@
         <v>49.5</v>
       </c>
       <c r="M60" s="38" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="N60" s="38" t="n">
-        <v>0.3</v>
+        <v>51.5</v>
+      </c>
+      <c r="N60" s="43" t="n">
+        <v>-2</v>
       </c>
       <c r="O60" s="38" t="n">
         <v>34</v>
@@ -51946,10 +51954,10 @@
         <v>-7.7</v>
       </c>
       <c r="H61" s="38" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I61" s="43" t="n">
-        <v>6.7</v>
+        <v>4.7</v>
       </c>
       <c r="J61" s="38" t="n">
         <v>-0.2</v>
@@ -51961,10 +51969,10 @@
         <v>60.5</v>
       </c>
       <c r="M61" s="38" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="N61" s="43" t="n">
-        <v>3</v>
+        <v>60.2</v>
+      </c>
+      <c r="N61" s="38" t="n">
+        <v>0.2</v>
       </c>
       <c r="O61" s="38" t="n"/>
       <c r="P61" s="38" t="n"/>
@@ -52003,10 +52011,10 @@
         <v>5.6</v>
       </c>
       <c r="H62" s="38" t="n">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="I62" s="43" t="n">
-        <v>-15.6</v>
+        <v>-15.1</v>
       </c>
       <c r="J62" s="38" t="n">
         <v>-8.6</v>
@@ -52018,10 +52026,10 @@
         <v>48.7</v>
       </c>
       <c r="M62" s="38" t="n">
-        <v>51</v>
-      </c>
-      <c r="N62" s="43" t="n">
-        <v>-2.3</v>
+        <v>49.5</v>
+      </c>
+      <c r="N62" s="38" t="n">
+        <v>-0.8</v>
       </c>
       <c r="O62" s="38" t="n"/>
       <c r="P62" s="38" t="n"/>
@@ -52075,10 +52083,10 @@
         <v>55.2</v>
       </c>
       <c r="M63" s="38" t="n">
-        <v>54</v>
-      </c>
-      <c r="N63" s="38" t="n">
-        <v>1.2</v>
+        <v>51.8</v>
+      </c>
+      <c r="N63" s="43" t="n">
+        <v>3.4</v>
       </c>
       <c r="O63" s="38" t="n"/>
       <c r="P63" s="38" t="n"/>
@@ -52132,10 +52140,10 @@
         <v>49.3</v>
       </c>
       <c r="M64" s="38" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="N64" s="38" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="O64" s="38" t="n"/>
       <c r="P64" s="38" t="n"/>
@@ -52173,8 +52181,12 @@
       <c r="G65" s="38" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H65" s="38" t="n"/>
-      <c r="I65" s="38" t="n"/>
+      <c r="H65" s="38" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I65" s="38" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J65" s="38" t="n">
         <v>-15.7</v>
       </c>
@@ -52184,8 +52196,12 @@
       <c r="L65" s="38" t="n">
         <v>60.7</v>
       </c>
-      <c r="M65" s="38" t="n"/>
-      <c r="N65" s="38" t="n"/>
+      <c r="M65" s="38" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="N65" s="43" t="n">
+        <v>2.2</v>
+      </c>
       <c r="O65" s="38" t="n"/>
       <c r="P65" s="38" t="n"/>
       <c r="Q65" s="38" t="n"/>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1624,7 +1624,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -1680,7 +1680,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-33.1</v>
+        <v>-33.4</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -1744,7 +1744,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-17.6</v>
+        <v>-16.9</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -1864,7 +1864,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-13.2</v>
+        <v>-13</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-30.3</v>
+        <v>-29.9</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -1976,7 +1976,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -2088,7 +2088,7 @@
       <c r="P37" s="42" t="n"/>
       <c r="Q37" s="42" t="n"/>
       <c r="R37" s="42" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="S37" s="51" t="n"/>
       <c r="T37" s="51" t="n"/>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-4.5</v>
+        <v>-5.4</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="S42" s="53" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="R43" s="42" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="S43" s="52" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="R44" s="42" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="S44" s="53" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>-13.4</v>
+        <v>-13.5</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="S46" s="52" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>-37.8</v>
+        <v>-36.9</v>
       </c>
       <c r="S47" s="52" t="inlineStr">
         <is>
@@ -2820,9 +2820,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U47" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U47" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V47" s="52" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="S51" s="53" t="inlineStr">
         <is>
@@ -3027,9 +3027,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U51" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U51" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V51" s="53" t="inlineStr">
@@ -3102,7 +3102,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R52" s="42" t="n"/>
+      <c r="R52" s="42" t="n">
+        <v>6.7</v>
+      </c>
       <c r="S52" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -3113,7 +3115,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U52" s="51" t="n"/>
+      <c r="U52" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V52" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -3185,7 +3191,7 @@
         </is>
       </c>
       <c r="R53" s="42" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S53" s="52" t="inlineStr">
         <is>
@@ -3273,7 +3279,7 @@
         </is>
       </c>
       <c r="R54" s="42" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="S54" s="52" t="inlineStr">
         <is>
@@ -3361,7 +3367,7 @@
         </is>
       </c>
       <c r="R55" s="42" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="S55" s="52" t="inlineStr">
         <is>
@@ -3449,7 +3455,7 @@
         </is>
       </c>
       <c r="R56" s="42" t="n">
-        <v>-20.8</v>
+        <v>-20.1</v>
       </c>
       <c r="S56" s="52" t="inlineStr">
         <is>
@@ -3461,9 +3467,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U56" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U56" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V56" s="53" t="inlineStr">
@@ -3537,7 +3543,7 @@
         </is>
       </c>
       <c r="R57" s="42" t="n">
-        <v>-8</v>
+        <v>-8.1</v>
       </c>
       <c r="S57" s="53" t="inlineStr">
         <is>
@@ -3625,7 +3631,7 @@
         </is>
       </c>
       <c r="R58" s="42" t="n">
-        <v>-6.2</v>
+        <v>-6.8</v>
       </c>
       <c r="S58" s="53" t="inlineStr">
         <is>
@@ -3713,7 +3719,7 @@
         </is>
       </c>
       <c r="R59" s="42" t="n">
-        <v>-6.8</v>
+        <v>-7</v>
       </c>
       <c r="S59" s="53" t="inlineStr">
         <is>
@@ -4360,7 +4366,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -4416,7 +4422,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -4472,7 +4478,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -4528,7 +4534,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -4584,7 +4590,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-15.7</v>
+        <v>-14.8</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -4640,7 +4646,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-11.4</v>
+        <v>-10.9</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -4696,7 +4702,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-11</v>
+        <v>-11.7</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -4888,7 +4894,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="S36" s="52" t="inlineStr">
         <is>
@@ -4976,7 +4982,7 @@
         </is>
       </c>
       <c r="R37" s="42" t="n">
-        <v>-4.5</v>
+        <v>-4.8</v>
       </c>
       <c r="S37" s="54" t="inlineStr">
         <is>
@@ -5064,7 +5070,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>-12.1</v>
+        <v>-12.7</v>
       </c>
       <c r="S38" s="53" t="inlineStr">
         <is>
@@ -5152,7 +5158,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>-12.4</v>
+        <v>-11</v>
       </c>
       <c r="S39" s="53" t="inlineStr">
         <is>
@@ -5240,7 +5246,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -5328,7 +5334,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-25.8</v>
+        <v>-25.3</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -5416,7 +5422,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="S42" s="52" t="inlineStr">
         <is>
@@ -5623,7 +5629,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="S46" s="52" t="inlineStr">
         <is>
@@ -5711,7 +5717,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="S47" s="53" t="inlineStr">
         <is>
@@ -5798,7 +5804,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R48" s="42" t="n"/>
+      <c r="R48" s="42" t="n">
+        <v>-32.2</v>
+      </c>
       <c r="S48" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -5809,7 +5817,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U48" s="51" t="n"/>
+      <c r="U48" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V48" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -5880,7 +5892,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R49" s="42" t="n"/>
+      <c r="R49" s="42" t="n">
+        <v>15.9</v>
+      </c>
       <c r="S49" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -5891,7 +5905,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U49" s="51" t="n"/>
+      <c r="U49" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V49" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -5962,7 +5980,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R50" s="42" t="n"/>
+      <c r="R50" s="42" t="n">
+        <v>-13.6</v>
+      </c>
       <c r="S50" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -5973,7 +5993,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U50" s="51" t="n"/>
+      <c r="U50" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V50" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -6045,7 +6069,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>-24</v>
+        <v>-23.8</v>
       </c>
       <c r="S51" s="52" t="inlineStr">
         <is>
@@ -6133,7 +6157,7 @@
         </is>
       </c>
       <c r="R52" s="42" t="n">
-        <v>-2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="S52" s="52" t="inlineStr">
         <is>
@@ -6145,9 +6169,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U52" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U52" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V52" s="53" t="inlineStr">
@@ -6220,7 +6244,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R53" s="42" t="n"/>
+      <c r="R53" s="42" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="S53" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -6231,7 +6257,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U53" s="51" t="n"/>
+      <c r="U53" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V53" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -6970,7 +7000,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -7034,7 +7064,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-16.9</v>
+        <v>-15.6</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -7098,7 +7128,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-11.3</v>
+        <v>-10.7</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -7154,7 +7184,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-18.2</v>
+        <v>-18</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -7210,7 +7240,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -7266,7 +7296,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -7458,7 +7488,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>-13.8</v>
+        <v>-14.7</v>
       </c>
       <c r="S38" s="53" t="inlineStr">
         <is>
@@ -7546,7 +7576,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
       <c r="S39" s="52" t="inlineStr">
         <is>
@@ -7558,9 +7588,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U39" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U39" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V39" s="53" t="inlineStr">
@@ -7634,7 +7664,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="S40" s="52" t="inlineStr">
         <is>
@@ -7722,7 +7752,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -7810,7 +7840,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>-14.9</v>
+        <v>-14.5</v>
       </c>
       <c r="S42" s="53" t="inlineStr">
         <is>
@@ -7898,7 +7928,7 @@
         </is>
       </c>
       <c r="R43" s="42" t="n">
-        <v>-18.8</v>
+        <v>-19.7</v>
       </c>
       <c r="S43" s="53" t="inlineStr">
         <is>
@@ -8104,7 +8134,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R47" s="42" t="n"/>
+      <c r="R47" s="42" t="n">
+        <v>17.7</v>
+      </c>
       <c r="S47" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -8115,7 +8147,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U47" s="51" t="n"/>
+      <c r="U47" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V47" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -8187,7 +8223,7 @@
         </is>
       </c>
       <c r="R48" s="42" t="n">
-        <v>-12.8</v>
+        <v>-12.3</v>
       </c>
       <c r="S48" s="52" t="inlineStr">
         <is>
@@ -8363,7 +8399,7 @@
         </is>
       </c>
       <c r="R50" s="42" t="n">
-        <v>-13.7</v>
+        <v>-13</v>
       </c>
       <c r="S50" s="53" t="inlineStr">
         <is>
@@ -8450,7 +8486,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R51" s="42" t="n"/>
+      <c r="R51" s="42" t="n">
+        <v>6.2</v>
+      </c>
       <c r="S51" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -8461,7 +8499,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U51" s="51" t="n"/>
+      <c r="U51" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V51" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -8532,7 +8574,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R52" s="42" t="n"/>
+      <c r="R52" s="42" t="n">
+        <v>-13.1</v>
+      </c>
       <c r="S52" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -8543,7 +8587,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U52" s="51" t="n"/>
+      <c r="U52" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V52" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -8614,7 +8662,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R53" s="42" t="n"/>
+      <c r="R53" s="42" t="n">
+        <v>-7.8</v>
+      </c>
       <c r="S53" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -8625,7 +8675,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U53" s="51" t="n"/>
+      <c r="U53" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V53" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -9352,7 +9406,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -9472,7 +9526,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-8.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -9528,7 +9582,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -9556,43 +9610,35 @@
       </c>
       <c r="E34" s="42" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="F34" s="42" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="G34" s="42" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="H34" s="42" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="I34" s="42" t="n">
-        <v>-1.1</v>
-      </c>
+        <v>8.6</v>
+      </c>
+      <c r="H34" s="42" t="n"/>
+      <c r="I34" s="42" t="n"/>
       <c r="J34" s="42" t="n">
-        <v>-18.1</v>
+        <v>8.4</v>
       </c>
       <c r="K34" s="42" t="n">
-        <v>-1.4</v>
+        <v>-7.1</v>
       </c>
       <c r="L34" s="42" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="M34" s="42" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="N34" s="47" t="n">
-        <v>-4.8</v>
-      </c>
+        <v>51.7</v>
+      </c>
+      <c r="M34" s="42" t="n"/>
+      <c r="N34" s="42" t="n"/>
       <c r="O34" s="42" t="n"/>
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-15.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -9620,35 +9666,43 @@
       </c>
       <c r="E35" s="42" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="F35" s="42" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="G35" s="42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H35" s="42" t="n"/>
-      <c r="I35" s="42" t="n"/>
+        <v>-5.9</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I35" s="47" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J35" s="42" t="n">
-        <v>8.4</v>
+        <v>-5.4</v>
       </c>
       <c r="K35" s="42" t="n">
         <v>-7.1</v>
       </c>
       <c r="L35" s="42" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="M35" s="42" t="n"/>
-      <c r="N35" s="42" t="n"/>
+        <v>44.4</v>
+      </c>
+      <c r="M35" s="42" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="N35" s="47" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="O35" s="42" t="n"/>
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>8.9</v>
+        <v>-7.8</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -9661,7 +9715,7 @@
       </c>
       <c r="B36" s="42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C36" s="42" t="inlineStr">
@@ -9676,43 +9730,43 @@
       </c>
       <c r="E36" s="42" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="F36" s="42" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G36" s="42" t="n">
-        <v>-5.9</v>
+        <v>-11.4</v>
       </c>
       <c r="H36" s="42" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I36" s="47" t="n">
-        <v>2.4</v>
+        <v>-12.5</v>
+      </c>
+      <c r="I36" s="42" t="n">
+        <v>-1.1</v>
       </c>
       <c r="J36" s="42" t="n">
-        <v>-5.4</v>
+        <v>-18.1</v>
       </c>
       <c r="K36" s="42" t="n">
-        <v>-7.1</v>
+        <v>-1.4</v>
       </c>
       <c r="L36" s="42" t="n">
-        <v>44.4</v>
+        <v>53.7</v>
       </c>
       <c r="M36" s="42" t="n">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="N36" s="47" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
       <c r="O36" s="42" t="n"/>
       <c r="P36" s="42" t="n"/>
       <c r="Q36" s="42" t="n"/>
       <c r="R36" s="42" t="n">
-        <v>-7.6</v>
+        <v>-15.2</v>
       </c>
       <c r="S36" s="51" t="n"/>
       <c r="T36" s="51" t="n"/>
@@ -9903,7 +9957,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="S40" s="52" t="inlineStr">
         <is>
@@ -9991,7 +10045,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="S41" s="52" t="inlineStr">
         <is>
@@ -10079,7 +10133,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>-24.1</v>
+        <v>-26.2</v>
       </c>
       <c r="S42" s="52" t="inlineStr">
         <is>
@@ -10255,7 +10309,7 @@
         </is>
       </c>
       <c r="R44" s="42" t="n">
-        <v>-24.6</v>
+        <v>-25.6</v>
       </c>
       <c r="S44" s="52" t="inlineStr">
         <is>
@@ -10343,7 +10397,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -10431,7 +10485,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="S46" s="53" t="inlineStr">
         <is>
@@ -10519,7 +10573,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="S47" s="52" t="inlineStr">
         <is>
@@ -10726,7 +10780,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>-12.5</v>
+        <v>-12.3</v>
       </c>
       <c r="S51" s="52" t="inlineStr">
         <is>
@@ -10814,7 +10868,7 @@
         </is>
       </c>
       <c r="R52" s="42" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="S52" s="52" t="inlineStr">
         <is>
@@ -10902,7 +10956,7 @@
         </is>
       </c>
       <c r="R53" s="42" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="S53" s="53" t="inlineStr">
         <is>
@@ -10990,7 +11044,7 @@
         </is>
       </c>
       <c r="R54" s="42" t="n">
-        <v>-11.2</v>
+        <v>-11.3</v>
       </c>
       <c r="S54" s="53" t="inlineStr">
         <is>
@@ -11078,7 +11132,7 @@
         </is>
       </c>
       <c r="R55" s="42" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S55" s="52" t="inlineStr">
         <is>
@@ -11165,7 +11219,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R56" s="42" t="n"/>
+      <c r="R56" s="42" t="n">
+        <v>-4.7</v>
+      </c>
       <c r="S56" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -11176,7 +11232,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U56" s="51" t="n"/>
+      <c r="U56" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V56" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -11248,7 +11308,7 @@
         </is>
       </c>
       <c r="R57" s="42" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="S57" s="52" t="inlineStr">
         <is>
@@ -11335,7 +11395,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R58" s="42" t="n"/>
+      <c r="R58" s="42" t="n">
+        <v>16.8</v>
+      </c>
       <c r="S58" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -11346,7 +11408,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U58" s="51" t="n"/>
+      <c r="U58" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V58" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -11897,7 +11963,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -11961,7 +12027,7 @@
       <c r="P23" s="42" t="n"/>
       <c r="Q23" s="42" t="n"/>
       <c r="R23" s="42" t="n">
-        <v>-11.4</v>
+        <v>-12.2</v>
       </c>
       <c r="S23" s="51" t="n"/>
       <c r="T23" s="51" t="n"/>
@@ -12025,7 +12091,7 @@
       <c r="P24" s="42" t="n"/>
       <c r="Q24" s="42" t="n"/>
       <c r="R24" s="42" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S24" s="51" t="n"/>
       <c r="T24" s="51" t="n"/>
@@ -12089,7 +12155,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -12281,7 +12347,7 @@
         </is>
       </c>
       <c r="R29" s="42" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="S29" s="52" t="inlineStr">
         <is>
@@ -12369,7 +12435,7 @@
         </is>
       </c>
       <c r="R30" s="42" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S30" s="52" t="inlineStr">
         <is>
@@ -12457,7 +12523,7 @@
         </is>
       </c>
       <c r="R31" s="42" t="n">
-        <v>-13.2</v>
+        <v>-11.8</v>
       </c>
       <c r="S31" s="53" t="inlineStr">
         <is>
@@ -12469,9 +12535,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U31" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U31" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V31" s="52" t="inlineStr">
@@ -12545,7 +12611,7 @@
         </is>
       </c>
       <c r="R32" s="42" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="S32" s="53" t="inlineStr">
         <is>
@@ -12752,7 +12818,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>-13.7</v>
+        <v>-13</v>
       </c>
       <c r="S36" s="53" t="inlineStr">
         <is>
@@ -12840,7 +12906,7 @@
         </is>
       </c>
       <c r="R37" s="42" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="S37" s="52" t="inlineStr">
         <is>
@@ -12928,7 +12994,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="S38" s="52" t="inlineStr">
         <is>
@@ -13506,7 +13572,7 @@
         </is>
       </c>
       <c r="R18" s="42" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="S18" s="52" t="inlineStr">
         <is>
@@ -13594,7 +13660,7 @@
         </is>
       </c>
       <c r="R19" s="42" t="n">
-        <v>-37.8</v>
+        <v>-36.9</v>
       </c>
       <c r="S19" s="52" t="inlineStr">
         <is>
@@ -13606,9 +13672,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U19" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U19" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V19" s="52" t="inlineStr">
@@ -13801,7 +13867,7 @@
         </is>
       </c>
       <c r="R23" s="42" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="S23" s="52" t="inlineStr">
         <is>
@@ -13889,7 +13955,7 @@
         </is>
       </c>
       <c r="R24" s="42" t="n">
-        <v>-6.2</v>
+        <v>-6.8</v>
       </c>
       <c r="S24" s="53" t="inlineStr">
         <is>
@@ -14514,7 +14580,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>-15.7</v>
+        <v>-14.8</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -14570,7 +14636,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -14626,7 +14692,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>-14.8</v>
+        <v>-14</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -14682,7 +14748,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -14738,7 +14804,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -14794,7 +14860,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-10.3</v>
+        <v>-11</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -14850,7 +14916,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -15042,7 +15108,7 @@
         </is>
       </c>
       <c r="R35" s="42" t="n">
-        <v>-24.1</v>
+        <v>-26.2</v>
       </c>
       <c r="S35" s="52" t="inlineStr">
         <is>
@@ -15130,7 +15196,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="S36" s="53" t="inlineStr">
         <is>
@@ -15218,7 +15284,7 @@
         </is>
       </c>
       <c r="R37" s="42" t="n">
-        <v>-9.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="S37" s="53" t="inlineStr">
         <is>
@@ -15306,7 +15372,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S38" s="52" t="inlineStr">
         <is>
@@ -15482,7 +15548,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-14.4</v>
+        <v>-13.6</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -15570,7 +15636,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-15.7</v>
+        <v>-15.5</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -15777,7 +15843,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>15.3</v>
+        <v>13.7</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -15865,7 +15931,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="S46" s="52" t="inlineStr">
         <is>
@@ -15953,7 +16019,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
       <c r="S47" s="53" t="inlineStr">
         <is>
@@ -16041,7 +16107,7 @@
         </is>
       </c>
       <c r="R48" s="42" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="S48" s="52" t="inlineStr">
         <is>
@@ -16129,7 +16195,7 @@
         </is>
       </c>
       <c r="R49" s="42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="S49" s="53" t="inlineStr">
         <is>
@@ -16217,7 +16283,7 @@
         </is>
       </c>
       <c r="R50" s="42" t="n">
-        <v>-11</v>
+        <v>-11.1</v>
       </c>
       <c r="S50" s="52" t="inlineStr">
         <is>
@@ -16776,7 +16842,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -16832,7 +16898,7 @@
       <c r="P23" s="42" t="n"/>
       <c r="Q23" s="42" t="n"/>
       <c r="R23" s="42" t="n">
-        <v>-18.2</v>
+        <v>-19</v>
       </c>
       <c r="S23" s="51" t="n"/>
       <c r="T23" s="51" t="n"/>
@@ -16888,7 +16954,7 @@
       <c r="P24" s="42" t="n"/>
       <c r="Q24" s="42" t="n"/>
       <c r="R24" s="42" t="n">
-        <v>-6.6</v>
+        <v>-6.3</v>
       </c>
       <c r="S24" s="51" t="n"/>
       <c r="T24" s="51" t="n"/>
@@ -16944,7 +17010,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -17000,7 +17066,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -17192,7 +17258,7 @@
         </is>
       </c>
       <c r="R30" s="42" t="n">
-        <v>-14.9</v>
+        <v>-14.5</v>
       </c>
       <c r="S30" s="53" t="inlineStr">
         <is>
@@ -17280,7 +17346,7 @@
         </is>
       </c>
       <c r="R31" s="42" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="S31" s="53" t="inlineStr">
         <is>
@@ -17368,7 +17434,7 @@
         </is>
       </c>
       <c r="R32" s="42" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="S32" s="52" t="inlineStr">
         <is>
@@ -17456,7 +17522,7 @@
         </is>
       </c>
       <c r="R33" s="42" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="S33" s="52" t="inlineStr">
         <is>
@@ -17515,7 +17581,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I34" s="42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J34" s="42" t="n">
         <v>5</v>
@@ -17544,7 +17610,7 @@
         </is>
       </c>
       <c r="R34" s="42" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="S34" s="53" t="inlineStr">
         <is>
@@ -17751,7 +17817,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>-2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="S38" s="52" t="inlineStr">
         <is>
@@ -17763,9 +17829,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U38" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U38" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V38" s="53" t="inlineStr">
@@ -17839,7 +17905,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>-20.7</v>
+        <v>-22</v>
       </c>
       <c r="S39" s="53" t="inlineStr">
         <is>
@@ -17927,7 +17993,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-21.1</v>
+        <v>-21.8</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -18015,7 +18081,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-6.8</v>
+        <v>-7</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -18102,7 +18168,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R42" s="42" t="n"/>
+      <c r="R42" s="42" t="n">
+        <v>-7.3</v>
+      </c>
       <c r="S42" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -18113,7 +18181,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U42" s="51" t="n"/>
+      <c r="U42" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V42" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -18620,7 +18692,7 @@
       <c r="P20" s="42" t="n"/>
       <c r="Q20" s="42" t="n"/>
       <c r="R20" s="42" t="n">
-        <v>-14.5</v>
+        <v>-15.2</v>
       </c>
       <c r="S20" s="51" t="n"/>
       <c r="T20" s="51" t="n"/>
@@ -18676,7 +18748,7 @@
       <c r="P21" s="42" t="n"/>
       <c r="Q21" s="42" t="n"/>
       <c r="R21" s="42" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
       <c r="S21" s="51" t="n"/>
       <c r="T21" s="51" t="n"/>
@@ -18732,7 +18804,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -18924,7 +18996,7 @@
         </is>
       </c>
       <c r="R26" s="42" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S26" s="52" t="inlineStr">
         <is>
@@ -19012,7 +19084,7 @@
         </is>
       </c>
       <c r="R27" s="42" t="n">
-        <v>-2.6</v>
+        <v>-1.5</v>
       </c>
       <c r="S27" s="53" t="inlineStr">
         <is>
@@ -19100,7 +19172,7 @@
         </is>
       </c>
       <c r="R28" s="42" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S28" s="53" t="inlineStr">
         <is>
@@ -19306,7 +19378,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R32" s="42" t="n"/>
+      <c r="R32" s="42" t="n">
+        <v>-15</v>
+      </c>
       <c r="S32" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -19317,7 +19391,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U32" s="51" t="n"/>
+      <c r="U32" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V32" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -19388,7 +19466,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R33" s="42" t="n"/>
+      <c r="R33" s="42" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="S33" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -19399,7 +19479,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U33" s="51" t="n"/>
+      <c r="U33" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V33" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -19470,7 +19554,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R34" s="42" t="n"/>
+      <c r="R34" s="42" t="n">
+        <v>1.5</v>
+      </c>
       <c r="S34" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -19481,7 +19567,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U34" s="51" t="n"/>
+      <c r="U34" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V34" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -19552,7 +19642,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R35" s="42" t="n"/>
+      <c r="R35" s="42" t="n">
+        <v>1.3</v>
+      </c>
       <c r="S35" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -19563,7 +19655,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U35" s="51" t="n"/>
+      <c r="U35" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V35" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -20246,7 +20342,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -20310,7 +20406,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-10.5</v>
+        <v>-10.6</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -20374,7 +20470,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-15</v>
+        <v>-14.7</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -20438,7 +20534,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-10.1</v>
+        <v>-10.2</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -20502,7 +20598,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -20566,7 +20662,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-15.4</v>
+        <v>-16.2</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -20622,7 +20718,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-33.1</v>
+        <v>-33.4</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -20678,7 +20774,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>-11.7</v>
+        <v>-11.5</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -20870,7 +20966,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="S39" s="53" t="inlineStr">
         <is>
@@ -20958,7 +21054,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="S40" s="52" t="inlineStr">
         <is>
@@ -21046,7 +21142,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -21134,7 +21230,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="S42" s="52" t="inlineStr">
         <is>
@@ -21222,7 +21318,7 @@
         </is>
       </c>
       <c r="R43" s="42" t="n">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
       <c r="S43" s="52" t="inlineStr">
         <is>
@@ -21310,7 +21406,7 @@
         </is>
       </c>
       <c r="R44" s="42" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="S44" s="52" t="inlineStr">
         <is>
@@ -21398,7 +21494,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -21605,7 +21701,7 @@
         </is>
       </c>
       <c r="R49" s="42" t="n">
-        <v>-15.5</v>
+        <v>-16.4</v>
       </c>
       <c r="S49" s="53" t="inlineStr">
         <is>
@@ -21692,7 +21788,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R50" s="42" t="n"/>
+      <c r="R50" s="42" t="n">
+        <v>-40.5</v>
+      </c>
       <c r="S50" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -21703,7 +21801,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U50" s="51" t="n"/>
+      <c r="U50" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V50" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -21775,7 +21877,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="S51" s="53" t="inlineStr">
         <is>
@@ -21863,7 +21965,7 @@
         </is>
       </c>
       <c r="R52" s="42" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="S52" s="52" t="inlineStr">
         <is>
@@ -21951,7 +22053,7 @@
         </is>
       </c>
       <c r="R53" s="42" t="n">
-        <v>-5.5</v>
+        <v>-4.9</v>
       </c>
       <c r="S53" s="52" t="inlineStr">
         <is>
@@ -22039,7 +22141,7 @@
         </is>
       </c>
       <c r="R54" s="42" t="n">
-        <v>-13.5</v>
+        <v>-13.3</v>
       </c>
       <c r="S54" s="53" t="inlineStr">
         <is>
@@ -22126,7 +22228,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R55" s="42" t="n"/>
+      <c r="R55" s="42" t="n">
+        <v>-13.8</v>
+      </c>
       <c r="S55" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -22137,7 +22241,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U55" s="51" t="n"/>
+      <c r="U55" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V55" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -22872,7 +22980,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -22928,7 +23036,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -22984,7 +23092,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-24</v>
+        <v>-23.7</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -23040,7 +23148,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -23096,7 +23204,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -23152,7 +23260,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -23344,7 +23452,7 @@
         </is>
       </c>
       <c r="R35" s="42" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.6</v>
       </c>
       <c r="S35" s="52" t="inlineStr">
         <is>
@@ -23432,7 +23540,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="S36" s="52" t="inlineStr">
         <is>
@@ -23520,7 +23628,7 @@
         </is>
       </c>
       <c r="R37" s="42" t="n">
-        <v>-5.8</v>
+        <v>-5.1</v>
       </c>
       <c r="S37" s="53" t="inlineStr">
         <is>
@@ -23608,7 +23716,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="S38" s="52" t="inlineStr">
         <is>
@@ -23696,7 +23804,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="S39" s="52" t="inlineStr">
         <is>
@@ -23784,7 +23892,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-14.1</v>
+        <v>-13.2</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -23990,7 +24098,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R44" s="42" t="n"/>
+      <c r="R44" s="42" t="n">
+        <v>2.2</v>
+      </c>
       <c r="S44" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -24001,7 +24111,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U44" s="51" t="n"/>
+      <c r="U44" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V44" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -24161,7 +24275,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>-14.2</v>
+        <v>-14.4</v>
       </c>
       <c r="S46" s="53" t="inlineStr">
         <is>
@@ -24248,7 +24362,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R47" s="42" t="n"/>
+      <c r="R47" s="42" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="S47" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -24259,7 +24375,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U47" s="51" t="n"/>
+      <c r="U47" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V47" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -24330,7 +24450,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R48" s="42" t="n"/>
+      <c r="R48" s="42" t="n">
+        <v>-19</v>
+      </c>
       <c r="S48" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -24341,7 +24463,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U48" s="51" t="n"/>
+      <c r="U48" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V48" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -24412,7 +24538,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R49" s="42" t="n"/>
+      <c r="R49" s="42" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="S49" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -24423,7 +24551,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U49" s="51" t="n"/>
+      <c r="U49" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V49" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -35381,7 +35513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -59866,7 +59998,7 @@
       <c r="P9" s="42" t="n"/>
       <c r="Q9" s="42" t="n"/>
       <c r="R9" s="42" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S9" s="51" t="n"/>
       <c r="T9" s="51" t="n"/>
@@ -59922,7 +60054,7 @@
       <c r="P10" s="42" t="n"/>
       <c r="Q10" s="42" t="n"/>
       <c r="R10" s="42" t="n">
-        <v>-33.1</v>
+        <v>-33.4</v>
       </c>
       <c r="S10" s="51" t="n"/>
       <c r="T10" s="51" t="n"/>
@@ -59986,7 +60118,7 @@
       <c r="P11" s="42" t="n"/>
       <c r="Q11" s="42" t="n"/>
       <c r="R11" s="42" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S11" s="51" t="n"/>
       <c r="T11" s="51" t="n"/>
@@ -60050,7 +60182,7 @@
       <c r="P12" s="42" t="n"/>
       <c r="Q12" s="42" t="n"/>
       <c r="R12" s="42" t="n">
-        <v>-17.6</v>
+        <v>-16.9</v>
       </c>
       <c r="S12" s="51" t="n"/>
       <c r="T12" s="51" t="n"/>
@@ -60106,7 +60238,7 @@
       <c r="P13" s="42" t="n"/>
       <c r="Q13" s="42" t="n"/>
       <c r="R13" s="42" t="n">
-        <v>-13.2</v>
+        <v>-13</v>
       </c>
       <c r="S13" s="51" t="n"/>
       <c r="T13" s="51" t="n"/>
@@ -60162,7 +60294,7 @@
       <c r="P14" s="42" t="n"/>
       <c r="Q14" s="42" t="n"/>
       <c r="R14" s="42" t="n">
-        <v>-30.3</v>
+        <v>-29.9</v>
       </c>
       <c r="S14" s="51" t="n"/>
       <c r="T14" s="51" t="n"/>
@@ -60218,7 +60350,7 @@
       <c r="P15" s="42" t="n"/>
       <c r="Q15" s="42" t="n"/>
       <c r="R15" s="42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="S15" s="51" t="n"/>
       <c r="T15" s="51" t="n"/>
@@ -60330,7 +60462,7 @@
       <c r="P17" s="42" t="n"/>
       <c r="Q17" s="42" t="n"/>
       <c r="R17" s="42" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="S17" s="51" t="n"/>
       <c r="T17" s="51" t="n"/>
@@ -60386,7 +60518,7 @@
       <c r="P18" s="42" t="n"/>
       <c r="Q18" s="42" t="n"/>
       <c r="R18" s="42" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="S18" s="51" t="n"/>
       <c r="T18" s="51" t="n"/>
@@ -60442,7 +60574,7 @@
       <c r="P19" s="42" t="n"/>
       <c r="Q19" s="42" t="n"/>
       <c r="R19" s="42" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="S19" s="51" t="n"/>
       <c r="T19" s="51" t="n"/>
@@ -60498,7 +60630,7 @@
       <c r="P20" s="42" t="n"/>
       <c r="Q20" s="42" t="n"/>
       <c r="R20" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S20" s="51" t="n"/>
       <c r="T20" s="51" t="n"/>
@@ -60554,7 +60686,7 @@
       <c r="P21" s="42" t="n"/>
       <c r="Q21" s="42" t="n"/>
       <c r="R21" s="42" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="S21" s="51" t="n"/>
       <c r="T21" s="51" t="n"/>
@@ -60610,7 +60742,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>-15.7</v>
+        <v>-14.8</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -60666,7 +60798,7 @@
       <c r="P23" s="42" t="n"/>
       <c r="Q23" s="42" t="n"/>
       <c r="R23" s="42" t="n">
-        <v>-11.4</v>
+        <v>-10.9</v>
       </c>
       <c r="S23" s="51" t="n"/>
       <c r="T23" s="51" t="n"/>
@@ -60722,7 +60854,7 @@
       <c r="P24" s="42" t="n"/>
       <c r="Q24" s="42" t="n"/>
       <c r="R24" s="42" t="n">
-        <v>-11</v>
+        <v>-11.7</v>
       </c>
       <c r="S24" s="51" t="n"/>
       <c r="T24" s="51" t="n"/>
@@ -60842,7 +60974,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -60906,7 +61038,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>-16.9</v>
+        <v>-15.6</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -60970,7 +61102,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-11.3</v>
+        <v>-10.7</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -61026,7 +61158,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-18.2</v>
+        <v>-18</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -61082,7 +61214,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -61138,7 +61270,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -61202,7 +61334,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -61322,7 +61454,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-8.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -61378,7 +61510,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -61406,43 +61538,35 @@
       </c>
       <c r="E36" s="42" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="F36" s="42" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="G36" s="42" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="H36" s="42" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="I36" s="42" t="n">
-        <v>-1.1</v>
-      </c>
+        <v>8.6</v>
+      </c>
+      <c r="H36" s="42" t="n"/>
+      <c r="I36" s="42" t="n"/>
       <c r="J36" s="42" t="n">
-        <v>-18.1</v>
+        <v>8.4</v>
       </c>
       <c r="K36" s="42" t="n">
-        <v>-1.4</v>
+        <v>-7.1</v>
       </c>
       <c r="L36" s="42" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="M36" s="42" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="N36" s="47" t="n">
-        <v>-4.8</v>
-      </c>
+        <v>51.7</v>
+      </c>
+      <c r="M36" s="42" t="n"/>
+      <c r="N36" s="42" t="n"/>
       <c r="O36" s="42" t="n"/>
       <c r="P36" s="42" t="n"/>
       <c r="Q36" s="42" t="n"/>
       <c r="R36" s="42" t="n">
-        <v>-15.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S36" s="51" t="n"/>
       <c r="T36" s="51" t="n"/>
@@ -61470,35 +61594,43 @@
       </c>
       <c r="E37" s="42" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="F37" s="42" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="G37" s="42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H37" s="42" t="n"/>
-      <c r="I37" s="42" t="n"/>
+        <v>-5.9</v>
+      </c>
+      <c r="H37" s="42" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I37" s="47" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J37" s="42" t="n">
-        <v>8.4</v>
+        <v>-5.4</v>
       </c>
       <c r="K37" s="42" t="n">
         <v>-7.1</v>
       </c>
       <c r="L37" s="42" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="M37" s="42" t="n"/>
-      <c r="N37" s="42" t="n"/>
+        <v>44.4</v>
+      </c>
+      <c r="M37" s="42" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="N37" s="47" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="O37" s="42" t="n"/>
       <c r="P37" s="42" t="n"/>
       <c r="Q37" s="42" t="n"/>
       <c r="R37" s="42" t="n">
-        <v>8.9</v>
+        <v>-7.8</v>
       </c>
       <c r="S37" s="51" t="n"/>
       <c r="T37" s="51" t="n"/>
@@ -61511,7 +61643,7 @@
       </c>
       <c r="B38" s="42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C38" s="42" t="inlineStr">
@@ -61526,43 +61658,43 @@
       </c>
       <c r="E38" s="42" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="F38" s="42" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G38" s="42" t="n">
-        <v>-5.9</v>
+        <v>-11.4</v>
       </c>
       <c r="H38" s="42" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I38" s="47" t="n">
-        <v>2.4</v>
+        <v>-12.5</v>
+      </c>
+      <c r="I38" s="42" t="n">
+        <v>-1.1</v>
       </c>
       <c r="J38" s="42" t="n">
-        <v>-5.4</v>
+        <v>-18.1</v>
       </c>
       <c r="K38" s="42" t="n">
-        <v>-7.1</v>
+        <v>-1.4</v>
       </c>
       <c r="L38" s="42" t="n">
-        <v>44.4</v>
+        <v>53.7</v>
       </c>
       <c r="M38" s="42" t="n">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="N38" s="47" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
       <c r="O38" s="42" t="n"/>
       <c r="P38" s="42" t="n"/>
       <c r="Q38" s="42" t="n"/>
       <c r="R38" s="42" t="n">
-        <v>-7.6</v>
+        <v>-15.2</v>
       </c>
       <c r="S38" s="51" t="n"/>
       <c r="T38" s="51" t="n"/>
@@ -61626,7 +61758,7 @@
       <c r="P39" s="42" t="n"/>
       <c r="Q39" s="42" t="n"/>
       <c r="R39" s="42" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="S39" s="51" t="n"/>
       <c r="T39" s="51" t="n"/>
@@ -61690,7 +61822,7 @@
       <c r="P40" s="42" t="n"/>
       <c r="Q40" s="42" t="n"/>
       <c r="R40" s="42" t="n">
-        <v>-11.4</v>
+        <v>-12.2</v>
       </c>
       <c r="S40" s="51" t="n"/>
       <c r="T40" s="51" t="n"/>
@@ -61754,7 +61886,7 @@
       <c r="P41" s="42" t="n"/>
       <c r="Q41" s="42" t="n"/>
       <c r="R41" s="42" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S41" s="51" t="n"/>
       <c r="T41" s="51" t="n"/>
@@ -61818,7 +61950,7 @@
       <c r="P42" s="42" t="n"/>
       <c r="Q42" s="42" t="n"/>
       <c r="R42" s="42" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S42" s="51" t="n"/>
       <c r="T42" s="51" t="n"/>
@@ -61874,7 +62006,7 @@
       <c r="P43" s="42" t="n"/>
       <c r="Q43" s="42" t="n"/>
       <c r="R43" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="S43" s="51" t="n"/>
       <c r="T43" s="51" t="n"/>
@@ -61930,7 +62062,7 @@
       <c r="P44" s="42" t="n"/>
       <c r="Q44" s="42" t="n"/>
       <c r="R44" s="42" t="n">
-        <v>-14.8</v>
+        <v>-14</v>
       </c>
       <c r="S44" s="51" t="n"/>
       <c r="T44" s="51" t="n"/>
@@ -61986,7 +62118,7 @@
       <c r="P45" s="42" t="n"/>
       <c r="Q45" s="42" t="n"/>
       <c r="R45" s="42" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="S45" s="51" t="n"/>
       <c r="T45" s="51" t="n"/>
@@ -62042,7 +62174,7 @@
       <c r="P46" s="42" t="n"/>
       <c r="Q46" s="42" t="n"/>
       <c r="R46" s="42" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="S46" s="51" t="n"/>
       <c r="T46" s="51" t="n"/>
@@ -62098,7 +62230,7 @@
       <c r="P47" s="42" t="n"/>
       <c r="Q47" s="42" t="n"/>
       <c r="R47" s="42" t="n">
-        <v>-10.3</v>
+        <v>-11</v>
       </c>
       <c r="S47" s="51" t="n"/>
       <c r="T47" s="51" t="n"/>
@@ -62154,7 +62286,7 @@
       <c r="P48" s="42" t="n"/>
       <c r="Q48" s="42" t="n"/>
       <c r="R48" s="42" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="S48" s="51" t="n"/>
       <c r="T48" s="51" t="n"/>
@@ -62210,7 +62342,7 @@
       <c r="P49" s="42" t="n"/>
       <c r="Q49" s="42" t="n"/>
       <c r="R49" s="42" t="n">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="S49" s="51" t="n"/>
       <c r="T49" s="51" t="n"/>
@@ -62266,7 +62398,7 @@
       <c r="P50" s="42" t="n"/>
       <c r="Q50" s="42" t="n"/>
       <c r="R50" s="42" t="n">
-        <v>-18.2</v>
+        <v>-19</v>
       </c>
       <c r="S50" s="51" t="n"/>
       <c r="T50" s="51" t="n"/>
@@ -62322,7 +62454,7 @@
       <c r="P51" s="42" t="n"/>
       <c r="Q51" s="42" t="n"/>
       <c r="R51" s="42" t="n">
-        <v>-6.6</v>
+        <v>-6.3</v>
       </c>
       <c r="S51" s="51" t="n"/>
       <c r="T51" s="51" t="n"/>
@@ -62378,7 +62510,7 @@
       <c r="P52" s="42" t="n"/>
       <c r="Q52" s="42" t="n"/>
       <c r="R52" s="42" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S52" s="51" t="n"/>
       <c r="T52" s="51" t="n"/>
@@ -62434,7 +62566,7 @@
       <c r="P53" s="42" t="n"/>
       <c r="Q53" s="42" t="n"/>
       <c r="R53" s="42" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S53" s="51" t="n"/>
       <c r="T53" s="51" t="n"/>
@@ -62498,7 +62630,7 @@
       <c r="P54" s="42" t="n"/>
       <c r="Q54" s="42" t="n"/>
       <c r="R54" s="42" t="n">
-        <v>-14.5</v>
+        <v>-15.2</v>
       </c>
       <c r="S54" s="51" t="n"/>
       <c r="T54" s="51" t="n"/>
@@ -62554,7 +62686,7 @@
       <c r="P55" s="42" t="n"/>
       <c r="Q55" s="42" t="n"/>
       <c r="R55" s="42" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
       <c r="S55" s="51" t="n"/>
       <c r="T55" s="51" t="n"/>
@@ -62610,7 +62742,7 @@
       <c r="P56" s="42" t="n"/>
       <c r="Q56" s="42" t="n"/>
       <c r="R56" s="42" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="S56" s="51" t="n"/>
       <c r="T56" s="51" t="n"/>
@@ -62674,7 +62806,7 @@
       <c r="P57" s="42" t="n"/>
       <c r="Q57" s="42" t="n"/>
       <c r="R57" s="42" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="S57" s="51" t="n"/>
       <c r="T57" s="51" t="n"/>
@@ -62738,7 +62870,7 @@
       <c r="P58" s="42" t="n"/>
       <c r="Q58" s="42" t="n"/>
       <c r="R58" s="42" t="n">
-        <v>-10.5</v>
+        <v>-10.6</v>
       </c>
       <c r="S58" s="51" t="n"/>
       <c r="T58" s="51" t="n"/>
@@ -62802,7 +62934,7 @@
       <c r="P59" s="42" t="n"/>
       <c r="Q59" s="42" t="n"/>
       <c r="R59" s="42" t="n">
-        <v>-15</v>
+        <v>-14.7</v>
       </c>
       <c r="S59" s="51" t="n"/>
       <c r="T59" s="51" t="n"/>
@@ -62866,7 +62998,7 @@
       <c r="P60" s="42" t="n"/>
       <c r="Q60" s="42" t="n"/>
       <c r="R60" s="42" t="n">
-        <v>-10.1</v>
+        <v>-10.2</v>
       </c>
       <c r="S60" s="51" t="n"/>
       <c r="T60" s="51" t="n"/>
@@ -62930,7 +63062,7 @@
       <c r="P61" s="42" t="n"/>
       <c r="Q61" s="42" t="n"/>
       <c r="R61" s="42" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S61" s="51" t="n"/>
       <c r="T61" s="51" t="n"/>
@@ -62994,7 +63126,7 @@
       <c r="P62" s="42" t="n"/>
       <c r="Q62" s="42" t="n"/>
       <c r="R62" s="42" t="n">
-        <v>-15.4</v>
+        <v>-16.2</v>
       </c>
       <c r="S62" s="51" t="n"/>
       <c r="T62" s="51" t="n"/>
@@ -63050,7 +63182,7 @@
       <c r="P63" s="42" t="n"/>
       <c r="Q63" s="42" t="n"/>
       <c r="R63" s="42" t="n">
-        <v>-33.1</v>
+        <v>-33.4</v>
       </c>
       <c r="S63" s="51" t="n"/>
       <c r="T63" s="51" t="n"/>
@@ -63106,7 +63238,7 @@
       <c r="P64" s="42" t="n"/>
       <c r="Q64" s="42" t="n"/>
       <c r="R64" s="42" t="n">
-        <v>-11.7</v>
+        <v>-11.5</v>
       </c>
       <c r="S64" s="51" t="n"/>
       <c r="T64" s="51" t="n"/>
@@ -63162,7 +63294,7 @@
       <c r="P65" s="42" t="n"/>
       <c r="Q65" s="42" t="n"/>
       <c r="R65" s="42" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="S65" s="51" t="n"/>
       <c r="T65" s="51" t="n"/>
@@ -63218,7 +63350,7 @@
       <c r="P66" s="42" t="n"/>
       <c r="Q66" s="42" t="n"/>
       <c r="R66" s="42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="S66" s="51" t="n"/>
       <c r="T66" s="51" t="n"/>
@@ -63274,7 +63406,7 @@
       <c r="P67" s="42" t="n"/>
       <c r="Q67" s="42" t="n"/>
       <c r="R67" s="42" t="n">
-        <v>-24</v>
+        <v>-23.7</v>
       </c>
       <c r="S67" s="51" t="n"/>
       <c r="T67" s="51" t="n"/>
@@ -63330,7 +63462,7 @@
       <c r="P68" s="42" t="n"/>
       <c r="Q68" s="42" t="n"/>
       <c r="R68" s="42" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="S68" s="51" t="n"/>
       <c r="T68" s="51" t="n"/>
@@ -63386,7 +63518,7 @@
       <c r="P69" s="42" t="n"/>
       <c r="Q69" s="42" t="n"/>
       <c r="R69" s="42" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="S69" s="51" t="n"/>
       <c r="T69" s="51" t="n"/>
@@ -63442,7 +63574,7 @@
       <c r="P70" s="42" t="n"/>
       <c r="Q70" s="42" t="n"/>
       <c r="R70" s="42" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="S70" s="51" t="n"/>
       <c r="T70" s="51" t="n"/>
@@ -63633,7 +63765,7 @@
         </is>
       </c>
       <c r="R74" s="42" t="n">
-        <v>-4.5</v>
+        <v>-5.4</v>
       </c>
       <c r="S74" s="53" t="inlineStr">
         <is>
@@ -63721,7 +63853,7 @@
         </is>
       </c>
       <c r="R75" s="42" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="S75" s="53" t="inlineStr">
         <is>
@@ -63809,7 +63941,7 @@
         </is>
       </c>
       <c r="R76" s="42" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="S76" s="52" t="inlineStr">
         <is>
@@ -63897,7 +64029,7 @@
         </is>
       </c>
       <c r="R77" s="42" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="S77" s="53" t="inlineStr">
         <is>
@@ -63985,7 +64117,7 @@
         </is>
       </c>
       <c r="R78" s="42" t="n">
-        <v>-13.4</v>
+        <v>-13.5</v>
       </c>
       <c r="S78" s="52" t="inlineStr">
         <is>
@@ -64073,7 +64205,7 @@
         </is>
       </c>
       <c r="R79" s="42" t="n">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="S79" s="52" t="inlineStr">
         <is>
@@ -64161,7 +64293,7 @@
         </is>
       </c>
       <c r="R80" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="S80" s="52" t="inlineStr">
         <is>
@@ -64249,7 +64381,7 @@
         </is>
       </c>
       <c r="R81" s="42" t="n">
-        <v>-4.5</v>
+        <v>-4.8</v>
       </c>
       <c r="S81" s="54" t="inlineStr">
         <is>
@@ -64337,7 +64469,7 @@
         </is>
       </c>
       <c r="R82" s="42" t="n">
-        <v>-12.1</v>
+        <v>-12.7</v>
       </c>
       <c r="S82" s="53" t="inlineStr">
         <is>
@@ -64425,7 +64557,7 @@
         </is>
       </c>
       <c r="R83" s="42" t="n">
-        <v>-12.4</v>
+        <v>-11</v>
       </c>
       <c r="S83" s="53" t="inlineStr">
         <is>
@@ -64513,7 +64645,7 @@
         </is>
       </c>
       <c r="R84" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="S84" s="53" t="inlineStr">
         <is>
@@ -64601,7 +64733,7 @@
         </is>
       </c>
       <c r="R85" s="42" t="n">
-        <v>-25.8</v>
+        <v>-25.3</v>
       </c>
       <c r="S85" s="53" t="inlineStr">
         <is>
@@ -64689,7 +64821,7 @@
         </is>
       </c>
       <c r="R86" s="42" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="S86" s="52" t="inlineStr">
         <is>
@@ -64777,7 +64909,7 @@
         </is>
       </c>
       <c r="R87" s="42" t="n">
-        <v>-13.8</v>
+        <v>-14.7</v>
       </c>
       <c r="S87" s="53" t="inlineStr">
         <is>
@@ -64865,7 +64997,7 @@
         </is>
       </c>
       <c r="R88" s="42" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
       <c r="S88" s="52" t="inlineStr">
         <is>
@@ -64877,9 +65009,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U88" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U88" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V88" s="53" t="inlineStr">
@@ -64953,7 +65085,7 @@
         </is>
       </c>
       <c r="R89" s="42" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="S89" s="52" t="inlineStr">
         <is>
@@ -65041,7 +65173,7 @@
         </is>
       </c>
       <c r="R90" s="42" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="S90" s="53" t="inlineStr">
         <is>
@@ -65129,7 +65261,7 @@
         </is>
       </c>
       <c r="R91" s="42" t="n">
-        <v>-14.9</v>
+        <v>-14.5</v>
       </c>
       <c r="S91" s="53" t="inlineStr">
         <is>
@@ -65217,7 +65349,7 @@
         </is>
       </c>
       <c r="R92" s="42" t="n">
-        <v>-18.8</v>
+        <v>-19.7</v>
       </c>
       <c r="S92" s="53" t="inlineStr">
         <is>
@@ -65305,7 +65437,7 @@
         </is>
       </c>
       <c r="R93" s="42" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="S93" s="52" t="inlineStr">
         <is>
@@ -65393,7 +65525,7 @@
         </is>
       </c>
       <c r="R94" s="42" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="S94" s="52" t="inlineStr">
         <is>
@@ -65481,7 +65613,7 @@
         </is>
       </c>
       <c r="R95" s="42" t="n">
-        <v>-24.1</v>
+        <v>-26.2</v>
       </c>
       <c r="S95" s="52" t="inlineStr">
         <is>
@@ -65657,7 +65789,7 @@
         </is>
       </c>
       <c r="R97" s="42" t="n">
-        <v>-24.6</v>
+        <v>-25.6</v>
       </c>
       <c r="S97" s="52" t="inlineStr">
         <is>
@@ -65745,7 +65877,7 @@
         </is>
       </c>
       <c r="R98" s="42" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="S98" s="52" t="inlineStr">
         <is>
@@ -65833,7 +65965,7 @@
         </is>
       </c>
       <c r="R99" s="42" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="S99" s="53" t="inlineStr">
         <is>
@@ -65921,7 +66053,7 @@
         </is>
       </c>
       <c r="R100" s="42" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="S100" s="52" t="inlineStr">
         <is>
@@ -66009,7 +66141,7 @@
         </is>
       </c>
       <c r="R101" s="42" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="S101" s="52" t="inlineStr">
         <is>
@@ -66097,7 +66229,7 @@
         </is>
       </c>
       <c r="R102" s="42" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S102" s="52" t="inlineStr">
         <is>
@@ -66185,7 +66317,7 @@
         </is>
       </c>
       <c r="R103" s="42" t="n">
-        <v>-13.2</v>
+        <v>-11.8</v>
       </c>
       <c r="S103" s="53" t="inlineStr">
         <is>
@@ -66197,9 +66329,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U103" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U103" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V103" s="52" t="inlineStr">
@@ -66273,7 +66405,7 @@
         </is>
       </c>
       <c r="R104" s="42" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="S104" s="53" t="inlineStr">
         <is>
@@ -66361,7 +66493,7 @@
         </is>
       </c>
       <c r="R105" s="42" t="n">
-        <v>-37.8</v>
+        <v>-36.9</v>
       </c>
       <c r="S105" s="52" t="inlineStr">
         <is>
@@ -66373,9 +66505,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U105" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U105" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V105" s="52" t="inlineStr">
@@ -66449,7 +66581,7 @@
         </is>
       </c>
       <c r="R106" s="42" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="S106" s="53" t="inlineStr">
         <is>
@@ -66537,7 +66669,7 @@
         </is>
       </c>
       <c r="R107" s="42" t="n">
-        <v>-9.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="S107" s="53" t="inlineStr">
         <is>
@@ -66625,7 +66757,7 @@
         </is>
       </c>
       <c r="R108" s="42" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S108" s="52" t="inlineStr">
         <is>
@@ -66801,7 +66933,7 @@
         </is>
       </c>
       <c r="R110" s="42" t="n">
-        <v>-14.4</v>
+        <v>-13.6</v>
       </c>
       <c r="S110" s="53" t="inlineStr">
         <is>
@@ -66889,7 +67021,7 @@
         </is>
       </c>
       <c r="R111" s="42" t="n">
-        <v>-15.7</v>
+        <v>-15.5</v>
       </c>
       <c r="S111" s="53" t="inlineStr">
         <is>
@@ -66977,7 +67109,7 @@
         </is>
       </c>
       <c r="R112" s="42" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="S112" s="53" t="inlineStr">
         <is>
@@ -67065,7 +67197,7 @@
         </is>
       </c>
       <c r="R113" s="42" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="S113" s="52" t="inlineStr">
         <is>
@@ -67153,7 +67285,7 @@
         </is>
       </c>
       <c r="R114" s="42" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="S114" s="52" t="inlineStr">
         <is>
@@ -67212,7 +67344,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I115" s="42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J115" s="42" t="n">
         <v>5</v>
@@ -67241,7 +67373,7 @@
         </is>
       </c>
       <c r="R115" s="42" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="S115" s="53" t="inlineStr">
         <is>
@@ -67329,7 +67461,7 @@
         </is>
       </c>
       <c r="R116" s="42" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S116" s="52" t="inlineStr">
         <is>
@@ -67417,7 +67549,7 @@
         </is>
       </c>
       <c r="R117" s="42" t="n">
-        <v>-2.6</v>
+        <v>-1.5</v>
       </c>
       <c r="S117" s="53" t="inlineStr">
         <is>
@@ -67505,7 +67637,7 @@
         </is>
       </c>
       <c r="R118" s="42" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S118" s="53" t="inlineStr">
         <is>
@@ -67593,7 +67725,7 @@
         </is>
       </c>
       <c r="R119" s="42" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="S119" s="53" t="inlineStr">
         <is>
@@ -67681,7 +67813,7 @@
         </is>
       </c>
       <c r="R120" s="42" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="S120" s="52" t="inlineStr">
         <is>
@@ -67769,7 +67901,7 @@
         </is>
       </c>
       <c r="R121" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="S121" s="53" t="inlineStr">
         <is>
@@ -67857,7 +67989,7 @@
         </is>
       </c>
       <c r="R122" s="42" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="S122" s="52" t="inlineStr">
         <is>
@@ -67945,7 +68077,7 @@
         </is>
       </c>
       <c r="R123" s="42" t="n">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
       <c r="S123" s="52" t="inlineStr">
         <is>
@@ -68033,7 +68165,7 @@
         </is>
       </c>
       <c r="R124" s="42" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="S124" s="52" t="inlineStr">
         <is>
@@ -68121,7 +68253,7 @@
         </is>
       </c>
       <c r="R125" s="42" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="S125" s="52" t="inlineStr">
         <is>
@@ -68209,7 +68341,7 @@
         </is>
       </c>
       <c r="R126" s="42" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.6</v>
       </c>
       <c r="S126" s="52" t="inlineStr">
         <is>
@@ -68297,7 +68429,7 @@
         </is>
       </c>
       <c r="R127" s="42" t="n">
-        <v>0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="S127" s="52" t="inlineStr">
         <is>
@@ -68385,7 +68517,7 @@
         </is>
       </c>
       <c r="R128" s="42" t="n">
-        <v>-5.8</v>
+        <v>-5.1</v>
       </c>
       <c r="S128" s="53" t="inlineStr">
         <is>
@@ -68473,7 +68605,7 @@
         </is>
       </c>
       <c r="R129" s="42" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="S129" s="52" t="inlineStr">
         <is>
@@ -68561,7 +68693,7 @@
         </is>
       </c>
       <c r="R130" s="42" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="S130" s="52" t="inlineStr">
         <is>
@@ -68649,7 +68781,7 @@
         </is>
       </c>
       <c r="R131" s="42" t="n">
-        <v>-14.1</v>
+        <v>-13.2</v>
       </c>
       <c r="S131" s="53" t="inlineStr">
         <is>
@@ -68856,7 +68988,7 @@
         </is>
       </c>
       <c r="R135" s="42" t="n">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="S135" s="53" t="inlineStr">
         <is>
@@ -68868,9 +69000,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U135" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U135" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V135" s="53" t="inlineStr">
@@ -68943,7 +69075,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R136" s="42" t="n"/>
+      <c r="R136" s="42" t="n">
+        <v>6.7</v>
+      </c>
       <c r="S136" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -68954,7 +69088,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U136" s="51" t="n"/>
+      <c r="U136" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V136" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -69026,7 +69164,7 @@
         </is>
       </c>
       <c r="R137" s="42" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S137" s="52" t="inlineStr">
         <is>
@@ -69114,7 +69252,7 @@
         </is>
       </c>
       <c r="R138" s="42" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="S138" s="52" t="inlineStr">
         <is>
@@ -69202,7 +69340,7 @@
         </is>
       </c>
       <c r="R139" s="42" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="S139" s="52" t="inlineStr">
         <is>
@@ -69290,7 +69428,7 @@
         </is>
       </c>
       <c r="R140" s="42" t="n">
-        <v>-20.8</v>
+        <v>-20.1</v>
       </c>
       <c r="S140" s="52" t="inlineStr">
         <is>
@@ -69302,9 +69440,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U140" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U140" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V140" s="53" t="inlineStr">
@@ -69378,7 +69516,7 @@
         </is>
       </c>
       <c r="R141" s="42" t="n">
-        <v>-8</v>
+        <v>-8.1</v>
       </c>
       <c r="S141" s="53" t="inlineStr">
         <is>
@@ -69466,7 +69604,7 @@
         </is>
       </c>
       <c r="R142" s="42" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="S142" s="52" t="inlineStr">
         <is>
@@ -69554,7 +69692,7 @@
         </is>
       </c>
       <c r="R143" s="42" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="S143" s="53" t="inlineStr">
         <is>
@@ -69641,7 +69779,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R144" s="42" t="n"/>
+      <c r="R144" s="42" t="n">
+        <v>-32.2</v>
+      </c>
       <c r="S144" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -69652,7 +69792,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U144" s="51" t="n"/>
+      <c r="U144" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V144" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -69723,7 +69867,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R145" s="42" t="n"/>
+      <c r="R145" s="42" t="n">
+        <v>15.9</v>
+      </c>
       <c r="S145" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -69734,7 +69880,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U145" s="51" t="n"/>
+      <c r="U145" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V145" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -69805,7 +69955,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R146" s="42" t="n"/>
+      <c r="R146" s="42" t="n">
+        <v>-13.6</v>
+      </c>
       <c r="S146" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -69816,7 +69968,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U146" s="51" t="n"/>
+      <c r="U146" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V146" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -69888,7 +70044,7 @@
         </is>
       </c>
       <c r="R147" s="42" t="n">
-        <v>-24</v>
+        <v>-23.8</v>
       </c>
       <c r="S147" s="52" t="inlineStr">
         <is>
@@ -69975,7 +70131,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R148" s="42" t="n"/>
+      <c r="R148" s="42" t="n">
+        <v>17.7</v>
+      </c>
       <c r="S148" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -69986,7 +70144,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U148" s="51" t="n"/>
+      <c r="U148" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V148" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -70058,7 +70220,7 @@
         </is>
       </c>
       <c r="R149" s="42" t="n">
-        <v>-12.8</v>
+        <v>-12.3</v>
       </c>
       <c r="S149" s="52" t="inlineStr">
         <is>
@@ -70234,7 +70396,7 @@
         </is>
       </c>
       <c r="R151" s="42" t="n">
-        <v>-13.7</v>
+        <v>-13</v>
       </c>
       <c r="S151" s="53" t="inlineStr">
         <is>
@@ -70321,7 +70483,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R152" s="42" t="n"/>
+      <c r="R152" s="42" t="n">
+        <v>6.2</v>
+      </c>
       <c r="S152" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -70332,7 +70496,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U152" s="51" t="n"/>
+      <c r="U152" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V152" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -70403,7 +70571,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R153" s="42" t="n"/>
+      <c r="R153" s="42" t="n">
+        <v>-13.1</v>
+      </c>
       <c r="S153" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -70414,7 +70584,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U153" s="51" t="n"/>
+      <c r="U153" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V153" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -70485,7 +70659,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R154" s="42" t="n"/>
+      <c r="R154" s="42" t="n">
+        <v>-7.8</v>
+      </c>
       <c r="S154" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -70496,7 +70672,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U154" s="51" t="n"/>
+      <c r="U154" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V154" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -70568,7 +70748,7 @@
         </is>
       </c>
       <c r="R155" s="42" t="n">
-        <v>-12.5</v>
+        <v>-12.3</v>
       </c>
       <c r="S155" s="52" t="inlineStr">
         <is>
@@ -70656,7 +70836,7 @@
         </is>
       </c>
       <c r="R156" s="42" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="S156" s="52" t="inlineStr">
         <is>
@@ -70744,7 +70924,7 @@
         </is>
       </c>
       <c r="R157" s="42" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="S157" s="53" t="inlineStr">
         <is>
@@ -70832,7 +71012,7 @@
         </is>
       </c>
       <c r="R158" s="42" t="n">
-        <v>-11.2</v>
+        <v>-11.3</v>
       </c>
       <c r="S158" s="53" t="inlineStr">
         <is>
@@ -70920,7 +71100,7 @@
         </is>
       </c>
       <c r="R159" s="42" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S159" s="52" t="inlineStr">
         <is>
@@ -71007,7 +71187,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R160" s="42" t="n"/>
+      <c r="R160" s="42" t="n">
+        <v>-4.7</v>
+      </c>
       <c r="S160" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -71018,7 +71200,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U160" s="51" t="n"/>
+      <c r="U160" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V160" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -71090,7 +71276,7 @@
         </is>
       </c>
       <c r="R161" s="42" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="S161" s="52" t="inlineStr">
         <is>
@@ -71177,7 +71363,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R162" s="42" t="n"/>
+      <c r="R162" s="42" t="n">
+        <v>16.8</v>
+      </c>
       <c r="S162" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -71188,7 +71376,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U162" s="51" t="n"/>
+      <c r="U162" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V162" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -71260,7 +71452,7 @@
         </is>
       </c>
       <c r="R163" s="42" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="S163" s="52" t="inlineStr">
         <is>
@@ -71348,7 +71540,7 @@
         </is>
       </c>
       <c r="R164" s="42" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="S164" s="52" t="inlineStr">
         <is>
@@ -71436,7 +71628,7 @@
         </is>
       </c>
       <c r="R165" s="42" t="n">
-        <v>-6.2</v>
+        <v>-6.8</v>
       </c>
       <c r="S165" s="53" t="inlineStr">
         <is>
@@ -71524,7 +71716,7 @@
         </is>
       </c>
       <c r="R166" s="42" t="n">
-        <v>15.3</v>
+        <v>13.7</v>
       </c>
       <c r="S166" s="52" t="inlineStr">
         <is>
@@ -71612,7 +71804,7 @@
         </is>
       </c>
       <c r="R167" s="42" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="S167" s="52" t="inlineStr">
         <is>
@@ -71700,7 +71892,7 @@
         </is>
       </c>
       <c r="R168" s="42" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
       <c r="S168" s="53" t="inlineStr">
         <is>
@@ -71788,7 +71980,7 @@
         </is>
       </c>
       <c r="R169" s="42" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="S169" s="52" t="inlineStr">
         <is>
@@ -71876,7 +72068,7 @@
         </is>
       </c>
       <c r="R170" s="42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="S170" s="53" t="inlineStr">
         <is>
@@ -71964,7 +72156,7 @@
         </is>
       </c>
       <c r="R171" s="42" t="n">
-        <v>-11</v>
+        <v>-11.1</v>
       </c>
       <c r="S171" s="52" t="inlineStr">
         <is>
@@ -72052,7 +72244,7 @@
         </is>
       </c>
       <c r="R172" s="42" t="n">
-        <v>-2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="S172" s="52" t="inlineStr">
         <is>
@@ -72064,9 +72256,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U172" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U172" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V172" s="53" t="inlineStr">
@@ -72140,7 +72332,7 @@
         </is>
       </c>
       <c r="R173" s="42" t="n">
-        <v>-20.7</v>
+        <v>-22</v>
       </c>
       <c r="S173" s="53" t="inlineStr">
         <is>
@@ -72228,7 +72420,7 @@
         </is>
       </c>
       <c r="R174" s="42" t="n">
-        <v>-21.1</v>
+        <v>-21.8</v>
       </c>
       <c r="S174" s="53" t="inlineStr">
         <is>
@@ -72316,7 +72508,7 @@
         </is>
       </c>
       <c r="R175" s="42" t="n">
-        <v>-6.8</v>
+        <v>-7</v>
       </c>
       <c r="S175" s="53" t="inlineStr">
         <is>
@@ -72403,7 +72595,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R176" s="42" t="n"/>
+      <c r="R176" s="42" t="n">
+        <v>-7.3</v>
+      </c>
       <c r="S176" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -72414,7 +72608,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U176" s="51" t="n"/>
+      <c r="U176" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V176" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -72485,7 +72683,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R177" s="42" t="n"/>
+      <c r="R177" s="42" t="n">
+        <v>-15</v>
+      </c>
       <c r="S177" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -72496,7 +72696,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U177" s="51" t="n"/>
+      <c r="U177" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V177" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -72567,7 +72771,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R178" s="42" t="n"/>
+      <c r="R178" s="42" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="S178" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -72578,7 +72784,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U178" s="51" t="n"/>
+      <c r="U178" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V178" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -72649,7 +72859,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R179" s="42" t="n"/>
+      <c r="R179" s="42" t="n">
+        <v>1.5</v>
+      </c>
       <c r="S179" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -72660,7 +72872,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U179" s="51" t="n"/>
+      <c r="U179" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V179" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -72731,7 +72947,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R180" s="42" t="n"/>
+      <c r="R180" s="42" t="n">
+        <v>1.3</v>
+      </c>
       <c r="S180" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -72742,7 +72960,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U180" s="51" t="n"/>
+      <c r="U180" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V180" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -72814,7 +73036,7 @@
         </is>
       </c>
       <c r="R181" s="42" t="n">
-        <v>-15.5</v>
+        <v>-16.4</v>
       </c>
       <c r="S181" s="53" t="inlineStr">
         <is>
@@ -72901,7 +73123,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R182" s="42" t="n"/>
+      <c r="R182" s="42" t="n">
+        <v>-40.5</v>
+      </c>
       <c r="S182" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -72912,7 +73136,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U182" s="51" t="n"/>
+      <c r="U182" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V182" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -72984,7 +73212,7 @@
         </is>
       </c>
       <c r="R183" s="42" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="S183" s="53" t="inlineStr">
         <is>
@@ -73072,7 +73300,7 @@
         </is>
       </c>
       <c r="R184" s="42" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="S184" s="52" t="inlineStr">
         <is>
@@ -73160,7 +73388,7 @@
         </is>
       </c>
       <c r="R185" s="42" t="n">
-        <v>-5.5</v>
+        <v>-4.9</v>
       </c>
       <c r="S185" s="52" t="inlineStr">
         <is>
@@ -73248,7 +73476,7 @@
         </is>
       </c>
       <c r="R186" s="42" t="n">
-        <v>-13.5</v>
+        <v>-13.3</v>
       </c>
       <c r="S186" s="53" t="inlineStr">
         <is>
@@ -73335,7 +73563,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R187" s="42" t="n"/>
+      <c r="R187" s="42" t="n">
+        <v>-13.8</v>
+      </c>
       <c r="S187" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -73346,7 +73576,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U187" s="51" t="n"/>
+      <c r="U187" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V187" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -73417,7 +73651,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R188" s="42" t="n"/>
+      <c r="R188" s="42" t="n">
+        <v>2.2</v>
+      </c>
       <c r="S188" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -73428,7 +73664,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U188" s="51" t="n"/>
+      <c r="U188" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V188" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -73588,7 +73828,7 @@
         </is>
       </c>
       <c r="R190" s="42" t="n">
-        <v>-14.2</v>
+        <v>-14.4</v>
       </c>
       <c r="S190" s="53" t="inlineStr">
         <is>
@@ -73675,7 +73915,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="R191" s="42" t="n"/>
+      <c r="R191" s="42" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="S191" s="52" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -73686,7 +73928,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U191" s="51" t="n"/>
+      <c r="U191" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V191" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -73757,7 +74003,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R192" s="42" t="n"/>
+      <c r="R192" s="42" t="n">
+        <v>-19</v>
+      </c>
       <c r="S192" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -73768,7 +74016,11 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U192" s="51" t="n"/>
+      <c r="U192" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="V192" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -73839,7 +74091,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="R193" s="42" t="n"/>
+      <c r="R193" s="42" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="S193" s="53" t="inlineStr">
         <is>
           <t>Win</t>
@@ -73850,7 +74104,11 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U193" s="51" t="n"/>
+      <c r="U193" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="V193" s="52" t="inlineStr">
         <is>
           <t>Loss</t>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1632,7 +1632,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -1688,7 +1688,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-33.7</v>
+        <v>-33.4</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -1752,7 +1752,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-9.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -1816,7 +1816,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-17</v>
+        <v>-17.6</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -1880,7 +1880,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-12.4</v>
+        <v>-12.5</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-30.1</v>
+        <v>-29.9</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -2064,7 +2064,7 @@
       <c r="P36" s="42" t="n"/>
       <c r="Q36" s="42" t="n"/>
       <c r="R36" s="42" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="S36" s="51" t="n"/>
       <c r="T36" s="51" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="P37" s="42" t="n"/>
       <c r="Q37" s="42" t="n"/>
       <c r="R37" s="42" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" s="51" t="n"/>
       <c r="T37" s="51" t="n"/>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-5.4</v>
+        <v>-5.6</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="R43" s="42" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="S43" s="52" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="R44" s="42" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="S44" s="53" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>-13.5</v>
+        <v>-13.2</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>-4.8</v>
+        <v>-4.3</v>
       </c>
       <c r="S46" s="52" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>-36.9</v>
+        <v>-37.5</v>
       </c>
       <c r="S47" s="52" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="S51" s="53" t="inlineStr">
         <is>
@@ -3067,9 +3067,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U51" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U51" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V51" s="53" t="inlineStr">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="R52" s="42" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="S52" s="53" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="R54" s="42" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="S54" s="52" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="R55" s="42" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="S55" s="52" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="R56" s="42" t="n">
-        <v>-20.1</v>
+        <v>-20.8</v>
       </c>
       <c r="S56" s="52" t="inlineStr">
         <is>
@@ -3507,9 +3507,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U56" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U56" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V56" s="53" t="inlineStr">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="R57" s="42" t="n">
-        <v>-8.1</v>
+        <v>-7.6</v>
       </c>
       <c r="S57" s="53" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="R58" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="S58" s="53" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="R59" s="42" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="S59" s="53" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -4542,7 +4542,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-8.9</v>
+        <v>-7.5</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -4606,7 +4606,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -4670,7 +4670,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-14.7</v>
+        <v>-14.9</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -4734,7 +4734,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-11.5</v>
+        <v>-11.9</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -4798,7 +4798,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-11</v>
+        <v>-11.4</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>-6.1</v>
+        <v>-6.8</v>
       </c>
       <c r="S36" s="52" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="R37" s="42" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="S37" s="54" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>-12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="S38" s="53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>-11</v>
+        <v>-12.1</v>
       </c>
       <c r="S39" s="53" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-6.7</v>
+        <v>-6.6</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-25.3</v>
+        <v>-24.3</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="S42" s="52" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="S47" s="53" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="R49" s="42" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="S49" s="52" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="R50" s="42" t="n">
-        <v>-13.6</v>
+        <v>-13</v>
       </c>
       <c r="S50" s="52" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>-23.8</v>
+        <v>-24.1</v>
       </c>
       <c r="S51" s="52" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="R52" s="42" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="S52" s="52" t="inlineStr">
         <is>
@@ -6265,9 +6265,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U52" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U52" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V52" s="53" t="inlineStr">
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="R53" s="42" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="S53" s="52" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -7168,7 +7168,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-16.6</v>
+        <v>-16.8</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -7232,7 +7232,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-11</v>
+        <v>-10.7</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -7296,7 +7296,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-18.5</v>
+        <v>-18</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -7360,7 +7360,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -7424,7 +7424,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>17.2</v>
+        <v>18.7</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="S39" s="52" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S40" s="52" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>-14.5</v>
+        <v>-15.5</v>
       </c>
       <c r="S42" s="53" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="R43" s="42" t="n">
-        <v>-19.7</v>
+        <v>-19.2</v>
       </c>
       <c r="S43" s="53" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="S47" s="53" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="R48" s="42" t="n">
-        <v>-12.3</v>
+        <v>-13.6</v>
       </c>
       <c r="S48" s="52" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="R49" s="42" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="S49" s="54" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="R50" s="42" t="n">
-        <v>-13</v>
+        <v>-13.2</v>
       </c>
       <c r="S50" s="53" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="S51" s="52" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="R52" s="42" t="n">
-        <v>-13.1</v>
+        <v>-13</v>
       </c>
       <c r="S52" s="52" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="R53" s="42" t="n">
-        <v>-7.8</v>
+        <v>-7.1</v>
       </c>
       <c r="S53" s="53" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -9598,7 +9598,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -9662,7 +9662,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-7.7</v>
+        <v>-8.4</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -9726,7 +9726,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -9790,7 +9790,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -9854,7 +9854,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>-7.4</v>
+        <v>-7.1</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -9918,7 +9918,7 @@
       <c r="P36" s="42" t="n"/>
       <c r="Q36" s="42" t="n"/>
       <c r="R36" s="42" t="n">
-        <v>-15.8</v>
+        <v>-15.5</v>
       </c>
       <c r="S36" s="51" t="n"/>
       <c r="T36" s="51" t="n"/>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="S40" s="52" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="S41" s="52" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>-26.2</v>
+        <v>-26</v>
       </c>
       <c r="S42" s="52" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         </is>
       </c>
       <c r="R44" s="42" t="n">
-        <v>-25.6</v>
+        <v>-25.3</v>
       </c>
       <c r="S44" s="52" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="S46" s="53" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="S47" s="52" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>-12.3</v>
+        <v>-12.8</v>
       </c>
       <c r="S51" s="52" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="R53" s="42" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="S53" s="53" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="R54" s="42" t="n">
-        <v>-11.3</v>
+        <v>-11.1</v>
       </c>
       <c r="S54" s="53" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="R55" s="42" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S55" s="52" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         </is>
       </c>
       <c r="R56" s="42" t="n">
-        <v>-4.7</v>
+        <v>-4.6</v>
       </c>
       <c r="S56" s="53" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="R57" s="42" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="S57" s="52" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="R58" s="42" t="n">
-        <v>16.8</v>
+        <v>15.5</v>
       </c>
       <c r="S58" s="53" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         </is>
       </c>
       <c r="R22" s="42" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="S22" s="52" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="R23" s="42" t="n">
-        <v>-11.6</v>
+        <v>-11.3</v>
       </c>
       <c r="S23" s="54" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="R24" s="42" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S24" s="53" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="R25" s="42" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="S25" s="53" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="R29" s="42" t="n">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="S29" s="52" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="R30" s="42" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="S30" s="52" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="R31" s="42" t="n">
-        <v>-11.8</v>
+        <v>-11.6</v>
       </c>
       <c r="S31" s="53" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="R32" s="42" t="n">
-        <v>-8.5</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S32" s="53" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>-13</v>
+        <v>-13.2</v>
       </c>
       <c r="S36" s="53" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S38" s="52" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
       <c r="P14" s="42" t="n"/>
       <c r="Q14" s="42" t="n"/>
       <c r="R14" s="42" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="S14" s="51" t="n"/>
       <c r="T14" s="51" t="n"/>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="R18" s="42" t="n">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="S18" s="52" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="R19" s="42" t="n">
-        <v>-36.9</v>
+        <v>-37.5</v>
       </c>
       <c r="S19" s="52" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="R23" s="42" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="S23" s="52" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="R24" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="S24" s="53" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>-14.7</v>
+        <v>-14.9</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -14964,7 +14964,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>-14.4</v>
+        <v>-14.6</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -15028,7 +15028,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -15092,7 +15092,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -15156,7 +15156,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-10.3</v>
+        <v>-10.8</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -15220,7 +15220,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="R35" s="42" t="n">
-        <v>-26.2</v>
+        <v>-26</v>
       </c>
       <c r="S35" s="52" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="S36" s="53" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         </is>
       </c>
       <c r="R37" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="S37" s="53" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>-7</v>
+        <v>-7.4</v>
       </c>
       <c r="S39" s="53" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-13.6</v>
+        <v>-13.9</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-15.5</v>
+        <v>-15.8</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="S46" s="52" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>-7.3</v>
+        <v>-7.5</v>
       </c>
       <c r="S47" s="53" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         </is>
       </c>
       <c r="R48" s="42" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="S48" s="52" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         </is>
       </c>
       <c r="R49" s="42" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="S49" s="53" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         </is>
       </c>
       <c r="R50" s="42" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="S50" s="52" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -17218,7 +17218,7 @@
       <c r="P23" s="42" t="n"/>
       <c r="Q23" s="42" t="n"/>
       <c r="R23" s="42" t="n">
-        <v>-18.8</v>
+        <v>-19.5</v>
       </c>
       <c r="S23" s="51" t="n"/>
       <c r="T23" s="51" t="n"/>
@@ -17282,7 +17282,7 @@
       <c r="P24" s="42" t="n"/>
       <c r="Q24" s="42" t="n"/>
       <c r="R24" s="42" t="n">
-        <v>-6.6</v>
+        <v>-6.9</v>
       </c>
       <c r="S24" s="51" t="n"/>
       <c r="T24" s="51" t="n"/>
@@ -17346,7 +17346,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -17410,7 +17410,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -17602,7 +17602,7 @@
         </is>
       </c>
       <c r="R30" s="42" t="n">
-        <v>-14.5</v>
+        <v>-15.5</v>
       </c>
       <c r="S30" s="53" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         </is>
       </c>
       <c r="R31" s="42" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="S31" s="53" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="R32" s="42" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="S32" s="52" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="R33" s="42" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="S33" s="52" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I34" s="42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J34" s="42" t="n">
         <v>5</v>
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="R34" s="42" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="S34" s="53" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="S38" s="52" t="inlineStr">
         <is>
@@ -18173,9 +18173,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U38" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U38" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V38" s="53" t="inlineStr">
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>-22</v>
+        <v>-21.7</v>
       </c>
       <c r="S39" s="53" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-21.8</v>
+        <v>-21.3</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>-7.3</v>
+        <v>-7.6</v>
       </c>
       <c r="S42" s="52" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
       <c r="P20" s="42" t="n"/>
       <c r="Q20" s="42" t="n"/>
       <c r="R20" s="42" t="n">
-        <v>-14.6</v>
+        <v>-14.5</v>
       </c>
       <c r="S20" s="51" t="n"/>
       <c r="T20" s="51" t="n"/>
@@ -19100,7 +19100,7 @@
       <c r="P21" s="42" t="n"/>
       <c r="Q21" s="42" t="n"/>
       <c r="R21" s="42" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="S21" s="51" t="n"/>
       <c r="T21" s="51" t="n"/>
@@ -19164,7 +19164,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="R26" s="42" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S26" s="52" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         </is>
       </c>
       <c r="R27" s="42" t="n">
-        <v>-1.5</v>
+        <v>-2.2</v>
       </c>
       <c r="S27" s="53" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="R28" s="42" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="S28" s="53" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         </is>
       </c>
       <c r="R32" s="42" t="n">
-        <v>-15</v>
+        <v>-15.7</v>
       </c>
       <c r="S32" s="53" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         </is>
       </c>
       <c r="R34" s="42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S34" s="53" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="R35" s="42" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="S35" s="52" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-23.7</v>
+        <v>-22.2</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -20766,7 +20766,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-10.6</v>
+        <v>-10.4</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -20830,7 +20830,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-14.1</v>
+        <v>-14.3</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -20894,7 +20894,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-10.7</v>
+        <v>-10.5</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -20958,7 +20958,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -21022,7 +21022,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-15.4</v>
+        <v>-16.2</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -21078,7 +21078,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-33.9</v>
+        <v>-33.2</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -21142,7 +21142,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>-11.7</v>
+        <v>-11.8</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -21334,7 +21334,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="S39" s="53" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S40" s="52" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="R43" s="42" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="S43" s="52" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         </is>
       </c>
       <c r="R44" s="42" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="S44" s="52" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -21874,9 +21874,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U45" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U45" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V45" s="52" t="inlineStr">
@@ -22157,7 +22157,7 @@
         </is>
       </c>
       <c r="R50" s="42" t="n">
-        <v>-40.5</v>
+        <v>-40.4</v>
       </c>
       <c r="S50" s="52" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         </is>
       </c>
       <c r="R51" s="42" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="S51" s="53" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         </is>
       </c>
       <c r="R52" s="42" t="n">
-        <v>-3.3</v>
+        <v>-2.6</v>
       </c>
       <c r="S52" s="52" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="R53" s="42" t="n">
-        <v>-4.9</v>
+        <v>-5.4</v>
       </c>
       <c r="S53" s="52" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         </is>
       </c>
       <c r="R54" s="42" t="n">
-        <v>-13.3</v>
+        <v>-13.4</v>
       </c>
       <c r="S54" s="53" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         </is>
       </c>
       <c r="R55" s="42" t="n">
-        <v>-13.8</v>
+        <v>-13.2</v>
       </c>
       <c r="S55" s="53" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -23420,7 +23420,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -23484,7 +23484,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-24.1</v>
+        <v>-24.3</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -23548,7 +23548,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -23612,7 +23612,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -23676,7 +23676,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -23868,7 +23868,7 @@
         </is>
       </c>
       <c r="R35" s="42" t="n">
-        <v>-7.6</v>
+        <v>-7.5</v>
       </c>
       <c r="S35" s="52" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         </is>
       </c>
       <c r="R36" s="42" t="n">
-        <v>-1.6</v>
+        <v>-0.9</v>
       </c>
       <c r="S36" s="52" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         </is>
       </c>
       <c r="R37" s="42" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="S37" s="53" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         </is>
       </c>
       <c r="R38" s="42" t="n">
-        <v>17.6</v>
+        <v>16.5</v>
       </c>
       <c r="S38" s="52" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="S39" s="52" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-13.2</v>
+        <v>-13.8</v>
       </c>
       <c r="S40" s="53" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         </is>
       </c>
       <c r="R44" s="42" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S44" s="53" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="R45" s="42" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="S45" s="52" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         </is>
       </c>
       <c r="R46" s="42" t="n">
-        <v>-14.4</v>
+        <v>-14.6</v>
       </c>
       <c r="S46" s="53" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         </is>
       </c>
       <c r="R47" s="42" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="S47" s="52" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         </is>
       </c>
       <c r="R48" s="42" t="n">
-        <v>-19</v>
+        <v>-18.2</v>
       </c>
       <c r="S48" s="53" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="R49" s="42" t="n">
-        <v>-5.1</v>
+        <v>-6.3</v>
       </c>
       <c r="S49" s="53" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -60872,7 +60872,7 @@
       <c r="P9" s="42" t="n"/>
       <c r="Q9" s="42" t="n"/>
       <c r="R9" s="42" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S9" s="51" t="n"/>
       <c r="T9" s="51" t="n"/>
@@ -60928,7 +60928,7 @@
       <c r="P10" s="42" t="n"/>
       <c r="Q10" s="42" t="n"/>
       <c r="R10" s="42" t="n">
-        <v>-33.7</v>
+        <v>-33.4</v>
       </c>
       <c r="S10" s="51" t="n"/>
       <c r="T10" s="51" t="n"/>
@@ -60992,7 +60992,7 @@
       <c r="P11" s="42" t="n"/>
       <c r="Q11" s="42" t="n"/>
       <c r="R11" s="42" t="n">
-        <v>-9.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="S11" s="51" t="n"/>
       <c r="T11" s="51" t="n"/>
@@ -61056,7 +61056,7 @@
       <c r="P12" s="42" t="n"/>
       <c r="Q12" s="42" t="n"/>
       <c r="R12" s="42" t="n">
-        <v>-17</v>
+        <v>-17.6</v>
       </c>
       <c r="S12" s="51" t="n"/>
       <c r="T12" s="51" t="n"/>
@@ -61120,7 +61120,7 @@
       <c r="P13" s="42" t="n"/>
       <c r="Q13" s="42" t="n"/>
       <c r="R13" s="42" t="n">
-        <v>-12.4</v>
+        <v>-12.5</v>
       </c>
       <c r="S13" s="51" t="n"/>
       <c r="T13" s="51" t="n"/>
@@ -61176,7 +61176,7 @@
       <c r="P14" s="42" t="n"/>
       <c r="Q14" s="42" t="n"/>
       <c r="R14" s="42" t="n">
-        <v>-30.1</v>
+        <v>-29.9</v>
       </c>
       <c r="S14" s="51" t="n"/>
       <c r="T14" s="51" t="n"/>
@@ -61240,7 +61240,7 @@
       <c r="P15" s="42" t="n"/>
       <c r="Q15" s="42" t="n"/>
       <c r="R15" s="42" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="S15" s="51" t="n"/>
       <c r="T15" s="51" t="n"/>
@@ -61304,7 +61304,7 @@
       <c r="P16" s="42" t="n"/>
       <c r="Q16" s="42" t="n"/>
       <c r="R16" s="42" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="S16" s="51" t="n"/>
       <c r="T16" s="51" t="n"/>
@@ -61368,7 +61368,7 @@
       <c r="P17" s="42" t="n"/>
       <c r="Q17" s="42" t="n"/>
       <c r="R17" s="42" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S17" s="51" t="n"/>
       <c r="T17" s="51" t="n"/>
@@ -61432,7 +61432,7 @@
       <c r="P18" s="42" t="n"/>
       <c r="Q18" s="42" t="n"/>
       <c r="R18" s="42" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="S18" s="51" t="n"/>
       <c r="T18" s="51" t="n"/>
@@ -61560,7 +61560,7 @@
       <c r="P20" s="42" t="n"/>
       <c r="Q20" s="42" t="n"/>
       <c r="R20" s="42" t="n">
-        <v>-8.9</v>
+        <v>-7.5</v>
       </c>
       <c r="S20" s="51" t="n"/>
       <c r="T20" s="51" t="n"/>
@@ -61624,7 +61624,7 @@
       <c r="P21" s="42" t="n"/>
       <c r="Q21" s="42" t="n"/>
       <c r="R21" s="42" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="S21" s="51" t="n"/>
       <c r="T21" s="51" t="n"/>
@@ -61688,7 +61688,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>-14.7</v>
+        <v>-14.9</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -61752,7 +61752,7 @@
       <c r="P23" s="42" t="n"/>
       <c r="Q23" s="42" t="n"/>
       <c r="R23" s="42" t="n">
-        <v>-11.5</v>
+        <v>-11.9</v>
       </c>
       <c r="S23" s="51" t="n"/>
       <c r="T23" s="51" t="n"/>
@@ -61816,7 +61816,7 @@
       <c r="P24" s="42" t="n"/>
       <c r="Q24" s="42" t="n"/>
       <c r="R24" s="42" t="n">
-        <v>-11</v>
+        <v>-11.4</v>
       </c>
       <c r="S24" s="51" t="n"/>
       <c r="T24" s="51" t="n"/>
@@ -61880,7 +61880,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -62008,7 +62008,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>-16.6</v>
+        <v>-16.8</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -62072,7 +62072,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-11</v>
+        <v>-10.7</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -62136,7 +62136,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-18.5</v>
+        <v>-18</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -62200,7 +62200,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -62264,7 +62264,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>17.2</v>
+        <v>18.7</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -62328,7 +62328,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -62392,7 +62392,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -62456,7 +62456,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-7.7</v>
+        <v>-8.4</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -62520,7 +62520,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -62584,7 +62584,7 @@
       <c r="P36" s="42" t="n"/>
       <c r="Q36" s="42" t="n"/>
       <c r="R36" s="42" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S36" s="51" t="n"/>
       <c r="T36" s="51" t="n"/>
@@ -62648,7 +62648,7 @@
       <c r="P37" s="42" t="n"/>
       <c r="Q37" s="42" t="n"/>
       <c r="R37" s="42" t="n">
-        <v>-7.4</v>
+        <v>-7.1</v>
       </c>
       <c r="S37" s="51" t="n"/>
       <c r="T37" s="51" t="n"/>
@@ -62712,7 +62712,7 @@
       <c r="P38" s="42" t="n"/>
       <c r="Q38" s="42" t="n"/>
       <c r="R38" s="42" t="n">
-        <v>-15.8</v>
+        <v>-15.5</v>
       </c>
       <c r="S38" s="51" t="n"/>
       <c r="T38" s="51" t="n"/>
@@ -62784,7 +62784,7 @@
         </is>
       </c>
       <c r="R39" s="42" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="S39" s="52" t="inlineStr">
         <is>
@@ -62872,7 +62872,7 @@
         </is>
       </c>
       <c r="R40" s="42" t="n">
-        <v>-11.6</v>
+        <v>-11.3</v>
       </c>
       <c r="S40" s="54" t="inlineStr">
         <is>
@@ -62960,7 +62960,7 @@
         </is>
       </c>
       <c r="R41" s="42" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S41" s="53" t="inlineStr">
         <is>
@@ -63048,7 +63048,7 @@
         </is>
       </c>
       <c r="R42" s="42" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="S42" s="53" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
       <c r="P44" s="42" t="n"/>
       <c r="Q44" s="42" t="n"/>
       <c r="R44" s="42" t="n">
-        <v>-14.4</v>
+        <v>-14.6</v>
       </c>
       <c r="S44" s="51" t="n"/>
       <c r="T44" s="51" t="n"/>
@@ -63256,7 +63256,7 @@
       <c r="P45" s="42" t="n"/>
       <c r="Q45" s="42" t="n"/>
       <c r="R45" s="42" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="S45" s="51" t="n"/>
       <c r="T45" s="51" t="n"/>
@@ -63320,7 +63320,7 @@
       <c r="P46" s="42" t="n"/>
       <c r="Q46" s="42" t="n"/>
       <c r="R46" s="42" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="S46" s="51" t="n"/>
       <c r="T46" s="51" t="n"/>
@@ -63384,7 +63384,7 @@
       <c r="P47" s="42" t="n"/>
       <c r="Q47" s="42" t="n"/>
       <c r="R47" s="42" t="n">
-        <v>-10.3</v>
+        <v>-10.8</v>
       </c>
       <c r="S47" s="51" t="n"/>
       <c r="T47" s="51" t="n"/>
@@ -63448,7 +63448,7 @@
       <c r="P48" s="42" t="n"/>
       <c r="Q48" s="42" t="n"/>
       <c r="R48" s="42" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="S48" s="51" t="n"/>
       <c r="T48" s="51" t="n"/>
@@ -63512,7 +63512,7 @@
       <c r="P49" s="42" t="n"/>
       <c r="Q49" s="42" t="n"/>
       <c r="R49" s="42" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="S49" s="51" t="n"/>
       <c r="T49" s="51" t="n"/>
@@ -63576,7 +63576,7 @@
       <c r="P50" s="42" t="n"/>
       <c r="Q50" s="42" t="n"/>
       <c r="R50" s="42" t="n">
-        <v>-18.8</v>
+        <v>-19.5</v>
       </c>
       <c r="S50" s="51" t="n"/>
       <c r="T50" s="51" t="n"/>
@@ -63640,7 +63640,7 @@
       <c r="P51" s="42" t="n"/>
       <c r="Q51" s="42" t="n"/>
       <c r="R51" s="42" t="n">
-        <v>-6.6</v>
+        <v>-6.9</v>
       </c>
       <c r="S51" s="51" t="n"/>
       <c r="T51" s="51" t="n"/>
@@ -63704,7 +63704,7 @@
       <c r="P52" s="42" t="n"/>
       <c r="Q52" s="42" t="n"/>
       <c r="R52" s="42" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="S52" s="51" t="n"/>
       <c r="T52" s="51" t="n"/>
@@ -63768,7 +63768,7 @@
       <c r="P53" s="42" t="n"/>
       <c r="Q53" s="42" t="n"/>
       <c r="R53" s="42" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S53" s="51" t="n"/>
       <c r="T53" s="51" t="n"/>
@@ -63832,7 +63832,7 @@
       <c r="P54" s="42" t="n"/>
       <c r="Q54" s="42" t="n"/>
       <c r="R54" s="42" t="n">
-        <v>-14.6</v>
+        <v>-14.5</v>
       </c>
       <c r="S54" s="51" t="n"/>
       <c r="T54" s="51" t="n"/>
@@ -63896,7 +63896,7 @@
       <c r="P55" s="42" t="n"/>
       <c r="Q55" s="42" t="n"/>
       <c r="R55" s="42" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="S55" s="51" t="n"/>
       <c r="T55" s="51" t="n"/>
@@ -63960,7 +63960,7 @@
       <c r="P56" s="42" t="n"/>
       <c r="Q56" s="42" t="n"/>
       <c r="R56" s="42" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="S56" s="51" t="n"/>
       <c r="T56" s="51" t="n"/>
@@ -64024,7 +64024,7 @@
       <c r="P57" s="42" t="n"/>
       <c r="Q57" s="42" t="n"/>
       <c r="R57" s="42" t="n">
-        <v>-23.7</v>
+        <v>-22.2</v>
       </c>
       <c r="S57" s="51" t="n"/>
       <c r="T57" s="51" t="n"/>
@@ -64088,7 +64088,7 @@
       <c r="P58" s="42" t="n"/>
       <c r="Q58" s="42" t="n"/>
       <c r="R58" s="42" t="n">
-        <v>-10.6</v>
+        <v>-10.4</v>
       </c>
       <c r="S58" s="51" t="n"/>
       <c r="T58" s="51" t="n"/>
@@ -64152,7 +64152,7 @@
       <c r="P59" s="42" t="n"/>
       <c r="Q59" s="42" t="n"/>
       <c r="R59" s="42" t="n">
-        <v>-14.1</v>
+        <v>-14.3</v>
       </c>
       <c r="S59" s="51" t="n"/>
       <c r="T59" s="51" t="n"/>
@@ -64216,7 +64216,7 @@
       <c r="P60" s="42" t="n"/>
       <c r="Q60" s="42" t="n"/>
       <c r="R60" s="42" t="n">
-        <v>-10.7</v>
+        <v>-10.5</v>
       </c>
       <c r="S60" s="51" t="n"/>
       <c r="T60" s="51" t="n"/>
@@ -64280,7 +64280,7 @@
       <c r="P61" s="42" t="n"/>
       <c r="Q61" s="42" t="n"/>
       <c r="R61" s="42" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="S61" s="51" t="n"/>
       <c r="T61" s="51" t="n"/>
@@ -64344,7 +64344,7 @@
       <c r="P62" s="42" t="n"/>
       <c r="Q62" s="42" t="n"/>
       <c r="R62" s="42" t="n">
-        <v>-15.4</v>
+        <v>-16.2</v>
       </c>
       <c r="S62" s="51" t="n"/>
       <c r="T62" s="51" t="n"/>
@@ -64400,7 +64400,7 @@
       <c r="P63" s="42" t="n"/>
       <c r="Q63" s="42" t="n"/>
       <c r="R63" s="42" t="n">
-        <v>-33.9</v>
+        <v>-33.2</v>
       </c>
       <c r="S63" s="51" t="n"/>
       <c r="T63" s="51" t="n"/>
@@ -64464,7 +64464,7 @@
       <c r="P64" s="42" t="n"/>
       <c r="Q64" s="42" t="n"/>
       <c r="R64" s="42" t="n">
-        <v>-11.7</v>
+        <v>-11.8</v>
       </c>
       <c r="S64" s="51" t="n"/>
       <c r="T64" s="51" t="n"/>
@@ -64528,7 +64528,7 @@
       <c r="P65" s="42" t="n"/>
       <c r="Q65" s="42" t="n"/>
       <c r="R65" s="42" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="S65" s="51" t="n"/>
       <c r="T65" s="51" t="n"/>
@@ -64592,7 +64592,7 @@
       <c r="P66" s="42" t="n"/>
       <c r="Q66" s="42" t="n"/>
       <c r="R66" s="42" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="S66" s="51" t="n"/>
       <c r="T66" s="51" t="n"/>
@@ -64656,7 +64656,7 @@
       <c r="P67" s="42" t="n"/>
       <c r="Q67" s="42" t="n"/>
       <c r="R67" s="42" t="n">
-        <v>-24.1</v>
+        <v>-24.3</v>
       </c>
       <c r="S67" s="51" t="n"/>
       <c r="T67" s="51" t="n"/>
@@ -64720,7 +64720,7 @@
       <c r="P68" s="42" t="n"/>
       <c r="Q68" s="42" t="n"/>
       <c r="R68" s="42" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="S68" s="51" t="n"/>
       <c r="T68" s="51" t="n"/>
@@ -64784,7 +64784,7 @@
       <c r="P69" s="42" t="n"/>
       <c r="Q69" s="42" t="n"/>
       <c r="R69" s="42" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S69" s="51" t="n"/>
       <c r="T69" s="51" t="n"/>
@@ -64848,7 +64848,7 @@
       <c r="P70" s="42" t="n"/>
       <c r="Q70" s="42" t="n"/>
       <c r="R70" s="42" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="S70" s="51" t="n"/>
       <c r="T70" s="51" t="n"/>
@@ -65039,7 +65039,7 @@
         </is>
       </c>
       <c r="R74" s="42" t="n">
-        <v>-5.4</v>
+        <v>-5.6</v>
       </c>
       <c r="S74" s="53" t="inlineStr">
         <is>
@@ -65215,7 +65215,7 @@
         </is>
       </c>
       <c r="R76" s="42" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="S76" s="52" t="inlineStr">
         <is>
@@ -65303,7 +65303,7 @@
         </is>
       </c>
       <c r="R77" s="42" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="S77" s="53" t="inlineStr">
         <is>
@@ -65391,7 +65391,7 @@
         </is>
       </c>
       <c r="R78" s="42" t="n">
-        <v>-13.5</v>
+        <v>-13.2</v>
       </c>
       <c r="S78" s="52" t="inlineStr">
         <is>
@@ -65479,7 +65479,7 @@
         </is>
       </c>
       <c r="R79" s="42" t="n">
-        <v>-4.8</v>
+        <v>-4.3</v>
       </c>
       <c r="S79" s="52" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         </is>
       </c>
       <c r="R80" s="42" t="n">
-        <v>-6.1</v>
+        <v>-6.8</v>
       </c>
       <c r="S80" s="52" t="inlineStr">
         <is>
@@ -65655,7 +65655,7 @@
         </is>
       </c>
       <c r="R81" s="42" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="S81" s="54" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         </is>
       </c>
       <c r="R82" s="42" t="n">
-        <v>-12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="S82" s="53" t="inlineStr">
         <is>
@@ -65831,7 +65831,7 @@
         </is>
       </c>
       <c r="R83" s="42" t="n">
-        <v>-11</v>
+        <v>-12.1</v>
       </c>
       <c r="S83" s="53" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         </is>
       </c>
       <c r="R84" s="42" t="n">
-        <v>-6.7</v>
+        <v>-6.6</v>
       </c>
       <c r="S84" s="53" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         </is>
       </c>
       <c r="R85" s="42" t="n">
-        <v>-25.3</v>
+        <v>-24.3</v>
       </c>
       <c r="S85" s="53" t="inlineStr">
         <is>
@@ -66095,7 +66095,7 @@
         </is>
       </c>
       <c r="R86" s="42" t="n">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="S86" s="52" t="inlineStr">
         <is>
@@ -66271,7 +66271,7 @@
         </is>
       </c>
       <c r="R88" s="42" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="S88" s="52" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         </is>
       </c>
       <c r="R89" s="42" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S89" s="52" t="inlineStr">
         <is>
@@ -66447,7 +66447,7 @@
         </is>
       </c>
       <c r="R90" s="42" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="S90" s="53" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         </is>
       </c>
       <c r="R91" s="42" t="n">
-        <v>-14.5</v>
+        <v>-15.5</v>
       </c>
       <c r="S91" s="53" t="inlineStr">
         <is>
@@ -66623,7 +66623,7 @@
         </is>
       </c>
       <c r="R92" s="42" t="n">
-        <v>-19.7</v>
+        <v>-19.2</v>
       </c>
       <c r="S92" s="53" t="inlineStr">
         <is>
@@ -66711,7 +66711,7 @@
         </is>
       </c>
       <c r="R93" s="42" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="S93" s="52" t="inlineStr">
         <is>
@@ -66799,7 +66799,7 @@
         </is>
       </c>
       <c r="R94" s="42" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="S94" s="52" t="inlineStr">
         <is>
@@ -66887,7 +66887,7 @@
         </is>
       </c>
       <c r="R95" s="42" t="n">
-        <v>-26.2</v>
+        <v>-26</v>
       </c>
       <c r="S95" s="52" t="inlineStr">
         <is>
@@ -67063,7 +67063,7 @@
         </is>
       </c>
       <c r="R97" s="42" t="n">
-        <v>-25.6</v>
+        <v>-25.3</v>
       </c>
       <c r="S97" s="52" t="inlineStr">
         <is>
@@ -67151,7 +67151,7 @@
         </is>
       </c>
       <c r="R98" s="42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S98" s="52" t="inlineStr">
         <is>
@@ -67239,7 +67239,7 @@
         </is>
       </c>
       <c r="R99" s="42" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="S99" s="53" t="inlineStr">
         <is>
@@ -67327,7 +67327,7 @@
         </is>
       </c>
       <c r="R100" s="42" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="S100" s="52" t="inlineStr">
         <is>
@@ -67415,7 +67415,7 @@
         </is>
       </c>
       <c r="R101" s="42" t="n">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="S101" s="52" t="inlineStr">
         <is>
@@ -67503,7 +67503,7 @@
         </is>
       </c>
       <c r="R102" s="42" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="S102" s="52" t="inlineStr">
         <is>
@@ -67591,7 +67591,7 @@
         </is>
       </c>
       <c r="R103" s="42" t="n">
-        <v>-11.8</v>
+        <v>-11.6</v>
       </c>
       <c r="S103" s="53" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         </is>
       </c>
       <c r="R104" s="42" t="n">
-        <v>-8.5</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="S104" s="53" t="inlineStr">
         <is>
@@ -67767,7 +67767,7 @@
         </is>
       </c>
       <c r="R105" s="42" t="n">
-        <v>-36.9</v>
+        <v>-37.5</v>
       </c>
       <c r="S105" s="52" t="inlineStr">
         <is>
@@ -67855,7 +67855,7 @@
         </is>
       </c>
       <c r="R106" s="42" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="S106" s="53" t="inlineStr">
         <is>
@@ -67943,7 +67943,7 @@
         </is>
       </c>
       <c r="R107" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="S107" s="53" t="inlineStr">
         <is>
@@ -68119,7 +68119,7 @@
         </is>
       </c>
       <c r="R109" s="42" t="n">
-        <v>-7</v>
+        <v>-7.4</v>
       </c>
       <c r="S109" s="53" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         </is>
       </c>
       <c r="R110" s="42" t="n">
-        <v>-13.6</v>
+        <v>-13.9</v>
       </c>
       <c r="S110" s="53" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         </is>
       </c>
       <c r="R111" s="42" t="n">
-        <v>-15.5</v>
+        <v>-15.8</v>
       </c>
       <c r="S111" s="53" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         </is>
       </c>
       <c r="R112" s="42" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="S112" s="53" t="inlineStr">
         <is>
@@ -68471,7 +68471,7 @@
         </is>
       </c>
       <c r="R113" s="42" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="S113" s="52" t="inlineStr">
         <is>
@@ -68559,7 +68559,7 @@
         </is>
       </c>
       <c r="R114" s="42" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="S114" s="52" t="inlineStr">
         <is>
@@ -68618,7 +68618,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I115" s="42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J115" s="42" t="n">
         <v>5</v>
@@ -68647,7 +68647,7 @@
         </is>
       </c>
       <c r="R115" s="42" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="S115" s="53" t="inlineStr">
         <is>
@@ -68735,7 +68735,7 @@
         </is>
       </c>
       <c r="R116" s="42" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S116" s="52" t="inlineStr">
         <is>
@@ -68823,7 +68823,7 @@
         </is>
       </c>
       <c r="R117" s="42" t="n">
-        <v>-1.5</v>
+        <v>-2.2</v>
       </c>
       <c r="S117" s="53" t="inlineStr">
         <is>
@@ -68911,7 +68911,7 @@
         </is>
       </c>
       <c r="R118" s="42" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="S118" s="53" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         </is>
       </c>
       <c r="R119" s="42" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="S119" s="53" t="inlineStr">
         <is>
@@ -69087,7 +69087,7 @@
         </is>
       </c>
       <c r="R120" s="42" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S120" s="52" t="inlineStr">
         <is>
@@ -69175,7 +69175,7 @@
         </is>
       </c>
       <c r="R121" s="42" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="S121" s="53" t="inlineStr">
         <is>
@@ -69351,7 +69351,7 @@
         </is>
       </c>
       <c r="R123" s="42" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="S123" s="52" t="inlineStr">
         <is>
@@ -69439,7 +69439,7 @@
         </is>
       </c>
       <c r="R124" s="42" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="S124" s="52" t="inlineStr">
         <is>
@@ -69527,7 +69527,7 @@
         </is>
       </c>
       <c r="R125" s="42" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S125" s="52" t="inlineStr">
         <is>
@@ -69539,9 +69539,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U125" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U125" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V125" s="52" t="inlineStr">
@@ -69615,7 +69615,7 @@
         </is>
       </c>
       <c r="R126" s="42" t="n">
-        <v>-7.6</v>
+        <v>-7.5</v>
       </c>
       <c r="S126" s="52" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         </is>
       </c>
       <c r="R127" s="42" t="n">
-        <v>-1.6</v>
+        <v>-0.9</v>
       </c>
       <c r="S127" s="52" t="inlineStr">
         <is>
@@ -69791,7 +69791,7 @@
         </is>
       </c>
       <c r="R128" s="42" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="S128" s="53" t="inlineStr">
         <is>
@@ -69879,7 +69879,7 @@
         </is>
       </c>
       <c r="R129" s="42" t="n">
-        <v>17.6</v>
+        <v>16.5</v>
       </c>
       <c r="S129" s="52" t="inlineStr">
         <is>
@@ -69967,7 +69967,7 @@
         </is>
       </c>
       <c r="R130" s="42" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="S130" s="52" t="inlineStr">
         <is>
@@ -70055,7 +70055,7 @@
         </is>
       </c>
       <c r="R131" s="42" t="n">
-        <v>-13.2</v>
+        <v>-13.8</v>
       </c>
       <c r="S131" s="53" t="inlineStr">
         <is>
@@ -70262,7 +70262,7 @@
         </is>
       </c>
       <c r="R135" s="42" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="S135" s="53" t="inlineStr">
         <is>
@@ -70274,9 +70274,9 @@
           <t>Loss</t>
         </is>
       </c>
-      <c r="U135" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U135" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V135" s="53" t="inlineStr">
@@ -70350,7 +70350,7 @@
         </is>
       </c>
       <c r="R136" s="42" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="S136" s="53" t="inlineStr">
         <is>
@@ -70526,7 +70526,7 @@
         </is>
       </c>
       <c r="R138" s="42" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="S138" s="52" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         </is>
       </c>
       <c r="R139" s="42" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="S139" s="52" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         </is>
       </c>
       <c r="R140" s="42" t="n">
-        <v>-20.1</v>
+        <v>-20.8</v>
       </c>
       <c r="S140" s="52" t="inlineStr">
         <is>
@@ -70714,9 +70714,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U140" s="53" t="inlineStr">
-        <is>
-          <t>Win</t>
+      <c r="U140" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
         </is>
       </c>
       <c r="V140" s="53" t="inlineStr">
@@ -70790,7 +70790,7 @@
         </is>
       </c>
       <c r="R141" s="42" t="n">
-        <v>-8.1</v>
+        <v>-7.6</v>
       </c>
       <c r="S141" s="53" t="inlineStr">
         <is>
@@ -70966,7 +70966,7 @@
         </is>
       </c>
       <c r="R143" s="42" t="n">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="S143" s="53" t="inlineStr">
         <is>
@@ -71142,7 +71142,7 @@
         </is>
       </c>
       <c r="R145" s="42" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="S145" s="52" t="inlineStr">
         <is>
@@ -71230,7 +71230,7 @@
         </is>
       </c>
       <c r="R146" s="42" t="n">
-        <v>-13.6</v>
+        <v>-13</v>
       </c>
       <c r="S146" s="52" t="inlineStr">
         <is>
@@ -71318,7 +71318,7 @@
         </is>
       </c>
       <c r="R147" s="42" t="n">
-        <v>-23.8</v>
+        <v>-24.1</v>
       </c>
       <c r="S147" s="52" t="inlineStr">
         <is>
@@ -71406,7 +71406,7 @@
         </is>
       </c>
       <c r="R148" s="42" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="S148" s="53" t="inlineStr">
         <is>
@@ -71494,7 +71494,7 @@
         </is>
       </c>
       <c r="R149" s="42" t="n">
-        <v>-12.3</v>
+        <v>-13.6</v>
       </c>
       <c r="S149" s="52" t="inlineStr">
         <is>
@@ -71582,7 +71582,7 @@
         </is>
       </c>
       <c r="R150" s="42" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="S150" s="54" t="inlineStr">
         <is>
@@ -71670,7 +71670,7 @@
         </is>
       </c>
       <c r="R151" s="42" t="n">
-        <v>-13</v>
+        <v>-13.2</v>
       </c>
       <c r="S151" s="53" t="inlineStr">
         <is>
@@ -71758,7 +71758,7 @@
         </is>
       </c>
       <c r="R152" s="42" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="S152" s="52" t="inlineStr">
         <is>
@@ -71846,7 +71846,7 @@
         </is>
       </c>
       <c r="R153" s="42" t="n">
-        <v>-13.1</v>
+        <v>-13</v>
       </c>
       <c r="S153" s="52" t="inlineStr">
         <is>
@@ -71934,7 +71934,7 @@
         </is>
       </c>
       <c r="R154" s="42" t="n">
-        <v>-7.8</v>
+        <v>-7.1</v>
       </c>
       <c r="S154" s="53" t="inlineStr">
         <is>
@@ -72022,7 +72022,7 @@
         </is>
       </c>
       <c r="R155" s="42" t="n">
-        <v>-12.3</v>
+        <v>-12.8</v>
       </c>
       <c r="S155" s="52" t="inlineStr">
         <is>
@@ -72198,7 +72198,7 @@
         </is>
       </c>
       <c r="R157" s="42" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="S157" s="53" t="inlineStr">
         <is>
@@ -72286,7 +72286,7 @@
         </is>
       </c>
       <c r="R158" s="42" t="n">
-        <v>-11.3</v>
+        <v>-11.1</v>
       </c>
       <c r="S158" s="53" t="inlineStr">
         <is>
@@ -72374,7 +72374,7 @@
         </is>
       </c>
       <c r="R159" s="42" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S159" s="52" t="inlineStr">
         <is>
@@ -72462,7 +72462,7 @@
         </is>
       </c>
       <c r="R160" s="42" t="n">
-        <v>-4.7</v>
+        <v>-4.6</v>
       </c>
       <c r="S160" s="53" t="inlineStr">
         <is>
@@ -72550,7 +72550,7 @@
         </is>
       </c>
       <c r="R161" s="42" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="S161" s="52" t="inlineStr">
         <is>
@@ -72638,7 +72638,7 @@
         </is>
       </c>
       <c r="R162" s="42" t="n">
-        <v>16.8</v>
+        <v>15.5</v>
       </c>
       <c r="S162" s="53" t="inlineStr">
         <is>
@@ -72814,7 +72814,7 @@
         </is>
       </c>
       <c r="R164" s="42" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S164" s="52" t="inlineStr">
         <is>
@@ -72902,7 +72902,7 @@
         </is>
       </c>
       <c r="R165" s="42" t="n">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="S165" s="53" t="inlineStr">
         <is>
@@ -72990,7 +72990,7 @@
         </is>
       </c>
       <c r="R166" s="42" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="S166" s="52" t="inlineStr">
         <is>
@@ -73078,7 +73078,7 @@
         </is>
       </c>
       <c r="R167" s="42" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="S167" s="52" t="inlineStr">
         <is>
@@ -73166,7 +73166,7 @@
         </is>
       </c>
       <c r="R168" s="42" t="n">
-        <v>-7.3</v>
+        <v>-7.5</v>
       </c>
       <c r="S168" s="53" t="inlineStr">
         <is>
@@ -73254,7 +73254,7 @@
         </is>
       </c>
       <c r="R169" s="42" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="S169" s="52" t="inlineStr">
         <is>
@@ -73342,7 +73342,7 @@
         </is>
       </c>
       <c r="R170" s="42" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="S170" s="53" t="inlineStr">
         <is>
@@ -73430,7 +73430,7 @@
         </is>
       </c>
       <c r="R171" s="42" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="S171" s="52" t="inlineStr">
         <is>
@@ -73518,7 +73518,7 @@
         </is>
       </c>
       <c r="R172" s="42" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="S172" s="52" t="inlineStr">
         <is>
@@ -73530,9 +73530,9 @@
           <t>Win</t>
         </is>
       </c>
-      <c r="U172" s="52" t="inlineStr">
-        <is>
-          <t>Loss</t>
+      <c r="U172" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
         </is>
       </c>
       <c r="V172" s="53" t="inlineStr">
@@ -73606,7 +73606,7 @@
         </is>
       </c>
       <c r="R173" s="42" t="n">
-        <v>-22</v>
+        <v>-21.7</v>
       </c>
       <c r="S173" s="53" t="inlineStr">
         <is>
@@ -73694,7 +73694,7 @@
         </is>
       </c>
       <c r="R174" s="42" t="n">
-        <v>-21.8</v>
+        <v>-21.3</v>
       </c>
       <c r="S174" s="53" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         </is>
       </c>
       <c r="R175" s="42" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="S175" s="53" t="inlineStr">
         <is>
@@ -73870,7 +73870,7 @@
         </is>
       </c>
       <c r="R176" s="42" t="n">
-        <v>-7.3</v>
+        <v>-7.6</v>
       </c>
       <c r="S176" s="52" t="inlineStr">
         <is>
@@ -73958,7 +73958,7 @@
         </is>
       </c>
       <c r="R177" s="42" t="n">
-        <v>-15</v>
+        <v>-15.7</v>
       </c>
       <c r="S177" s="53" t="inlineStr">
         <is>
@@ -74134,7 +74134,7 @@
         </is>
       </c>
       <c r="R179" s="42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S179" s="53" t="inlineStr">
         <is>
@@ -74222,7 +74222,7 @@
         </is>
       </c>
       <c r="R180" s="42" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="S180" s="52" t="inlineStr">
         <is>
@@ -74398,7 +74398,7 @@
         </is>
       </c>
       <c r="R182" s="42" t="n">
-        <v>-40.5</v>
+        <v>-40.4</v>
       </c>
       <c r="S182" s="52" t="inlineStr">
         <is>
@@ -74486,7 +74486,7 @@
         </is>
       </c>
       <c r="R183" s="42" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="S183" s="53" t="inlineStr">
         <is>
@@ -74574,7 +74574,7 @@
         </is>
       </c>
       <c r="R184" s="42" t="n">
-        <v>-3.3</v>
+        <v>-2.6</v>
       </c>
       <c r="S184" s="52" t="inlineStr">
         <is>
@@ -74662,7 +74662,7 @@
         </is>
       </c>
       <c r="R185" s="42" t="n">
-        <v>-4.9</v>
+        <v>-5.4</v>
       </c>
       <c r="S185" s="52" t="inlineStr">
         <is>
@@ -74750,7 +74750,7 @@
         </is>
       </c>
       <c r="R186" s="42" t="n">
-        <v>-13.3</v>
+        <v>-13.4</v>
       </c>
       <c r="S186" s="53" t="inlineStr">
         <is>
@@ -74838,7 +74838,7 @@
         </is>
       </c>
       <c r="R187" s="42" t="n">
-        <v>-13.8</v>
+        <v>-13.2</v>
       </c>
       <c r="S187" s="53" t="inlineStr">
         <is>
@@ -74926,7 +74926,7 @@
         </is>
       </c>
       <c r="R188" s="42" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S188" s="53" t="inlineStr">
         <is>
@@ -75014,7 +75014,7 @@
         </is>
       </c>
       <c r="R189" s="42" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="S189" s="52" t="inlineStr">
         <is>
@@ -75102,7 +75102,7 @@
         </is>
       </c>
       <c r="R190" s="42" t="n">
-        <v>-14.4</v>
+        <v>-14.6</v>
       </c>
       <c r="S190" s="53" t="inlineStr">
         <is>
@@ -75190,7 +75190,7 @@
         </is>
       </c>
       <c r="R191" s="42" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="S191" s="52" t="inlineStr">
         <is>
@@ -75278,7 +75278,7 @@
         </is>
       </c>
       <c r="R192" s="42" t="n">
-        <v>-19</v>
+        <v>-18.2</v>
       </c>
       <c r="S192" s="53" t="inlineStr">
         <is>
@@ -75366,7 +75366,7 @@
         </is>
       </c>
       <c r="R193" s="42" t="n">
-        <v>-5.1</v>
+        <v>-6.3</v>
       </c>
       <c r="S193" s="53" t="inlineStr">
         <is>

--- a/excel/MW_Handicapping_Tracker.xlsx
+++ b/excel/MW_Handicapping_Tracker.xlsx
@@ -1590,7 +1590,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -1654,7 +1654,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -1710,7 +1710,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-7.1</v>
+        <v>-6.7</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -1774,7 +1774,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-14.6</v>
+        <v>-14.3</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -1830,7 +1830,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-8</v>
+        <v>-7.6</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -1886,7 +1886,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-17</v>
+        <v>-15.5</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -1950,7 +1950,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -5099,7 +5099,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>-5.7</v>
+        <v>-5.5</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -5155,7 +5155,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>-7.6</v>
+        <v>-7.4</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -5211,7 +5211,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -5275,7 +5275,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -5331,7 +5331,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -8307,7 +8307,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-13.6</v>
+        <v>-13.4</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -8363,7 +8363,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -8427,7 +8427,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -8539,7 +8539,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -8595,7 +8595,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-9.9</v>
+        <v>-9</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -8641,7 +8641,7 @@
         <v>-8.1</v>
       </c>
       <c r="J34" s="42" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="K34" s="42" t="n">
         <v>1.8</v>
@@ -8659,7 +8659,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>17.8</v>
+        <v>18.6</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="B35" s="42" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C35" s="42" t="inlineStr">
@@ -8723,7 +8723,7 @@
       <c r="P35" s="42" t="n"/>
       <c r="Q35" s="42" t="n"/>
       <c r="R35" s="42" t="n">
-        <v>-7</v>
+        <v>-8.4</v>
       </c>
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="51" t="n"/>
@@ -11561,7 +11561,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -11625,7 +11625,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -11689,7 +11689,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -11753,7 +11753,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-11.9</v>
+        <v>-11.8</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -11817,7 +11817,7 @@
       <c r="P34" s="42" t="n"/>
       <c r="Q34" s="42" t="n"/>
       <c r="R34" s="42" t="n">
-        <v>-16.2</v>
+        <v>-16</v>
       </c>
       <c r="S34" s="51" t="n"/>
       <c r="T34" s="51" t="n"/>
@@ -14339,11 +14339,11 @@
       </c>
       <c r="B3" s="42" t="inlineStr">
         <is>
-          <t>29-21-1</t>
+          <t>30-22-1</t>
         </is>
       </c>
       <c r="C3" s="45" t="n">
-        <v>0.58</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="4">
@@ -14463,7 +14463,7 @@
     <row r="11">
       <c r="A11" s="42" t="inlineStr">
         <is>
-          <t>Western Kentucky</t>
+          <t>Middle Tennessee</t>
         </is>
       </c>
       <c r="B11" s="42" t="n">
@@ -14476,38 +14476,38 @@
         <v>0.667</v>
       </c>
       <c r="E11" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="F11" s="42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="42" t="inlineStr">
         <is>
-          <t>Florida International</t>
+          <t>Western Kentucky</t>
         </is>
       </c>
       <c r="B12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="42" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="42" t="inlineStr">
         <is>
-          <t>Middle Tennessee</t>
+          <t>New Mexico State</t>
         </is>
       </c>
       <c r="B13" s="42" t="n">
@@ -14520,29 +14520,29 @@
         <v>0.5</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="26.5" customHeight="1">
       <c r="A14" s="42" t="inlineStr">
         <is>
-          <t>Missouri State</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B14" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="42" t="n">
         <v>4</v>
@@ -14551,20 +14551,20 @@
     <row r="15">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>New Mexico State</t>
+          <t>Florida International</t>
         </is>
       </c>
       <c r="B15" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="42" t="n">
         <v>4</v>
@@ -14573,23 +14573,23 @@
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Missouri State</t>
         </is>
       </c>
       <c r="B16" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="42" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>2</v>
       </c>
       <c r="F16" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -14809,16 +14809,40 @@
       <c r="N22" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="O22" s="42" t="n"/>
-      <c r="P22" s="42" t="n"/>
-      <c r="Q22" s="42" t="n"/>
+      <c r="O22" s="42" t="n">
+        <v>38</v>
+      </c>
+      <c r="P22" s="42" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q22" s="47" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
       <c r="R22" s="42" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="51" t="n"/>
+        <v>-7.9</v>
+      </c>
+      <c r="S22" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="T22" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="U22" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V22" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="42" t="n">
@@ -14873,16 +14897,40 @@
       <c r="N23" s="47" t="n">
         <v>5.3</v>
       </c>
-      <c r="O23" s="42" t="n"/>
-      <c r="P23" s="42" t="n"/>
-      <c r="Q23" s="42" t="n"/>
+      <c r="O23" s="42" t="n">
+        <v>26</v>
+      </c>
+      <c r="P23" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="48" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="R23" s="42" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="51" t="n"/>
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="S23" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="T23" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="U23" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="V23" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="42" t="n">
@@ -15005,7 +15053,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>-3.5</v>
+        <v>-2.8</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -16702,7 +16750,7 @@
       <c r="P14" s="42" t="n"/>
       <c r="Q14" s="42" t="n"/>
       <c r="R14" s="42" t="n">
-        <v>-22.6</v>
+        <v>-23</v>
       </c>
       <c r="S14" s="51" t="n"/>
       <c r="T14" s="51" t="n"/>
@@ -18116,7 +18164,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>-22.6</v>
+        <v>-23</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -18172,7 +18220,7 @@
       <c r="P26" s="42" t="n"/>
       <c r="Q26" s="42" t="n"/>
       <c r="R26" s="42" t="n">
-        <v>-8.699999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="S26" s="51" t="n"/>
       <c r="T26" s="51" t="n"/>
@@ -18228,7 +18276,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>-5.8</v>
+        <v>-5.4</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -18284,7 +18332,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -18340,7 +18388,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -18396,7 +18444,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-11.8</v>
+        <v>-12.3</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -18452,7 +18500,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -21113,7 +21161,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>-5.1</v>
+        <v>-5.5</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -21169,7 +21217,7 @@
       <c r="P23" s="42" t="n"/>
       <c r="Q23" s="42" t="n"/>
       <c r="R23" s="42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S23" s="51" t="n"/>
       <c r="T23" s="51" t="n"/>
@@ -21233,7 +21281,7 @@
       <c r="P24" s="42" t="n"/>
       <c r="Q24" s="42" t="n"/>
       <c r="R24" s="42" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="S24" s="51" t="n"/>
       <c r="T24" s="51" t="n"/>
@@ -21297,7 +21345,7 @@
       <c r="P25" s="42" t="n"/>
       <c r="Q25" s="42" t="n"/>
       <c r="R25" s="42" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="51" t="n"/>
@@ -23473,7 +23521,7 @@
       <c r="P20" s="42" t="n"/>
       <c r="Q20" s="42" t="n"/>
       <c r="R20" s="42" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="S20" s="51" t="n"/>
       <c r="T20" s="51" t="n"/>
@@ -23529,7 +23577,7 @@
       <c r="P21" s="42" t="n"/>
       <c r="Q21" s="42" t="n"/>
       <c r="R21" s="42" t="n">
-        <v>-10.7</v>
+        <v>-11</v>
       </c>
       <c r="S21" s="51" t="n"/>
       <c r="T21" s="51" t="n"/>
@@ -23585,7 +23633,7 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="42" t="n"/>
       <c r="R22" s="42" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="S22" s="51" t="n"/>
       <c r="T22" s="51" t="n"/>
@@ -25506,7 +25554,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-8.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -25570,7 +25618,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -25634,7 +25682,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>-0.7</v>
+        <v>-1.3</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -25690,7 +25738,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -25754,7 +25802,7 @@
       <c r="P32" s="42" t="n"/>
       <c r="Q32" s="42" t="n"/>
       <c r="R32" s="42" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="S32" s="51" t="n"/>
       <c r="T32" s="51" t="n"/>
@@ -25818,7 +25866,7 @@
       <c r="P33" s="42" t="n"/>
       <c r="Q33" s="42" t="n"/>
       <c r="R33" s="42" t="n">
-        <v>-4.5</v>
+        <v>-5.1</v>
       </c>
       <c r="S33" s="51" t="n"/>
       <c r="T33" s="51" t="n"/>
@@ -28268,11 +28316,11 @@
       </c>
       <c r="B3" s="42" t="inlineStr">
         <is>
-          <t>39-32-1</t>
+          <t>40-32-1</t>
         </is>
       </c>
       <c r="C3" s="45" t="n">
-        <v>0.549</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="4">
@@ -28392,20 +28440,20 @@
     <row r="11">
       <c r="A11" s="42" t="inlineStr">
         <is>
-          <t>South Alabama</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B11" s="42" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>2</v>
@@ -28414,7 +28462,7 @@
     <row r="12">
       <c r="A12" s="42" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>South Alabama</t>
         </is>
       </c>
       <c r="B12" s="42" t="n">
@@ -28427,10 +28475,10 @@
         <v>0.667</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -28524,7 +28572,7 @@
     <row r="17">
       <c r="A17" s="42" t="inlineStr">
         <is>
-          <t>Arkansas State</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B17" s="42" t="n">
@@ -28537,16 +28585,16 @@
         <v>0.333</v>
       </c>
       <c r="E17" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="18" ht="26.5" customHeight="1">
       <c r="A18" s="42" t="inlineStr">
         <is>
-          <t>Coastal Carolina</t>
+          <t>Arkansas State</t>
         </is>
       </c>
       <c r="B18" s="42" t="n">
@@ -28559,26 +28607,26 @@
         <v>0.333</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Coastal Carolina</t>
         </is>
       </c>
       <c r="B19" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>2</v>
@@ -28590,23 +28638,23 @@
     <row r="20">
       <c r="A20" s="42" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="B20" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E20" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="42" t="n">
-        <v>3</v>
-      </c>
       <c r="F20" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -28826,16 +28874,40 @@
       <c r="N26" s="42" t="n">
         <v>0.7</v>
       </c>
-      <c r="O26" s="42" t="n"/>
-      <c r="P26" s="42" t="n"/>
-      <c r="Q26" s="42" t="n"/>
+      <c r="O26" s="42" t="n">
+        <v>13</v>
+      </c>
+      <c r="P26" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q26" s="48" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
       <c r="R26" s="42" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="51" t="n"/>
+        <v>-2.9</v>
+      </c>
+      <c r="S26" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="T26" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="U26" s="53" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="V26" s="52" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="42" t="n">
@@ -28894,7 +28966,7 @@
       <c r="P27" s="42" t="n"/>
       <c r="Q27" s="42" t="n"/>
       <c r="R27" s="42" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="S27" s="51" t="n"/>
       <c r="T27" s="51" t="n"/>
@@ -28950,7 +29022,7 @@
       <c r="P28" s="42" t="n"/>
       <c r="Q28" s="42" t="n"/>
       <c r="R28" s="42" t="n">
-        <v>-2.4</v>
+        <v>-1.7</v>
       </c>
       <c r="S28" s="51" t="n"/>
       <c r="T28" s="51" t="n"/>
@@ -29006,7 +29078,7 @@
       <c r="P29" s="42" t="n"/>
       <c r="Q29" s="42" t="n"/>
       <c r="R29" s="42" t="n">
-        <v>-4.7</v>
+        <v>-5.6</v>
       </c>
       <c r="S29" s="51" t="n"/>
       <c r="T29" s="51" t="n"/>
@@ -29062,7 +29134,7 @@
       <c r="P30" s="42" t="n"/>
       <c r="Q30" s="42" t="n"/>
       <c r="R30" s="42" t="n">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
       <c r="S30" s="51" t="n"/>
       <c r="T30" s="51" t="n"/>
@@ -29118,7 +29190,7 @@
       <c r="P31" s="42" t="n"/>
       <c r="Q31" s="42" t="n"/>
       <c r="R31" s="42" t="n">
-        <v>-16.5</v>
+        <v>-16.2</v>
       </c>
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="51" t="n"/>
@@ -50392,6 +50464,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
@@ -50437,6 +50510,11 @@
           <t>Week 7</t>
         </is>
       </c>
+      <c r="I1" s="40" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
       <c r="V1" s="41" t="inlineStr">
         <is>
           <t>Matchup Spread Calculator</t>
@@ -50470,6 +50548,9 @@
       <c r="H2" s="42" t="n">
         <v>95</v>
       </c>
+      <c r="I2" s="42" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="42" t="inlineStr">
@@ -50498,6 +50579,9 @@
       <c r="H3" s="42" t="n">
         <v>91.3</v>
       </c>
+      <c r="I3" s="42" t="n">
+        <v>91.3</v>
+      </c>
       <c r="V3" s="42" t="inlineStr">
         <is>
           <t>Home Team</t>
@@ -50536,6 +50620,9 @@
       <c r="H4" s="42" t="n">
         <v>88</v>
       </c>
+      <c r="I4" s="42" t="n">
+        <v>88.09999999999999</v>
+      </c>
       <c r="V4" s="42" t="inlineStr">
         <is>
           <t>Away Team</t>
@@ -50574,6 +50661,9 @@
       <c r="H5" s="42" t="n">
         <v>87.90000000000001</v>
       </c>
+      <c r="I5" s="42" t="n">
+        <v>87.90000000000001</v>
+      </c>
       <c r="V5" s="42" t="inlineStr">
         <is>
           <t>Neutral Site? (Y/N)</t>
@@ -50612,6 +50702,9 @@
       <c r="H6" s="42" t="n">
         <v>87.8</v>
       </c>
+      <c r="I6" s="42" t="n">
+        <v>87.90000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="42" t="inlineStr">
@@ -50640,6 +50733,9 @@
       <c r="H7" s="42" t="n">
         <v>86.8</v>
       </c>
+      <c r="I7" s="42" t="n">
+        <v>86.8</v>
+      </c>
       <c r="V7" s="42" t="inlineStr">
         <is>
           <t>HFA (model constant)</t>
@@ -50676,6 +50772,9 @@
       <c r="H8" s="42" t="n">
         <v>86.5</v>
       </c>
+      <c r="I8" s="42" t="n">
+        <v>86.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
@@ -50704,13 +50803,16 @@
       <c r="H9" s="42" t="n">
         <v>85.3</v>
       </c>
+      <c r="I9" s="42" t="n">
+        <v>85.3</v>
+      </c>
       <c r="V9" s="43" t="inlineStr">
         <is>
           <t>Predicted Spread (Home)</t>
         </is>
       </c>
       <c r="W9" s="43">
-        <f>IF(OR(W3="",W4=""),"",INDEX($H$2:$H$139,MATCH(W4,$A$2:$A$139,0))-INDEX($H$2:$H$139,MATCH(W3,$A$2:$A$139,0))-IF(UPPER(W5)="Y",0,W7))</f>
+        <f>IF(OR(W3="",W4=""),"",INDEX($I$2:$I$139,MATCH(W4,$A$2:$A$139,0))-INDEX($I$2:$I$139,MATCH(W3,$A$2:$A$139,0))-IF(UPPER(W5)="Y",0,W7))</f>
         <v/>
       </c>
     </row>
@@ -50741,6 +50843,9 @@
       <c r="H10" s="42" t="n">
         <v>84.8</v>
       </c>
+      <c r="I10" s="42" t="n">
+        <v>84.8</v>
+      </c>
       <c r="V10" s="44" t="inlineStr">
         <is>
           <t>(negative = home team favored, e.g. "Home -6.5")</t>
@@ -50774,6 +50879,9 @@
       <c r="H11" s="42" t="n">
         <v>83.2</v>
       </c>
+      <c r="I11" s="42" t="n">
+        <v>83.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="42" t="inlineStr">
@@ -50802,6 +50910,9 @@
       <c r="H12" s="42" t="n">
         <v>83.09999999999999</v>
       </c>
+      <c r="I12" s="42" t="n">
+        <v>83.09999999999999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="42" t="inlineStr">
@@ -50830,6 +50941,9 @@
       <c r="H13" s="42" t="n">
         <v>82.59999999999999</v>
       </c>
+      <c r="I13" s="42" t="n">
+        <v>82.59999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="42" t="inlineStr">
@@ -50858,6 +50972,9 @@
       <c r="H14" s="42" t="n">
         <v>82.2</v>
       </c>
+      <c r="I14" s="42" t="n">
+        <v>82.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="42" t="inlineStr">
@@ -50886,6 +51003,9 @@
       <c r="H15" s="42" t="n">
         <v>82</v>
       </c>
+      <c r="I15" s="42" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
@@ -50914,6 +51034,9 @@
       <c r="H16" s="42" t="n">
         <v>81.90000000000001</v>
       </c>
+      <c r="I16" s="42" t="n">
+        <v>81.90000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="42" t="inlineStr">
@@ -50942,6 +51065,9 @@
       <c r="H17" s="42" t="n">
         <v>81.09999999999999</v>
       </c>
+      <c r="I17" s="42" t="n">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="42" t="inlineStr">
@@ -50970,6 +51096,9 @@
       <c r="H18" s="42" t="n">
         <v>81.09999999999999</v>
       </c>
+      <c r="I18" s="42" t="n">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
@@ -50998,6 +51127,9 @@
       <c r="H19" s="42" t="n">
         <v>80.09999999999999</v>
       </c>
+      <c r="I19" s="42" t="n">
+        <v>79.90000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="42" t="inlineStr">
@@ -51026,6 +51158,9 @@
       <c r="H20" s="42" t="n">
         <v>79.5</v>
       </c>
+      <c r="I20" s="42" t="n">
+        <v>79.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="42" t="inlineStr">
@@ -51054,6 +51189,9 @@
       <c r="H21" s="42" t="n">
         <v>78.5</v>
       </c>
+      <c r="I21" s="42" t="n">
+        <v>78.5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="42" t="inlineStr">
@@ -51082,6 +51220,9 @@
       <c r="H22" s="42" t="n">
         <v>78.40000000000001</v>
       </c>
+      <c r="I22" s="42" t="n">
+        <v>78.40000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="42" t="inlineStr">
@@ -51110,6 +51251,9 @@
       <c r="H23" s="42" t="n">
         <v>78.09999999999999</v>
       </c>
+      <c r="I23" s="42" t="n">
+        <v>78.09999999999999</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
@@ -51138,6 +51282,9 @@
       <c r="H24" s="42" t="n">
         <v>77.7</v>
       </c>
+      <c r="I24" s="42" t="n">
+        <v>77.7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="42" t="inlineStr">
@@ -51166,6 +51313,9 @@
       <c r="H25" s="42" t="n">
         <v>77</v>
       </c>
+      <c r="I25" s="42" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="42" t="inlineStr">
@@ -51194,6 +51344,9 @@
       <c r="H26" s="42" t="n">
         <v>76.3</v>
       </c>
+      <c r="I26" s="42" t="n">
+        <v>76.3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="42" t="inlineStr">
@@ -51222,6 +51375,9 @@
       <c r="H27" s="42" t="n">
         <v>76</v>
       </c>
+      <c r="I27" s="42" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
@@ -51250,6 +51406,9 @@
       <c r="H28" s="42" t="n">
         <v>75.90000000000001</v>
       </c>
+      <c r="I28" s="42" t="n">
+        <v>75.90000000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="42" t="inlineStr">
@@ -51278,6 +51437,9 @@
       <c r="H29" s="42" t="n">
         <v>75.2</v>
       </c>
+      <c r="I29" s="42" t="n">
+        <v>75.2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="42" t="inlineStr">
@@ -51306,6 +51468,9 @@
       <c r="H30" s="42" t="n">
         <v>74.7</v>
       </c>
+      <c r="I30" s="42" t="n">
+        <v>74.7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="42" t="inlineStr">
@@ -51334,6 +51499,9 @@
       <c r="H31" s="42" t="n">
         <v>74.59999999999999</v>
       </c>
+      <c r="I31" s="42" t="n">
+        <v>74.59999999999999</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="42" t="inlineStr">
@@ -51362,6 +51530,9 @@
       <c r="H32" s="42" t="n">
         <v>74.5</v>
       </c>
+      <c r="I32" s="42" t="n">
+        <v>74.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="42" t="inlineStr">
@@ -51390,6 +51561,9 @@
       <c r="H33" s="42" t="n">
         <v>74.5</v>
       </c>
+      <c r="I33" s="42" t="n">
+        <v>74.5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="42" t="inlineStr">
@@ -51418,6 +51592,9 @@
       <c r="H34" s="42" t="n">
         <v>74.09999999999999</v>
       </c>
+      <c r="I34" s="42" t="n">
+        <v>74.09999999999999</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="42" t="inlineStr">
@@ -51446,6 +51623,9 @@
       <c r="H35" s="42" t="n">
         <v>74.09999999999999</v>
       </c>
+      <c r="I35" s="42" t="n">
+        <v>74.09999999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="42" t="inlineStr">
@@ -51474,6 +51654,9 @@
       <c r="H36" s="42" t="n">
         <v>74</v>
       </c>
+      <c r="I36" s="42" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="42" t="inlineStr">
@@ -51502,6 +51685,9 @@
       <c r="H37" s="42" t="n">
         <v>73.59999999999999</v>
       </c>
+      <c r="I37" s="42" t="n">
+        <v>73.59999999999999</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="42" t="inlineStr">
@@ -51530,6 +51716,9 @@
       <c r="H38" s="42" t="n">
         <v>73.59999999999999</v>
       </c>
+      <c r="I38" s="42" t="n">
+        <v>73.59999999999999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="42" t="inlineStr">
@@ -51558,6 +51747,9 @@
       <c r="H39" s="42" t="n">
         <v>73.40000000000001</v>
       </c>
+      <c r="I39" s="42" t="n">
+        <v>73.5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="42" t="inlineStr">
@@ -51586,6 +51778,9 @@
       <c r="H40" s="42" t="n">
         <v>73</v>
       </c>
+      <c r="I40" s="42" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="42" t="inlineStr">
@@ -51614,6 +51809,9 @@
       <c r="H41" s="42" t="n">
         <v>72.8</v>
       </c>
+      <c r="I41" s="42" t="n">
+        <v>72.8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="42" t="inlineStr">
@@ -51642,6 +51840,9 @@
       <c r="H42" s="42" t="n">
         <v>72.3</v>
       </c>
+      <c r="I42" s="42" t="n">
+        <v>72.3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="42" t="inlineStr">
@@ -51670,6 +51871,9 @@
       <c r="H43" s="42" t="n">
         <v>72.3</v>
       </c>
+      <c r="I43" s="42" t="n">
+        <v>72.3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="42" t="inlineStr">
@@ -51698,6 +51902,9 @@
       <c r="H44" s="42" t="n">
         <v>72.09999999999999</v>
       </c>
+      <c r="I44" s="42" t="n">
+        <v>72.09999999999999</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="42" t="inlineStr">
@@ -51726,6 +51933,9 @@
       <c r="H45" s="42" t="n">
         <v>72.09999999999999</v>
       </c>
+      <c r="I45" s="42" t="n">
+        <v>72.09999999999999</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="42" t="inlineStr">
@@ -51754,6 +51964,9 @@
       <c r="H46" s="42" t="n">
         <v>70.8</v>
       </c>
+      <c r="I46" s="42" t="n">
+        <v>70.8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="42" t="inlineStr">
@@ -51782,6 +51995,9 @@
       <c r="H47" s="42" t="n">
         <v>69.90000000000001</v>
       </c>
+      <c r="I47" s="42" t="n">
+        <v>69.90000000000001</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="42" t="inlineStr">
@@ -51810,6 +52026,9 @@
       <c r="H48" s="42" t="n">
         <v>69.90000000000001</v>
       </c>
+      <c r="I48" s="42" t="n">
+        <v>69.90000000000001</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="42" t="inlineStr">
@@ -51838,6 +52057,9 @@
       <c r="H49" s="42" t="n">
         <v>69.5</v>
       </c>
+      <c r="I49" s="42" t="n">
+        <v>69.5</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="42" t="inlineStr">
@@ -51866,6 +52088,9 @@
       <c r="H50" s="42" t="n">
         <v>69.5</v>
       </c>
+      <c r="I50" s="42" t="n">
+        <v>69.5</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="42" t="inlineStr">
@@ -51894,6 +52119,9 @@
       <c r="H51" s="42" t="n">
         <v>69.40000000000001</v>
       </c>
+      <c r="I51" s="42" t="n">
+        <v>69.40000000000001</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="42" t="inlineStr">
@@ -51922,6 +52150,9 @@
       <c r="H52" s="42" t="n">
         <v>68.8</v>
       </c>
+      <c r="I52" s="42" t="n">
+        <v>68.8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="42" t="inlineStr">
@@ -51950,6 +52181,9 @@
       <c r="H53" s="42" t="n">
         <v>68.59999999999999</v>
       </c>
+      <c r="I53" s="42" t="n">
+        <v>68.5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="42" t="inlineStr">
@@ -51978,6 +52212,9 @@
       <c r="H54" s="42" t="n">
         <v>68.2</v>
       </c>
+      <c r="I54" s="42" t="n">
+        <v>68.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="42" t="inlineStr">
@@ -52006,6 +52243,9 @@
       <c r="H55" s="42" t="n">
         <v>67.90000000000001</v>
       </c>
+      <c r="I55" s="42" t="n">
+        <v>67.90000000000001</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="42" t="inlineStr">
@@ -52034,6 +52274,9 @@
       <c r="H56" s="42" t="n">
         <v>67.59999999999999</v>
       </c>
+      <c r="I56" s="42" t="n">
+        <v>67.59999999999999</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="42" t="inlineStr">
@@ -52062,6 +52305,9 @@
       <c r="H57" s="42" t="n">
         <v>67.09999999999999</v>
       </c>
+      <c r="I57" s="42" t="n">
+        <v>67.09999999999999</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="42" t="inlineStr">
@@ -52090,6 +52336,9 @@
       <c r="H58" s="42" t="n">
         <v>67</v>
       </c>
+      <c r="I58" s="42" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="42" t="inlineStr">
@@ -52118,6 +52367,9 @@
       <c r="H59" s="42" t="n">
         <v>67</v>
       </c>
+      <c r="I59" s="42" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="42" t="inlineStr">
@@ -52146,6 +52398,9 @@
       <c r="H60" s="42" t="n">
         <v>66.90000000000001</v>
       </c>
+      <c r="I60" s="42" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="42" t="inlineStr">
@@ -52174,6 +52429,9 @@
       <c r="H61" s="42" t="n">
         <v>66.8</v>
       </c>
+      <c r="I61" s="42" t="n">
+        <v>66.90000000000001</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="42" t="inlineStr">
@@ -52202,62 +52460,71 @@
       <c r="H62" s="42" t="n">
         <v>66.7</v>
       </c>
+      <c r="I62" s="42" t="n">
+        <v>66.7</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="42" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B63" s="42" t="n">
-        <v>61.3</v>
+        <v>69.3</v>
       </c>
       <c r="C63" s="42" t="n">
-        <v>62.7</v>
+        <v>71.8</v>
       </c>
       <c r="D63" s="42" t="n">
-        <v>62.4</v>
+        <v>70.5</v>
       </c>
       <c r="E63" s="42" t="n">
-        <v>62.4</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F63" s="42" t="n">
-        <v>64</v>
+        <v>67.2</v>
       </c>
       <c r="G63" s="42" t="n">
-        <v>64.8</v>
+        <v>67.3</v>
       </c>
       <c r="H63" s="42" t="n">
         <v>66.40000000000001</v>
       </c>
+      <c r="I63" s="42" t="n">
+        <v>66.40000000000001</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="42" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="B64" s="42" t="n">
-        <v>69.3</v>
+        <v>61.3</v>
       </c>
       <c r="C64" s="42" t="n">
-        <v>71.8</v>
+        <v>62.7</v>
       </c>
       <c r="D64" s="42" t="n">
-        <v>70.5</v>
+        <v>62.4</v>
       </c>
       <c r="E64" s="42" t="n">
-        <v>70.90000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="F64" s="42" t="n">
-        <v>67.2</v>
+        <v>64</v>
       </c>
       <c r="G64" s="42" t="n">
-        <v>67.3</v>
+        <v>64.8</v>
       </c>
       <c r="H64" s="42" t="n">
         <v>66.40000000000001</v>
       </c>
+      <c r="I64" s="42" t="n">
+        <v>66.40000000000001</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="42" t="inlineStr">
@@ -52286,6 +52553,9 @@
       <c r="H65" s="42" t="n">
         <v>66.3</v>
       </c>
+      <c r="I65" s="42" t="n">
+        <v>66.3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="42" t="inlineStr">
@@ -52314,6 +52584,9 @@
       <c r="H66" s="42" t="n">
         <v>66.2</v>
       </c>
+      <c r="I66" s="42" t="n">
+        <v>66.3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="42" t="inlineStr">
@@ -52342,6 +52615,9 @@
       <c r="H67" s="42" t="n">
         <v>66</v>
       </c>
+      <c r="I67" s="42" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="42" t="inlineStr">
@@ -52370,6 +52646,9 @@
       <c r="H68" s="42" t="n">
         <v>65.5</v>
       </c>
+      <c r="I68" s="42" t="n">
+        <v>65.5</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="42" t="inlineStr">
@@ -52398,6 +52677,9 @@
       <c r="H69" s="42" t="n">
         <v>64.90000000000001</v>
       </c>
+      <c r="I69" s="42" t="n">
+        <v>64.90000000000001</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="42" t="inlineStr">
@@ -52426,6 +52708,9 @@
       <c r="H70" s="42" t="n">
         <v>64.59999999999999</v>
       </c>
+      <c r="I70" s="42" t="n">
+        <v>64.59999999999999</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="42" t="inlineStr">
@@ -52454,6 +52739,9 @@
       <c r="H71" s="42" t="n">
         <v>64.3</v>
       </c>
+      <c r="I71" s="42" t="n">
+        <v>64.3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="42" t="inlineStr">
@@ -52482,6 +52770,9 @@
       <c r="H72" s="42" t="n">
         <v>64.3</v>
       </c>
+      <c r="I72" s="42" t="n">
+        <v>64.3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="42" t="inlineStr">
@@ -52510,6 +52801,9 @@
       <c r="H73" s="42" t="n">
         <v>64.3</v>
       </c>
+      <c r="I73" s="42" t="n">
+        <v>64.3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="42" t="inlineStr">
@@ -52538,6 +52832,9 @@
       <c r="H74" s="42" t="n">
         <v>63.4</v>
       </c>
+      <c r="I74" s="42" t="n">
+        <v>63.4</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="42" t="inlineStr">
@@ -52566,6 +52863,9 @@
       <c r="H75" s="42" t="n">
         <v>63.3</v>
       </c>
+      <c r="I75" s="42" t="n">
+        <v>63.3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="42" t="inlineStr">
@@ -52594,6 +52894,9 @@
       <c r="H76" s="42" t="n">
         <v>63.2</v>
       </c>
+      <c r="I76" s="42" t="n">
+        <v>63.2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="42" t="inlineStr">
@@ -52622,6 +52925,9 @@
       <c r="H77" s="42" t="n">
         <v>63</v>
       </c>
+      <c r="I77" s="42" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="42" t="inlineStr">
@@ -52650,6 +52956,9 @@
       <c r="H78" s="42" t="n">
         <v>62.9</v>
       </c>
+      <c r="I78" s="42" t="n">
+        <v>62.9</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="42" t="inlineStr">
@@ -52678,6 +52987,9 @@
       <c r="H79" s="42" t="n">
         <v>62.8</v>
       </c>
+      <c r="I79" s="42" t="n">
+        <v>62.8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="42" t="inlineStr">
@@ -52706,6 +53018,9 @@
       <c r="H80" s="42" t="n">
         <v>62.7</v>
       </c>
+      <c r="I80" s="42" t="n">
+        <v>62.7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="42" t="inlineStr">
@@ -52734,6 +53049,9 @@
       <c r="H81" s="42" t="n">
         <v>62.4</v>
       </c>
+      <c r="I81" s="42" t="n">
+        <v>62.4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="42" t="inlineStr">
@@ -52762,6 +53080,9 @@
       <c r="H82" s="42" t="n">
         <v>62.1</v>
       </c>
+      <c r="I82" s="42" t="n">
+        <